--- a/data/BGN.MI.xlsx
+++ b/data/BGN.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4796009063721</t>
+    <t xml:space="preserve">17.4795989990234</t>
   </si>
   <si>
     <t xml:space="preserve">BGN.MI</t>
@@ -56,13 +56,13 @@
     <t xml:space="preserve">16.262825012207</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3678226470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5098876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9422454833984</t>
+    <t xml:space="preserve">16.3678245544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5098838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9422435760498</t>
   </si>
   <si>
     <t xml:space="preserve">16.6457710266113</t>
@@ -71,37 +71,37 @@
     <t xml:space="preserve">16.1269416809082</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6760501861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9601716995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0707521438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0769300460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5092868804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5401725769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.428991317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.601936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1942844390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4784049987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2931089401245</t>
+    <t xml:space="preserve">15.6760540008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9601755142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0707540512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0769281387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5092887878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.540168762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4289884567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6019344329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.194281578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4784030914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2931051254272</t>
   </si>
   <si>
     <t xml:space="preserve">15.0213413238525</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">13.8230895996094</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7180862426758</t>
+    <t xml:space="preserve">13.7180871963501</t>
   </si>
   <si>
     <t xml:space="preserve">13.5945587158203</t>
@@ -119,103 +119,103 @@
     <t xml:space="preserve">12.4580764770508</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6804323196411</t>
+    <t xml:space="preserve">12.6804342269897</t>
   </si>
   <si>
     <t xml:space="preserve">13.5636749267578</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1745538711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4154386520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0022115707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8477964401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3851556777954</t>
+    <t xml:space="preserve">13.1745557785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4154396057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0022134780884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8477983474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.385157585144</t>
   </si>
   <si>
     <t xml:space="preserve">14.4098615646362</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1936807632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4963321685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1813297271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3233909606934</t>
+    <t xml:space="preserve">14.1936836242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4963359832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1813325881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.323390007019</t>
   </si>
   <si>
     <t xml:space="preserve">14.3357439041138</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5210418701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8607511520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2436943054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5710525512695</t>
+    <t xml:space="preserve">14.5210390090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8607473373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2436962127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5710506439209</t>
   </si>
   <si>
     <t xml:space="preserve">15.4969339370728</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4351692199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4413433074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3239908218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0157642364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2010593414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2937088012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1578235626221</t>
+    <t xml:space="preserve">15.4351673126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4413461685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.323992729187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0157623291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.201057434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2937049865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1578216552734</t>
   </si>
   <si>
     <t xml:space="preserve">16.3431167602539</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8489952087402</t>
+    <t xml:space="preserve">15.8489971160889</t>
   </si>
   <si>
     <t xml:space="preserve">15.8922319412231</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6081104278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9354658126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9663515090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0095882415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8675241470337</t>
+    <t xml:space="preserve">15.6081085205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9354677200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9663496017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0095863342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8675260543823</t>
   </si>
   <si>
     <t xml:space="preserve">14.8298673629761</t>
@@ -224,10 +224,10 @@
     <t xml:space="preserve">14.8854541778564</t>
   </si>
   <si>
-    <t xml:space="preserve">14.656925201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9410448074341</t>
+    <t xml:space="preserve">14.6569232940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.941047668457</t>
   </si>
   <si>
     <t xml:space="preserve">15.3981094360352</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">15.5339918136597</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8737020492554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9478206634521</t>
+    <t xml:space="preserve">15.8737001419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9478187561035</t>
   </si>
   <si>
     <t xml:space="preserve">16.1145858764648</t>
@@ -248,88 +248,88 @@
     <t xml:space="preserve">16.083703994751</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0713539123535</t>
+    <t xml:space="preserve">16.0713520050049</t>
   </si>
   <si>
     <t xml:space="preserve">16.1084098815918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2072353363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0590000152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2998828887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1701774597168</t>
+    <t xml:space="preserve">16.2072334289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0589981079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2998867034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1701755523682</t>
   </si>
   <si>
     <t xml:space="preserve">16.1207637786865</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7316408157349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3795804977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1201648712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8916330337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7063369750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6383943557739</t>
+    <t xml:space="preserve">15.7316436767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3795766830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1201629638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8916349411011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7063388824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6383962631226</t>
   </si>
   <si>
     <t xml:space="preserve">14.6075096130371</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2986841201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4530973434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6692781448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3419189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3666248321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3913326263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3975086212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5537910461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8142604827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9640321731567</t>
+    <t xml:space="preserve">14.2986831665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4530982971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6692762374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3419218063354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.366626739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3913335800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3975095748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5537919998169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8142623901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9640340805054</t>
   </si>
   <si>
     <t xml:space="preserve">15.5110206604004</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5956754684448</t>
+    <t xml:space="preserve">15.5956716537476</t>
   </si>
   <si>
     <t xml:space="preserve">15.3742733001709</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3286914825439</t>
+    <t xml:space="preserve">15.3286933898926</t>
   </si>
   <si>
     <t xml:space="preserve">15.1138029098511</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">15.0096139907837</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0551996231079</t>
+    <t xml:space="preserve">15.055196762085</t>
   </si>
   <si>
     <t xml:space="preserve">15.211480140686</t>
@@ -356,13 +356,13 @@
     <t xml:space="preserve">14.8533315658569</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0979661941528</t>
+    <t xml:space="preserve">14.0979709625244</t>
   </si>
   <si>
     <t xml:space="preserve">13.2058563232422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9649209976196</t>
+    <t xml:space="preserve">12.9649229049683</t>
   </si>
   <si>
     <t xml:space="preserve">12.945384979248</t>
@@ -371,22 +371,22 @@
     <t xml:space="preserve">13.1993436813354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.661678314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8374977111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1565752029419</t>
+    <t xml:space="preserve">13.6616811752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8375005722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1565742492676</t>
   </si>
   <si>
     <t xml:space="preserve">14.5733261108398</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8737592697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.66907787323</t>
+    <t xml:space="preserve">12.8737564086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6690788269043</t>
   </si>
   <si>
     <t xml:space="preserve">11.7341985702515</t>
@@ -404,70 +404,70 @@
     <t xml:space="preserve">11.2002334594727</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8160409927368</t>
+    <t xml:space="preserve">10.8160400390625</t>
   </si>
   <si>
     <t xml:space="preserve">10.431845664978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7444095611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2588376998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9230375289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3137435913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2616491317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5286340713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5677032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6588678359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.372350692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5221195220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5416574478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3397951126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5025873184204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2551374435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4895601272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.242115020752</t>
+    <t xml:space="preserve">10.7444105148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2588405609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.923038482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3137454986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2616500854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5286331176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.567702293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6588668823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3723497390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5221214294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5416555404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3397922515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.502589225769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2551393508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4895629882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2421140670776</t>
   </si>
   <si>
     <t xml:space="preserve">12.0337390899658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8188514709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6300096511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4281444549561</t>
+    <t xml:space="preserve">11.8188505172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6300106048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4281435012817</t>
   </si>
   <si>
     <t xml:space="preserve">11.3825626373291</t>
@@ -476,25 +476,25 @@
     <t xml:space="preserve">11.8579206466675</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9946699142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1835098266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2030439376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0532732009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.94908618927</t>
+    <t xml:space="preserve">11.9946689605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1835117340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2030448913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0532741546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9490871429443</t>
   </si>
   <si>
     <t xml:space="preserve">11.7928037643433</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5258226394653</t>
+    <t xml:space="preserve">11.525821685791</t>
   </si>
   <si>
     <t xml:space="preserve">11.7667570114136</t>
@@ -503,43 +503,43 @@
     <t xml:space="preserve">11.4411678314209</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3630266189575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5583820343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7797803878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5388431549072</t>
+    <t xml:space="preserve">11.3630256652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5583810806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7797822952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5388441085815</t>
   </si>
   <si>
     <t xml:space="preserve">11.7472238540649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6951274871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9425754547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1314144134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1379251480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4114236831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4830493927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6653804779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8021287918091</t>
+    <t xml:space="preserve">11.695125579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9425745010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1314163208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1379261016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4114217758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4830503463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.665379524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8021268844604</t>
   </si>
   <si>
     <t xml:space="preserve">12.3788633346558</t>
@@ -548,34 +548,34 @@
     <t xml:space="preserve">12.1183929443359</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1249046325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2876996994019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8709449768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7016382217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.851411819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9165258407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2523279190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1937208175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.148138999939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0830211639404</t>
+    <t xml:space="preserve">12.124903678894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2876987457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.870945930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7016372680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8514108657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9165287017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.252329826355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1937198638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1481399536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0830221176147</t>
   </si>
   <si>
     <t xml:space="preserve">11.1220932006836</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">11.1741857528687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1090679168701</t>
+    <t xml:space="preserve">11.1090688705444</t>
   </si>
   <si>
     <t xml:space="preserve">11.2848863601685</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">11.0765113830566</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1872081756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0244150161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0179033279419</t>
+    <t xml:space="preserve">11.1872110366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0244169235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0179042816162</t>
   </si>
   <si>
     <t xml:space="preserve">11.6430339813232</t>
@@ -620,43 +620,43 @@
     <t xml:space="preserve">12.29421043396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4309558868408</t>
+    <t xml:space="preserve">12.4309549331665</t>
   </si>
   <si>
     <t xml:space="preserve">12.9779453277588</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0365505218506</t>
+    <t xml:space="preserve">13.036548614502</t>
   </si>
   <si>
     <t xml:space="preserve">13.3816738128662</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5640048980713</t>
+    <t xml:space="preserve">13.564003944397</t>
   </si>
   <si>
     <t xml:space="preserve">13.414234161377</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1732969284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0560846328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9258499145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8281736373901</t>
+    <t xml:space="preserve">13.1732978820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0560855865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9258527755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8281745910645</t>
   </si>
   <si>
     <t xml:space="preserve">13.3295783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7984275817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5444688796997</t>
+    <t xml:space="preserve">13.7984266281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5444669723511</t>
   </si>
   <si>
     <t xml:space="preserve">13.8830804824829</t>
@@ -665,52 +665,52 @@
     <t xml:space="preserve">13.8309841156006</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9481973648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8895921707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1240158081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4923725128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9388761520386</t>
+    <t xml:space="preserve">13.9481983184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.889594078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1240167617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4923734664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9388751983643</t>
   </si>
   <si>
     <t xml:space="preserve">12.9323625564575</t>
   </si>
   <si>
-    <t xml:space="preserve">12.867244720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9714336395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9909677505493</t>
+    <t xml:space="preserve">12.8672466278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9714326858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9909706115723</t>
   </si>
   <si>
     <t xml:space="preserve">12.7760820388794</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7956132888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7304964065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7435207366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4691400527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2896203994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8887014389038</t>
+    <t xml:space="preserve">12.795615196228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7304973602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.743522644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4691362380981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2896184921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8887033462524</t>
   </si>
   <si>
     <t xml:space="preserve">15.5761394500732</t>
@@ -719,13 +719,13 @@
     <t xml:space="preserve">15.361252784729</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4784622192383</t>
+    <t xml:space="preserve">15.4784641265869</t>
   </si>
   <si>
     <t xml:space="preserve">15.0747318267822</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1854362487793</t>
+    <t xml:space="preserve">15.1854295730591</t>
   </si>
   <si>
     <t xml:space="preserve">14.8989133834839</t>
@@ -737,16 +737,16 @@
     <t xml:space="preserve">14.9575204849243</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9770565032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0031042098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7817029953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5863485336304</t>
+    <t xml:space="preserve">14.9770574569702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0031003952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7817058563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5863513946533</t>
   </si>
   <si>
     <t xml:space="preserve">14.7556562423706</t>
@@ -758,46 +758,46 @@
     <t xml:space="preserve">15.3417139053345</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4459066390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8403091430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2700843811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5305576324463</t>
+    <t xml:space="preserve">15.4459047317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8403100967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2700881958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5305557250977</t>
   </si>
   <si>
     <t xml:space="preserve">15.4133453369141</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3482284545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5631151199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5138282775879</t>
+    <t xml:space="preserve">15.3482265472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5631141662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5138301849365</t>
   </si>
   <si>
     <t xml:space="preserve">16.6570911407471</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5659275054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1231269836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0514984130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6803245544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7454452514648</t>
+    <t xml:space="preserve">16.5659255981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1231231689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0514965057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6803283691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7454433441162</t>
   </si>
   <si>
     <t xml:space="preserve">15.7584686279297</t>
@@ -806,31 +806,31 @@
     <t xml:space="preserve">15.0356616973877</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3352041244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2375249862671</t>
+    <t xml:space="preserve">15.3352022171021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2375268936157</t>
   </si>
   <si>
     <t xml:space="preserve">15.4328804016113</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2208023071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2924308776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1491737365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9538192749023</t>
+    <t xml:space="preserve">16.2208042144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2924346923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1491718292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9538202285767</t>
   </si>
   <si>
     <t xml:space="preserve">16.1752185821533</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8626546859741</t>
+    <t xml:space="preserve">15.8626565933228</t>
   </si>
   <si>
     <t xml:space="preserve">15.5566024780273</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">15.1593866348267</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2245025634766</t>
+    <t xml:space="preserve">15.2245044708252</t>
   </si>
   <si>
     <t xml:space="preserve">14.8468217849731</t>
@@ -848,13 +848,13 @@
     <t xml:space="preserve">15.1658973693848</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4003210067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3091583251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6021842956543</t>
+    <t xml:space="preserve">15.4003190994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3091564178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6021862030029</t>
   </si>
   <si>
     <t xml:space="preserve">15.6217203140259</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">15.5500917434692</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3677606582642</t>
+    <t xml:space="preserve">15.3677625656128</t>
   </si>
   <si>
     <t xml:space="preserve">15.3938083648682</t>
@@ -878,10 +878,10 @@
     <t xml:space="preserve">15.1072912216187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0812463760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6152076721191</t>
+    <t xml:space="preserve">15.081244468689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6152086257935</t>
   </si>
   <si>
     <t xml:space="preserve">15.6282339096069</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">15.5435800552368</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7975397109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9342842102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2012691497803</t>
+    <t xml:space="preserve">15.7975378036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9342861175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2012672424316</t>
   </si>
   <si>
     <t xml:space="preserve">16.4422035217285</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3770847320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2794094085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1426658630371</t>
+    <t xml:space="preserve">16.377082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.279411315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1426639556885</t>
   </si>
   <si>
     <t xml:space="preserve">16.481273651123</t>
@@ -920,64 +920,64 @@
     <t xml:space="preserve">16.2338275909424</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2561721801758</t>
+    <t xml:space="preserve">17.2561740875244</t>
   </si>
   <si>
     <t xml:space="preserve">17.2691974639893</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1584987640381</t>
+    <t xml:space="preserve">17.1585006713867</t>
   </si>
   <si>
     <t xml:space="preserve">17.1454734802246</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1845436096191</t>
+    <t xml:space="preserve">17.1845474243164</t>
   </si>
   <si>
     <t xml:space="preserve">17.1389636993408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.646879196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6273460388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.389217376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.167818069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1027030944824</t>
+    <t xml:space="preserve">17.6468772888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6273441314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3892230987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1678199768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1027011871338</t>
   </si>
   <si>
     <t xml:space="preserve">18.3501491546631</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1352615356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.493408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0896797180176</t>
+    <t xml:space="preserve">18.1352634429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4934062957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0896778106689</t>
   </si>
   <si>
     <t xml:space="preserve">18.2264251708984</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8588123321533</t>
+    <t xml:space="preserve">18.858814239502</t>
   </si>
   <si>
     <t xml:space="preserve">18.8723430633545</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6896438598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.642276763916</t>
+    <t xml:space="preserve">18.6896419525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6422729492188</t>
   </si>
   <si>
     <t xml:space="preserve">18.513708114624</t>
@@ -986,28 +986,28 @@
     <t xml:space="preserve">17.8370399475098</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6543350219727</t>
+    <t xml:space="preserve">17.6543388366699</t>
   </si>
   <si>
     <t xml:space="preserve">17.3836688995361</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9047031402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.931770324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5393047332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.546070098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9926719665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6761093139648</t>
+    <t xml:space="preserve">17.9047050476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9317722320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5393009185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5460681915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9926738739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6761074066162</t>
   </si>
   <si>
     <t xml:space="preserve">18.926477432251</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">18.6219749450684</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0400390625</t>
+    <t xml:space="preserve">18.0400428771973</t>
   </si>
   <si>
     <t xml:space="preserve">18.3377723693848</t>
@@ -1034,46 +1034,46 @@
     <t xml:space="preserve">17.9994411468506</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8641033172607</t>
+    <t xml:space="preserve">17.864107131958</t>
   </si>
   <si>
     <t xml:space="preserve">17.8032035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0062046051025</t>
+    <t xml:space="preserve">18.0062084197998</t>
   </si>
   <si>
     <t xml:space="preserve">18.4054412841797</t>
   </si>
   <si>
-    <t xml:space="preserve">18.060338973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6340389251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2430400848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2701053619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6490421295166</t>
+    <t xml:space="preserve">18.0603408813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6340351104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2430381774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2701072692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6490440368652</t>
   </si>
   <si>
     <t xml:space="preserve">18.4528102874756</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7031764984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4595756530762</t>
+    <t xml:space="preserve">18.7031745910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4595718383789</t>
   </si>
   <si>
     <t xml:space="preserve">19.1024112701416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9467792510986</t>
+    <t xml:space="preserve">18.94677734375</t>
   </si>
   <si>
     <t xml:space="preserve">18.9197101593018</t>
@@ -1082,10 +1082,10 @@
     <t xml:space="preserve">18.77760887146</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8791084289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1362476348877</t>
+    <t xml:space="preserve">18.8791122436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1362495422363</t>
   </si>
   <si>
     <t xml:space="preserve">19.0415115356445</t>
@@ -1094,61 +1094,61 @@
     <t xml:space="preserve">19.1836128234863</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3730792999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2918815612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8264484405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9414844512939</t>
+    <t xml:space="preserve">19.3730773925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2918796539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8264465332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9414825439453</t>
   </si>
   <si>
     <t xml:space="preserve">20.3001194000244</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5166530609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0971183776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9956150054932</t>
+    <t xml:space="preserve">20.5166549682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0971164703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9956169128418</t>
   </si>
   <si>
     <t xml:space="preserve">20.1241855621338</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1444816589355</t>
+    <t xml:space="preserve">20.1444854736328</t>
   </si>
   <si>
     <t xml:space="preserve">20.6384544372559</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2392196655273</t>
+    <t xml:space="preserve">20.2392177581787</t>
   </si>
   <si>
     <t xml:space="preserve">19.8941173553467</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5625476837158</t>
+    <t xml:space="preserve">19.5625495910645</t>
   </si>
   <si>
     <t xml:space="preserve">19.7587833404541</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9211864471436</t>
+    <t xml:space="preserve">19.9211845397949</t>
   </si>
   <si>
     <t xml:space="preserve">19.9008827209473</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7993812561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7655506134033</t>
+    <t xml:space="preserve">19.7993831634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7655467987061</t>
   </si>
   <si>
     <t xml:space="preserve">19.8129138946533</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">19.4813480377197</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5828495025635</t>
+    <t xml:space="preserve">19.5828475952148</t>
   </si>
   <si>
     <t xml:space="preserve">19.4881153106689</t>
@@ -1169,115 +1169,115 @@
     <t xml:space="preserve">18.7640743255615</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7573089599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5949096679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8452796936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8655738830566</t>
+    <t xml:space="preserve">18.7573070526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5949115753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8452758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8655776977539</t>
   </si>
   <si>
     <t xml:space="preserve">18.534008026123</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0144443511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2242126464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1700801849365</t>
+    <t xml:space="preserve">19.0144462585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2242107391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1700782775879</t>
   </si>
   <si>
     <t xml:space="preserve">19.2512798309326</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1971454620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.447509765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1633148193359</t>
+    <t xml:space="preserve">19.1971492767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4475173950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1633129119873</t>
   </si>
   <si>
     <t xml:space="preserve">19.2648143768311</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4678153991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2580451965332</t>
+    <t xml:space="preserve">19.4678134918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2580432891846</t>
   </si>
   <si>
     <t xml:space="preserve">19.8602828979492</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8670482635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0159149169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4204483032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.569314956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5490131378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4272136688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3663139343262</t>
+    <t xml:space="preserve">19.8670520782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0159187316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.420446395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5693130493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.549015045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4272117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3663120269775</t>
   </si>
   <si>
     <t xml:space="preserve">19.4136810302734</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3527793884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5016460418701</t>
+    <t xml:space="preserve">19.3527812957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5016441345215</t>
   </si>
   <si>
     <t xml:space="preserve">18.9400100708008</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8114433288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8858795166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2783470153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1565456390381</t>
+    <t xml:space="preserve">18.8114414215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8858757019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2783451080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1565437316895</t>
   </si>
   <si>
     <t xml:space="preserve">19.0685787200928</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2106781005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1091766357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3189449310303</t>
+    <t xml:space="preserve">19.2106800079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1091785430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3189487457275</t>
   </si>
   <si>
     <t xml:space="preserve">19.3324813842773</t>
   </si>
   <si>
-    <t xml:space="preserve">19.230978012085</t>
+    <t xml:space="preserve">19.2309799194336</t>
   </si>
   <si>
     <t xml:space="preserve">19.6572799682617</t>
@@ -1286,22 +1286,22 @@
     <t xml:space="preserve">20.1106510162354</t>
   </si>
   <si>
-    <t xml:space="preserve">19.982084274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7858486175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5354804992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9482498168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5760803222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6166839599609</t>
+    <t xml:space="preserve">19.9820823669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7858505249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5354824066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9482460021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5760822296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6166801452637</t>
   </si>
   <si>
     <t xml:space="preserve">19.5557804107666</t>
@@ -1310,19 +1310,19 @@
     <t xml:space="preserve">19.3460121154785</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6911144256592</t>
+    <t xml:space="preserve">19.6911163330078</t>
   </si>
   <si>
     <t xml:space="preserve">19.6775817871094</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2986450195312</t>
+    <t xml:space="preserve">19.2986469268799</t>
   </si>
   <si>
     <t xml:space="preserve">19.1903800964355</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3121814727783</t>
+    <t xml:space="preserve">19.312183380127</t>
   </si>
   <si>
     <t xml:space="preserve">18.791145324707</t>
@@ -1331,28 +1331,28 @@
     <t xml:space="preserve">18.8182106018066</t>
   </si>
   <si>
-    <t xml:space="preserve">18.967077255249</t>
+    <t xml:space="preserve">18.9670791625977</t>
   </si>
   <si>
     <t xml:space="preserve">18.7708435058594</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4663391113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.188907623291</t>
+    <t xml:space="preserve">18.4663429260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1889057159424</t>
   </si>
   <si>
     <t xml:space="preserve">18.6084423065186</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1497802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1768474578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4745807647705</t>
+    <t xml:space="preserve">19.1497764587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1768493652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4745826721191</t>
   </si>
   <si>
     <t xml:space="preserve">20.0294494628906</t>
@@ -1370,22 +1370,22 @@
     <t xml:space="preserve">20.8008575439453</t>
   </si>
   <si>
-    <t xml:space="preserve">20.76025390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.719654083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8685207366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7061233520508</t>
+    <t xml:space="preserve">20.7602558135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7196559906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8685245513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7061195373535</t>
   </si>
   <si>
     <t xml:space="preserve">20.2459850311279</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4083843231201</t>
+    <t xml:space="preserve">20.4083881378174</t>
   </si>
   <si>
     <t xml:space="preserve">20.3136520385742</t>
@@ -1394,22 +1394,22 @@
     <t xml:space="preserve">19.8805847167969</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8926429748535</t>
+    <t xml:space="preserve">18.8926448822021</t>
   </si>
   <si>
     <t xml:space="preserve">19.0550441741943</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0265064239502</t>
+    <t xml:space="preserve">18.0265045166016</t>
   </si>
   <si>
     <t xml:space="preserve">18.2024402618408</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2565727233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5813770294189</t>
+    <t xml:space="preserve">18.2565765380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5813751220703</t>
   </si>
   <si>
     <t xml:space="preserve">18.5407752990723</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">18.4189739227295</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5272388458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4731025695801</t>
+    <t xml:space="preserve">18.5272426605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.473108291626</t>
   </si>
   <si>
     <t xml:space="preserve">17.9859046936035</t>
@@ -1442,22 +1442,22 @@
     <t xml:space="preserve">18.7437782287598</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7302417755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3783740997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8505725860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7558326721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7287712097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9723739624023</t>
+    <t xml:space="preserve">18.7302436828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3783760070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8505687713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7558364868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7287731170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9723720550537</t>
   </si>
   <si>
     <t xml:space="preserve">18.0671062469482</t>
@@ -1466,79 +1466,79 @@
     <t xml:space="preserve">18.1483058929443</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2159767150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3242378234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3513050079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3648414611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7167091369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7979106903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.906177520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1618385314941</t>
+    <t xml:space="preserve">18.2159748077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.324239730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3513088226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.364839553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7167110443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.797908782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9061756134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1618366241455</t>
   </si>
   <si>
     <t xml:space="preserve">18.1212406158447</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8235054016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6205043792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6611042022705</t>
+    <t xml:space="preserve">17.82350730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6205024719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6611061096191</t>
   </si>
   <si>
     <t xml:space="preserve">17.1738986968994</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0521011352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7814311981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7600536346436</t>
+    <t xml:space="preserve">17.0520992279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7814331054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7600517272949</t>
   </si>
   <si>
     <t xml:space="preserve">16.8028087615967</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5605297088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7030467987061</t>
+    <t xml:space="preserve">16.5605316162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7030448913574</t>
   </si>
   <si>
     <t xml:space="preserve">16.3039970397949</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2066144943237</t>
+    <t xml:space="preserve">15.2066116333008</t>
   </si>
   <si>
     <t xml:space="preserve">14.2802515029907</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8503217697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8218193054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5344018936157</t>
+    <t xml:space="preserve">14.8503198623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8218173980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5344038009644</t>
   </si>
   <si>
     <t xml:space="preserve">15.3206262588501</t>
@@ -1547,10 +1547,10 @@
     <t xml:space="preserve">14.8930759429932</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4631471633911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8336915969849</t>
+    <t xml:space="preserve">15.4631452560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8336906433105</t>
   </si>
   <si>
     <t xml:space="preserve">15.3491315841675</t>
@@ -1559,10 +1559,10 @@
     <t xml:space="preserve">15.9477043151855</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8479433059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8621959686279</t>
+    <t xml:space="preserve">15.8479413986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8621940612793</t>
   </si>
   <si>
     <t xml:space="preserve">15.9192008972168</t>
@@ -1571,64 +1571,64 @@
     <t xml:space="preserve">15.7054252624512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7339286804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7196769714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3633823394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5059013366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4203901290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4488935470581</t>
+    <t xml:space="preserve">15.7339305877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7196750640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3633813858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5058994293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.420389175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4488916397095</t>
   </si>
   <si>
     <t xml:space="preserve">14.9500818252563</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9358282089233</t>
+    <t xml:space="preserve">14.9358320236206</t>
   </si>
   <si>
     <t xml:space="preserve">15.178108215332</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5629062652588</t>
+    <t xml:space="preserve">15.5629053115845</t>
   </si>
   <si>
     <t xml:space="preserve">15.6484174728394</t>
   </si>
   <si>
-    <t xml:space="preserve">15.890697479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0189647674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4346437454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3776321411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4916515350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.52015209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7909355163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7766847610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6056613922119</t>
+    <t xml:space="preserve">15.8906955718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0189666748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4346408843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3776340484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4916477203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5201511383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7909374237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7766828536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6056623458862</t>
   </si>
   <si>
     <t xml:space="preserve">16.4750194549561</t>
@@ -1640,19 +1640,19 @@
     <t xml:space="preserve">16.1329765319824</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4465179443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5035247802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9619550704956</t>
+    <t xml:space="preserve">16.4465160369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5035228729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9619569778442</t>
   </si>
   <si>
     <t xml:space="preserve">16.0474662780762</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2184886932373</t>
+    <t xml:space="preserve">16.2184867858887</t>
   </si>
   <si>
     <t xml:space="preserve">16.2042369842529</t>
@@ -1664,10 +1664,10 @@
     <t xml:space="preserve">15.74817943573</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9049501419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2754955291748</t>
+    <t xml:space="preserve">15.9049482345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2754936218262</t>
   </si>
   <si>
     <t xml:space="preserve">16.4037609100342</t>
@@ -1676,10 +1676,10 @@
     <t xml:space="preserve">16.3325004577637</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2636213302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0783462524414</t>
+    <t xml:space="preserve">15.2636194229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0783500671387</t>
   </si>
   <si>
     <t xml:space="preserve">15.30637550354</t>
@@ -1688,25 +1688,25 @@
     <t xml:space="preserve">15.2921237945557</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5486536026001</t>
+    <t xml:space="preserve">15.5486574172974</t>
   </si>
   <si>
     <t xml:space="preserve">15.6769208908081</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6175384521484</t>
+    <t xml:space="preserve">16.6175346374512</t>
   </si>
   <si>
     <t xml:space="preserve">16.7885589599609</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8598175048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3443737030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3871307373047</t>
+    <t xml:space="preserve">16.8598155975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3443756103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3871288299561</t>
   </si>
   <si>
     <t xml:space="preserve">17.1020965576172</t>
@@ -1715,52 +1715,52 @@
     <t xml:space="preserve">15.8764486312866</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6911716461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6626691818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.964334487915</t>
+    <t xml:space="preserve">15.6911735534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6626710891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9643306732178</t>
   </si>
   <si>
     <t xml:space="preserve">14.7933130264282</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3515071868896</t>
+    <t xml:space="preserve">14.3515110015869</t>
   </si>
   <si>
     <t xml:space="preserve">14.2161159515381</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3372573852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7220544815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4227666854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0593490600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5391597747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2042436599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7268095016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3776416778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4203977584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.285005569458</t>
+    <t xml:space="preserve">14.3372583389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7220525741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4227676391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0593461990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.539158821106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2042446136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7268104553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3776407241821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4203968048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2850036621094</t>
   </si>
   <si>
     <t xml:space="preserve">12.4061460494995</t>
@@ -1769,28 +1769,28 @@
     <t xml:space="preserve">12.1353626251221</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3705167770386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9049558639526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8622016906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.93346118927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1472368240356</t>
+    <t xml:space="preserve">12.3705177307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9049577713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8622007369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9334602355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.147234916687</t>
   </si>
   <si>
     <t xml:space="preserve">13.275502204895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1187334060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0688524246216</t>
+    <t xml:space="preserve">13.1187314987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0688514709473</t>
   </si>
   <si>
     <t xml:space="preserve">13.5462856292725</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">12.7838172912598</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7339372634888</t>
+    <t xml:space="preserve">12.7339363098145</t>
   </si>
   <si>
     <t xml:space="preserve">12.6698036193848</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">12.9548387527466</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2469987869263</t>
+    <t xml:space="preserve">13.2469997406006</t>
   </si>
   <si>
     <t xml:space="preserve">13.5961675643921</t>
@@ -1823,13 +1823,13 @@
     <t xml:space="preserve">14.1092290878296</t>
   </si>
   <si>
-    <t xml:space="preserve">13.945333480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8812036514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8883285522461</t>
+    <t xml:space="preserve">13.9453325271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8812017440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8883275985718</t>
   </si>
   <si>
     <t xml:space="preserve">14.465521812439</t>
@@ -1838,115 +1838,115 @@
     <t xml:space="preserve">14.2232437133789</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0878534317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3681392669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4679002761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1258583068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9690923690796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.489278793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6317958831787</t>
+    <t xml:space="preserve">14.0878524780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3681383132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4678993225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1258573532104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.969090461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4892797470093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6317939758301</t>
   </si>
   <si>
     <t xml:space="preserve">13.2327480316162</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3966426849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8265724182129</t>
+    <t xml:space="preserve">13.3966417312622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8265714645386</t>
   </si>
   <si>
     <t xml:space="preserve">12.5344095230103</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1044797897339</t>
+    <t xml:space="preserve">13.1044816970825</t>
   </si>
   <si>
     <t xml:space="preserve">12.9975938796997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6104192733765</t>
+    <t xml:space="preserve">13.6104183197021</t>
   </si>
   <si>
     <t xml:space="preserve">13.7529354095459</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6389226913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1448583602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3230047225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.201865196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947402954102</t>
+    <t xml:space="preserve">13.6389198303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1448602676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3230056762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2018642425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947393417358</t>
   </si>
   <si>
     <t xml:space="preserve">13.895453453064</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3942680358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.593789100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7078018188477</t>
+    <t xml:space="preserve">14.39426612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5937881469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.707802772522</t>
   </si>
   <si>
     <t xml:space="preserve">14.5082778930664</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6935520172119</t>
+    <t xml:space="preserve">14.6935510635376</t>
   </si>
   <si>
     <t xml:space="preserve">14.8075656890869</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6365442276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7648067474365</t>
+    <t xml:space="preserve">14.6365461349487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7648105621338</t>
   </si>
   <si>
     <t xml:space="preserve">14.7363061904907</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6792984008789</t>
+    <t xml:space="preserve">14.6793022155762</t>
   </si>
   <si>
     <t xml:space="preserve">14.265998840332</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5367832183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2945022583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5510320663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.192361831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.978588104248</t>
+    <t xml:space="preserve">14.5367841720581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2945041656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5510330200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1923599243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9785842895508</t>
   </si>
   <si>
     <t xml:space="preserve">15.277871131897</t>
@@ -1961,16 +1961,16 @@
     <t xml:space="preserve">15.4061403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8194408416748</t>
+    <t xml:space="preserve">15.8194370269775</t>
   </si>
   <si>
     <t xml:space="preserve">15.8051862716675</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6341676712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5914115905762</t>
+    <t xml:space="preserve">15.6341667175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5914077758789</t>
   </si>
   <si>
     <t xml:space="preserve">16.4322643280029</t>
@@ -1979,79 +1979,79 @@
     <t xml:space="preserve">16.6032848358154</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7173004150391</t>
+    <t xml:space="preserve">16.7172966003418</t>
   </si>
   <si>
     <t xml:space="preserve">16.7743053436279</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8170604705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0308399200439</t>
+    <t xml:space="preserve">16.8170623779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0308380126953</t>
   </si>
   <si>
     <t xml:space="preserve">17.1591014862061</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2588634490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3158721923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4583892822266</t>
+    <t xml:space="preserve">17.2588653564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3158702850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4583911895752</t>
   </si>
   <si>
     <t xml:space="preserve">17.4726409912109</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9714527130127</t>
+    <t xml:space="preserve">17.9714546203613</t>
   </si>
   <si>
     <t xml:space="preserve">17.7861766815186</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9286994934082</t>
+    <t xml:space="preserve">17.9286956787109</t>
   </si>
   <si>
     <t xml:space="preserve">18.0569648742676</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0854644775391</t>
+    <t xml:space="preserve">18.0854663848877</t>
   </si>
   <si>
     <t xml:space="preserve">17.5581493377686</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5866546630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2018547058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4298839569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5296497344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4868965148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7196502685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8547992706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2991847991943</t>
+    <t xml:space="preserve">17.5866565704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2018585205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4298877716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5296478271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4868946075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7196521759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8548011779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.299186706543</t>
   </si>
   <si>
     <t xml:space="preserve">17.2241039276123</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2691516876221</t>
+    <t xml:space="preserve">17.2691497802734</t>
   </si>
   <si>
     <t xml:space="preserve">17.149019241333</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">16.7435684204102</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8787174224854</t>
+    <t xml:space="preserve">16.878719329834</t>
   </si>
   <si>
     <t xml:space="preserve">16.9237689971924</t>
@@ -2069,19 +2069,19 @@
     <t xml:space="preserve">16.6985187530518</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2541332244873</t>
+    <t xml:space="preserve">17.2541351318359</t>
   </si>
   <si>
     <t xml:space="preserve">17.5394515991211</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1640357971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0589160919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4343338012695</t>
+    <t xml:space="preserve">17.1640338897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0589179992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4343318939209</t>
   </si>
   <si>
     <t xml:space="preserve">17.8247699737549</t>
@@ -2090,91 +2090,91 @@
     <t xml:space="preserve">17.9298839569092</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8397846221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7496814727783</t>
+    <t xml:space="preserve">17.8397827148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.749683380127</t>
   </si>
   <si>
     <t xml:space="preserve">17.9449024200439</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6657028198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8459014892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1762657165527</t>
+    <t xml:space="preserve">18.665699005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8458995819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.17626953125</t>
   </si>
   <si>
     <t xml:space="preserve">19.3714809417725</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0561332702637</t>
+    <t xml:space="preserve">19.0561351776123</t>
   </si>
   <si>
     <t xml:space="preserve">19.131217956543</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4165363311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1462345123291</t>
+    <t xml:space="preserve">19.4165325164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1462326049805</t>
   </si>
   <si>
     <t xml:space="preserve">19.0110855102539</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2213191986084</t>
+    <t xml:space="preserve">19.2213172912598</t>
   </si>
   <si>
     <t xml:space="preserve">19.7318820953369</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7769336700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7919483184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8069648742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0772686004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9721488952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2574672698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1373310089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1823844909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.897066116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.047233581543</t>
+    <t xml:space="preserve">19.7769355773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7919502258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8069629669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0772647857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9721508026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2574653625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1373329162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1823825836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8970680236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0472316741943</t>
   </si>
   <si>
     <t xml:space="preserve">20.1523494720459</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0172004699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6568012237549</t>
+    <t xml:space="preserve">20.017204284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6567993164062</t>
   </si>
   <si>
     <t xml:space="preserve">19.821985244751</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6868343353271</t>
+    <t xml:space="preserve">19.6868324279785</t>
   </si>
   <si>
     <t xml:space="preserve">19.8369998931885</t>
@@ -2183,22 +2183,22 @@
     <t xml:space="preserve">19.9421157836914</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3325481414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.581714630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4916152954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6718139648438</t>
+    <t xml:space="preserve">20.3325462341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5817165374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4916133880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6718158721924</t>
   </si>
   <si>
     <t xml:space="preserve">19.7168674468994</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7619171142578</t>
+    <t xml:space="preserve">19.7619152069092</t>
   </si>
   <si>
     <t xml:space="preserve">20.2875003814697</t>
@@ -2207,58 +2207,58 @@
     <t xml:space="preserve">19.9120845794678</t>
   </si>
   <si>
-    <t xml:space="preserve">20.122314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0622501373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3025169372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5728149414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6629161834717</t>
+    <t xml:space="preserve">20.1223163604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0622482299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3025150299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5728130340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6629180908203</t>
   </si>
   <si>
     <t xml:space="preserve">20.993278503418</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1434497833252</t>
+    <t xml:space="preserve">21.1434459686279</t>
   </si>
   <si>
     <t xml:space="preserve">21.1584663391113</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3536815643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0083026885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2635841369629</t>
+    <t xml:space="preserve">21.3536834716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0082988739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2635822296143</t>
   </si>
   <si>
     <t xml:space="preserve">21.2936134338379</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4287662506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6089649200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5338840484619</t>
+    <t xml:space="preserve">21.4287643432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6089668273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5338821411133</t>
   </si>
   <si>
     <t xml:space="preserve">20.9782657623291</t>
   </si>
   <si>
-    <t xml:space="preserve">20.888162612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2335510253906</t>
+    <t xml:space="preserve">20.8881645202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.233549118042</t>
   </si>
   <si>
     <t xml:space="preserve">21.2485637664795</t>
@@ -2267,73 +2267,73 @@
     <t xml:space="preserve">21.1734828948975</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6478977203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6328792572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7680320739746</t>
+    <t xml:space="preserve">20.6478958129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6328811645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7680339813232</t>
   </si>
   <si>
     <t xml:space="preserve">21.083381652832</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7980651855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8670310974121</t>
+    <t xml:space="preserve">20.7980632781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8670330047607</t>
   </si>
   <si>
     <t xml:space="preserve">20.7229824066162</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2035121917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3086318969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4888305664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5639152526855</t>
+    <t xml:space="preserve">21.2035160064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.308629989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4888324737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5639133453369</t>
   </si>
   <si>
     <t xml:space="preserve">21.1134147644043</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3837146759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3236484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5789279937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8191947937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8492298126221</t>
+    <t xml:space="preserve">21.3837127685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3236465454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5789318084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8191986083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8492317199707</t>
   </si>
   <si>
     <t xml:space="preserve">21.954345703125</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5850448608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4799289703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6601295471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1256465911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3208637237549</t>
+    <t xml:space="preserve">22.5850486755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4799327850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6601314544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1256446838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3208618164062</t>
   </si>
   <si>
     <t xml:space="preserve">23.0805969238281</t>
@@ -2342,19 +2342,19 @@
     <t xml:space="preserve">23.2007274627686</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3058471679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4259777069092</t>
+    <t xml:space="preserve">23.3058490753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4259815216064</t>
   </si>
   <si>
     <t xml:space="preserve">23.6962776184082</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9215297698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7263126373291</t>
+    <t xml:space="preserve">23.9215316772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7263145446777</t>
   </si>
   <si>
     <t xml:space="preserve">23.6662464141846</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">23.90651512146</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2908267974854</t>
+    <t xml:space="preserve">23.2908306121826</t>
   </si>
   <si>
     <t xml:space="preserve">23.3959465026855</t>
@@ -2372,16 +2372,16 @@
     <t xml:space="preserve">23.2758121490479</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0956115722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4949474334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6300964355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5249805450439</t>
+    <t xml:space="preserve">23.0956134796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4949493408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6300945281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5249786376953</t>
   </si>
   <si>
     <t xml:space="preserve">23.0355472564697</t>
@@ -2396,94 +2396,94 @@
     <t xml:space="preserve">22.6000652313232</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6451110839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7352123260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2096328735352</t>
+    <t xml:space="preserve">22.645112991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7352161407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2096309661865</t>
   </si>
   <si>
     <t xml:space="preserve">22.1946144104004</t>
   </si>
   <si>
-    <t xml:space="preserve">22.104513168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1795978546143</t>
+    <t xml:space="preserve">22.1045150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1795997619629</t>
   </si>
   <si>
     <t xml:space="preserve">21.7290992736816</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0594654083252</t>
+    <t xml:space="preserve">22.0594615936279</t>
   </si>
   <si>
     <t xml:space="preserve">21.7441139221191</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5939483642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2785949707031</t>
+    <t xml:space="preserve">21.5939464569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2785968780518</t>
   </si>
   <si>
     <t xml:space="preserve">22.0294322967529</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7652454376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7051811218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9904956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9754829406738</t>
+    <t xml:space="preserve">22.7652473449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7051773071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9904975891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9754810333252</t>
   </si>
   <si>
     <t xml:space="preserve">22.8102970123291</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8253154754639</t>
+    <t xml:space="preserve">22.8253135681152</t>
   </si>
   <si>
     <t xml:space="preserve">22.0744819641113</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8853797912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1645812988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2997303009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8553504943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7952785491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3508968353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1017284393311</t>
+    <t xml:space="preserve">22.8853816986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1645793914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.299732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8553466796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7952823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3508949279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1017303466797</t>
   </si>
   <si>
     <t xml:space="preserve">24.4471130371094</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4170780181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.67236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6573448181152</t>
+    <t xml:space="preserve">24.4170799255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6723613739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6573429107666</t>
   </si>
   <si>
     <t xml:space="preserve">24.7774772644043</t>
@@ -2492,10 +2492,10 @@
     <t xml:space="preserve">24.3269805908203</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8764801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2396621704102</t>
+    <t xml:space="preserve">23.8764820098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2396640777588</t>
   </si>
   <si>
     <t xml:space="preserve">20.9181976318359</t>
@@ -2504,91 +2504,91 @@
     <t xml:space="preserve">20.4226474761963</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4827175140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0411148071289</t>
+    <t xml:space="preserve">20.4827156066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0411167144775</t>
   </si>
   <si>
     <t xml:space="preserve">18.5906181335449</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9688205718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8876190185547</t>
+    <t xml:space="preserve">16.9688186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8876209259033</t>
   </si>
   <si>
     <t xml:space="preserve">15.7975206375122</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6201066970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6937952041626</t>
+    <t xml:space="preserve">13.6201038360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6937942504883</t>
   </si>
   <si>
     <t xml:space="preserve">13.2146558761597</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9894027709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6590375900269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0344552993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7266149520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8917970657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.905421257019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0180463790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.581169128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0781126022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.355920791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1982460021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3183784484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0555858612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7688798904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.46715259552</t>
+    <t xml:space="preserve">12.9894037246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6590394973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0344562530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7266139984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8917961120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9054231643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.018045425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5811710357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0781116485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3559226989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1982450485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3183765411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0555868148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7688779830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4671564102173</t>
   </si>
   <si>
     <t xml:space="preserve">16.7886180877686</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7074193954468</t>
+    <t xml:space="preserve">15.7074184417725</t>
   </si>
   <si>
     <t xml:space="preserve">15.9026355743408</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9326696395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.767484664917</t>
+    <t xml:space="preserve">15.9326677322388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7674837112427</t>
   </si>
   <si>
     <t xml:space="preserve">15.1518039703369</t>
@@ -2609,22 +2609,22 @@
     <t xml:space="preserve">17.3442363739014</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0138702392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.533332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5033016204834</t>
+    <t xml:space="preserve">17.0138683319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5333347320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.503303527832</t>
   </si>
   <si>
     <t xml:space="preserve">16.9087505340576</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4643688201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1039695739746</t>
+    <t xml:space="preserve">17.4643669128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.103967666626</t>
   </si>
   <si>
     <t xml:space="preserve">17.5244369506836</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">17.1189842224121</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2391166687012</t>
+    <t xml:space="preserve">17.2391147613525</t>
   </si>
   <si>
     <t xml:space="preserve">17.1340007781982</t>
@@ -2642,13 +2642,13 @@
     <t xml:space="preserve">17.3892860412598</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4043045043945</t>
+    <t xml:space="preserve">17.4043006896973</t>
   </si>
   <si>
     <t xml:space="preserve">17.6896190643311</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3653659820557</t>
+    <t xml:space="preserve">18.3653678894043</t>
   </si>
   <si>
     <t xml:space="preserve">18.2902851104736</t>
@@ -2657,25 +2657,25 @@
     <t xml:space="preserve">18.485502243042</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9510173797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2813835144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.852014541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3414497375488</t>
+    <t xml:space="preserve">18.9510192871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2813854217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8520164489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3414535522461</t>
   </si>
   <si>
     <t xml:space="preserve">19.5516834259033</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3954010009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.431547164917</t>
+    <t xml:space="preserve">18.3954029083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4315490722656</t>
   </si>
   <si>
     <t xml:space="preserve">20.167366027832</t>
@@ -2684,55 +2684,55 @@
     <t xml:space="preserve">19.3264331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9571304321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1073017120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6779327392578</t>
+    <t xml:space="preserve">19.9571323394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1072998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6779308319092</t>
   </si>
   <si>
     <t xml:space="preserve">19.2663650512695</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5066318511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8820476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0922794342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3475646972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3775997161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5967311859131</t>
+    <t xml:space="preserve">19.5066337585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8820495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0922832489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3475666046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3775959014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.596736907959</t>
   </si>
   <si>
     <t xml:space="preserve">18.7107524871826</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9209861755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7708168029785</t>
+    <t xml:space="preserve">18.9209823608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7708206176758</t>
   </si>
   <si>
     <t xml:space="preserve">18.8308849334717</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5666980743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0861663818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9059638977051</t>
+    <t xml:space="preserve">19.5666961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0861644744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9059677124023</t>
   </si>
   <si>
     <t xml:space="preserve">19.0711517333984</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">19.4766006469727</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2963981628418</t>
+    <t xml:space="preserve">19.2964000701904</t>
   </si>
   <si>
     <t xml:space="preserve">19.5366687774658</t>
@@ -2756,19 +2756,19 @@
     <t xml:space="preserve">19.3114147186279</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9810485839844</t>
+    <t xml:space="preserve">18.981050491333</t>
   </si>
   <si>
     <t xml:space="preserve">20.4526805877686</t>
   </si>
   <si>
-    <t xml:space="preserve">20.617862701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6117515563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3625812530518</t>
+    <t xml:space="preserve">20.6178607940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6117496490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3625831604004</t>
   </si>
   <si>
     <t xml:space="preserve">19.6417846679688</t>
@@ -2783,52 +2783,52 @@
     <t xml:space="preserve">20.2424468994141</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7379989624023</t>
+    <t xml:space="preserve">20.7379970550537</t>
   </si>
   <si>
     <t xml:space="preserve">20.0021820068359</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2152004241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.140115737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3203163146973</t>
+    <t xml:space="preserve">18.215202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1401176452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3203144073486</t>
   </si>
   <si>
     <t xml:space="preserve">20.5577964782715</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4376640319824</t>
+    <t xml:space="preserve">20.4376659393311</t>
   </si>
   <si>
     <t xml:space="preserve">21.1284313201904</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7830467224121</t>
+    <t xml:space="preserve">20.7830505371094</t>
   </si>
   <si>
     <t xml:space="preserve">20.497730255127</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0233154296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.413745880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3687000274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9031829833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.038330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4076328277588</t>
+    <t xml:space="preserve">21.0233135223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4137477874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3686962127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9031810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0383319854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4076309204102</t>
   </si>
   <si>
     <t xml:space="preserve">20.5427837371826</t>
@@ -2837,10 +2837,10 @@
     <t xml:space="preserve">20.317533493042</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2124176025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4465656280518</t>
+    <t xml:space="preserve">20.2124156951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.446569442749</t>
   </si>
   <si>
     <t xml:space="preserve">19.746898651123</t>
@@ -2849,31 +2849,31 @@
     <t xml:space="preserve">19.2363338470459</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5277652740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7140808105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.684045791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6389980316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3386650085449</t>
+    <t xml:space="preserve">20.5277633666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7140789031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6840476989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6389961242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3386669158936</t>
   </si>
   <si>
     <t xml:space="preserve">21.6239814758301</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8642482757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3987293243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4437828063965</t>
+    <t xml:space="preserve">21.8642463684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3987312316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4437808990479</t>
   </si>
   <si>
     <t xml:space="preserve">21.1884956359863</t>
@@ -2882,25 +2882,25 @@
     <t xml:space="preserve">21.9092998504639</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8942794799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8342132568359</t>
+    <t xml:space="preserve">21.8942813873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8342151641846</t>
   </si>
   <si>
     <t xml:space="preserve">21.503849029541</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2546787261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0444450378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2847156524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3447780609131</t>
+    <t xml:space="preserve">22.2546806335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0444469451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2847118377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3447818756104</t>
   </si>
   <si>
     <t xml:space="preserve">22.4649124145508</t>
@@ -2918,37 +2918,37 @@
     <t xml:space="preserve">22.5700302124023</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6751480102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5775394439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9079055786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0430526733398</t>
+    <t xml:space="preserve">22.6751499176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5775356292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9079036712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0430545806885</t>
   </si>
   <si>
     <t xml:space="preserve">23.0881042480469</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8178062438965</t>
+    <t xml:space="preserve">22.8178043365479</t>
   </si>
   <si>
     <t xml:space="preserve">22.8403301239014</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1706962585449</t>
+    <t xml:space="preserve">23.1706981658936</t>
   </si>
   <si>
     <t xml:space="preserve">23.215747833252</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3809299468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.523588180542</t>
+    <t xml:space="preserve">23.3809280395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5235862731934</t>
   </si>
   <si>
     <t xml:space="preserve">23.0505638122559</t>
@@ -2957,43 +2957,43 @@
     <t xml:space="preserve">22.9154148101807</t>
   </si>
   <si>
-    <t xml:space="preserve">23.073091506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.253288269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3433856964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.29833984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8914947509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2594089508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0942192077637</t>
+    <t xml:space="preserve">23.0730876922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2532863616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3433876037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2983379364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8914928436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2594051361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0942211151123</t>
   </si>
   <si>
     <t xml:space="preserve">24.6648540496826</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5522289276123</t>
+    <t xml:space="preserve">24.5522308349609</t>
   </si>
   <si>
     <t xml:space="preserve">24.4621295928955</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7924938201904</t>
+    <t xml:space="preserve">24.7924957275391</t>
   </si>
   <si>
     <t xml:space="preserve">24.402063369751</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0491714477539</t>
+    <t xml:space="preserve">24.0491695404053</t>
   </si>
   <si>
     <t xml:space="preserve">24.4696388244629</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">24.4245853424072</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1993350982666</t>
+    <t xml:space="preserve">24.1993370056152</t>
   </si>
   <si>
     <t xml:space="preserve">23.9590702056885</t>
@@ -3011,22 +3011,22 @@
     <t xml:space="preserve">24.1617965698242</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2293701171875</t>
+    <t xml:space="preserve">24.2293682098389</t>
   </si>
   <si>
     <t xml:space="preserve">24.627311706543</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8075122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8150215148926</t>
+    <t xml:space="preserve">24.8075103759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8150196075439</t>
   </si>
   <si>
     <t xml:space="preserve">25.1078414916992</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2204685211182</t>
+    <t xml:space="preserve">25.2204723358154</t>
   </si>
   <si>
     <t xml:space="preserve">25.1003360748291</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">25.1829299926758</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2955493927002</t>
+    <t xml:space="preserve">25.2955532073975</t>
   </si>
   <si>
     <t xml:space="preserve">25.5208034515381</t>
@@ -3044,16 +3044,16 @@
     <t xml:space="preserve">25.8286476135254</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8061199188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7385444641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7835941314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0538940429688</t>
+    <t xml:space="preserve">25.8061180114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7385406494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7835922241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0538959503174</t>
   </si>
   <si>
     <t xml:space="preserve">25.8661861419678</t>
@@ -3062,16 +3062,16 @@
     <t xml:space="preserve">26.4893760681152</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5119018554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3767528533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4668502807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6545658111572</t>
+    <t xml:space="preserve">26.5119075775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3767547607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.466854095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6545562744141</t>
   </si>
   <si>
     <t xml:space="preserve">26.5869846343994</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">27.1050586700439</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5180206298828</t>
+    <t xml:space="preserve">27.5180225372314</t>
   </si>
   <si>
     <t xml:space="preserve">27.1350936889648</t>
@@ -3092,46 +3092,46 @@
     <t xml:space="preserve">27.0149593353271</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0374870300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2176818847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1951580047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.225191116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2566204071045</t>
+    <t xml:space="preserve">27.037483215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2176876068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.195161819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2251930236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2566165924072</t>
   </si>
   <si>
     <t xml:space="preserve">26.6845951080322</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1726341247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0299758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7446594238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6245269775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.89621925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0163497924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3992748260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3542251586914</t>
+    <t xml:space="preserve">27.1726322174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0299739837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7446613311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6245250701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8962211608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0163536071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3992767333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.35422706604</t>
   </si>
   <si>
     <t xml:space="preserve">26.5569534301758</t>
@@ -3140,19 +3140,19 @@
     <t xml:space="preserve">26.001335144043</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0238628387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4217987060547</t>
+    <t xml:space="preserve">26.0238571166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4218006134033</t>
   </si>
   <si>
     <t xml:space="preserve">26.2866516113281</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2115650177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8873176574707</t>
+    <t xml:space="preserve">26.2115707397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8873157501221</t>
   </si>
   <si>
     <t xml:space="preserve">27.1125679016113</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">27.3603420257568</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3828716278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6456604003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6231365203857</t>
+    <t xml:space="preserve">27.3828659057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6456565856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6231346130371</t>
   </si>
   <si>
     <t xml:space="preserve">27.7808074951172</t>
@@ -3182,64 +3182,64 @@
     <t xml:space="preserve">27.5630645751953</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7883148193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7132301330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9535026550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9835338592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2613410949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1412086486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2087821960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1862621307373</t>
+    <t xml:space="preserve">27.7883167266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7132320404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.953498840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9835357666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2613430023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1412143707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2087841033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1862602233887</t>
   </si>
   <si>
     <t xml:space="preserve">28.3814735412598</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2012805938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0586166381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1186809539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4115085601807</t>
+    <t xml:space="preserve">28.2012748718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0586185455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1186866760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4115104675293</t>
   </si>
   <si>
     <t xml:space="preserve">29.1698474884033</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3875904083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5077209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2899780273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9145641326904</t>
+    <t xml:space="preserve">29.3875885009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5077247619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2899799346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9145698547363</t>
   </si>
   <si>
     <t xml:space="preserve">28.4190139770508</t>
   </si>
   <si>
-    <t xml:space="preserve">28.64426612854</t>
+    <t xml:space="preserve">28.6442718505859</t>
   </si>
   <si>
     <t xml:space="preserve">29.1923770904541</t>
@@ -3248,16 +3248,16 @@
     <t xml:space="preserve">29.1323070526123</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2148971557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5842018127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4865913391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4565620422363</t>
+    <t xml:space="preserve">29.2148952484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5842056274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4865875244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4565582275391</t>
   </si>
   <si>
     <t xml:space="preserve">28.5466594696045</t>
@@ -3266,22 +3266,22 @@
     <t xml:space="preserve">28.4640693664551</t>
   </si>
   <si>
-    <t xml:space="preserve">27.87841796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4715766906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4039993286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0736351013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3964920043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0285873413086</t>
+    <t xml:space="preserve">27.8784160614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4715728759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4039974212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0736293792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3964900970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0285816192627</t>
   </si>
   <si>
     <t xml:space="preserve">28.7644023895264</t>
@@ -3290,31 +3290,31 @@
     <t xml:space="preserve">29.6954288482666</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7179565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9432067871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4012145996094</t>
+    <t xml:space="preserve">29.717960357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9432144165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.401216506958</t>
   </si>
   <si>
     <t xml:space="preserve">30.7240734100342</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5213432312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6940383911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5288581848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7090549468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4988231658936</t>
+    <t xml:space="preserve">30.5213508605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6940422058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5288543701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7090587615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4988193511963</t>
   </si>
   <si>
     <t xml:space="preserve">30.7766304016113</t>
@@ -3323,16 +3323,16 @@
     <t xml:space="preserve">31.7602157592773</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2107276916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.435977935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7377014160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1506614685059</t>
+    <t xml:space="preserve">32.2107238769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4359703063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7376976013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1506538391113</t>
   </si>
   <si>
     <t xml:space="preserve">32.3083305358887</t>
@@ -3344,160 +3344,160 @@
     <t xml:space="preserve">31.8728485107422</t>
   </si>
   <si>
-    <t xml:space="preserve">31.137035369873</t>
+    <t xml:space="preserve">31.1370277404785</t>
   </si>
   <si>
     <t xml:space="preserve">30.859224319458</t>
   </si>
   <si>
-    <t xml:space="preserve">31.054443359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4641075134277</t>
+    <t xml:space="preserve">31.0544395446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4641036987305</t>
   </si>
   <si>
     <t xml:space="preserve">30.2592010498047</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0342864990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6406860351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8052825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1265888214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.08642578125</t>
+    <t xml:space="preserve">30.0342807769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6406803131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8052845001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1265907287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0864219665527</t>
   </si>
   <si>
     <t xml:space="preserve">30.0583820343018</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9378910064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1146144866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5885391235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.359676361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3195152282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0303382873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1508293151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.335578918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2632904052734</t>
+    <t xml:space="preserve">29.9378929138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1146106719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5885410308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3596839904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3195190429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0303440093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1508312225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3355808258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2632884979248</t>
   </si>
   <si>
     <t xml:space="preserve">31.1668968200684</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1186981201172</t>
+    <t xml:space="preserve">31.1187000274658</t>
   </si>
   <si>
     <t xml:space="preserve">30.6046028137207</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7531414031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4118232727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5644474029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5483779907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9419822692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2713241577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1829643249512</t>
+    <t xml:space="preserve">29.7531452178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4118251800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5644435882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.548376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9419784545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2713203430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1829566955566</t>
   </si>
   <si>
     <t xml:space="preserve">31.1267318725586</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2150955200195</t>
+    <t xml:space="preserve">31.2150917053223</t>
   </si>
   <si>
     <t xml:space="preserve">31.2311592102051</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1909980773926</t>
+    <t xml:space="preserve">31.1909923553467</t>
   </si>
   <si>
     <t xml:space="preserve">30.4359188079834</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2029724121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1788711547852</t>
+    <t xml:space="preserve">30.2029705047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1788749694824</t>
   </si>
   <si>
     <t xml:space="preserve">30.8375549316406</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8616504669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5082111358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3475589752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.291332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4800300598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8856048583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3997001647949</t>
+    <t xml:space="preserve">30.8616485595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5082130432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3475608825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2913303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4800281524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8856086730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3997020721436</t>
   </si>
   <si>
     <t xml:space="preserve">28.9338035583496</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7208652496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1907043457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.680700302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9939785003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0743083953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5803661346436</t>
+    <t xml:space="preserve">27.7208690643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1907062530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6807022094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9939804077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0743045806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5803642272949</t>
   </si>
   <si>
     <t xml:space="preserve">28.9659385681152</t>
@@ -3506,10 +3506,10 @@
     <t xml:space="preserve">29.0783939361572</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8695411682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8374156951904</t>
+    <t xml:space="preserve">28.8695430755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8374137878418</t>
   </si>
   <si>
     <t xml:space="preserve">28.8133144378662</t>
@@ -3518,31 +3518,31 @@
     <t xml:space="preserve">28.6285591125488</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3595390319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0944557189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9579029083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3152847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1587219238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3675727844238</t>
+    <t xml:space="preserve">29.3595352172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.09446144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9579010009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3152885437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1587200164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3675708770752</t>
   </si>
   <si>
     <t xml:space="preserve">28.8936405181885</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8026962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2799015045166</t>
+    <t xml:space="preserve">28.8026943206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2799034118652</t>
   </si>
   <si>
     <t xml:space="preserve">28.4105987548828</t>
@@ -3551,31 +3551,31 @@
     <t xml:space="preserve">25.9600048065186</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9974250793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.981086730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9028186798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9273281097412</t>
+    <t xml:space="preserve">26.9974231719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9810829162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9028205871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9273300170898</t>
   </si>
   <si>
     <t xml:space="preserve">25.3228454589844</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3623676300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8885860443115</t>
+    <t xml:space="preserve">23.3623695373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8885879516602</t>
   </si>
   <si>
     <t xml:space="preserve">23.5175762176514</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3963642120361</t>
+    <t xml:space="preserve">25.3963661193848</t>
   </si>
   <si>
     <t xml:space="preserve">24.7101993560791</t>
@@ -3584,13 +3584,13 @@
     <t xml:space="preserve">25.306510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7231121063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8211364746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1281185150146</t>
+    <t xml:space="preserve">25.7231101989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8211345672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1281223297119</t>
   </si>
   <si>
     <t xml:space="preserve">26.956579208374</t>
@@ -3599,37 +3599,37 @@
     <t xml:space="preserve">27.144458770752</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7768669128418</t>
+    <t xml:space="preserve">26.7768688201904</t>
   </si>
   <si>
     <t xml:space="preserve">27.1036167144775</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0709381103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9892539978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0300979614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3486747741699</t>
+    <t xml:space="preserve">27.0709400177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9892520904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0300998687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3486766815186</t>
   </si>
   <si>
     <t xml:space="preserve">28.1328678131104</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9041442871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5447216033936</t>
+    <t xml:space="preserve">27.9041404724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5447254180908</t>
   </si>
   <si>
     <t xml:space="preserve">27.9776611328125</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5937347412109</t>
+    <t xml:space="preserve">27.5937366485596</t>
   </si>
   <si>
     <t xml:space="preserve">26.5481472015381</t>
@@ -3641,7 +3641,7 @@
     <t xml:space="preserve">26.8830623626709</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8667240142822</t>
+    <t xml:space="preserve">26.8667259216309</t>
   </si>
   <si>
     <t xml:space="preserve">26.5399799346924</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">26.3439292907715</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6414260864258</t>
+    <t xml:space="preserve">25.6414241790771</t>
   </si>
   <si>
     <t xml:space="preserve">26.237735748291</t>
@@ -3674,22 +3674,22 @@
     <t xml:space="preserve">25.3310165405273</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2738342285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6740989685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8048000335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3555240631104</t>
+    <t xml:space="preserve">25.2738380432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6741008758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8047981262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.355525970459</t>
   </si>
   <si>
     <t xml:space="preserve">24.9634246826172</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9913558959961</t>
+    <t xml:space="preserve">23.9913578033447</t>
   </si>
   <si>
     <t xml:space="preserve">24.3017654418945</t>
@@ -3701,22 +3701,22 @@
     <t xml:space="preserve">26.3766059875488</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4256172180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5154724121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4419536590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6380023956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5073051452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5489616394043</t>
+    <t xml:space="preserve">26.4256153106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.515474319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.441951751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6380004882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.507303237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5489635467529</t>
   </si>
   <si>
     <t xml:space="preserve">26.7698364257812</t>
@@ -3725,10 +3725,10 @@
     <t xml:space="preserve">26.4734287261963</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5743732452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6759967803955</t>
+    <t xml:space="preserve">27.5743713378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6759948730469</t>
   </si>
   <si>
     <t xml:space="preserve">27.9639339447021</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">27.5235576629639</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7274894714355</t>
+    <t xml:space="preserve">26.7274913787842</t>
   </si>
   <si>
     <t xml:space="preserve">27.5320262908936</t>
@@ -3752,25 +3752,25 @@
     <t xml:space="preserve">26.9561500549316</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2108955383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5164527893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3992576599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8149127960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.348445892334</t>
+    <t xml:space="preserve">26.2108974456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5164546966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3992557525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8149108886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3484439849854</t>
   </si>
   <si>
     <t xml:space="preserve">23.9751358032227</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9250087738037</t>
+    <t xml:space="preserve">22.9250049591064</t>
   </si>
   <si>
     <t xml:space="preserve">23.4161968231201</t>
@@ -3785,10 +3785,10 @@
     <t xml:space="preserve">23.0859146118164</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8904457092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6194458007812</t>
+    <t xml:space="preserve">23.8904476165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6194477081299</t>
   </si>
   <si>
     <t xml:space="preserve">23.5093536376953</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">23.3230400085449</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8318462371826</t>
+    <t xml:space="preserve">22.8318481445312</t>
   </si>
   <si>
     <t xml:space="preserve">22.747163772583</t>
@@ -3809,7 +3809,7 @@
     <t xml:space="preserve">21.64621925354</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9510974884033</t>
+    <t xml:space="preserve">21.9510955810547</t>
   </si>
   <si>
     <t xml:space="preserve">22.264440536499</t>
@@ -3818,7 +3818,7 @@
     <t xml:space="preserve">22.7810363769531</t>
   </si>
   <si>
-    <t xml:space="preserve">22.112003326416</t>
+    <t xml:space="preserve">22.1120014190674</t>
   </si>
   <si>
     <t xml:space="preserve">22.4592247009277</t>
@@ -3836,10 +3836,10 @@
     <t xml:space="preserve">22.2898483276367</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0520362854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0351009368896</t>
+    <t xml:space="preserve">23.052038192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0351028442383</t>
   </si>
   <si>
     <t xml:space="preserve">22.5185050964355</t>
@@ -3854,31 +3854,31 @@
     <t xml:space="preserve">22.6116619110107</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1536636352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.966667175293</t>
+    <t xml:space="preserve">23.1536655426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9666652679443</t>
   </si>
   <si>
     <t xml:space="preserve">24.0513553619385</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9327945709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4239807128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5256080627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9497318267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8565711975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4416007995605</t>
+    <t xml:space="preserve">23.9327926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4239826202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5256061553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9497299194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8565731048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4416046142578</t>
   </si>
   <si>
     <t xml:space="preserve">23.7888240814209</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">24.1275749206543</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1360416412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5008850097656</t>
+    <t xml:space="preserve">24.1360397338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5008811950684</t>
   </si>
   <si>
     <t xml:space="preserve">23.7380084991455</t>
@@ -3899,10 +3899,10 @@
     <t xml:space="preserve">23.0774459838867</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5354404449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9334754943848</t>
+    <t xml:space="preserve">22.5354442596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9334735870361</t>
   </si>
   <si>
     <t xml:space="preserve">22.7725677490234</t>
@@ -3911,22 +3911,22 @@
     <t xml:space="preserve">22.095064163208</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0273170471191</t>
+    <t xml:space="preserve">22.0273132324219</t>
   </si>
   <si>
     <t xml:space="preserve">22.2559719085693</t>
   </si>
   <si>
-    <t xml:space="preserve">22.391471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9256858825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.23903465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3237228393555</t>
+    <t xml:space="preserve">22.3914737701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.925687789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2390365600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3237247467041</t>
   </si>
   <si>
     <t xml:space="preserve">22.4422855377197</t>
@@ -3935,25 +3935,25 @@
     <t xml:space="preserve">23.0689754486084</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9243240356445</t>
+    <t xml:space="preserve">23.9243259429932</t>
   </si>
   <si>
     <t xml:space="preserve">23.3907909393311</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9419441223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6455383300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.730224609375</t>
+    <t xml:space="preserve">22.9419460296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6455345153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7302227020264</t>
   </si>
   <si>
     <t xml:space="preserve">21.3921566009521</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5022525787354</t>
+    <t xml:space="preserve">21.5022506713867</t>
   </si>
   <si>
     <t xml:space="preserve">21.341344833374</t>
@@ -3962,25 +3962,25 @@
     <t xml:space="preserve">20.7908706665039</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0957489013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6553726196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8078117370605</t>
+    <t xml:space="preserve">21.0957469940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6553707122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8078079223633</t>
   </si>
   <si>
     <t xml:space="preserve">20.3335590362549</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2207317352295</t>
+    <t xml:space="preserve">24.2207298278809</t>
   </si>
   <si>
     <t xml:space="preserve">23.2552890777588</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0344161987305</t>
+    <t xml:space="preserve">24.0344181060791</t>
   </si>
   <si>
     <t xml:space="preserve">23.4246654510498</t>
@@ -3992,7 +3992,7 @@
     <t xml:space="preserve">23.4331340789795</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6533241271973</t>
+    <t xml:space="preserve">23.6533222198486</t>
   </si>
   <si>
     <t xml:space="preserve">24.0174789428711</t>
@@ -4010,16 +4010,16 @@
     <t xml:space="preserve">24.79660987854</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1438293457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8297996520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9737701416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2871150970459</t>
+    <t xml:space="preserve">25.1438312530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8298015594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9737720489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2871170043945</t>
   </si>
   <si>
     <t xml:space="preserve">26.3802719116211</t>
@@ -4028,25 +4028,25 @@
     <t xml:space="preserve">25.6265506744385</t>
   </si>
   <si>
-    <t xml:space="preserve">25.719705581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6858310699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3294582366943</t>
+    <t xml:space="preserve">25.7197074890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6858291625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.329460144043</t>
   </si>
   <si>
     <t xml:space="preserve">27.3118381500244</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9307422637939</t>
+    <t xml:space="preserve">26.9307441711426</t>
   </si>
   <si>
     <t xml:space="preserve">26.9053363800049</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1756553649902</t>
+    <t xml:space="preserve">28.1756534576416</t>
   </si>
   <si>
     <t xml:space="preserve">28.2264671325684</t>
@@ -4055,31 +4055,31 @@
     <t xml:space="preserve">28.074031829834</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4551258087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2434024810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1163730621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3111553192139</t>
+    <t xml:space="preserve">28.4551239013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2434043884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1163749694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3111534118652</t>
   </si>
   <si>
     <t xml:space="preserve">28.1671848297119</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4297180175781</t>
+    <t xml:space="preserve">28.4297161102295</t>
   </si>
   <si>
     <t xml:space="preserve">28.7091903686523</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1848049163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2779636383057</t>
+    <t xml:space="preserve">27.1848068237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.277961730957</t>
   </si>
   <si>
     <t xml:space="preserve">27.0069599151611</t>
@@ -4091,61 +4091,61 @@
     <t xml:space="preserve">27.286434173584</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0238990783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6675243377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4981536865234</t>
+    <t xml:space="preserve">27.0239009857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6675262451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4981517791748</t>
   </si>
   <si>
     <t xml:space="preserve">27.2610244750977</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0577754974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2694931030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5574340820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0909671783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.125524520874</t>
+    <t xml:space="preserve">27.0577735900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.269495010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5574321746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0909652709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1255226135254</t>
   </si>
   <si>
     <t xml:space="preserve">27.0916500091553</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7105560302734</t>
+    <t xml:space="preserve">26.7105541229248</t>
   </si>
   <si>
     <t xml:space="preserve">26.7952423095703</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4219360351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2271518707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4304008483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3203067779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1509304046631</t>
+    <t xml:space="preserve">27.4219341278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2271499633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4304027557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3203048706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1509323120117</t>
   </si>
   <si>
     <t xml:space="preserve">27.7014026641846</t>
   </si>
   <si>
-    <t xml:space="preserve">28.234935760498</t>
+    <t xml:space="preserve">28.2349376678467</t>
   </si>
   <si>
     <t xml:space="preserve">27.9046535491943</t>
@@ -4154,13 +4154,13 @@
     <t xml:space="preserve">28.1925926208496</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4720611572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4635963439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0818157196045</t>
+    <t xml:space="preserve">28.4720630645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4635925292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0818138122559</t>
   </si>
   <si>
     <t xml:space="preserve">29.2935352325439</t>
@@ -4169,40 +4169,40 @@
     <t xml:space="preserve">29.0479393005371</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7938747406006</t>
+    <t xml:space="preserve">28.7938766479492</t>
   </si>
   <si>
     <t xml:space="preserve">28.692253112793</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4043121337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7176551818848</t>
+    <t xml:space="preserve">28.4043140411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7176570892334</t>
   </si>
   <si>
     <t xml:space="preserve">28.844690322876</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8362197875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8531551361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6245002746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8108158111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8785629272461</t>
+    <t xml:space="preserve">28.8362216949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.853157043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6244983673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8108139038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8785610198975</t>
   </si>
   <si>
     <t xml:space="preserve">29.0902824401855</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8700923919678</t>
+    <t xml:space="preserve">28.8700942993164</t>
   </si>
   <si>
     <t xml:space="preserve">28.8277530670166</t>
@@ -4214,13 +4214,13 @@
     <t xml:space="preserve">28.7599983215332</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6753120422363</t>
+    <t xml:space="preserve">28.6753101348877</t>
   </si>
   <si>
     <t xml:space="preserve">28.759183883667</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2301406860352</t>
+    <t xml:space="preserve">28.2301387786865</t>
   </si>
   <si>
     <t xml:space="preserve">28.0740299224854</t>
@@ -4229,22 +4229,22 @@
     <t xml:space="preserve">28.1954479217529</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0133171081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2908477783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3515586853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2995223999023</t>
+    <t xml:space="preserve">28.0133190155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2908496856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3515567779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.299524307251</t>
   </si>
   <si>
     <t xml:space="preserve">28.1520843505859</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3081970214844</t>
+    <t xml:space="preserve">28.3081951141357</t>
   </si>
   <si>
     <t xml:space="preserve">28.2214679718018</t>
@@ -4253,7 +4253,7 @@
     <t xml:space="preserve">28.1434154510498</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9812526702881</t>
+    <t xml:space="preserve">26.9812507629395</t>
   </si>
   <si>
     <t xml:space="preserve">26.1660003662109</t>
@@ -4262,16 +4262,16 @@
     <t xml:space="preserve">25.4027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0185642242432</t>
+    <t xml:space="preserve">26.0185623168945</t>
   </si>
   <si>
     <t xml:space="preserve">24.934455871582</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0558776855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2753200531006</t>
+    <t xml:space="preserve">25.0558757781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.275318145752</t>
   </si>
   <si>
     <t xml:space="preserve">24.9951648712158</t>
@@ -4280,7 +4280,7 @@
     <t xml:space="preserve">25.8017406463623</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3594245910645</t>
+    <t xml:space="preserve">25.3594264984131</t>
   </si>
   <si>
     <t xml:space="preserve">25.3247356414795</t>
@@ -4292,13 +4292,13 @@
     <t xml:space="preserve">25.0125102996826</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7176322937012</t>
+    <t xml:space="preserve">24.7176342010498</t>
   </si>
   <si>
     <t xml:space="preserve">25.1686229705811</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4634971618652</t>
+    <t xml:space="preserve">25.4635009765625</t>
   </si>
   <si>
     <t xml:space="preserve">25.4808464050293</t>
@@ -4310,19 +4310,19 @@
     <t xml:space="preserve">25.3073902130127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9518032073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5068626403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9058151245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1052932739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6716480255127</t>
+    <t xml:space="preserve">24.9518013000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5068664550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9058170318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1052913665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6716499328613</t>
   </si>
   <si>
     <t xml:space="preserve">26.0359077453613</t>
@@ -4331,22 +4331,22 @@
     <t xml:space="preserve">25.6196117401123</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2006931304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4088439941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.443531036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5042400360107</t>
+    <t xml:space="preserve">26.2006912231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.408842086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4435329437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5042419433594</t>
   </si>
   <si>
     <t xml:space="preserve">26.313440322876</t>
   </si>
   <si>
-    <t xml:space="preserve">26.183349609375</t>
+    <t xml:space="preserve">26.1833477020264</t>
   </si>
   <si>
     <t xml:space="preserve">26.4522037506104</t>
@@ -4364,13 +4364,13 @@
     <t xml:space="preserve">25.3767719268799</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3307838439941</t>
+    <t xml:space="preserve">26.3307857513428</t>
   </si>
   <si>
     <t xml:space="preserve">26.1920204162598</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0098896026611</t>
+    <t xml:space="preserve">26.0098915100098</t>
   </si>
   <si>
     <t xml:space="preserve">25.8104133605957</t>
@@ -4385,10 +4385,10 @@
     <t xml:space="preserve">26.4868984222412</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5996437072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7297382354736</t>
+    <t xml:space="preserve">26.599645614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.729736328125</t>
   </si>
   <si>
     <t xml:space="preserve">27.1062126159668</t>
@@ -4406,22 +4406,22 @@
     <t xml:space="preserve">26.675952911377</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7028465270996</t>
+    <t xml:space="preserve">26.702844619751</t>
   </si>
   <si>
     <t xml:space="preserve">26.3084411621094</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8154392242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3622245788574</t>
+    <t xml:space="preserve">25.8154373168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3622264862061</t>
   </si>
   <si>
     <t xml:space="preserve">26.8821201324463</t>
   </si>
   <si>
-    <t xml:space="preserve">26.693883895874</t>
+    <t xml:space="preserve">26.6938819885254</t>
   </si>
   <si>
     <t xml:space="preserve">27.2048110961914</t>
@@ -4433,7 +4433,7 @@
     <t xml:space="preserve">27.5185413360596</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3930473327637</t>
+    <t xml:space="preserve">27.3930492401123</t>
   </si>
   <si>
     <t xml:space="preserve">27.6529979705811</t>
@@ -4442,7 +4442,7 @@
     <t xml:space="preserve">27.7157440185547</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9219074249268</t>
+    <t xml:space="preserve">27.9219055175781</t>
   </si>
   <si>
     <t xml:space="preserve">27.8860549926758</t>
@@ -4457,7 +4457,7 @@
     <t xml:space="preserve">27.7605609893799</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6619606018066</t>
+    <t xml:space="preserve">27.6619625091553</t>
   </si>
   <si>
     <t xml:space="preserve">27.4647598266602</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">27.3213386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6081771850586</t>
+    <t xml:space="preserve">27.60817527771</t>
   </si>
   <si>
     <t xml:space="preserve">27.9487991333008</t>
@@ -4481,10 +4481,10 @@
     <t xml:space="preserve">28.2356357574463</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7644939422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3611297607422</t>
+    <t xml:space="preserve">28.7644958496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3611278533936</t>
   </si>
   <si>
     <t xml:space="preserve">27.9129428863525</t>
@@ -4496,7 +4496,7 @@
     <t xml:space="preserve">27.8233089447021</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9577617645264</t>
+    <t xml:space="preserve">27.957763671875</t>
   </si>
   <si>
     <t xml:space="preserve">28.5045471191406</t>
@@ -4523,10 +4523,10 @@
     <t xml:space="preserve">29.3740272521973</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2306060791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.705680847168</t>
+    <t xml:space="preserve">29.2306079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7056827545166</t>
   </si>
   <si>
     <t xml:space="preserve">30.1000862121582</t>
@@ -4535,7 +4535,7 @@
     <t xml:space="preserve">30.9606018066406</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5482730865479</t>
+    <t xml:space="preserve">30.5482711791992</t>
   </si>
   <si>
     <t xml:space="preserve">30.1986827850342</t>
@@ -4547,10 +4547,10 @@
     <t xml:space="preserve">29.8311729431152</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7734565734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1588954925537</t>
+    <t xml:space="preserve">28.773458480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1588973999023</t>
   </si>
   <si>
     <t xml:space="preserve">29.3202438354492</t>
@@ -4559,7 +4559,7 @@
     <t xml:space="preserve">29.1140785217285</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4457359313965</t>
+    <t xml:space="preserve">29.4457340240479</t>
   </si>
   <si>
     <t xml:space="preserve">29.3650608062744</t>
@@ -4571,31 +4571,31 @@
     <t xml:space="preserve">28.7017478942871</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9975509643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1768245697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2574996948242</t>
+    <t xml:space="preserve">28.9975490570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1768226623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2574977874756</t>
   </si>
   <si>
     <t xml:space="preserve">29.3112812042236</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5712299346924</t>
+    <t xml:space="preserve">29.5712280273438</t>
   </si>
   <si>
     <t xml:space="preserve">30.1628322601318</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9745903015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2166137695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0014877319336</t>
+    <t xml:space="preserve">29.9745922088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2166118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.001485824585</t>
   </si>
   <si>
     <t xml:space="preserve">30.0283756256104</t>
@@ -4610,37 +4610,37 @@
     <t xml:space="preserve">29.7684268951416</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1717967987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.180757522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4586315155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0104503631592</t>
+    <t xml:space="preserve">30.1717948913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1807556152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4586334228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0104484558105</t>
   </si>
   <si>
     <t xml:space="preserve">30.2703971862793</t>
   </si>
   <si>
-    <t xml:space="preserve">30.593090057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.144905090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.153865814209</t>
+    <t xml:space="preserve">30.5930881500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1449069976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1538677215576</t>
   </si>
   <si>
     <t xml:space="preserve">30.0463027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0373382568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.696720123291</t>
+    <t xml:space="preserve">30.0373363494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6967220306396</t>
   </si>
   <si>
     <t xml:space="preserve">29.1678619384766</t>
@@ -4649,7 +4649,7 @@
     <t xml:space="preserve">29.6877555847168</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3292083740234</t>
+    <t xml:space="preserve">29.3292102813721</t>
   </si>
   <si>
     <t xml:space="preserve">29.4278087615967</t>
@@ -4658,13 +4658,13 @@
     <t xml:space="preserve">30.0552654266357</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7107124328613</t>
+    <t xml:space="preserve">28.7107105255127</t>
   </si>
   <si>
     <t xml:space="preserve">28.5224742889404</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4776573181152</t>
+    <t xml:space="preserve">28.4776592254639</t>
   </si>
   <si>
     <t xml:space="preserve">28.2177066802979</t>
@@ -4673,7 +4673,7 @@
     <t xml:space="preserve">27.7426338195801</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3392677307129</t>
+    <t xml:space="preserve">27.3392658233643</t>
   </si>
   <si>
     <t xml:space="preserve">27.5095767974854</t>
@@ -4682,13 +4682,13 @@
     <t xml:space="preserve">27.3571949005127</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0524291992188</t>
+    <t xml:space="preserve">27.0524311065674</t>
   </si>
   <si>
     <t xml:space="preserve">27.1868839263916</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2854862213135</t>
+    <t xml:space="preserve">27.2854843139648</t>
   </si>
   <si>
     <t xml:space="preserve">27.2944507598877</t>
@@ -4700,7 +4700,7 @@
     <t xml:space="preserve">27.5454330444336</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0294723510742</t>
+    <t xml:space="preserve">28.0294742584229</t>
   </si>
   <si>
     <t xml:space="preserve">28.4059467315674</t>
@@ -4709,7 +4709,7 @@
     <t xml:space="preserve">28.1191101074219</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2714939117432</t>
+    <t xml:space="preserve">28.2714920043945</t>
   </si>
   <si>
     <t xml:space="preserve">28.6838207244873</t>
@@ -4721,7 +4721,7 @@
     <t xml:space="preserve">29.0423717498779</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7325744628906</t>
+    <t xml:space="preserve">29.732572555542</t>
   </si>
   <si>
     <t xml:space="preserve">29.7863540649414</t>
@@ -4733,7 +4733,7 @@
     <t xml:space="preserve">29.4547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">29.849100112915</t>
+    <t xml:space="preserve">29.8491020202637</t>
   </si>
   <si>
     <t xml:space="preserve">29.194751739502</t>
@@ -4742,10 +4742,10 @@
     <t xml:space="preserve">28.8989524841309</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2664642333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0602931976318</t>
+    <t xml:space="preserve">29.2664623260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0602951049805</t>
   </si>
   <si>
     <t xml:space="preserve">29.1499328613281</t>
@@ -4757,7 +4757,7 @@
     <t xml:space="preserve">29.0961513519287</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2485332489014</t>
+    <t xml:space="preserve">29.24853515625</t>
   </si>
   <si>
     <t xml:space="preserve">29.5891513824463</t>
@@ -4766,10 +4766,10 @@
     <t xml:space="preserve">29.6070823669434</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7953205108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2883224487305</t>
+    <t xml:space="preserve">29.7953224182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2883243560791</t>
   </si>
   <si>
     <t xml:space="preserve">30.0731925964355</t>
@@ -4778,10 +4778,10 @@
     <t xml:space="preserve">30.4048480987549</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4317436218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3600311279297</t>
+    <t xml:space="preserve">30.4317417144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3600330352783</t>
   </si>
   <si>
     <t xml:space="preserve">30.2255764007568</t>
@@ -4790,7 +4790,7 @@
     <t xml:space="preserve">30.1359405517578</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3152141571045</t>
+    <t xml:space="preserve">30.3152122497559</t>
   </si>
   <si>
     <t xml:space="preserve">30.3421020507812</t>
@@ -4799,43 +4799,43 @@
     <t xml:space="preserve">30.7454719543457</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3331432342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.06422996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6110191345215</t>
+    <t xml:space="preserve">30.3331394195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0642318725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6110172271729</t>
   </si>
   <si>
     <t xml:space="preserve">30.8440723419189</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0860939025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1936569213867</t>
+    <t xml:space="preserve">31.0860919952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1936588287354</t>
   </si>
   <si>
     <t xml:space="preserve">31.1577987670898</t>
   </si>
   <si>
-    <t xml:space="preserve">31.175724029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3818912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5522041320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8121509552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8480033874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0003890991211</t>
+    <t xml:space="preserve">31.1757259368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3818893432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5522079467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8121547698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8480072021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0003852844238</t>
   </si>
   <si>
     <t xml:space="preserve">31.2384738922119</t>
@@ -4856,13 +4856,13 @@
     <t xml:space="preserve">31.821117401123</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1258773803711</t>
+    <t xml:space="preserve">32.1258811950684</t>
   </si>
   <si>
     <t xml:space="preserve">32.0900230407715</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2743263244629</t>
+    <t xml:space="preserve">31.2743301391602</t>
   </si>
   <si>
     <t xml:space="preserve">30.9068183898926</t>
@@ -4874,19 +4874,19 @@
     <t xml:space="preserve">30.1090469360352</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3958854675293</t>
+    <t xml:space="preserve">30.3958873748779</t>
   </si>
   <si>
     <t xml:space="preserve">30.8551158905029</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3069038391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6632423400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.430736541748</t>
+    <t xml:space="preserve">30.3069019317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6632404327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4307384490967</t>
   </si>
   <si>
     <t xml:space="preserve">32.2896003723145</t>
@@ -4898,7 +4898,7 @@
     <t xml:space="preserve">31.5769271850586</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3667812347412</t>
+    <t xml:space="preserve">31.3667774200439</t>
   </si>
   <si>
     <t xml:space="preserve">31.2114505767822</t>
@@ -4907,16 +4907,16 @@
     <t xml:space="preserve">31.3941860198975</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4764194488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6957015991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.860164642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9698104858398</t>
+    <t xml:space="preserve">31.4764213562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6957035064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8601665496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9698085784912</t>
   </si>
   <si>
     <t xml:space="preserve">31.9789447784424</t>
@@ -4952,22 +4952,22 @@
     <t xml:space="preserve">33.7423553466797</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7971801757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7514953613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6418495178223</t>
+    <t xml:space="preserve">33.797176361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7514915466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6418533325195</t>
   </si>
   <si>
     <t xml:space="preserve">32.947452545166</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2946472167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3311996459961</t>
+    <t xml:space="preserve">33.2946510314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3311958312988</t>
   </si>
   <si>
     <t xml:space="preserve">33.2398300170898</t>
@@ -4976,7 +4976,7 @@
     <t xml:space="preserve">33.404296875</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0936393737793</t>
+    <t xml:space="preserve">33.0936431884766</t>
   </si>
   <si>
     <t xml:space="preserve">32.6367988586426</t>
@@ -4988,19 +4988,19 @@
     <t xml:space="preserve">32.3809623718262</t>
   </si>
   <si>
-    <t xml:space="preserve">31.613468170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8144817352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5819778442383</t>
+    <t xml:space="preserve">31.6134700775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8144836425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.581974029541</t>
   </si>
   <si>
     <t xml:space="preserve">32.5454292297363</t>
   </si>
   <si>
-    <t xml:space="preserve">33.130184173584</t>
+    <t xml:space="preserve">33.1301879882812</t>
   </si>
   <si>
     <t xml:space="preserve">33.075366973877</t>
@@ -5012,10 +5012,10 @@
     <t xml:space="preserve">33.1850090026855</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4408378601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7697677612305</t>
+    <t xml:space="preserve">33.4408416748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7697639465332</t>
   </si>
   <si>
     <t xml:space="preserve">33.9525032043457</t>
@@ -5024,7 +5024,7 @@
     <t xml:space="preserve">34.4093437194824</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8844604492188</t>
+    <t xml:space="preserve">34.884464263916</t>
   </si>
   <si>
     <t xml:space="preserve">35.4692192077637</t>
@@ -5039,28 +5039,28 @@
     <t xml:space="preserve">37.0955772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9128456115723</t>
+    <t xml:space="preserve">36.912841796875</t>
   </si>
   <si>
     <t xml:space="preserve">37.0590324401855</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7849235534668</t>
+    <t xml:space="preserve">36.7849273681641</t>
   </si>
   <si>
     <t xml:space="preserve">37.0985145568848</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9844818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1555252075195</t>
+    <t xml:space="preserve">36.9844779968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1555290222168</t>
   </si>
   <si>
     <t xml:space="preserve">37.1365280151367</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3265762329102</t>
+    <t xml:space="preserve">37.3265800476074</t>
   </si>
   <si>
     <t xml:space="preserve">37.0224914550781</t>
@@ -5084,7 +5084,7 @@
     <t xml:space="preserve">36.4523315429688</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8704490661621</t>
+    <t xml:space="preserve">36.8704452514648</t>
   </si>
   <si>
     <t xml:space="preserve">36.9084625244141</t>
@@ -5093,10 +5093,10 @@
     <t xml:space="preserve">36.5853691101074</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5473556518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0912284851074</t>
+    <t xml:space="preserve">36.5473594665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0912246704102</t>
   </si>
   <si>
     <t xml:space="preserve">36.5663642883301</t>
@@ -5105,7 +5105,7 @@
     <t xml:space="preserve">35.7301254272461</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0839424133301</t>
+    <t xml:space="preserve">35.0839385986328</t>
   </si>
   <si>
     <t xml:space="preserve">35.1219520568848</t>
@@ -5120,7 +5120,7 @@
     <t xml:space="preserve">35.7491302490234</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3572998046875</t>
+    <t xml:space="preserve">36.3573036193848</t>
   </si>
   <si>
     <t xml:space="preserve">36.0722198486328</t>
@@ -5129,13 +5129,13 @@
     <t xml:space="preserve">35.8821678161621</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7871398925781</t>
+    <t xml:space="preserve">35.7871437072754</t>
   </si>
   <si>
     <t xml:space="preserve">35.5970878601074</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9201774597168</t>
+    <t xml:space="preserve">35.9201812744141</t>
   </si>
   <si>
     <t xml:space="preserve">35.9391860961914</t>
@@ -5147,13 +5147,13 @@
     <t xml:space="preserve">35.8631629943848</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9011764526367</t>
+    <t xml:space="preserve">35.9011726379395</t>
   </si>
   <si>
     <t xml:space="preserve">36.3763084411621</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8514442443848</t>
+    <t xml:space="preserve">36.8514404296875</t>
   </si>
   <si>
     <t xml:space="preserve">37.2885704040527</t>
@@ -5177,7 +5177,7 @@
     <t xml:space="preserve">38.3718757629395</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4478950500488</t>
+    <t xml:space="preserve">38.4478988647461</t>
   </si>
   <si>
     <t xml:space="preserve">38.5429229736328</t>
@@ -5189,7 +5189,7 @@
     <t xml:space="preserve">37.7446975708008</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6423873901367</t>
+    <t xml:space="preserve">36.6423835754395</t>
   </si>
   <si>
     <t xml:space="preserve">35.4450454711914</t>
@@ -5201,7 +5201,7 @@
     <t xml:space="preserve">35.8061485290527</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6921195983887</t>
+    <t xml:space="preserve">35.6921157836914</t>
   </si>
   <si>
     <t xml:space="preserve">36.1862564086914</t>
@@ -5210,7 +5210,7 @@
     <t xml:space="preserve">36.4903450012207</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8894538879395</t>
+    <t xml:space="preserve">36.8894577026367</t>
   </si>
   <si>
     <t xml:space="preserve">37.8017120361328</t>
@@ -5222,16 +5222,16 @@
     <t xml:space="preserve">37.7827072143555</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6876792907715</t>
+    <t xml:space="preserve">37.6876831054688</t>
   </si>
   <si>
     <t xml:space="preserve">37.9727592468262</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9917678833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3338623046875</t>
+    <t xml:space="preserve">37.9917640686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3338661193848</t>
   </si>
   <si>
     <t xml:space="preserve">38.4098815917969</t>
@@ -5246,7 +5246,7 @@
     <t xml:space="preserve">37.7066879272461</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2198333740234</t>
+    <t xml:space="preserve">38.2198295593262</t>
   </si>
   <si>
     <t xml:space="preserve">38.0107727050781</t>
@@ -5255,10 +5255,10 @@
     <t xml:space="preserve">38.2768478393555</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2578392028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.238842010498</t>
+    <t xml:space="preserve">38.2578430175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2388381958008</t>
   </si>
   <si>
     <t xml:space="preserve">38.5809326171875</t>
@@ -5276,7 +5276,7 @@
     <t xml:space="preserve">39.0940780639648</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5999412536621</t>
+    <t xml:space="preserve">38.5999374389648</t>
   </si>
   <si>
     <t xml:space="preserve">37.7256927490234</t>
@@ -5297,7 +5297,7 @@
     <t xml:space="preserve">39.4741897583008</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8162841796875</t>
+    <t xml:space="preserve">39.8162879943848</t>
   </si>
   <si>
     <t xml:space="preserve">39.9493217468262</t>
@@ -5315,7 +5315,7 @@
     <t xml:space="preserve">39.6452369689941</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3981666564941</t>
+    <t xml:space="preserve">39.3981628417969</t>
   </si>
   <si>
     <t xml:space="preserve">39.3601531982422</t>
@@ -5342,10 +5342,10 @@
     <t xml:space="preserve">38.5619316101074</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9873352050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8923072814941</t>
+    <t xml:space="preserve">39.9873313903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8923034667969</t>
   </si>
   <si>
     <t xml:space="preserve">40.1773834228516</t>
@@ -5372,10 +5372,10 @@
     <t xml:space="preserve">40.9946174621582</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3557205200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5267715454102</t>
+    <t xml:space="preserve">41.3557243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5267677307129</t>
   </si>
   <si>
     <t xml:space="preserve">41.3747291564941</t>
@@ -5387,13 +5387,13 @@
     <t xml:space="preserve">41.6978187561035</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1349411010742</t>
+    <t xml:space="preserve">42.1349449157715</t>
   </si>
   <si>
     <t xml:space="preserve">42.0209121704102</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7548294067383</t>
+    <t xml:space="preserve">41.7548332214355</t>
   </si>
   <si>
     <t xml:space="preserve">42.3820114135742</t>
@@ -5402,7 +5402,7 @@
     <t xml:space="preserve">42.4390258789062</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4580345153809</t>
+    <t xml:space="preserve">42.4580307006836</t>
   </si>
   <si>
     <t xml:space="preserve">42.2869834899902</t>
@@ -5420,7 +5420,7 @@
     <t xml:space="preserve">43.5223350524902</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8761520385742</t>
+    <t xml:space="preserve">42.876148223877</t>
   </si>
   <si>
     <t xml:space="preserve">42.9521751403809</t>
@@ -5432,7 +5432,7 @@
     <t xml:space="preserve">43.0852088928223</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3059921264648</t>
+    <t xml:space="preserve">42.3059883117676</t>
   </si>
   <si>
     <t xml:space="preserve">42.7431144714355</t>
@@ -5453,13 +5453,13 @@
     <t xml:space="preserve">42.9901847839355</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8951568603516</t>
+    <t xml:space="preserve">42.8951530456543</t>
   </si>
   <si>
     <t xml:space="preserve">43.7123908996582</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4653205871582</t>
+    <t xml:space="preserve">43.4653167724609</t>
   </si>
   <si>
     <t xml:space="preserve">44.0354804992676</t>
@@ -5477,19 +5477,19 @@
     <t xml:space="preserve">46.6202163696289</t>
   </si>
   <si>
-    <t xml:space="preserve">46.639217376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6962356567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.582202911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7722587585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2781143188477</t>
+    <t xml:space="preserve">46.6392211914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.696231842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5821990966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7722549438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2781181335449</t>
   </si>
   <si>
     <t xml:space="preserve">46.1070671081543</t>
@@ -5498,7 +5498,7 @@
     <t xml:space="preserve">45.8219871520996</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0310440063477</t>
+    <t xml:space="preserve">46.0310478210449</t>
   </si>
   <si>
     <t xml:space="preserve">45.7839736938477</t>
@@ -5540,7 +5540,7 @@
     <t xml:space="preserve">48.9388694763184</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8438415527344</t>
+    <t xml:space="preserve">48.8438453674316</t>
   </si>
   <si>
     <t xml:space="preserve">48.7963256835938</t>
@@ -70940,7 +70940,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6493287037</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>130651</v>
@@ -70961,6 +70961,32 @@
         <v>1933</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6494097222</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>145409</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>48.6800003051758</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>47.6800003051758</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>47.9799995422363</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>48.4000015258789</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1974</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BGN.MI.xlsx
+++ b/data/BGN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1976" uniqueCount="1976">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1977" uniqueCount="1977">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4795989990234</t>
+    <t xml:space="preserve">17.4796009063721</t>
   </si>
   <si>
     <t xml:space="preserve">BGN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2943077087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7816524505615</t>
+    <t xml:space="preserve">17.2943058013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7816505432129</t>
   </si>
   <si>
     <t xml:space="preserve">16.528413772583</t>
@@ -62,124 +62,124 @@
     <t xml:space="preserve">16.5098838806152</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9422435760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6457710266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1269416809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6760540008545</t>
+    <t xml:space="preserve">16.9422416687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6457691192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1269397735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6760530471802</t>
   </si>
   <si>
     <t xml:space="preserve">15.9601755142212</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0707540512085</t>
+    <t xml:space="preserve">15.0707521438599</t>
   </si>
   <si>
     <t xml:space="preserve">15.0769281387329</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5092887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.540168762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4289884567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6019344329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.194281578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4784030914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2931051254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0213413238525</t>
+    <t xml:space="preserve">15.5092868804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5401706695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4289932250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6019334793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1942844390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.478401184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2931032180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0213384628296</t>
   </si>
   <si>
     <t xml:space="preserve">13.8230895996094</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7180871963501</t>
+    <t xml:space="preserve">13.718090057373</t>
   </si>
   <si>
     <t xml:space="preserve">13.5945587158203</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4580764770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6804342269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5636749267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1745557785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4154396057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0022134780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8477983474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.385157585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4098615646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1936836242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4963359832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1813325881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.323390007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3357439041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5210390090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8607473373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2436962127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5710506439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4969339370728</t>
+    <t xml:space="preserve">12.4580783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6804304122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5636768341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1745538711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4154386520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0022106170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8477964401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3851537704468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4098625183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1936855316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4963321685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1813306808472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3233919143677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3357419967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5210399627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8607482910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.243691444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5710496902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4969348907471</t>
   </si>
   <si>
     <t xml:space="preserve">15.4351673126221</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4413461685181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.323992729187</t>
+    <t xml:space="preserve">15.4413452148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3239889144897</t>
   </si>
   <si>
     <t xml:space="preserve">16.0157623291016</t>
@@ -188,22 +188,22 @@
     <t xml:space="preserve">16.201057434082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2937049865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1578216552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3431167602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8489971160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8922319412231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6081085205078</t>
+    <t xml:space="preserve">16.2937088012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1578235626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3431205749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8489933013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8922338485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6081113815308</t>
   </si>
   <si>
     <t xml:space="preserve">15.9354677200317</t>
@@ -215,34 +215,34 @@
     <t xml:space="preserve">16.0095863342285</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8675260543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8298673629761</t>
+    <t xml:space="preserve">15.867525100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8298692703247</t>
   </si>
   <si>
     <t xml:space="preserve">14.8854541778564</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6569232940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.941047668457</t>
+    <t xml:space="preserve">14.6569261550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9410429000854</t>
   </si>
   <si>
     <t xml:space="preserve">15.3981094360352</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5339918136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8737001419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9478187561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1145858764648</t>
+    <t xml:space="preserve">15.5339889526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8736982345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9478197097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1145839691162</t>
   </si>
   <si>
     <t xml:space="preserve">16.083703994751</t>
@@ -251,58 +251,58 @@
     <t xml:space="preserve">16.0713520050049</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1084098815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2072334289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0589981079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2998867034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1701755523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1207637786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7316436767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3795766830444</t>
+    <t xml:space="preserve">16.1084079742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2072353363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0589962005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2998828887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1701774597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1207618713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7316427230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3795785903931</t>
   </si>
   <si>
     <t xml:space="preserve">15.1201629638672</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8916349411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7063388824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6383962631226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6075096130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2986831665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4530982971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6692762374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3419218063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.366626739502</t>
+    <t xml:space="preserve">14.8916339874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.706335067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6383924484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6075115203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2986860275269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4530973434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6692771911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3419208526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3666276931763</t>
   </si>
   <si>
     <t xml:space="preserve">14.3913335800171</t>
@@ -314,91 +314,91 @@
     <t xml:space="preserve">14.5537919998169</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8142623901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9640340805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5110206604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5956716537476</t>
+    <t xml:space="preserve">14.8142642974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9640312194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5110235214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5956745147705</t>
   </si>
   <si>
     <t xml:space="preserve">15.3742733001709</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3286933898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1138029098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0096139907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.055196762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.211480140686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3547382354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3026447296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.257061958313</t>
+    <t xml:space="preserve">15.3286924362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1137990951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0096168518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0551986694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2114782333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3547401428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3026418685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2570638656616</t>
   </si>
   <si>
     <t xml:space="preserve">14.8533315658569</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0979709625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2058563232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9649229049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.945384979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1993436813354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6616811752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8375005722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1565742492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5733261108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8737564086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6690788269043</t>
+    <t xml:space="preserve">14.0979681015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2058591842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9649209976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.945387840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1993455886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6616792678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.837495803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1565704345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5733270645142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8737573623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6690816879272</t>
   </si>
   <si>
     <t xml:space="preserve">11.7341985702515</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6560564041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6821041107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6039619445801</t>
+    <t xml:space="preserve">11.6560554504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6821022033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6039628982544</t>
   </si>
   <si>
     <t xml:space="preserve">11.2002334594727</t>
@@ -407,67 +407,67 @@
     <t xml:space="preserve">10.8160400390625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.431845664978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7444105148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2588405609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.923038482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3137454986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2616500854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5286331176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.567702293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6588668823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3723497390747</t>
+    <t xml:space="preserve">10.4318466186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7444095611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2588396072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.923041343689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3137435913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2616510391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5286340713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5677032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6588687896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3723516464233</t>
   </si>
   <si>
     <t xml:space="preserve">12.5221214294434</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5416555404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3397922515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.502589225769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2551393508911</t>
+    <t xml:space="preserve">12.5416574478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3397941589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5025863647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2551374435425</t>
   </si>
   <si>
     <t xml:space="preserve">12.4895629882812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2421140670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0337390899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8188505172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6300106048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4281435012817</t>
+    <t xml:space="preserve">12.242115020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0337371826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8188514709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6300086975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4281454086304</t>
   </si>
   <si>
     <t xml:space="preserve">11.3825626373291</t>
@@ -476,22 +476,22 @@
     <t xml:space="preserve">11.8579206466675</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9946689605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1835117340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2030448913574</t>
+    <t xml:space="preserve">11.9946699142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1835088729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2030439376831</t>
   </si>
   <si>
     <t xml:space="preserve">12.0532741546631</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9490871429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7928037643433</t>
+    <t xml:space="preserve">11.9490842819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7928047180176</t>
   </si>
   <si>
     <t xml:space="preserve">11.525821685791</t>
@@ -500,55 +500,55 @@
     <t xml:space="preserve">11.7667570114136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4411678314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3630256652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5583810806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7797822952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5388441085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7472238540649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.695125579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9425745010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1314163208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1379261016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4114217758179</t>
+    <t xml:space="preserve">11.4411697387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3630275726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5583801269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7797794342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5388450622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7472219467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6951274871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9425754547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1314134597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1379280090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4114198684692</t>
   </si>
   <si>
     <t xml:space="preserve">12.4830503463745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.665379524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8021268844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3788633346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1183929443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.124903678894</t>
+    <t xml:space="preserve">12.6653814315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8021278381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3788623809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1183919906616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.124906539917</t>
   </si>
   <si>
     <t xml:space="preserve">12.2876987457275</t>
@@ -557,19 +557,19 @@
     <t xml:space="preserve">11.870945930481</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7016372680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8514108657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9165287017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.252329826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1937198638916</t>
+    <t xml:space="preserve">11.701639175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8514089584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9165267944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.252326965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1937217712402</t>
   </si>
   <si>
     <t xml:space="preserve">11.1481399536133</t>
@@ -578,19 +578,19 @@
     <t xml:space="preserve">11.0830221176147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1220932006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1741857528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1090688705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2848863601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1351156234741</t>
+    <t xml:space="preserve">11.122091293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.174186706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1090698242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2848873138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1351165771484</t>
   </si>
   <si>
     <t xml:space="preserve">11.0765113830566</t>
@@ -599,43 +599,43 @@
     <t xml:space="preserve">11.1872110366821</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0244169235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0179042816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6430339813232</t>
+    <t xml:space="preserve">11.0244140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0179061889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6430330276489</t>
   </si>
   <si>
     <t xml:space="preserve">11.5779161453247</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9100160598755</t>
+    <t xml:space="preserve">11.9100151062012</t>
   </si>
   <si>
     <t xml:space="preserve">12.1769981384277</t>
   </si>
   <si>
-    <t xml:space="preserve">12.29421043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4309549331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9779453277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.036548614502</t>
+    <t xml:space="preserve">12.2942113876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4309568405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9779462814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0365505218506</t>
   </si>
   <si>
     <t xml:space="preserve">13.3816738128662</t>
   </si>
   <si>
-    <t xml:space="preserve">13.564003944397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.414234161377</t>
+    <t xml:space="preserve">13.5640029907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4142322540283</t>
   </si>
   <si>
     <t xml:space="preserve">13.1732978820801</t>
@@ -644,70 +644,70 @@
     <t xml:space="preserve">13.0560855865479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9258527755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8281745910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3295783996582</t>
+    <t xml:space="preserve">12.9258508682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8281755447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3295803070068</t>
   </si>
   <si>
     <t xml:space="preserve">13.7984266281128</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5444669723511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8830804824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8309841156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9481983184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.889594078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1240167617798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4923734664917</t>
+    <t xml:space="preserve">13.5444679260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8830766677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8309879302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9481992721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.889591217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1240148544312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4923725128174</t>
   </si>
   <si>
     <t xml:space="preserve">12.9388751983643</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9323625564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8672466278076</t>
+    <t xml:space="preserve">12.9323635101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8672456741333</t>
   </si>
   <si>
     <t xml:space="preserve">12.9714326858521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9909706115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7760820388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.795615196228</t>
+    <t xml:space="preserve">12.9909696578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7760791778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7956161499023</t>
   </si>
   <si>
     <t xml:space="preserve">12.7304973602295</t>
   </si>
   <si>
-    <t xml:space="preserve">12.743522644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4691362380981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2896184921265</t>
+    <t xml:space="preserve">12.7435216903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4691381454468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.289623260498</t>
   </si>
   <si>
     <t xml:space="preserve">15.8887033462524</t>
@@ -716,184 +716,184 @@
     <t xml:space="preserve">15.5761394500732</t>
   </si>
   <si>
-    <t xml:space="preserve">15.361252784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4784641265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0747318267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1854295730591</t>
+    <t xml:space="preserve">15.3612489700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4784622192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0747337341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1854343414307</t>
   </si>
   <si>
     <t xml:space="preserve">14.8989133834839</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8793821334839</t>
+    <t xml:space="preserve">14.8793802261353</t>
   </si>
   <si>
     <t xml:space="preserve">14.9575204849243</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9770574569702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0031003952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7817058563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5863513946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7556562423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8598432540894</t>
+    <t xml:space="preserve">14.9770584106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0031042098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7817077636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5863494873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7556571960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.859842300415</t>
   </si>
   <si>
     <t xml:space="preserve">15.3417139053345</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4459047317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8403100967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2700881958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5305557250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4133453369141</t>
+    <t xml:space="preserve">15.4459018707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8403091430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2700834274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5305547714233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4133434295654</t>
   </si>
   <si>
     <t xml:space="preserve">15.3482265472412</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5631141662598</t>
+    <t xml:space="preserve">15.5631160736084</t>
   </si>
   <si>
     <t xml:space="preserve">16.5138301849365</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6570911407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5659255981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1231231689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0514965057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6803283691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7454433441162</t>
+    <t xml:space="preserve">16.6570930480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5659275054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1231250762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0514984130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6803255081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7454471588135</t>
   </si>
   <si>
     <t xml:space="preserve">15.7584686279297</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0356616973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3352022171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2375268936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4328804016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2208042144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2924346923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1491718292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9538202285767</t>
+    <t xml:space="preserve">15.0356636047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3352031707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2375249862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4328775405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2208023071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2924327850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1491756439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9538230895996</t>
   </si>
   <si>
     <t xml:space="preserve">16.1752185821533</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8626565933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5566024780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1593866348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2245044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8468217849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1658973693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4003190994263</t>
+    <t xml:space="preserve">15.8626575469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.556601524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1593856811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2245035171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8468198776245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1658945083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4003210067749</t>
   </si>
   <si>
     <t xml:space="preserve">15.3091564178467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6021862030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6217203140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6738138198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5500917434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3677625656128</t>
+    <t xml:space="preserve">15.6021871566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6217193603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6738119125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5500926971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3677616119385</t>
   </si>
   <si>
     <t xml:space="preserve">15.3938083648682</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1398506164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1072912216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.081244468689</t>
+    <t xml:space="preserve">15.1398487091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1072931289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0812454223633</t>
   </si>
   <si>
     <t xml:space="preserve">15.6152086257935</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6282339096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5435800552368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7975378036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9342861175537</t>
+    <t xml:space="preserve">15.628231048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5435838699341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7975397109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9342851638794</t>
   </si>
   <si>
     <t xml:space="preserve">16.2012672424316</t>
@@ -902,22 +902,22 @@
     <t xml:space="preserve">16.4422035217285</t>
   </si>
   <si>
-    <t xml:space="preserve">16.377082824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.279411315918</t>
+    <t xml:space="preserve">16.3770847320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2794075012207</t>
   </si>
   <si>
     <t xml:space="preserve">16.1426639556885</t>
   </si>
   <si>
-    <t xml:space="preserve">16.481273651123</t>
+    <t xml:space="preserve">16.4812698364258</t>
   </si>
   <si>
     <t xml:space="preserve">16.6049976348877</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2338275909424</t>
+    <t xml:space="preserve">16.2338256835938</t>
   </si>
   <si>
     <t xml:space="preserve">17.2561740875244</t>
@@ -926,25 +926,25 @@
     <t xml:space="preserve">17.2691974639893</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1585006713867</t>
+    <t xml:space="preserve">17.1584968566895</t>
   </si>
   <si>
     <t xml:space="preserve">17.1454734802246</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1845474243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1389636993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6468772888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6273441314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3892230987549</t>
+    <t xml:space="preserve">17.1845417022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1389617919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6468811035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6273403167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.389217376709</t>
   </si>
   <si>
     <t xml:space="preserve">18.1678199768066</t>
@@ -953,52 +953,52 @@
     <t xml:space="preserve">18.1027011871338</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3501491546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1352634429932</t>
+    <t xml:space="preserve">18.3501510620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1352596282959</t>
   </si>
   <si>
     <t xml:space="preserve">18.4934062957764</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0896778106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2264251708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.858814239502</t>
+    <t xml:space="preserve">18.0896797180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2264270782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8588066101074</t>
   </si>
   <si>
     <t xml:space="preserve">18.8723430633545</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6896419525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6422729492188</t>
+    <t xml:space="preserve">18.6896457672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6422748565674</t>
   </si>
   <si>
     <t xml:space="preserve">18.513708114624</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8370399475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6543388366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3836688995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9047050476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9317722320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5393009185791</t>
+    <t xml:space="preserve">17.8370380401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6543350219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3836708068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9047069549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.931770324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5393028259277</t>
   </si>
   <si>
     <t xml:space="preserve">17.5460681915283</t>
@@ -1007,43 +1007,43 @@
     <t xml:space="preserve">17.9926738739014</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6761074066162</t>
+    <t xml:space="preserve">18.6761093139648</t>
   </si>
   <si>
     <t xml:space="preserve">18.926477432251</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8046798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9806118011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6219749450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0400428771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3377723693848</t>
+    <t xml:space="preserve">18.8046779632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9806098937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.621976852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3377742767334</t>
   </si>
   <si>
     <t xml:space="preserve">18.2092056274414</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9994411468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.864107131958</t>
+    <t xml:space="preserve">17.9994373321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8640995025635</t>
   </si>
   <si>
     <t xml:space="preserve">17.8032035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0062084197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4054412841797</t>
+    <t xml:space="preserve">18.0062065124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4054393768311</t>
   </si>
   <si>
     <t xml:space="preserve">18.0603408813477</t>
@@ -1052,22 +1052,22 @@
     <t xml:space="preserve">17.6340351104736</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2430381774902</t>
+    <t xml:space="preserve">18.2430400848389</t>
   </si>
   <si>
     <t xml:space="preserve">18.2701072692871</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6490440368652</t>
+    <t xml:space="preserve">18.6490421295166</t>
   </si>
   <si>
     <t xml:space="preserve">18.4528102874756</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7031745910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4595718383789</t>
+    <t xml:space="preserve">18.7031726837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4595756530762</t>
   </si>
   <si>
     <t xml:space="preserve">19.1024112701416</t>
@@ -1082,10 +1082,10 @@
     <t xml:space="preserve">18.77760887146</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8791122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1362495422363</t>
+    <t xml:space="preserve">18.8791103363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1362457275391</t>
   </si>
   <si>
     <t xml:space="preserve">19.0415115356445</t>
@@ -1094,31 +1094,31 @@
     <t xml:space="preserve">19.1836128234863</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3730773925781</t>
+    <t xml:space="preserve">19.3730812072754</t>
   </si>
   <si>
     <t xml:space="preserve">19.2918796539307</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8264465332031</t>
+    <t xml:space="preserve">19.8264503479004</t>
   </si>
   <si>
     <t xml:space="preserve">19.9414825439453</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3001194000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5166549682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0971164703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9956169128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1241855621338</t>
+    <t xml:space="preserve">20.3001155853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5166530609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0971183776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9956188201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1241836547852</t>
   </si>
   <si>
     <t xml:space="preserve">20.1444854736328</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">20.6384544372559</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2392177581787</t>
+    <t xml:space="preserve">20.2392196655273</t>
   </si>
   <si>
     <t xml:space="preserve">19.8941173553467</t>
@@ -1139,28 +1139,28 @@
     <t xml:space="preserve">19.7587833404541</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9211845397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9008827209473</t>
+    <t xml:space="preserve">19.9211864471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9008846282959</t>
   </si>
   <si>
     <t xml:space="preserve">19.7993831634521</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7655467987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8129138946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4813480377197</t>
+    <t xml:space="preserve">19.7655487060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8129177093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4813461303711</t>
   </si>
   <si>
     <t xml:space="preserve">19.5828475952148</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4881153106689</t>
+    <t xml:space="preserve">19.4881114959717</t>
   </si>
   <si>
     <t xml:space="preserve">19.2851123809814</t>
@@ -1169,22 +1169,22 @@
     <t xml:space="preserve">18.7640743255615</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7573070526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5949115753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8452758789062</t>
+    <t xml:space="preserve">18.7573089599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5949077606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8452777862549</t>
   </si>
   <si>
     <t xml:space="preserve">18.8655776977539</t>
   </si>
   <si>
-    <t xml:space="preserve">18.534008026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0144462585449</t>
+    <t xml:space="preserve">18.5340099334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0144443511963</t>
   </si>
   <si>
     <t xml:space="preserve">19.2242107391357</t>
@@ -1193,49 +1193,49 @@
     <t xml:space="preserve">19.1700782775879</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2512798309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1971492767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4475173950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1633129119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2648143768311</t>
+    <t xml:space="preserve">19.251277923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1971454620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4475154876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1633148193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2648105621338</t>
   </si>
   <si>
     <t xml:space="preserve">19.4678134918213</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2580432891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8602828979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8670520782471</t>
+    <t xml:space="preserve">19.2580451965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8602848052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8670501708984</t>
   </si>
   <si>
     <t xml:space="preserve">20.0159187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">19.420446395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5693130493164</t>
+    <t xml:space="preserve">19.4204444885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.569314956665</t>
   </si>
   <si>
     <t xml:space="preserve">19.549015045166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4272117614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3663120269775</t>
+    <t xml:space="preserve">19.4272136688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3663139343262</t>
   </si>
   <si>
     <t xml:space="preserve">19.4136810302734</t>
@@ -1244,16 +1244,16 @@
     <t xml:space="preserve">19.3527812957764</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5016441345215</t>
+    <t xml:space="preserve">19.5016498565674</t>
   </si>
   <si>
     <t xml:space="preserve">18.9400100708008</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8114414215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8858757019043</t>
+    <t xml:space="preserve">18.8114433288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8858776092529</t>
   </si>
   <si>
     <t xml:space="preserve">19.2783451080322</t>
@@ -1262,52 +1262,52 @@
     <t xml:space="preserve">19.1565437316895</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0685787200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2106800079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1091785430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3189487457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3324813842773</t>
+    <t xml:space="preserve">19.0685768127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2106781005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1091766357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3189449310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3324794769287</t>
   </si>
   <si>
     <t xml:space="preserve">19.2309799194336</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6572799682617</t>
+    <t xml:space="preserve">19.6572818756104</t>
   </si>
   <si>
     <t xml:space="preserve">20.1106510162354</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9820823669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7858505249023</t>
+    <t xml:space="preserve">19.9820861816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7858486175537</t>
   </si>
   <si>
     <t xml:space="preserve">19.5354824066162</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9482460021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5760822296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6166801452637</t>
+    <t xml:space="preserve">19.9482479095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.576078414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6166820526123</t>
   </si>
   <si>
     <t xml:space="preserve">19.5557804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3460121154785</t>
+    <t xml:space="preserve">19.3460140228271</t>
   </si>
   <si>
     <t xml:space="preserve">19.6911163330078</t>
@@ -1316,22 +1316,22 @@
     <t xml:space="preserve">19.6775817871094</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2986469268799</t>
+    <t xml:space="preserve">19.2986488342285</t>
   </si>
   <si>
     <t xml:space="preserve">19.1903800964355</t>
   </si>
   <si>
-    <t xml:space="preserve">19.312183380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.791145324707</t>
+    <t xml:space="preserve">19.3121776580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7911415100098</t>
   </si>
   <si>
     <t xml:space="preserve">18.8182106018066</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9670791625977</t>
+    <t xml:space="preserve">18.967077255249</t>
   </si>
   <si>
     <t xml:space="preserve">18.7708435058594</t>
@@ -1340,16 +1340,16 @@
     <t xml:space="preserve">18.4663429260254</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1889057159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6084423065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1497764587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1768493652344</t>
+    <t xml:space="preserve">18.188907623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6084442138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1497783660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1768455505371</t>
   </si>
   <si>
     <t xml:space="preserve">19.4745826721191</t>
@@ -1358,16 +1358,16 @@
     <t xml:space="preserve">20.0294494628906</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0835857391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5301856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5031204223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8008575439453</t>
+    <t xml:space="preserve">20.0835819244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5301876068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.503116607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.800853729248</t>
   </si>
   <si>
     <t xml:space="preserve">20.7602558135986</t>
@@ -1376,25 +1376,25 @@
     <t xml:space="preserve">20.7196559906006</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8685245513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7061195373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2459850311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4083881378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3136520385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8805847167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8926448822021</t>
+    <t xml:space="preserve">20.868522644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7061214447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2459869384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4083862304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3136539459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8805809020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8926429748535</t>
   </si>
   <si>
     <t xml:space="preserve">19.0550441741943</t>
@@ -1406,40 +1406,40 @@
     <t xml:space="preserve">18.2024402618408</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2565765380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5813751220703</t>
+    <t xml:space="preserve">18.2565727233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5813732147217</t>
   </si>
   <si>
     <t xml:space="preserve">18.5407752990723</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4866409301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4189739227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5272426605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.473108291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9859046936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4460430145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.662576675415</t>
+    <t xml:space="preserve">18.4866428375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4189758300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5272407531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4731063842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9859027862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4460411071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6625785827637</t>
   </si>
   <si>
     <t xml:space="preserve">18.5678443908691</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7437782287598</t>
+    <t xml:space="preserve">18.7437801361084</t>
   </si>
   <si>
     <t xml:space="preserve">18.7302436828613</t>
@@ -1448,58 +1448,58 @@
     <t xml:space="preserve">18.3783760070801</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8505687713623</t>
+    <t xml:space="preserve">17.8505706787109</t>
   </si>
   <si>
     <t xml:space="preserve">17.7558364868164</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7287731170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9723720550537</t>
+    <t xml:space="preserve">17.7287693023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9723739624023</t>
   </si>
   <si>
     <t xml:space="preserve">18.0671062469482</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1483058929443</t>
+    <t xml:space="preserve">18.148307800293</t>
   </si>
   <si>
     <t xml:space="preserve">18.2159748077393</t>
   </si>
   <si>
-    <t xml:space="preserve">18.324239730835</t>
+    <t xml:space="preserve">18.3242435455322</t>
   </si>
   <si>
     <t xml:space="preserve">18.3513088226318</t>
   </si>
   <si>
-    <t xml:space="preserve">18.364839553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7167110443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.797908782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9061756134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1618366241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1212406158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.82350730896</t>
+    <t xml:space="preserve">18.3648414611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7167091369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7979106903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9061794281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1618385314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1212425231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8235034942627</t>
   </si>
   <si>
     <t xml:space="preserve">17.6205024719238</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6611061096191</t>
+    <t xml:space="preserve">17.6611042022705</t>
   </si>
   <si>
     <t xml:space="preserve">17.1738986968994</t>
@@ -1508,76 +1508,76 @@
     <t xml:space="preserve">17.0520992279053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7814331054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7600517272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8028087615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5605316162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7030448913574</t>
+    <t xml:space="preserve">16.7814311981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7600536346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8028125762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5605297088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7030467987061</t>
   </si>
   <si>
     <t xml:space="preserve">16.3039970397949</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2066116333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2802515029907</t>
+    <t xml:space="preserve">15.2066135406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2802505493164</t>
   </si>
   <si>
     <t xml:space="preserve">14.8503198623657</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8218173980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5344038009644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3206262588501</t>
+    <t xml:space="preserve">14.8218145370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.53440284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3206281661987</t>
   </si>
   <si>
     <t xml:space="preserve">14.8930759429932</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4631452560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8336906433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3491315841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9477043151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8479413986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8621940612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9192008972168</t>
+    <t xml:space="preserve">15.4631462097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8336925506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3491306304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9477052688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8479433059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8621959686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9192028045654</t>
   </si>
   <si>
     <t xml:space="preserve">15.7054252624512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7339305877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7196750640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3633813858032</t>
+    <t xml:space="preserve">15.7339296340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7196769714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3633852005005</t>
   </si>
   <si>
     <t xml:space="preserve">15.5058994293213</t>
@@ -1589,118 +1589,118 @@
     <t xml:space="preserve">15.4488916397095</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9500818252563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9358320236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.178108215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5629053115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6484174728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8906955718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0189666748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4346408843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3776340484619</t>
+    <t xml:space="preserve">14.950080871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9358291625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1781091690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5629062652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6484184265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.890697479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0189647674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4346389770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.377631187439</t>
   </si>
   <si>
     <t xml:space="preserve">15.4916477203369</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5201511383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7909374237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7766828536987</t>
+    <t xml:space="preserve">15.5201501846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7909364700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7766819000244</t>
   </si>
   <si>
     <t xml:space="preserve">15.6056623458862</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4750194549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2469902038574</t>
+    <t xml:space="preserve">16.4750213623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2469921112061</t>
   </si>
   <si>
     <t xml:space="preserve">16.1329765319824</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4465160369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5035228729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9619569778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0474662780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2184867858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2042369842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1614799499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.74817943573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9049482345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2754936218262</t>
+    <t xml:space="preserve">16.4465141296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5035266876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9619560241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0474700927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2184906005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2042331695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1614818572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7481803894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9049501419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2754974365234</t>
   </si>
   <si>
     <t xml:space="preserve">16.4037609100342</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3325004577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2636194229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0783500671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.30637550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2921237945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5486574172974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6769208908081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6175346374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7885589599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8598155975342</t>
+    <t xml:space="preserve">16.3325023651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2636203765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0783462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3063716888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2921209335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5486555099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6769237518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6175384521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7885570526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8598175048828</t>
   </si>
   <si>
     <t xml:space="preserve">17.3443756103516</t>
@@ -1712,55 +1712,55 @@
     <t xml:space="preserve">17.1020965576172</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8764486312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6911735534668</t>
+    <t xml:space="preserve">15.8764448165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6911745071411</t>
   </si>
   <si>
     <t xml:space="preserve">15.6626710891724</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9643306732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7933130264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3515110015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2161159515381</t>
+    <t xml:space="preserve">14.9643335342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7933120727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.351508140564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.216118812561</t>
   </si>
   <si>
     <t xml:space="preserve">14.3372583389282</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7220525741577</t>
+    <t xml:space="preserve">14.7220554351807</t>
   </si>
   <si>
     <t xml:space="preserve">14.4227676391602</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0593461990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.539158821106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2042446136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7268104553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3776407241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4203968048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2850036621094</t>
+    <t xml:space="preserve">14.05934715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5391607284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2042455673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7268085479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3776435852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4203977584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2850046157837</t>
   </si>
   <si>
     <t xml:space="preserve">12.4061460494995</t>
@@ -1772,61 +1772,61 @@
     <t xml:space="preserve">12.3705177307129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9049577713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8622007369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9334602355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.147234916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.275502204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1187314987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0688514709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5462856292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1116075515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7838172912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7339363098145</t>
+    <t xml:space="preserve">12.904956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8621997833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.93346118927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.14723777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2755012512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1187334060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0688524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5462846755981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1116065979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7838153839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7339372634888</t>
   </si>
   <si>
     <t xml:space="preserve">12.6698036193848</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9192085266113</t>
+    <t xml:space="preserve">12.9192066192627</t>
   </si>
   <si>
     <t xml:space="preserve">12.9548387527466</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2469997406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5961675643921</t>
+    <t xml:space="preserve">13.246997833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5961685180664</t>
   </si>
   <si>
     <t xml:space="preserve">14.1092290878296</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9453325271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8812017440796</t>
+    <t xml:space="preserve">13.9453344345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8811988830566</t>
   </si>
   <si>
     <t xml:space="preserve">13.8883275985718</t>
@@ -1838,232 +1838,232 @@
     <t xml:space="preserve">14.2232437133789</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0878524780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3681383132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4678993225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1258573532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.969090461731</t>
+    <t xml:space="preserve">14.0878534317017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3681402206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4679021835327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1258602142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9690895080566</t>
   </si>
   <si>
     <t xml:space="preserve">13.4892797470093</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6317939758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2327480316162</t>
+    <t xml:space="preserve">13.6317958831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2327470779419</t>
   </si>
   <si>
     <t xml:space="preserve">13.3966417312622</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8265714645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5344095230103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1044816970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9975938796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6104183197021</t>
+    <t xml:space="preserve">12.8265705108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5344114303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1044788360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9975919723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6104192733765</t>
   </si>
   <si>
     <t xml:space="preserve">13.7529354095459</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6389198303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1448602676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3230056762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2018642425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947393417358</t>
+    <t xml:space="preserve">13.6389207839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1448583602905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3230047225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2018671035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947383880615</t>
   </si>
   <si>
     <t xml:space="preserve">13.895453453064</t>
   </si>
   <si>
-    <t xml:space="preserve">14.39426612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5937881469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.707802772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5082778930664</t>
+    <t xml:space="preserve">14.3942642211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.593789100647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7078037261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5082788467407</t>
   </si>
   <si>
     <t xml:space="preserve">14.6935510635376</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8075656890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6365461349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7648105621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7363061904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6793022155762</t>
+    <t xml:space="preserve">14.8075637817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6365442276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7648067474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7363052368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6792974472046</t>
   </si>
   <si>
     <t xml:space="preserve">14.265998840332</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5367841720581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2945041656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5510330200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1923599243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9785842895508</t>
+    <t xml:space="preserve">14.5367813110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2945013046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5510339736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1923589706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9785861968994</t>
   </si>
   <si>
     <t xml:space="preserve">15.277871131897</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2493696212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2208671569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4061403274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8194370269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8051862716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6341667175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5914077758789</t>
+    <t xml:space="preserve">15.2493686676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2208662033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.406138420105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8194398880005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8051891326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.634165763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5914115905762</t>
   </si>
   <si>
     <t xml:space="preserve">16.4322643280029</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6032848358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7172966003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7743053436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8170623779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0308380126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1591014862061</t>
+    <t xml:space="preserve">16.6032867431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7173004150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7743072509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8170604705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0308361053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1591033935547</t>
   </si>
   <si>
     <t xml:space="preserve">17.2588653564453</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3158702850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4583911895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4726409912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9714546203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7861766815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9286956787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0569648742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0854663848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5581493377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5866565704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2018585205078</t>
+    <t xml:space="preserve">17.3158721923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4583892822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4726448059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9714527130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7861785888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9286994934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0569591522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0854644775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5581512451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5866527557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2018566131592</t>
   </si>
   <si>
     <t xml:space="preserve">17.4298877716064</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5296478271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4868946075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7196521759033</t>
+    <t xml:space="preserve">17.5296497344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4868927001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.719654083252</t>
   </si>
   <si>
     <t xml:space="preserve">17.8548011779785</t>
   </si>
   <si>
-    <t xml:space="preserve">17.299186706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2241039276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2691497802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.149019241333</t>
+    <t xml:space="preserve">17.2991847991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.224100112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2691516876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1490173339844</t>
   </si>
   <si>
     <t xml:space="preserve">16.7435684204102</t>
   </si>
   <si>
-    <t xml:space="preserve">16.878719329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9237689971924</t>
+    <t xml:space="preserve">16.8787174224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.923770904541</t>
   </si>
   <si>
     <t xml:space="preserve">16.6985187530518</t>
@@ -2075,67 +2075,67 @@
     <t xml:space="preserve">17.5394515991211</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1640338897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0589179992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4343318939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8247699737549</t>
+    <t xml:space="preserve">17.1640357971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0589160919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4343338012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8247680664062</t>
   </si>
   <si>
     <t xml:space="preserve">17.9298839569092</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8397827148438</t>
+    <t xml:space="preserve">17.8397846221924</t>
   </si>
   <si>
     <t xml:space="preserve">17.749683380127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9449024200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.665699005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8458995819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.17626953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3714809417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0561351776123</t>
+    <t xml:space="preserve">17.9449043273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6657009124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8459014892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1762657165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3714847564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.056131362915</t>
   </si>
   <si>
     <t xml:space="preserve">19.131217956543</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4165325164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1462326049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0110855102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2213172912598</t>
+    <t xml:space="preserve">19.4165306091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1462345123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0110836029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2213153839111</t>
   </si>
   <si>
     <t xml:space="preserve">19.7318820953369</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7769355773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7919502258301</t>
+    <t xml:space="preserve">19.7769317626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7919483184814</t>
   </si>
   <si>
     <t xml:space="preserve">19.8069629669189</t>
@@ -2150,28 +2150,28 @@
     <t xml:space="preserve">20.2574653625488</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1373329162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1823825836182</t>
+    <t xml:space="preserve">20.1373310089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1823806762695</t>
   </si>
   <si>
     <t xml:space="preserve">19.8970680236816</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0472316741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1523494720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.017204284668</t>
+    <t xml:space="preserve">20.0472354888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1523475646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0171985626221</t>
   </si>
   <si>
     <t xml:space="preserve">19.6567993164062</t>
   </si>
   <si>
-    <t xml:space="preserve">19.821985244751</t>
+    <t xml:space="preserve">19.8219814300537</t>
   </si>
   <si>
     <t xml:space="preserve">19.6868324279785</t>
@@ -2180,49 +2180,49 @@
     <t xml:space="preserve">19.8369998931885</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9421157836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3325462341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5817165374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4916133880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6718158721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7168674468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7619152069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2875003814697</t>
+    <t xml:space="preserve">19.9421138763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3325481414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.581714630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4916172027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.671817779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7168655395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7619171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2874984741211</t>
   </si>
   <si>
     <t xml:space="preserve">19.9120845794678</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1223163604736</t>
+    <t xml:space="preserve">20.122314453125</t>
   </si>
   <si>
     <t xml:space="preserve">20.0622482299805</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3025150299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5728130340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6629180908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.993278503418</t>
+    <t xml:space="preserve">20.3025169372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5728149414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6629161834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9932804107666</t>
   </si>
   <si>
     <t xml:space="preserve">21.1434459686279</t>
@@ -2231,7 +2231,7 @@
     <t xml:space="preserve">21.1584663391113</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3536834716797</t>
+    <t xml:space="preserve">21.3536815643311</t>
   </si>
   <si>
     <t xml:space="preserve">21.0082988739014</t>
@@ -2240,19 +2240,19 @@
     <t xml:space="preserve">21.2635822296143</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2936134338379</t>
+    <t xml:space="preserve">21.2936172485352</t>
   </si>
   <si>
     <t xml:space="preserve">21.4287643432617</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6089668273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5338821411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9782657623291</t>
+    <t xml:space="preserve">21.6089649200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5338802337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9782638549805</t>
   </si>
   <si>
     <t xml:space="preserve">20.8881645202637</t>
@@ -2261,40 +2261,40 @@
     <t xml:space="preserve">21.233549118042</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2485637664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1734828948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6478958129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6328811645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7680339813232</t>
+    <t xml:space="preserve">21.2485618591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1734848022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6479015350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6328792572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7680320739746</t>
   </si>
   <si>
     <t xml:space="preserve">21.083381652832</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7980632781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8670330047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7229824066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2035160064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.308629989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4888324737549</t>
+    <t xml:space="preserve">20.7980670928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8670349121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7229804992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2035140991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3086280822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4888305664062</t>
   </si>
   <si>
     <t xml:space="preserve">21.5639133453369</t>
@@ -2303,19 +2303,19 @@
     <t xml:space="preserve">21.1134147644043</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3837127685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3236465454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5789318084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8191986083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8492317199707</t>
+    <t xml:space="preserve">21.3837146759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3236484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.578929901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8192005157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8492336273193</t>
   </si>
   <si>
     <t xml:space="preserve">21.954345703125</t>
@@ -2324,10 +2324,10 @@
     <t xml:space="preserve">22.5850486755371</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4799327850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6601314544678</t>
+    <t xml:space="preserve">22.4799308776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6601276397705</t>
   </si>
   <si>
     <t xml:space="preserve">23.1256446838379</t>
@@ -2336,55 +2336,55 @@
     <t xml:space="preserve">23.3208618164062</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0805969238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2007274627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3058490753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4259815216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6962776184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9215316772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7263145446777</t>
+    <t xml:space="preserve">23.0805950164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2007255554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3058471679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4259796142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6962757110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9215297698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7263126373291</t>
   </si>
   <si>
     <t xml:space="preserve">23.6662464141846</t>
   </si>
   <si>
-    <t xml:space="preserve">23.90651512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2908306121826</t>
+    <t xml:space="preserve">23.9065093994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.290828704834</t>
   </si>
   <si>
     <t xml:space="preserve">23.3959465026855</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2758121490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0956134796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4949493408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6300945281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5249786376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0355472564697</t>
+    <t xml:space="preserve">23.2758140563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0956153869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.494945526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6300983428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5249805450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0355453491211</t>
   </si>
   <si>
     <t xml:space="preserve">22.9454441070557</t>
@@ -2393,31 +2393,31 @@
     <t xml:space="preserve">22.5399971008301</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6000652313232</t>
+    <t xml:space="preserve">22.6000633239746</t>
   </si>
   <si>
     <t xml:space="preserve">22.645112991333</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7352161407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2096309661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1946144104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1045150756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1795997619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7290992736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0594615936279</t>
+    <t xml:space="preserve">22.7352123260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2096328735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.194616317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.104513168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1795978546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.729097366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0594635009766</t>
   </si>
   <si>
     <t xml:space="preserve">21.7441139221191</t>
@@ -2426,16 +2426,16 @@
     <t xml:space="preserve">21.5939464569092</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2785968780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0294322967529</t>
+    <t xml:space="preserve">21.2785987854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0294303894043</t>
   </si>
   <si>
     <t xml:space="preserve">22.7652473449707</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7051773071289</t>
+    <t xml:space="preserve">22.7051830291748</t>
   </si>
   <si>
     <t xml:space="preserve">22.9904975891113</t>
@@ -2447,61 +2447,61 @@
     <t xml:space="preserve">22.8102970123291</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8253135681152</t>
+    <t xml:space="preserve">22.8253154754639</t>
   </si>
   <si>
     <t xml:space="preserve">22.0744819641113</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8853816986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1645793914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.299732208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8553466796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7952823638916</t>
+    <t xml:space="preserve">22.8853797912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1645812988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2997283935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8553447723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.795280456543</t>
   </si>
   <si>
     <t xml:space="preserve">23.3508949279785</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1017303466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4471130371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4170799255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6723613739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6573429107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7774772644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3269805908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8764820098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2396640777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9181976318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4226474761963</t>
+    <t xml:space="preserve">24.1017284393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4471111297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4170780181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.67236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6573467254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7774791717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3269824981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8764781951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2396659851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9181995391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4226512908936</t>
   </si>
   <si>
     <t xml:space="preserve">20.4827156066895</t>
@@ -2510,19 +2510,19 @@
     <t xml:space="preserve">19.0411167144775</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5906181335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9688186645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8876209259033</t>
+    <t xml:space="preserve">18.5906162261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9688167572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8876190185547</t>
   </si>
   <si>
     <t xml:space="preserve">15.7975206375122</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6201038360596</t>
+    <t xml:space="preserve">13.6201047897339</t>
   </si>
   <si>
     <t xml:space="preserve">14.6937942504883</t>
@@ -2531,13 +2531,13 @@
     <t xml:space="preserve">13.2146558761597</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9894037246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6590394973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0344562530518</t>
+    <t xml:space="preserve">12.989405632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6590385437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0344552993774</t>
   </si>
   <si>
     <t xml:space="preserve">12.7266139984131</t>
@@ -2546,58 +2546,58 @@
     <t xml:space="preserve">12.8917961120605</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9054231643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.018045425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5811710357666</t>
+    <t xml:space="preserve">13.9054203033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0180473327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.581169128418</t>
   </si>
   <si>
     <t xml:space="preserve">14.0781116485596</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3559226989746</t>
+    <t xml:space="preserve">14.355920791626</t>
   </si>
   <si>
     <t xml:space="preserve">14.1982450485229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3183765411377</t>
+    <t xml:space="preserve">14.318377494812</t>
   </si>
   <si>
     <t xml:space="preserve">14.0555868148804</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7688779830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4671564102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7886180877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7074184417725</t>
+    <t xml:space="preserve">14.7688789367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.46715259552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7886199951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7074193954468</t>
   </si>
   <si>
     <t xml:space="preserve">15.9026355743408</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9326677322388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7674837112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1518039703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3770523071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4821701049805</t>
+    <t xml:space="preserve">15.9326696395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7674875259399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1518049240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3770532608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4821710586548</t>
   </si>
   <si>
     <t xml:space="preserve">16.6835021972656</t>
@@ -2606,73 +2606,73 @@
     <t xml:space="preserve">16.8937339782715</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3442363739014</t>
+    <t xml:space="preserve">17.3442344665527</t>
   </si>
   <si>
     <t xml:space="preserve">17.0138683319092</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5333347320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.503303527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9087505340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4643669128418</t>
+    <t xml:space="preserve">16.5333385467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5033016204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9087524414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4643688201904</t>
   </si>
   <si>
     <t xml:space="preserve">17.103967666626</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5244369506836</t>
+    <t xml:space="preserve">17.5244331359863</t>
   </si>
   <si>
     <t xml:space="preserve">17.1189842224121</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2391147613525</t>
+    <t xml:space="preserve">17.2391166687012</t>
   </si>
   <si>
     <t xml:space="preserve">17.1340007781982</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3892860412598</t>
+    <t xml:space="preserve">17.389289855957</t>
   </si>
   <si>
     <t xml:space="preserve">17.4043006896973</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6896190643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3653678894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2902851104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.485502243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9510192871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2813854217529</t>
+    <t xml:space="preserve">17.6896171569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3653659820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2902870178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4855003356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9510173797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2813835144043</t>
   </si>
   <si>
     <t xml:space="preserve">19.8520164489746</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3414535522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5516834259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3954029083252</t>
+    <t xml:space="preserve">19.3414497375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5516796112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3953971862793</t>
   </si>
   <si>
     <t xml:space="preserve">19.4315490722656</t>
@@ -2684,13 +2684,13 @@
     <t xml:space="preserve">19.3264331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9571323394775</t>
+    <t xml:space="preserve">19.9571304321289</t>
   </si>
   <si>
     <t xml:space="preserve">20.1072998046875</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6779308319092</t>
+    <t xml:space="preserve">20.6779327392578</t>
   </si>
   <si>
     <t xml:space="preserve">19.2663650512695</t>
@@ -2699,106 +2699,106 @@
     <t xml:space="preserve">19.5066337585449</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8820495605469</t>
+    <t xml:space="preserve">19.8820514678955</t>
   </si>
   <si>
     <t xml:space="preserve">20.0922832489014</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3475666046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3775959014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.596736907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7107524871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9209823608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7708206176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8308849334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5666961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0861644744873</t>
+    <t xml:space="preserve">20.3475646972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3775978088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5967330932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.710750579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9209842681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7708148956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8308811187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5666980743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0861663818359</t>
   </si>
   <si>
     <t xml:space="preserve">18.9059677124023</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0711517333984</t>
+    <t xml:space="preserve">19.0711479187012</t>
   </si>
   <si>
     <t xml:space="preserve">18.7558002471924</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4766006469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2964000701904</t>
+    <t xml:space="preserve">19.476598739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2963981628418</t>
   </si>
   <si>
     <t xml:space="preserve">19.5366687774658</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5216522216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3114147186279</t>
+    <t xml:space="preserve">19.5216503143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3114185333252</t>
   </si>
   <si>
     <t xml:space="preserve">18.981050491333</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4526805877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6178607940674</t>
+    <t xml:space="preserve">20.4526824951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6178646087646</t>
   </si>
   <si>
     <t xml:space="preserve">19.6117496490479</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3625831604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6417846679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0322151184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5127468109131</t>
+    <t xml:space="preserve">20.3625793457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6417827606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0322170257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5127487182617</t>
   </si>
   <si>
     <t xml:space="preserve">20.2424468994141</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7379970550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0021820068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.215202331543</t>
+    <t xml:space="preserve">20.7379989624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0021800994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2152004241943</t>
   </si>
   <si>
     <t xml:space="preserve">18.1401176452637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3203144073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5577964782715</t>
+    <t xml:space="preserve">18.3203163146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5578002929688</t>
   </si>
   <si>
     <t xml:space="preserve">20.4376659393311</t>
@@ -2807,16 +2807,16 @@
     <t xml:space="preserve">21.1284313201904</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7830505371094</t>
+    <t xml:space="preserve">20.783052444458</t>
   </si>
   <si>
     <t xml:space="preserve">20.497730255127</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0233135223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4137477874756</t>
+    <t xml:space="preserve">21.0233154296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4137496948242</t>
   </si>
   <si>
     <t xml:space="preserve">21.3686962127686</t>
@@ -2831,25 +2831,25 @@
     <t xml:space="preserve">20.4076309204102</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5427837371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.317533493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2124156951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.446569442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.746898651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2363338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5277633666992</t>
+    <t xml:space="preserve">20.5427799224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3175315856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2124176025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4465637207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7469005584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2363357543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5277652740479</t>
   </si>
   <si>
     <t xml:space="preserve">21.7140789031982</t>
@@ -2858,37 +2858,37 @@
     <t xml:space="preserve">21.6840476989746</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6389961242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3386669158936</t>
+    <t xml:space="preserve">21.6389980316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3386650085449</t>
   </si>
   <si>
     <t xml:space="preserve">21.6239814758301</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8642463684082</t>
+    <t xml:space="preserve">21.8642482757568</t>
   </si>
   <si>
     <t xml:space="preserve">21.3987312316895</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4437808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1884956359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9092998504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8942813873291</t>
+    <t xml:space="preserve">21.4437828063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.188497543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9092960357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8942794799805</t>
   </si>
   <si>
     <t xml:space="preserve">21.8342151641846</t>
   </si>
   <si>
-    <t xml:space="preserve">21.503849029541</t>
+    <t xml:space="preserve">21.5038471221924</t>
   </si>
   <si>
     <t xml:space="preserve">22.2546806335449</t>
@@ -2897,31 +2897,31 @@
     <t xml:space="preserve">22.0444469451904</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2847118377686</t>
+    <t xml:space="preserve">22.2847137451172</t>
   </si>
   <si>
     <t xml:space="preserve">22.3447818756104</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4649124145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.69016456604</t>
+    <t xml:space="preserve">22.4649143218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6901626586914</t>
   </si>
   <si>
     <t xml:space="preserve">22.8703632354736</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6150817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5700302124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6751499176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5775356292725</t>
+    <t xml:space="preserve">22.6150779724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.570032119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6751441955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5775375366211</t>
   </si>
   <si>
     <t xml:space="preserve">22.9079036712646</t>
@@ -2933,19 +2933,19 @@
     <t xml:space="preserve">23.0881042480469</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8178043365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8403301239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1706981658936</t>
+    <t xml:space="preserve">22.8178024291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8403282165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1706962585449</t>
   </si>
   <si>
     <t xml:space="preserve">23.215747833252</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3809280395508</t>
+    <t xml:space="preserve">23.3809299468994</t>
   </si>
   <si>
     <t xml:space="preserve">23.5235862731934</t>
@@ -2954,7 +2954,7 @@
     <t xml:space="preserve">23.0505638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9154148101807</t>
+    <t xml:space="preserve">22.915412902832</t>
   </si>
   <si>
     <t xml:space="preserve">23.0730876922607</t>
@@ -2963,13 +2963,13 @@
     <t xml:space="preserve">23.2532863616943</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3433876037598</t>
+    <t xml:space="preserve">23.3433895111084</t>
   </si>
   <si>
     <t xml:space="preserve">23.2983379364014</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8914928436279</t>
+    <t xml:space="preserve">23.8914966583252</t>
   </si>
   <si>
     <t xml:space="preserve">24.2594051361084</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">24.0942211151123</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6648540496826</t>
+    <t xml:space="preserve">24.664852142334</t>
   </si>
   <si>
     <t xml:space="preserve">24.5522308349609</t>
@@ -2987,37 +2987,37 @@
     <t xml:space="preserve">24.4621295928955</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7924957275391</t>
+    <t xml:space="preserve">24.7924938201904</t>
   </si>
   <si>
     <t xml:space="preserve">24.402063369751</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0491695404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4696388244629</t>
+    <t xml:space="preserve">24.0491676330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4696369171143</t>
   </si>
   <si>
     <t xml:space="preserve">24.4245853424072</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1993370056152</t>
+    <t xml:space="preserve">24.1993350982666</t>
   </si>
   <si>
     <t xml:space="preserve">23.9590702056885</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1617965698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2293682098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.627311706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8075103759766</t>
+    <t xml:space="preserve">24.1617946624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2293701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6273097991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8075122833252</t>
   </si>
   <si>
     <t xml:space="preserve">24.8150196075439</t>
@@ -3026,58 +3026,58 @@
     <t xml:space="preserve">25.1078414916992</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2204723358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1003360748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1829299926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2955532073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5208034515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8286476135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8061180114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7385406494141</t>
+    <t xml:space="preserve">25.2204685211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1003379821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1829280853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2955513000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5208015441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8286437988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8061199188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7385444641113</t>
   </si>
   <si>
     <t xml:space="preserve">25.7835922241211</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0538959503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8661861419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4893760681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5119075775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3767547607422</t>
+    <t xml:space="preserve">26.0538921356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8661823272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4893779754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5118999481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3767509460449</t>
   </si>
   <si>
     <t xml:space="preserve">26.466854095459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6545562744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5869846343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1050586700439</t>
+    <t xml:space="preserve">26.65456199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.586986541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1050605773926</t>
   </si>
   <si>
     <t xml:space="preserve">27.5180225372314</t>
@@ -3095,28 +3095,28 @@
     <t xml:space="preserve">27.037483215332</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2176876068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.195161819458</t>
+    <t xml:space="preserve">27.2176818847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1951599121094</t>
   </si>
   <si>
     <t xml:space="preserve">27.2251930236816</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2566165924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6845951080322</t>
+    <t xml:space="preserve">26.2566184997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.684591293335</t>
   </si>
   <si>
     <t xml:space="preserve">27.1726322174072</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0299739837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7446613311768</t>
+    <t xml:space="preserve">27.029972076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7446537017822</t>
   </si>
   <si>
     <t xml:space="preserve">26.6245250701904</t>
@@ -3128,19 +3128,19 @@
     <t xml:space="preserve">26.0163536071777</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3992767333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.35422706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5569534301758</t>
+    <t xml:space="preserve">26.3992729187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3542232513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5569515228271</t>
   </si>
   <si>
     <t xml:space="preserve">26.001335144043</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0238571166992</t>
+    <t xml:space="preserve">26.0238609313965</t>
   </si>
   <si>
     <t xml:space="preserve">26.4218006134033</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">26.2115707397461</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8873157501221</t>
+    <t xml:space="preserve">26.8873195648193</t>
   </si>
   <si>
     <t xml:space="preserve">27.1125679016113</t>
@@ -3161,106 +3161,106 @@
     <t xml:space="preserve">27.3603420257568</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3828659057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6456565856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6231346130371</t>
+    <t xml:space="preserve">27.3828678131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6456623077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6231327056885</t>
   </si>
   <si>
     <t xml:space="preserve">27.7808074951172</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5931034088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4204082489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5630645751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7883167266846</t>
+    <t xml:space="preserve">27.5931053161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.42041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5630626678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7883186340332</t>
   </si>
   <si>
     <t xml:space="preserve">27.7132320404053</t>
   </si>
   <si>
-    <t xml:space="preserve">27.953498840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9835357666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2613430023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1412143707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2087841033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1862602233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3814735412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2012748718262</t>
+    <t xml:space="preserve">27.9534969329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9835319519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2613391876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.141206741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2087860107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1862621307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3814754486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2012767791748</t>
   </si>
   <si>
     <t xml:space="preserve">28.0586185455322</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1186866760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4115104675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1698474884033</t>
+    <t xml:space="preserve">28.1186828613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4115123748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.169849395752</t>
   </si>
   <si>
     <t xml:space="preserve">29.3875885009766</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5077247619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2899799346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9145698547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4190139770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6442718505859</t>
+    <t xml:space="preserve">29.5077209472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2899856567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9145622253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.419017791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6442623138428</t>
   </si>
   <si>
     <t xml:space="preserve">29.1923770904541</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1323070526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2148952484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5842056274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4865875244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4565582275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5466594696045</t>
+    <t xml:space="preserve">29.1323051452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2149028778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5841999053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.48659324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4565620422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5466575622559</t>
   </si>
   <si>
     <t xml:space="preserve">28.4640693664551</t>
@@ -3269,187 +3269,187 @@
     <t xml:space="preserve">27.8784160614014</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4715728759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4039974212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0736293792725</t>
+    <t xml:space="preserve">28.4715747833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4039993286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0736351013184</t>
   </si>
   <si>
     <t xml:space="preserve">28.3964900970459</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0285816192627</t>
+    <t xml:space="preserve">28.0285835266113</t>
   </si>
   <si>
     <t xml:space="preserve">28.7644023895264</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6954288482666</t>
+    <t xml:space="preserve">29.6954307556152</t>
   </si>
   <si>
     <t xml:space="preserve">29.717960357666</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9432144165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.401216506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7240734100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5213508605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6940422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5288543701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7090587615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4988193511963</t>
+    <t xml:space="preserve">29.943208694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4012145996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7240695953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.521354675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6940402984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5288581848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7090511322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4988250732422</t>
   </si>
   <si>
     <t xml:space="preserve">30.7766304016113</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7602157592773</t>
+    <t xml:space="preserve">31.7602233886719</t>
   </si>
   <si>
     <t xml:space="preserve">32.2107238769531</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4359703063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7376976013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1506538391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3083305358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3458709716797</t>
+    <t xml:space="preserve">32.4359741210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7376937866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1506500244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3083343505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.345874786377</t>
   </si>
   <si>
     <t xml:space="preserve">31.8728485107422</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1370277404785</t>
+    <t xml:space="preserve">31.1370315551758</t>
   </si>
   <si>
     <t xml:space="preserve">30.859224319458</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0544395446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4641036987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2592010498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0342807769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6406803131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8052845001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1265907287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0864219665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0583820343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9378929138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1146106719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5885410308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3596839904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3195190429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0303440093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1508312225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3355808258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2632884979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1668968200684</t>
+    <t xml:space="preserve">31.0544338226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4641075134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2591991424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0342788696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6406764984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8052806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1265850067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.08642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.058385848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9378890991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1146125793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5885429382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3596782684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3195247650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0303401947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1508331298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.335578918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2632904052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1668949127197</t>
   </si>
   <si>
     <t xml:space="preserve">31.1187000274658</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6046028137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7531452178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4118251800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5644435882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.548376083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9419784545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2713203430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1829566955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1267318725586</t>
+    <t xml:space="preserve">30.604606628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7531394958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4118232727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5644454956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5483798980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9419803619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2713222503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1829624176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1267337799072</t>
   </si>
   <si>
     <t xml:space="preserve">31.2150917053223</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2311592102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1909923553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4359188079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2029705047607</t>
+    <t xml:space="preserve">31.2311573028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1909961700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4359264373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2029685974121</t>
   </si>
   <si>
     <t xml:space="preserve">30.1788749694824</t>
@@ -3458,40 +3458,40 @@
     <t xml:space="preserve">30.8375549316406</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8616485595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5082130432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3475608825684</t>
+    <t xml:space="preserve">30.8616542816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5082149505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3475646972656</t>
   </si>
   <si>
     <t xml:space="preserve">30.2913303375244</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4800281524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8856086730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3997020721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9338035583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7208690643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1907062530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6807022094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9939804077148</t>
+    <t xml:space="preserve">29.4800300598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8856048583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3996982574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9338054656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7208652496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1907043457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.680700302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9939746856689</t>
   </si>
   <si>
     <t xml:space="preserve">28.0743045806885</t>
@@ -3500,43 +3500,43 @@
     <t xml:space="preserve">28.5803642272949</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9659385681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0783939361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8695430755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8374137878418</t>
+    <t xml:space="preserve">28.9659328460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0783920288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8695411682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8374118804932</t>
   </si>
   <si>
     <t xml:space="preserve">28.8133144378662</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6285591125488</t>
+    <t xml:space="preserve">28.6285629272461</t>
   </si>
   <si>
     <t xml:space="preserve">29.3595352172852</t>
   </si>
   <si>
-    <t xml:space="preserve">29.09446144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9579010009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3152885437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1587200164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3675708770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8936405181885</t>
+    <t xml:space="preserve">29.0944576263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9579029083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3152828216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1587181091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3675727844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8936443328857</t>
   </si>
   <si>
     <t xml:space="preserve">28.8026943206787</t>
@@ -3545,49 +3545,49 @@
     <t xml:space="preserve">28.2799034118652</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4105987548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9600048065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9974231719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9810829162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9028205871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9273300170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3228454589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3623695373535</t>
+    <t xml:space="preserve">28.4106025695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9600028991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9974250793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9810848236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9028244018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9273262023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3228492736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3623714447021</t>
   </si>
   <si>
     <t xml:space="preserve">22.8885879516602</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5175762176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3963661193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7101993560791</t>
+    <t xml:space="preserve">23.5175743103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3963623046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7101974487305</t>
   </si>
   <si>
     <t xml:space="preserve">25.306510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7231101989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8211345672607</t>
+    <t xml:space="preserve">25.7231121063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8211364746094</t>
   </si>
   <si>
     <t xml:space="preserve">27.1281223297119</t>
@@ -3602,49 +3602,49 @@
     <t xml:space="preserve">26.7768688201904</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1036167144775</t>
+    <t xml:space="preserve">27.1036186218262</t>
   </si>
   <si>
     <t xml:space="preserve">27.0709400177002</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9892520904541</t>
+    <t xml:space="preserve">26.9892559051514</t>
   </si>
   <si>
     <t xml:space="preserve">27.0300998687744</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3486766815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1328678131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9041404724121</t>
+    <t xml:space="preserve">27.3486747741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1328639984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9041442871094</t>
   </si>
   <si>
     <t xml:space="preserve">27.5447254180908</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9776611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5937366485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5481472015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7523651123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8830623626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8667259216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5399799346924</t>
+    <t xml:space="preserve">27.9776630401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5937385559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5481491088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7523670196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8830604553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8667221069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5399780273438</t>
   </si>
   <si>
     <t xml:space="preserve">26.4991340637207</t>
@@ -3656,16 +3656,16 @@
     <t xml:space="preserve">25.6414241790771</t>
   </si>
   <si>
-    <t xml:space="preserve">26.237735748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3520984649658</t>
+    <t xml:space="preserve">26.2377376556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3520946502686</t>
   </si>
   <si>
     <t xml:space="preserve">26.1152076721191</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9109916687012</t>
+    <t xml:space="preserve">25.9109897613525</t>
   </si>
   <si>
     <t xml:space="preserve">25.3146800994873</t>
@@ -3677,46 +3677,46 @@
     <t xml:space="preserve">25.2738380432129</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6741008758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8047981262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.355525970459</t>
+    <t xml:space="preserve">25.6740989685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8048000335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3555221557617</t>
   </si>
   <si>
     <t xml:space="preserve">24.9634246826172</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9913578033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3017654418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8374729156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3766059875488</t>
+    <t xml:space="preserve">23.9913558959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3017635345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8374710083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3766040802002</t>
   </si>
   <si>
     <t xml:space="preserve">26.4256153106689</t>
   </si>
   <si>
-    <t xml:space="preserve">26.515474319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.441951751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6380004882812</t>
+    <t xml:space="preserve">26.5154705047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4419536590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6380023956299</t>
   </si>
   <si>
     <t xml:space="preserve">26.507303237915</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5489635467529</t>
+    <t xml:space="preserve">27.5489654541016</t>
   </si>
   <si>
     <t xml:space="preserve">26.7698364257812</t>
@@ -3725,13 +3725,13 @@
     <t xml:space="preserve">26.4734287261963</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5743713378906</t>
+    <t xml:space="preserve">27.5743732452393</t>
   </si>
   <si>
     <t xml:space="preserve">27.6759948730469</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9639339447021</t>
+    <t xml:space="preserve">27.9639358520508</t>
   </si>
   <si>
     <t xml:space="preserve">27.5828399658203</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">27.3457126617432</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5235576629639</t>
+    <t xml:space="preserve">27.5235595703125</t>
   </si>
   <si>
     <t xml:space="preserve">26.7274913787842</t>
@@ -3749,7 +3749,7 @@
     <t xml:space="preserve">27.5320262908936</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9561500549316</t>
+    <t xml:space="preserve">26.956148147583</t>
   </si>
   <si>
     <t xml:space="preserve">26.2108974456787</t>
@@ -3761,10 +3761,10 @@
     <t xml:space="preserve">23.3992557525635</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8149108886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3484439849854</t>
+    <t xml:space="preserve">22.8149127960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.348445892334</t>
   </si>
   <si>
     <t xml:space="preserve">23.9751358032227</t>
@@ -3773,13 +3773,13 @@
     <t xml:space="preserve">22.9250049591064</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4161968231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5686321258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3569164276123</t>
+    <t xml:space="preserve">23.4161949157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5686340332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3569145202637</t>
   </si>
   <si>
     <t xml:space="preserve">23.0859146118164</t>
@@ -3797,13 +3797,13 @@
     <t xml:space="preserve">23.3230400085449</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8318481445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.747163772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.713285446167</t>
+    <t xml:space="preserve">22.8318500518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7471618652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7132873535156</t>
   </si>
   <si>
     <t xml:space="preserve">21.64621925354</t>
@@ -3812,13 +3812,13 @@
     <t xml:space="preserve">21.9510955810547</t>
   </si>
   <si>
-    <t xml:space="preserve">22.264440536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7810363769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1120014190674</t>
+    <t xml:space="preserve">22.2644443511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7810382843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.112003326416</t>
   </si>
   <si>
     <t xml:space="preserve">22.4592247009277</t>
@@ -3827,25 +3827,25 @@
     <t xml:space="preserve">22.222095489502</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3074684143066</t>
+    <t xml:space="preserve">21.3074703216553</t>
   </si>
   <si>
     <t xml:space="preserve">21.7563152313232</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2898483276367</t>
+    <t xml:space="preserve">22.2898502349854</t>
   </si>
   <si>
     <t xml:space="preserve">23.052038192749</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0351028442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5185050964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.009693145752</t>
+    <t xml:space="preserve">23.0351009368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5185031890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0096950531006</t>
   </si>
   <si>
     <t xml:space="preserve">22.5015659332275</t>
@@ -3857,7 +3857,7 @@
     <t xml:space="preserve">23.1536655426025</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9666652679443</t>
+    <t xml:space="preserve">23.966667175293</t>
   </si>
   <si>
     <t xml:space="preserve">24.0513553619385</t>
@@ -3866,10 +3866,10 @@
     <t xml:space="preserve">23.9327926635742</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4239826202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5256061553955</t>
+    <t xml:space="preserve">24.4239807128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5256080627441</t>
   </si>
   <si>
     <t xml:space="preserve">23.9497299194336</t>
@@ -3878,22 +3878,22 @@
     <t xml:space="preserve">23.8565731048584</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4416046142578</t>
+    <t xml:space="preserve">23.4416007995605</t>
   </si>
   <si>
     <t xml:space="preserve">23.7888240814209</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1275749206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1360397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5008811950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7380084991455</t>
+    <t xml:space="preserve">24.1275730133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.136043548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.500883102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7380104064941</t>
   </si>
   <si>
     <t xml:space="preserve">23.0774459838867</t>
@@ -3902,22 +3902,22 @@
     <t xml:space="preserve">22.5354442596436</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9334735870361</t>
+    <t xml:space="preserve">22.9334754943848</t>
   </si>
   <si>
     <t xml:space="preserve">22.7725677490234</t>
   </si>
   <si>
-    <t xml:space="preserve">22.095064163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0273132324219</t>
+    <t xml:space="preserve">22.0950660705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0273170471191</t>
   </si>
   <si>
     <t xml:space="preserve">22.2559719085693</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3914737701416</t>
+    <t xml:space="preserve">22.391471862793</t>
   </si>
   <si>
     <t xml:space="preserve">21.925687789917</t>
@@ -3935,34 +3935,34 @@
     <t xml:space="preserve">23.0689754486084</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9243259429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3907909393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9419460296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6455345153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7302227020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3921566009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5022506713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.341344833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7908706665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0957469940186</t>
+    <t xml:space="preserve">23.9243240356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3907871246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9419441223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6455364227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7302265167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3921546936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5022468566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3413429260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7908725738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0957489013672</t>
   </si>
   <si>
     <t xml:space="preserve">20.6553707122803</t>
@@ -3971,16 +3971,16 @@
     <t xml:space="preserve">20.8078079223633</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3335590362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2207298278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2552890777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0344181060791</t>
+    <t xml:space="preserve">20.3335571289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2207336425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2552871704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0344161987305</t>
   </si>
   <si>
     <t xml:space="preserve">23.4246654510498</t>
@@ -3995,7 +3995,7 @@
     <t xml:space="preserve">23.6533222198486</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0174789428711</t>
+    <t xml:space="preserve">24.0174808502197</t>
   </si>
   <si>
     <t xml:space="preserve">24.3308238983154</t>
@@ -4010,43 +4010,43 @@
     <t xml:space="preserve">24.79660987854</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1438312530518</t>
+    <t xml:space="preserve">25.1438293457031</t>
   </si>
   <si>
     <t xml:space="preserve">25.8298015594482</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9737720489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2871170043945</t>
+    <t xml:space="preserve">25.9737701416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2871150970459</t>
   </si>
   <si>
     <t xml:space="preserve">26.3802719116211</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6265506744385</t>
+    <t xml:space="preserve">25.6265487670898</t>
   </si>
   <si>
     <t xml:space="preserve">25.7197074890137</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6858291625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.329460144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3118381500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9307441711426</t>
+    <t xml:space="preserve">25.6858329772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3294563293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3118362426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9307422637939</t>
   </si>
   <si>
     <t xml:space="preserve">26.9053363800049</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1756534576416</t>
+    <t xml:space="preserve">28.1756572723389</t>
   </si>
   <si>
     <t xml:space="preserve">28.2264671325684</t>
@@ -4055,43 +4055,43 @@
     <t xml:space="preserve">28.074031829834</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4551239013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2434043884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1163749694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3111534118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1671848297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4297161102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7091903686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1848068237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.277961730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0069599151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.947681427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.286434173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0239009857178</t>
+    <t xml:space="preserve">28.4551219940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2434062957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1163730621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3111572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1671867370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4297199249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.709192276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1848049163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2779636383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0069637298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9476795196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2864322662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0238971710205</t>
   </si>
   <si>
     <t xml:space="preserve">27.6675262451172</t>
@@ -4100,46 +4100,46 @@
     <t xml:space="preserve">27.4981517791748</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2610244750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0577735900879</t>
+    <t xml:space="preserve">27.2610263824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0577754974365</t>
   </si>
   <si>
     <t xml:space="preserve">27.269495010376</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5574321746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0909652709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1255226135254</t>
+    <t xml:space="preserve">27.5574340820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0909633636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.125524520874</t>
   </si>
   <si>
     <t xml:space="preserve">27.0916500091553</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7105541229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7952423095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4219341278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2271499633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4304027557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3203048706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1509323120117</t>
+    <t xml:space="preserve">26.7105579376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7952404022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.421932220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2271537780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4304008483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3203029632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1509342193604</t>
   </si>
   <si>
     <t xml:space="preserve">27.7014026641846</t>
@@ -4148,16 +4148,16 @@
     <t xml:space="preserve">28.2349376678467</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9046535491943</t>
+    <t xml:space="preserve">27.9046516418457</t>
   </si>
   <si>
     <t xml:space="preserve">28.1925926208496</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4720630645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4635925292969</t>
+    <t xml:space="preserve">28.4720611572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4635963439941</t>
   </si>
   <si>
     <t xml:space="preserve">29.0818138122559</t>
@@ -4166,73 +4166,73 @@
     <t xml:space="preserve">29.2935352325439</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0479393005371</t>
+    <t xml:space="preserve">29.0479373931885</t>
   </si>
   <si>
     <t xml:space="preserve">28.7938766479492</t>
   </si>
   <si>
-    <t xml:space="preserve">28.692253112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4043140411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7176570892334</t>
+    <t xml:space="preserve">28.6922550201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4043121337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.717658996582</t>
   </si>
   <si>
     <t xml:space="preserve">28.844690322876</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8362216949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.853157043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6244983673096</t>
+    <t xml:space="preserve">28.836217880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8531551361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6244964599609</t>
   </si>
   <si>
     <t xml:space="preserve">28.8108139038086</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8785610198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0902824401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8700942993164</t>
+    <t xml:space="preserve">28.8785648345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0902805328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.870096206665</t>
   </si>
   <si>
     <t xml:space="preserve">28.8277530670166</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1417770385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7599983215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6753101348877</t>
+    <t xml:space="preserve">28.1417789459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7600021362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6753120422363</t>
   </si>
   <si>
     <t xml:space="preserve">28.759183883667</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2301387786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0740299224854</t>
+    <t xml:space="preserve">28.2301368713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0740280151367</t>
   </si>
   <si>
     <t xml:space="preserve">28.1954479217529</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0133190155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2908496856689</t>
+    <t xml:space="preserve">28.0133171081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2908515930176</t>
   </si>
   <si>
     <t xml:space="preserve">28.3515567779541</t>
@@ -4244,13 +4244,13 @@
     <t xml:space="preserve">28.1520843505859</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3081951141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2214679718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1434154510498</t>
+    <t xml:space="preserve">28.308198928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2214698791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1434135437012</t>
   </si>
   <si>
     <t xml:space="preserve">26.9812507629395</t>
@@ -4265,22 +4265,22 @@
     <t xml:space="preserve">26.0185623168945</t>
   </si>
   <si>
-    <t xml:space="preserve">24.934455871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0558757781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.275318145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9951648712158</t>
+    <t xml:space="preserve">24.9344539642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0558738708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2753200531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9951667785645</t>
   </si>
   <si>
     <t xml:space="preserve">25.8017406463623</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3594264984131</t>
+    <t xml:space="preserve">25.3594245910645</t>
   </si>
   <si>
     <t xml:space="preserve">25.3247356414795</t>
@@ -4310,10 +4310,10 @@
     <t xml:space="preserve">25.3073902130127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9518013000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5068664550781</t>
+    <t xml:space="preserve">24.9518032073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5068626403809</t>
   </si>
   <si>
     <t xml:space="preserve">25.9058170318604</t>
@@ -4322,7 +4322,7 @@
     <t xml:space="preserve">26.1052913665771</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6716499328613</t>
+    <t xml:space="preserve">25.6716480255127</t>
   </si>
   <si>
     <t xml:space="preserve">26.0359077453613</t>
@@ -4331,25 +4331,25 @@
     <t xml:space="preserve">25.6196117401123</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2006912231445</t>
+    <t xml:space="preserve">26.2006931304932</t>
   </si>
   <si>
     <t xml:space="preserve">26.408842086792</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4435329437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5042419433594</t>
+    <t xml:space="preserve">26.4435348510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5042400360107</t>
   </si>
   <si>
     <t xml:space="preserve">26.313440322876</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1833477020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4522037506104</t>
+    <t xml:space="preserve">26.1833457946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.452205657959</t>
   </si>
   <si>
     <t xml:space="preserve">26.0966186523438</t>
@@ -4358,25 +4358,25 @@
     <t xml:space="preserve">25.4721736907959</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6109390258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3767719268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3307857513428</t>
+    <t xml:space="preserve">25.6109409332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3767700195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3307838439941</t>
   </si>
   <si>
     <t xml:space="preserve">26.1920204162598</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0098915100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8104133605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5215892791748</t>
+    <t xml:space="preserve">26.0098896026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8104152679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5215854644775</t>
   </si>
   <si>
     <t xml:space="preserve">26.8424835205078</t>
@@ -4385,46 +4385,46 @@
     <t xml:space="preserve">26.4868984222412</t>
   </si>
   <si>
-    <t xml:space="preserve">26.599645614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.729736328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1062126159668</t>
+    <t xml:space="preserve">26.5996437072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7297382354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1062088012695</t>
   </si>
   <si>
     <t xml:space="preserve">27.0882835388184</t>
   </si>
   <si>
-    <t xml:space="preserve">26.335334777832</t>
+    <t xml:space="preserve">26.3353328704834</t>
   </si>
   <si>
     <t xml:space="preserve">26.4070415496826</t>
   </si>
   <si>
-    <t xml:space="preserve">26.675952911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.702844619751</t>
+    <t xml:space="preserve">26.6759548187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7028465270996</t>
   </si>
   <si>
     <t xml:space="preserve">26.3084411621094</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8154373168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3622264862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8821201324463</t>
+    <t xml:space="preserve">25.8154392242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3622245788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8821182250977</t>
   </si>
   <si>
     <t xml:space="preserve">26.6938819885254</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2048110961914</t>
+    <t xml:space="preserve">27.20481300354</t>
   </si>
   <si>
     <t xml:space="preserve">27.4737224578857</t>
@@ -4433,13 +4433,13 @@
     <t xml:space="preserve">27.5185413360596</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3930492401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6529979705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7157440185547</t>
+    <t xml:space="preserve">27.3930473327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6529960632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7157421112061</t>
   </si>
   <si>
     <t xml:space="preserve">27.9219055175781</t>
@@ -4451,25 +4451,25 @@
     <t xml:space="preserve">27.9667263031006</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9398365020752</t>
+    <t xml:space="preserve">27.9398345947266</t>
   </si>
   <si>
     <t xml:space="preserve">27.7605609893799</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6619625091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4647598266602</t>
+    <t xml:space="preserve">27.6619606018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4647579193115</t>
   </si>
   <si>
     <t xml:space="preserve">27.3840847015381</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3213386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.60817527771</t>
+    <t xml:space="preserve">27.3213405609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6081790924072</t>
   </si>
   <si>
     <t xml:space="preserve">27.9487991333008</t>
@@ -4478,16 +4478,16 @@
     <t xml:space="preserve">28.0115451812744</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2356357574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7644958496094</t>
+    <t xml:space="preserve">28.2356376647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7644939422607</t>
   </si>
   <si>
     <t xml:space="preserve">28.3611278533936</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9129428863525</t>
+    <t xml:space="preserve">27.9129447937012</t>
   </si>
   <si>
     <t xml:space="preserve">27.4378681182861</t>
@@ -4502,43 +4502,43 @@
     <t xml:space="preserve">28.5045471191406</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7465667724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6927833557129</t>
+    <t xml:space="preserve">28.7465686798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6927852630615</t>
   </si>
   <si>
     <t xml:space="preserve">28.7555332183838</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9796237945557</t>
+    <t xml:space="preserve">28.9796257019043</t>
   </si>
   <si>
     <t xml:space="preserve">29.0334053039551</t>
   </si>
   <si>
-    <t xml:space="preserve">29.132007598877</t>
+    <t xml:space="preserve">29.1320056915283</t>
   </si>
   <si>
     <t xml:space="preserve">29.3740272521973</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2306079864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7056827545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1000862121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9606018066406</t>
+    <t xml:space="preserve">29.2306060791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7056846618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1000881195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9606037139893</t>
   </si>
   <si>
     <t xml:space="preserve">30.5482711791992</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1986827850342</t>
+    <t xml:space="preserve">30.1986865997314</t>
   </si>
   <si>
     <t xml:space="preserve">29.8132457733154</t>
@@ -4547,10 +4547,10 @@
     <t xml:space="preserve">29.8311729431152</t>
   </si>
   <si>
-    <t xml:space="preserve">28.773458480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1588973999023</t>
+    <t xml:space="preserve">28.7734565734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1588954925537</t>
   </si>
   <si>
     <t xml:space="preserve">29.3202438354492</t>
@@ -4559,13 +4559,13 @@
     <t xml:space="preserve">29.1140785217285</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4457340240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3650608062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0871906280518</t>
+    <t xml:space="preserve">29.4457321166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.365062713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0871887207031</t>
   </si>
   <si>
     <t xml:space="preserve">28.7017478942871</t>
@@ -4577,31 +4577,31 @@
     <t xml:space="preserve">29.1768226623535</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2574977874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3112812042236</t>
+    <t xml:space="preserve">29.2574996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3112831115723</t>
   </si>
   <si>
     <t xml:space="preserve">29.5712280273438</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1628322601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9745922088623</t>
+    <t xml:space="preserve">30.1628303527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.974588394165</t>
   </si>
   <si>
     <t xml:space="preserve">30.2166118621826</t>
   </si>
   <si>
-    <t xml:space="preserve">30.001485824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0283756256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7773933410645</t>
+    <t xml:space="preserve">30.0014839172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0283737182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7773914337158</t>
   </si>
   <si>
     <t xml:space="preserve">29.7236099243164</t>
@@ -4610,13 +4610,13 @@
     <t xml:space="preserve">29.7684268951416</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1717948913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1807556152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4586334228516</t>
+    <t xml:space="preserve">30.1717967987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.180757522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4586353302002</t>
   </si>
   <si>
     <t xml:space="preserve">30.0104484558105</t>
@@ -4625,52 +4625,52 @@
     <t xml:space="preserve">30.2703971862793</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5930881500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1449069976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1538677215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0463027954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0373363494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6967220306396</t>
+    <t xml:space="preserve">30.593090057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.144905090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.153865814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0463047027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0373382568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6967182159424</t>
   </si>
   <si>
     <t xml:space="preserve">29.1678619384766</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6877555847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3292102813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4278087615967</t>
+    <t xml:space="preserve">29.6877536773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3292083740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4278125762939</t>
   </si>
   <si>
     <t xml:space="preserve">30.0552654266357</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7107105255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5224742889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4776592254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2177066802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7426338195801</t>
+    <t xml:space="preserve">28.7107124328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5224761962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4776554107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2177085876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7426319122314</t>
   </si>
   <si>
     <t xml:space="preserve">27.3392658233643</t>
@@ -4679,10 +4679,10 @@
     <t xml:space="preserve">27.5095767974854</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3571949005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0524311065674</t>
+    <t xml:space="preserve">27.3571968078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0524291992188</t>
   </si>
   <si>
     <t xml:space="preserve">27.1868839263916</t>
@@ -4691,49 +4691,49 @@
     <t xml:space="preserve">27.2854843139648</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2944507598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4468307495117</t>
+    <t xml:space="preserve">27.2944488525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4468326568604</t>
   </si>
   <si>
     <t xml:space="preserve">27.5454330444336</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0294742584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4059467315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1191101074219</t>
+    <t xml:space="preserve">28.0294723510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.405948638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1191082000732</t>
   </si>
   <si>
     <t xml:space="preserve">28.2714920043945</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6838207244873</t>
+    <t xml:space="preserve">28.6838226318359</t>
   </si>
   <si>
     <t xml:space="preserve">28.495584487915</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0423717498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.732572555542</t>
+    <t xml:space="preserve">29.0423698425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7325744628906</t>
   </si>
   <si>
     <t xml:space="preserve">29.7863540649414</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3919544219971</t>
+    <t xml:space="preserve">29.3919525146484</t>
   </si>
   <si>
     <t xml:space="preserve">29.4547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8491020202637</t>
+    <t xml:space="preserve">29.849100112915</t>
   </si>
   <si>
     <t xml:space="preserve">29.194751739502</t>
@@ -4748,10 +4748,10 @@
     <t xml:space="preserve">29.0602951049805</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1499328613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4367713928223</t>
+    <t xml:space="preserve">29.1499366760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4367733001709</t>
   </si>
   <si>
     <t xml:space="preserve">29.0961513519287</t>
@@ -4760,49 +4760,49 @@
     <t xml:space="preserve">29.24853515625</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5891513824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6070823669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7953224182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2883243560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0731925964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4048480987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4317417144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3600330352783</t>
+    <t xml:space="preserve">29.5891532897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6070804595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7953205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2883262634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0731945037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4048500061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4317436218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3600292205811</t>
   </si>
   <si>
     <t xml:space="preserve">30.2255764007568</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1359405517578</t>
+    <t xml:space="preserve">30.1359367370605</t>
   </si>
   <si>
     <t xml:space="preserve">30.3152122497559</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3421020507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7454719543457</t>
+    <t xml:space="preserve">30.3421039581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7454700469971</t>
   </si>
   <si>
     <t xml:space="preserve">30.3331394195557</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0642318725586</t>
+    <t xml:space="preserve">30.0642337799072</t>
   </si>
   <si>
     <t xml:space="preserve">30.6110172271729</t>
@@ -4814,82 +4814,82 @@
     <t xml:space="preserve">31.0860919952393</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1936588287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1577987670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1757259368896</t>
+    <t xml:space="preserve">31.1936550140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1578006744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1757297515869</t>
   </si>
   <si>
     <t xml:space="preserve">31.3818893432617</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5522079467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8121547698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8480072021484</t>
+    <t xml:space="preserve">31.5522041320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8121528625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8480052947998</t>
   </si>
   <si>
     <t xml:space="preserve">32.0003852844238</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2384738922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.713550567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7314796447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5432357788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8300762176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.821117401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1258811950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0900230407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2743301391602</t>
+    <t xml:space="preserve">31.2384719848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7135543823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.731481552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5432415008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8211135864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1258773803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0900268554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2743282318115</t>
   </si>
   <si>
     <t xml:space="preserve">30.9068183898926</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9785289764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1090469360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3958873748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8551158905029</t>
+    <t xml:space="preserve">30.9785308837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1090507507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3958892822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8551120758057</t>
   </si>
   <si>
     <t xml:space="preserve">30.3069019317627</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6632404327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4307384490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2896003723145</t>
+    <t xml:space="preserve">30.6632442474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.430736541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2895965576172</t>
   </si>
   <si>
     <t xml:space="preserve">31.9606704711914</t>
@@ -4907,16 +4907,16 @@
     <t xml:space="preserve">31.3941860198975</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4764213562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6957035064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8601665496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9698085784912</t>
+    <t xml:space="preserve">31.4764194488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6957015991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.860164642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9698104858398</t>
   </si>
   <si>
     <t xml:space="preserve">31.9789447784424</t>
@@ -4925,7 +4925,7 @@
     <t xml:space="preserve">31.9241237640381</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6550750732422</t>
+    <t xml:space="preserve">32.6550712585449</t>
   </si>
   <si>
     <t xml:space="preserve">32.3626899719238</t>
@@ -4937,10 +4937,10 @@
     <t xml:space="preserve">32.9748611450195</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0205459594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2672424316406</t>
+    <t xml:space="preserve">33.0205421447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2672386169434</t>
   </si>
   <si>
     <t xml:space="preserve">33.3677444458008</t>
@@ -4955,43 +4955,43 @@
     <t xml:space="preserve">33.797176361084</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7514915466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6418533325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.947452545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2946510314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3311958312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2398300170898</t>
+    <t xml:space="preserve">33.7514953613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6418495178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9474487304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2946472167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3311996459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2398338317871</t>
   </si>
   <si>
     <t xml:space="preserve">33.404296875</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0936431884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6367988586426</t>
+    <t xml:space="preserve">33.0936393737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6368026733398</t>
   </si>
   <si>
     <t xml:space="preserve">32.4175148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3809623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6134700775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8144836425781</t>
+    <t xml:space="preserve">32.3809661865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.613468170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8144817352295</t>
   </si>
   <si>
     <t xml:space="preserve">32.581974029541</t>
@@ -5000,7 +5000,7 @@
     <t xml:space="preserve">32.5454292297363</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1301879882812</t>
+    <t xml:space="preserve">33.130184173584</t>
   </si>
   <si>
     <t xml:space="preserve">33.075366973877</t>
@@ -5012,7 +5012,7 @@
     <t xml:space="preserve">33.1850090026855</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4408416748047</t>
+    <t xml:space="preserve">33.4408378601074</t>
   </si>
   <si>
     <t xml:space="preserve">33.7697639465332</t>
@@ -5024,7 +5024,7 @@
     <t xml:space="preserve">34.4093437194824</t>
   </si>
   <si>
-    <t xml:space="preserve">34.884464263916</t>
+    <t xml:space="preserve">34.8844566345215</t>
   </si>
   <si>
     <t xml:space="preserve">35.4692192077637</t>
@@ -5033,34 +5033,34 @@
     <t xml:space="preserve">36.5108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0773048400879</t>
+    <t xml:space="preserve">37.0773010253906</t>
   </si>
   <si>
     <t xml:space="preserve">37.0955772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">36.912841796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0590324401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7849273681641</t>
+    <t xml:space="preserve">36.9128456115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0590286254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7849197387695</t>
   </si>
   <si>
     <t xml:space="preserve">37.0985145568848</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9844779968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1555290222168</t>
+    <t xml:space="preserve">36.9844818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1555252075195</t>
   </si>
   <si>
     <t xml:space="preserve">37.1365280151367</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3265800476074</t>
+    <t xml:space="preserve">37.3265762329102</t>
   </si>
   <si>
     <t xml:space="preserve">37.0224914550781</t>
@@ -5084,7 +5084,7 @@
     <t xml:space="preserve">36.4523315429688</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8704452514648</t>
+    <t xml:space="preserve">36.8704490661621</t>
   </si>
   <si>
     <t xml:space="preserve">36.9084625244141</t>
@@ -5093,10 +5093,10 @@
     <t xml:space="preserve">36.5853691101074</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5473594665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0912246704102</t>
+    <t xml:space="preserve">36.5473556518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0912284851074</t>
   </si>
   <si>
     <t xml:space="preserve">36.5663642883301</t>
@@ -5105,7 +5105,7 @@
     <t xml:space="preserve">35.7301254272461</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0839385986328</t>
+    <t xml:space="preserve">35.0839424133301</t>
   </si>
   <si>
     <t xml:space="preserve">35.1219520568848</t>
@@ -5120,7 +5120,7 @@
     <t xml:space="preserve">35.7491302490234</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3573036193848</t>
+    <t xml:space="preserve">36.3572998046875</t>
   </si>
   <si>
     <t xml:space="preserve">36.0722198486328</t>
@@ -5129,13 +5129,13 @@
     <t xml:space="preserve">35.8821678161621</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7871437072754</t>
+    <t xml:space="preserve">35.7871398925781</t>
   </si>
   <si>
     <t xml:space="preserve">35.5970878601074</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9201812744141</t>
+    <t xml:space="preserve">35.9201774597168</t>
   </si>
   <si>
     <t xml:space="preserve">35.9391860961914</t>
@@ -5147,13 +5147,13 @@
     <t xml:space="preserve">35.8631629943848</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9011726379395</t>
+    <t xml:space="preserve">35.9011764526367</t>
   </si>
   <si>
     <t xml:space="preserve">36.3763084411621</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8514404296875</t>
+    <t xml:space="preserve">36.8514442443848</t>
   </si>
   <si>
     <t xml:space="preserve">37.2885704040527</t>
@@ -5177,7 +5177,7 @@
     <t xml:space="preserve">38.3718757629395</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4478988647461</t>
+    <t xml:space="preserve">38.4478950500488</t>
   </si>
   <si>
     <t xml:space="preserve">38.5429229736328</t>
@@ -5189,7 +5189,7 @@
     <t xml:space="preserve">37.7446975708008</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6423835754395</t>
+    <t xml:space="preserve">36.6423873901367</t>
   </si>
   <si>
     <t xml:space="preserve">35.4450454711914</t>
@@ -5201,7 +5201,7 @@
     <t xml:space="preserve">35.8061485290527</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6921157836914</t>
+    <t xml:space="preserve">35.6921195983887</t>
   </si>
   <si>
     <t xml:space="preserve">36.1862564086914</t>
@@ -5210,7 +5210,7 @@
     <t xml:space="preserve">36.4903450012207</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8894577026367</t>
+    <t xml:space="preserve">36.8894538879395</t>
   </si>
   <si>
     <t xml:space="preserve">37.8017120361328</t>
@@ -5222,16 +5222,16 @@
     <t xml:space="preserve">37.7827072143555</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6876831054688</t>
+    <t xml:space="preserve">37.6876792907715</t>
   </si>
   <si>
     <t xml:space="preserve">37.9727592468262</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9917640686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3338661193848</t>
+    <t xml:space="preserve">37.9917678833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3338623046875</t>
   </si>
   <si>
     <t xml:space="preserve">38.4098815917969</t>
@@ -5246,7 +5246,7 @@
     <t xml:space="preserve">37.7066879272461</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2198295593262</t>
+    <t xml:space="preserve">38.2198333740234</t>
   </si>
   <si>
     <t xml:space="preserve">38.0107727050781</t>
@@ -5255,10 +5255,10 @@
     <t xml:space="preserve">38.2768478393555</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2578430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2388381958008</t>
+    <t xml:space="preserve">38.2578392028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.238842010498</t>
   </si>
   <si>
     <t xml:space="preserve">38.5809326171875</t>
@@ -5276,7 +5276,7 @@
     <t xml:space="preserve">39.0940780639648</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5999374389648</t>
+    <t xml:space="preserve">38.5999412536621</t>
   </si>
   <si>
     <t xml:space="preserve">37.7256927490234</t>
@@ -5297,7 +5297,7 @@
     <t xml:space="preserve">39.4741897583008</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8162879943848</t>
+    <t xml:space="preserve">39.8162841796875</t>
   </si>
   <si>
     <t xml:space="preserve">39.9493217468262</t>
@@ -5315,7 +5315,7 @@
     <t xml:space="preserve">39.6452369689941</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3981628417969</t>
+    <t xml:space="preserve">39.3981666564941</t>
   </si>
   <si>
     <t xml:space="preserve">39.3601531982422</t>
@@ -5342,10 +5342,10 @@
     <t xml:space="preserve">38.5619316101074</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9873313903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8923034667969</t>
+    <t xml:space="preserve">39.9873352050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8923072814941</t>
   </si>
   <si>
     <t xml:space="preserve">40.1773834228516</t>
@@ -5372,10 +5372,10 @@
     <t xml:space="preserve">40.9946174621582</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3557243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5267677307129</t>
+    <t xml:space="preserve">41.3557205200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5267715454102</t>
   </si>
   <si>
     <t xml:space="preserve">41.3747291564941</t>
@@ -5387,13 +5387,13 @@
     <t xml:space="preserve">41.6978187561035</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1349449157715</t>
+    <t xml:space="preserve">42.1349411010742</t>
   </si>
   <si>
     <t xml:space="preserve">42.0209121704102</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7548332214355</t>
+    <t xml:space="preserve">41.7548294067383</t>
   </si>
   <si>
     <t xml:space="preserve">42.3820114135742</t>
@@ -5402,7 +5402,7 @@
     <t xml:space="preserve">42.4390258789062</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4580307006836</t>
+    <t xml:space="preserve">42.4580345153809</t>
   </si>
   <si>
     <t xml:space="preserve">42.2869834899902</t>
@@ -5420,7 +5420,7 @@
     <t xml:space="preserve">43.5223350524902</t>
   </si>
   <si>
-    <t xml:space="preserve">42.876148223877</t>
+    <t xml:space="preserve">42.8761520385742</t>
   </si>
   <si>
     <t xml:space="preserve">42.9521751403809</t>
@@ -5432,7 +5432,7 @@
     <t xml:space="preserve">43.0852088928223</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3059883117676</t>
+    <t xml:space="preserve">42.3059921264648</t>
   </si>
   <si>
     <t xml:space="preserve">42.7431144714355</t>
@@ -5453,13 +5453,13 @@
     <t xml:space="preserve">42.9901847839355</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8951530456543</t>
+    <t xml:space="preserve">42.8951568603516</t>
   </si>
   <si>
     <t xml:space="preserve">43.7123908996582</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4653167724609</t>
+    <t xml:space="preserve">43.4653205871582</t>
   </si>
   <si>
     <t xml:space="preserve">44.0354804992676</t>
@@ -5477,19 +5477,19 @@
     <t xml:space="preserve">46.6202163696289</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6392211914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.696231842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5821990966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7722549438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2781181335449</t>
+    <t xml:space="preserve">46.639217376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6962356567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.582202911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7722587585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2781143188477</t>
   </si>
   <si>
     <t xml:space="preserve">46.1070671081543</t>
@@ -5498,7 +5498,7 @@
     <t xml:space="preserve">45.8219871520996</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0310478210449</t>
+    <t xml:space="preserve">46.0310440063477</t>
   </si>
   <si>
     <t xml:space="preserve">45.7839736938477</t>
@@ -5540,7 +5540,7 @@
     <t xml:space="preserve">48.9388694763184</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8438453674316</t>
+    <t xml:space="preserve">48.8438415527344</t>
   </si>
   <si>
     <t xml:space="preserve">48.7963256835938</t>
@@ -5940,6 +5940,9 @@
   </si>
   <si>
     <t xml:space="preserve">47.9799995422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48</t>
   </si>
 </sst>
 </file>
@@ -70966,7 +70969,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6494097222</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>145409</v>
@@ -70987,6 +70990,32 @@
         <v>1974</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6503703704</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>120356</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>48.7999992370605</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>48.0999984741211</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>48.7799987792969</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>48</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>1976</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BGN.MI.xlsx
+++ b/data/BGN.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4796009063721</t>
+    <t xml:space="preserve">17.4795989990234</t>
   </si>
   <si>
     <t xml:space="preserve">BGN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2943058013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7816505432129</t>
+    <t xml:space="preserve">17.2943019866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7816524505615</t>
   </si>
   <si>
     <t xml:space="preserve">16.528413772583</t>
   </si>
   <si>
-    <t xml:space="preserve">16.262825012207</t>
+    <t xml:space="preserve">16.2628211975098</t>
   </si>
   <si>
     <t xml:space="preserve">16.3678245544434</t>
@@ -62,109 +62,109 @@
     <t xml:space="preserve">16.5098838806152</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9422416687012</t>
+    <t xml:space="preserve">16.9422435760498</t>
   </si>
   <si>
     <t xml:space="preserve">16.6457691192627</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1269397735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6760530471802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9601755142212</t>
+    <t xml:space="preserve">16.1269416809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6760492324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9601745605469</t>
   </si>
   <si>
     <t xml:space="preserve">15.0707521438599</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0769281387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5092868804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5401706695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4289932250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6019334793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1942844390869</t>
+    <t xml:space="preserve">15.0769262313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5092878341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5401678085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.428991317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6019344329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1942796707153</t>
   </si>
   <si>
     <t xml:space="preserve">15.478401184082</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2931032180786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0213384628296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8230895996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.718090057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5945587158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4580783843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6804304122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5636768341064</t>
+    <t xml:space="preserve">15.2931089401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0213394165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8230924606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7180891036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5945606231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4580774307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6804323196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5636758804321</t>
   </si>
   <si>
     <t xml:space="preserve">13.1745538711548</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4154386520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0022106170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8477964401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3851537704468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4098625183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1936855316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4963321685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1813306808472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3233919143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3357419967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5210399627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8607482910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.243691444397</t>
+    <t xml:space="preserve">13.4154376983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0022115707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8477973937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3851556777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4098644256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1936826705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4963331222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1813325881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3233909606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3357410430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5210390090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8607473373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2436962127686</t>
   </si>
   <si>
     <t xml:space="preserve">15.5710496902466</t>
@@ -173,133 +173,133 @@
     <t xml:space="preserve">15.4969348907471</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4351673126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4413452148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3239889144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0157623291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.201057434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2937088012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1578235626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3431205749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8489933013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8922338485718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6081113815308</t>
+    <t xml:space="preserve">15.4351692199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4413423538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3239879608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0157604217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2010593414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2937049865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1578216552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3431186676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8489952087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8922309875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6081104278564</t>
   </si>
   <si>
     <t xml:space="preserve">15.9354677200317</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9663496017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0095863342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.867525100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8298692703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8854541778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6569261550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9410429000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3981094360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5339889526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8736982345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9478197097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1145839691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.083703994751</t>
+    <t xml:space="preserve">15.966347694397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0095844268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8675231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8298683166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8854551315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6569223403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9410457611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3981103897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5339937210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8737001419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9478216171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1145858764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0837020874023</t>
   </si>
   <si>
     <t xml:space="preserve">16.0713520050049</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1084079742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2072353363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0589962005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2998828887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1701774597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1207618713379</t>
+    <t xml:space="preserve">16.1084098815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2072334289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0590000152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2998790740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1701755523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1207637786865</t>
   </si>
   <si>
     <t xml:space="preserve">15.7316427230835</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3795785903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1201629638672</t>
+    <t xml:space="preserve">15.3795795440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1201658248901</t>
   </si>
   <si>
     <t xml:space="preserve">14.8916339874268</t>
   </si>
   <si>
-    <t xml:space="preserve">14.706335067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6383924484253</t>
+    <t xml:space="preserve">14.7063369750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6383962631226</t>
   </si>
   <si>
     <t xml:space="preserve">14.6075115203857</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2986860275269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4530973434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6692771911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3419208526611</t>
+    <t xml:space="preserve">14.2986850738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4530982971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6692743301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3419189453125</t>
   </si>
   <si>
     <t xml:space="preserve">14.3666276931763</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">14.3913335800171</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3975095748901</t>
+    <t xml:space="preserve">14.3975067138672</t>
   </si>
   <si>
     <t xml:space="preserve">14.5537919998169</t>
@@ -320,10 +320,10 @@
     <t xml:space="preserve">14.9640312194824</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5110235214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5956745147705</t>
+    <t xml:space="preserve">15.5110206604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5956726074219</t>
   </si>
   <si>
     <t xml:space="preserve">15.3742733001709</t>
@@ -332,70 +332,70 @@
     <t xml:space="preserve">15.3286924362183</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1137990951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0096168518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0551986694336</t>
+    <t xml:space="preserve">15.1138010025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0096139907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0552005767822</t>
   </si>
   <si>
     <t xml:space="preserve">15.2114782333374</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3547401428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3026418685913</t>
+    <t xml:space="preserve">15.3547372817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3026456832886</t>
   </si>
   <si>
     <t xml:space="preserve">15.2570638656616</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8533315658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0979681015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2058591842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9649209976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.945387840271</t>
+    <t xml:space="preserve">14.8533325195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0979719161987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2058572769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9649200439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9453859329224</t>
   </si>
   <si>
     <t xml:space="preserve">13.1993455886841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6616792678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.837495803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1565704345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5733270645142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8737573623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6690816879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7341985702515</t>
+    <t xml:space="preserve">13.6616802215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8374996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1565742492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5733261108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.87375831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6690826416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7342004776001</t>
   </si>
   <si>
     <t xml:space="preserve">11.6560554504395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6821022033691</t>
+    <t xml:space="preserve">11.6821041107178</t>
   </si>
   <si>
     <t xml:space="preserve">11.6039628982544</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">11.2002334594727</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8160400390625</t>
+    <t xml:space="preserve">10.8160390853882</t>
   </si>
   <si>
     <t xml:space="preserve">10.4318466186523</t>
@@ -416,55 +416,55 @@
     <t xml:space="preserve">11.2588396072388</t>
   </si>
   <si>
-    <t xml:space="preserve">11.923041343689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3137435913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2616510391235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5286340713501</t>
+    <t xml:space="preserve">11.9230394363403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3137464523315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2616519927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5286331176758</t>
   </si>
   <si>
     <t xml:space="preserve">12.5677032470703</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6588687896729</t>
+    <t xml:space="preserve">12.6588678359985</t>
   </si>
   <si>
     <t xml:space="preserve">12.3723516464233</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5221214294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5416574478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3397941589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5025863647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2551374435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4895629882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.242115020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0337371826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8188514709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6300086975098</t>
+    <t xml:space="preserve">12.522120475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5416564941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3397922515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5025873184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2551393508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4895639419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2421169281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0337390899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8188524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6300115585327</t>
   </si>
   <si>
     <t xml:space="preserve">11.4281454086304</t>
@@ -473,46 +473,46 @@
     <t xml:space="preserve">11.3825626373291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8579206466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9946699142456</t>
+    <t xml:space="preserve">11.8579216003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9946689605713</t>
   </si>
   <si>
     <t xml:space="preserve">12.1835088729858</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2030439376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0532741546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9490842819214</t>
+    <t xml:space="preserve">12.2030429840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0532732009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9490852355957</t>
   </si>
   <si>
     <t xml:space="preserve">11.7928047180176</t>
   </si>
   <si>
-    <t xml:space="preserve">11.525821685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7667570114136</t>
+    <t xml:space="preserve">11.5258207321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7667579650879</t>
   </si>
   <si>
     <t xml:space="preserve">11.4411697387695</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3630275726318</t>
+    <t xml:space="preserve">11.3630266189575</t>
   </si>
   <si>
     <t xml:space="preserve">11.5583801269531</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7797794342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5388450622559</t>
+    <t xml:space="preserve">11.7797784805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5388460159302</t>
   </si>
   <si>
     <t xml:space="preserve">11.7472219467163</t>
@@ -521,412 +521,412 @@
     <t xml:space="preserve">11.6951274871826</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9425754547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1314134597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1379280090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4114198684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4830503463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6653814315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8021278381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3788623809814</t>
+    <t xml:space="preserve">11.9425745010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1314153671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1379261016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4114208221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4830493927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.665379524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8021268844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3788633346558</t>
   </si>
   <si>
     <t xml:space="preserve">12.1183919906616</t>
   </si>
   <si>
-    <t xml:space="preserve">12.124906539917</t>
+    <t xml:space="preserve">12.1249046325684</t>
   </si>
   <si>
     <t xml:space="preserve">12.2876987457275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.870945930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.701639175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8514089584351</t>
+    <t xml:space="preserve">11.8709449768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7016382217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8514099121094</t>
   </si>
   <si>
     <t xml:space="preserve">11.9165267944336</t>
   </si>
   <si>
-    <t xml:space="preserve">11.252326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1937217712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1481399536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0830221176147</t>
+    <t xml:space="preserve">11.2523288726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1937208175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.148138999939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0830211639404</t>
   </si>
   <si>
     <t xml:space="preserve">11.122091293335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.174186706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1090698242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2848873138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1351165771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0765113830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1872110366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0179061889648</t>
+    <t xml:space="preserve">11.1741847991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1090688705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2848854064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1351156234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.076509475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1872100830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0244159698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0179052352905</t>
   </si>
   <si>
     <t xml:space="preserve">11.6430330276489</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5779161453247</t>
+    <t xml:space="preserve">11.5779151916504</t>
   </si>
   <si>
     <t xml:space="preserve">11.9100151062012</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1769981384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2942113876343</t>
+    <t xml:space="preserve">12.1769971847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2942094802856</t>
   </si>
   <si>
     <t xml:space="preserve">12.4309568405151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9779462814331</t>
+    <t xml:space="preserve">12.9779472351074</t>
   </si>
   <si>
     <t xml:space="preserve">13.0365505218506</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3816738128662</t>
+    <t xml:space="preserve">13.3816747665405</t>
   </si>
   <si>
     <t xml:space="preserve">13.5640029907227</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4142322540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1732978820801</t>
+    <t xml:space="preserve">13.414234161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1732950210571</t>
   </si>
   <si>
     <t xml:space="preserve">13.0560855865479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9258508682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8281755447388</t>
+    <t xml:space="preserve">12.9258499145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8281764984131</t>
   </si>
   <si>
     <t xml:space="preserve">13.3295803070068</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7984266281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5444679260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8830766677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8309879302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9481992721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.889591217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1240148544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4923725128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9388751983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9323635101318</t>
+    <t xml:space="preserve">13.7984256744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5444669723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8830804824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8309850692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9481983184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8895931243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1240139007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4923734664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9388732910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9323644638062</t>
   </si>
   <si>
     <t xml:space="preserve">12.8672456741333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9714326858521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9909696578979</t>
+    <t xml:space="preserve">12.9714317321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9909677505493</t>
   </si>
   <si>
     <t xml:space="preserve">12.7760791778564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7956161499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7304973602295</t>
+    <t xml:space="preserve">12.7956142425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7304964065552</t>
   </si>
   <si>
     <t xml:space="preserve">12.7435216903687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4691381454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.289623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8887033462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5761394500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3612489700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4784622192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0747337341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1854343414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8989133834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8793802261353</t>
+    <t xml:space="preserve">14.4691390991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2896223068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8887023925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5761384963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.361252784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4784631729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0747327804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1854333877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8989124298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8793821334839</t>
   </si>
   <si>
     <t xml:space="preserve">14.9575204849243</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9770584106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0031042098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7817077636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5863494873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7556571960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.859842300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3417139053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4459018707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8403091430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2700834274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5305547714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4133434295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3482265472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5631160736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5138301849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6570930480957</t>
+    <t xml:space="preserve">14.9770574569702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0031061172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7817029953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5863485336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7556581497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8598413467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3417129516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4459028244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8403081893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2700881958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.530556678772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4133443832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3482284545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.563117980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5138339996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6570892333984</t>
   </si>
   <si>
     <t xml:space="preserve">16.5659275054932</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1231250762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0514984130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6803255081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7454471588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7584686279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0356636047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3352031707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2375249862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4328775405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2208023071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2924327850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1491756439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9538230895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1752185821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8626575469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.556601524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1593856811523</t>
+    <t xml:space="preserve">16.1231269836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0514965057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6803274154663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7454442977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.758469581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.035662651062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3352041244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2375259399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.43288230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2208061218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2924346923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.149169921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.953821182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.175220489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8626537322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5566024780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1593866348267</t>
   </si>
   <si>
     <t xml:space="preserve">15.2245035171509</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8468198776245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1658945083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4003210067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3091564178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6021871566772</t>
+    <t xml:space="preserve">14.8468227386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1658964157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4003238677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3091583251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.60218334198</t>
   </si>
   <si>
     <t xml:space="preserve">15.6217193603516</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6738119125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5500926971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3677616119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3938083648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1398487091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1072931289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0812454223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6152086257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.628231048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5435838699341</t>
+    <t xml:space="preserve">15.6738128662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5500907897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3677597045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3938074111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1398515701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.107292175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0812435150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6152105331421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6282300949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5435800552368</t>
   </si>
   <si>
     <t xml:space="preserve">15.7975397109985</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9342851638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2012672424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4422035217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3770847320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2794075012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1426639556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4812698364258</t>
+    <t xml:space="preserve">15.9342832565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.201265335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4422016143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3770809173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2794094085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1426620483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.481273651123</t>
   </si>
   <si>
     <t xml:space="preserve">16.6049976348877</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2338256835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2561740875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2691974639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1584968566895</t>
+    <t xml:space="preserve">16.2338275909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.256175994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2691993713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1584987640381</t>
   </si>
   <si>
     <t xml:space="preserve">17.1454734802246</t>
@@ -935,46 +935,46 @@
     <t xml:space="preserve">17.1845417022705</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1389617919922</t>
+    <t xml:space="preserve">17.1389598846436</t>
   </si>
   <si>
     <t xml:space="preserve">17.6468811035156</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6273403167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.389217376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1678199768066</t>
+    <t xml:space="preserve">17.6273422241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3892211914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1678237915039</t>
   </si>
   <si>
     <t xml:space="preserve">18.1027011871338</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3501510620117</t>
+    <t xml:space="preserve">18.3501472473145</t>
   </si>
   <si>
     <t xml:space="preserve">18.1352596282959</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4934062957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0896797180176</t>
+    <t xml:space="preserve">18.4934101104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0896816253662</t>
   </si>
   <si>
     <t xml:space="preserve">18.2264270782471</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8588066101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8723430633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6896457672119</t>
+    <t xml:space="preserve">18.8588085174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8723449707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6896419525146</t>
   </si>
   <si>
     <t xml:space="preserve">18.6422748565674</t>
@@ -986,40 +986,40 @@
     <t xml:space="preserve">17.8370380401611</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6543350219727</t>
+    <t xml:space="preserve">17.6543388366699</t>
   </si>
   <si>
     <t xml:space="preserve">17.3836708068848</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9047069549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.931770324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5393028259277</t>
+    <t xml:space="preserve">17.9047050476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9317741394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5393009185791</t>
   </si>
   <si>
     <t xml:space="preserve">17.5460681915283</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9926738739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6761093139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.926477432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8046779632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9806098937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.621976852417</t>
+    <t xml:space="preserve">17.9926700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6761074066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9264755249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8046760559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9806118011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6219749450684</t>
   </si>
   <si>
     <t xml:space="preserve">18.0400390625</t>
@@ -1028,73 +1028,73 @@
     <t xml:space="preserve">18.3377742767334</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2092056274414</t>
+    <t xml:space="preserve">18.2092094421387</t>
   </si>
   <si>
     <t xml:space="preserve">17.9994373321533</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8640995025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8032035827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0062065124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4054393768311</t>
+    <t xml:space="preserve">17.8641052246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8032054901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0062026977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4054431915283</t>
   </si>
   <si>
     <t xml:space="preserve">18.0603408813477</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6340351104736</t>
+    <t xml:space="preserve">17.6340370178223</t>
   </si>
   <si>
     <t xml:space="preserve">18.2430400848389</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2701072692871</t>
+    <t xml:space="preserve">18.2701053619385</t>
   </si>
   <si>
     <t xml:space="preserve">18.6490421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4528102874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7031726837158</t>
+    <t xml:space="preserve">18.4528064727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7031764984131</t>
   </si>
   <si>
     <t xml:space="preserve">18.4595756530762</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1024112701416</t>
+    <t xml:space="preserve">19.102409362793</t>
   </si>
   <si>
     <t xml:space="preserve">18.94677734375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9197101593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.77760887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8791103363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1362457275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0415115356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1836128234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3730812072754</t>
+    <t xml:space="preserve">18.9197082519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7776107788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.879114151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1362438201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0415096282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.183614730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3730773925781</t>
   </si>
   <si>
     <t xml:space="preserve">19.2918796539307</t>
@@ -1103,13 +1103,13 @@
     <t xml:space="preserve">19.8264503479004</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9414825439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3001155853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5166530609131</t>
+    <t xml:space="preserve">19.9414844512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.300121307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5166511535645</t>
   </si>
   <si>
     <t xml:space="preserve">20.0971183776855</t>
@@ -1118,13 +1118,13 @@
     <t xml:space="preserve">19.9956188201904</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1241836547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1444854736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6384544372559</t>
+    <t xml:space="preserve">20.1241855621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1444835662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6384525299072</t>
   </si>
   <si>
     <t xml:space="preserve">20.2392196655273</t>
@@ -1133,52 +1133,52 @@
     <t xml:space="preserve">19.8941173553467</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5625495910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7587833404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9211864471436</t>
+    <t xml:space="preserve">19.5625476837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7587852478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9211845397949</t>
   </si>
   <si>
     <t xml:space="preserve">19.9008846282959</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7993831634521</t>
+    <t xml:space="preserve">19.7993850708008</t>
   </si>
   <si>
     <t xml:space="preserve">19.7655487060547</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8129177093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4813461303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5828475952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4881114959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2851123809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7640743255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7573089599609</t>
+    <t xml:space="preserve">19.812915802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4813499450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5828495025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4881134033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2851142883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7640781402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7573108673096</t>
   </si>
   <si>
     <t xml:space="preserve">18.5949077606201</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8452777862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8655776977539</t>
+    <t xml:space="preserve">18.8452758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8655757904053</t>
   </si>
   <si>
     <t xml:space="preserve">18.5340099334717</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">19.0144443511963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2242107391357</t>
+    <t xml:space="preserve">19.224214553833</t>
   </si>
   <si>
     <t xml:space="preserve">19.1700782775879</t>
@@ -1196,25 +1196,25 @@
     <t xml:space="preserve">19.251277923584</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1971454620361</t>
+    <t xml:space="preserve">19.1971473693848</t>
   </si>
   <si>
     <t xml:space="preserve">19.4475154876709</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1633148193359</t>
+    <t xml:space="preserve">19.1633129119873</t>
   </si>
   <si>
     <t xml:space="preserve">19.2648105621338</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4678134918213</t>
+    <t xml:space="preserve">19.4678173065186</t>
   </si>
   <si>
     <t xml:space="preserve">19.2580451965332</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8602848052979</t>
+    <t xml:space="preserve">19.8602828979492</t>
   </si>
   <si>
     <t xml:space="preserve">19.8670501708984</t>
@@ -1223,19 +1223,19 @@
     <t xml:space="preserve">20.0159187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4204444885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.569314956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.549015045166</t>
+    <t xml:space="preserve">19.4204502105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5693111419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5490131378174</t>
   </si>
   <si>
     <t xml:space="preserve">19.4272136688232</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3663139343262</t>
+    <t xml:space="preserve">19.3663120269775</t>
   </si>
   <si>
     <t xml:space="preserve">19.4136810302734</t>
@@ -1250,10 +1250,10 @@
     <t xml:space="preserve">18.9400100708008</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8114433288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8858776092529</t>
+    <t xml:space="preserve">18.8114414215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8858757019043</t>
   </si>
   <si>
     <t xml:space="preserve">19.2783451080322</t>
@@ -1268,25 +1268,25 @@
     <t xml:space="preserve">19.2106781005859</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1091766357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3189449310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3324794769287</t>
+    <t xml:space="preserve">19.1091785430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3189468383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3324775695801</t>
   </si>
   <si>
     <t xml:space="preserve">19.2309799194336</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6572818756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1106510162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9820861816406</t>
+    <t xml:space="preserve">19.6572799682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1106491088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9820823669434</t>
   </si>
   <si>
     <t xml:space="preserve">19.7858486175537</t>
@@ -1295,10 +1295,10 @@
     <t xml:space="preserve">19.5354824066162</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9482479095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.576078414917</t>
+    <t xml:space="preserve">19.9482498168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5760803222656</t>
   </si>
   <si>
     <t xml:space="preserve">19.6166820526123</t>
@@ -1307,22 +1307,22 @@
     <t xml:space="preserve">19.5557804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3460140228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6911163330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6775817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2986488342285</t>
+    <t xml:space="preserve">19.3460121154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6911201477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.677583694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2986431121826</t>
   </si>
   <si>
     <t xml:space="preserve">19.1903800964355</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3121776580811</t>
+    <t xml:space="preserve">19.3121814727783</t>
   </si>
   <si>
     <t xml:space="preserve">18.7911415100098</t>
@@ -1331,13 +1331,13 @@
     <t xml:space="preserve">18.8182106018066</t>
   </si>
   <si>
-    <t xml:space="preserve">18.967077255249</t>
+    <t xml:space="preserve">18.9670810699463</t>
   </si>
   <si>
     <t xml:space="preserve">18.7708435058594</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4663429260254</t>
+    <t xml:space="preserve">18.4663391113281</t>
   </si>
   <si>
     <t xml:space="preserve">18.188907623291</t>
@@ -1346,28 +1346,28 @@
     <t xml:space="preserve">18.6084442138672</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1497783660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1768455505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4745826721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0294494628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0835819244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5301876068115</t>
+    <t xml:space="preserve">19.1497764587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1768474578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4745807647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0294513702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0835857391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5301895141602</t>
   </si>
   <si>
     <t xml:space="preserve">20.503116607666</t>
   </si>
   <si>
-    <t xml:space="preserve">20.800853729248</t>
+    <t xml:space="preserve">20.8008575439453</t>
   </si>
   <si>
     <t xml:space="preserve">20.7602558135986</t>
@@ -1376,25 +1376,25 @@
     <t xml:space="preserve">20.7196559906006</t>
   </si>
   <si>
-    <t xml:space="preserve">20.868522644043</t>
+    <t xml:space="preserve">20.8685207366943</t>
   </si>
   <si>
     <t xml:space="preserve">20.7061214447021</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2459869384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4083862304688</t>
+    <t xml:space="preserve">20.2459850311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4083843231201</t>
   </si>
   <si>
     <t xml:space="preserve">20.3136539459229</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8805809020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8926429748535</t>
+    <t xml:space="preserve">19.8805847167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8926448822021</t>
   </si>
   <si>
     <t xml:space="preserve">19.0550441741943</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">18.0265045166016</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2024402618408</t>
+    <t xml:space="preserve">18.2024383544922</t>
   </si>
   <si>
     <t xml:space="preserve">18.2565727233887</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">18.5813732147217</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5407752990723</t>
+    <t xml:space="preserve">18.5407733917236</t>
   </si>
   <si>
     <t xml:space="preserve">18.4866428375244</t>
@@ -1424,79 +1424,79 @@
     <t xml:space="preserve">18.5272407531738</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4731063842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9859027862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4460411071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6625785827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5678443908691</t>
+    <t xml:space="preserve">18.473108291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9859046936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4460391998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.662576675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5678424835205</t>
   </si>
   <si>
     <t xml:space="preserve">18.7437801361084</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7302436828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3783760070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8505706787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7558364868164</t>
+    <t xml:space="preserve">18.73024559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3783740997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8505744934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7558345794678</t>
   </si>
   <si>
     <t xml:space="preserve">17.7287693023682</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9723739624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0671062469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.148307800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2159748077393</t>
+    <t xml:space="preserve">17.9723701477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0671081542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1483058929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2159729003906</t>
   </si>
   <si>
     <t xml:space="preserve">18.3242435455322</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3513088226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3648414611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7167091369629</t>
+    <t xml:space="preserve">18.3513069152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3648376464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7167110443115</t>
   </si>
   <si>
     <t xml:space="preserve">18.7979106903076</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9061794281006</t>
+    <t xml:space="preserve">18.9061737060547</t>
   </si>
   <si>
     <t xml:space="preserve">18.1618385314941</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1212425231934</t>
+    <t xml:space="preserve">18.1212387084961</t>
   </si>
   <si>
     <t xml:space="preserve">17.8235034942627</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6205024719238</t>
+    <t xml:space="preserve">17.6205043792725</t>
   </si>
   <si>
     <t xml:space="preserve">17.6611042022705</t>
@@ -1508,13 +1508,13 @@
     <t xml:space="preserve">17.0520992279053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7814311981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7600536346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8028125762939</t>
+    <t xml:space="preserve">16.7814273834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7600555419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8028106689453</t>
   </si>
   <si>
     <t xml:space="preserve">16.5605297088623</t>
@@ -1526,73 +1526,73 @@
     <t xml:space="preserve">16.3039970397949</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2066135406494</t>
+    <t xml:space="preserve">15.2066116333008</t>
   </si>
   <si>
     <t xml:space="preserve">14.2802505493164</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8503198623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8218145370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.53440284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3206281661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8930759429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4631462097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8336925506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3491306304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9477052688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8479433059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8621959686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9192028045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7054252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7339296340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7196769714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3633852005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5058994293213</t>
+    <t xml:space="preserve">14.85032081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.821816444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5344066619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3206233978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8930740356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4631433486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8336887359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3491315841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9477033615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8479413986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8621978759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9192037582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7054224014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7339267730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7196779251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3633832931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5059013366699</t>
   </si>
   <si>
     <t xml:space="preserve">15.420389175415</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4488916397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.950080871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9358291625977</t>
+    <t xml:space="preserve">15.4488935470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9500827789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.935830116272</t>
   </si>
   <si>
     <t xml:space="preserve">15.1781091690063</t>
@@ -1601,73 +1601,73 @@
     <t xml:space="preserve">15.5629062652588</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6484184265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.890697479248</t>
+    <t xml:space="preserve">15.648419380188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8906955718994</t>
   </si>
   <si>
     <t xml:space="preserve">16.0189647674561</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4346389770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.377631187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4916477203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5201501846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7909364700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7766819000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6056623458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4750213623047</t>
+    <t xml:space="preserve">15.434642791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3776340484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4916496276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5201539993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7909374237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7766847610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6056594848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4750194549561</t>
   </si>
   <si>
     <t xml:space="preserve">16.2469921112061</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1329765319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4465141296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5035266876221</t>
+    <t xml:space="preserve">16.1329784393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4465160369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5035209655762</t>
   </si>
   <si>
     <t xml:space="preserve">15.9619560241699</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0474700927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2184906005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2042331695557</t>
+    <t xml:space="preserve">16.0474681854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2184867858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2042350769043</t>
   </si>
   <si>
     <t xml:space="preserve">16.1614818572998</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7481803894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9049501419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2754974365234</t>
+    <t xml:space="preserve">15.74817943573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9049510955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2754955291748</t>
   </si>
   <si>
     <t xml:space="preserve">16.4037609100342</t>
@@ -1676,88 +1676,88 @@
     <t xml:space="preserve">16.3325023651123</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2636203765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0783462524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3063716888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2921209335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5486555099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6769237518311</t>
+    <t xml:space="preserve">15.2636213302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.07834815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.30637550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.29212474823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5486536026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6769247055054</t>
   </si>
   <si>
     <t xml:space="preserve">16.6175384521484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7885570526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8598175048828</t>
+    <t xml:space="preserve">16.7885551452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8598155975342</t>
   </si>
   <si>
     <t xml:space="preserve">17.3443756103516</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3871288299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1020965576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8764448165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6911745071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6626710891724</t>
+    <t xml:space="preserve">17.3871307373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1020946502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.876446723938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6911716461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.662670135498</t>
   </si>
   <si>
     <t xml:space="preserve">14.9643335342407</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7933120727539</t>
+    <t xml:space="preserve">14.7933130264282</t>
   </si>
   <si>
     <t xml:space="preserve">14.351508140564</t>
   </si>
   <si>
-    <t xml:space="preserve">14.216118812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3372583389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7220554351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4227676391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.05934715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5391607284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2042455673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7268085479736</t>
+    <t xml:space="preserve">14.2161169052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3372573852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.722053527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4227685928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0593490600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5391597747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2042446136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7268123626709</t>
   </si>
   <si>
     <t xml:space="preserve">12.3776435852051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4203977584839</t>
+    <t xml:space="preserve">12.4203968048096</t>
   </si>
   <si>
     <t xml:space="preserve">12.2850046157837</t>
@@ -1766,25 +1766,25 @@
     <t xml:space="preserve">12.4061460494995</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1353626251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3705177307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.904956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8621997833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.93346118927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.14723777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2755012512207</t>
+    <t xml:space="preserve">12.1353635787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3705167770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9049577713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8622016906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9334602355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1472368240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.275502204895</t>
   </si>
   <si>
     <t xml:space="preserve">13.1187334060669</t>
@@ -1799,55 +1799,55 @@
     <t xml:space="preserve">13.1116065979004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7838153839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7339372634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6698036193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9192066192627</t>
+    <t xml:space="preserve">12.7838163375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7339363098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6698026657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.919207572937</t>
   </si>
   <si>
     <t xml:space="preserve">12.9548387527466</t>
   </si>
   <si>
-    <t xml:space="preserve">13.246997833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5961685180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1092290878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9453344345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8811988830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8883275985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.465521812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2232437133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0878534317017</t>
+    <t xml:space="preserve">13.2469997406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5961675643921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1092300415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9453325271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8812017440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8883266448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4655208587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2232427597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.087851524353</t>
   </si>
   <si>
     <t xml:space="preserve">13.3681402206421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4679021835327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1258602142334</t>
+    <t xml:space="preserve">13.4678993225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1258592605591</t>
   </si>
   <si>
     <t xml:space="preserve">12.9690895080566</t>
@@ -1856,13 +1856,13 @@
     <t xml:space="preserve">13.4892797470093</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6317958831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2327470779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3966417312622</t>
+    <t xml:space="preserve">13.6317939758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2327461242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3966426849365</t>
   </si>
   <si>
     <t xml:space="preserve">12.8265705108643</t>
@@ -1871,16 +1871,16 @@
     <t xml:space="preserve">12.5344114303589</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1044788360596</t>
+    <t xml:space="preserve">13.1044807434082</t>
   </si>
   <si>
     <t xml:space="preserve">12.9975919723511</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6104192733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7529354095459</t>
+    <t xml:space="preserve">13.6104173660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7529344558716</t>
   </si>
   <si>
     <t xml:space="preserve">13.6389207839966</t>
@@ -1889,28 +1889,28 @@
     <t xml:space="preserve">14.1448583602905</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3230047225952</t>
+    <t xml:space="preserve">14.3230028152466</t>
   </si>
   <si>
     <t xml:space="preserve">14.2018671035767</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1947383880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.895453453064</t>
+    <t xml:space="preserve">14.1947393417358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8954515457153</t>
   </si>
   <si>
     <t xml:space="preserve">14.3942642211914</t>
   </si>
   <si>
-    <t xml:space="preserve">14.593789100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7078037261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5082788467407</t>
+    <t xml:space="preserve">14.5937881469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7078046798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5082778930664</t>
   </si>
   <si>
     <t xml:space="preserve">14.6935510635376</t>
@@ -1919,82 +1919,82 @@
     <t xml:space="preserve">14.8075637817383</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6365442276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7648067474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7363052368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6792974472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.265998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5367813110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2945013046265</t>
+    <t xml:space="preserve">14.6365451812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7648086547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7363042831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6793012619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2659978866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5367822647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2945022583008</t>
   </si>
   <si>
     <t xml:space="preserve">14.5510339736938</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1923589706421</t>
+    <t xml:space="preserve">15.1923637390137</t>
   </si>
   <si>
     <t xml:space="preserve">14.9785861968994</t>
   </si>
   <si>
-    <t xml:space="preserve">15.277871131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2493686676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2208662033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.406138420105</t>
+    <t xml:space="preserve">15.2778739929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2493696212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2208652496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4061374664307</t>
   </si>
   <si>
     <t xml:space="preserve">15.8194398880005</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8051891326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.634165763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5914115905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4322643280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6032867431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7173004150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7743072509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8170604705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0308361053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1591033935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2588653564453</t>
+    <t xml:space="preserve">15.8051853179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6341686248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5914096832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4322624206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6032829284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7172985076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7743053436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8170585632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0308380126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1591014862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.258861541748</t>
   </si>
   <si>
     <t xml:space="preserve">17.3158721923828</t>
@@ -2003,25 +2003,25 @@
     <t xml:space="preserve">17.4583892822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4726448059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9714527130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7861785888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9286994934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0569591522217</t>
+    <t xml:space="preserve">17.4726428985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9714508056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7861766815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9286956787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0569629669189</t>
   </si>
   <si>
     <t xml:space="preserve">18.0854644775391</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5581512451172</t>
+    <t xml:space="preserve">17.5581550598145</t>
   </si>
   <si>
     <t xml:space="preserve">17.5866527557373</t>
@@ -2030,85 +2030,85 @@
     <t xml:space="preserve">17.2018566131592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4298877716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5296497344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4868927001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.719654083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8548011779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2991847991943</t>
+    <t xml:space="preserve">17.4298858642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5296478271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4868946075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7196521759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8548030853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2991886138916</t>
   </si>
   <si>
     <t xml:space="preserve">17.224100112915</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2691516876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1490173339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7435684204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8787174224854</t>
+    <t xml:space="preserve">17.2691535949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.149019241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7435665130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8787212371826</t>
   </si>
   <si>
     <t xml:space="preserve">16.923770904541</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6985187530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2541351318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5394515991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1640357971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0589160919189</t>
+    <t xml:space="preserve">16.6985168457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2541332244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5394535064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1640338897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0589199066162</t>
   </si>
   <si>
     <t xml:space="preserve">17.4343338012695</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8247680664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9298839569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8397846221924</t>
+    <t xml:space="preserve">17.8247661590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9298820495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8397827148438</t>
   </si>
   <si>
     <t xml:space="preserve">17.749683380127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9449043273926</t>
+    <t xml:space="preserve">17.9449005126953</t>
   </si>
   <si>
     <t xml:space="preserve">18.6657009124756</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8459014892578</t>
+    <t xml:space="preserve">18.8458995819092</t>
   </si>
   <si>
     <t xml:space="preserve">19.1762657165527</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3714847564697</t>
+    <t xml:space="preserve">19.3714828491211</t>
   </si>
   <si>
     <t xml:space="preserve">19.056131362915</t>
@@ -2117,37 +2117,37 @@
     <t xml:space="preserve">19.131217956543</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4165306091309</t>
+    <t xml:space="preserve">19.4165344238281</t>
   </si>
   <si>
     <t xml:space="preserve">19.1462345123291</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0110836029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2213153839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7318820953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7769317626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7919483184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8069629669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0772647857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9721508026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2574653625488</t>
+    <t xml:space="preserve">19.0110816955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2213191986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7318840026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7769355773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7919521331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8069686889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0772666931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9721527099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2574634552002</t>
   </si>
   <si>
     <t xml:space="preserve">20.1373310089111</t>
@@ -2156,7 +2156,7 @@
     <t xml:space="preserve">20.1823806762695</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8970680236816</t>
+    <t xml:space="preserve">19.897066116333</t>
   </si>
   <si>
     <t xml:space="preserve">20.0472354888916</t>
@@ -2168,19 +2168,19 @@
     <t xml:space="preserve">20.0171985626221</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6567993164062</t>
+    <t xml:space="preserve">19.6568012237549</t>
   </si>
   <si>
     <t xml:space="preserve">19.8219814300537</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6868324279785</t>
+    <t xml:space="preserve">19.6868343353271</t>
   </si>
   <si>
     <t xml:space="preserve">19.8369998931885</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9421138763428</t>
+    <t xml:space="preserve">19.9421157836914</t>
   </si>
   <si>
     <t xml:space="preserve">20.3325481414795</t>
@@ -2189,46 +2189,46 @@
     <t xml:space="preserve">19.581714630127</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4916172027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.671817779541</t>
+    <t xml:space="preserve">19.4916152954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6718158721924</t>
   </si>
   <si>
     <t xml:space="preserve">19.7168655395508</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7619171142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2874984741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9120845794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.122314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0622482299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3025169372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5728149414062</t>
+    <t xml:space="preserve">19.7619132995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2875003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9120826721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1223163604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0622501373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3025150299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5728130340576</t>
   </si>
   <si>
     <t xml:space="preserve">20.6629161834717</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9932804107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1434459686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1584663391113</t>
+    <t xml:space="preserve">20.993278503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1434497833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1584625244141</t>
   </si>
   <si>
     <t xml:space="preserve">21.3536815643311</t>
@@ -2237,22 +2237,22 @@
     <t xml:space="preserve">21.0082988739014</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2635822296143</t>
+    <t xml:space="preserve">21.2635841369629</t>
   </si>
   <si>
     <t xml:space="preserve">21.2936172485352</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4287643432617</t>
+    <t xml:space="preserve">21.4287662506104</t>
   </si>
   <si>
     <t xml:space="preserve">21.6089649200439</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5338802337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9782638549805</t>
+    <t xml:space="preserve">21.533878326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9782657623291</t>
   </si>
   <si>
     <t xml:space="preserve">20.8881645202637</t>
@@ -2261,43 +2261,43 @@
     <t xml:space="preserve">21.233549118042</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2485618591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1734848022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6479015350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6328792572021</t>
+    <t xml:space="preserve">21.2485637664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1734809875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6478996276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6328811645508</t>
   </si>
   <si>
     <t xml:space="preserve">20.7680320739746</t>
   </si>
   <si>
-    <t xml:space="preserve">21.083381652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7980670928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8670349121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7229804992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2035140991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3086280822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4888305664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5639133453369</t>
+    <t xml:space="preserve">21.0833797454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7980632781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8670310974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7229843139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2035160064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.308629989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4888324737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5639152526855</t>
   </si>
   <si>
     <t xml:space="preserve">21.1134147644043</t>
@@ -2309,10 +2309,10 @@
     <t xml:space="preserve">21.3236484527588</t>
   </si>
   <si>
-    <t xml:space="preserve">21.578929901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8192005157471</t>
+    <t xml:space="preserve">21.5789337158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8191947937012</t>
   </si>
   <si>
     <t xml:space="preserve">21.8492336273193</t>
@@ -2321,37 +2321,37 @@
     <t xml:space="preserve">21.954345703125</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5850486755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4799308776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6601276397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1256446838379</t>
+    <t xml:space="preserve">22.5850467681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4799327850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6601295471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1256465911865</t>
   </si>
   <si>
     <t xml:space="preserve">23.3208618164062</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0805950164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2007255554199</t>
+    <t xml:space="preserve">23.0805969238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2007312774658</t>
   </si>
   <si>
     <t xml:space="preserve">23.3058471679688</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4259796142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6962757110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9215297698975</t>
+    <t xml:space="preserve">23.4259777069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6962776184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9215316772461</t>
   </si>
   <si>
     <t xml:space="preserve">23.7263126373291</t>
@@ -2360,10 +2360,10 @@
     <t xml:space="preserve">23.6662464141846</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9065093994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.290828704834</t>
+    <t xml:space="preserve">23.9065113067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2908306121826</t>
   </si>
   <si>
     <t xml:space="preserve">23.3959465026855</t>
@@ -2375,16 +2375,16 @@
     <t xml:space="preserve">23.0956153869629</t>
   </si>
   <si>
-    <t xml:space="preserve">22.494945526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6300983428955</t>
+    <t xml:space="preserve">22.4949474334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6300945281982</t>
   </si>
   <si>
     <t xml:space="preserve">22.5249805450439</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0355453491211</t>
+    <t xml:space="preserve">23.0355491638184</t>
   </si>
   <si>
     <t xml:space="preserve">22.9454441070557</t>
@@ -2393,28 +2393,28 @@
     <t xml:space="preserve">22.5399971008301</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6000633239746</t>
+    <t xml:space="preserve">22.6000652313232</t>
   </si>
   <si>
     <t xml:space="preserve">22.645112991333</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7352123260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2096328735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.194616317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.104513168335</t>
+    <t xml:space="preserve">22.7352142333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2096290588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1946125030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1045150756836</t>
   </si>
   <si>
     <t xml:space="preserve">22.1795978546143</t>
   </si>
   <si>
-    <t xml:space="preserve">21.729097366333</t>
+    <t xml:space="preserve">21.7290992736816</t>
   </si>
   <si>
     <t xml:space="preserve">22.0594635009766</t>
@@ -2426,115 +2426,115 @@
     <t xml:space="preserve">21.5939464569092</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2785987854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0294303894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7652473449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7051830291748</t>
+    <t xml:space="preserve">21.2785949707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0294284820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7652454376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7051792144775</t>
   </si>
   <si>
     <t xml:space="preserve">22.9904975891113</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9754810333252</t>
+    <t xml:space="preserve">22.9754829406738</t>
   </si>
   <si>
     <t xml:space="preserve">22.8102970123291</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8253154754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0744819641113</t>
+    <t xml:space="preserve">22.8253116607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0744800567627</t>
   </si>
   <si>
     <t xml:space="preserve">22.8853797912598</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1645812988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2997283935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8553447723389</t>
+    <t xml:space="preserve">22.1645851135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.299732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8553466796875</t>
   </si>
   <si>
     <t xml:space="preserve">22.795280456543</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3508949279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1017284393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4471111297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4170780181885</t>
+    <t xml:space="preserve">23.3508968353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1017303466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4471130371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4170799255371</t>
   </si>
   <si>
     <t xml:space="preserve">24.67236328125</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6573467254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7774791717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3269824981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8764781951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2396659851074</t>
+    <t xml:space="preserve">24.6573448181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7774772644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3269786834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8764801025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2396640777588</t>
   </si>
   <si>
     <t xml:space="preserve">20.9181995391846</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4226512908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4827156066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0411167144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5906162261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9688167572021</t>
+    <t xml:space="preserve">20.4226474761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4827175140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0411186218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5906181335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9688186645508</t>
   </si>
   <si>
     <t xml:space="preserve">15.8876190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7975206375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6201047897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6937942504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2146558761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.989405632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6590385437012</t>
+    <t xml:space="preserve">15.7975196838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6201057434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6937952041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.214656829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9894046783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6590394973755</t>
   </si>
   <si>
     <t xml:space="preserve">13.0344552993774</t>
@@ -2543,13 +2543,13 @@
     <t xml:space="preserve">12.7266139984131</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8917961120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9054203033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0180473327637</t>
+    <t xml:space="preserve">12.8917970657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.905421257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0180463790894</t>
   </si>
   <si>
     <t xml:space="preserve">14.581169128418</t>
@@ -2558,61 +2558,61 @@
     <t xml:space="preserve">14.0781116485596</t>
   </si>
   <si>
-    <t xml:space="preserve">14.355920791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1982450485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.318377494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0555868148804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7688789367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.46715259552</t>
+    <t xml:space="preserve">14.3559246063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1982440948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3183784484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0555877685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7688779830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.467155456543</t>
   </si>
   <si>
     <t xml:space="preserve">16.7886199951172</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7074193954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9026355743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9326696395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7674875259399</t>
+    <t xml:space="preserve">15.7074203491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9026374816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9326725006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7674865722656</t>
   </si>
   <si>
     <t xml:space="preserve">15.1518049240112</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3770532608032</t>
+    <t xml:space="preserve">15.3770551681519</t>
   </si>
   <si>
     <t xml:space="preserve">15.4821710586548</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6835021972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8937339782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3442344665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0138683319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5333385467529</t>
+    <t xml:space="preserve">16.6835041046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8937358856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3442363739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0138664245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5333347320557</t>
   </si>
   <si>
     <t xml:space="preserve">16.5033016204834</t>
@@ -2621,13 +2621,13 @@
     <t xml:space="preserve">16.9087524414062</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4643688201904</t>
+    <t xml:space="preserve">17.4643707275391</t>
   </si>
   <si>
     <t xml:space="preserve">17.103967666626</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5244331359863</t>
+    <t xml:space="preserve">17.524435043335</t>
   </si>
   <si>
     <t xml:space="preserve">17.1189842224121</t>
@@ -2636,13 +2636,13 @@
     <t xml:space="preserve">17.2391166687012</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1340007781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.389289855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4043006896973</t>
+    <t xml:space="preserve">17.1339988708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3892841339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4043025970459</t>
   </si>
   <si>
     <t xml:space="preserve">17.6896171569824</t>
@@ -2651,55 +2651,55 @@
     <t xml:space="preserve">18.3653659820557</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2902870178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4855003356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9510173797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2813835144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8520164489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3414497375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5516796112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3953971862793</t>
+    <t xml:space="preserve">18.2902851104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4855041503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9510192871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2813816070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8520183563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3414516448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5516815185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3954029083252</t>
   </si>
   <si>
     <t xml:space="preserve">19.4315490722656</t>
   </si>
   <si>
-    <t xml:space="preserve">20.167366027832</t>
+    <t xml:space="preserve">20.1673679351807</t>
   </si>
   <si>
     <t xml:space="preserve">19.3264331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9571304321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1072998046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6779327392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2663650512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5066337585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8820514678955</t>
+    <t xml:space="preserve">19.9571323394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1073017120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6779346466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2663669586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5066318511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8820476531982</t>
   </si>
   <si>
     <t xml:space="preserve">20.0922832489014</t>
@@ -2720,40 +2720,40 @@
     <t xml:space="preserve">18.9209842681885</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7708148956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8308811187744</t>
+    <t xml:space="preserve">18.7708168029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.830883026123</t>
   </si>
   <si>
     <t xml:space="preserve">19.5666980743408</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0861663818359</t>
+    <t xml:space="preserve">19.0861644744873</t>
   </si>
   <si>
     <t xml:space="preserve">18.9059677124023</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0711479187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7558002471924</t>
+    <t xml:space="preserve">19.0711517333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7558040618896</t>
   </si>
   <si>
     <t xml:space="preserve">19.476598739624</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2963981628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5366687774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5216503143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3114185333252</t>
+    <t xml:space="preserve">19.2964000701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5366668701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5216484069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3114166259766</t>
   </si>
   <si>
     <t xml:space="preserve">18.981050491333</t>
@@ -2762,40 +2762,40 @@
     <t xml:space="preserve">20.4526824951172</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6178646087646</t>
+    <t xml:space="preserve">20.617862701416</t>
   </si>
   <si>
     <t xml:space="preserve">19.6117496490479</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3625793457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6417827606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0322170257568</t>
+    <t xml:space="preserve">20.3625831604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6417808532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0322151184082</t>
   </si>
   <si>
     <t xml:space="preserve">20.5127487182617</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2424468994141</t>
+    <t xml:space="preserve">20.2424488067627</t>
   </si>
   <si>
     <t xml:space="preserve">20.7379989624023</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0021800994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2152004241943</t>
+    <t xml:space="preserve">20.0021820068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.215202331543</t>
   </si>
   <si>
     <t xml:space="preserve">18.1401176452637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3203163146973</t>
+    <t xml:space="preserve">18.3203201293945</t>
   </si>
   <si>
     <t xml:space="preserve">20.5578002929688</t>
@@ -2807,7 +2807,7 @@
     <t xml:space="preserve">21.1284313201904</t>
   </si>
   <si>
-    <t xml:space="preserve">20.783052444458</t>
+    <t xml:space="preserve">20.7830486297607</t>
   </si>
   <si>
     <t xml:space="preserve">20.497730255127</t>
@@ -2825,34 +2825,34 @@
     <t xml:space="preserve">20.9031810760498</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0383319854736</t>
+    <t xml:space="preserve">21.038330078125</t>
   </si>
   <si>
     <t xml:space="preserve">20.4076309204102</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5427799224854</t>
+    <t xml:space="preserve">20.5427837371826</t>
   </si>
   <si>
     <t xml:space="preserve">20.3175315856934</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2124176025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4465637207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7469005584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2363357543945</t>
+    <t xml:space="preserve">20.2124156951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4465618133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.746898651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2363338470459</t>
   </si>
   <si>
     <t xml:space="preserve">20.5277652740479</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7140789031982</t>
+    <t xml:space="preserve">21.7140808105469</t>
   </si>
   <si>
     <t xml:space="preserve">21.6840476989746</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">21.6389980316162</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3386650085449</t>
+    <t xml:space="preserve">21.3386631011963</t>
   </si>
   <si>
     <t xml:space="preserve">21.6239814758301</t>
@@ -2870,31 +2870,31 @@
     <t xml:space="preserve">21.8642482757568</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3987312316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4437828063965</t>
+    <t xml:space="preserve">21.3987331390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4437808990479</t>
   </si>
   <si>
     <t xml:space="preserve">21.188497543335</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9092960357666</t>
+    <t xml:space="preserve">21.9092979431152</t>
   </si>
   <si>
     <t xml:space="preserve">21.8942794799805</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8342151641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5038471221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2546806335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0444469451904</t>
+    <t xml:space="preserve">21.8342113494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.503849029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2546787261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0444488525391</t>
   </si>
   <si>
     <t xml:space="preserve">22.2847137451172</t>
@@ -2909,34 +2909,34 @@
     <t xml:space="preserve">22.6901626586914</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8703632354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6150779724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.570032119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6751441955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5775375366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9079036712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0430545806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0881042480469</t>
+    <t xml:space="preserve">22.870361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6150817871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5700283050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6751461029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5775356292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9079074859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0430564880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0881061553955</t>
   </si>
   <si>
     <t xml:space="preserve">22.8178024291992</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8403282165527</t>
+    <t xml:space="preserve">22.8403301239014</t>
   </si>
   <si>
     <t xml:space="preserve">23.1706962585449</t>
@@ -2945,25 +2945,25 @@
     <t xml:space="preserve">23.215747833252</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3809299468994</t>
+    <t xml:space="preserve">23.3809280395508</t>
   </si>
   <si>
     <t xml:space="preserve">23.5235862731934</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0505638122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.915412902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0730876922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2532863616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3433895111084</t>
+    <t xml:space="preserve">23.0505619049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9154148101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0730895996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.253288269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3433876037598</t>
   </si>
   <si>
     <t xml:space="preserve">23.2983379364014</t>
@@ -2978,25 +2978,25 @@
     <t xml:space="preserve">24.0942211151123</t>
   </si>
   <si>
-    <t xml:space="preserve">24.664852142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5522308349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4621295928955</t>
+    <t xml:space="preserve">24.6648540496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5522289276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4621276855469</t>
   </si>
   <si>
     <t xml:space="preserve">24.7924938201904</t>
   </si>
   <si>
-    <t xml:space="preserve">24.402063369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0491676330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4696369171143</t>
+    <t xml:space="preserve">24.4020614624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0491695404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4696350097656</t>
   </si>
   <si>
     <t xml:space="preserve">24.4245853424072</t>
@@ -3005,82 +3005,82 @@
     <t xml:space="preserve">24.1993350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9590702056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1617946624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2293701171875</t>
+    <t xml:space="preserve">23.9590721130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.161792755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2293720245361</t>
   </si>
   <si>
     <t xml:space="preserve">24.6273097991943</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8075122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8150196075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1078414916992</t>
+    <t xml:space="preserve">24.8075141906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8150215148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1078433990479</t>
   </si>
   <si>
     <t xml:space="preserve">25.2204685211182</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1003379821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1829280853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2955513000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5208015441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8286437988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8061199188232</t>
+    <t xml:space="preserve">25.1003360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1829261779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2955532073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5208053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8286457061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8061180114746</t>
   </si>
   <si>
     <t xml:space="preserve">25.7385444641113</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7835922241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0538921356201</t>
+    <t xml:space="preserve">25.7835941314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0538940429688</t>
   </si>
   <si>
     <t xml:space="preserve">25.8661823272705</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4893779754639</t>
+    <t xml:space="preserve">26.4893760681152</t>
   </si>
   <si>
     <t xml:space="preserve">26.5118999481201</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3767509460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.466854095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.65456199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.586986541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1050605773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5180225372314</t>
+    <t xml:space="preserve">26.3767547607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4668521881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6545600891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5869846343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1050567626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5180187225342</t>
   </si>
   <si>
     <t xml:space="preserve">27.1350936889648</t>
@@ -3089,19 +3089,19 @@
     <t xml:space="preserve">27.3903751373291</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0149593353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.037483215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2176818847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1951599121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2251930236816</t>
+    <t xml:space="preserve">27.0149631500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0374851226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2176856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.195161819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.225191116333</t>
   </si>
   <si>
     <t xml:space="preserve">26.2566184997559</t>
@@ -3110,106 +3110,106 @@
     <t xml:space="preserve">26.684591293335</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1726322174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.029972076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7446537017822</t>
+    <t xml:space="preserve">27.1726360321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0299739837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7446594238281</t>
   </si>
   <si>
     <t xml:space="preserve">26.6245250701904</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8962211608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0163536071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3992729187012</t>
+    <t xml:space="preserve">25.8962230682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0163555145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3992748260498</t>
   </si>
   <si>
     <t xml:space="preserve">26.3542232513428</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5569515228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.001335144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0238609313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4218006134033</t>
+    <t xml:space="preserve">26.5569496154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0013370513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0238628387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4217987060547</t>
   </si>
   <si>
     <t xml:space="preserve">26.2866516113281</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2115707397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8873195648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1125679016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3603420257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3828678131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6456623077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6231327056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7808074951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5931053161621</t>
+    <t xml:space="preserve">26.2115726470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.887321472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.11256980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3603401184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3828639984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.645658493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6231365203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7808132171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5930995941162</t>
   </si>
   <si>
     <t xml:space="preserve">27.42041015625</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5630626678467</t>
+    <t xml:space="preserve">27.5630645751953</t>
   </si>
   <si>
     <t xml:space="preserve">27.7883186340332</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7132320404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9534969329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9835319519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2613391876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.141206741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2087860107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1862621307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3814754486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2012767791748</t>
+    <t xml:space="preserve">27.7132358551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9535026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9835357666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2613430023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1412048339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2087821960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.18625831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3814735412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2012748718262</t>
   </si>
   <si>
     <t xml:space="preserve">28.0586185455322</t>
@@ -3218,16 +3218,16 @@
     <t xml:space="preserve">28.1186828613281</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4115123748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.169849395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3875885009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5077209472656</t>
+    <t xml:space="preserve">28.4115104675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1698474884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3875904083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.507719039917</t>
   </si>
   <si>
     <t xml:space="preserve">29.2899856567383</t>
@@ -3236,37 +3236,37 @@
     <t xml:space="preserve">28.9145622253418</t>
   </si>
   <si>
-    <t xml:space="preserve">28.419017791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6442623138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1923770904541</t>
+    <t xml:space="preserve">28.4190158843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6442718505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1923751831055</t>
   </si>
   <si>
     <t xml:space="preserve">29.1323051452637</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2149028778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5841999053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.48659324646</t>
+    <t xml:space="preserve">29.2148971557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5842018127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4865913391113</t>
   </si>
   <si>
     <t xml:space="preserve">28.4565620422363</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5466575622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4640693664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8784160614014</t>
+    <t xml:space="preserve">28.5466556549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4640655517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8784198760986</t>
   </si>
   <si>
     <t xml:space="preserve">28.4715747833252</t>
@@ -3275,52 +3275,52 @@
     <t xml:space="preserve">28.4039993286133</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0736351013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3964900970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0285835266113</t>
+    <t xml:space="preserve">28.0736331939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3964881896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0285816192627</t>
   </si>
   <si>
     <t xml:space="preserve">28.7644023895264</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6954307556152</t>
+    <t xml:space="preserve">29.6954288482666</t>
   </si>
   <si>
     <t xml:space="preserve">29.717960357666</t>
   </si>
   <si>
-    <t xml:space="preserve">29.943208694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4012145996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7240695953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.521354675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6940402984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5288581848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7090511322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4988250732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7766304016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7602233886719</t>
+    <t xml:space="preserve">29.9432067871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4012184143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7240676879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5213508605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6940460205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5288524627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7090530395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4988212585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7766265869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7602195739746</t>
   </si>
   <si>
     <t xml:space="preserve">32.2107238769531</t>
@@ -3329,10 +3329,10 @@
     <t xml:space="preserve">32.4359741210938</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7376937866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1506500244141</t>
+    <t xml:space="preserve">31.7377052307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1506614685059</t>
   </si>
   <si>
     <t xml:space="preserve">32.3083343505859</t>
@@ -3341,43 +3341,43 @@
     <t xml:space="preserve">32.345874786377</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8728485107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1370315551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.859224319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0544338226318</t>
+    <t xml:space="preserve">31.8728446960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1370334625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8592205047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0544376373291</t>
   </si>
   <si>
     <t xml:space="preserve">31.4641075134277</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2591991424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0342788696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6406764984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8052806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1265850067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.08642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.058385848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9378890991211</t>
+    <t xml:space="preserve">30.2592010498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0342826843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.640682220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8052825927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1265869140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0864276885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0583820343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.937894821167</t>
   </si>
   <si>
     <t xml:space="preserve">30.1146125793457</t>
@@ -3386,40 +3386,40 @@
     <t xml:space="preserve">30.5885429382324</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3596782684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3195247650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0303401947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1508331298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.335578918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2632904052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1668949127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1187000274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.604606628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7531394958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4118232727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5644454956055</t>
+    <t xml:space="preserve">31.3596801757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3195190429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0303421020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1508293151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3355865478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2632884979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1668930053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1187038421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6046047210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7531452178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4118213653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5644435882568</t>
   </si>
   <si>
     <t xml:space="preserve">30.5483798980713</t>
@@ -3428,127 +3428,127 @@
     <t xml:space="preserve">30.9419803619385</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2713222503662</t>
+    <t xml:space="preserve">31.2713241577148</t>
   </si>
   <si>
     <t xml:space="preserve">31.1829624176025</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1267337799072</t>
+    <t xml:space="preserve">31.1267318725586</t>
   </si>
   <si>
     <t xml:space="preserve">31.2150917053223</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2311573028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1909961700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4359264373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2029685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1788749694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8375549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8616542816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5082149505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3475646972656</t>
+    <t xml:space="preserve">31.2311592102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1909980773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4359188079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2029724121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1788730621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8375606536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8616523742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5082111358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3475589752197</t>
   </si>
   <si>
     <t xml:space="preserve">30.2913303375244</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4800300598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8856048583984</t>
+    <t xml:space="preserve">29.4800319671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8856067657471</t>
   </si>
   <si>
     <t xml:space="preserve">29.3996982574463</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9338054656982</t>
+    <t xml:space="preserve">28.933801651001</t>
   </si>
   <si>
     <t xml:space="preserve">27.7208652496338</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1907043457031</t>
+    <t xml:space="preserve">27.190710067749</t>
   </si>
   <si>
     <t xml:space="preserve">27.680700302124</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9939746856689</t>
+    <t xml:space="preserve">27.9939765930176</t>
   </si>
   <si>
     <t xml:space="preserve">28.0743045806885</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5803642272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9659328460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0783920288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8695411682129</t>
+    <t xml:space="preserve">28.5803680419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9659366607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0783882141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8695430755615</t>
   </si>
   <si>
     <t xml:space="preserve">28.8374118804932</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8133144378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6285629272461</t>
+    <t xml:space="preserve">28.8133125305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6285610198975</t>
   </si>
   <si>
     <t xml:space="preserve">29.3595352172852</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0944576263428</t>
+    <t xml:space="preserve">29.09446144104</t>
   </si>
   <si>
     <t xml:space="preserve">28.9579029083252</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3152828216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1587181091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3675727844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8936443328857</t>
+    <t xml:space="preserve">28.3152885437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1587219238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3675708770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8936386108398</t>
   </si>
   <si>
     <t xml:space="preserve">28.8026943206787</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2799034118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4106025695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9600028991699</t>
+    <t xml:space="preserve">28.2799015045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4106044769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9600048065186</t>
   </si>
   <si>
     <t xml:space="preserve">26.9974250793457</t>
@@ -3557,16 +3557,16 @@
     <t xml:space="preserve">26.9810848236084</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9028244018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9273262023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3228492736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3623714447021</t>
+    <t xml:space="preserve">25.9028224945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9273281097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.322847366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3623676300049</t>
   </si>
   <si>
     <t xml:space="preserve">22.8885879516602</t>
@@ -3575,40 +3575,40 @@
     <t xml:space="preserve">23.5175743103027</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3963623046875</t>
+    <t xml:space="preserve">25.3963661193848</t>
   </si>
   <si>
     <t xml:space="preserve">24.7101974487305</t>
   </si>
   <si>
-    <t xml:space="preserve">25.306510925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7231121063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8211364746094</t>
+    <t xml:space="preserve">25.3065090179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7231101989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8211345672607</t>
   </si>
   <si>
     <t xml:space="preserve">27.1281223297119</t>
   </si>
   <si>
-    <t xml:space="preserve">26.956579208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.144458770752</t>
+    <t xml:space="preserve">26.9565773010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1444568634033</t>
   </si>
   <si>
     <t xml:space="preserve">26.7768688201904</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1036186218262</t>
+    <t xml:space="preserve">27.1036167144775</t>
   </si>
   <si>
     <t xml:space="preserve">27.0709400177002</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9892559051514</t>
+    <t xml:space="preserve">26.9892539978027</t>
   </si>
   <si>
     <t xml:space="preserve">27.0300998687744</t>
@@ -3626,46 +3626,46 @@
     <t xml:space="preserve">27.5447254180908</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9776630401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5937385559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5481491088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7523670196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8830604553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8667221069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5399780273438</t>
+    <t xml:space="preserve">27.9776668548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5937347412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5481472015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7523651123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8830623626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8667240142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5399799346924</t>
   </si>
   <si>
     <t xml:space="preserve">26.4991340637207</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3439292907715</t>
+    <t xml:space="preserve">26.3439311981201</t>
   </si>
   <si>
     <t xml:space="preserve">25.6414241790771</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2377376556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3520946502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1152076721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9109897613525</t>
+    <t xml:space="preserve">26.2377395629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3521003723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1152057647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9109916687012</t>
   </si>
   <si>
     <t xml:space="preserve">25.3146800994873</t>
@@ -3677,34 +3677,34 @@
     <t xml:space="preserve">25.2738380432129</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6740989685059</t>
+    <t xml:space="preserve">25.6741008758545</t>
   </si>
   <si>
     <t xml:space="preserve">25.8048000335693</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3555221557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9634246826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9913558959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3017635345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8374710083008</t>
+    <t xml:space="preserve">25.3555240631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9634265899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9913578033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3017673492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8374729156494</t>
   </si>
   <si>
     <t xml:space="preserve">26.3766040802002</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4256153106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5154705047607</t>
+    <t xml:space="preserve">26.4256172180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.515474319458</t>
   </si>
   <si>
     <t xml:space="preserve">26.4419536590576</t>
@@ -3713,19 +3713,19 @@
     <t xml:space="preserve">26.6380023956299</t>
   </si>
   <si>
-    <t xml:space="preserve">26.507303237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5489654541016</t>
+    <t xml:space="preserve">26.5073051452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5489635467529</t>
   </si>
   <si>
     <t xml:space="preserve">26.7698364257812</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4734287261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5743732452393</t>
+    <t xml:space="preserve">26.4734306335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5743713378906</t>
   </si>
   <si>
     <t xml:space="preserve">27.6759948730469</t>
@@ -3734,13 +3734,13 @@
     <t xml:space="preserve">27.9639358520508</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5828399658203</t>
+    <t xml:space="preserve">27.5828380584717</t>
   </si>
   <si>
     <t xml:space="preserve">27.3457126617432</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5235595703125</t>
+    <t xml:space="preserve">27.5235576629639</t>
   </si>
   <si>
     <t xml:space="preserve">26.7274913787842</t>
@@ -3749,10 +3749,10 @@
     <t xml:space="preserve">27.5320262908936</t>
   </si>
   <si>
-    <t xml:space="preserve">26.956148147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2108974456787</t>
+    <t xml:space="preserve">26.9561500549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2108993530273</t>
   </si>
   <si>
     <t xml:space="preserve">25.5164546966553</t>
@@ -3761,7 +3761,7 @@
     <t xml:space="preserve">23.3992557525635</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8149127960205</t>
+    <t xml:space="preserve">22.8149108886719</t>
   </si>
   <si>
     <t xml:space="preserve">23.348445892334</t>
@@ -3776,13 +3776,13 @@
     <t xml:space="preserve">23.4161949157715</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5686340332031</t>
+    <t xml:space="preserve">23.5686321258545</t>
   </si>
   <si>
     <t xml:space="preserve">23.3569145202637</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0859146118164</t>
+    <t xml:space="preserve">23.085916519165</t>
   </si>
   <si>
     <t xml:space="preserve">23.8904476165771</t>
@@ -3797,13 +3797,13 @@
     <t xml:space="preserve">23.3230400085449</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8318500518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7471618652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7132873535156</t>
+    <t xml:space="preserve">22.8318481445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.747163772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.713285446167</t>
   </si>
   <si>
     <t xml:space="preserve">21.64621925354</t>
@@ -3812,43 +3812,43 @@
     <t xml:space="preserve">21.9510955810547</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2644443511963</t>
+    <t xml:space="preserve">22.264440536499</t>
   </si>
   <si>
     <t xml:space="preserve">22.7810382843018</t>
   </si>
   <si>
-    <t xml:space="preserve">22.112003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4592247009277</t>
+    <t xml:space="preserve">22.1120014190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4592227935791</t>
   </si>
   <si>
     <t xml:space="preserve">22.222095489502</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3074703216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7563152313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2898502349854</t>
+    <t xml:space="preserve">21.3074684143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7563133239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2898483276367</t>
   </si>
   <si>
     <t xml:space="preserve">23.052038192749</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0351009368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5185031890869</t>
+    <t xml:space="preserve">23.0351028442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5185050964355</t>
   </si>
   <si>
     <t xml:space="preserve">23.0096950531006</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5015659332275</t>
+    <t xml:space="preserve">22.5015678405762</t>
   </si>
   <si>
     <t xml:space="preserve">22.6116619110107</t>
@@ -3857,16 +3857,16 @@
     <t xml:space="preserve">23.1536655426025</t>
   </si>
   <si>
-    <t xml:space="preserve">23.966667175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0513553619385</t>
+    <t xml:space="preserve">23.9666652679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0513534545898</t>
   </si>
   <si>
     <t xml:space="preserve">23.9327926635742</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4239807128906</t>
+    <t xml:space="preserve">24.4239826202393</t>
   </si>
   <si>
     <t xml:space="preserve">24.5256080627441</t>
@@ -3878,16 +3878,16 @@
     <t xml:space="preserve">23.8565731048584</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4416007995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7888240814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1275730133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.136043548584</t>
+    <t xml:space="preserve">23.4416027069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7888221740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1275749206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1360416412354</t>
   </si>
   <si>
     <t xml:space="preserve">23.500883102417</t>
@@ -3902,22 +3902,22 @@
     <t xml:space="preserve">22.5354442596436</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9334754943848</t>
+    <t xml:space="preserve">22.9334735870361</t>
   </si>
   <si>
     <t xml:space="preserve">22.7725677490234</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0950660705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0273170471191</t>
+    <t xml:space="preserve">22.095064163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0273132324219</t>
   </si>
   <si>
     <t xml:space="preserve">22.2559719085693</t>
   </si>
   <si>
-    <t xml:space="preserve">22.391471862793</t>
+    <t xml:space="preserve">22.3914737701416</t>
   </si>
   <si>
     <t xml:space="preserve">21.925687789917</t>
@@ -3935,25 +3935,25 @@
     <t xml:space="preserve">23.0689754486084</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9243240356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3907871246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9419441223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6455364227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7302265167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3921546936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5022468566895</t>
+    <t xml:space="preserve">23.9243259429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3907909393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9419460296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6455345153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.730224609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3921566009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5022487640381</t>
   </si>
   <si>
     <t xml:space="preserve">21.3413429260254</t>
@@ -3965,19 +3965,19 @@
     <t xml:space="preserve">21.0957489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6553707122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8078079223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3335571289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2207336425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2552871704102</t>
+    <t xml:space="preserve">20.6553688049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8078098297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3335590362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2207298278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2552890777588</t>
   </si>
   <si>
     <t xml:space="preserve">24.0344161987305</t>
@@ -3989,7 +3989,7 @@
     <t xml:space="preserve">22.7979755401611</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4331340789795</t>
+    <t xml:space="preserve">23.4331359863281</t>
   </si>
   <si>
     <t xml:space="preserve">23.6533222198486</t>
@@ -4001,16 +4001,16 @@
     <t xml:space="preserve">24.3308238983154</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3477630615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2037944793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.79660987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1438293457031</t>
+    <t xml:space="preserve">24.3477649688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2037925720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7966079711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1438312530518</t>
   </si>
   <si>
     <t xml:space="preserve">25.8298015594482</t>
@@ -4019,34 +4019,34 @@
     <t xml:space="preserve">25.9737701416016</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2871150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3802719116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6265487670898</t>
+    <t xml:space="preserve">26.2871170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3802738189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6265506744385</t>
   </si>
   <si>
     <t xml:space="preserve">25.7197074890137</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6858329772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3294563293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3118362426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9307422637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9053363800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1756572723389</t>
+    <t xml:space="preserve">25.6858291625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.329460144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3118381500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9307441711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9053344726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1756553649902</t>
   </si>
   <si>
     <t xml:space="preserve">28.2264671325684</t>
@@ -4058,40 +4058,40 @@
     <t xml:space="preserve">28.4551219940186</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2434062957764</t>
+    <t xml:space="preserve">28.2434043884277</t>
   </si>
   <si>
     <t xml:space="preserve">28.1163730621338</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3111572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1671867370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4297199249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.709192276001</t>
+    <t xml:space="preserve">28.3111553192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1671848297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4297161102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7091903686523</t>
   </si>
   <si>
     <t xml:space="preserve">27.1848049163818</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2779636383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0069637298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9476795196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2864322662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0238971710205</t>
+    <t xml:space="preserve">27.277961730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0069599151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9476833343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.286434173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0238990783691</t>
   </si>
   <si>
     <t xml:space="preserve">27.6675262451172</t>
@@ -4100,7 +4100,7 @@
     <t xml:space="preserve">27.4981517791748</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2610263824463</t>
+    <t xml:space="preserve">27.2610244750977</t>
   </si>
   <si>
     <t xml:space="preserve">27.0577754974365</t>
@@ -4109,7 +4109,7 @@
     <t xml:space="preserve">27.269495010376</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5574340820312</t>
+    <t xml:space="preserve">27.5574321746826</t>
   </si>
   <si>
     <t xml:space="preserve">28.0909633636475</t>
@@ -4118,49 +4118,49 @@
     <t xml:space="preserve">27.125524520874</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0916500091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7105579376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7952404022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.421932220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2271537780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4304008483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3203029632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1509342193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7014026641846</t>
+    <t xml:space="preserve">27.0916481018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7105560302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7952423095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4219341278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2271518707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4304027557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3203067779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1509323120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7014007568359</t>
   </si>
   <si>
     <t xml:space="preserve">28.2349376678467</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9046516418457</t>
+    <t xml:space="preserve">27.9046535491943</t>
   </si>
   <si>
     <t xml:space="preserve">28.1925926208496</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4720611572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4635963439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0818138122559</t>
+    <t xml:space="preserve">28.4720630645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4635925292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0818176269531</t>
   </si>
   <si>
     <t xml:space="preserve">29.2935352325439</t>
@@ -4169,70 +4169,70 @@
     <t xml:space="preserve">29.0479373931885</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7938766479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6922550201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4043121337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.717658996582</t>
+    <t xml:space="preserve">28.7938747406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6922512054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4043140411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7176570892334</t>
   </si>
   <si>
     <t xml:space="preserve">28.844690322876</t>
   </si>
   <si>
-    <t xml:space="preserve">28.836217880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8531551361084</t>
+    <t xml:space="preserve">28.8362197875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.853157043457</t>
   </si>
   <si>
     <t xml:space="preserve">28.6244964599609</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8108139038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8785648345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0902805328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.870096206665</t>
+    <t xml:space="preserve">28.81081199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8785610198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0902824401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8700981140137</t>
   </si>
   <si>
     <t xml:space="preserve">28.8277530670166</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1417789459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7600021362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6753120422363</t>
+    <t xml:space="preserve">28.1417770385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7600002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6753101348877</t>
   </si>
   <si>
     <t xml:space="preserve">28.759183883667</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2301368713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0740280151367</t>
+    <t xml:space="preserve">28.2301387786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0740299224854</t>
   </si>
   <si>
     <t xml:space="preserve">28.1954479217529</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0133171081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2908515930176</t>
+    <t xml:space="preserve">28.0133190155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2908496856689</t>
   </si>
   <si>
     <t xml:space="preserve">28.3515567779541</t>
@@ -4244,13 +4244,13 @@
     <t xml:space="preserve">28.1520843505859</t>
   </si>
   <si>
-    <t xml:space="preserve">28.308198928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2214698791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1434135437012</t>
+    <t xml:space="preserve">28.3081951141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2214679718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1434154510498</t>
   </si>
   <si>
     <t xml:space="preserve">26.9812507629395</t>
@@ -4265,22 +4265,22 @@
     <t xml:space="preserve">26.0185623168945</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9344539642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0558738708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2753200531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9951667785645</t>
+    <t xml:space="preserve">24.934455871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0558757781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.275318145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9951648712158</t>
   </si>
   <si>
     <t xml:space="preserve">25.8017406463623</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3594245910645</t>
+    <t xml:space="preserve">25.3594264984131</t>
   </si>
   <si>
     <t xml:space="preserve">25.3247356414795</t>
@@ -4310,10 +4310,10 @@
     <t xml:space="preserve">25.3073902130127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9518032073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5068626403809</t>
+    <t xml:space="preserve">24.9518013000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5068664550781</t>
   </si>
   <si>
     <t xml:space="preserve">25.9058170318604</t>
@@ -4322,7 +4322,7 @@
     <t xml:space="preserve">26.1052913665771</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6716480255127</t>
+    <t xml:space="preserve">25.6716499328613</t>
   </si>
   <si>
     <t xml:space="preserve">26.0359077453613</t>
@@ -4331,25 +4331,25 @@
     <t xml:space="preserve">25.6196117401123</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2006931304932</t>
+    <t xml:space="preserve">26.2006912231445</t>
   </si>
   <si>
     <t xml:space="preserve">26.408842086792</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4435348510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5042400360107</t>
+    <t xml:space="preserve">26.4435329437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5042419433594</t>
   </si>
   <si>
     <t xml:space="preserve">26.313440322876</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1833457946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.452205657959</t>
+    <t xml:space="preserve">26.1833477020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4522037506104</t>
   </si>
   <si>
     <t xml:space="preserve">26.0966186523438</t>
@@ -4358,25 +4358,25 @@
     <t xml:space="preserve">25.4721736907959</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6109409332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3767700195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3307838439941</t>
+    <t xml:space="preserve">25.6109390258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3767719268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3307857513428</t>
   </si>
   <si>
     <t xml:space="preserve">26.1920204162598</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0098896026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8104152679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5215854644775</t>
+    <t xml:space="preserve">26.0098915100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8104133605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5215892791748</t>
   </si>
   <si>
     <t xml:space="preserve">26.8424835205078</t>
@@ -4385,46 +4385,46 @@
     <t xml:space="preserve">26.4868984222412</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5996437072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7297382354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1062088012695</t>
+    <t xml:space="preserve">26.599645614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.729736328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1062126159668</t>
   </si>
   <si>
     <t xml:space="preserve">27.0882835388184</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3353328704834</t>
+    <t xml:space="preserve">26.335334777832</t>
   </si>
   <si>
     <t xml:space="preserve">26.4070415496826</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6759548187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7028465270996</t>
+    <t xml:space="preserve">26.675952911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.702844619751</t>
   </si>
   <si>
     <t xml:space="preserve">26.3084411621094</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8154392242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3622245788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8821182250977</t>
+    <t xml:space="preserve">25.8154373168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3622264862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8821201324463</t>
   </si>
   <si>
     <t xml:space="preserve">26.6938819885254</t>
   </si>
   <si>
-    <t xml:space="preserve">27.20481300354</t>
+    <t xml:space="preserve">27.2048110961914</t>
   </si>
   <si>
     <t xml:space="preserve">27.4737224578857</t>
@@ -4433,13 +4433,13 @@
     <t xml:space="preserve">27.5185413360596</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3930473327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6529960632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7157421112061</t>
+    <t xml:space="preserve">27.3930492401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6529979705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7157440185547</t>
   </si>
   <si>
     <t xml:space="preserve">27.9219055175781</t>
@@ -4451,25 +4451,25 @@
     <t xml:space="preserve">27.9667263031006</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9398345947266</t>
+    <t xml:space="preserve">27.9398365020752</t>
   </si>
   <si>
     <t xml:space="preserve">27.7605609893799</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6619606018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4647579193115</t>
+    <t xml:space="preserve">27.6619625091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4647598266602</t>
   </si>
   <si>
     <t xml:space="preserve">27.3840847015381</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3213405609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6081790924072</t>
+    <t xml:space="preserve">27.3213386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.60817527771</t>
   </si>
   <si>
     <t xml:space="preserve">27.9487991333008</t>
@@ -4478,16 +4478,16 @@
     <t xml:space="preserve">28.0115451812744</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2356376647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7644939422607</t>
+    <t xml:space="preserve">28.2356357574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7644958496094</t>
   </si>
   <si>
     <t xml:space="preserve">28.3611278533936</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9129447937012</t>
+    <t xml:space="preserve">27.9129428863525</t>
   </si>
   <si>
     <t xml:space="preserve">27.4378681182861</t>
@@ -4502,43 +4502,43 @@
     <t xml:space="preserve">28.5045471191406</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7465686798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6927852630615</t>
+    <t xml:space="preserve">28.7465667724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6927833557129</t>
   </si>
   <si>
     <t xml:space="preserve">28.7555332183838</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9796257019043</t>
+    <t xml:space="preserve">28.9796237945557</t>
   </si>
   <si>
     <t xml:space="preserve">29.0334053039551</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1320056915283</t>
+    <t xml:space="preserve">29.132007598877</t>
   </si>
   <si>
     <t xml:space="preserve">29.3740272521973</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2306060791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7056846618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1000881195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9606037139893</t>
+    <t xml:space="preserve">29.2306079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7056827545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1000862121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9606018066406</t>
   </si>
   <si>
     <t xml:space="preserve">30.5482711791992</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1986865997314</t>
+    <t xml:space="preserve">30.1986827850342</t>
   </si>
   <si>
     <t xml:space="preserve">29.8132457733154</t>
@@ -4547,10 +4547,10 @@
     <t xml:space="preserve">29.8311729431152</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7734565734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1588954925537</t>
+    <t xml:space="preserve">28.773458480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1588973999023</t>
   </si>
   <si>
     <t xml:space="preserve">29.3202438354492</t>
@@ -4559,13 +4559,13 @@
     <t xml:space="preserve">29.1140785217285</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4457321166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.365062713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0871887207031</t>
+    <t xml:space="preserve">29.4457340240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3650608062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0871906280518</t>
   </si>
   <si>
     <t xml:space="preserve">28.7017478942871</t>
@@ -4577,31 +4577,31 @@
     <t xml:space="preserve">29.1768226623535</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2574996948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3112831115723</t>
+    <t xml:space="preserve">29.2574977874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3112812042236</t>
   </si>
   <si>
     <t xml:space="preserve">29.5712280273438</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1628303527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.974588394165</t>
+    <t xml:space="preserve">30.1628322601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9745922088623</t>
   </si>
   <si>
     <t xml:space="preserve">30.2166118621826</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0014839172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0283737182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7773914337158</t>
+    <t xml:space="preserve">30.001485824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0283756256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7773933410645</t>
   </si>
   <si>
     <t xml:space="preserve">29.7236099243164</t>
@@ -4610,13 +4610,13 @@
     <t xml:space="preserve">29.7684268951416</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1717967987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.180757522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4586353302002</t>
+    <t xml:space="preserve">30.1717948913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1807556152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4586334228516</t>
   </si>
   <si>
     <t xml:space="preserve">30.0104484558105</t>
@@ -4625,52 +4625,52 @@
     <t xml:space="preserve">30.2703971862793</t>
   </si>
   <si>
-    <t xml:space="preserve">30.593090057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.144905090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.153865814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0463047027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0373382568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6967182159424</t>
+    <t xml:space="preserve">30.5930881500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1449069976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1538677215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0463027954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0373363494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6967220306396</t>
   </si>
   <si>
     <t xml:space="preserve">29.1678619384766</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6877536773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3292083740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4278125762939</t>
+    <t xml:space="preserve">29.6877555847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3292102813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4278087615967</t>
   </si>
   <si>
     <t xml:space="preserve">30.0552654266357</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7107124328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5224761962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4776554107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2177085876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7426319122314</t>
+    <t xml:space="preserve">28.7107105255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5224742889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4776592254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2177066802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7426338195801</t>
   </si>
   <si>
     <t xml:space="preserve">27.3392658233643</t>
@@ -4679,10 +4679,10 @@
     <t xml:space="preserve">27.5095767974854</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3571968078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0524291992188</t>
+    <t xml:space="preserve">27.3571949005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0524311065674</t>
   </si>
   <si>
     <t xml:space="preserve">27.1868839263916</t>
@@ -4691,49 +4691,49 @@
     <t xml:space="preserve">27.2854843139648</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2944488525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4468326568604</t>
+    <t xml:space="preserve">27.2944507598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4468307495117</t>
   </si>
   <si>
     <t xml:space="preserve">27.5454330444336</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0294723510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.405948638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1191082000732</t>
+    <t xml:space="preserve">28.0294742584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4059467315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1191101074219</t>
   </si>
   <si>
     <t xml:space="preserve">28.2714920043945</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6838226318359</t>
+    <t xml:space="preserve">28.6838207244873</t>
   </si>
   <si>
     <t xml:space="preserve">28.495584487915</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0423698425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7325744628906</t>
+    <t xml:space="preserve">29.0423717498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.732572555542</t>
   </si>
   <si>
     <t xml:space="preserve">29.7863540649414</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3919525146484</t>
+    <t xml:space="preserve">29.3919544219971</t>
   </si>
   <si>
     <t xml:space="preserve">29.4547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">29.849100112915</t>
+    <t xml:space="preserve">29.8491020202637</t>
   </si>
   <si>
     <t xml:space="preserve">29.194751739502</t>
@@ -4748,10 +4748,10 @@
     <t xml:space="preserve">29.0602951049805</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1499366760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4367733001709</t>
+    <t xml:space="preserve">29.1499328613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4367713928223</t>
   </si>
   <si>
     <t xml:space="preserve">29.0961513519287</t>
@@ -4760,49 +4760,49 @@
     <t xml:space="preserve">29.24853515625</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5891532897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6070804595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7953205108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2883262634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0731945037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4048500061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4317436218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3600292205811</t>
+    <t xml:space="preserve">29.5891513824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6070823669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7953224182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2883243560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0731925964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4048480987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4317417144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3600330352783</t>
   </si>
   <si>
     <t xml:space="preserve">30.2255764007568</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1359367370605</t>
+    <t xml:space="preserve">30.1359405517578</t>
   </si>
   <si>
     <t xml:space="preserve">30.3152122497559</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3421039581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7454700469971</t>
+    <t xml:space="preserve">30.3421020507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7454719543457</t>
   </si>
   <si>
     <t xml:space="preserve">30.3331394195557</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0642337799072</t>
+    <t xml:space="preserve">30.0642318725586</t>
   </si>
   <si>
     <t xml:space="preserve">30.6110172271729</t>
@@ -4814,82 +4814,82 @@
     <t xml:space="preserve">31.0860919952393</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1936550140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1578006744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1757297515869</t>
+    <t xml:space="preserve">31.1936588287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1577987670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1757259368896</t>
   </si>
   <si>
     <t xml:space="preserve">31.3818893432617</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5522041320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8121528625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8480052947998</t>
+    <t xml:space="preserve">31.5522079467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8121547698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8480072021484</t>
   </si>
   <si>
     <t xml:space="preserve">32.0003852844238</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2384719848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7135543823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.731481552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5432415008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8211135864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1258773803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0900268554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2743282318115</t>
+    <t xml:space="preserve">31.2384738922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.713550567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7314796447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5432357788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8300762176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.821117401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1258811950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0900230407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2743301391602</t>
   </si>
   <si>
     <t xml:space="preserve">30.9068183898926</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9785308837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1090507507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3958892822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8551120758057</t>
+    <t xml:space="preserve">30.9785289764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1090469360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3958873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8551158905029</t>
   </si>
   <si>
     <t xml:space="preserve">30.3069019317627</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6632442474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.430736541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2895965576172</t>
+    <t xml:space="preserve">30.6632404327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4307384490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2896003723145</t>
   </si>
   <si>
     <t xml:space="preserve">31.9606704711914</t>
@@ -4907,16 +4907,16 @@
     <t xml:space="preserve">31.3941860198975</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4764194488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6957015991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.860164642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9698104858398</t>
+    <t xml:space="preserve">31.4764213562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6957035064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8601665496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9698085784912</t>
   </si>
   <si>
     <t xml:space="preserve">31.9789447784424</t>
@@ -4925,7 +4925,7 @@
     <t xml:space="preserve">31.9241237640381</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6550712585449</t>
+    <t xml:space="preserve">32.6550750732422</t>
   </si>
   <si>
     <t xml:space="preserve">32.3626899719238</t>
@@ -4937,10 +4937,10 @@
     <t xml:space="preserve">32.9748611450195</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0205421447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2672386169434</t>
+    <t xml:space="preserve">33.0205459594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2672424316406</t>
   </si>
   <si>
     <t xml:space="preserve">33.3677444458008</t>
@@ -4955,43 +4955,43 @@
     <t xml:space="preserve">33.797176361084</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7514953613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6418495178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9474487304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2946472167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3311996459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2398338317871</t>
+    <t xml:space="preserve">33.7514915466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6418533325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.947452545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2946510314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3311958312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2398300170898</t>
   </si>
   <si>
     <t xml:space="preserve">33.404296875</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0936393737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6368026733398</t>
+    <t xml:space="preserve">33.0936431884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6367988586426</t>
   </si>
   <si>
     <t xml:space="preserve">32.4175148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3809661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.613468170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8144817352295</t>
+    <t xml:space="preserve">32.3809623718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6134700775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8144836425781</t>
   </si>
   <si>
     <t xml:space="preserve">32.581974029541</t>
@@ -5000,7 +5000,7 @@
     <t xml:space="preserve">32.5454292297363</t>
   </si>
   <si>
-    <t xml:space="preserve">33.130184173584</t>
+    <t xml:space="preserve">33.1301879882812</t>
   </si>
   <si>
     <t xml:space="preserve">33.075366973877</t>
@@ -5012,7 +5012,7 @@
     <t xml:space="preserve">33.1850090026855</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4408378601074</t>
+    <t xml:space="preserve">33.4408416748047</t>
   </si>
   <si>
     <t xml:space="preserve">33.7697639465332</t>
@@ -5024,7 +5024,7 @@
     <t xml:space="preserve">34.4093437194824</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8844566345215</t>
+    <t xml:space="preserve">34.884464263916</t>
   </si>
   <si>
     <t xml:space="preserve">35.4692192077637</t>
@@ -5033,34 +5033,34 @@
     <t xml:space="preserve">36.5108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0773010253906</t>
+    <t xml:space="preserve">37.0773048400879</t>
   </si>
   <si>
     <t xml:space="preserve">37.0955772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9128456115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0590286254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7849197387695</t>
+    <t xml:space="preserve">36.912841796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0590324401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7849273681641</t>
   </si>
   <si>
     <t xml:space="preserve">37.0985145568848</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9844818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1555252075195</t>
+    <t xml:space="preserve">36.9844779968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1555290222168</t>
   </si>
   <si>
     <t xml:space="preserve">37.1365280151367</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3265762329102</t>
+    <t xml:space="preserve">37.3265800476074</t>
   </si>
   <si>
     <t xml:space="preserve">37.0224914550781</t>
@@ -5084,7 +5084,7 @@
     <t xml:space="preserve">36.4523315429688</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8704490661621</t>
+    <t xml:space="preserve">36.8704452514648</t>
   </si>
   <si>
     <t xml:space="preserve">36.9084625244141</t>
@@ -5093,10 +5093,10 @@
     <t xml:space="preserve">36.5853691101074</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5473556518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0912284851074</t>
+    <t xml:space="preserve">36.5473594665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0912246704102</t>
   </si>
   <si>
     <t xml:space="preserve">36.5663642883301</t>
@@ -5105,7 +5105,7 @@
     <t xml:space="preserve">35.7301254272461</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0839424133301</t>
+    <t xml:space="preserve">35.0839385986328</t>
   </si>
   <si>
     <t xml:space="preserve">35.1219520568848</t>
@@ -5120,7 +5120,7 @@
     <t xml:space="preserve">35.7491302490234</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3572998046875</t>
+    <t xml:space="preserve">36.3573036193848</t>
   </si>
   <si>
     <t xml:space="preserve">36.0722198486328</t>
@@ -5129,13 +5129,13 @@
     <t xml:space="preserve">35.8821678161621</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7871398925781</t>
+    <t xml:space="preserve">35.7871437072754</t>
   </si>
   <si>
     <t xml:space="preserve">35.5970878601074</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9201774597168</t>
+    <t xml:space="preserve">35.9201812744141</t>
   </si>
   <si>
     <t xml:space="preserve">35.9391860961914</t>
@@ -5147,13 +5147,13 @@
     <t xml:space="preserve">35.8631629943848</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9011764526367</t>
+    <t xml:space="preserve">35.9011726379395</t>
   </si>
   <si>
     <t xml:space="preserve">36.3763084411621</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8514442443848</t>
+    <t xml:space="preserve">36.8514404296875</t>
   </si>
   <si>
     <t xml:space="preserve">37.2885704040527</t>
@@ -5177,7 +5177,7 @@
     <t xml:space="preserve">38.3718757629395</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4478950500488</t>
+    <t xml:space="preserve">38.4478988647461</t>
   </si>
   <si>
     <t xml:space="preserve">38.5429229736328</t>
@@ -5189,7 +5189,7 @@
     <t xml:space="preserve">37.7446975708008</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6423873901367</t>
+    <t xml:space="preserve">36.6423835754395</t>
   </si>
   <si>
     <t xml:space="preserve">35.4450454711914</t>
@@ -5201,7 +5201,7 @@
     <t xml:space="preserve">35.8061485290527</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6921195983887</t>
+    <t xml:space="preserve">35.6921157836914</t>
   </si>
   <si>
     <t xml:space="preserve">36.1862564086914</t>
@@ -5210,7 +5210,7 @@
     <t xml:space="preserve">36.4903450012207</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8894538879395</t>
+    <t xml:space="preserve">36.8894577026367</t>
   </si>
   <si>
     <t xml:space="preserve">37.8017120361328</t>
@@ -5222,16 +5222,16 @@
     <t xml:space="preserve">37.7827072143555</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6876792907715</t>
+    <t xml:space="preserve">37.6876831054688</t>
   </si>
   <si>
     <t xml:space="preserve">37.9727592468262</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9917678833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3338623046875</t>
+    <t xml:space="preserve">37.9917640686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3338661193848</t>
   </si>
   <si>
     <t xml:space="preserve">38.4098815917969</t>
@@ -5246,7 +5246,7 @@
     <t xml:space="preserve">37.7066879272461</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2198333740234</t>
+    <t xml:space="preserve">38.2198295593262</t>
   </si>
   <si>
     <t xml:space="preserve">38.0107727050781</t>
@@ -5255,10 +5255,10 @@
     <t xml:space="preserve">38.2768478393555</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2578392028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.238842010498</t>
+    <t xml:space="preserve">38.2578430175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2388381958008</t>
   </si>
   <si>
     <t xml:space="preserve">38.5809326171875</t>
@@ -5276,7 +5276,7 @@
     <t xml:space="preserve">39.0940780639648</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5999412536621</t>
+    <t xml:space="preserve">38.5999374389648</t>
   </si>
   <si>
     <t xml:space="preserve">37.7256927490234</t>
@@ -5297,7 +5297,7 @@
     <t xml:space="preserve">39.4741897583008</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8162841796875</t>
+    <t xml:space="preserve">39.8162879943848</t>
   </si>
   <si>
     <t xml:space="preserve">39.9493217468262</t>
@@ -5315,7 +5315,7 @@
     <t xml:space="preserve">39.6452369689941</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3981666564941</t>
+    <t xml:space="preserve">39.3981628417969</t>
   </si>
   <si>
     <t xml:space="preserve">39.3601531982422</t>
@@ -5342,10 +5342,10 @@
     <t xml:space="preserve">38.5619316101074</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9873352050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8923072814941</t>
+    <t xml:space="preserve">39.9873313903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8923034667969</t>
   </si>
   <si>
     <t xml:space="preserve">40.1773834228516</t>
@@ -5372,10 +5372,10 @@
     <t xml:space="preserve">40.9946174621582</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3557205200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5267715454102</t>
+    <t xml:space="preserve">41.3557243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5267677307129</t>
   </si>
   <si>
     <t xml:space="preserve">41.3747291564941</t>
@@ -5387,13 +5387,13 @@
     <t xml:space="preserve">41.6978187561035</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1349411010742</t>
+    <t xml:space="preserve">42.1349449157715</t>
   </si>
   <si>
     <t xml:space="preserve">42.0209121704102</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7548294067383</t>
+    <t xml:space="preserve">41.7548332214355</t>
   </si>
   <si>
     <t xml:space="preserve">42.3820114135742</t>
@@ -5402,7 +5402,7 @@
     <t xml:space="preserve">42.4390258789062</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4580345153809</t>
+    <t xml:space="preserve">42.4580307006836</t>
   </si>
   <si>
     <t xml:space="preserve">42.2869834899902</t>
@@ -5420,7 +5420,7 @@
     <t xml:space="preserve">43.5223350524902</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8761520385742</t>
+    <t xml:space="preserve">42.876148223877</t>
   </si>
   <si>
     <t xml:space="preserve">42.9521751403809</t>
@@ -5432,7 +5432,7 @@
     <t xml:space="preserve">43.0852088928223</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3059921264648</t>
+    <t xml:space="preserve">42.3059883117676</t>
   </si>
   <si>
     <t xml:space="preserve">42.7431144714355</t>
@@ -5453,13 +5453,13 @@
     <t xml:space="preserve">42.9901847839355</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8951568603516</t>
+    <t xml:space="preserve">42.8951530456543</t>
   </si>
   <si>
     <t xml:space="preserve">43.7123908996582</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4653205871582</t>
+    <t xml:space="preserve">43.4653167724609</t>
   </si>
   <si>
     <t xml:space="preserve">44.0354804992676</t>
@@ -5477,19 +5477,19 @@
     <t xml:space="preserve">46.6202163696289</t>
   </si>
   <si>
-    <t xml:space="preserve">46.639217376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6962356567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.582202911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7722587585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2781143188477</t>
+    <t xml:space="preserve">46.6392211914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.696231842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5821990966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7722549438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2781181335449</t>
   </si>
   <si>
     <t xml:space="preserve">46.1070671081543</t>
@@ -5498,7 +5498,7 @@
     <t xml:space="preserve">45.8219871520996</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0310440063477</t>
+    <t xml:space="preserve">46.0310478210449</t>
   </si>
   <si>
     <t xml:space="preserve">45.7839736938477</t>
@@ -5540,7 +5540,7 @@
     <t xml:space="preserve">48.9388694763184</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8438415527344</t>
+    <t xml:space="preserve">48.8438453674316</t>
   </si>
   <si>
     <t xml:space="preserve">48.7963256835938</t>
@@ -70995,7 +70995,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6503703704</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>120356</v>
@@ -71004,7 +71004,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="D2490" t="n">
-        <v>48.0999984741211</v>
+        <v>48</v>
       </c>
       <c r="E2490" t="n">
         <v>48.7799987792969</v>
@@ -71016,6 +71016,32 @@
         <v>1976</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6513425926</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>162777</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>48.1399993896484</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>46.6800003051758</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>47.9799995422363</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>47.1800003051758</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>1918</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BGN.MI.xlsx
+++ b/data/BGN.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4795989990234</t>
+    <t xml:space="preserve">17.4796009063721</t>
   </si>
   <si>
     <t xml:space="preserve">BGN.MI</t>
@@ -47,199 +47,199 @@
     <t xml:space="preserve">17.2943058013916</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7816505432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.528413772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2628231048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.367826461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5098876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9422435760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6457672119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1269416809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6760549545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9601736068726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0707540512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0769271850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5092897415161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5401659011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4289903640747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6019315719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.194281578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4784002304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2931070327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0213394165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.823091506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7180891036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5945596694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4580755233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6804323196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5636758804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1745529174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4154396057129</t>
+    <t xml:space="preserve">16.7816524505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5284156799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.262825012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3678245544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5098838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9422416687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6457691192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1269397735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6760492324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9601745605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0707492828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0769290924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5092840194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5401678085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4289894104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6019344329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1942844390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4784021377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2931079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0213384628296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8230905532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7180910110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5945587158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4580764770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6804332733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5636730194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1745567321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4154376983643</t>
   </si>
   <si>
     <t xml:space="preserve">14.0022106170654</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8477983474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3851556777954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4098634719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1936845779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4963321685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1813297271729</t>
+    <t xml:space="preserve">13.8477993011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.385157585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4098615646362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1936836242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4963350296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1813287734985</t>
   </si>
   <si>
     <t xml:space="preserve">14.3233919143677</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3357448577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5210409164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8607473373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2436933517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5710515975952</t>
+    <t xml:space="preserve">14.3357410430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5210399627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8607501983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2436952590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5710487365723</t>
   </si>
   <si>
     <t xml:space="preserve">15.4969329833984</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4351692199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4413433074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3239908218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0157623291016</t>
+    <t xml:space="preserve">15.4351663589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4413452148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3239917755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0157642364502</t>
   </si>
   <si>
     <t xml:space="preserve">16.201057434082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2937049865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1578235626221</t>
+    <t xml:space="preserve">16.2937068939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1578216552734</t>
   </si>
   <si>
     <t xml:space="preserve">16.3431186676025</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8489961624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8922309875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6081123352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9354639053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9663496017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0095825195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8675289154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8298673629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8854541778564</t>
+    <t xml:space="preserve">15.8489952087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8922328948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6081104278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9354677200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9663515090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0095863342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8675231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8298683166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8854579925537</t>
   </si>
   <si>
     <t xml:space="preserve">14.6569223403931</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9410486221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3981084823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5339918136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8737030029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9478206634521</t>
+    <t xml:space="preserve">14.9410438537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3981094360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.533989906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.873703956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9478216171265</t>
   </si>
   <si>
     <t xml:space="preserve">16.1145877838135</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">16.0713500976562</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1084079742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2072372436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0589981079102</t>
+    <t xml:space="preserve">16.1084098815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2072353363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0590000152588</t>
   </si>
   <si>
     <t xml:space="preserve">16.2998828887939</t>
@@ -266,109 +266,109 @@
     <t xml:space="preserve">16.1701774597168</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1207637786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7316408157349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.379581451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1201667785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8916349411011</t>
+    <t xml:space="preserve">16.1207675933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7316427230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3795785903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1201639175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8916330337524</t>
   </si>
   <si>
     <t xml:space="preserve">14.706335067749</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6383943557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6075077056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2986841201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4531002044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6692790985107</t>
+    <t xml:space="preserve">14.6383953094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6075105667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2986850738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4530982971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6692781448364</t>
   </si>
   <si>
     <t xml:space="preserve">14.3419208526611</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3666276931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3913345336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3975076675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5537910461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.814263343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9640340805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.511022567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5956726074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3742761611938</t>
+    <t xml:space="preserve">14.3666248321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3913316726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3975105285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5537919998169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8142604827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9640331268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5110187530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5956745147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3742752075195</t>
   </si>
   <si>
     <t xml:space="preserve">15.3286924362183</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1138038635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0096168518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0551958084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.211483001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3547372817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3026399612427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2570610046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8533306121826</t>
+    <t xml:space="preserve">15.1138010025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0096158981323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0551977157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2114791870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3547391891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3026456832886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.257061958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8533334732056</t>
   </si>
   <si>
     <t xml:space="preserve">14.0979671478271</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2058582305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9649209976196</t>
+    <t xml:space="preserve">13.2058572769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9649219512939</t>
   </si>
   <si>
     <t xml:space="preserve">12.9453840255737</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1993436813354</t>
+    <t xml:space="preserve">13.1993446350098</t>
   </si>
   <si>
     <t xml:space="preserve">13.6616792678833</t>
@@ -377,31 +377,31 @@
     <t xml:space="preserve">13.8374967575073</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1565742492676</t>
+    <t xml:space="preserve">14.1565704345703</t>
   </si>
   <si>
     <t xml:space="preserve">14.5733261108398</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8737592697144</t>
+    <t xml:space="preserve">12.8737573623657</t>
   </si>
   <si>
     <t xml:space="preserve">11.6690797805786</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7341966629028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6560564041138</t>
+    <t xml:space="preserve">11.7341976165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6560573577881</t>
   </si>
   <si>
     <t xml:space="preserve">11.6821041107178</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6039638519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.200234413147</t>
+    <t xml:space="preserve">11.6039619445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2002334594727</t>
   </si>
   <si>
     <t xml:space="preserve">10.8160390853882</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">10.431845664978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7444105148315</t>
+    <t xml:space="preserve">10.7444095611572</t>
   </si>
   <si>
     <t xml:space="preserve">11.2588396072388</t>
@@ -422,79 +422,79 @@
     <t xml:space="preserve">12.3137454986572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2616519927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5286340713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5677042007446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6588687896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3723497390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5221214294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5416564941406</t>
+    <t xml:space="preserve">12.2616510391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5286321640015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5677032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6588697433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.372350692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.522120475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5416574478149</t>
   </si>
   <si>
     <t xml:space="preserve">12.3397922515869</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5025863647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2551383972168</t>
+    <t xml:space="preserve">12.5025854110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2551393508911</t>
   </si>
   <si>
     <t xml:space="preserve">12.4895629882812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2421131134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0337390899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8188505172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6300096511841</t>
+    <t xml:space="preserve">12.2421140670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0337381362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8188524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6300115585327</t>
   </si>
   <si>
     <t xml:space="preserve">11.4281454086304</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3825635910034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8579206466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.994668006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1835107803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2030458450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0532751083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9490852355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7928047180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5258226394653</t>
+    <t xml:space="preserve">11.3825616836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8579216003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9946689605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1835079193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2030439376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0532760620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9490880966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7928056716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.525821685791</t>
   </si>
   <si>
     <t xml:space="preserve">11.7667570114136</t>
@@ -503,10 +503,10 @@
     <t xml:space="preserve">11.4411687850952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3630266189575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5583820343018</t>
+    <t xml:space="preserve">11.3630275726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5583810806274</t>
   </si>
   <si>
     <t xml:space="preserve">11.7797803878784</t>
@@ -515,28 +515,28 @@
     <t xml:space="preserve">11.5388441085815</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472219467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6951284408569</t>
+    <t xml:space="preserve">11.7472229003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.695125579834</t>
   </si>
   <si>
     <t xml:space="preserve">11.9425745010376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1314153671265</t>
+    <t xml:space="preserve">12.1314163208008</t>
   </si>
   <si>
     <t xml:space="preserve">12.1379261016846</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4114208221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4830513000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6653804779053</t>
+    <t xml:space="preserve">12.4114198684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4830493927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6653814315796</t>
   </si>
   <si>
     <t xml:space="preserve">12.8021268844604</t>
@@ -545,49 +545,49 @@
     <t xml:space="preserve">12.3788623809814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1183938980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1249055862427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2876968383789</t>
+    <t xml:space="preserve">12.1183929443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1249046325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2876987457275</t>
   </si>
   <si>
     <t xml:space="preserve">11.8709449768066</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7016382217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8514099121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9165258407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2523279190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1937217712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1481409072876</t>
+    <t xml:space="preserve">11.701639175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8514089584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9165267944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.252326965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1937236785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.148138999939</t>
   </si>
   <si>
     <t xml:space="preserve">11.0830211639404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1220922470093</t>
+    <t xml:space="preserve">11.122091293335</t>
   </si>
   <si>
     <t xml:space="preserve">11.1741857528687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1090688705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2848873138428</t>
+    <t xml:space="preserve">11.1090669631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2848863601685</t>
   </si>
   <si>
     <t xml:space="preserve">11.1351156234741</t>
@@ -599,19 +599,19 @@
     <t xml:space="preserve">11.1872100830078</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0244159698486</t>
+    <t xml:space="preserve">11.0244150161743</t>
   </si>
   <si>
     <t xml:space="preserve">11.0179042816162</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6430330276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5779151916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9100160598755</t>
+    <t xml:space="preserve">11.6430311203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5779161453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9100170135498</t>
   </si>
   <si>
     <t xml:space="preserve">12.1769971847534</t>
@@ -623,133 +623,133 @@
     <t xml:space="preserve">12.4309568405151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9779462814331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0365505218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3816728591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5640020370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4142351150513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1732950210571</t>
+    <t xml:space="preserve">12.9779443740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0365514755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3816747665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5640048980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4142322540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1732978820801</t>
   </si>
   <si>
     <t xml:space="preserve">13.0560855865479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9258518218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8281755447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3295783996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7984275817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5444650650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8830823898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8309850692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9481964111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8895902633667</t>
+    <t xml:space="preserve">12.9258499145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8281745910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3295793533325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7984285354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5444679260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.88307762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8309831619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9482002258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8895931243896</t>
   </si>
   <si>
     <t xml:space="preserve">14.1240139007568</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4923734664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9388742446899</t>
+    <t xml:space="preserve">13.4923715591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9388751983643</t>
   </si>
   <si>
     <t xml:space="preserve">12.9323635101318</t>
   </si>
   <si>
-    <t xml:space="preserve">12.867241859436</t>
+    <t xml:space="preserve">12.8672437667847</t>
   </si>
   <si>
     <t xml:space="preserve">12.9714326858521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.990966796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7760820388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7956161499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7304992675781</t>
+    <t xml:space="preserve">12.9909696578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7760801315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7956142425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7304983139038</t>
   </si>
   <si>
     <t xml:space="preserve">12.7435216903687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4691400527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.289623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8887052536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5761375427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3612499237061</t>
+    <t xml:space="preserve">14.4691381454468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2896203994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8887004852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5761384963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3612508773804</t>
   </si>
   <si>
     <t xml:space="preserve">15.4784603118896</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0747308731079</t>
+    <t xml:space="preserve">15.0747337341309</t>
   </si>
   <si>
     <t xml:space="preserve">15.185432434082</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8989124298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8793792724609</t>
+    <t xml:space="preserve">14.8989133834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8793802261353</t>
   </si>
   <si>
     <t xml:space="preserve">14.9575223922729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9770545959473</t>
+    <t xml:space="preserve">14.9770574569702</t>
   </si>
   <si>
     <t xml:space="preserve">15.0031032562256</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7817049026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5863523483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7556571960449</t>
+    <t xml:space="preserve">14.7817029953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5863513946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7556581497192</t>
   </si>
   <si>
     <t xml:space="preserve">14.859845161438</t>
@@ -761,16 +761,16 @@
     <t xml:space="preserve">15.4459028244019</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8403081893921</t>
+    <t xml:space="preserve">14.8403120040894</t>
   </si>
   <si>
     <t xml:space="preserve">15.2700881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">15.530553817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4133462905884</t>
+    <t xml:space="preserve">15.5305547714233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4133443832397</t>
   </si>
   <si>
     <t xml:space="preserve">15.3482275009155</t>
@@ -779,34 +779,34 @@
     <t xml:space="preserve">15.5631151199341</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5138339996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6570930480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5659255981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1231250762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0514984130859</t>
+    <t xml:space="preserve">16.5138301849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6570911407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5659275054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1231269836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0514965057373</t>
   </si>
   <si>
     <t xml:space="preserve">15.6803274154663</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7454452514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.758469581604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0356616973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3352022171021</t>
+    <t xml:space="preserve">15.7454481124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7584676742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0356636047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.335205078125</t>
   </si>
   <si>
     <t xml:space="preserve">15.2375259399414</t>
@@ -815,25 +815,25 @@
     <t xml:space="preserve">15.4328804016113</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2208042144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2924308776855</t>
+    <t xml:space="preserve">16.2208023071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2924346923828</t>
   </si>
   <si>
     <t xml:space="preserve">16.1491718292236</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9538202285767</t>
+    <t xml:space="preserve">15.9538192749023</t>
   </si>
   <si>
     <t xml:space="preserve">16.175220489502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8626537322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.556604385376</t>
+    <t xml:space="preserve">15.8626575469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5566024780273</t>
   </si>
   <si>
     <t xml:space="preserve">15.1593856811523</t>
@@ -845,91 +845,91 @@
     <t xml:space="preserve">14.8468208312988</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1658973693848</t>
+    <t xml:space="preserve">15.1658983230591</t>
   </si>
   <si>
     <t xml:space="preserve">15.4003200531006</t>
   </si>
   <si>
-    <t xml:space="preserve">15.309157371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6021871566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6217222213745</t>
+    <t xml:space="preserve">15.3091564178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6021852493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6217212677002</t>
   </si>
   <si>
     <t xml:space="preserve">15.6738147735596</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5500869750977</t>
+    <t xml:space="preserve">15.5500898361206</t>
   </si>
   <si>
     <t xml:space="preserve">15.3677616119385</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3938093185425</t>
+    <t xml:space="preserve">15.3938064575195</t>
   </si>
   <si>
     <t xml:space="preserve">15.1398515701294</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1072940826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0812454223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6152076721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.628231048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5435800552368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7975397109985</t>
+    <t xml:space="preserve">15.1072912216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0812425613403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6152105331421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6282339096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5435781478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7975416183472</t>
   </si>
   <si>
     <t xml:space="preserve">15.9342851638794</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2012672424316</t>
+    <t xml:space="preserve">16.2012634277344</t>
   </si>
   <si>
     <t xml:space="preserve">16.4422016143799</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3770866394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2794075012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1426601409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4812755584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6049995422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.233829498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2561740875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2691974639893</t>
+    <t xml:space="preserve">16.377082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.279411315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1426639556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4812717437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6049976348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2338275909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2561721801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.269193649292</t>
   </si>
   <si>
     <t xml:space="preserve">17.1584968566895</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1454734802246</t>
+    <t xml:space="preserve">17.1454753875732</t>
   </si>
   <si>
     <t xml:space="preserve">17.1845436096191</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">17.6273441314697</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3892211914062</t>
+    <t xml:space="preserve">18.3892192840576</t>
   </si>
   <si>
     <t xml:space="preserve">18.1678218841553</t>
@@ -953,7 +953,7 @@
     <t xml:space="preserve">18.1027030944824</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3501491546631</t>
+    <t xml:space="preserve">18.3501510620117</t>
   </si>
   <si>
     <t xml:space="preserve">18.1352615356445</t>
@@ -962,82 +962,82 @@
     <t xml:space="preserve">18.493408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0896816253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2264232635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8588104248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8723430633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.689640045166</t>
+    <t xml:space="preserve">18.0896797180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2264251708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8588123321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8723411560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6896419525146</t>
   </si>
   <si>
     <t xml:space="preserve">18.6422748565674</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5137119293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8370399475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6543407440186</t>
+    <t xml:space="preserve">18.5137100219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8370380401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6543388366699</t>
   </si>
   <si>
     <t xml:space="preserve">17.3836708068848</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9047069549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9317722320557</t>
+    <t xml:space="preserve">17.9047031402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.931770324707</t>
   </si>
   <si>
     <t xml:space="preserve">17.5393009185791</t>
   </si>
   <si>
-    <t xml:space="preserve">17.546070098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9926719665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6761112213135</t>
+    <t xml:space="preserve">17.5460720062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9926700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6761074066162</t>
   </si>
   <si>
     <t xml:space="preserve">18.926477432251</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8046760559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9806098937988</t>
+    <t xml:space="preserve">18.8046741485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9806118011475</t>
   </si>
   <si>
     <t xml:space="preserve">18.6219749450684</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0400371551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3377742767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.20920753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9994411468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.864107131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8032054901123</t>
+    <t xml:space="preserve">18.0400409698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.337776184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2092037200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.999439239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8641052246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8032035827637</t>
   </si>
   <si>
     <t xml:space="preserve">18.0062046051025</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">18.4054412841797</t>
   </si>
   <si>
-    <t xml:space="preserve">18.060338973999</t>
+    <t xml:space="preserve">18.0603408813477</t>
   </si>
   <si>
     <t xml:space="preserve">17.6340370178223</t>
@@ -1055,10 +1055,10 @@
     <t xml:space="preserve">18.2430400848389</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2701053619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.649040222168</t>
+    <t xml:space="preserve">18.2701091766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6490421295166</t>
   </si>
   <si>
     <t xml:space="preserve">18.4528064727783</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">18.7031745910645</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4595756530762</t>
+    <t xml:space="preserve">18.4595737457275</t>
   </si>
   <si>
     <t xml:space="preserve">19.1024112701416</t>
@@ -1076,70 +1076,70 @@
     <t xml:space="preserve">18.9467792510986</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9197101593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7776126861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8791122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1362476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0415134429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1836109161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3730792999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2918796539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8264484405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9414825439453</t>
+    <t xml:space="preserve">18.9197082519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7776107788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8791084289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1362457275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0415115356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.183614730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3730773925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2918758392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8264503479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9414806365967</t>
   </si>
   <si>
     <t xml:space="preserve">20.300121307373</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5166549682617</t>
+    <t xml:space="preserve">20.5166511535645</t>
   </si>
   <si>
     <t xml:space="preserve">20.0971202850342</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9956188201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1241855621338</t>
+    <t xml:space="preserve">19.9956169128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1241874694824</t>
   </si>
   <si>
     <t xml:space="preserve">20.1444854736328</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6384525299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2392158508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.894115447998</t>
+    <t xml:space="preserve">20.6384544372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2392177581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8941173553467</t>
   </si>
   <si>
     <t xml:space="preserve">19.5625457763672</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7587833404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9211864471436</t>
+    <t xml:space="preserve">19.7587814331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9211826324463</t>
   </si>
   <si>
     <t xml:space="preserve">19.9008846282959</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">19.7993831634521</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7655487060547</t>
+    <t xml:space="preserve">19.7655467987061</t>
   </si>
   <si>
     <t xml:space="preserve">19.812915802002</t>
@@ -1157,16 +1157,16 @@
     <t xml:space="preserve">19.4813480377197</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5828495025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4881114959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2851123809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7640743255615</t>
+    <t xml:space="preserve">19.5828475952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4881134033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2851104736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7640762329102</t>
   </si>
   <si>
     <t xml:space="preserve">18.7573089599609</t>
@@ -1175,7 +1175,7 @@
     <t xml:space="preserve">18.5949096679688</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8452777862549</t>
+    <t xml:space="preserve">18.8452758789062</t>
   </si>
   <si>
     <t xml:space="preserve">18.8655757904053</t>
@@ -1193,25 +1193,25 @@
     <t xml:space="preserve">19.1700782775879</t>
   </si>
   <si>
-    <t xml:space="preserve">19.251277923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1971454620361</t>
+    <t xml:space="preserve">19.2512798309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1971473693848</t>
   </si>
   <si>
     <t xml:space="preserve">19.4475135803223</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1633110046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2648124694824</t>
+    <t xml:space="preserve">19.1633129119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2648105621338</t>
   </si>
   <si>
     <t xml:space="preserve">19.4678134918213</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2580471038818</t>
+    <t xml:space="preserve">19.2580451965332</t>
   </si>
   <si>
     <t xml:space="preserve">19.8602828979492</t>
@@ -1220,58 +1220,58 @@
     <t xml:space="preserve">19.8670520782471</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0159187316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4204502105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.569314956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.549015045166</t>
+    <t xml:space="preserve">20.0159168243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4204483032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5693111419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5490131378174</t>
   </si>
   <si>
     <t xml:space="preserve">19.4272136688232</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3663158416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4136791229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3527793884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.501651763916</t>
+    <t xml:space="preserve">19.3663139343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4136829376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3527774810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5016479492188</t>
   </si>
   <si>
     <t xml:space="preserve">18.9400081634521</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8114433288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8858757019043</t>
+    <t xml:space="preserve">18.8114414215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8858776092529</t>
   </si>
   <si>
     <t xml:space="preserve">19.2783470153809</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1565456390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0685768127441</t>
+    <t xml:space="preserve">19.1565437316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0685787200928</t>
   </si>
   <si>
     <t xml:space="preserve">19.2106781005859</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1091785430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3189468383789</t>
+    <t xml:space="preserve">19.1091747283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3189449310303</t>
   </si>
   <si>
     <t xml:space="preserve">19.3324794769287</t>
@@ -1283,55 +1283,55 @@
     <t xml:space="preserve">19.6572818756104</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1106491088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9820823669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7858505249023</t>
+    <t xml:space="preserve">20.1106510162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.982084274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7858486175537</t>
   </si>
   <si>
     <t xml:space="preserve">19.5354804992676</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9482517242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5760822296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6166820526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5557842254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3460102081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6911163330078</t>
+    <t xml:space="preserve">19.9482479095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5760803222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6166801452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5557804107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3460121154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6911182403564</t>
   </si>
   <si>
     <t xml:space="preserve">19.6775817871094</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2986450195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1903800964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.312183380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7911434173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8182106018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9670791625977</t>
+    <t xml:space="preserve">19.2986488342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1903781890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3121795654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.791145324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8182125091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.967077255249</t>
   </si>
   <si>
     <t xml:space="preserve">18.7708435058594</t>
@@ -1340,49 +1340,49 @@
     <t xml:space="preserve">18.4663410186768</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1889057159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6084423065186</t>
+    <t xml:space="preserve">18.1889038085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6084442138672</t>
   </si>
   <si>
     <t xml:space="preserve">19.1497764587402</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1768474578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4745807647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0294532775879</t>
+    <t xml:space="preserve">19.1768455505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4745826721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.029447555542</t>
   </si>
   <si>
     <t xml:space="preserve">20.0835857391357</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5301856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5031185150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.800853729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7602558135986</t>
+    <t xml:space="preserve">20.5301876068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5031204223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8008556365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.76025390625</t>
   </si>
   <si>
     <t xml:space="preserve">20.7196559906006</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8685207366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7061195373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2459850311279</t>
+    <t xml:space="preserve">20.868522644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7061214447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2459869384766</t>
   </si>
   <si>
     <t xml:space="preserve">20.4083862304688</t>
@@ -1391,19 +1391,19 @@
     <t xml:space="preserve">20.3136520385742</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8805866241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8926448822021</t>
+    <t xml:space="preserve">19.8805828094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8926429748535</t>
   </si>
   <si>
     <t xml:space="preserve">19.0550441741943</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0265026092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2024421691895</t>
+    <t xml:space="preserve">18.0265064239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2024402618408</t>
   </si>
   <si>
     <t xml:space="preserve">18.2565727233887</t>
@@ -1430,7 +1430,7 @@
     <t xml:space="preserve">17.9859027862549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4460391998291</t>
+    <t xml:space="preserve">18.4460411071777</t>
   </si>
   <si>
     <t xml:space="preserve">18.662576675415</t>
@@ -1442,43 +1442,43 @@
     <t xml:space="preserve">18.7437763214111</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7302436828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3783740997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8505706787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.755838394165</t>
+    <t xml:space="preserve">18.73024559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3783760070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8505725860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7558345794678</t>
   </si>
   <si>
     <t xml:space="preserve">17.7287712097168</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9723720550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0671043395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.148307800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2159729003906</t>
+    <t xml:space="preserve">17.9723701477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0671081542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1483039855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.215970993042</t>
   </si>
   <si>
     <t xml:space="preserve">18.324239730835</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3513088226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.364839553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7167091369629</t>
+    <t xml:space="preserve">18.3513069152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3648414611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7167110443115</t>
   </si>
   <si>
     <t xml:space="preserve">18.7979125976562</t>
@@ -1487,16 +1487,16 @@
     <t xml:space="preserve">18.906177520752</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1618404388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1212387084961</t>
+    <t xml:space="preserve">18.1618423461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1212368011475</t>
   </si>
   <si>
     <t xml:space="preserve">17.8235034942627</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6205043792725</t>
+    <t xml:space="preserve">17.6205024719238</t>
   </si>
   <si>
     <t xml:space="preserve">17.6611022949219</t>
@@ -1505,175 +1505,175 @@
     <t xml:space="preserve">17.173900604248</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0520992279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7814292907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7600517272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8028087615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5605278015137</t>
+    <t xml:space="preserve">17.052095413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7814311981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7600536346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8028106689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5605316162109</t>
   </si>
   <si>
     <t xml:space="preserve">16.7030467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3039951324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2066144943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2802515029907</t>
+    <t xml:space="preserve">16.3039970397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2066116333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2802505493164</t>
   </si>
   <si>
     <t xml:space="preserve">14.8503189086914</t>
   </si>
   <si>
-    <t xml:space="preserve">14.821816444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5344018936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3206310272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8930759429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4631443023682</t>
+    <t xml:space="preserve">14.8218154907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.53440284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3206272125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8930740356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4631490707397</t>
   </si>
   <si>
     <t xml:space="preserve">15.8336906433105</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3491306304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9477024078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8479404449463</t>
+    <t xml:space="preserve">15.3491315841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9477033615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8479433059692</t>
   </si>
   <si>
     <t xml:space="preserve">15.8621940612793</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9192008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7054271697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7339286804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7196779251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3633804321289</t>
+    <t xml:space="preserve">15.9192018508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7054233551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7339267730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7196760177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3633842468262</t>
   </si>
   <si>
     <t xml:space="preserve">15.5059013366699</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4203872680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4488925933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.950080871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9358291625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1781091690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5629072189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6484174728394</t>
+    <t xml:space="preserve">15.4203882217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4488935470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9500827789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.935830116272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1781101226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5629081726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6484155654907</t>
   </si>
   <si>
     <t xml:space="preserve">15.890697479248</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0189647674561</t>
+    <t xml:space="preserve">16.0189628601074</t>
   </si>
   <si>
     <t xml:space="preserve">15.4346408843994</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3776340484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4916477203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.52015209198</t>
+    <t xml:space="preserve">15.3776350021362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4916458129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5201539993286</t>
   </si>
   <si>
     <t xml:space="preserve">15.7909355163574</t>
   </si>
   <si>
-    <t xml:space="preserve">15.776683807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6056642532349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4750194549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2469902038574</t>
+    <t xml:space="preserve">15.7766828536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6056632995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4750175476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2469921112061</t>
   </si>
   <si>
     <t xml:space="preserve">16.1329765319824</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4465160369873</t>
+    <t xml:space="preserve">16.4465179443359</t>
   </si>
   <si>
     <t xml:space="preserve">16.5035228729248</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9619569778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0474643707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.21848487854</t>
+    <t xml:space="preserve">15.9619579315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0474681854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2184886932373</t>
   </si>
   <si>
     <t xml:space="preserve">16.2042350769043</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1614780426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7481775283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9049510955811</t>
+    <t xml:space="preserve">16.1614818572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.74817943573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9049491882324</t>
   </si>
   <si>
     <t xml:space="preserve">16.2754955291748</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4037609100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3325023651123</t>
+    <t xml:space="preserve">16.4037590026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3325004577637</t>
   </si>
   <si>
     <t xml:space="preserve">15.2636213302612</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">15.0783491134644</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3063774108887</t>
+    <t xml:space="preserve">15.3063745498657</t>
   </si>
   <si>
     <t xml:space="preserve">15.2921237945557</t>
@@ -1691,61 +1691,61 @@
     <t xml:space="preserve">15.5486555099487</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6769189834595</t>
+    <t xml:space="preserve">15.6769247055054</t>
   </si>
   <si>
     <t xml:space="preserve">16.6175365447998</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7885589599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8598155975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3443775177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3871326446533</t>
+    <t xml:space="preserve">16.7885570526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8598136901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3443737030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.387134552002</t>
   </si>
   <si>
     <t xml:space="preserve">17.1020946502686</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8764476776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6911725997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6626691818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9643325805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7933149337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3515071868896</t>
+    <t xml:space="preserve">15.8764448165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6911735534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6626682281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9643354415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7933139801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3515090942383</t>
   </si>
   <si>
     <t xml:space="preserve">14.2161159515381</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3372573852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7220554351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4227676391602</t>
+    <t xml:space="preserve">14.3372554779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7220544815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4227666854858</t>
   </si>
   <si>
     <t xml:space="preserve">14.0593481063843</t>
   </si>
   <si>
-    <t xml:space="preserve">13.539158821106</t>
+    <t xml:space="preserve">13.5391616821289</t>
   </si>
   <si>
     <t xml:space="preserve">13.2042446136475</t>
@@ -1754,28 +1754,28 @@
     <t xml:space="preserve">12.7268104553223</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3776435852051</t>
+    <t xml:space="preserve">12.3776426315308</t>
   </si>
   <si>
     <t xml:space="preserve">12.4203968048096</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2850065231323</t>
+    <t xml:space="preserve">12.285005569458</t>
   </si>
   <si>
     <t xml:space="preserve">12.4061450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1353626251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3705177307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9049587249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8621997833252</t>
+    <t xml:space="preserve">12.1353616714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3705158233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.904956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8622007369995</t>
   </si>
   <si>
     <t xml:space="preserve">12.9334602355957</t>
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">13.1472358703613</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2755012512207</t>
+    <t xml:space="preserve">13.275502204895</t>
   </si>
   <si>
     <t xml:space="preserve">13.1187334060669</t>
@@ -1793,109 +1793,109 @@
     <t xml:space="preserve">13.0688514709473</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5462856292725</t>
+    <t xml:space="preserve">13.5462837219238</t>
   </si>
   <si>
     <t xml:space="preserve">13.1116065979004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7838182449341</t>
+    <t xml:space="preserve">12.7838153839111</t>
   </si>
   <si>
     <t xml:space="preserve">12.7339363098145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6698017120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9192085266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9548368453979</t>
+    <t xml:space="preserve">12.6698026657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.919207572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9548397064209</t>
   </si>
   <si>
     <t xml:space="preserve">13.2469997406006</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5961656570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1092300415039</t>
+    <t xml:space="preserve">13.5961675643921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1092281341553</t>
   </si>
   <si>
     <t xml:space="preserve">13.945333480835</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8812036514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8883275985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4655227661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.223240852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0878505706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3681402206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4679002761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1258583068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.969090461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4892778396606</t>
+    <t xml:space="preserve">13.881199836731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8883256912231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4655237197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2232427597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0878524780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3681392669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4679021835327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1258592605591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9690895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.489278793335</t>
   </si>
   <si>
     <t xml:space="preserve">13.6317949295044</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2327470779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3966407775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8265714645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5344133377075</t>
+    <t xml:space="preserve">13.2327461242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3966436386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8265724182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5344123840332</t>
   </si>
   <si>
     <t xml:space="preserve">13.1044816970825</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9975938796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6104192733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7529325485229</t>
+    <t xml:space="preserve">12.9975910186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6104183197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7529373168945</t>
   </si>
   <si>
     <t xml:space="preserve">13.6389217376709</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1448593139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3230056762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2018661499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947412490845</t>
+    <t xml:space="preserve">14.1448574066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3230047225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2018632888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947393417358</t>
   </si>
   <si>
     <t xml:space="preserve">13.8954524993896</t>
@@ -1904,34 +1904,34 @@
     <t xml:space="preserve">14.3942651748657</t>
   </si>
   <si>
-    <t xml:space="preserve">14.593789100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7078018188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5082788467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6935539245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8075656890869</t>
+    <t xml:space="preserve">14.5937900543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.707802772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5082778930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6935520172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8075647354126</t>
   </si>
   <si>
     <t xml:space="preserve">14.6365451812744</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7648105621338</t>
+    <t xml:space="preserve">14.7648086547852</t>
   </si>
   <si>
     <t xml:space="preserve">14.736307144165</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6792974472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2659969329834</t>
+    <t xml:space="preserve">14.6793012619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.265998840332</t>
   </si>
   <si>
     <t xml:space="preserve">14.5367813110352</t>
@@ -1940,91 +1940,91 @@
     <t xml:space="preserve">14.2945003509521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5510330200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1923627853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9785861968994</t>
+    <t xml:space="preserve">14.5510320663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.192361831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9785871505737</t>
   </si>
   <si>
     <t xml:space="preserve">15.2778730392456</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2493715286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2208681106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4061393737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8194389343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8051891326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6341676712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5914106369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4322624206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6032829284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7173004150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7743072509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8170623779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0308361053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1591033935547</t>
+    <t xml:space="preserve">15.2493686676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2208662033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.406138420105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8194417953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8051872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6341648101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5914115905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4322605133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6032848358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7172985076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7743053436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8170604705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0308380126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1591053009033</t>
   </si>
   <si>
     <t xml:space="preserve">17.2588653564453</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3158683776855</t>
+    <t xml:space="preserve">17.3158702850342</t>
   </si>
   <si>
     <t xml:space="preserve">17.4583911895752</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4726409912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9714508056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7861804962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9286975860596</t>
+    <t xml:space="preserve">17.4726428985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9714527130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7861785888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9286994934082</t>
   </si>
   <si>
     <t xml:space="preserve">18.0569629669189</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0854663848877</t>
+    <t xml:space="preserve">18.0854644775391</t>
   </si>
   <si>
     <t xml:space="preserve">17.5581493377686</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5866565704346</t>
+    <t xml:space="preserve">17.5866546630859</t>
   </si>
   <si>
     <t xml:space="preserve">17.2018566131592</t>
@@ -2039,19 +2039,19 @@
     <t xml:space="preserve">17.4868927001953</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7196521759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8548030853271</t>
+    <t xml:space="preserve">17.719654083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8548011779785</t>
   </si>
   <si>
     <t xml:space="preserve">17.299186706543</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2241039276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2691497802734</t>
+    <t xml:space="preserve">17.2241020202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2691516876221</t>
   </si>
   <si>
     <t xml:space="preserve">17.149019241333</t>
@@ -2060,10 +2060,10 @@
     <t xml:space="preserve">16.7435684204102</t>
   </si>
   <si>
-    <t xml:space="preserve">16.878719329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.923770904541</t>
+    <t xml:space="preserve">16.8787174224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9237689971924</t>
   </si>
   <si>
     <t xml:space="preserve">16.6985168457031</t>
@@ -2072,37 +2072,37 @@
     <t xml:space="preserve">17.2541332244873</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5394535064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1640319824219</t>
+    <t xml:space="preserve">17.5394515991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1640338897705</t>
   </si>
   <si>
     <t xml:space="preserve">17.0589160919189</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4343338012695</t>
+    <t xml:space="preserve">17.4343357086182</t>
   </si>
   <si>
     <t xml:space="preserve">17.8247661590576</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9298820495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8397827148438</t>
+    <t xml:space="preserve">17.9298839569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8397846221924</t>
   </si>
   <si>
     <t xml:space="preserve">17.7496852874756</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9449005126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.665699005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8458995819092</t>
+    <t xml:space="preserve">17.9448986053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6656970977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8459014892578</t>
   </si>
   <si>
     <t xml:space="preserve">19.1762676239014</t>
@@ -2114,7 +2114,7 @@
     <t xml:space="preserve">19.0561332702637</t>
   </si>
   <si>
-    <t xml:space="preserve">19.131217956543</t>
+    <t xml:space="preserve">19.1312160491943</t>
   </si>
   <si>
     <t xml:space="preserve">19.4165325164795</t>
@@ -2123,49 +2123,49 @@
     <t xml:space="preserve">19.1462345123291</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0110816955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2213172912598</t>
+    <t xml:space="preserve">19.0110836029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2213153839111</t>
   </si>
   <si>
     <t xml:space="preserve">19.7318840026855</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7769317626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7919521331787</t>
+    <t xml:space="preserve">19.7769336700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7919483184814</t>
   </si>
   <si>
     <t xml:space="preserve">19.8069667816162</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0772666931152</t>
+    <t xml:space="preserve">20.0772647857666</t>
   </si>
   <si>
     <t xml:space="preserve">19.9721508026123</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2574672698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1373348236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1823806762695</t>
+    <t xml:space="preserve">20.2574653625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1373310089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1823825836182</t>
   </si>
   <si>
     <t xml:space="preserve">19.8970680236816</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0472354888916</t>
+    <t xml:space="preserve">20.047233581543</t>
   </si>
   <si>
     <t xml:space="preserve">20.1523494720459</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0172004699707</t>
+    <t xml:space="preserve">20.0171985626221</t>
   </si>
   <si>
     <t xml:space="preserve">19.6567974090576</t>
@@ -2174,19 +2174,19 @@
     <t xml:space="preserve">19.821985244751</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6868343353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8369979858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9421138763428</t>
+    <t xml:space="preserve">19.6868324279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8370018005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9421157836914</t>
   </si>
   <si>
     <t xml:space="preserve">20.3325481414795</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5817127227783</t>
+    <t xml:space="preserve">19.581714630127</t>
   </si>
   <si>
     <t xml:space="preserve">19.4916152954102</t>
@@ -2198,13 +2198,13 @@
     <t xml:space="preserve">19.7168655395508</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7619132995605</t>
+    <t xml:space="preserve">19.7619171142578</t>
   </si>
   <si>
     <t xml:space="preserve">20.2874984741211</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9120826721191</t>
+    <t xml:space="preserve">19.9120864868164</t>
   </si>
   <si>
     <t xml:space="preserve">20.1223163604736</t>
@@ -2213,58 +2213,58 @@
     <t xml:space="preserve">20.0622482299805</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3025131225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5728149414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.662914276123</t>
+    <t xml:space="preserve">20.3025150299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5728168487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6629180908203</t>
   </si>
   <si>
     <t xml:space="preserve">20.9932804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1434497833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1584644317627</t>
+    <t xml:space="preserve">21.1434459686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1584663391113</t>
   </si>
   <si>
     <t xml:space="preserve">21.3536834716797</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0082969665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.263578414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2936134338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4287662506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6089668273926</t>
+    <t xml:space="preserve">21.0082988739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2635803222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2936153411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4287643432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6089649200439</t>
   </si>
   <si>
     <t xml:space="preserve">21.5338821411133</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9782657623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8881683349609</t>
+    <t xml:space="preserve">20.9782638549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8881664276123</t>
   </si>
   <si>
     <t xml:space="preserve">21.233549118042</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2485637664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1734809875488</t>
+    <t xml:space="preserve">21.2485656738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1734828948975</t>
   </si>
   <si>
     <t xml:space="preserve">20.6478996276855</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">20.7680320739746</t>
   </si>
   <si>
-    <t xml:space="preserve">21.083381652832</t>
+    <t xml:space="preserve">21.0833797454834</t>
   </si>
   <si>
     <t xml:space="preserve">20.7980670928955</t>
@@ -2285,10 +2285,10 @@
     <t xml:space="preserve">19.8670310974121</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7229804992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2035160064697</t>
+    <t xml:space="preserve">20.7229824066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2035121917725</t>
   </si>
   <si>
     <t xml:space="preserve">21.3086318969727</t>
@@ -2297,7 +2297,7 @@
     <t xml:space="preserve">21.4888324737549</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5639152526855</t>
+    <t xml:space="preserve">21.5639133453369</t>
   </si>
   <si>
     <t xml:space="preserve">21.1134147644043</t>
@@ -2306,76 +2306,76 @@
     <t xml:space="preserve">21.3837146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3236522674561</t>
+    <t xml:space="preserve">21.3236484527588</t>
   </si>
   <si>
     <t xml:space="preserve">21.5789318084717</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8191967010498</t>
+    <t xml:space="preserve">21.8191947937012</t>
   </si>
   <si>
     <t xml:space="preserve">21.8492298126221</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9543495178223</t>
+    <t xml:space="preserve">21.954345703125</t>
   </si>
   <si>
     <t xml:space="preserve">22.5850448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4799327850342</t>
+    <t xml:space="preserve">22.4799308776855</t>
   </si>
   <si>
     <t xml:space="preserve">22.6601314544678</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1256446838379</t>
+    <t xml:space="preserve">23.1256465911865</t>
   </si>
   <si>
     <t xml:space="preserve">23.3208618164062</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0805988311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2007312774658</t>
+    <t xml:space="preserve">23.0805969238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2007293701172</t>
   </si>
   <si>
     <t xml:space="preserve">23.3058471679688</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4259777069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6962776184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9215316772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7263145446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6662445068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9065132141113</t>
+    <t xml:space="preserve">23.4259796142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6962795257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9215278625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7263126373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6662483215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9065113067627</t>
   </si>
   <si>
     <t xml:space="preserve">23.2908306121826</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3959445953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2758159637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0956134796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4949493408203</t>
+    <t xml:space="preserve">23.3959465026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2758140563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0956153869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.494945526123</t>
   </si>
   <si>
     <t xml:space="preserve">22.6300945281982</t>
@@ -2396,22 +2396,22 @@
     <t xml:space="preserve">22.6000633239746</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6451148986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7352161407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2096328735352</t>
+    <t xml:space="preserve">22.6451110839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7352123260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2096309661865</t>
   </si>
   <si>
     <t xml:space="preserve">22.1946125030518</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1045169830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1795978546143</t>
+    <t xml:space="preserve">22.104513168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1795959472656</t>
   </si>
   <si>
     <t xml:space="preserve">21.7290992736816</t>
@@ -2420,7 +2420,7 @@
     <t xml:space="preserve">22.0594635009766</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7441158294678</t>
+    <t xml:space="preserve">21.7441139221191</t>
   </si>
   <si>
     <t xml:space="preserve">21.5939483642578</t>
@@ -2432,28 +2432,28 @@
     <t xml:space="preserve">22.0294303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7652454376221</t>
+    <t xml:space="preserve">22.7652492523193</t>
   </si>
   <si>
     <t xml:space="preserve">22.7051792144775</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9904975891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9754772186279</t>
+    <t xml:space="preserve">22.99049949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9754810333252</t>
   </si>
   <si>
     <t xml:space="preserve">22.8102970123291</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8253154754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.07448387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8853797912598</t>
+    <t xml:space="preserve">22.8253135681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0744819641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8853816986084</t>
   </si>
   <si>
     <t xml:space="preserve">22.1645812988281</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">22.299732208252</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8553485870361</t>
+    <t xml:space="preserve">22.8553447723389</t>
   </si>
   <si>
     <t xml:space="preserve">22.795280456543</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">24.1017265319824</t>
   </si>
   <si>
-    <t xml:space="preserve">24.447114944458</t>
+    <t xml:space="preserve">24.4471111297607</t>
   </si>
   <si>
     <t xml:space="preserve">24.4170799255371</t>
@@ -2483,25 +2483,25 @@
     <t xml:space="preserve">24.67236328125</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6573448181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7774810791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3269786834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8764762878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2396659851074</t>
+    <t xml:space="preserve">24.6573467254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7774791717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3269805908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8764801025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2396640777588</t>
   </si>
   <si>
     <t xml:space="preserve">20.9181976318359</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4226493835449</t>
+    <t xml:space="preserve">20.4226474761963</t>
   </si>
   <si>
     <t xml:space="preserve">20.4827156066895</t>
@@ -2513,58 +2513,58 @@
     <t xml:space="preserve">18.5906162261963</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9688205718994</t>
+    <t xml:space="preserve">16.9688186645508</t>
   </si>
   <si>
     <t xml:space="preserve">15.8876209259033</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7975234985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6201028823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6937952041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.214653968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9894027709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6590404510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0344572067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7266130447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8917989730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9054222106934</t>
+    <t xml:space="preserve">15.7975177764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6201057434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6937942504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2146549224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.989405632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6590375900269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0344562530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7266149520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8917961120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.905421257019</t>
   </si>
   <si>
     <t xml:space="preserve">14.0180463790894</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5811700820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0781135559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3559226989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1982440948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3183794021606</t>
+    <t xml:space="preserve">14.5811710357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0781126022339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3559217453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1982460021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3183813095093</t>
   </si>
   <si>
     <t xml:space="preserve">14.0555849075317</t>
@@ -2573,52 +2573,52 @@
     <t xml:space="preserve">14.7688798904419</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4671516418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7886219024658</t>
+    <t xml:space="preserve">15.4671535491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7886199951172</t>
   </si>
   <si>
     <t xml:space="preserve">15.7074184417725</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9026374816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9326686859131</t>
+    <t xml:space="preserve">15.9026355743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9326705932617</t>
   </si>
   <si>
     <t xml:space="preserve">15.767484664917</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1518049240112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3770532608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4821729660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6835021972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8937377929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3442344665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0138683319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5333347320557</t>
+    <t xml:space="preserve">15.1518058776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3770542144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4821710586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6834983825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8937358856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3442363739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0138702392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.533332824707</t>
   </si>
   <si>
     <t xml:space="preserve">16.5033016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">16.908748626709</t>
+    <t xml:space="preserve">16.9087524414062</t>
   </si>
   <si>
     <t xml:space="preserve">17.4643688201904</t>
@@ -2630,49 +2630,49 @@
     <t xml:space="preserve">17.5244331359863</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1189842224121</t>
+    <t xml:space="preserve">17.1189861297607</t>
   </si>
   <si>
     <t xml:space="preserve">17.2391166687012</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1340026855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3892841339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4043045043945</t>
+    <t xml:space="preserve">17.1339988708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3892860412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4043006896973</t>
   </si>
   <si>
     <t xml:space="preserve">17.6896190643311</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3653659820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2902870178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4855041503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9510173797607</t>
+    <t xml:space="preserve">18.3653678894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2902851104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.485502243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9510135650635</t>
   </si>
   <si>
     <t xml:space="preserve">19.2813835144043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.852014541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3414497375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5516834259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3954029083252</t>
+    <t xml:space="preserve">19.8520126342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3414516448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.551685333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3953990936279</t>
   </si>
   <si>
     <t xml:space="preserve">19.431547164917</t>
@@ -2684,76 +2684,76 @@
     <t xml:space="preserve">19.3264331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9571342468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1073017120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6779346466064</t>
+    <t xml:space="preserve">19.9571323394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1072998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6779327392578</t>
   </si>
   <si>
     <t xml:space="preserve">19.2663688659668</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5066318511963</t>
+    <t xml:space="preserve">19.5066299438477</t>
   </si>
   <si>
     <t xml:space="preserve">19.8820514678955</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0922813415527</t>
+    <t xml:space="preserve">20.0922832489014</t>
   </si>
   <si>
     <t xml:space="preserve">20.3475646972656</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3775959014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5967330932617</t>
+    <t xml:space="preserve">20.3775978088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5967350006104</t>
   </si>
   <si>
     <t xml:space="preserve">18.710750579834</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9209861755371</t>
+    <t xml:space="preserve">18.9209842681885</t>
   </si>
   <si>
     <t xml:space="preserve">18.7708148956299</t>
   </si>
   <si>
-    <t xml:space="preserve">18.830883026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5666980743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0861663818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9059658050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0711517333984</t>
+    <t xml:space="preserve">18.8308849334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5666961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0861682891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9059677124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0711479187012</t>
   </si>
   <si>
     <t xml:space="preserve">18.7558002471924</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4766006469727</t>
+    <t xml:space="preserve">19.476598739624</t>
   </si>
   <si>
     <t xml:space="preserve">19.2964000701904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5366668701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5216484069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3114147186279</t>
+    <t xml:space="preserve">19.5366687774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5216503143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3114166259766</t>
   </si>
   <si>
     <t xml:space="preserve">18.9810523986816</t>
@@ -2762,7 +2762,7 @@
     <t xml:space="preserve">20.4526824951172</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6178646087646</t>
+    <t xml:space="preserve">20.6178665161133</t>
   </si>
   <si>
     <t xml:space="preserve">19.6117515563965</t>
@@ -2771,19 +2771,19 @@
     <t xml:space="preserve">20.3625831604004</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6417827606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0322151184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5127468109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2424488067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.738000869751</t>
+    <t xml:space="preserve">19.6417808532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0322170257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5127506256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2424468994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7379989624023</t>
   </si>
   <si>
     <t xml:space="preserve">20.0021820068359</t>
@@ -2795,13 +2795,13 @@
     <t xml:space="preserve">18.1401176452637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3203182220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5577983856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4376621246338</t>
+    <t xml:space="preserve">18.3203163146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5577964782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4376659393311</t>
   </si>
   <si>
     <t xml:space="preserve">21.1284294128418</t>
@@ -2813,22 +2813,22 @@
     <t xml:space="preserve">20.497730255127</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0233135223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4137477874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3686943054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9031829833984</t>
+    <t xml:space="preserve">21.0233154296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4137496948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3686981201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9031848907471</t>
   </si>
   <si>
     <t xml:space="preserve">21.0383319854736</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4076328277588</t>
+    <t xml:space="preserve">20.4076309204102</t>
   </si>
   <si>
     <t xml:space="preserve">20.5427837371826</t>
@@ -2837,34 +2837,34 @@
     <t xml:space="preserve">20.3175315856934</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2124156951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4465637207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.746898651123</t>
+    <t xml:space="preserve">20.2124137878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4465656280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7468967437744</t>
   </si>
   <si>
     <t xml:space="preserve">19.2363338470459</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5277652740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7140808105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6840476989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6389980316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3386631011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6239814758301</t>
+    <t xml:space="preserve">20.5277633666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7140827178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6840496063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6389999389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3386650085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6239833831787</t>
   </si>
   <si>
     <t xml:space="preserve">21.8642482757568</t>
@@ -2873,64 +2873,64 @@
     <t xml:space="preserve">21.3987312316895</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4437789916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1884956359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9092960357666</t>
+    <t xml:space="preserve">21.4437808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.188497543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9092979431152</t>
   </si>
   <si>
     <t xml:space="preserve">21.8942794799805</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8342113494873</t>
+    <t xml:space="preserve">21.8342132568359</t>
   </si>
   <si>
     <t xml:space="preserve">21.5038452148438</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2546768188477</t>
+    <t xml:space="preserve">22.2546806335449</t>
   </si>
   <si>
     <t xml:space="preserve">22.0444469451904</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2847175598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3447799682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4649143218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6901607513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8703632354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6150798797607</t>
+    <t xml:space="preserve">22.2847118377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3447818756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.464916229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6901626586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.870361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6150817871094</t>
   </si>
   <si>
     <t xml:space="preserve">22.5700283050537</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6751461029053</t>
+    <t xml:space="preserve">22.6751480102539</t>
   </si>
   <si>
     <t xml:space="preserve">22.5775375366211</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9079055786133</t>
+    <t xml:space="preserve">22.9079074859619</t>
   </si>
   <si>
     <t xml:space="preserve">23.0430545806885</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0881080627441</t>
+    <t xml:space="preserve">23.0881023406982</t>
   </si>
   <si>
     <t xml:space="preserve">22.8178043365479</t>
@@ -2945,25 +2945,25 @@
     <t xml:space="preserve">23.2157459259033</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3809280395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.523588180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0505638122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.915412902832</t>
+    <t xml:space="preserve">23.380931854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5235900878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0505657196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9154148101807</t>
   </si>
   <si>
     <t xml:space="preserve">23.0730876922607</t>
   </si>
   <si>
-    <t xml:space="preserve">23.253288269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3433856964111</t>
+    <t xml:space="preserve">23.2532920837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3433876037598</t>
   </si>
   <si>
     <t xml:space="preserve">23.29833984375</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">24.0942211151123</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6648502349854</t>
+    <t xml:space="preserve">24.664852142334</t>
   </si>
   <si>
     <t xml:space="preserve">24.5522308349609</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">24.4020614624023</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0491695404053</t>
+    <t xml:space="preserve">24.0491714477539</t>
   </si>
   <si>
     <t xml:space="preserve">24.4696369171143</t>
@@ -3005,16 +3005,16 @@
     <t xml:space="preserve">24.1993350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9590702056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1617946624756</t>
+    <t xml:space="preserve">23.9590721130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1617984771729</t>
   </si>
   <si>
     <t xml:space="preserve">24.2293701171875</t>
   </si>
   <si>
-    <t xml:space="preserve">24.627311706543</t>
+    <t xml:space="preserve">24.6273097991943</t>
   </si>
   <si>
     <t xml:space="preserve">24.8075122833252</t>
@@ -3026,13 +3026,13 @@
     <t xml:space="preserve">25.1078395843506</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2204685211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1003379821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1829261779785</t>
+    <t xml:space="preserve">25.2204704284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1003360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1829299926758</t>
   </si>
   <si>
     <t xml:space="preserve">25.2955532073975</t>
@@ -3044,160 +3044,160 @@
     <t xml:space="preserve">25.8286437988281</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8061199188232</t>
+    <t xml:space="preserve">25.8061141967773</t>
   </si>
   <si>
     <t xml:space="preserve">25.7385425567627</t>
   </si>
   <si>
-    <t xml:space="preserve">25.783597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0538959503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8661880493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4893760681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5119018554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3767566680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4668502807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.65456199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5869846343994</t>
+    <t xml:space="preserve">25.7835922241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0538921356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8661842346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4893779754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5119037628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3767509460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.466854095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6545600891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5869827270508</t>
   </si>
   <si>
     <t xml:space="preserve">27.1050567626953</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5180206298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1350936889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3903770446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0149555206299</t>
+    <t xml:space="preserve">27.5180168151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1350955963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3903694152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0149593353271</t>
   </si>
   <si>
     <t xml:space="preserve">27.0374851226807</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2176856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1951637268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2251930236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2566184997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.684591293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1726360321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0299758911133</t>
+    <t xml:space="preserve">27.2176837921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1951580047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2251892089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2566223144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6845951080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1726341247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0299797058105</t>
   </si>
   <si>
     <t xml:space="preserve">26.7446594238281</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6245269775391</t>
+    <t xml:space="preserve">26.6245231628418</t>
   </si>
   <si>
     <t xml:space="preserve">25.8962173461914</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0163536071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3992805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3542289733887</t>
+    <t xml:space="preserve">26.0163516998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3992786407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3542251586914</t>
   </si>
   <si>
     <t xml:space="preserve">26.5569496154785</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0013313293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0238590240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.421802520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2866516113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2115707397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8873176574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1125679016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3603401184082</t>
+    <t xml:space="preserve">26.0013370513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0238609313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4218063354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2866477966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2115688323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8873195648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1125736236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3603420257568</t>
   </si>
   <si>
     <t xml:space="preserve">27.3828678131104</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6456604003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6231365203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7808094024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5930995941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4204063415527</t>
+    <t xml:space="preserve">27.6456565856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6231346130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7808074951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5931015014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4204082489014</t>
   </si>
   <si>
     <t xml:space="preserve">27.5630664825439</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7883186340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7132358551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9535026550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9835357666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2613391876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1412105560303</t>
+    <t xml:space="preserve">27.7883148193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7132301330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9535007476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9835376739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2613430023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1412086486816</t>
   </si>
   <si>
     <t xml:space="preserve">28.2087821960449</t>
@@ -3206,37 +3206,37 @@
     <t xml:space="preserve">28.18625831604</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3814735412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2012767791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0586185455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1186828613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.411506652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1698455810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3875904083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.507719039917</t>
+    <t xml:space="preserve">28.3814754486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2012748718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.058614730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1186809539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4115047454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.169849395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3875885009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5077247619629</t>
   </si>
   <si>
     <t xml:space="preserve">29.289981842041</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9145679473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4190101623535</t>
+    <t xml:space="preserve">28.9145641326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4190158843994</t>
   </si>
   <si>
     <t xml:space="preserve">28.6442680358887</t>
@@ -3245,19 +3245,19 @@
     <t xml:space="preserve">29.1923751831055</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1323089599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2149047851562</t>
+    <t xml:space="preserve">29.1323108673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.214900970459</t>
   </si>
   <si>
     <t xml:space="preserve">28.5842018127441</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4865951538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4565563201904</t>
+    <t xml:space="preserve">28.4865894317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4565601348877</t>
   </si>
   <si>
     <t xml:space="preserve">28.5466594696045</t>
@@ -3266,25 +3266,25 @@
     <t xml:space="preserve">28.4640693664551</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8784198760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4715747833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4040031433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0736293792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3964881896973</t>
+    <t xml:space="preserve">27.87841796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4715728759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4040012359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0736351013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3964920043945</t>
   </si>
   <si>
     <t xml:space="preserve">28.02858543396</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7644004821777</t>
+    <t xml:space="preserve">28.7643985748291</t>
   </si>
   <si>
     <t xml:space="preserve">29.6954288482666</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">29.7179584503174</t>
   </si>
   <si>
-    <t xml:space="preserve">29.943208694458</t>
+    <t xml:space="preserve">29.9432048797607</t>
   </si>
   <si>
     <t xml:space="preserve">30.401216506958</t>
@@ -3305,19 +3305,19 @@
     <t xml:space="preserve">30.5213489532471</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6940441131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5288543701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7090606689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4988269805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7766284942627</t>
+    <t xml:space="preserve">30.6940402984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5288524627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7090549468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4988193511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.77663230896</t>
   </si>
   <si>
     <t xml:space="preserve">31.7602233886719</t>
@@ -3326,13 +3326,13 @@
     <t xml:space="preserve">32.2107276916504</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4359741210938</t>
+    <t xml:space="preserve">32.4359703063965</t>
   </si>
   <si>
     <t xml:space="preserve">31.7376976013184</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1506538391113</t>
+    <t xml:space="preserve">32.1506576538086</t>
   </si>
   <si>
     <t xml:space="preserve">32.3083343505859</t>
@@ -3341,40 +3341,40 @@
     <t xml:space="preserve">32.3458709716797</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8728523254395</t>
+    <t xml:space="preserve">31.8728485107422</t>
   </si>
   <si>
     <t xml:space="preserve">31.1370334625244</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8592224121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0544414520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4641036987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2591953277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0342807769775</t>
+    <t xml:space="preserve">30.8592166900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0544452667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4641075134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2591972351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0342864990234</t>
   </si>
   <si>
     <t xml:space="preserve">29.640682220459</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8052864074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1265888214111</t>
+    <t xml:space="preserve">28.8052787780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1265850067139</t>
   </si>
   <si>
     <t xml:space="preserve">29.0864238739014</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0583801269531</t>
+    <t xml:space="preserve">30.0583820343018</t>
   </si>
   <si>
     <t xml:space="preserve">29.9378967285156</t>
@@ -3386,25 +3386,25 @@
     <t xml:space="preserve">30.5885448455811</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3596839904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3195190429688</t>
+    <t xml:space="preserve">31.3596801757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3195152282715</t>
   </si>
   <si>
     <t xml:space="preserve">31.0303382873535</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1508331298828</t>
+    <t xml:space="preserve">31.1508369445801</t>
   </si>
   <si>
     <t xml:space="preserve">31.3355827331543</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2632846832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1668968200684</t>
+    <t xml:space="preserve">31.2632884979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.166898727417</t>
   </si>
   <si>
     <t xml:space="preserve">31.1187000274658</t>
@@ -3416,25 +3416,25 @@
     <t xml:space="preserve">29.7531414031982</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4118251800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5644435882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.548376083374</t>
+    <t xml:space="preserve">30.4118270874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5644416809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5483741760254</t>
   </si>
   <si>
     <t xml:space="preserve">30.9419841766357</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2713241577148</t>
+    <t xml:space="preserve">31.2713203430176</t>
   </si>
   <si>
     <t xml:space="preserve">31.1829586029053</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1267356872559</t>
+    <t xml:space="preserve">31.1267318725586</t>
   </si>
   <si>
     <t xml:space="preserve">31.2150917053223</t>
@@ -3443,58 +3443,58 @@
     <t xml:space="preserve">31.2311592102051</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1909980773926</t>
+    <t xml:space="preserve">31.1909942626953</t>
   </si>
   <si>
     <t xml:space="preserve">30.4359188079834</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2029685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1788749694824</t>
+    <t xml:space="preserve">30.2029781341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1788730621338</t>
   </si>
   <si>
     <t xml:space="preserve">30.8375549316406</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8616561889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5082111358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.347562789917</t>
+    <t xml:space="preserve">30.8616523742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5082149505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3475570678711</t>
   </si>
   <si>
     <t xml:space="preserve">30.2913303375244</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4800281524658</t>
+    <t xml:space="preserve">29.4800319671631</t>
   </si>
   <si>
     <t xml:space="preserve">28.8856086730957</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3997001647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9338073730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7208671569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1907043457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.680700302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9939765930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0743064880371</t>
+    <t xml:space="preserve">29.3997039794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9338035583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7208633422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1907062530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6807022094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9939746856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0743083953857</t>
   </si>
   <si>
     <t xml:space="preserve">28.5803661346436</t>
@@ -3503,97 +3503,97 @@
     <t xml:space="preserve">28.965934753418</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0783920288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8695411682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8374099731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8133125305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6285648345947</t>
+    <t xml:space="preserve">29.0783939361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8695430755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8374137878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8133144378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6285591125488</t>
   </si>
   <si>
     <t xml:space="preserve">29.3595371246338</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0944633483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9579029083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3152847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1587181091309</t>
+    <t xml:space="preserve">29.0944576263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9578990936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3152866363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1587219238281</t>
   </si>
   <si>
     <t xml:space="preserve">29.3675746917725</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8936405181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8026943206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2799034118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4105987548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9600048065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9974231719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9810829162598</t>
+    <t xml:space="preserve">28.8936424255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8026962280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2799053192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4106025695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9600028991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9974212646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9810810089111</t>
   </si>
   <si>
     <t xml:space="preserve">25.9028205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9273300170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.322847366333</t>
+    <t xml:space="preserve">25.9273281097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3228492736816</t>
   </si>
   <si>
     <t xml:space="preserve">23.3623714447021</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8885860443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5175762176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3963661193848</t>
+    <t xml:space="preserve">22.8885898590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5175743103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3963680267334</t>
   </si>
   <si>
     <t xml:space="preserve">24.7101993560791</t>
   </si>
   <si>
-    <t xml:space="preserve">25.306510925293</t>
+    <t xml:space="preserve">25.3065090179443</t>
   </si>
   <si>
     <t xml:space="preserve">25.7231121063232</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8211345672607</t>
+    <t xml:space="preserve">25.8211364746094</t>
   </si>
   <si>
     <t xml:space="preserve">27.1281204223633</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9565773010254</t>
+    <t xml:space="preserve">26.956579208374</t>
   </si>
   <si>
     <t xml:space="preserve">27.144458770752</t>
@@ -3605,22 +3605,22 @@
     <t xml:space="preserve">27.1036167144775</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0709400177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9892539978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0300998687744</t>
+    <t xml:space="preserve">27.0709438323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9892559051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0300979614258</t>
   </si>
   <si>
     <t xml:space="preserve">27.3486766815186</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1328678131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9041442871094</t>
+    <t xml:space="preserve">28.1328659057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.904146194458</t>
   </si>
   <si>
     <t xml:space="preserve">27.5447235107422</t>
@@ -3629,46 +3629,46 @@
     <t xml:space="preserve">27.9776630401611</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5937366485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5481491088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7523651123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8830623626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8667240142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.539981842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4991359710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3439311981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6414241790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2377395629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3521003723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1152057647705</t>
+    <t xml:space="preserve">27.5937347412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5481472015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7523612976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8830604553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8667221069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5399780273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4991321563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3439292907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6414260864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2377376556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3520965576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1152076721191</t>
   </si>
   <si>
     <t xml:space="preserve">25.9109916687012</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3146781921387</t>
+    <t xml:space="preserve">25.3146800994873</t>
   </si>
   <si>
     <t xml:space="preserve">25.3310165405273</t>
@@ -3683,13 +3683,13 @@
     <t xml:space="preserve">25.8048000335693</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3555240631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9634265899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9913558959961</t>
+    <t xml:space="preserve">25.355525970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9634246826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9913539886475</t>
   </si>
   <si>
     <t xml:space="preserve">24.3017654418945</t>
@@ -3713,7 +3713,7 @@
     <t xml:space="preserve">26.6380023956299</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5073051452637</t>
+    <t xml:space="preserve">26.5073013305664</t>
   </si>
   <si>
     <t xml:space="preserve">27.5489635467529</t>
@@ -3722,52 +3722,52 @@
     <t xml:space="preserve">26.7698364257812</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4734306335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5743732452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6759948730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9639339447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5828380584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3457126617432</t>
+    <t xml:space="preserve">26.4734268188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5743713378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6759967803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9639320373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5828399658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3457164764404</t>
   </si>
   <si>
     <t xml:space="preserve">27.5235576629639</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7274894714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5320243835449</t>
+    <t xml:space="preserve">26.7274913787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5320262908936</t>
   </si>
   <si>
     <t xml:space="preserve">26.9561500549316</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2108974456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5164527893066</t>
+    <t xml:space="preserve">26.2108955383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5164546966553</t>
   </si>
   <si>
     <t xml:space="preserve">23.3992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8149127960205</t>
+    <t xml:space="preserve">22.8149108886719</t>
   </si>
   <si>
     <t xml:space="preserve">23.348445892334</t>
   </si>
   <si>
-    <t xml:space="preserve">23.975133895874</t>
+    <t xml:space="preserve">23.9751358032227</t>
   </si>
   <si>
     <t xml:space="preserve">22.9250049591064</t>
@@ -3779,49 +3779,49 @@
     <t xml:space="preserve">23.5686340332031</t>
   </si>
   <si>
-    <t xml:space="preserve">23.356912612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0859146118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8904457092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6194458007812</t>
+    <t xml:space="preserve">23.3569164276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0859127044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8904495239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6194477081299</t>
   </si>
   <si>
     <t xml:space="preserve">23.5093536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3230381011963</t>
+    <t xml:space="preserve">23.3230400085449</t>
   </si>
   <si>
     <t xml:space="preserve">22.8318481445312</t>
   </si>
   <si>
-    <t xml:space="preserve">22.747163772583</t>
+    <t xml:space="preserve">22.7471599578857</t>
   </si>
   <si>
     <t xml:space="preserve">22.7132873535156</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6462211608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9510955810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.264440536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7810382843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1120052337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4592227935791</t>
+    <t xml:space="preserve">21.64621925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9510974884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2644424438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7810363769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.112003326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4592266082764</t>
   </si>
   <si>
     <t xml:space="preserve">22.222095489502</t>
@@ -3830,10 +3830,10 @@
     <t xml:space="preserve">21.3074684143066</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7563133239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2898464202881</t>
+    <t xml:space="preserve">21.7563152313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2898502349854</t>
   </si>
   <si>
     <t xml:space="preserve">23.052038192749</t>
@@ -3845,46 +3845,46 @@
     <t xml:space="preserve">22.5185050964355</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0096950531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5015659332275</t>
+    <t xml:space="preserve">23.009693145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5015678405762</t>
   </si>
   <si>
     <t xml:space="preserve">22.6116619110107</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1536636352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9666652679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0513553619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9327926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.423978805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5256080627441</t>
+    <t xml:space="preserve">23.1536617279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.966667175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0513572692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9327945709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4239807128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5256061553955</t>
   </si>
   <si>
     <t xml:space="preserve">23.9497299194336</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8565731048584</t>
+    <t xml:space="preserve">23.856575012207</t>
   </si>
   <si>
     <t xml:space="preserve">23.4416027069092</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7888221740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1275730133057</t>
+    <t xml:space="preserve">23.7888240814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1275749206543</t>
   </si>
   <si>
     <t xml:space="preserve">24.1360416412354</t>
@@ -3893,10 +3893,10 @@
     <t xml:space="preserve">23.500883102417</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7380084991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0774459838867</t>
+    <t xml:space="preserve">23.7380123138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0774440765381</t>
   </si>
   <si>
     <t xml:space="preserve">22.5354442596436</t>
@@ -3911,7 +3911,7 @@
     <t xml:space="preserve">22.0950660705566</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0273132324219</t>
+    <t xml:space="preserve">22.0273151397705</t>
   </si>
   <si>
     <t xml:space="preserve">22.2559719085693</t>
@@ -3920,19 +3920,19 @@
     <t xml:space="preserve">22.3914737701416</t>
   </si>
   <si>
-    <t xml:space="preserve">21.925687789917</t>
+    <t xml:space="preserve">21.9256896972656</t>
   </si>
   <si>
     <t xml:space="preserve">22.2390365600586</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3237228393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4422836303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0689754486084</t>
+    <t xml:space="preserve">22.3237247467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4422855377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0689735412598</t>
   </si>
   <si>
     <t xml:space="preserve">23.9243240356445</t>
@@ -3944,16 +3944,16 @@
     <t xml:space="preserve">22.9419441223145</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6455364227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.730224609375</t>
+    <t xml:space="preserve">22.6455383300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7302227020264</t>
   </si>
   <si>
     <t xml:space="preserve">21.3921566009521</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5022506713867</t>
+    <t xml:space="preserve">21.5022487640381</t>
   </si>
   <si>
     <t xml:space="preserve">21.3413429260254</t>
@@ -3971,25 +3971,25 @@
     <t xml:space="preserve">20.8078098297119</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3335590362549</t>
+    <t xml:space="preserve">20.3335609436035</t>
   </si>
   <si>
     <t xml:space="preserve">24.2207317352295</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2552871704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0344161987305</t>
+    <t xml:space="preserve">23.2552852630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0344181060791</t>
   </si>
   <si>
     <t xml:space="preserve">23.4246635437012</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7979736328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4331359863281</t>
+    <t xml:space="preserve">22.7979755401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4331340789795</t>
   </si>
   <si>
     <t xml:space="preserve">23.6533222198486</t>
@@ -3998,85 +3998,85 @@
     <t xml:space="preserve">24.0174808502197</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3308238983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3477649688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2037925720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.79660987854</t>
+    <t xml:space="preserve">24.3308277130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3477630615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2037944793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7966079711914</t>
   </si>
   <si>
     <t xml:space="preserve">25.1438312530518</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8298015594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9737739562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2871150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3802738189697</t>
+    <t xml:space="preserve">25.8297996520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9737701416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2871170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3802700042725</t>
   </si>
   <si>
     <t xml:space="preserve">25.6265506744385</t>
   </si>
   <si>
-    <t xml:space="preserve">25.719705581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6858291625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.329460144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3118362426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9307422637939</t>
+    <t xml:space="preserve">25.7197093963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6858310699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3294563293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3118381500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9307441711426</t>
   </si>
   <si>
     <t xml:space="preserve">26.9053363800049</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1756553649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2264671325684</t>
+    <t xml:space="preserve">28.1756534576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.226469039917</t>
   </si>
   <si>
     <t xml:space="preserve">28.074031829834</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4551239013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2434043884277</t>
+    <t xml:space="preserve">28.4551219940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2434062957764</t>
   </si>
   <si>
     <t xml:space="preserve">28.1163711547852</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3111553192139</t>
+    <t xml:space="preserve">28.3111534118652</t>
   </si>
   <si>
     <t xml:space="preserve">28.1671848297119</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4297180175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7091865539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1848049163818</t>
+    <t xml:space="preserve">28.4297199249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7091884613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1848068237305</t>
   </si>
   <si>
     <t xml:space="preserve">27.2779655456543</t>
@@ -4088,40 +4088,40 @@
     <t xml:space="preserve">26.947681427002</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2864322662354</t>
+    <t xml:space="preserve">27.286434173584</t>
   </si>
   <si>
     <t xml:space="preserve">27.0238990783691</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6675262451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4981498718262</t>
+    <t xml:space="preserve">27.6675281524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4981517791748</t>
   </si>
   <si>
     <t xml:space="preserve">27.2610244750977</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0577735900879</t>
+    <t xml:space="preserve">27.0577754974365</t>
   </si>
   <si>
     <t xml:space="preserve">27.269495010376</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5574321746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0909652709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.125524520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0916500091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7105579376221</t>
+    <t xml:space="preserve">27.5574340820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0909671783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1255264282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0916481018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7105541229248</t>
   </si>
   <si>
     <t xml:space="preserve">26.7952423095703</t>
@@ -4130,22 +4130,22 @@
     <t xml:space="preserve">27.4219341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2271499633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.43039894104</t>
+    <t xml:space="preserve">27.2271518707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4304008483887</t>
   </si>
   <si>
     <t xml:space="preserve">27.3203048706055</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1509304046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7013988494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2349376678467</t>
+    <t xml:space="preserve">27.1509323120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7014026641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.234935760498</t>
   </si>
   <si>
     <t xml:space="preserve">27.9046535491943</t>
@@ -4154,67 +4154,67 @@
     <t xml:space="preserve">28.1925945281982</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4720611572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4635944366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0818195343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2935352325439</t>
+    <t xml:space="preserve">28.4720592498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4635906219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0818157196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2935371398926</t>
   </si>
   <si>
     <t xml:space="preserve">29.0479393005371</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7938747406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6922492980957</t>
+    <t xml:space="preserve">28.7938766479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.692253112793</t>
   </si>
   <si>
     <t xml:space="preserve">28.4043140411377</t>
   </si>
   <si>
-    <t xml:space="preserve">28.717658996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8446922302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8362197875977</t>
+    <t xml:space="preserve">28.7176570892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8446884155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.836217880249</t>
   </si>
   <si>
     <t xml:space="preserve">28.8531589508057</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6245002746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8108177185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8785648345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0902824401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8700942993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.827751159668</t>
+    <t xml:space="preserve">28.6244983673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.81081199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8785629272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0902843475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8700923919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8277530670166</t>
   </si>
   <si>
     <t xml:space="preserve">28.1417770385742</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7599983215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6753120422363</t>
+    <t xml:space="preserve">28.7600002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.675313949585</t>
   </si>
   <si>
     <t xml:space="preserve">28.759183883667</t>
@@ -4229,16 +4229,16 @@
     <t xml:space="preserve">28.1954479217529</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0133190155029</t>
+    <t xml:space="preserve">28.0133171081543</t>
   </si>
   <si>
     <t xml:space="preserve">28.2908496856689</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3515605926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2995223999023</t>
+    <t xml:space="preserve">28.3515586853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.299524307251</t>
   </si>
   <si>
     <t xml:space="preserve">28.1520843505859</t>
@@ -4250,22 +4250,22 @@
     <t xml:space="preserve">28.2214679718018</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1434154510498</t>
+    <t xml:space="preserve">28.1434135437012</t>
   </si>
   <si>
     <t xml:space="preserve">26.9812507629395</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1660003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4027919769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0185642242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9344577789307</t>
+    <t xml:space="preserve">26.1660022735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4027900695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0185623168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.934455871582</t>
   </si>
   <si>
     <t xml:space="preserve">25.0558757781982</t>
@@ -4274,22 +4274,22 @@
     <t xml:space="preserve">24.275318145752</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9951648712158</t>
+    <t xml:space="preserve">24.9951667785645</t>
   </si>
   <si>
     <t xml:space="preserve">25.8017406463623</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3594264984131</t>
+    <t xml:space="preserve">25.3594245910645</t>
   </si>
   <si>
     <t xml:space="preserve">25.3247356414795</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8997650146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.012508392334</t>
+    <t xml:space="preserve">24.8997669219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0125102996826</t>
   </si>
   <si>
     <t xml:space="preserve">24.7176342010498</t>
@@ -4298,7 +4298,7 @@
     <t xml:space="preserve">25.1686248779297</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4635009765625</t>
+    <t xml:space="preserve">25.4634990692139</t>
   </si>
   <si>
     <t xml:space="preserve">25.4808444976807</t>
@@ -4307,7 +4307,7 @@
     <t xml:space="preserve">25.4461536407471</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3073902130127</t>
+    <t xml:space="preserve">25.3073883056641</t>
   </si>
   <si>
     <t xml:space="preserve">24.9518032073975</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">25.9058170318604</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1052932739258</t>
+    <t xml:space="preserve">26.1052913665771</t>
   </si>
   <si>
     <t xml:space="preserve">25.6716499328613</t>
@@ -4331,7 +4331,7 @@
     <t xml:space="preserve">25.6196117401123</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2006912231445</t>
+    <t xml:space="preserve">26.2006931304932</t>
   </si>
   <si>
     <t xml:space="preserve">26.4088401794434</t>
@@ -4340,16 +4340,16 @@
     <t xml:space="preserve">26.4435329437256</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5042419433594</t>
+    <t xml:space="preserve">26.5042400360107</t>
   </si>
   <si>
     <t xml:space="preserve">26.313440322876</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1833477020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.452205657959</t>
+    <t xml:space="preserve">26.1833457946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4522037506104</t>
   </si>
   <si>
     <t xml:space="preserve">26.0966186523438</t>
@@ -4358,13 +4358,13 @@
     <t xml:space="preserve">25.4721736907959</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6109390258789</t>
+    <t xml:space="preserve">25.6109409332275</t>
   </si>
   <si>
     <t xml:space="preserve">25.3767700195312</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3307876586914</t>
+    <t xml:space="preserve">26.3307857513428</t>
   </si>
   <si>
     <t xml:space="preserve">26.1920223236084</t>
@@ -4373,25 +4373,25 @@
     <t xml:space="preserve">26.0098896026611</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8104133605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5215892791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8424835205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4868984222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5996475219727</t>
+    <t xml:space="preserve">25.8104152679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5215873718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8424816131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4868965148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5996437072754</t>
   </si>
   <si>
     <t xml:space="preserve">26.7297382354736</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1062126159668</t>
+    <t xml:space="preserve">27.1062088012695</t>
   </si>
   <si>
     <t xml:space="preserve">27.0882835388184</t>
@@ -4403,7 +4403,7 @@
     <t xml:space="preserve">26.4070415496826</t>
   </si>
   <si>
-    <t xml:space="preserve">26.675952911377</t>
+    <t xml:space="preserve">26.6759548187256</t>
   </si>
   <si>
     <t xml:space="preserve">26.7028465270996</t>
@@ -4412,7 +4412,7 @@
     <t xml:space="preserve">26.3084411621094</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8154373168945</t>
+    <t xml:space="preserve">25.8154392242432</t>
   </si>
   <si>
     <t xml:space="preserve">26.3622245788574</t>
@@ -4424,7 +4424,7 @@
     <t xml:space="preserve">26.6938819885254</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2048110961914</t>
+    <t xml:space="preserve">27.20481300354</t>
   </si>
   <si>
     <t xml:space="preserve">27.4737224578857</t>
@@ -4433,25 +4433,25 @@
     <t xml:space="preserve">27.5185413360596</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3930492401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6529979705811</t>
+    <t xml:space="preserve">27.3930473327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6529960632324</t>
   </si>
   <si>
     <t xml:space="preserve">27.7157421112061</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9219074249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8860530853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9667282104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9398365020752</t>
+    <t xml:space="preserve">27.9219055175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8860549926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9667263031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9398345947266</t>
   </si>
   <si>
     <t xml:space="preserve">27.7605609893799</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">27.3213405609131</t>
   </si>
   <si>
-    <t xml:space="preserve">27.60817527771</t>
+    <t xml:space="preserve">27.6081790924072</t>
   </si>
   <si>
     <t xml:space="preserve">27.9487991333008</t>
@@ -4481,97 +4481,97 @@
     <t xml:space="preserve">28.2356376647949</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7644958496094</t>
+    <t xml:space="preserve">28.7644939422607</t>
   </si>
   <si>
     <t xml:space="preserve">28.3611278533936</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9129428863525</t>
+    <t xml:space="preserve">27.9129447937012</t>
   </si>
   <si>
     <t xml:space="preserve">27.4378681182861</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8233070373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9577617645264</t>
+    <t xml:space="preserve">27.8233089447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.957763671875</t>
   </si>
   <si>
     <t xml:space="preserve">28.5045471191406</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7465667724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6927833557129</t>
+    <t xml:space="preserve">28.7465686798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6927852630615</t>
   </si>
   <si>
     <t xml:space="preserve">28.7555332183838</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9796237945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0334033966064</t>
+    <t xml:space="preserve">28.9796257019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0334053039551</t>
   </si>
   <si>
     <t xml:space="preserve">29.1320056915283</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3740234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2306079864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.705680847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1000862121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9606018066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5482730865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1986827850342</t>
+    <t xml:space="preserve">29.3740272521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2306060791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7056846618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1000881195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9606037139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5482711791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1986865997314</t>
   </si>
   <si>
     <t xml:space="preserve">29.8132457733154</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8311710357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7734546661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1588973999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3202419281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1140804290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4457340240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3650608062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0871906280518</t>
+    <t xml:space="preserve">29.8311729431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7734565734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1588954925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3202438354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1140785217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4457321166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.365062713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0871887207031</t>
   </si>
   <si>
     <t xml:space="preserve">28.7017478942871</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9975509643555</t>
+    <t xml:space="preserve">28.9975490570068</t>
   </si>
   <si>
     <t xml:space="preserve">29.1768226623535</t>
@@ -4580,19 +4580,19 @@
     <t xml:space="preserve">29.2574996948242</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3112812042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.571231842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1628322601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9745922088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2166137695312</t>
+    <t xml:space="preserve">29.3112831115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5712280273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1628303527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.974588394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2166118621826</t>
   </si>
   <si>
     <t xml:space="preserve">30.0014839172363</t>
@@ -4601,46 +4601,46 @@
     <t xml:space="preserve">30.0283737182617</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7773933410645</t>
+    <t xml:space="preserve">29.7773914337158</t>
   </si>
   <si>
     <t xml:space="preserve">29.7236099243164</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7684288024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1717948913574</t>
+    <t xml:space="preserve">29.7684268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1717967987061</t>
   </si>
   <si>
     <t xml:space="preserve">30.180757522583</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4586334228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0104503631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.270393371582</t>
+    <t xml:space="preserve">30.4586353302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0104484558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2703971862793</t>
   </si>
   <si>
     <t xml:space="preserve">30.593090057373</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1449031829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1538677215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0463027954102</t>
+    <t xml:space="preserve">30.144905090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.153865814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0463047027588</t>
   </si>
   <si>
     <t xml:space="preserve">30.0373382568359</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6967220306396</t>
+    <t xml:space="preserve">29.6967182159424</t>
   </si>
   <si>
     <t xml:space="preserve">29.1678619384766</t>
@@ -4649,37 +4649,37 @@
     <t xml:space="preserve">29.6877536773682</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3292102813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4278087615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0552673339844</t>
+    <t xml:space="preserve">29.3292083740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4278125762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0552654266357</t>
   </si>
   <si>
     <t xml:space="preserve">28.7107124328613</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5224742889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4776573181152</t>
+    <t xml:space="preserve">28.5224761962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4776554107666</t>
   </si>
   <si>
     <t xml:space="preserve">28.2177085876465</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7426338195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3392677307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.509578704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3571949005127</t>
+    <t xml:space="preserve">27.7426319122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3392658233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5095767974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3571968078613</t>
   </si>
   <si>
     <t xml:space="preserve">27.0524291992188</t>
@@ -4688,13 +4688,13 @@
     <t xml:space="preserve">27.1868839263916</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2854862213135</t>
+    <t xml:space="preserve">27.2854843139648</t>
   </si>
   <si>
     <t xml:space="preserve">27.2944488525391</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4468307495117</t>
+    <t xml:space="preserve">27.4468326568604</t>
   </si>
   <si>
     <t xml:space="preserve">27.5454330444336</t>
@@ -4703,25 +4703,25 @@
     <t xml:space="preserve">28.0294723510742</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4059467315674</t>
+    <t xml:space="preserve">28.405948638916</t>
   </si>
   <si>
     <t xml:space="preserve">28.1191082000732</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2714939117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6838207244873</t>
+    <t xml:space="preserve">28.2714920043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6838226318359</t>
   </si>
   <si>
     <t xml:space="preserve">28.495584487915</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0423736572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.732572555542</t>
+    <t xml:space="preserve">29.0423698425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7325744628906</t>
   </si>
   <si>
     <t xml:space="preserve">29.7863540649414</t>
@@ -4739,139 +4739,139 @@
     <t xml:space="preserve">29.194751739502</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8989505767822</t>
+    <t xml:space="preserve">28.8989524841309</t>
   </si>
   <si>
     <t xml:space="preserve">29.2664623260498</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0602970123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1499328613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4367713928223</t>
+    <t xml:space="preserve">29.0602951049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1499366760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4367733001709</t>
   </si>
   <si>
     <t xml:space="preserve">29.0961513519287</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2485332489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5891513824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6070823669434</t>
+    <t xml:space="preserve">29.24853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5891532897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6070804595947</t>
   </si>
   <si>
     <t xml:space="preserve">29.7953205108643</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2883224487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0731925964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4048480987549</t>
+    <t xml:space="preserve">30.2883262634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0731945037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4048500061035</t>
   </si>
   <si>
     <t xml:space="preserve">30.4317436218262</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3600311279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2255802154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1359405517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3152103424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3421020507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7454719543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3331432342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0642318725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6110153198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8440685272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0860900878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1936569213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1577987670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1757278442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3818912506104</t>
+    <t xml:space="preserve">30.3600292205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2255764007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1359367370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3152122497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3421039581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7454700469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3331394195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0642337799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6110172271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8440723419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0860919952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1936550140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1578006744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1757297515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3818893432617</t>
   </si>
   <si>
     <t xml:space="preserve">31.5522041320801</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8121509552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8480072021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0003890991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2384738922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.713550567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7314796447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5432357788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8300762176514</t>
+    <t xml:space="preserve">31.8121528625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8480052947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0003852844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2384719848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7135543823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.731481552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5432415008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.830078125</t>
   </si>
   <si>
     <t xml:space="preserve">31.8211135864258</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1258811950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0900230407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2743301391602</t>
+    <t xml:space="preserve">32.1258773803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0900268554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2743282318115</t>
   </si>
   <si>
     <t xml:space="preserve">30.9068183898926</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9785289764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1090488433838</t>
+    <t xml:space="preserve">30.9785308837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1090507507324</t>
   </si>
   <si>
     <t xml:space="preserve">30.3958892822266</t>
@@ -71073,7 +71073,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6495717593</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>121832</v>
@@ -71094,6 +71094,32 @@
         <v>1928</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6496064815</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>136063</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>47.9599990844727</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>47.3199996948242</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>47.4799995422363</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>47.4799995422363</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1971</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BGN.MI.xlsx
+++ b/data/BGN.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4796009063721</t>
+    <t xml:space="preserve">17.4795970916748</t>
   </si>
   <si>
     <t xml:space="preserve">BGN.MI</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">16.7816524505615</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5284156799316</t>
+    <t xml:space="preserve">16.528413772583</t>
   </si>
   <si>
     <t xml:space="preserve">16.262825012207</t>
@@ -59,49 +59,49 @@
     <t xml:space="preserve">16.3678245544434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5098838806152</t>
+    <t xml:space="preserve">16.5098819732666</t>
   </si>
   <si>
     <t xml:space="preserve">16.9422416687012</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6457691192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1269397735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6760492324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9601745605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0707492828369</t>
+    <t xml:space="preserve">16.6457710266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1269378662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6760511398315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9601764678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0707540512085</t>
   </si>
   <si>
     <t xml:space="preserve">15.0769290924072</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5092840194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5401678085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4289894104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6019344329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1942844390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4784021377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2931079864502</t>
+    <t xml:space="preserve">15.5092878341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.540168762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4289922714233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6019353866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1942825317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.478404045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2931089401245</t>
   </si>
   <si>
     <t xml:space="preserve">15.0213384628296</t>
@@ -110,172 +110,172 @@
     <t xml:space="preserve">13.8230905532837</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7180910110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5945587158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4580764770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6804332733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5636730194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1745567321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4154376983643</t>
+    <t xml:space="preserve">13.718090057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5945596694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4580736160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6804313659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5636777877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1745557785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4154386520386</t>
   </si>
   <si>
     <t xml:space="preserve">14.0022106170654</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8477993011475</t>
+    <t xml:space="preserve">13.8477973937988</t>
   </si>
   <si>
     <t xml:space="preserve">14.385157585144</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4098615646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1936836242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4963350296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1813287734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3233919143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3357410430908</t>
+    <t xml:space="preserve">14.4098625183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1936826705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4963340759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1813306808472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3233909606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3357429504395</t>
   </si>
   <si>
     <t xml:space="preserve">14.5210399627686</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8607501983643</t>
+    <t xml:space="preserve">14.8607473373413</t>
   </si>
   <si>
     <t xml:space="preserve">15.2436952590942</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5710487365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4969329833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4351663589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4413452148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3239917755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0157642364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.201057434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2937068939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1578216552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3431186676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8489952087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8922328948975</t>
+    <t xml:space="preserve">15.5710525512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4969339370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4351673126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4413433074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3239898681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0157623291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2010593414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2937049865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1578254699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3431167602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8489942550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8922319412231</t>
   </si>
   <si>
     <t xml:space="preserve">15.6081104278564</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9354677200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9663515090942</t>
+    <t xml:space="preserve">15.9354686737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9663486480713</t>
   </si>
   <si>
     <t xml:space="preserve">16.0095863342285</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8675231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8298683166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8854579925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6569223403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9410438537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3981094360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.533989906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.873703956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9478216171265</t>
+    <t xml:space="preserve">15.8675260543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8298654556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8854541778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6569242477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.941047668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3981113433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5339879989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8737001419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9478206634521</t>
   </si>
   <si>
     <t xml:space="preserve">16.1145877838135</t>
   </si>
   <si>
-    <t xml:space="preserve">16.083703994751</t>
+    <t xml:space="preserve">16.0837020874023</t>
   </si>
   <si>
     <t xml:space="preserve">16.0713500976562</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1084098815918</t>
+    <t xml:space="preserve">16.1084079742432</t>
   </si>
   <si>
     <t xml:space="preserve">16.2072353363037</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0590000152588</t>
+    <t xml:space="preserve">16.0589981079102</t>
   </si>
   <si>
     <t xml:space="preserve">16.2998828887939</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1701774597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1207675933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7316427230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3795785903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1201639175415</t>
+    <t xml:space="preserve">16.1701755523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1207637786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7316398620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3795776367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1201658248901</t>
   </si>
   <si>
     <t xml:space="preserve">14.8916330337524</t>
@@ -284,16 +284,16 @@
     <t xml:space="preserve">14.706335067749</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6383953094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6075105667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2986850738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4530982971191</t>
+    <t xml:space="preserve">14.6383962631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6075134277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2986869812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4530973434448</t>
   </si>
   <si>
     <t xml:space="preserve">14.6692781448364</t>
@@ -305,46 +305,46 @@
     <t xml:space="preserve">14.3666248321533</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3913316726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3975105285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5537919998169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8142604827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9640331268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5110187530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5956745147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3742752075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3286924362183</t>
+    <t xml:space="preserve">14.3913326263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3975095748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5537948608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8142623901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9640302658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5110197067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5956735610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3742742538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3286895751953</t>
   </si>
   <si>
     <t xml:space="preserve">15.1138010025024</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0096158981323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0551977157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2114791870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3547391891479</t>
+    <t xml:space="preserve">15.0096130371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0551958084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.211480140686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3547372817993</t>
   </si>
   <si>
     <t xml:space="preserve">15.3026456832886</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">15.257061958313</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8533334732056</t>
+    <t xml:space="preserve">14.8533325195312</t>
   </si>
   <si>
     <t xml:space="preserve">14.0979671478271</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">13.2058572769165</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9649219512939</t>
+    <t xml:space="preserve">12.9649200439453</t>
   </si>
   <si>
     <t xml:space="preserve">12.9453840255737</t>
@@ -374,37 +374,37 @@
     <t xml:space="preserve">13.6616792678833</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8374967575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1565704345703</t>
+    <t xml:space="preserve">13.8374977111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1565732955933</t>
   </si>
   <si>
     <t xml:space="preserve">14.5733261108398</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8737573623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6690797805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7341976165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6560573577881</t>
+    <t xml:space="preserve">12.87375831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6690807342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7341995239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6560564041138</t>
   </si>
   <si>
     <t xml:space="preserve">11.6821041107178</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6039619445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2002334594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8160390853882</t>
+    <t xml:space="preserve">11.6039628982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.200234413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8160400390625</t>
   </si>
   <si>
     <t xml:space="preserve">10.431845664978</t>
@@ -413,106 +413,106 @@
     <t xml:space="preserve">10.7444095611572</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2588396072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.923038482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3137454986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2616510391235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5286321640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5677032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6588697433472</t>
+    <t xml:space="preserve">11.2588386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9230403900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3137435913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2616500854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5286340713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.567702293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6588678359985</t>
   </si>
   <si>
     <t xml:space="preserve">12.372350692749</t>
   </si>
   <si>
-    <t xml:space="preserve">12.522120475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5416574478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3397922515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5025854110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2551393508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4895629882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2421140670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0337381362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8188524246216</t>
+    <t xml:space="preserve">12.5221195220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5416555404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3397941589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5025882720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2551403045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4895620346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.242115020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0337390899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8188505172729</t>
   </si>
   <si>
     <t xml:space="preserve">11.6300115585327</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4281454086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3825616836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8579216003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9946689605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1835079193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2030439376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0532760620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9490880966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7928056716919</t>
+    <t xml:space="preserve">11.4281463623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3825626373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8579196929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9946699142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1835088729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2030467987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0532751083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.94908618927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7928047180176</t>
   </si>
   <si>
     <t xml:space="preserve">11.525821685791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7667570114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4411687850952</t>
+    <t xml:space="preserve">11.7667560577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4411678314209</t>
   </si>
   <si>
     <t xml:space="preserve">11.3630275726318</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5583810806274</t>
+    <t xml:space="preserve">11.5583791732788</t>
   </si>
   <si>
     <t xml:space="preserve">11.7797803878784</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5388441085815</t>
+    <t xml:space="preserve">11.5388450622559</t>
   </si>
   <si>
     <t xml:space="preserve">11.7472229003906</t>
@@ -524,13 +524,13 @@
     <t xml:space="preserve">11.9425745010376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1314163208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1379261016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4114198684692</t>
+    <t xml:space="preserve">12.1314144134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1379251480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4114217758179</t>
   </si>
   <si>
     <t xml:space="preserve">12.4830493927002</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">12.6653814315796</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8021268844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3788623809814</t>
+    <t xml:space="preserve">12.8021259307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3788633346558</t>
   </si>
   <si>
     <t xml:space="preserve">12.1183929443359</t>
@@ -554,133 +554,133 @@
     <t xml:space="preserve">12.2876987457275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8709449768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.701639175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8514089584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9165267944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.252326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1937236785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.148138999939</t>
+    <t xml:space="preserve">11.870945930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7016401290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.851411819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9165258407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2523279190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1937217712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1481399536133</t>
   </si>
   <si>
     <t xml:space="preserve">11.0830211639404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.122091293335</t>
+    <t xml:space="preserve">11.1220932006836</t>
   </si>
   <si>
     <t xml:space="preserve">11.1741857528687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1090669631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2848863601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1351156234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.076509475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1872100830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0244150161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0179042816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6430311203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5779161453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9100170135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1769971847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.294207572937</t>
+    <t xml:space="preserve">11.1090679168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2848854064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1351146697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0765104293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1872091293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0244169235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0179033279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6430330276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.577917098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9100160598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1769981384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.29421043396</t>
   </si>
   <si>
     <t xml:space="preserve">12.4309568405151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9779443740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0365514755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3816747665405</t>
+    <t xml:space="preserve">12.9779462814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0365495681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3816719055176</t>
   </si>
   <si>
     <t xml:space="preserve">13.5640048980713</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4142322540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1732978820801</t>
+    <t xml:space="preserve">13.414231300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1732969284058</t>
   </si>
   <si>
     <t xml:space="preserve">13.0560855865479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9258499145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8281745910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3295793533325</t>
+    <t xml:space="preserve">12.9258527755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8281755447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3295822143555</t>
   </si>
   <si>
     <t xml:space="preserve">13.7984285354614</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5444679260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.88307762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8309831619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9482002258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8895931243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1240139007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4923715591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9388751983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9323635101318</t>
+    <t xml:space="preserve">13.5444660186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8830795288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8309850692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9481964111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8895921707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1240177154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.492374420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9388732910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9323625564575</t>
   </si>
   <si>
     <t xml:space="preserve">12.8672437667847</t>
@@ -689,28 +689,28 @@
     <t xml:space="preserve">12.9714326858521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9909696578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7760801315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7956142425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7304983139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7435216903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4691381454468</t>
+    <t xml:space="preserve">12.9909706115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7760791778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.795615196228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7304944992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.74351978302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4691400527954</t>
   </si>
   <si>
     <t xml:space="preserve">15.2896203994751</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8887004852295</t>
+    <t xml:space="preserve">15.8887062072754</t>
   </si>
   <si>
     <t xml:space="preserve">15.5761384963989</t>
@@ -719,91 +719,91 @@
     <t xml:space="preserve">15.3612508773804</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4784603118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0747337341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.185432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8989133834839</t>
+    <t xml:space="preserve">15.478461265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0747356414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1854314804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8989152908325</t>
   </si>
   <si>
     <t xml:space="preserve">14.8793802261353</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9575223922729</t>
+    <t xml:space="preserve">14.9575204849243</t>
   </si>
   <si>
     <t xml:space="preserve">14.9770574569702</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0031032562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7817029953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5863513946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7556581497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.859845161438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3417148590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4459028244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8403120040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2700881958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5305547714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4133443832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3482275009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5631151199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5138301849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6570911407471</t>
+    <t xml:space="preserve">15.0031051635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7817039489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5863475799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7556552886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8598442077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3417129516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4459018707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.840311050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2700853347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5305576324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4133453369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3482294082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5631141662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5138339996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6570930480957</t>
   </si>
   <si>
     <t xml:space="preserve">16.5659275054932</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1231269836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0514965057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6803274154663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7454481124878</t>
+    <t xml:space="preserve">16.1231288909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0514984130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6803255081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7454471588135</t>
   </si>
   <si>
     <t xml:space="preserve">15.7584676742554</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0356636047363</t>
+    <t xml:space="preserve">15.0356616973877</t>
   </si>
   <si>
     <t xml:space="preserve">15.335205078125</t>
@@ -812,121 +812,121 @@
     <t xml:space="preserve">15.2375259399414</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4328804016113</t>
+    <t xml:space="preserve">15.432879447937</t>
   </si>
   <si>
     <t xml:space="preserve">16.2208023071289</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2924346923828</t>
+    <t xml:space="preserve">16.2924327850342</t>
   </si>
   <si>
     <t xml:space="preserve">16.1491718292236</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9538192749023</t>
+    <t xml:space="preserve">15.9538202285767</t>
   </si>
   <si>
     <t xml:space="preserve">16.175220489502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8626575469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5566024780273</t>
+    <t xml:space="preserve">15.8626556396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5566005706787</t>
   </si>
   <si>
     <t xml:space="preserve">15.1593856811523</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2245016098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8468208312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1658983230591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4003200531006</t>
+    <t xml:space="preserve">15.2245044708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8468227386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1658992767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4003219604492</t>
   </si>
   <si>
     <t xml:space="preserve">15.3091564178467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6021852493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6217212677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6738147735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5500898361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3677616119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3938064575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1398515701294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1072912216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0812425613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6152105331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6282339096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5435781478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7975416183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9342851638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2012634277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4422016143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.377082824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.279411315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1426639556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4812717437744</t>
+    <t xml:space="preserve">15.6021842956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6217193603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6738157272339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5500926971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3677635192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3938102722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1398496627808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.107292175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0812454223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6152095794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6282320022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5435810089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7975378036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9342861175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2012672424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4422035217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3770847320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2794094085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1426601409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4812755584717</t>
   </si>
   <si>
     <t xml:space="preserve">16.6049976348877</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2338275909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2561721801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.269193649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1584968566895</t>
+    <t xml:space="preserve">16.233829498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2561740875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2691993713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1584987640381</t>
   </si>
   <si>
     <t xml:space="preserve">17.1454753875732</t>
@@ -935,16 +935,16 @@
     <t xml:space="preserve">17.1845436096191</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1389617919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.646879196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6273441314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3892192840576</t>
+    <t xml:space="preserve">17.1389598846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6468811035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6273403167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3892211914062</t>
   </si>
   <si>
     <t xml:space="preserve">18.1678218841553</t>
@@ -953,25 +953,25 @@
     <t xml:space="preserve">18.1027030944824</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3501510620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1352615356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.493408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0896797180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2264251708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8588123321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8723411560059</t>
+    <t xml:space="preserve">18.3501491546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1352596282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4934062957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0896778106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2264270782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8588104248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8723430633545</t>
   </si>
   <si>
     <t xml:space="preserve">18.6896419525146</t>
@@ -980,52 +980,52 @@
     <t xml:space="preserve">18.6422748565674</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5137100219727</t>
+    <t xml:space="preserve">18.513708114624</t>
   </si>
   <si>
     <t xml:space="preserve">17.8370380401611</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6543388366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3836708068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9047031402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.931770324707</t>
+    <t xml:space="preserve">17.6543369293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3836688995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9047050476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9317722320557</t>
   </si>
   <si>
     <t xml:space="preserve">17.5393009185791</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5460720062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9926700592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6761074066162</t>
+    <t xml:space="preserve">17.546070098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.99267578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6761093139648</t>
   </si>
   <si>
     <t xml:space="preserve">18.926477432251</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8046741485596</t>
+    <t xml:space="preserve">18.8046779632568</t>
   </si>
   <si>
     <t xml:space="preserve">18.9806118011475</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6219749450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0400409698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.337776184082</t>
+    <t xml:space="preserve">18.621976852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0400371551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3377742767334</t>
   </si>
   <si>
     <t xml:space="preserve">18.2092037200928</t>
@@ -1043,73 +1043,73 @@
     <t xml:space="preserve">18.0062046051025</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4054412841797</t>
+    <t xml:space="preserve">18.4054431915283</t>
   </si>
   <si>
     <t xml:space="preserve">18.0603408813477</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6340370178223</t>
+    <t xml:space="preserve">17.6340351104736</t>
   </si>
   <si>
     <t xml:space="preserve">18.2430400848389</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2701091766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6490421295166</t>
+    <t xml:space="preserve">18.2701072692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.649040222168</t>
   </si>
   <si>
     <t xml:space="preserve">18.4528064727783</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7031745910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4595737457275</t>
+    <t xml:space="preserve">18.7031764984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4595756530762</t>
   </si>
   <si>
     <t xml:space="preserve">19.1024112701416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9467792510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9197082519531</t>
+    <t xml:space="preserve">18.9467754364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9197120666504</t>
   </si>
   <si>
     <t xml:space="preserve">18.7776107788086</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8791084289551</t>
+    <t xml:space="preserve">18.8791122436523</t>
   </si>
   <si>
     <t xml:space="preserve">19.1362457275391</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0415115356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.183614730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3730773925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2918758392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8264503479004</t>
+    <t xml:space="preserve">19.0415096282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1836128234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3730792999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2918796539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8264465332031</t>
   </si>
   <si>
     <t xml:space="preserve">19.9414806365967</t>
   </si>
   <si>
-    <t xml:space="preserve">20.300121307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5166511535645</t>
+    <t xml:space="preserve">20.3001194000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5166549682617</t>
   </si>
   <si>
     <t xml:space="preserve">20.0971202850342</t>
@@ -1118,31 +1118,31 @@
     <t xml:space="preserve">19.9956169128418</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1241874694824</t>
+    <t xml:space="preserve">20.1241855621338</t>
   </si>
   <si>
     <t xml:space="preserve">20.1444854736328</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6384544372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2392177581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8941173553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5625457763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7587814331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9211826324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9008846282959</t>
+    <t xml:space="preserve">20.6384525299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2392196655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8941192626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5625495910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7587833404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9211845397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9008827209473</t>
   </si>
   <si>
     <t xml:space="preserve">19.7993831634521</t>
@@ -1151,19 +1151,19 @@
     <t xml:space="preserve">19.7655467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">19.812915802002</t>
+    <t xml:space="preserve">19.8129177093506</t>
   </si>
   <si>
     <t xml:space="preserve">19.4813480377197</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5828475952148</t>
+    <t xml:space="preserve">19.5828495025635</t>
   </si>
   <si>
     <t xml:space="preserve">19.4881134033203</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2851104736328</t>
+    <t xml:space="preserve">19.2851161956787</t>
   </si>
   <si>
     <t xml:space="preserve">18.7640762329102</t>
@@ -1172,16 +1172,16 @@
     <t xml:space="preserve">18.7573089599609</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5949096679688</t>
+    <t xml:space="preserve">18.5949077606201</t>
   </si>
   <si>
     <t xml:space="preserve">18.8452758789062</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8655757904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.534008026123</t>
+    <t xml:space="preserve">18.8655776977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5340099334717</t>
   </si>
   <si>
     <t xml:space="preserve">19.0144443511963</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">19.2242126464844</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1700782775879</t>
+    <t xml:space="preserve">19.1700801849365</t>
   </si>
   <si>
     <t xml:space="preserve">19.2512798309326</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">19.1971473693848</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4475135803223</t>
+    <t xml:space="preserve">19.4475154876709</t>
   </si>
   <si>
     <t xml:space="preserve">19.1633129119873</t>
@@ -1208,10 +1208,10 @@
     <t xml:space="preserve">19.2648105621338</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4678134918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2580451965332</t>
+    <t xml:space="preserve">19.4678153991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2580471038818</t>
   </si>
   <si>
     <t xml:space="preserve">19.8602828979492</t>
@@ -1223,10 +1223,10 @@
     <t xml:space="preserve">20.0159168243408</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4204483032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5693111419678</t>
+    <t xml:space="preserve">19.4204502105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5693130493164</t>
   </si>
   <si>
     <t xml:space="preserve">19.5490131378174</t>
@@ -1238,37 +1238,37 @@
     <t xml:space="preserve">19.3663139343262</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4136829376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3527774810791</t>
+    <t xml:space="preserve">19.4136791229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3527793884277</t>
   </si>
   <si>
     <t xml:space="preserve">19.5016479492188</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9400081634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8114414215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8858776092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2783470153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1565437316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0685787200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2106781005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1091747283936</t>
+    <t xml:space="preserve">18.9400119781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8114433288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8858757019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2783451080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1565456390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0685806274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2106819152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1091804504395</t>
   </si>
   <si>
     <t xml:space="preserve">19.3189449310303</t>
@@ -1277,28 +1277,28 @@
     <t xml:space="preserve">19.3324794769287</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2309799194336</t>
+    <t xml:space="preserve">19.230978012085</t>
   </si>
   <si>
     <t xml:space="preserve">19.6572818756104</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1106510162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.982084274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7858486175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5354804992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9482479095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5760803222656</t>
+    <t xml:space="preserve">20.1106491088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9820823669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7858505249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5354824066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9482498168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5760822296143</t>
   </si>
   <si>
     <t xml:space="preserve">19.6166801452637</t>
@@ -1307,61 +1307,61 @@
     <t xml:space="preserve">19.5557804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3460121154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6911182403564</t>
+    <t xml:space="preserve">19.3460140228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6911144256592</t>
   </si>
   <si>
     <t xml:space="preserve">19.6775817871094</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2986488342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1903781890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3121795654297</t>
+    <t xml:space="preserve">19.2986469268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1903800964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.312183380127</t>
   </si>
   <si>
     <t xml:space="preserve">18.791145324707</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8182125091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.967077255249</t>
+    <t xml:space="preserve">18.8182106018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9670753479004</t>
   </si>
   <si>
     <t xml:space="preserve">18.7708435058594</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4663410186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1889038085938</t>
+    <t xml:space="preserve">18.4663429260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1889057159424</t>
   </si>
   <si>
     <t xml:space="preserve">18.6084442138672</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1497764587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1768455505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4745826721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.029447555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0835857391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5301876068115</t>
+    <t xml:space="preserve">19.1497745513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1768436431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4745788574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0294513702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0835819244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5301856994629</t>
   </si>
   <si>
     <t xml:space="preserve">20.5031204223633</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">20.8008556365967</t>
   </si>
   <si>
-    <t xml:space="preserve">20.76025390625</t>
+    <t xml:space="preserve">20.7602519989014</t>
   </si>
   <si>
     <t xml:space="preserve">20.7196559906006</t>
@@ -1382,52 +1382,52 @@
     <t xml:space="preserve">20.7061214447021</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2459869384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4083862304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3136520385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8805828094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8926429748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0550441741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0265064239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2024402618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2565727233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5813732147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5407752990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4866409301758</t>
+    <t xml:space="preserve">20.2459850311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4083843231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3136558532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8805809020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8926448822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.055046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0265045166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2024383544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2565746307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5813751220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5407733917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.486644744873</t>
   </si>
   <si>
     <t xml:space="preserve">18.4189739227295</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5272407531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.473108291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9859027862549</t>
+    <t xml:space="preserve">18.5272388458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4731063842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9859046936035</t>
   </si>
   <si>
     <t xml:space="preserve">18.4460411071777</t>
@@ -1436,64 +1436,64 @@
     <t xml:space="preserve">18.662576675415</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5678424835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7437763214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.73024559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3783760070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8505725860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7558345794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7287712097168</t>
+    <t xml:space="preserve">18.5678405761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7437782287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7302436828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3783740997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8505687713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7558364868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7287731170654</t>
   </si>
   <si>
     <t xml:space="preserve">17.9723701477051</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0671081542969</t>
+    <t xml:space="preserve">18.0671062469482</t>
   </si>
   <si>
     <t xml:space="preserve">18.1483039855957</t>
   </si>
   <si>
-    <t xml:space="preserve">18.215970993042</t>
+    <t xml:space="preserve">18.2159729003906</t>
   </si>
   <si>
     <t xml:space="preserve">18.324239730835</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3513069152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3648414611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7167110443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7979125976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.906177520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1618423461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1212368011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8235034942627</t>
+    <t xml:space="preserve">18.3513107299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.364839553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7167091369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.797908782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9061794281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1618385314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1212387084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8235054016113</t>
   </si>
   <si>
     <t xml:space="preserve">17.6205024719238</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">17.173900604248</t>
   </si>
   <si>
-    <t xml:space="preserve">17.052095413208</t>
+    <t xml:space="preserve">17.0521011352539</t>
   </si>
   <si>
     <t xml:space="preserve">16.7814311981201</t>
@@ -1514,10 +1514,10 @@
     <t xml:space="preserve">16.7600536346436</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8028106689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5605316162109</t>
+    <t xml:space="preserve">16.8028087615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.560525894165</t>
   </si>
   <si>
     <t xml:space="preserve">16.7030467987061</t>
@@ -1526,16 +1526,16 @@
     <t xml:space="preserve">16.3039970397949</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2066116333008</t>
+    <t xml:space="preserve">15.2066144943237</t>
   </si>
   <si>
     <t xml:space="preserve">14.2802505493164</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8503189086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8218154907227</t>
+    <t xml:space="preserve">14.850323677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.821816444397</t>
   </si>
   <si>
     <t xml:space="preserve">15.53440284729</t>
@@ -1547,109 +1547,109 @@
     <t xml:space="preserve">14.8930740356445</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4631490707397</t>
+    <t xml:space="preserve">15.4631443023682</t>
   </si>
   <si>
     <t xml:space="preserve">15.8336906433105</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3491315841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9477033615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8479433059692</t>
+    <t xml:space="preserve">15.3491325378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9477071762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8479442596436</t>
   </si>
   <si>
     <t xml:space="preserve">15.8621940612793</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9192018508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7054233551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7339267730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7196760177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3633842468262</t>
+    <t xml:space="preserve">15.9191999435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7054262161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7339296340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7196779251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3633813858032</t>
   </si>
   <si>
     <t xml:space="preserve">15.5059013366699</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4203882217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4488935470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9500827789307</t>
+    <t xml:space="preserve">15.4203910827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4488954544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.950080871582</t>
   </si>
   <si>
     <t xml:space="preserve">14.935830116272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1781101226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5629081726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6484155654907</t>
+    <t xml:space="preserve">15.178111076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5629072189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6484174728394</t>
   </si>
   <si>
     <t xml:space="preserve">15.890697479248</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0189628601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4346408843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3776350021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4916458129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5201539993286</t>
+    <t xml:space="preserve">16.0189609527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4346399307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3776340484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4916486740112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.52015209198</t>
   </si>
   <si>
     <t xml:space="preserve">15.7909355163574</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7766828536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6056632995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4750175476074</t>
+    <t xml:space="preserve">15.7766799926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6056661605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4750194549561</t>
   </si>
   <si>
     <t xml:space="preserve">16.2469921112061</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1329765319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4465179443359</t>
+    <t xml:space="preserve">16.1329784393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4465160369873</t>
   </si>
   <si>
     <t xml:space="preserve">16.5035228729248</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9619579315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0474681854248</t>
+    <t xml:space="preserve">15.9619569778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0474643707275</t>
   </si>
   <si>
     <t xml:space="preserve">16.2184886932373</t>
@@ -1658,82 +1658,82 @@
     <t xml:space="preserve">16.2042350769043</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1614818572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.74817943573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9049491882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2754955291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4037590026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3325004577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2636213302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0783491134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3063745498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2921237945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5486555099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6769247055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6175365447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7885570526123</t>
+    <t xml:space="preserve">16.1614837646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7481803894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9049482345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2754917144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4037628173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3325023651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2636222839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0783462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.30637550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.292121887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5486536026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6769227981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6175346374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7885589599609</t>
   </si>
   <si>
     <t xml:space="preserve">16.8598136901855</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3443737030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.387134552002</t>
+    <t xml:space="preserve">17.3443794250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3871326446533</t>
   </si>
   <si>
     <t xml:space="preserve">17.1020946502686</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8764448165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6911735534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6626682281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9643354415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7933139801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3515090942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2161159515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3372554779053</t>
+    <t xml:space="preserve">15.8764476776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6911725997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6626691818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.964337348938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7933130264282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3515110015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2161169052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3372592926025</t>
   </si>
   <si>
     <t xml:space="preserve">14.7220544815063</t>
@@ -1745,157 +1745,157 @@
     <t xml:space="preserve">14.0593481063843</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5391616821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2042446136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7268104553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3776426315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4203968048096</t>
+    <t xml:space="preserve">13.5391597747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2042436599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7268123626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3776416778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4203977584839</t>
   </si>
   <si>
     <t xml:space="preserve">12.285005569458</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4061450958252</t>
+    <t xml:space="preserve">12.4061441421509</t>
   </si>
   <si>
     <t xml:space="preserve">12.1353616714478</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3705158233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.904956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8622007369995</t>
+    <t xml:space="preserve">12.3705177307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9049549102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8622016906738</t>
   </si>
   <si>
     <t xml:space="preserve">12.9334602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1472358703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.275502204895</t>
+    <t xml:space="preserve">13.1472368240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2755002975464</t>
   </si>
   <si>
     <t xml:space="preserve">13.1187334060669</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0688514709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5462837219238</t>
+    <t xml:space="preserve">13.0688524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5462856292725</t>
   </si>
   <si>
     <t xml:space="preserve">13.1116065979004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7838153839111</t>
+    <t xml:space="preserve">12.7838163375854</t>
   </si>
   <si>
     <t xml:space="preserve">12.7339363098145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6698026657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.919207572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9548397064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2469997406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5961675643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1092281341553</t>
+    <t xml:space="preserve">12.6698045730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9192066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9548377990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.246997833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5961685180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1092290878296</t>
   </si>
   <si>
     <t xml:space="preserve">13.945333480835</t>
   </si>
   <si>
-    <t xml:space="preserve">13.881199836731</t>
+    <t xml:space="preserve">13.8812017440796</t>
   </si>
   <si>
     <t xml:space="preserve">13.8883256912231</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4655237197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2232427597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0878524780273</t>
+    <t xml:space="preserve">14.4655227661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2232437133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0878553390503</t>
   </si>
   <si>
     <t xml:space="preserve">13.3681392669678</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4679021835327</t>
+    <t xml:space="preserve">13.4679002761841</t>
   </si>
   <si>
     <t xml:space="preserve">13.1258592605591</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9690895080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.489278793335</t>
+    <t xml:space="preserve">12.969090461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4892807006836</t>
   </si>
   <si>
     <t xml:space="preserve">13.6317949295044</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2327461242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3966436386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8265724182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5344123840332</t>
+    <t xml:space="preserve">13.2327480316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3966407775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8265695571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5344114303589</t>
   </si>
   <si>
     <t xml:space="preserve">13.1044816970825</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9975910186768</t>
+    <t xml:space="preserve">12.9975938796997</t>
   </si>
   <si>
     <t xml:space="preserve">13.6104183197021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7529373168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6389217376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1448574066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3230047225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2018632888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947393417358</t>
+    <t xml:space="preserve">13.7529344558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6389226913452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1448593139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3230056762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.201865196228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947402954102</t>
   </si>
   <si>
     <t xml:space="preserve">13.8954524993896</t>
@@ -1904,43 +1904,43 @@
     <t xml:space="preserve">14.3942651748657</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5937900543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.707802772522</t>
+    <t xml:space="preserve">14.5937881469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7078008651733</t>
   </si>
   <si>
     <t xml:space="preserve">14.5082778930664</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6935520172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8075647354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6365451812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7648086547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.736307144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6793012619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.265998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5367813110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2945003509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5510320663452</t>
+    <t xml:space="preserve">14.6935548782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8075637817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.636547088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7648067474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7363052368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6792984008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2659978866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5367822647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2944984436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5510339736938</t>
   </si>
   <si>
     <t xml:space="preserve">15.192361831665</t>
@@ -1952,31 +1952,31 @@
     <t xml:space="preserve">15.2778730392456</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2493686676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2208662033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.406138420105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8194417953491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8051872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6341648101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5914115905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4322605133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6032848358154</t>
+    <t xml:space="preserve">15.2493677139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2208652496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4061403274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8194408416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8051853179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6341676712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5914106369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4322662353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6032867431641</t>
   </si>
   <si>
     <t xml:space="preserve">16.7172985076904</t>
@@ -1985,46 +1985,46 @@
     <t xml:space="preserve">16.7743053436279</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8170604705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0308380126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1591053009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2588653564453</t>
+    <t xml:space="preserve">16.8170623779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0308361053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1591014862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2588634490967</t>
   </si>
   <si>
     <t xml:space="preserve">17.3158702850342</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4583911895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4726428985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9714527130127</t>
+    <t xml:space="preserve">17.4583892822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4726390838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9714546203613</t>
   </si>
   <si>
     <t xml:space="preserve">17.7861785888672</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9286994934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0569629669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0854644775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5581493377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5866546630859</t>
+    <t xml:space="preserve">17.9286956787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0569610595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0854663848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5581512451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5866565704346</t>
   </si>
   <si>
     <t xml:space="preserve">17.2018566131592</t>
@@ -2033,13 +2033,13 @@
     <t xml:space="preserve">17.4298858642578</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5296497344971</t>
+    <t xml:space="preserve">17.5296478271484</t>
   </si>
   <si>
     <t xml:space="preserve">17.4868927001953</t>
   </si>
   <si>
-    <t xml:space="preserve">17.719654083252</t>
+    <t xml:space="preserve">17.7196521759033</t>
   </si>
   <si>
     <t xml:space="preserve">17.8548011779785</t>
@@ -2054,10 +2054,10 @@
     <t xml:space="preserve">17.2691516876221</t>
   </si>
   <si>
-    <t xml:space="preserve">17.149019241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7435684204102</t>
+    <t xml:space="preserve">17.1490173339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7435665130615</t>
   </si>
   <si>
     <t xml:space="preserve">16.8787174224854</t>
@@ -2066,22 +2066,22 @@
     <t xml:space="preserve">16.9237689971924</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6985168457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2541332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5394515991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1640338897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0589160919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4343357086182</t>
+    <t xml:space="preserve">16.6985206604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2541351318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5394496917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1640357971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0589179992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4343318939209</t>
   </si>
   <si>
     <t xml:space="preserve">17.8247661590576</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">17.9298839569092</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8397846221924</t>
+    <t xml:space="preserve">17.839786529541</t>
   </si>
   <si>
     <t xml:space="preserve">17.7496852874756</t>
@@ -2099,13 +2099,13 @@
     <t xml:space="preserve">17.9448986053467</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6656970977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8459014892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1762676239014</t>
+    <t xml:space="preserve">18.6657009124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8458995819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1762657165527</t>
   </si>
   <si>
     <t xml:space="preserve">19.3714828491211</t>
@@ -2120,25 +2120,25 @@
     <t xml:space="preserve">19.4165325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1462345123291</t>
+    <t xml:space="preserve">19.1462306976318</t>
   </si>
   <si>
     <t xml:space="preserve">19.0110836029053</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2213153839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7318840026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7769336700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7919483184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8069667816162</t>
+    <t xml:space="preserve">19.2213172912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7318820953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7769317626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7919502258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8069648742676</t>
   </si>
   <si>
     <t xml:space="preserve">20.0772647857666</t>
@@ -2150,40 +2150,40 @@
     <t xml:space="preserve">20.2574653625488</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1373310089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1823825836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8970680236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.047233581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1523494720459</t>
+    <t xml:space="preserve">20.1373329162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1823806762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.897066116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0472297668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1523475646973</t>
   </si>
   <si>
     <t xml:space="preserve">20.0171985626221</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6567974090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.821985244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6868324279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8370018005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9421157836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3325481414795</t>
+    <t xml:space="preserve">19.6568012237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8219833374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6868343353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8369979858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9421138763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3325462341309</t>
   </si>
   <si>
     <t xml:space="preserve">19.581714630127</t>
@@ -2198,52 +2198,52 @@
     <t xml:space="preserve">19.7168655395508</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7619171142578</t>
+    <t xml:space="preserve">19.7619152069092</t>
   </si>
   <si>
     <t xml:space="preserve">20.2874984741211</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9120864868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1223163604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0622482299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3025150299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5728168487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6629180908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9932804107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1434459686279</t>
+    <t xml:space="preserve">19.9120845794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1223182678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0622501373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3025169372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5728130340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6629161834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9932823181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1434497833252</t>
   </si>
   <si>
     <t xml:space="preserve">21.1584663391113</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3536834716797</t>
+    <t xml:space="preserve">21.3536796569824</t>
   </si>
   <si>
     <t xml:space="preserve">21.0082988739014</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2635803222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2936153411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4287643432617</t>
+    <t xml:space="preserve">21.2635822296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2936115264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4287662506104</t>
   </si>
   <si>
     <t xml:space="preserve">21.6089649200439</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">21.5338821411133</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9782638549805</t>
+    <t xml:space="preserve">20.9782657623291</t>
   </si>
   <si>
     <t xml:space="preserve">20.8881664276123</t>
@@ -2261,16 +2261,16 @@
     <t xml:space="preserve">21.233549118042</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2485656738281</t>
+    <t xml:space="preserve">21.2485618591309</t>
   </si>
   <si>
     <t xml:space="preserve">21.1734828948975</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6478996276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6328811645508</t>
+    <t xml:space="preserve">20.6478977203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6328830718994</t>
   </si>
   <si>
     <t xml:space="preserve">20.7680320739746</t>
@@ -2279,67 +2279,67 @@
     <t xml:space="preserve">21.0833797454834</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7980670928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8670310974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7229824066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2035121917725</t>
+    <t xml:space="preserve">20.7980651855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8670330047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7229804992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2035179138184</t>
   </si>
   <si>
     <t xml:space="preserve">21.3086318969727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4888324737549</t>
+    <t xml:space="preserve">21.4888305664062</t>
   </si>
   <si>
     <t xml:space="preserve">21.5639133453369</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1134147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3837146759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3236484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5789318084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8191947937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8492298126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.954345703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5850448608398</t>
+    <t xml:space="preserve">21.1134166717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3837127685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3236465454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.578929901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8191967010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8492317199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9543495178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5850467681885</t>
   </si>
   <si>
     <t xml:space="preserve">22.4799308776855</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6601314544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1256465911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3208618164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0805969238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2007293701172</t>
+    <t xml:space="preserve">22.6601295471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1256446838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3208637237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0805988311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2007274627686</t>
   </si>
   <si>
     <t xml:space="preserve">23.3058471679688</t>
@@ -2348,13 +2348,13 @@
     <t xml:space="preserve">23.4259796142578</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6962795257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9215278625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7263126373291</t>
+    <t xml:space="preserve">23.6962776184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9215297698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7263107299805</t>
   </si>
   <si>
     <t xml:space="preserve">23.6662483215332</t>
@@ -2366,52 +2366,52 @@
     <t xml:space="preserve">23.2908306121826</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3959465026855</t>
+    <t xml:space="preserve">23.3959445953369</t>
   </si>
   <si>
     <t xml:space="preserve">23.2758140563965</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0956153869629</t>
+    <t xml:space="preserve">23.0956134796143</t>
   </si>
   <si>
     <t xml:space="preserve">22.494945526123</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6300945281982</t>
+    <t xml:space="preserve">22.6300964355469</t>
   </si>
   <si>
     <t xml:space="preserve">22.5249805450439</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0355472564697</t>
+    <t xml:space="preserve">23.0355453491211</t>
   </si>
   <si>
     <t xml:space="preserve">22.9454460144043</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5399971008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6000633239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6451110839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7352123260498</t>
+    <t xml:space="preserve">22.5399990081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.600061416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.645112991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7352142333984</t>
   </si>
   <si>
     <t xml:space="preserve">22.2096309661865</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1946125030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.104513168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1795959472656</t>
+    <t xml:space="preserve">22.194616317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1045169830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1795978546143</t>
   </si>
   <si>
     <t xml:space="preserve">21.7290992736816</t>
@@ -2420,52 +2420,52 @@
     <t xml:space="preserve">22.0594635009766</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7441139221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5939483642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2785968780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0294303894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7652492523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7051792144775</t>
+    <t xml:space="preserve">21.7441120147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5939464569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2785987854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0294284820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7652473449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7051811218262</t>
   </si>
   <si>
     <t xml:space="preserve">22.99049949646</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9754810333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8102970123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8253135681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0744819641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8853816986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1645812988281</t>
+    <t xml:space="preserve">22.9754829406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8102951049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8253154754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0744800567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8853797912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1645793914795</t>
   </si>
   <si>
     <t xml:space="preserve">22.299732208252</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8553447723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.795280456543</t>
+    <t xml:space="preserve">22.8553485870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7952823638916</t>
   </si>
   <si>
     <t xml:space="preserve">23.3508968353271</t>
@@ -2474,10 +2474,10 @@
     <t xml:space="preserve">24.1017265319824</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4471111297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4170799255371</t>
+    <t xml:space="preserve">24.447114944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4170780181885</t>
   </si>
   <si>
     <t xml:space="preserve">24.67236328125</t>
@@ -2486,22 +2486,22 @@
     <t xml:space="preserve">24.6573467254639</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7774791717529</t>
+    <t xml:space="preserve">24.7774772644043</t>
   </si>
   <si>
     <t xml:space="preserve">24.3269805908203</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8764801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2396640777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9181976318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4226474761963</t>
+    <t xml:space="preserve">23.8764781951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2396659851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9181995391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4226512908936</t>
   </si>
   <si>
     <t xml:space="preserve">20.4827156066895</t>
@@ -2510,40 +2510,40 @@
     <t xml:space="preserve">19.0411186218262</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5906162261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9688186645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8876209259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7975177764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6201057434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6937942504883</t>
+    <t xml:space="preserve">18.5906181335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9688205718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8876180648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7975215911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6201038360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6937952041626</t>
   </si>
   <si>
     <t xml:space="preserve">13.2146549224854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.989405632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6590375900269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0344562530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7266149520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8917961120605</t>
+    <t xml:space="preserve">12.9894037246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6590394973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0344572067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7266139984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8917980194092</t>
   </si>
   <si>
     <t xml:space="preserve">13.905421257019</t>
@@ -2555,97 +2555,97 @@
     <t xml:space="preserve">14.5811710357666</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0781126022339</t>
+    <t xml:space="preserve">14.0781116485596</t>
   </si>
   <si>
     <t xml:space="preserve">14.3559217453003</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1982460021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3183813095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0555849075317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7688798904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4671535491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7886199951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7074184417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9026355743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9326705932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.767484664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1518058776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3770542144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4821710586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6834983825684</t>
+    <t xml:space="preserve">14.1982450485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.318380355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0555877685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7688789367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.46715259552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7886180877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7074203491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9026374816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.932671546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7674894332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1518030166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3770532608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4821729660034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6835021972656</t>
   </si>
   <si>
     <t xml:space="preserve">16.8937358856201</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3442363739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0138702392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.533332824707</t>
+    <t xml:space="preserve">17.3442344665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0138683319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5333366394043</t>
   </si>
   <si>
     <t xml:space="preserve">16.5033016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9087524414062</t>
+    <t xml:space="preserve">16.9087505340576</t>
   </si>
   <si>
     <t xml:space="preserve">17.4643688201904</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1039695739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5244331359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1189861297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2391166687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1339988708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3892860412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4043006896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6896190643311</t>
+    <t xml:space="preserve">17.103967666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5244369506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1189842224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2391204833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1340045928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3892822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4043025970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6896171569824</t>
   </si>
   <si>
     <t xml:space="preserve">18.3653678894043</t>
@@ -2654,19 +2654,19 @@
     <t xml:space="preserve">18.2902851104736</t>
   </si>
   <si>
-    <t xml:space="preserve">18.485502243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9510135650635</t>
+    <t xml:space="preserve">18.4855003356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9510173797607</t>
   </si>
   <si>
     <t xml:space="preserve">19.2813835144043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8520126342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3414516448975</t>
+    <t xml:space="preserve">19.8520183563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3414497375488</t>
   </si>
   <si>
     <t xml:space="preserve">19.551685333252</t>
@@ -2675,31 +2675,31 @@
     <t xml:space="preserve">18.3953990936279</t>
   </si>
   <si>
-    <t xml:space="preserve">19.431547164917</t>
+    <t xml:space="preserve">19.4315509796143</t>
   </si>
   <si>
     <t xml:space="preserve">20.167366027832</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3264331817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9571323394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1072998046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6779327392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2663688659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5066299438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8820514678955</t>
+    <t xml:space="preserve">19.3264350891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9571342468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1073017120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6779308319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2663669586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5066318511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8820476531982</t>
   </si>
   <si>
     <t xml:space="preserve">20.0922832489014</t>
@@ -2708,64 +2708,64 @@
     <t xml:space="preserve">20.3475646972656</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3775978088379</t>
+    <t xml:space="preserve">20.3775997161865</t>
   </si>
   <si>
     <t xml:space="preserve">19.5967350006104</t>
   </si>
   <si>
-    <t xml:space="preserve">18.710750579834</t>
+    <t xml:space="preserve">18.7107524871826</t>
   </si>
   <si>
     <t xml:space="preserve">18.9209842681885</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7708148956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8308849334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5666961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0861682891846</t>
+    <t xml:space="preserve">18.7708168029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.830883026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5666999816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0861663818359</t>
   </si>
   <si>
     <t xml:space="preserve">18.9059677124023</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0711479187012</t>
+    <t xml:space="preserve">19.0711517333984</t>
   </si>
   <si>
     <t xml:space="preserve">18.7558002471924</t>
   </si>
   <si>
-    <t xml:space="preserve">19.476598739624</t>
+    <t xml:space="preserve">19.4765968322754</t>
   </si>
   <si>
     <t xml:space="preserve">19.2964000701904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5366687774658</t>
+    <t xml:space="preserve">19.5366668701172</t>
   </si>
   <si>
     <t xml:space="preserve">19.5216503143311</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3114166259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9810523986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4526824951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6178665161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6117515563965</t>
+    <t xml:space="preserve">19.3114147186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9810485839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4526805877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6178646087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6117477416992</t>
   </si>
   <si>
     <t xml:space="preserve">20.3625831604004</t>
@@ -2774,10 +2774,10 @@
     <t xml:space="preserve">19.6417808532715</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0322170257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5127506256104</t>
+    <t xml:space="preserve">20.0322151184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5127468109131</t>
   </si>
   <si>
     <t xml:space="preserve">20.2424468994141</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">20.7379989624023</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0021820068359</t>
+    <t xml:space="preserve">20.0021839141846</t>
   </si>
   <si>
     <t xml:space="preserve">18.2152004241943</t>
@@ -2795,10 +2795,10 @@
     <t xml:space="preserve">18.1401176452637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3203163146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5577964782715</t>
+    <t xml:space="preserve">18.3203182220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5577983856201</t>
   </si>
   <si>
     <t xml:space="preserve">20.4376659393311</t>
@@ -2810,10 +2810,10 @@
     <t xml:space="preserve">20.7830486297607</t>
   </si>
   <si>
-    <t xml:space="preserve">20.497730255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0233154296875</t>
+    <t xml:space="preserve">20.4977283477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0233135223389</t>
   </si>
   <si>
     <t xml:space="preserve">21.4137496948242</t>
@@ -2822,85 +2822,85 @@
     <t xml:space="preserve">21.3686981201172</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9031848907471</t>
+    <t xml:space="preserve">20.9031829833984</t>
   </si>
   <si>
     <t xml:space="preserve">21.0383319854736</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4076309204102</t>
+    <t xml:space="preserve">20.4076328277588</t>
   </si>
   <si>
     <t xml:space="preserve">20.5427837371826</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3175315856934</t>
+    <t xml:space="preserve">20.317533493042</t>
   </si>
   <si>
     <t xml:space="preserve">20.2124137878418</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4465656280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7468967437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2363338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5277633666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7140827178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6840496063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6389999389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3386650085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6239833831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8642482757568</t>
+    <t xml:space="preserve">19.4465637207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7469005584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2363357543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5277652740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7140789031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.684045791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6389980316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3386669158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6239814758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8642463684082</t>
   </si>
   <si>
     <t xml:space="preserve">21.3987312316895</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4437808990479</t>
+    <t xml:space="preserve">21.4437828063965</t>
   </si>
   <si>
     <t xml:space="preserve">21.188497543335</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9092979431152</t>
+    <t xml:space="preserve">21.9092960357666</t>
   </si>
   <si>
     <t xml:space="preserve">21.8942794799805</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8342132568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5038452148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2546806335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0444469451904</t>
+    <t xml:space="preserve">21.8342151641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.503849029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2546825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0444488525391</t>
   </si>
   <si>
     <t xml:space="preserve">22.2847118377686</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3447818756104</t>
+    <t xml:space="preserve">22.3447799682617</t>
   </si>
   <si>
     <t xml:space="preserve">22.464916229248</t>
@@ -2909,121 +2909,121 @@
     <t xml:space="preserve">22.6901626586914</t>
   </si>
   <si>
-    <t xml:space="preserve">22.870361328125</t>
+    <t xml:space="preserve">22.8703632354736</t>
   </si>
   <si>
     <t xml:space="preserve">22.6150817871094</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5700283050537</t>
+    <t xml:space="preserve">22.5700302124023</t>
   </si>
   <si>
     <t xml:space="preserve">22.6751480102539</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5775375366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9079074859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0430545806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0881023406982</t>
+    <t xml:space="preserve">22.5775394439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9079055786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0430564880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0881042480469</t>
   </si>
   <si>
     <t xml:space="preserve">22.8178043365479</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8403282165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1706981658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2157459259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.380931854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5235900878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0505657196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9154148101807</t>
+    <t xml:space="preserve">22.8403301239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1706962585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.215747833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3809299468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.523588180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0505638122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.915412902832</t>
   </si>
   <si>
     <t xml:space="preserve">23.0730876922607</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2532920837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3433876037598</t>
+    <t xml:space="preserve">23.2532863616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3433895111084</t>
   </si>
   <si>
     <t xml:space="preserve">23.29833984375</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8914966583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2594051361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0942211151123</t>
+    <t xml:space="preserve">23.8914985656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.259407043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0942230224609</t>
   </si>
   <si>
     <t xml:space="preserve">24.664852142334</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5522308349609</t>
+    <t xml:space="preserve">24.5522289276123</t>
   </si>
   <si>
     <t xml:space="preserve">24.4621295928955</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7924976348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4020614624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0491714477539</t>
+    <t xml:space="preserve">24.7924957275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4020595550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0491695404053</t>
   </si>
   <si>
     <t xml:space="preserve">24.4696369171143</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4245853424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1993350982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9590721130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1617984771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2293701171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6273097991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8075122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8150196075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1078395843506</t>
+    <t xml:space="preserve">24.4245891571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1993370056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9590702056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1617946624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2293720245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6273136138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8075141906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8150215148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1078414916992</t>
   </si>
   <si>
     <t xml:space="preserve">25.2204704284668</t>
@@ -3032,79 +3032,79 @@
     <t xml:space="preserve">25.1003360748291</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1829299926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2955532073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5208034515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8286437988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8061141967773</t>
+    <t xml:space="preserve">25.1829280853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2955493927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5208015441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8286457061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8061180114746</t>
   </si>
   <si>
     <t xml:space="preserve">25.7385425567627</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7835922241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0538921356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8661842346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4893779754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5119037628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3767509460449</t>
+    <t xml:space="preserve">25.7835960388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0538959503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8661861419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.489372253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5119018554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3767528533936</t>
   </si>
   <si>
     <t xml:space="preserve">26.466854095459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6545600891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5869827270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1050567626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5180168151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1350955963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3903694152832</t>
+    <t xml:space="preserve">26.6545543670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.586986541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1050605773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5180187225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1350917816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3903770446777</t>
   </si>
   <si>
     <t xml:space="preserve">27.0149593353271</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0374851226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2176837921143</t>
+    <t xml:space="preserve">27.037483215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2176876068115</t>
   </si>
   <si>
     <t xml:space="preserve">27.1951580047607</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2251892089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2566223144531</t>
+    <t xml:space="preserve">27.225191116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2566184997559</t>
   </si>
   <si>
     <t xml:space="preserve">26.6845951080322</t>
@@ -3113,25 +3113,25 @@
     <t xml:space="preserve">27.1726341247559</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0299797058105</t>
+    <t xml:space="preserve">27.029972076416</t>
   </si>
   <si>
     <t xml:space="preserve">26.7446594238281</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6245231628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8962173461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0163516998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3992786407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3542251586914</t>
+    <t xml:space="preserve">26.6245269775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8962230682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0163555145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3992767333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.35422706604</t>
   </si>
   <si>
     <t xml:space="preserve">26.5569496154785</t>
@@ -3140,43 +3140,43 @@
     <t xml:space="preserve">26.0013370513916</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0238609313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4218063354492</t>
+    <t xml:space="preserve">26.0238571166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.421802520752</t>
   </si>
   <si>
     <t xml:space="preserve">26.2866477966309</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2115688323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8873195648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1125736236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3603420257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3828678131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6456565856934</t>
+    <t xml:space="preserve">26.2115726470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8873176574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.11256980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3603382110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.382869720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6456604003906</t>
   </si>
   <si>
     <t xml:space="preserve">27.6231346130371</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7808074951172</t>
+    <t xml:space="preserve">27.7808132171631</t>
   </si>
   <si>
     <t xml:space="preserve">27.5931015014648</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4204082489014</t>
+    <t xml:space="preserve">27.42041015625</t>
   </si>
   <si>
     <t xml:space="preserve">27.5630664825439</t>
@@ -3185,70 +3185,70 @@
     <t xml:space="preserve">27.7883148193359</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7132301330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9535007476807</t>
+    <t xml:space="preserve">27.7132396697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.953498840332</t>
   </si>
   <si>
     <t xml:space="preserve">27.9835376739502</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2613430023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1412086486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2087821960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.18625831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3814754486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2012748718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.058614730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1186809539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4115047454834</t>
+    <t xml:space="preserve">28.261344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1412105560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2087841033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1862602233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3814735412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2012805938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0586166381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1186828613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4115104675293</t>
   </si>
   <si>
     <t xml:space="preserve">29.169849395752</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3875885009766</t>
+    <t xml:space="preserve">29.3875904083252</t>
   </si>
   <si>
     <t xml:space="preserve">29.5077247619629</t>
   </si>
   <si>
-    <t xml:space="preserve">29.289981842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9145641326904</t>
+    <t xml:space="preserve">29.2899780273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9145698547363</t>
   </si>
   <si>
     <t xml:space="preserve">28.4190158843994</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6442680358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1923751831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1323108673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.214900970459</t>
+    <t xml:space="preserve">28.64426612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1923770904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1323127746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2148971557617</t>
   </si>
   <si>
     <t xml:space="preserve">28.5842018127441</t>
@@ -3263,112 +3263,112 @@
     <t xml:space="preserve">28.5466594696045</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4640693664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.87841796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4715728759766</t>
+    <t xml:space="preserve">28.4640636444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8784217834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4715709686279</t>
   </si>
   <si>
     <t xml:space="preserve">28.4040012359619</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0736351013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3964920043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.02858543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7643985748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6954288482666</t>
+    <t xml:space="preserve">28.0736293792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3964900970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0285873413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7644023895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6954307556152</t>
   </si>
   <si>
     <t xml:space="preserve">29.7179584503174</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9432048797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.401216506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7240734100342</t>
+    <t xml:space="preserve">29.9432067871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4012184143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7240753173828</t>
   </si>
   <si>
     <t xml:space="preserve">30.5213489532471</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6940402984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5288524627686</t>
+    <t xml:space="preserve">30.6940383911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5288581848145</t>
   </si>
   <si>
     <t xml:space="preserve">30.7090549468994</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4988193511963</t>
+    <t xml:space="preserve">30.4988231658936</t>
   </si>
   <si>
     <t xml:space="preserve">30.77663230896</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7602233886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2107276916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4359703063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7376976013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1506576538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3083343505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3458709716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8728485107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1370334625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8592166900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0544452667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4641075134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2591972351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0342864990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.640682220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8052787780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1265850067139</t>
+    <t xml:space="preserve">31.7602252960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2107238769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4359741210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7377014160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1506538391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3083229064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.345874786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8728446960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1370315551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8592205047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0544395446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4641036987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2591991424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0342826843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6406841278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8052845001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1265869140625</t>
   </si>
   <si>
     <t xml:space="preserve">29.0864238739014</t>
@@ -3377,34 +3377,34 @@
     <t xml:space="preserve">30.0583820343018</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9378967285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1146144866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5885448455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3596801757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3195152282715</t>
+    <t xml:space="preserve">29.937894821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.114616394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5885429382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3596820831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3195209503174</t>
   </si>
   <si>
     <t xml:space="preserve">31.0303382873535</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1508369445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3355827331543</t>
+    <t xml:space="preserve">31.1508312225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.335578918457</t>
   </si>
   <si>
     <t xml:space="preserve">31.2632884979248</t>
   </si>
   <si>
-    <t xml:space="preserve">31.166898727417</t>
+    <t xml:space="preserve">31.1669006347656</t>
   </si>
   <si>
     <t xml:space="preserve">31.1187000274658</t>
@@ -3416,31 +3416,31 @@
     <t xml:space="preserve">29.7531414031982</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4118270874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5644416809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5483741760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9419841766357</t>
+    <t xml:space="preserve">30.4118251800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5644435882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.548376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9419803619385</t>
   </si>
   <si>
     <t xml:space="preserve">31.2713203430176</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1829586029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1267318725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2150917053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2311592102051</t>
+    <t xml:space="preserve">31.1829605102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1267337799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2150955200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2311611175537</t>
   </si>
   <si>
     <t xml:space="preserve">31.1909942626953</t>
@@ -3449,49 +3449,49 @@
     <t xml:space="preserve">30.4359188079834</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2029781341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1788730621338</t>
+    <t xml:space="preserve">30.2029685974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1788749694824</t>
   </si>
   <si>
     <t xml:space="preserve">30.8375549316406</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8616523742676</t>
+    <t xml:space="preserve">30.8616504669189</t>
   </si>
   <si>
     <t xml:space="preserve">30.5082149505615</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3475570678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2913303375244</t>
+    <t xml:space="preserve">30.3475646972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.291332244873</t>
   </si>
   <si>
     <t xml:space="preserve">29.4800319671631</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8856086730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3997039794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9338035583496</t>
+    <t xml:space="preserve">28.8856048583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3997001647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9338054656982</t>
   </si>
   <si>
     <t xml:space="preserve">27.7208633422852</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1907062530518</t>
+    <t xml:space="preserve">27.1907043457031</t>
   </si>
   <si>
     <t xml:space="preserve">27.6807022094727</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9939746856689</t>
+    <t xml:space="preserve">27.9939765930176</t>
   </si>
   <si>
     <t xml:space="preserve">28.0743083953857</t>
@@ -3500,88 +3500,88 @@
     <t xml:space="preserve">28.5803661346436</t>
   </si>
   <si>
-    <t xml:space="preserve">28.965934753418</t>
+    <t xml:space="preserve">28.9659366607666</t>
   </si>
   <si>
     <t xml:space="preserve">29.0783939361572</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8695430755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8374137878418</t>
+    <t xml:space="preserve">28.8695449829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8374118804932</t>
   </si>
   <si>
     <t xml:space="preserve">28.8133144378662</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6285591125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3595371246338</t>
+    <t xml:space="preserve">28.6285648345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3595352172852</t>
   </si>
   <si>
     <t xml:space="preserve">29.0944576263428</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9578990936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3152866363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1587219238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3675746917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8936424255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8026962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2799053192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4106025695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9600028991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9974212646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9810810089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9028205871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9273281097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3228492736816</t>
+    <t xml:space="preserve">28.9579029083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3152885437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1587200164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3675708770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8936443328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.802698135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2799015045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4105987548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9600067138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9974250793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9810848236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9028244018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9273300170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.322847366333</t>
   </si>
   <si>
     <t xml:space="preserve">23.3623714447021</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8885898590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5175743103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3963680267334</t>
+    <t xml:space="preserve">22.8885879516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5175762176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3963661193848</t>
   </si>
   <si>
     <t xml:space="preserve">24.7101993560791</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3065090179443</t>
+    <t xml:space="preserve">25.3065128326416</t>
   </si>
   <si>
     <t xml:space="preserve">25.7231121063232</t>
@@ -3593,22 +3593,22 @@
     <t xml:space="preserve">27.1281204223633</t>
   </si>
   <si>
-    <t xml:space="preserve">26.956579208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.144458770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7768688201904</t>
+    <t xml:space="preserve">26.9565811157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1444568634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7768707275391</t>
   </si>
   <si>
     <t xml:space="preserve">27.1036167144775</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0709438323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9892559051514</t>
+    <t xml:space="preserve">27.0709400177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9892578125</t>
   </si>
   <si>
     <t xml:space="preserve">27.0300979614258</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">27.3486766815186</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1328659057617</t>
+    <t xml:space="preserve">28.1328639984131</t>
   </si>
   <si>
     <t xml:space="preserve">27.904146194458</t>
@@ -3626,34 +3626,34 @@
     <t xml:space="preserve">27.5447235107422</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9776630401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5937347412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5481472015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7523612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8830604553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8667221069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5399780273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4991321563721</t>
+    <t xml:space="preserve">27.9776611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5937366485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5481433868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7523632049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8830642700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8667278289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5399799346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4991340637207</t>
   </si>
   <si>
     <t xml:space="preserve">26.3439292907715</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6414260864258</t>
+    <t xml:space="preserve">25.6414241790771</t>
   </si>
   <si>
     <t xml:space="preserve">26.2377376556396</t>
@@ -3662,61 +3662,61 @@
     <t xml:space="preserve">26.3520965576172</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1152076721191</t>
+    <t xml:space="preserve">26.1152057647705</t>
   </si>
   <si>
     <t xml:space="preserve">25.9109916687012</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3146800994873</t>
+    <t xml:space="preserve">25.3146781921387</t>
   </si>
   <si>
     <t xml:space="preserve">25.3310165405273</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2738361358643</t>
+    <t xml:space="preserve">25.2738342285156</t>
   </si>
   <si>
     <t xml:space="preserve">25.6740989685059</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8048000335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.355525970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9634246826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9913539886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3017654418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8374729156494</t>
+    <t xml:space="preserve">25.8047981262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3555240631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9634265899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9913578033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3017673492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.837474822998</t>
   </si>
   <si>
     <t xml:space="preserve">26.3766059875488</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4256172180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5154724121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4419536590576</t>
+    <t xml:space="preserve">26.4256153106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5154705047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.441951751709</t>
   </si>
   <si>
     <t xml:space="preserve">26.6380023956299</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5073013305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5489635467529</t>
+    <t xml:space="preserve">26.507303237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5489673614502</t>
   </si>
   <si>
     <t xml:space="preserve">26.7698364257812</t>
@@ -3725,22 +3725,22 @@
     <t xml:space="preserve">26.4734268188477</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5743713378906</t>
+    <t xml:space="preserve">27.5743732452393</t>
   </si>
   <si>
     <t xml:space="preserve">27.6759967803955</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9639320373535</t>
+    <t xml:space="preserve">27.9639339447021</t>
   </si>
   <si>
     <t xml:space="preserve">27.5828399658203</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3457164764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5235576629639</t>
+    <t xml:space="preserve">27.3457107543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5235557556152</t>
   </si>
   <si>
     <t xml:space="preserve">26.7274913787842</t>
@@ -3755,40 +3755,40 @@
     <t xml:space="preserve">26.2108955383301</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5164546966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3992576599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8149108886719</t>
+    <t xml:space="preserve">25.5164566040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3992595672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8149127960205</t>
   </si>
   <si>
     <t xml:space="preserve">23.348445892334</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9751358032227</t>
+    <t xml:space="preserve">23.9751319885254</t>
   </si>
   <si>
     <t xml:space="preserve">22.9250049591064</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4161949157715</t>
+    <t xml:space="preserve">23.4161968231201</t>
   </si>
   <si>
     <t xml:space="preserve">23.5686340332031</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3569164276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0859127044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8904495239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6194477081299</t>
+    <t xml:space="preserve">23.3569145202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0859146118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8904476165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6194458007812</t>
   </si>
   <si>
     <t xml:space="preserve">23.5093536376953</t>
@@ -3800,16 +3800,16 @@
     <t xml:space="preserve">22.8318481445312</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7471599578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7132873535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.64621925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9510974884033</t>
+    <t xml:space="preserve">22.7471618652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.713285446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6462211608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9510955810547</t>
   </si>
   <si>
     <t xml:space="preserve">22.2644424438477</t>
@@ -3827,19 +3827,19 @@
     <t xml:space="preserve">22.222095489502</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3074684143066</t>
+    <t xml:space="preserve">21.307466506958</t>
   </si>
   <si>
     <t xml:space="preserve">21.7563152313232</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2898502349854</t>
+    <t xml:space="preserve">22.2898445129395</t>
   </si>
   <si>
     <t xml:space="preserve">23.052038192749</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0351009368896</t>
+    <t xml:space="preserve">23.0351028442383</t>
   </si>
   <si>
     <t xml:space="preserve">22.5185050964355</t>
@@ -3857,25 +3857,25 @@
     <t xml:space="preserve">23.1536617279053</t>
   </si>
   <si>
-    <t xml:space="preserve">23.966667175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0513572692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9327945709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4239807128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5256061553955</t>
+    <t xml:space="preserve">23.9666652679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0513553619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9327907562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.423978805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5256080627441</t>
   </si>
   <si>
     <t xml:space="preserve">23.9497299194336</t>
   </si>
   <si>
-    <t xml:space="preserve">23.856575012207</t>
+    <t xml:space="preserve">23.8565731048584</t>
   </si>
   <si>
     <t xml:space="preserve">23.4416027069092</t>
@@ -3884,22 +3884,22 @@
     <t xml:space="preserve">23.7888240814209</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1275749206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1360416412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.500883102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7380123138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0774440765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5354442596436</t>
+    <t xml:space="preserve">24.1275730133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1360454559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5008850097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7380104064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0774421691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5354423522949</t>
   </si>
   <si>
     <t xml:space="preserve">22.9334735870361</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">22.7725677490234</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0950660705566</t>
+    <t xml:space="preserve">22.095064163208</t>
   </si>
   <si>
     <t xml:space="preserve">22.0273151397705</t>
@@ -3923,31 +3923,31 @@
     <t xml:space="preserve">21.9256896972656</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2390365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3237247467041</t>
+    <t xml:space="preserve">22.23903465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3237209320068</t>
   </si>
   <si>
     <t xml:space="preserve">22.4422855377197</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0689735412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9243240356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3907909393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9419441223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6455383300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7302227020264</t>
+    <t xml:space="preserve">23.0689754486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9243221282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3907890319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9419422149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6455364227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.730224609375</t>
   </si>
   <si>
     <t xml:space="preserve">21.3921566009521</t>
@@ -3959,7 +3959,7 @@
     <t xml:space="preserve">21.3413429260254</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7908706665039</t>
+    <t xml:space="preserve">20.7908725738525</t>
   </si>
   <si>
     <t xml:space="preserve">21.0957489013672</t>
@@ -3968,16 +3968,16 @@
     <t xml:space="preserve">20.6553707122803</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8078098297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3335609436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2207317352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2552852630615</t>
+    <t xml:space="preserve">20.8078117370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3335552215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2207336425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2552890777588</t>
   </si>
   <si>
     <t xml:space="preserve">24.0344181060791</t>
@@ -3986,70 +3986,70 @@
     <t xml:space="preserve">23.4246635437012</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7979755401611</t>
+    <t xml:space="preserve">22.7979736328125</t>
   </si>
   <si>
     <t xml:space="preserve">23.4331340789795</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6533222198486</t>
+    <t xml:space="preserve">23.6533203125</t>
   </si>
   <si>
     <t xml:space="preserve">24.0174808502197</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3308277130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3477630615234</t>
+    <t xml:space="preserve">24.3308258056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3477649688721</t>
   </si>
   <si>
     <t xml:space="preserve">24.2037944793701</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7966079711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1438312530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8297996520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9737701416016</t>
+    <t xml:space="preserve">24.79660987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1438274383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8298015594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9737720489502</t>
   </si>
   <si>
     <t xml:space="preserve">26.2871170043945</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3802700042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6265506744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7197093963623</t>
+    <t xml:space="preserve">26.3802719116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6265487670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.719705581665</t>
   </si>
   <si>
     <t xml:space="preserve">25.6858310699463</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3294563293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3118381500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9307441711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9053363800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1756534576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.226469039917</t>
+    <t xml:space="preserve">26.3294582366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3118362426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9307422637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9053382873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1756553649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2264671325684</t>
   </si>
   <si>
     <t xml:space="preserve">28.074031829834</t>
@@ -4058,13 +4058,13 @@
     <t xml:space="preserve">28.4551219940186</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2434062957764</t>
+    <t xml:space="preserve">28.2434043884277</t>
   </si>
   <si>
     <t xml:space="preserve">28.1163711547852</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3111534118652</t>
+    <t xml:space="preserve">28.3111553192139</t>
   </si>
   <si>
     <t xml:space="preserve">28.1671848297119</t>
@@ -4076,10 +4076,10 @@
     <t xml:space="preserve">28.7091884613037</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1848068237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2779655456543</t>
+    <t xml:space="preserve">27.1848049163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2779636383057</t>
   </si>
   <si>
     <t xml:space="preserve">27.0069618225098</t>
@@ -4088,7 +4088,7 @@
     <t xml:space="preserve">26.947681427002</t>
   </si>
   <si>
-    <t xml:space="preserve">27.286434173584</t>
+    <t xml:space="preserve">27.2864322662354</t>
   </si>
   <si>
     <t xml:space="preserve">27.0238990783691</t>
@@ -4112,16 +4112,16 @@
     <t xml:space="preserve">27.5574340820312</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0909671783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1255264282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0916481018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7105541229248</t>
+    <t xml:space="preserve">28.0909633636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.125524520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0916500091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7105560302734</t>
   </si>
   <si>
     <t xml:space="preserve">26.7952423095703</t>
@@ -4130,7 +4130,7 @@
     <t xml:space="preserve">27.4219341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2271518707275</t>
+    <t xml:space="preserve">27.2271499633789</t>
   </si>
   <si>
     <t xml:space="preserve">27.4304008483887</t>
@@ -4142,37 +4142,37 @@
     <t xml:space="preserve">27.1509323120117</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7014026641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.234935760498</t>
+    <t xml:space="preserve">27.7014007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2349376678467</t>
   </si>
   <si>
     <t xml:space="preserve">27.9046535491943</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1925945281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4720592498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4635906219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0818157196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2935371398926</t>
+    <t xml:space="preserve">28.1925926208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4720630645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4635963439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0818176269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2935352325439</t>
   </si>
   <si>
     <t xml:space="preserve">29.0479393005371</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7938766479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.692253112793</t>
+    <t xml:space="preserve">28.7938785552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6922473907471</t>
   </si>
   <si>
     <t xml:space="preserve">28.4043140411377</t>
@@ -4184,16 +4184,16 @@
     <t xml:space="preserve">28.8446884155273</t>
   </si>
   <si>
-    <t xml:space="preserve">28.836217880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8531589508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6244983673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.81081199646</t>
+    <t xml:space="preserve">28.8362197875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.853157043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6245002746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8108158111572</t>
   </si>
   <si>
     <t xml:space="preserve">28.8785629272461</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">28.8700923919678</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8277530670166</t>
+    <t xml:space="preserve">28.827751159668</t>
   </si>
   <si>
     <t xml:space="preserve">28.1417770385742</t>
@@ -4217,7 +4217,7 @@
     <t xml:space="preserve">28.675313949585</t>
   </si>
   <si>
-    <t xml:space="preserve">28.759183883667</t>
+    <t xml:space="preserve">28.7591857910156</t>
   </si>
   <si>
     <t xml:space="preserve">28.2301387786865</t>
@@ -4229,13 +4229,13 @@
     <t xml:space="preserve">28.1954479217529</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0133171081543</t>
+    <t xml:space="preserve">28.0133190155029</t>
   </si>
   <si>
     <t xml:space="preserve">28.2908496856689</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3515586853027</t>
+    <t xml:space="preserve">28.3515605926514</t>
   </si>
   <si>
     <t xml:space="preserve">28.299524307251</t>
@@ -4244,7 +4244,7 @@
     <t xml:space="preserve">28.1520843505859</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3081970214844</t>
+    <t xml:space="preserve">28.3081951141357</t>
   </si>
   <si>
     <t xml:space="preserve">28.2214679718018</t>
@@ -4253,52 +4253,52 @@
     <t xml:space="preserve">28.1434135437012</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9812507629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1660022735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4027900695801</t>
+    <t xml:space="preserve">26.9812488555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1660003662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4027919769287</t>
   </si>
   <si>
     <t xml:space="preserve">26.0185623168945</t>
   </si>
   <si>
-    <t xml:space="preserve">24.934455871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0558757781982</t>
+    <t xml:space="preserve">24.9344577789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0558738708496</t>
   </si>
   <si>
     <t xml:space="preserve">24.275318145752</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9951667785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8017406463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3594245910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3247356414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8997669219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0125102996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7176342010498</t>
+    <t xml:space="preserve">24.9951648712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8017425537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3594264984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3247337341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8997650146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.012508392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7176361083984</t>
   </si>
   <si>
     <t xml:space="preserve">25.1686248779297</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4634990692139</t>
+    <t xml:space="preserve">25.4635009765625</t>
   </si>
   <si>
     <t xml:space="preserve">25.4808444976807</t>
@@ -4313,7 +4313,7 @@
     <t xml:space="preserve">24.9518032073975</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5068645477295</t>
+    <t xml:space="preserve">25.5068664550781</t>
   </si>
   <si>
     <t xml:space="preserve">25.9058170318604</t>
@@ -4322,79 +4322,79 @@
     <t xml:space="preserve">26.1052913665771</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6716499328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0359077453613</t>
+    <t xml:space="preserve">25.67165184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.03590965271</t>
   </si>
   <si>
     <t xml:space="preserve">25.6196117401123</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2006931304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4088401794434</t>
+    <t xml:space="preserve">26.2006912231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.408842086792</t>
   </si>
   <si>
     <t xml:space="preserve">26.4435329437256</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5042400360107</t>
+    <t xml:space="preserve">26.5042419433594</t>
   </si>
   <si>
     <t xml:space="preserve">26.313440322876</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1833457946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4522037506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0966186523438</t>
+    <t xml:space="preserve">26.1833477020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.452205657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0966205596924</t>
   </si>
   <si>
     <t xml:space="preserve">25.4721736907959</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6109409332275</t>
+    <t xml:space="preserve">25.6109371185303</t>
   </si>
   <si>
     <t xml:space="preserve">25.3767700195312</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3307857513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1920223236084</t>
+    <t xml:space="preserve">26.3307876586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1920204162598</t>
   </si>
   <si>
     <t xml:space="preserve">26.0098896026611</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8104152679443</t>
+    <t xml:space="preserve">25.8104133605957</t>
   </si>
   <si>
     <t xml:space="preserve">26.5215873718262</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8424816131592</t>
+    <t xml:space="preserve">26.8424835205078</t>
   </si>
   <si>
     <t xml:space="preserve">26.4868965148926</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5996437072754</t>
+    <t xml:space="preserve">26.599645614624</t>
   </si>
   <si>
     <t xml:space="preserve">26.7297382354736</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1062088012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0882835388184</t>
+    <t xml:space="preserve">27.1062107086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0882816314697</t>
   </si>
   <si>
     <t xml:space="preserve">26.3353328704834</t>
@@ -4403,7 +4403,7 @@
     <t xml:space="preserve">26.4070415496826</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6759548187256</t>
+    <t xml:space="preserve">26.675952911377</t>
   </si>
   <si>
     <t xml:space="preserve">26.7028465270996</t>
@@ -4412,10 +4412,10 @@
     <t xml:space="preserve">26.3084411621094</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8154392242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3622245788574</t>
+    <t xml:space="preserve">25.8154373168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3622264862061</t>
   </si>
   <si>
     <t xml:space="preserve">26.8821182250977</t>
@@ -4424,7 +4424,7 @@
     <t xml:space="preserve">26.6938819885254</t>
   </si>
   <si>
-    <t xml:space="preserve">27.20481300354</t>
+    <t xml:space="preserve">27.2048110961914</t>
   </si>
   <si>
     <t xml:space="preserve">27.4737224578857</t>
@@ -4433,43 +4433,43 @@
     <t xml:space="preserve">27.5185413360596</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3930473327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6529960632324</t>
+    <t xml:space="preserve">27.3930492401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6529979705811</t>
   </si>
   <si>
     <t xml:space="preserve">27.7157421112061</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9219055175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8860549926758</t>
+    <t xml:space="preserve">27.9219074249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8860511779785</t>
   </si>
   <si>
     <t xml:space="preserve">27.9667263031006</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9398345947266</t>
+    <t xml:space="preserve">27.9398365020752</t>
   </si>
   <si>
     <t xml:space="preserve">27.7605609893799</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6619606018066</t>
+    <t xml:space="preserve">27.6619625091553</t>
   </si>
   <si>
     <t xml:space="preserve">27.4647579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3840847015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3213405609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6081790924072</t>
+    <t xml:space="preserve">27.3840866088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3213386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.60817527771</t>
   </si>
   <si>
     <t xml:space="preserve">27.9487991333008</t>
@@ -4481,13 +4481,13 @@
     <t xml:space="preserve">28.2356376647949</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7644939422607</t>
+    <t xml:space="preserve">28.7644958496094</t>
   </si>
   <si>
     <t xml:space="preserve">28.3611278533936</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9129447937012</t>
+    <t xml:space="preserve">27.9129428863525</t>
   </si>
   <si>
     <t xml:space="preserve">27.4378681182861</t>
@@ -4502,67 +4502,67 @@
     <t xml:space="preserve">28.5045471191406</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7465686798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6927852630615</t>
+    <t xml:space="preserve">28.7465648651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6927833557129</t>
   </si>
   <si>
     <t xml:space="preserve">28.7555332183838</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9796257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0334053039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1320056915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3740272521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2306060791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7056846618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1000881195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9606037139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5482711791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1986865997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8132457733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8311729431152</t>
+    <t xml:space="preserve">28.9796237945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0334033966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1320037841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3740253448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2306079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.705680847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1000862121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9606018066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5482730865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1986808776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8132476806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8311710357666</t>
   </si>
   <si>
     <t xml:space="preserve">28.7734565734863</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1588954925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3202438354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1140785217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4457321166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.365062713623</t>
+    <t xml:space="preserve">29.158899307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3202419281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1140804290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4457340240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3650608062744</t>
   </si>
   <si>
     <t xml:space="preserve">29.0871887207031</t>
@@ -4571,25 +4571,25 @@
     <t xml:space="preserve">28.7017478942871</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9975490570068</t>
+    <t xml:space="preserve">28.9975509643555</t>
   </si>
   <si>
     <t xml:space="preserve">29.1768226623535</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2574996948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3112831115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5712280273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1628303527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.974588394165</t>
+    <t xml:space="preserve">29.2574977874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.311279296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.571231842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1628322601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9745922088623</t>
   </si>
   <si>
     <t xml:space="preserve">30.2166118621826</t>
@@ -4601,28 +4601,28 @@
     <t xml:space="preserve">30.0283737182617</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7773914337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7236099243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7684268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1717967987061</t>
+    <t xml:space="preserve">29.7773933410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.723611831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7684288024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1717929840088</t>
   </si>
   <si>
     <t xml:space="preserve">30.180757522583</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4586353302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0104484558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2703971862793</t>
+    <t xml:space="preserve">30.4586315155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0104503631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2703952789307</t>
   </si>
   <si>
     <t xml:space="preserve">30.593090057373</t>
@@ -4631,16 +4631,16 @@
     <t xml:space="preserve">30.144905090332</t>
   </si>
   <si>
-    <t xml:space="preserve">30.153865814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0463047027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0373382568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6967182159424</t>
+    <t xml:space="preserve">30.1538677215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0463027954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0373363494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.696720123291</t>
   </si>
   <si>
     <t xml:space="preserve">29.1678619384766</t>
@@ -4649,13 +4649,13 @@
     <t xml:space="preserve">29.6877536773682</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3292083740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4278125762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0552654266357</t>
+    <t xml:space="preserve">29.3292102813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4278106689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0552673339844</t>
   </si>
   <si>
     <t xml:space="preserve">28.7107124328613</t>
@@ -4664,46 +4664,46 @@
     <t xml:space="preserve">28.5224761962891</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4776554107666</t>
+    <t xml:space="preserve">28.4776573181152</t>
   </si>
   <si>
     <t xml:space="preserve">28.2177085876465</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7426319122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3392658233643</t>
+    <t xml:space="preserve">27.7426338195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3392677307129</t>
   </si>
   <si>
     <t xml:space="preserve">27.5095767974854</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3571968078613</t>
+    <t xml:space="preserve">27.3571949005127</t>
   </si>
   <si>
     <t xml:space="preserve">27.0524291992188</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1868839263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2854843139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2944488525391</t>
+    <t xml:space="preserve">27.1868858337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2854862213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2944507598877</t>
   </si>
   <si>
     <t xml:space="preserve">27.4468326568604</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5454330444336</t>
+    <t xml:space="preserve">27.545431137085</t>
   </si>
   <si>
     <t xml:space="preserve">28.0294723510742</t>
   </si>
   <si>
-    <t xml:space="preserve">28.405948638916</t>
+    <t xml:space="preserve">28.4059467315674</t>
   </si>
   <si>
     <t xml:space="preserve">28.1191082000732</t>
@@ -4715,13 +4715,13 @@
     <t xml:space="preserve">28.6838226318359</t>
   </si>
   <si>
-    <t xml:space="preserve">28.495584487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0423698425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7325744628906</t>
+    <t xml:space="preserve">28.4955825805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0423717498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7325706481934</t>
   </si>
   <si>
     <t xml:space="preserve">29.7863540649414</t>
@@ -4733,25 +4733,25 @@
     <t xml:space="preserve">29.4547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">29.849100112915</t>
+    <t xml:space="preserve">29.8491020202637</t>
   </si>
   <si>
     <t xml:space="preserve">29.194751739502</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8989524841309</t>
+    <t xml:space="preserve">28.8989505767822</t>
   </si>
   <si>
     <t xml:space="preserve">29.2664623260498</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0602951049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1499366760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4367733001709</t>
+    <t xml:space="preserve">29.0602970123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1499328613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4367713928223</t>
   </si>
   <si>
     <t xml:space="preserve">29.0961513519287</t>
@@ -4760,7 +4760,7 @@
     <t xml:space="preserve">29.24853515625</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5891532897949</t>
+    <t xml:space="preserve">29.5891513824463</t>
   </si>
   <si>
     <t xml:space="preserve">29.6070804595947</t>
@@ -4769,25 +4769,25 @@
     <t xml:space="preserve">29.7953205108643</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2883262634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0731945037842</t>
+    <t xml:space="preserve">30.2883224487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0731906890869</t>
   </si>
   <si>
     <t xml:space="preserve">30.4048500061035</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4317436218262</t>
+    <t xml:space="preserve">30.4317417144775</t>
   </si>
   <si>
     <t xml:space="preserve">30.3600292205811</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2255764007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1359367370605</t>
+    <t xml:space="preserve">30.2255783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1359405517578</t>
   </si>
   <si>
     <t xml:space="preserve">30.3152122497559</t>
@@ -4796,31 +4796,31 @@
     <t xml:space="preserve">30.3421039581299</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7454700469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3331394195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0642337799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6110172271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8440723419189</t>
+    <t xml:space="preserve">30.7454719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3331413269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0642318725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6110153198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8440685272217</t>
   </si>
   <si>
     <t xml:space="preserve">31.0860919952393</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1936550140381</t>
+    <t xml:space="preserve">31.1936588287354</t>
   </si>
   <si>
     <t xml:space="preserve">31.1578006744385</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1757297515869</t>
+    <t xml:space="preserve">31.1757259368896</t>
   </si>
   <si>
     <t xml:space="preserve">31.3818893432617</t>
@@ -4829,37 +4829,37 @@
     <t xml:space="preserve">31.5522041320801</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8121528625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8480052947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0003852844238</t>
+    <t xml:space="preserve">31.8121509552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8480072021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0003890991211</t>
   </si>
   <si>
     <t xml:space="preserve">31.2384719848633</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7135543823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.731481552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5432415008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8211135864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1258773803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0900268554688</t>
+    <t xml:space="preserve">31.713550567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7314796447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5432395935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8300800323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8211097717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1258811950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0900192260742</t>
   </si>
   <si>
     <t xml:space="preserve">31.2743282318115</t>
@@ -4868,22 +4868,22 @@
     <t xml:space="preserve">30.9068183898926</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9785308837891</t>
+    <t xml:space="preserve">30.9785270690918</t>
   </si>
   <si>
     <t xml:space="preserve">30.1090507507324</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3958892822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8551120758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3069019317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6632442474365</t>
+    <t xml:space="preserve">30.3958873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8551139831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3069000244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6632423400879</t>
   </si>
   <si>
     <t xml:space="preserve">31.430736541748</t>
@@ -4892,16 +4892,16 @@
     <t xml:space="preserve">32.2895965576172</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9606704711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5769271850586</t>
+    <t xml:space="preserve">31.96067237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.57692527771</t>
   </si>
   <si>
     <t xml:space="preserve">31.3667774200439</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2114505767822</t>
+    <t xml:space="preserve">31.2114524841309</t>
   </si>
   <si>
     <t xml:space="preserve">31.3941860198975</t>
@@ -4913,19 +4913,19 @@
     <t xml:space="preserve">31.6957015991211</t>
   </si>
   <si>
-    <t xml:space="preserve">31.860164642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9698104858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9789447784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9241237640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6550712585449</t>
+    <t xml:space="preserve">31.8601665496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9698123931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.978946685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9241218566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6550750732422</t>
   </si>
   <si>
     <t xml:space="preserve">32.3626899719238</t>
@@ -4937,7 +4937,7 @@
     <t xml:space="preserve">32.9748611450195</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0205421447754</t>
+    <t xml:space="preserve">33.0205459594727</t>
   </si>
   <si>
     <t xml:space="preserve">33.2672386169434</t>
@@ -4952,16 +4952,16 @@
     <t xml:space="preserve">33.7423553466797</t>
   </si>
   <si>
-    <t xml:space="preserve">33.797176361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7514953613281</t>
+    <t xml:space="preserve">33.7971801757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7514915466309</t>
   </si>
   <si>
     <t xml:space="preserve">33.6418495178223</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9474487304688</t>
+    <t xml:space="preserve">32.947452545166</t>
   </si>
   <si>
     <t xml:space="preserve">33.2946472167969</t>
@@ -4973,7 +4973,7 @@
     <t xml:space="preserve">33.2398338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">33.404296875</t>
+    <t xml:space="preserve">33.4042930603027</t>
   </si>
   <si>
     <t xml:space="preserve">33.0936393737793</t>
@@ -4991,10 +4991,10 @@
     <t xml:space="preserve">31.613468170166</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8144817352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.581974029541</t>
+    <t xml:space="preserve">31.8144798278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5819778442383</t>
   </si>
   <si>
     <t xml:space="preserve">32.5454292297363</t>
@@ -5024,7 +5024,7 @@
     <t xml:space="preserve">34.4093437194824</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8844566345215</t>
+    <t xml:space="preserve">34.8844604492188</t>
   </si>
   <si>
     <t xml:space="preserve">35.4692192077637</t>
@@ -5033,7 +5033,7 @@
     <t xml:space="preserve">36.5108184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0773010253906</t>
+    <t xml:space="preserve">37.0773048400879</t>
   </si>
   <si>
     <t xml:space="preserve">37.0955772399902</t>
@@ -71099,7 +71099,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6496064815</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>136063</v>
@@ -71120,6 +71120,32 @@
         <v>1971</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.649375</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>188595</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>48.3600006103516</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>47.3199996948242</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>46.8800010681152</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>48.0200004577637</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>1973</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BGN.MI.xlsx
+++ b/data/BGN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1977" uniqueCount="1977">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="1978">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,58 +38,58 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4795970916748</t>
+    <t xml:space="preserve">17.4796009063721</t>
   </si>
   <si>
     <t xml:space="preserve">BGN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2943058013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7816524505615</t>
+    <t xml:space="preserve">17.294303894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7816543579102</t>
   </si>
   <si>
     <t xml:space="preserve">16.528413772583</t>
   </si>
   <si>
-    <t xml:space="preserve">16.262825012207</t>
+    <t xml:space="preserve">16.2628231048584</t>
   </si>
   <si>
     <t xml:space="preserve">16.3678245544434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5098819732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9422416687012</t>
+    <t xml:space="preserve">16.5098838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9422435760498</t>
   </si>
   <si>
     <t xml:space="preserve">16.6457710266113</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1269378662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6760511398315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9601764678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0707540512085</t>
+    <t xml:space="preserve">16.1269397735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6760520935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9601716995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0707502365112</t>
   </si>
   <si>
     <t xml:space="preserve">15.0769290924072</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5092878341675</t>
+    <t xml:space="preserve">15.5092859268188</t>
   </si>
   <si>
     <t xml:space="preserve">15.540168762207</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4289922714233</t>
+    <t xml:space="preserve">15.4289894104004</t>
   </si>
   <si>
     <t xml:space="preserve">15.6019353866577</t>
@@ -98,76 +98,76 @@
     <t xml:space="preserve">15.1942825317383</t>
   </si>
   <si>
-    <t xml:space="preserve">15.478404045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2931089401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0213384628296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8230905532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.718090057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5945596694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4580736160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6804313659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5636777877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1745557785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4154386520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0022106170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8477973937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.385157585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4098625183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1936826705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4963340759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1813306808472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3233909606934</t>
+    <t xml:space="preserve">15.4784021377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2931070327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0213394165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8230895996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7180891036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5945568084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4580774307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6804342269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5636758804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1745548248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4154396057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0022087097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8477964401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3851566314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4098606109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1936836242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4963350296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1813316345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3233938217163</t>
   </si>
   <si>
     <t xml:space="preserve">14.3357429504395</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5210399627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8607473373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2436952590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5710525512695</t>
+    <t xml:space="preserve">14.5210409164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8607492446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2436933517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5710496902466</t>
   </si>
   <si>
     <t xml:space="preserve">15.4969339370728</t>
@@ -176,76 +176,76 @@
     <t xml:space="preserve">15.4351673126221</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4413433074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3239898681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0157623291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2010593414307</t>
+    <t xml:space="preserve">15.4413442611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3239879608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0157585144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.201057434082</t>
   </si>
   <si>
     <t xml:space="preserve">16.2937049865723</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1578254699707</t>
+    <t xml:space="preserve">16.1578216552734</t>
   </si>
   <si>
     <t xml:space="preserve">16.3431167602539</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8489942550659</t>
+    <t xml:space="preserve">15.8489952087402</t>
   </si>
   <si>
     <t xml:space="preserve">15.8922319412231</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6081104278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9354686737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9663486480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0095863342285</t>
+    <t xml:space="preserve">15.6081075668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9354639053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9663496017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0095844268799</t>
   </si>
   <si>
     <t xml:space="preserve">15.8675260543823</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8298654556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8854541778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6569242477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.941047668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3981113433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5339879989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8737001419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9478206634521</t>
+    <t xml:space="preserve">14.8298664093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8854560852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6569232940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9410467147827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3981094360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.533989906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8737020492554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9478187561035</t>
   </si>
   <si>
     <t xml:space="preserve">16.1145877838135</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0837020874023</t>
+    <t xml:space="preserve">16.083703994751</t>
   </si>
   <si>
     <t xml:space="preserve">16.0713500976562</t>
@@ -254,43 +254,43 @@
     <t xml:space="preserve">16.1084079742432</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2072353363037</t>
+    <t xml:space="preserve">16.2072372436523</t>
   </si>
   <si>
     <t xml:space="preserve">16.0589981079102</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2998828887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1701755523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1207637786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7316398620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3795776367188</t>
+    <t xml:space="preserve">16.2998809814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1701774597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1207656860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7316408157349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3795804977417</t>
   </si>
   <si>
     <t xml:space="preserve">15.1201658248901</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8916330337524</t>
+    <t xml:space="preserve">14.8916320800781</t>
   </si>
   <si>
     <t xml:space="preserve">14.706335067749</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6383962631226</t>
+    <t xml:space="preserve">14.6383953094482</t>
   </si>
   <si>
     <t xml:space="preserve">14.6075134277344</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2986869812012</t>
+    <t xml:space="preserve">14.2986841201782</t>
   </si>
   <si>
     <t xml:space="preserve">14.4530973434448</t>
@@ -302,25 +302,25 @@
     <t xml:space="preserve">14.3419208526611</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3666248321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3913326263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3975095748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5537948608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8142623901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9640302658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5110197067261</t>
+    <t xml:space="preserve">14.366626739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3913316726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3975114822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5537919998169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8142642974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9640340805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5110216140747</t>
   </si>
   <si>
     <t xml:space="preserve">15.5956735610962</t>
@@ -329,28 +329,28 @@
     <t xml:space="preserve">15.3742742538452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3286895751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1138010025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0096130371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0551958084106</t>
+    <t xml:space="preserve">15.3286933898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1138029098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0096158981323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0551986694336</t>
   </si>
   <si>
     <t xml:space="preserve">15.211480140686</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3547372817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3026456832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.257061958313</t>
+    <t xml:space="preserve">15.3547401428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3026437759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2570610046387</t>
   </si>
   <si>
     <t xml:space="preserve">14.8533325195312</t>
@@ -359,25 +359,25 @@
     <t xml:space="preserve">14.0979671478271</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2058572769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9649200439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9453840255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1993446350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6616792678833</t>
+    <t xml:space="preserve">13.2058553695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9649219512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9453859329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1993436813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6616811752319</t>
   </si>
   <si>
     <t xml:space="preserve">13.8374977111816</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1565732955933</t>
+    <t xml:space="preserve">14.1565752029419</t>
   </si>
   <si>
     <t xml:space="preserve">14.5733261108398</t>
@@ -404,22 +404,22 @@
     <t xml:space="preserve">11.200234413147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8160400390625</t>
+    <t xml:space="preserve">10.8160390853882</t>
   </si>
   <si>
     <t xml:space="preserve">10.431845664978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7444095611572</t>
+    <t xml:space="preserve">10.7444114685059</t>
   </si>
   <si>
     <t xml:space="preserve">11.2588386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9230403900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3137435913086</t>
+    <t xml:space="preserve">11.923038482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3137445449829</t>
   </si>
   <si>
     <t xml:space="preserve">12.2616500854492</t>
@@ -428,142 +428,142 @@
     <t xml:space="preserve">12.5286340713501</t>
   </si>
   <si>
-    <t xml:space="preserve">12.567702293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6588678359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.372350692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5221195220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5416555404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3397941589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5025882720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2551403045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4895620346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.242115020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0337390899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8188505172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6300115585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4281463623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3825626373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8579196929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9946699142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1835088729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2030467987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0532751083374</t>
+    <t xml:space="preserve">12.5677013397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6588687896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3723516464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5221223831177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5416564941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3397922515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5025873184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2551393508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4895648956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2421159744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0337381362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8188495635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6300096511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4281454086304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3825616836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8579216003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.994668006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1835079193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2030439376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0532732009888</t>
   </si>
   <si>
     <t xml:space="preserve">11.94908618927</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7928047180176</t>
+    <t xml:space="preserve">11.7928056716919</t>
   </si>
   <si>
     <t xml:space="preserve">11.525821685791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7667560577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4411678314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3630275726318</t>
+    <t xml:space="preserve">11.7667570114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4411687850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3630285263062</t>
   </si>
   <si>
     <t xml:space="preserve">11.5583791732788</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7797803878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5388450622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7472229003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.695125579834</t>
+    <t xml:space="preserve">11.7797794342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5388460159302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7472219467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6951265335083</t>
   </si>
   <si>
     <t xml:space="preserve">11.9425745010376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1314144134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1379251480103</t>
+    <t xml:space="preserve">12.1314153671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1379280090332</t>
   </si>
   <si>
     <t xml:space="preserve">12.4114217758179</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4830493927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6653814315796</t>
+    <t xml:space="preserve">12.4830522537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6653823852539</t>
   </si>
   <si>
     <t xml:space="preserve">12.8021259307861</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3788633346558</t>
+    <t xml:space="preserve">12.3788614273071</t>
   </si>
   <si>
     <t xml:space="preserve">12.1183929443359</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1249046325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2876987457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.870945930481</t>
+    <t xml:space="preserve">12.1249055862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2876977920532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8709440231323</t>
   </si>
   <si>
     <t xml:space="preserve">11.7016401290894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.851411819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9165258407593</t>
+    <t xml:space="preserve">11.8514089584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9165267944336</t>
   </si>
   <si>
     <t xml:space="preserve">11.2523279190063</t>
@@ -575,31 +575,31 @@
     <t xml:space="preserve">11.1481399536133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0830211639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1220932006836</t>
+    <t xml:space="preserve">11.0830221176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1220922470093</t>
   </si>
   <si>
     <t xml:space="preserve">11.1741857528687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1090679168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2848854064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1351146697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0765104293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1872091293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0244169235229</t>
+    <t xml:space="preserve">11.1090688705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2848863601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1351175308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.076509475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1872100830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0244150161743</t>
   </si>
   <si>
     <t xml:space="preserve">11.0179033279419</t>
@@ -608,52 +608,52 @@
     <t xml:space="preserve">11.6430330276489</t>
   </si>
   <si>
-    <t xml:space="preserve">11.577917098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9100160598755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1769981384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.29421043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4309568405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9779462814331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0365495681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3816719055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5640048980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.414231300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1732969284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0560855865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9258527755737</t>
+    <t xml:space="preserve">11.5779151916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9100151062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1769971847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2942113876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4309587478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9779443740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0365505218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3816738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5640029907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.414234161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1732959747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0560865402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9258518218994</t>
   </si>
   <si>
     <t xml:space="preserve">12.8281755447388</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3295822143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7984285354614</t>
+    <t xml:space="preserve">13.3295793533325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7984275817871</t>
   </si>
   <si>
     <t xml:space="preserve">13.5444660186768</t>
@@ -662,154 +662,154 @@
     <t xml:space="preserve">13.8830795288086</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8309850692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9481964111328</t>
+    <t xml:space="preserve">13.8309841156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9481973648071</t>
   </si>
   <si>
     <t xml:space="preserve">13.8895921707153</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1240177154541</t>
+    <t xml:space="preserve">14.1240158081055</t>
   </si>
   <si>
     <t xml:space="preserve">13.492374420166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9388732910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9323625564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8672437667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9714326858521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9909706115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7760791778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.795615196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7304944992065</t>
+    <t xml:space="preserve">12.9388742446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9323616027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.867244720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9714317321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9909687042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7760801315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7956132888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7304964065552</t>
   </si>
   <si>
     <t xml:space="preserve">12.74351978302</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4691400527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2896203994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8887062072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5761384963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3612508773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.478461265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0747356414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1854314804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8989152908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8793802261353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9575204849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9770574569702</t>
+    <t xml:space="preserve">14.4691390991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2896213531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8887014389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5761365890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3612480163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4784603118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0747337341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1854295730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8989143371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8793792724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.95751953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9770555496216</t>
   </si>
   <si>
     <t xml:space="preserve">15.0031051635742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7817039489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5863475799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7556552886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8598442077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3417129516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4459018707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.840311050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2700853347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5305576324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4133453369141</t>
+    <t xml:space="preserve">14.781702041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5863513946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.755654335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8598432540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3417139053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4459056854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8403091430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2700872421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5305595397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4133462905884</t>
   </si>
   <si>
     <t xml:space="preserve">15.3482294082642</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5631141662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5138339996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6570930480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5659275054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1231288909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0514984130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6803255081177</t>
+    <t xml:space="preserve">15.5631160736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5138320922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6570949554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5659255981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1231250762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0514965057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6803283691406</t>
   </si>
   <si>
     <t xml:space="preserve">15.7454471588135</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7584676742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0356616973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.335205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2375259399414</t>
+    <t xml:space="preserve">15.7584686279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.035662651062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3352031707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2375288009644</t>
   </si>
   <si>
     <t xml:space="preserve">15.432879447937</t>
@@ -818,19 +818,19 @@
     <t xml:space="preserve">16.2208023071289</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2924327850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1491718292236</t>
+    <t xml:space="preserve">16.2924365997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1491737365723</t>
   </si>
   <si>
     <t xml:space="preserve">15.9538202285767</t>
   </si>
   <si>
-    <t xml:space="preserve">16.175220489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8626556396484</t>
+    <t xml:space="preserve">16.1752223968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8626585006714</t>
   </si>
   <si>
     <t xml:space="preserve">15.5566005706787</t>
@@ -839,64 +839,64 @@
     <t xml:space="preserve">15.1593856811523</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2245044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8468227386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1658992767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4003219604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3091564178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6021842956543</t>
+    <t xml:space="preserve">15.2245006561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8468208312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1658973693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4003210067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.309157371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6021852493286</t>
   </si>
   <si>
     <t xml:space="preserve">15.6217193603516</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6738157272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5500926971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3677635192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3938102722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1398496627808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.107292175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0812454223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6152095794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6282320022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5435810089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7975378036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9342861175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2012672424316</t>
+    <t xml:space="preserve">15.6738128662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5500907897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3677625656128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3938083648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1398506164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1072912216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0812463760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6152057647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6282339096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5435781478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7975397109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9342880249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2012691497803</t>
   </si>
   <si>
     <t xml:space="preserve">16.4422035217285</t>
@@ -908,73 +908,73 @@
     <t xml:space="preserve">16.2794094085693</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1426601409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4812755584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6049976348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.233829498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2561740875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2691993713379</t>
+    <t xml:space="preserve">16.1426620483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4812717437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6049957275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2338275909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2561721801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2691974639893</t>
   </si>
   <si>
     <t xml:space="preserve">17.1584987640381</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1454753875732</t>
+    <t xml:space="preserve">17.1454734802246</t>
   </si>
   <si>
     <t xml:space="preserve">17.1845436096191</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1389598846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6468811035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6273403167725</t>
+    <t xml:space="preserve">17.1389617919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.646879196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6273441314697</t>
   </si>
   <si>
     <t xml:space="preserve">18.3892211914062</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1678218841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1027030944824</t>
+    <t xml:space="preserve">18.1678199768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1027011871338</t>
   </si>
   <si>
     <t xml:space="preserve">18.3501491546631</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1352596282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4934062957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0896778106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2264270782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8588104248047</t>
+    <t xml:space="preserve">18.1352634429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.493408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0896797180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2264251708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8588123321533</t>
   </si>
   <si>
     <t xml:space="preserve">18.8723430633545</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6896419525146</t>
+    <t xml:space="preserve">18.6896438598633</t>
   </si>
   <si>
     <t xml:space="preserve">18.6422748565674</t>
@@ -986,139 +986,139 @@
     <t xml:space="preserve">17.8370380401611</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6543369293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3836688995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9047050476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9317722320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5393009185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.546070098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.99267578125</t>
+    <t xml:space="preserve">17.6543388366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3836708068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9047031402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9317684173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5393028259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5460681915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9926719665527</t>
   </si>
   <si>
     <t xml:space="preserve">18.6761093139648</t>
   </si>
   <si>
-    <t xml:space="preserve">18.926477432251</t>
+    <t xml:space="preserve">18.9264793395996</t>
   </si>
   <si>
     <t xml:space="preserve">18.8046779632568</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9806118011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.621976852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0400371551514</t>
+    <t xml:space="preserve">18.9806098937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6219749450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0400409698486</t>
   </si>
   <si>
     <t xml:space="preserve">18.3377742767334</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2092037200928</t>
+    <t xml:space="preserve">18.2092056274414</t>
   </si>
   <si>
     <t xml:space="preserve">17.999439239502</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8641052246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8032035827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0062046051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4054431915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0603408813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6340351104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2430400848389</t>
+    <t xml:space="preserve">17.8641033172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.803201675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0062084197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4054412841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.060338973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6340370178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2430381774902</t>
   </si>
   <si>
     <t xml:space="preserve">18.2701072692871</t>
   </si>
   <si>
-    <t xml:space="preserve">18.649040222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4528064727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7031764984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4595756530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1024112701416</t>
+    <t xml:space="preserve">18.6490421295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4528102874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7031745910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4595718383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1024131774902</t>
   </si>
   <si>
     <t xml:space="preserve">18.9467754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9197120666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7776107788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8791122436523</t>
+    <t xml:space="preserve">18.9197101593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.77760887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8791103363037</t>
   </si>
   <si>
     <t xml:space="preserve">19.1362457275391</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0415096282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1836128234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3730792999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2918796539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8264465332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9414806365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3001194000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5166549682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0971202850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9956169128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1241855621338</t>
+    <t xml:space="preserve">19.0415115356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1836109161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3730773925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2918834686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8264503479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9414825439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.300121307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5166511535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0971164703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9956150054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1241836547852</t>
   </si>
   <si>
     <t xml:space="preserve">20.1444854736328</t>
@@ -1127,67 +1127,67 @@
     <t xml:space="preserve">20.6384525299072</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2392196655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8941192626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5625495910645</t>
+    <t xml:space="preserve">20.2392177581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8941173553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5625476837158</t>
   </si>
   <si>
     <t xml:space="preserve">19.7587833404541</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9211845397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9008827209473</t>
+    <t xml:space="preserve">19.9211864471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9008865356445</t>
   </si>
   <si>
     <t xml:space="preserve">19.7993831634521</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7655467987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8129177093506</t>
+    <t xml:space="preserve">19.7655487060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.812915802002</t>
   </si>
   <si>
     <t xml:space="preserve">19.4813480377197</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5828495025635</t>
+    <t xml:space="preserve">19.5828475952148</t>
   </si>
   <si>
     <t xml:space="preserve">19.4881134033203</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2851161956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7640762329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7573089599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5949077606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8452758789062</t>
+    <t xml:space="preserve">19.2851123809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7640743255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7573070526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5949096679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8452777862549</t>
   </si>
   <si>
     <t xml:space="preserve">18.8655776977539</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5340099334717</t>
+    <t xml:space="preserve">18.5340061187744</t>
   </si>
   <si>
     <t xml:space="preserve">19.0144443511963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2242126464844</t>
+    <t xml:space="preserve">19.2242107391357</t>
   </si>
   <si>
     <t xml:space="preserve">19.1700801849365</t>
@@ -1196,37 +1196,37 @@
     <t xml:space="preserve">19.2512798309326</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1971473693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4475154876709</t>
+    <t xml:space="preserve">19.1971454620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4475116729736</t>
   </si>
   <si>
     <t xml:space="preserve">19.1633129119873</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2648105621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4678153991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2580471038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8602828979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8670520782471</t>
+    <t xml:space="preserve">19.2648162841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4678134918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2580413818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8602809906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8670482635498</t>
   </si>
   <si>
     <t xml:space="preserve">20.0159168243408</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4204502105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5693130493164</t>
+    <t xml:space="preserve">19.4204483032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.569314956665</t>
   </si>
   <si>
     <t xml:space="preserve">19.5490131378174</t>
@@ -1235,16 +1235,16 @@
     <t xml:space="preserve">19.4272136688232</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3663139343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4136791229248</t>
+    <t xml:space="preserve">19.3663120269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4136829376221</t>
   </si>
   <si>
     <t xml:space="preserve">19.3527793884277</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5016479492188</t>
+    <t xml:space="preserve">19.5016441345215</t>
   </si>
   <si>
     <t xml:space="preserve">18.9400119781494</t>
@@ -1253,25 +1253,25 @@
     <t xml:space="preserve">18.8114433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8858757019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2783451080322</t>
+    <t xml:space="preserve">18.8858795166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2783470153809</t>
   </si>
   <si>
     <t xml:space="preserve">19.1565456390381</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0685806274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2106819152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1091804504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3189449310303</t>
+    <t xml:space="preserve">19.0685749053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2106781005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1091766357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3189468383789</t>
   </si>
   <si>
     <t xml:space="preserve">19.3324794769287</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">19.230978012085</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6572818756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1106491088867</t>
+    <t xml:space="preserve">19.6572799682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1106510162354</t>
   </si>
   <si>
     <t xml:space="preserve">19.9820823669434</t>
@@ -1292,16 +1292,16 @@
     <t xml:space="preserve">19.7858505249023</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5354824066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9482498168945</t>
+    <t xml:space="preserve">19.5354804992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9482479095459</t>
   </si>
   <si>
     <t xml:space="preserve">19.5760822296143</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6166801452637</t>
+    <t xml:space="preserve">19.6166820526123</t>
   </si>
   <si>
     <t xml:space="preserve">19.5557804107666</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">19.3460140228271</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6911144256592</t>
+    <t xml:space="preserve">19.6911163330078</t>
   </si>
   <si>
     <t xml:space="preserve">19.6775817871094</t>
@@ -1322,46 +1322,46 @@
     <t xml:space="preserve">19.1903800964355</t>
   </si>
   <si>
-    <t xml:space="preserve">19.312183380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.791145324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8182106018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9670753479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7708435058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4663429260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1889057159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6084442138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1497745513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1768436431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4745788574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0294513702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0835819244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5301856994629</t>
+    <t xml:space="preserve">19.3121814727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7911434173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8182067871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9670791625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7708396911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4663391113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1889038085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6084384918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1497802734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1768474578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4745826721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0294532775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0835838317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5301876068115</t>
   </si>
   <si>
     <t xml:space="preserve">20.5031204223633</t>
@@ -1370,16 +1370,16 @@
     <t xml:space="preserve">20.8008556365967</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7602519989014</t>
+    <t xml:space="preserve">20.76025390625</t>
   </si>
   <si>
     <t xml:space="preserve">20.7196559906006</t>
   </si>
   <si>
-    <t xml:space="preserve">20.868522644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7061214447021</t>
+    <t xml:space="preserve">20.8685207366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7061176300049</t>
   </si>
   <si>
     <t xml:space="preserve">20.2459850311279</t>
@@ -1388,22 +1388,22 @@
     <t xml:space="preserve">20.4083843231201</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3136558532715</t>
+    <t xml:space="preserve">20.3136520385742</t>
   </si>
   <si>
     <t xml:space="preserve">19.8805809020996</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8926448822021</t>
+    <t xml:space="preserve">18.8926467895508</t>
   </si>
   <si>
     <t xml:space="preserve">19.055046081543</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0265045166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2024383544922</t>
+    <t xml:space="preserve">18.0265064239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2024421691895</t>
   </si>
   <si>
     <t xml:space="preserve">18.2565746307373</t>
@@ -1412,34 +1412,34 @@
     <t xml:space="preserve">18.5813751220703</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5407733917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.486644744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4189739227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5272388458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4731063842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9859046936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4460411071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.662576675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5678405761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7437782287598</t>
+    <t xml:space="preserve">18.5407772064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4866409301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4189758300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5272426605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.473108291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9859085083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4460430145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6625785827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5678424835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7437744140625</t>
   </si>
   <si>
     <t xml:space="preserve">18.7302436828613</t>
@@ -1448,22 +1448,22 @@
     <t xml:space="preserve">18.3783740997314</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8505687713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7558364868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7287731170654</t>
+    <t xml:space="preserve">17.8505706787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.755838394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7287693023682</t>
   </si>
   <si>
     <t xml:space="preserve">17.9723701477051</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0671062469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1483039855957</t>
+    <t xml:space="preserve">18.0671081542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1483097076416</t>
   </si>
   <si>
     <t xml:space="preserve">18.2159729003906</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">18.324239730835</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3513107299805</t>
+    <t xml:space="preserve">18.3513069152832</t>
   </si>
   <si>
     <t xml:space="preserve">18.364839553833</t>
@@ -1481,25 +1481,25 @@
     <t xml:space="preserve">18.7167091369629</t>
   </si>
   <si>
-    <t xml:space="preserve">18.797908782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9061794281006</t>
+    <t xml:space="preserve">18.7979106903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.906177520752</t>
   </si>
   <si>
     <t xml:space="preserve">18.1618385314941</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1212387084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8235054016113</t>
+    <t xml:space="preserve">18.1212406158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.82350730896</t>
   </si>
   <si>
     <t xml:space="preserve">17.6205024719238</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6611022949219</t>
+    <t xml:space="preserve">17.6611061096191</t>
   </si>
   <si>
     <t xml:space="preserve">17.173900604248</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">16.8028087615967</t>
   </si>
   <si>
-    <t xml:space="preserve">16.560525894165</t>
+    <t xml:space="preserve">16.5605297088623</t>
   </si>
   <si>
     <t xml:space="preserve">16.7030467987061</t>
@@ -1526,22 +1526,22 @@
     <t xml:space="preserve">16.3039970397949</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2066144943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2802505493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.850323677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.821816444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.53440284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3206272125244</t>
+    <t xml:space="preserve">15.2066125869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2802515029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8503217697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8218193054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5344047546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.320629119873</t>
   </si>
   <si>
     <t xml:space="preserve">14.8930740356445</t>
@@ -1550,52 +1550,52 @@
     <t xml:space="preserve">15.4631443023682</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8336906433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3491325378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9477071762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8479442596436</t>
+    <t xml:space="preserve">15.8336887359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3491334915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9477043151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8479433059692</t>
   </si>
   <si>
     <t xml:space="preserve">15.8621940612793</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9191999435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7054262161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7339296340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7196779251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3633813858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5059013366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4203910827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4488954544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.950080871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.935830116272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.178111076355</t>
+    <t xml:space="preserve">15.9192028045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7054281234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7339286804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7196760177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3633832931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5059022903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4203901290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4488973617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9500827789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9358320236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.178108215332</t>
   </si>
   <si>
     <t xml:space="preserve">15.5629072189331</t>
@@ -1607,10 +1607,10 @@
     <t xml:space="preserve">15.890697479248</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0189609527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4346399307251</t>
+    <t xml:space="preserve">16.0189666748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4346418380737</t>
   </si>
   <si>
     <t xml:space="preserve">15.3776340484619</t>
@@ -1619,19 +1619,19 @@
     <t xml:space="preserve">15.4916486740112</t>
   </si>
   <si>
-    <t xml:space="preserve">15.52015209198</t>
+    <t xml:space="preserve">15.5201559066772</t>
   </si>
   <si>
     <t xml:space="preserve">15.7909355163574</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7766799926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6056661605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4750194549561</t>
+    <t xml:space="preserve">15.7766828536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6056623458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4750213623047</t>
   </si>
   <si>
     <t xml:space="preserve">16.2469921112061</t>
@@ -1643,115 +1643,115 @@
     <t xml:space="preserve">16.4465160369873</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5035228729248</t>
+    <t xml:space="preserve">16.5035209655762</t>
   </si>
   <si>
     <t xml:space="preserve">15.9619569778442</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0474643707275</t>
+    <t xml:space="preserve">16.0474662780762</t>
   </si>
   <si>
     <t xml:space="preserve">16.2184886932373</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2042350769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1614837646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7481803894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9049482345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2754917144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4037628173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3325023651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2636222839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0783462524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.30637550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.292121887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5486536026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6769227981567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6175346374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7885589599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8598136901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3443794250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3871326446533</t>
+    <t xml:space="preserve">16.2042369842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1614818572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7481813430786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9049501419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2754955291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4037590026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3325004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2636203765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0783472061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3063764572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2921228408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5486555099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6769218444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6175365447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7885570526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8598175048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3443737030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3871307373047</t>
   </si>
   <si>
     <t xml:space="preserve">17.1020946502686</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8764476776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6911725997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6626691818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.964337348938</t>
+    <t xml:space="preserve">15.876446723938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6911735534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6626682281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9643325805664</t>
   </si>
   <si>
     <t xml:space="preserve">14.7933130264282</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3515110015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2161169052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3372592926025</t>
+    <t xml:space="preserve">14.3515090942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2161178588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3372602462769</t>
   </si>
   <si>
     <t xml:space="preserve">14.7220544815063</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4227666854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0593481063843</t>
+    <t xml:space="preserve">14.4227685928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.05934715271</t>
   </si>
   <si>
     <t xml:space="preserve">13.5391597747803</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2042436599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7268123626709</t>
+    <t xml:space="preserve">13.2042446136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7268114089966</t>
   </si>
   <si>
     <t xml:space="preserve">12.3776416778564</t>
@@ -1763,109 +1763,109 @@
     <t xml:space="preserve">12.285005569458</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4061441421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1353616714478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3705177307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9049549102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8622016906738</t>
+    <t xml:space="preserve">12.4061450958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1353607177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3705186843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9049587249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8622007369995</t>
   </si>
   <si>
     <t xml:space="preserve">12.9334602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1472368240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2755002975464</t>
+    <t xml:space="preserve">13.1472358703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.275502204895</t>
   </si>
   <si>
     <t xml:space="preserve">13.1187334060669</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0688524246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5462856292725</t>
+    <t xml:space="preserve">13.0688533782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5462846755981</t>
   </si>
   <si>
     <t xml:space="preserve">13.1116065979004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7838163375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7339363098145</t>
+    <t xml:space="preserve">12.7838172912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7339372634888</t>
   </si>
   <si>
     <t xml:space="preserve">12.6698045730591</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9192066192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9548377990723</t>
+    <t xml:space="preserve">12.9192094802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9548397064209</t>
   </si>
   <si>
     <t xml:space="preserve">13.246997833252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5961685180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1092290878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.945333480835</t>
+    <t xml:space="preserve">13.5961675643921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1092281341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9453353881836</t>
   </si>
   <si>
     <t xml:space="preserve">13.8812017440796</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8883256912231</t>
+    <t xml:space="preserve">13.8883266448975</t>
   </si>
   <si>
     <t xml:space="preserve">14.4655227661133</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2232437133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0878553390503</t>
+    <t xml:space="preserve">14.2232427597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0878524780273</t>
   </si>
   <si>
     <t xml:space="preserve">13.3681392669678</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4679002761841</t>
+    <t xml:space="preserve">13.4679012298584</t>
   </si>
   <si>
     <t xml:space="preserve">13.1258592605591</t>
   </si>
   <si>
-    <t xml:space="preserve">12.969090461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4892807006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6317949295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2327480316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3966407775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8265695571899</t>
+    <t xml:space="preserve">12.9690914154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.489278793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6317939758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2327470779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3966436386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8265714645386</t>
   </si>
   <si>
     <t xml:space="preserve">12.5344114303589</t>
@@ -1874,109 +1874,109 @@
     <t xml:space="preserve">13.1044816970825</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9975938796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6104183197021</t>
+    <t xml:space="preserve">12.9975919723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6104192733765</t>
   </si>
   <si>
     <t xml:space="preserve">13.7529344558716</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6389226913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1448593139648</t>
+    <t xml:space="preserve">13.6389217376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1448583602905</t>
   </si>
   <si>
     <t xml:space="preserve">14.3230056762695</t>
   </si>
   <si>
-    <t xml:space="preserve">14.201865196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947402954102</t>
+    <t xml:space="preserve">14.2018642425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947412490845</t>
   </si>
   <si>
     <t xml:space="preserve">13.8954524993896</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3942651748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5937881469727</t>
+    <t xml:space="preserve">14.39426612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.593789100647</t>
   </si>
   <si>
     <t xml:space="preserve">14.7078008651733</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5082778930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6935548782349</t>
+    <t xml:space="preserve">14.508279800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6935501098633</t>
   </si>
   <si>
     <t xml:space="preserve">14.8075637817383</t>
   </si>
   <si>
-    <t xml:space="preserve">14.636547088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7648067474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7363052368164</t>
+    <t xml:space="preserve">14.6365442276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7648086547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7363080978394</t>
   </si>
   <si>
     <t xml:space="preserve">14.6792984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2659978866577</t>
+    <t xml:space="preserve">14.2660007476807</t>
   </si>
   <si>
     <t xml:space="preserve">14.5367822647095</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2944984436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5510339736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.192361831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9785871505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2778730392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2493677139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2208652496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4061403274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8194408416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8051853179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6341676712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5914106369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4322662353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6032867431641</t>
+    <t xml:space="preserve">14.2944993972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5510330200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1923637390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9785861968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2778720855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2493696212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2208681106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.406138420105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8194389343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8051862716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.634165763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5914096832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4322643280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6032848358154</t>
   </si>
   <si>
     <t xml:space="preserve">16.7172985076904</t>
@@ -1985,16 +1985,16 @@
     <t xml:space="preserve">16.7743053436279</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8170623779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0308361053467</t>
+    <t xml:space="preserve">16.8170642852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0308380126953</t>
   </si>
   <si>
     <t xml:space="preserve">17.1591014862061</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2588634490967</t>
+    <t xml:space="preserve">17.2588653564453</t>
   </si>
   <si>
     <t xml:space="preserve">17.3158702850342</t>
@@ -2003,19 +2003,19 @@
     <t xml:space="preserve">17.4583892822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4726390838623</t>
+    <t xml:space="preserve">17.4726428985596</t>
   </si>
   <si>
     <t xml:space="preserve">17.9714546203613</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7861785888672</t>
+    <t xml:space="preserve">17.7861766815186</t>
   </si>
   <si>
     <t xml:space="preserve">17.9286956787109</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0569610595703</t>
+    <t xml:space="preserve">18.0569648742676</t>
   </si>
   <si>
     <t xml:space="preserve">18.0854663848877</t>
@@ -2027,37 +2027,37 @@
     <t xml:space="preserve">17.5866565704346</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2018566131592</t>
+    <t xml:space="preserve">17.2018585205078</t>
   </si>
   <si>
     <t xml:space="preserve">17.4298858642578</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5296478271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4868927001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7196521759033</t>
+    <t xml:space="preserve">17.5296459197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4868946075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.719654083252</t>
   </si>
   <si>
     <t xml:space="preserve">17.8548011779785</t>
   </si>
   <si>
-    <t xml:space="preserve">17.299186706543</t>
+    <t xml:space="preserve">17.2991847991943</t>
   </si>
   <si>
     <t xml:space="preserve">17.2241020202637</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2691516876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1490173339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7435665130615</t>
+    <t xml:space="preserve">17.2691535949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.149019241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7435703277588</t>
   </si>
   <si>
     <t xml:space="preserve">16.8787174224854</t>
@@ -2066,22 +2066,22 @@
     <t xml:space="preserve">16.9237689971924</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6985206604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2541351318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5394496917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1640357971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0589179992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4343318939209</t>
+    <t xml:space="preserve">16.6985187530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2541332244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5394554138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1640338897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0589160919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4343338012695</t>
   </si>
   <si>
     <t xml:space="preserve">17.8247661590576</t>
@@ -2090,52 +2090,52 @@
     <t xml:space="preserve">17.9298839569092</t>
   </si>
   <si>
-    <t xml:space="preserve">17.839786529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7496852874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9448986053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6657009124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8458995819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1762657165527</t>
+    <t xml:space="preserve">17.8397827148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.749683380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9449024200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.665699005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8458976745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1762676239014</t>
   </si>
   <si>
     <t xml:space="preserve">19.3714828491211</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0561332702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1312160491943</t>
+    <t xml:space="preserve">19.0561351776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1312198638916</t>
   </si>
   <si>
     <t xml:space="preserve">19.4165325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1462306976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0110836029053</t>
+    <t xml:space="preserve">19.1462326049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0110855102539</t>
   </si>
   <si>
     <t xml:space="preserve">19.2213172912598</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7318820953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7769317626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7919502258301</t>
+    <t xml:space="preserve">19.7318840026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7769336700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7919483184814</t>
   </si>
   <si>
     <t xml:space="preserve">19.8069648742676</t>
@@ -2144,40 +2144,40 @@
     <t xml:space="preserve">20.0772647857666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9721508026123</t>
+    <t xml:space="preserve">19.9721488952637</t>
   </si>
   <si>
     <t xml:space="preserve">20.2574653625488</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1373329162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1823806762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.897066116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0472297668457</t>
+    <t xml:space="preserve">20.1373348236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1823825836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8970680236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.047233581543</t>
   </si>
   <si>
     <t xml:space="preserve">20.1523475646973</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0171985626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6568012237549</t>
+    <t xml:space="preserve">20.0172004699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6567993164062</t>
   </si>
   <si>
     <t xml:space="preserve">19.8219833374023</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6868343353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8369979858398</t>
+    <t xml:space="preserve">19.6868324279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8369998931885</t>
   </si>
   <si>
     <t xml:space="preserve">19.9421138763428</t>
@@ -2192,46 +2192,46 @@
     <t xml:space="preserve">19.4916152954102</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6718158721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7168655395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7619152069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2874984741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9120845794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1223182678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0622501373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3025169372559</t>
+    <t xml:space="preserve">19.671817779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7168674468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7619171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2875003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9120826721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1223163604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0622520446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3025150299072</t>
   </si>
   <si>
     <t xml:space="preserve">20.5728130340576</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6629161834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9932823181152</t>
+    <t xml:space="preserve">20.662914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9932804107666</t>
   </si>
   <si>
     <t xml:space="preserve">21.1434497833252</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1584663391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3536796569824</t>
+    <t xml:space="preserve">21.1584625244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3536815643311</t>
   </si>
   <si>
     <t xml:space="preserve">21.0082988739014</t>
@@ -2240,16 +2240,16 @@
     <t xml:space="preserve">21.2635822296143</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2936115264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4287662506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6089649200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5338821411133</t>
+    <t xml:space="preserve">21.2936134338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4287643432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6089668273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5338840484619</t>
   </si>
   <si>
     <t xml:space="preserve">20.9782657623291</t>
@@ -2261,13 +2261,13 @@
     <t xml:space="preserve">21.233549118042</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2485618591309</t>
+    <t xml:space="preserve">21.2485637664795</t>
   </si>
   <si>
     <t xml:space="preserve">21.1734828948975</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6478977203369</t>
+    <t xml:space="preserve">20.6478996276855</t>
   </si>
   <si>
     <t xml:space="preserve">20.6328830718994</t>
@@ -2276,25 +2276,25 @@
     <t xml:space="preserve">20.7680320739746</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0833797454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7980651855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8670330047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7229804992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2035179138184</t>
+    <t xml:space="preserve">21.0833835601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7980632781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8670310974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7229843139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2035121917725</t>
   </si>
   <si>
     <t xml:space="preserve">21.3086318969727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4888305664062</t>
+    <t xml:space="preserve">21.4888343811035</t>
   </si>
   <si>
     <t xml:space="preserve">21.5639133453369</t>
@@ -2303,13 +2303,13 @@
     <t xml:space="preserve">21.1134166717529</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3837127685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3236465454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.578929901123</t>
+    <t xml:space="preserve">21.3837146759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3236503601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5789318084717</t>
   </si>
   <si>
     <t xml:space="preserve">21.8191967010498</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">21.8492317199707</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9543495178223</t>
+    <t xml:space="preserve">21.9543476104736</t>
   </si>
   <si>
     <t xml:space="preserve">22.5850467681885</t>
@@ -2333,67 +2333,67 @@
     <t xml:space="preserve">23.1256446838379</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3208637237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0805988311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2007274627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3058471679688</t>
+    <t xml:space="preserve">23.3208618164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0805969238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2007293701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3058490753174</t>
   </si>
   <si>
     <t xml:space="preserve">23.4259796142578</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6962776184082</t>
+    <t xml:space="preserve">23.6962795257568</t>
   </si>
   <si>
     <t xml:space="preserve">23.9215297698975</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7263107299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6662483215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9065113067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2908306121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3959445953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2758140563965</t>
+    <t xml:space="preserve">23.7263126373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6662502288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9065132141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2908267974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3959465026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2758121490479</t>
   </si>
   <si>
     <t xml:space="preserve">23.0956134796143</t>
   </si>
   <si>
-    <t xml:space="preserve">22.494945526123</t>
+    <t xml:space="preserve">22.4949474334717</t>
   </si>
   <si>
     <t xml:space="preserve">22.6300964355469</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5249805450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0355453491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9454460144043</t>
+    <t xml:space="preserve">22.5249786376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0355472564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9454479217529</t>
   </si>
   <si>
     <t xml:space="preserve">22.5399990081787</t>
   </si>
   <si>
-    <t xml:space="preserve">22.600061416626</t>
+    <t xml:space="preserve">22.6000652313232</t>
   </si>
   <si>
     <t xml:space="preserve">22.645112991333</t>
@@ -2405,19 +2405,19 @@
     <t xml:space="preserve">22.2096309661865</t>
   </si>
   <si>
-    <t xml:space="preserve">22.194616317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1045169830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1795978546143</t>
+    <t xml:space="preserve">22.1946125030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.104513168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1795959472656</t>
   </si>
   <si>
     <t xml:space="preserve">21.7290992736816</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0594635009766</t>
+    <t xml:space="preserve">22.0594615936279</t>
   </si>
   <si>
     <t xml:space="preserve">21.7441120147705</t>
@@ -2426,58 +2426,58 @@
     <t xml:space="preserve">21.5939464569092</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2785987854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0294284820557</t>
+    <t xml:space="preserve">21.2785968780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0294322967529</t>
   </si>
   <si>
     <t xml:space="preserve">22.7652473449707</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7051811218262</t>
+    <t xml:space="preserve">22.7051792144775</t>
   </si>
   <si>
     <t xml:space="preserve">22.99049949646</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9754829406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8102951049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8253154754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0744800567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8853797912598</t>
+    <t xml:space="preserve">22.9754810333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8102970123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8253116607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.07448387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8853759765625</t>
   </si>
   <si>
     <t xml:space="preserve">22.1645793914795</t>
   </si>
   <si>
-    <t xml:space="preserve">22.299732208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8553485870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7952823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3508968353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1017265319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.447114944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4170780181885</t>
+    <t xml:space="preserve">22.2997303009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8553466796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.795280456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3508949279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1017284393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4471111297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4170799255371</t>
   </si>
   <si>
     <t xml:space="preserve">24.67236328125</t>
@@ -2498,28 +2498,28 @@
     <t xml:space="preserve">22.2396659851074</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9181995391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4226512908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4827156066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0411186218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5906181335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9688205718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8876180648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7975215911865</t>
+    <t xml:space="preserve">20.9181976318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4226493835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4827175140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0411167144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5906162261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9688186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8876190185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7975168228149</t>
   </si>
   <si>
     <t xml:space="preserve">13.6201038360596</t>
@@ -2528,85 +2528,85 @@
     <t xml:space="preserve">14.6937952041626</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2146549224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9894037246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6590394973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0344572067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7266139984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8917980194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.905421257019</t>
+    <t xml:space="preserve">13.2146558761597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9894065856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6590404510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0344562530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7266149520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8917970657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9054222106934</t>
   </si>
   <si>
     <t xml:space="preserve">14.0180463790894</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5811710357666</t>
+    <t xml:space="preserve">14.581169128418</t>
   </si>
   <si>
     <t xml:space="preserve">14.0781116485596</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3559217453003</t>
+    <t xml:space="preserve">14.3559188842773</t>
   </si>
   <si>
     <t xml:space="preserve">14.1982450485229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.318380355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0555877685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7688789367676</t>
+    <t xml:space="preserve">14.318377494812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.055588722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7688770294189</t>
   </si>
   <si>
     <t xml:space="preserve">15.46715259552</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7886180877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7074203491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9026374816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.932671546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7674894332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1518030166626</t>
+    <t xml:space="preserve">16.7886199951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7074184417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9026355743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9326677322388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7674865722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1518039703369</t>
   </si>
   <si>
     <t xml:space="preserve">15.3770532608032</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4821729660034</t>
+    <t xml:space="preserve">15.4821691513062</t>
   </si>
   <si>
     <t xml:space="preserve">16.6835021972656</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8937358856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3442344665527</t>
+    <t xml:space="preserve">16.8937339782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3442363739014</t>
   </si>
   <si>
     <t xml:space="preserve">17.0138683319092</t>
@@ -2624,28 +2624,28 @@
     <t xml:space="preserve">17.4643688201904</t>
   </si>
   <si>
-    <t xml:space="preserve">17.103967666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5244369506836</t>
+    <t xml:space="preserve">17.1039714813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.524435043335</t>
   </si>
   <si>
     <t xml:space="preserve">17.1189842224121</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2391204833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1340045928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3892822265625</t>
+    <t xml:space="preserve">17.2391166687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1340007781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3892841339111</t>
   </si>
   <si>
     <t xml:space="preserve">17.4043025970459</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6896171569824</t>
+    <t xml:space="preserve">17.6896190643311</t>
   </si>
   <si>
     <t xml:space="preserve">18.3653678894043</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">18.2902851104736</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4855003356934</t>
+    <t xml:space="preserve">18.4854984283447</t>
   </si>
   <si>
     <t xml:space="preserve">18.9510173797607</t>
@@ -2663,31 +2663,31 @@
     <t xml:space="preserve">19.2813835144043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8520183563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3414497375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.551685333252</t>
+    <t xml:space="preserve">19.8520164489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3414478302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5516834259033</t>
   </si>
   <si>
     <t xml:space="preserve">18.3953990936279</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4315509796143</t>
+    <t xml:space="preserve">19.431547164917</t>
   </si>
   <si>
     <t xml:space="preserve">20.167366027832</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3264350891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9571342468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1073017120361</t>
+    <t xml:space="preserve">19.3264312744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9571323394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1072978973389</t>
   </si>
   <si>
     <t xml:space="preserve">20.6779308319092</t>
@@ -2699,13 +2699,13 @@
     <t xml:space="preserve">19.5066318511963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8820476531982</t>
+    <t xml:space="preserve">19.8820495605469</t>
   </si>
   <si>
     <t xml:space="preserve">20.0922832489014</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3475646972656</t>
+    <t xml:space="preserve">20.3475666046143</t>
   </si>
   <si>
     <t xml:space="preserve">20.3775997161865</t>
@@ -2717,13 +2717,13 @@
     <t xml:space="preserve">18.7107524871826</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9209842681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7708168029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.830883026123</t>
+    <t xml:space="preserve">18.9209823608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7708187103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8308849334717</t>
   </si>
   <si>
     <t xml:space="preserve">19.5666999816895</t>
@@ -2735,49 +2735,49 @@
     <t xml:space="preserve">18.9059677124023</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0711517333984</t>
+    <t xml:space="preserve">19.0711498260498</t>
   </si>
   <si>
     <t xml:space="preserve">18.7558002471924</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4765968322754</t>
+    <t xml:space="preserve">19.476598739624</t>
   </si>
   <si>
     <t xml:space="preserve">19.2964000701904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5366668701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5216503143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3114147186279</t>
+    <t xml:space="preserve">19.5366687774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5216522216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3114166259766</t>
   </si>
   <si>
     <t xml:space="preserve">18.9810485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4526805877686</t>
+    <t xml:space="preserve">20.4526824951172</t>
   </si>
   <si>
     <t xml:space="preserve">20.6178646087646</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6117477416992</t>
+    <t xml:space="preserve">19.6117496490479</t>
   </si>
   <si>
     <t xml:space="preserve">20.3625831604004</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6417808532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0322151184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5127468109131</t>
+    <t xml:space="preserve">19.6417827606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0322170257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5127487182617</t>
   </si>
   <si>
     <t xml:space="preserve">20.2424468994141</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">20.7379989624023</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0021839141846</t>
+    <t xml:space="preserve">20.0021800994873</t>
   </si>
   <si>
     <t xml:space="preserve">18.2152004241943</t>
@@ -2795,73 +2795,73 @@
     <t xml:space="preserve">18.1401176452637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3203182220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5577983856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4376659393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1284294128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7830486297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4977283477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0233135223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4137496948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3686981201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9031829833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0383319854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4076328277588</t>
+    <t xml:space="preserve">18.3203144073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5577964782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4376640319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1284313201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7830505371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.497730255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0233154296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.413745880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3686943054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9031810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0383338928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4076290130615</t>
   </si>
   <si>
     <t xml:space="preserve">20.5427837371826</t>
   </si>
   <si>
-    <t xml:space="preserve">20.317533493042</t>
+    <t xml:space="preserve">20.3175354003906</t>
   </si>
   <si>
     <t xml:space="preserve">20.2124137878418</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4465637207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7469005584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2363357543945</t>
+    <t xml:space="preserve">19.4465656280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7468967437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2363338470459</t>
   </si>
   <si>
     <t xml:space="preserve">20.5277652740479</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7140789031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.684045791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6389980316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3386669158936</t>
+    <t xml:space="preserve">21.7140827178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6840476989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6389961242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3386631011963</t>
   </si>
   <si>
     <t xml:space="preserve">21.6239814758301</t>
@@ -2876,19 +2876,19 @@
     <t xml:space="preserve">21.4437828063965</t>
   </si>
   <si>
-    <t xml:space="preserve">21.188497543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9092960357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8942794799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8342151641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.503849029541</t>
+    <t xml:space="preserve">21.1884994506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9092979431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8942813873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8342132568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5038471221924</t>
   </si>
   <si>
     <t xml:space="preserve">22.2546825408936</t>
@@ -2903,10 +2903,10 @@
     <t xml:space="preserve">22.3447799682617</t>
   </si>
   <si>
-    <t xml:space="preserve">22.464916229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6901626586914</t>
+    <t xml:space="preserve">22.4649124145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.69016456604</t>
   </si>
   <si>
     <t xml:space="preserve">22.8703632354736</t>
@@ -2924,16 +2924,16 @@
     <t xml:space="preserve">22.5775394439697</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9079055786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0430564880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0881042480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8178043365479</t>
+    <t xml:space="preserve">22.9079036712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0430545806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0881004333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8178062438965</t>
   </si>
   <si>
     <t xml:space="preserve">22.8403301239014</t>
@@ -2945,124 +2945,124 @@
     <t xml:space="preserve">23.215747833252</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3809299468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.523588180542</t>
+    <t xml:space="preserve">23.3809280395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5235862731934</t>
   </si>
   <si>
     <t xml:space="preserve">23.0505638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">22.915412902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0730876922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2532863616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3433895111084</t>
+    <t xml:space="preserve">22.9154148101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0730895996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2532901763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3433876037598</t>
   </si>
   <si>
     <t xml:space="preserve">23.29833984375</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8914985656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.259407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0942230224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.664852142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5522289276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4621295928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7924957275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4020595550537</t>
+    <t xml:space="preserve">23.8914947509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2594051361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0942211151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6648540496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5522270202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4621315002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7924938201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.402063369751</t>
   </si>
   <si>
     <t xml:space="preserve">24.0491695404053</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4696369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4245891571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1993370056152</t>
+    <t xml:space="preserve">24.4696388244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4245853424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1993389129639</t>
   </si>
   <si>
     <t xml:space="preserve">23.9590702056885</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1617946624756</t>
+    <t xml:space="preserve">24.1617984771729</t>
   </si>
   <si>
     <t xml:space="preserve">24.2293720245361</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6273136138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8075141906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8150215148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1078414916992</t>
+    <t xml:space="preserve">24.627311706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8075122833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8150177001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1078433990479</t>
   </si>
   <si>
     <t xml:space="preserve">25.2204704284668</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1003360748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1829280853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2955493927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5208015441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8286457061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8061180114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7385425567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7835960388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0538959503174</t>
+    <t xml:space="preserve">25.1003341674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1829299926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2955551147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5208053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.828649520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8061199188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7385387420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7835941314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0538997650146</t>
   </si>
   <si>
     <t xml:space="preserve">25.8661861419678</t>
   </si>
   <si>
-    <t xml:space="preserve">26.489372253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5119018554688</t>
+    <t xml:space="preserve">26.4893760681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.511905670166</t>
   </si>
   <si>
     <t xml:space="preserve">26.3767528533936</t>
@@ -3071,13 +3071,13 @@
     <t xml:space="preserve">26.466854095459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6545543670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.586986541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1050605773926</t>
+    <t xml:space="preserve">26.6545600891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5869846343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1050567626953</t>
   </si>
   <si>
     <t xml:space="preserve">27.5180187225342</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">27.1350917816162</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3903770446777</t>
+    <t xml:space="preserve">27.3903751373291</t>
   </si>
   <si>
     <t xml:space="preserve">27.0149593353271</t>
@@ -3095,58 +3095,58 @@
     <t xml:space="preserve">27.037483215332</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2176876068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1951580047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.225191116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2566184997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6845951080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1726341247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.029972076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7446594238281</t>
+    <t xml:space="preserve">27.2176856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1951637268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2251930236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2566204071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6845932006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1726322174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0299777984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7446575164795</t>
   </si>
   <si>
     <t xml:space="preserve">26.6245269775391</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8962230682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0163555145264</t>
+    <t xml:space="preserve">25.8962173461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0163536071777</t>
   </si>
   <si>
     <t xml:space="preserve">26.3992767333984</t>
   </si>
   <si>
-    <t xml:space="preserve">26.35422706604</t>
+    <t xml:space="preserve">26.3542289733887</t>
   </si>
   <si>
     <t xml:space="preserve">26.5569496154785</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0013370513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0238571166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.421802520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2866477966309</t>
+    <t xml:space="preserve">26.001335144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0238628387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4217987060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2866535186768</t>
   </si>
   <si>
     <t xml:space="preserve">26.2115726470947</t>
@@ -3155,124 +3155,124 @@
     <t xml:space="preserve">26.8873176574707</t>
   </si>
   <si>
-    <t xml:space="preserve">27.11256980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3603382110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.382869720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6456604003906</t>
+    <t xml:space="preserve">27.1125679016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3603420257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3828716278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6456565856934</t>
   </si>
   <si>
     <t xml:space="preserve">27.6231346130371</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7808132171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5931015014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.42041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5630664825439</t>
+    <t xml:space="preserve">27.7808074951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5931053161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4204082489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5630645751953</t>
   </si>
   <si>
     <t xml:space="preserve">27.7883148193359</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7132396697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.953498840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9835376739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.261344909668</t>
+    <t xml:space="preserve">27.7132339477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9534969329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9835338592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2613430023193</t>
   </si>
   <si>
     <t xml:space="preserve">28.1412105560303</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2087841033936</t>
+    <t xml:space="preserve">28.2087821960449</t>
   </si>
   <si>
     <t xml:space="preserve">28.1862602233887</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3814735412598</t>
+    <t xml:space="preserve">28.3814792633057</t>
   </si>
   <si>
     <t xml:space="preserve">28.2012805938721</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0586166381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1186828613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4115104675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.169849395752</t>
+    <t xml:space="preserve">28.0586185455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1186866760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4115047454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1698474884033</t>
   </si>
   <si>
     <t xml:space="preserve">29.3875904083252</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5077247619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2899780273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9145698547363</t>
+    <t xml:space="preserve">29.5077266693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2899856567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9145660400391</t>
   </si>
   <si>
     <t xml:space="preserve">28.4190158843994</t>
   </si>
   <si>
-    <t xml:space="preserve">28.64426612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1923770904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1323127746582</t>
+    <t xml:space="preserve">28.6442737579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1923789978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1323108673096</t>
   </si>
   <si>
     <t xml:space="preserve">29.2148971557617</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5842018127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4865894317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4565601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5466594696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4640636444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8784217834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4715709686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4040012359619</t>
+    <t xml:space="preserve">28.5841999053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4865875244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4565563201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5466556549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4640693664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.87841796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4715728759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4040031433105</t>
   </si>
   <si>
     <t xml:space="preserve">28.0736293792725</t>
@@ -3281,16 +3281,16 @@
     <t xml:space="preserve">28.3964900970459</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0285873413086</t>
+    <t xml:space="preserve">28.0285816192627</t>
   </si>
   <si>
     <t xml:space="preserve">28.7644023895264</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6954307556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7179584503174</t>
+    <t xml:space="preserve">29.6954326629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7179622650146</t>
   </si>
   <si>
     <t xml:space="preserve">29.9432067871094</t>
@@ -3299,130 +3299,130 @@
     <t xml:space="preserve">30.4012184143066</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7240753173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5213489532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6940383911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5288581848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7090549468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4988231658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.77663230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7602252960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2107238769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4359741210938</t>
+    <t xml:space="preserve">30.7240734100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5213470458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6940402984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5288543701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7090644836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4988250732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7766284942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7602233886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2107200622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4359703063965</t>
   </si>
   <si>
     <t xml:space="preserve">31.7377014160156</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1506538391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3083229064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.345874786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8728446960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1370315551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8592205047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0544395446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4641036987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2591991424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0342826843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6406841278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8052845001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1265869140625</t>
+    <t xml:space="preserve">32.1506576538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3083305358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3458671569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8728523254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1370334625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8592262268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0544414520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4641056060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2591972351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0342807769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6406879425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8052806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1265907287598</t>
   </si>
   <si>
     <t xml:space="preserve">29.0864238739014</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0583820343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.937894821167</t>
+    <t xml:space="preserve">30.0583782196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9378910064697</t>
   </si>
   <si>
     <t xml:space="preserve">30.114616394043</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5885429382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3596820831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3195209503174</t>
+    <t xml:space="preserve">30.5885410308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3596782684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3195171356201</t>
   </si>
   <si>
     <t xml:space="preserve">31.0303382873535</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1508312225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.335578918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2632884979248</t>
+    <t xml:space="preserve">31.1508274078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3355865478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2632904052734</t>
   </si>
   <si>
     <t xml:space="preserve">31.1669006347656</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1187000274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.604606628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7531414031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4118251800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5644435882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.548376083374</t>
+    <t xml:space="preserve">31.1186981201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6046085357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7531433105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4118232727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5644474029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5483741760254</t>
   </si>
   <si>
     <t xml:space="preserve">30.9419803619385</t>
@@ -3437,25 +3437,25 @@
     <t xml:space="preserve">31.1267337799072</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2150955200195</t>
+    <t xml:space="preserve">31.2150974273682</t>
   </si>
   <si>
     <t xml:space="preserve">31.2311611175537</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1909942626953</t>
+    <t xml:space="preserve">31.1909961700439</t>
   </si>
   <si>
     <t xml:space="preserve">30.4359188079834</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2029685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1788749694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8375549316406</t>
+    <t xml:space="preserve">30.202974319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1788730621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8375568389893</t>
   </si>
   <si>
     <t xml:space="preserve">30.8616504669189</t>
@@ -3464,16 +3464,16 @@
     <t xml:space="preserve">30.5082149505615</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3475646972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.291332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4800319671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8856048583984</t>
+    <t xml:space="preserve">30.3475608825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2913303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4800262451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8856067657471</t>
   </si>
   <si>
     <t xml:space="preserve">29.3997001647949</t>
@@ -3482,10 +3482,10 @@
     <t xml:space="preserve">28.9338054656982</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7208633422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1907043457031</t>
+    <t xml:space="preserve">27.7208690643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1907062530518</t>
   </si>
   <si>
     <t xml:space="preserve">27.6807022094727</t>
@@ -3494,124 +3494,124 @@
     <t xml:space="preserve">27.9939765930176</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0743083953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5803661346436</t>
+    <t xml:space="preserve">28.0743064880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5803680419922</t>
   </si>
   <si>
     <t xml:space="preserve">28.9659366607666</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0783939361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8695449829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8374118804932</t>
+    <t xml:space="preserve">29.0783920288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8695430755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8374156951904</t>
   </si>
   <si>
     <t xml:space="preserve">28.8133144378662</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6285648345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3595352172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0944576263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9579029083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3152885437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1587200164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3675708770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8936443328857</t>
+    <t xml:space="preserve">28.6285591125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3595409393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.09446144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9579048156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3152904510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1587219238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3675727844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8936405181885</t>
   </si>
   <si>
     <t xml:space="preserve">28.802698135376</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2799015045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4105987548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9600067138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9974250793457</t>
+    <t xml:space="preserve">28.2799034118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4106006622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9600028991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9974231719971</t>
   </si>
   <si>
     <t xml:space="preserve">26.9810848236084</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9028244018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9273300170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.322847366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3623714447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8885879516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5175762176514</t>
+    <t xml:space="preserve">25.9028205871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9273281097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3228454589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3623695373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8885898590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5175743103027</t>
   </si>
   <si>
     <t xml:space="preserve">25.3963661193848</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7101993560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3065128326416</t>
+    <t xml:space="preserve">24.7102012634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3065090179443</t>
   </si>
   <si>
     <t xml:space="preserve">25.7231121063232</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8211364746094</t>
+    <t xml:space="preserve">25.821138381958</t>
   </si>
   <si>
     <t xml:space="preserve">27.1281204223633</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9565811157227</t>
+    <t xml:space="preserve">26.956579208374</t>
   </si>
   <si>
     <t xml:space="preserve">27.1444568634033</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7768707275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1036167144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0709400177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9892578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0300979614258</t>
+    <t xml:space="preserve">26.7768688201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1036186218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0709381103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9892559051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0300998687744</t>
   </si>
   <si>
     <t xml:space="preserve">27.3486766815186</t>
@@ -3620,10 +3620,10 @@
     <t xml:space="preserve">28.1328639984131</t>
   </si>
   <si>
-    <t xml:space="preserve">27.904146194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5447235107422</t>
+    <t xml:space="preserve">27.9041423797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5447254180908</t>
   </si>
   <si>
     <t xml:space="preserve">27.9776611328125</t>
@@ -3632,28 +3632,28 @@
     <t xml:space="preserve">27.5937366485596</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5481433868408</t>
+    <t xml:space="preserve">26.5481472015381</t>
   </si>
   <si>
     <t xml:space="preserve">26.7523632049561</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8830642700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8667278289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5399799346924</t>
+    <t xml:space="preserve">26.8830604553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8667259216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.539981842041</t>
   </si>
   <si>
     <t xml:space="preserve">26.4991340637207</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3439292907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6414241790771</t>
+    <t xml:space="preserve">26.3439311981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6414260864258</t>
   </si>
   <si>
     <t xml:space="preserve">26.2377376556396</t>
@@ -3662,142 +3662,142 @@
     <t xml:space="preserve">26.3520965576172</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1152057647705</t>
+    <t xml:space="preserve">26.1152076721191</t>
   </si>
   <si>
     <t xml:space="preserve">25.9109916687012</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3146781921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3310165405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2738342285156</t>
+    <t xml:space="preserve">25.3146800994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.331018447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2738361358643</t>
   </si>
   <si>
     <t xml:space="preserve">25.6740989685059</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8047981262207</t>
+    <t xml:space="preserve">25.8048000335693</t>
   </si>
   <si>
     <t xml:space="preserve">25.3555240631104</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9634265899658</t>
+    <t xml:space="preserve">24.9634284973145</t>
   </si>
   <si>
     <t xml:space="preserve">23.9913578033447</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3017673492432</t>
+    <t xml:space="preserve">24.3017654418945</t>
   </si>
   <si>
     <t xml:space="preserve">25.837474822998</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3766059875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4256153106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5154705047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.441951751709</t>
+    <t xml:space="preserve">26.3766098022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4256172180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5154685974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4419536590576</t>
   </si>
   <si>
     <t xml:space="preserve">26.6380023956299</t>
   </si>
   <si>
-    <t xml:space="preserve">26.507303237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5489673614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7698364257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4734268188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5743732452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6759967803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9639339447021</t>
+    <t xml:space="preserve">26.5073051452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5489635467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7698345184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4734287261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5743751525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6759948730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9639358520508</t>
   </si>
   <si>
     <t xml:space="preserve">27.5828399658203</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3457107543945</t>
+    <t xml:space="preserve">27.3457145690918</t>
   </si>
   <si>
     <t xml:space="preserve">27.5235557556152</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7274913787842</t>
+    <t xml:space="preserve">26.7274894714355</t>
   </si>
   <si>
     <t xml:space="preserve">27.5320262908936</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9561500549316</t>
+    <t xml:space="preserve">26.956148147583</t>
   </si>
   <si>
     <t xml:space="preserve">26.2108955383301</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5164566040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3992595672607</t>
+    <t xml:space="preserve">25.5164546966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3992576599121</t>
   </si>
   <si>
     <t xml:space="preserve">22.8149127960205</t>
   </si>
   <si>
-    <t xml:space="preserve">23.348445892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9751319885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9250049591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4161968231201</t>
+    <t xml:space="preserve">23.3484420776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9751358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9250068664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4161949157715</t>
   </si>
   <si>
     <t xml:space="preserve">23.5686340332031</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3569145202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0859146118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8904476165771</t>
+    <t xml:space="preserve">23.356912612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.085916519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8904495239258</t>
   </si>
   <si>
     <t xml:space="preserve">23.6194458007812</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5093536376953</t>
+    <t xml:space="preserve">23.5093517303467</t>
   </si>
   <si>
     <t xml:space="preserve">23.3230400085449</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8318481445312</t>
+    <t xml:space="preserve">22.8318462371826</t>
   </si>
   <si>
     <t xml:space="preserve">22.7471618652344</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">22.713285446167</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6462211608887</t>
+    <t xml:space="preserve">21.64621925354</t>
   </si>
   <si>
     <t xml:space="preserve">21.9510955810547</t>
@@ -3815,109 +3815,109 @@
     <t xml:space="preserve">22.2644424438477</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7810363769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.112003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4592266082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.222095489502</t>
+    <t xml:space="preserve">22.7810382843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1120052337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4592227935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2220973968506</t>
   </si>
   <si>
     <t xml:space="preserve">21.307466506958</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7563152313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2898445129395</t>
+    <t xml:space="preserve">21.756311416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2898483276367</t>
   </si>
   <si>
     <t xml:space="preserve">23.052038192749</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0351028442383</t>
+    <t xml:space="preserve">23.0351009368896</t>
   </si>
   <si>
     <t xml:space="preserve">22.5185050964355</t>
   </si>
   <si>
-    <t xml:space="preserve">23.009693145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5015678405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6116619110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1536617279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9666652679443</t>
+    <t xml:space="preserve">23.0096950531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5015659332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6116600036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1536636352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.966667175293</t>
   </si>
   <si>
     <t xml:space="preserve">24.0513553619385</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9327907562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.423978805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5256080627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9497299194336</t>
+    <t xml:space="preserve">23.9327926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4239807128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5256061553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.949728012085</t>
   </si>
   <si>
     <t xml:space="preserve">23.8565731048584</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4416027069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7888240814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1275730133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1360454559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5008850097656</t>
+    <t xml:space="preserve">23.4416046142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7888221740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1275749206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.136043548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.500883102417</t>
   </si>
   <si>
     <t xml:space="preserve">23.7380104064941</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0774421691895</t>
+    <t xml:space="preserve">23.0774459838867</t>
   </si>
   <si>
     <t xml:space="preserve">22.5354423522949</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9334735870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7725677490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.095064163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0273151397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2559719085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3914737701416</t>
+    <t xml:space="preserve">22.9334754943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7725696563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0950660705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0273170471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.255973815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.391471862793</t>
   </si>
   <si>
     <t xml:space="preserve">21.9256896972656</t>
@@ -3926,22 +3926,22 @@
     <t xml:space="preserve">22.23903465271</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3237209320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4422855377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0689754486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9243221282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3907890319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9419422149658</t>
+    <t xml:space="preserve">22.3237266540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4422874450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.068977355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9243259429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3907909393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9419460296631</t>
   </si>
   <si>
     <t xml:space="preserve">22.6455364227295</t>
@@ -3953,13 +3953,13 @@
     <t xml:space="preserve">21.3921566009521</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5022487640381</t>
+    <t xml:space="preserve">21.5022506713867</t>
   </si>
   <si>
     <t xml:space="preserve">21.3413429260254</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7908725738525</t>
+    <t xml:space="preserve">20.7908706665039</t>
   </si>
   <si>
     <t xml:space="preserve">21.0957489013672</t>
@@ -3968,16 +3968,16 @@
     <t xml:space="preserve">20.6553707122803</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8078117370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3335552215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2207336425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2552890777588</t>
+    <t xml:space="preserve">20.8078079223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3335590362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2207317352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2552871704102</t>
   </si>
   <si>
     <t xml:space="preserve">24.0344181060791</t>
@@ -3989,7 +3989,7 @@
     <t xml:space="preserve">22.7979736328125</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4331340789795</t>
+    <t xml:space="preserve">23.4331321716309</t>
   </si>
   <si>
     <t xml:space="preserve">23.6533203125</t>
@@ -3998,46 +3998,46 @@
     <t xml:space="preserve">24.0174808502197</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3308258056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3477649688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2037944793701</t>
+    <t xml:space="preserve">24.3308238983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3477630615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2037925720215</t>
   </si>
   <si>
     <t xml:space="preserve">24.79660987854</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1438274383545</t>
+    <t xml:space="preserve">25.1438293457031</t>
   </si>
   <si>
     <t xml:space="preserve">25.8298015594482</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9737720489502</t>
+    <t xml:space="preserve">25.9737701416016</t>
   </si>
   <si>
     <t xml:space="preserve">26.2871170043945</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3802719116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6265487670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.719705581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6858310699463</t>
+    <t xml:space="preserve">26.3802738189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6265506744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7197074890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6858329772949</t>
   </si>
   <si>
     <t xml:space="preserve">26.3294582366943</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3118362426758</t>
+    <t xml:space="preserve">27.3118381500244</t>
   </si>
   <si>
     <t xml:space="preserve">26.9307422637939</t>
@@ -4049,16 +4049,16 @@
     <t xml:space="preserve">28.1756553649902</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2264671325684</t>
+    <t xml:space="preserve">28.226469039917</t>
   </si>
   <si>
     <t xml:space="preserve">28.074031829834</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4551219940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2434043884277</t>
+    <t xml:space="preserve">28.4551239013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2434062957764</t>
   </si>
   <si>
     <t xml:space="preserve">28.1163711547852</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">28.3111553192139</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1671848297119</t>
+    <t xml:space="preserve">28.1671867370605</t>
   </si>
   <si>
     <t xml:space="preserve">28.4297199249268</t>
@@ -4082,10 +4082,10 @@
     <t xml:space="preserve">27.2779636383057</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0069618225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.947681427002</t>
+    <t xml:space="preserve">27.0069599151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9476795196533</t>
   </si>
   <si>
     <t xml:space="preserve">27.2864322662354</t>
@@ -4094,7 +4094,7 @@
     <t xml:space="preserve">27.0238990783691</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6675281524658</t>
+    <t xml:space="preserve">27.6675262451172</t>
   </si>
   <si>
     <t xml:space="preserve">27.4981517791748</t>
@@ -4112,7 +4112,7 @@
     <t xml:space="preserve">27.5574340820312</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0909633636475</t>
+    <t xml:space="preserve">28.0909652709961</t>
   </si>
   <si>
     <t xml:space="preserve">27.125524520874</t>
@@ -4121,7 +4121,7 @@
     <t xml:space="preserve">27.0916500091553</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7105560302734</t>
+    <t xml:space="preserve">26.7105541229248</t>
   </si>
   <si>
     <t xml:space="preserve">26.7952423095703</t>
@@ -4130,7 +4130,7 @@
     <t xml:space="preserve">27.4219341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2271499633789</t>
+    <t xml:space="preserve">27.2271518707275</t>
   </si>
   <si>
     <t xml:space="preserve">27.4304008483887</t>
@@ -4139,16 +4139,16 @@
     <t xml:space="preserve">27.3203048706055</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1509323120117</t>
+    <t xml:space="preserve">27.1509304046631</t>
   </si>
   <si>
     <t xml:space="preserve">27.7014007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2349376678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9046535491943</t>
+    <t xml:space="preserve">28.2349395751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9046516418457</t>
   </si>
   <si>
     <t xml:space="preserve">28.1925926208496</t>
@@ -4163,61 +4163,61 @@
     <t xml:space="preserve">29.0818176269531</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2935352325439</t>
+    <t xml:space="preserve">29.2935371398926</t>
   </si>
   <si>
     <t xml:space="preserve">29.0479393005371</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7938785552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6922473907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4043140411377</t>
+    <t xml:space="preserve">28.7938747406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.692253112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4043121337891</t>
   </si>
   <si>
     <t xml:space="preserve">28.7176570892334</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8446884155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8362197875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.853157043457</t>
+    <t xml:space="preserve">28.844690322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.836217880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8531608581543</t>
   </si>
   <si>
     <t xml:space="preserve">28.6245002746582</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8108158111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8785629272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0902843475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8700923919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.827751159668</t>
+    <t xml:space="preserve">28.8108139038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8785648345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0902824401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8700942993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8277492523193</t>
   </si>
   <si>
     <t xml:space="preserve">28.1417770385742</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7600002288818</t>
+    <t xml:space="preserve">28.7599983215332</t>
   </si>
   <si>
     <t xml:space="preserve">28.675313949585</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7591857910156</t>
+    <t xml:space="preserve">28.759183883667</t>
   </si>
   <si>
     <t xml:space="preserve">28.2301387786865</t>
@@ -4235,7 +4235,7 @@
     <t xml:space="preserve">28.2908496856689</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3515605926514</t>
+    <t xml:space="preserve">28.3515625</t>
   </si>
   <si>
     <t xml:space="preserve">28.299524307251</t>
@@ -4244,34 +4244,34 @@
     <t xml:space="preserve">28.1520843505859</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3081951141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2214679718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1434135437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9812488555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1660003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4027919769287</t>
+    <t xml:space="preserve">28.3081970214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2214698791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1434154510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9812507629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1660022735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4027900695801</t>
   </si>
   <si>
     <t xml:space="preserve">26.0185623168945</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9344577789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0558738708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.275318145752</t>
+    <t xml:space="preserve">24.934455871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0558757781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2753200531006</t>
   </si>
   <si>
     <t xml:space="preserve">24.9951648712158</t>
@@ -4280,19 +4280,19 @@
     <t xml:space="preserve">25.8017425537109</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3594264984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3247337341309</t>
+    <t xml:space="preserve">25.3594245910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3247375488281</t>
   </si>
   <si>
     <t xml:space="preserve">24.8997650146484</t>
   </si>
   <si>
-    <t xml:space="preserve">25.012508392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7176361083984</t>
+    <t xml:space="preserve">25.0125102996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7176342010498</t>
   </si>
   <si>
     <t xml:space="preserve">25.1686248779297</t>
@@ -4301,19 +4301,19 @@
     <t xml:space="preserve">25.4635009765625</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4808444976807</t>
+    <t xml:space="preserve">25.480842590332</t>
   </si>
   <si>
     <t xml:space="preserve">25.4461536407471</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3073883056641</t>
+    <t xml:space="preserve">25.3073902130127</t>
   </si>
   <si>
     <t xml:space="preserve">24.9518032073975</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5068664550781</t>
+    <t xml:space="preserve">25.5068645477295</t>
   </si>
   <si>
     <t xml:space="preserve">25.9058170318604</t>
@@ -4322,22 +4322,22 @@
     <t xml:space="preserve">26.1052913665771</t>
   </si>
   <si>
-    <t xml:space="preserve">25.67165184021</t>
+    <t xml:space="preserve">25.6716499328613</t>
   </si>
   <si>
     <t xml:space="preserve">26.03590965271</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6196117401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2006912231445</t>
+    <t xml:space="preserve">25.6196098327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2006931304932</t>
   </si>
   <si>
     <t xml:space="preserve">26.408842086792</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4435329437256</t>
+    <t xml:space="preserve">26.4435348510742</t>
   </si>
   <si>
     <t xml:space="preserve">26.5042419433594</t>
@@ -4352,28 +4352,28 @@
     <t xml:space="preserve">26.452205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0966205596924</t>
+    <t xml:space="preserve">26.0966167449951</t>
   </si>
   <si>
     <t xml:space="preserve">25.4721736907959</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6109371185303</t>
+    <t xml:space="preserve">25.6109390258789</t>
   </si>
   <si>
     <t xml:space="preserve">25.3767700195312</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3307876586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1920204162598</t>
+    <t xml:space="preserve">26.3307857513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1920223236084</t>
   </si>
   <si>
     <t xml:space="preserve">26.0098896026611</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8104133605957</t>
+    <t xml:space="preserve">25.8104152679443</t>
   </si>
   <si>
     <t xml:space="preserve">26.5215873718262</t>
@@ -4385,10 +4385,10 @@
     <t xml:space="preserve">26.4868965148926</t>
   </si>
   <si>
-    <t xml:space="preserve">26.599645614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7297382354736</t>
+    <t xml:space="preserve">26.5996437072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7297344207764</t>
   </si>
   <si>
     <t xml:space="preserve">27.1062107086182</t>
@@ -4409,13 +4409,13 @@
     <t xml:space="preserve">26.7028465270996</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3084411621094</t>
+    <t xml:space="preserve">26.308443069458</t>
   </si>
   <si>
     <t xml:space="preserve">25.8154373168945</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3622264862061</t>
+    <t xml:space="preserve">26.3622245788574</t>
   </si>
   <si>
     <t xml:space="preserve">26.8821182250977</t>
@@ -4424,19 +4424,19 @@
     <t xml:space="preserve">26.6938819885254</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2048110961914</t>
+    <t xml:space="preserve">27.20481300354</t>
   </si>
   <si>
     <t xml:space="preserve">27.4737224578857</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5185413360596</t>
+    <t xml:space="preserve">27.5185432434082</t>
   </si>
   <si>
     <t xml:space="preserve">27.3930492401123</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6529979705811</t>
+    <t xml:space="preserve">27.6529960632324</t>
   </si>
   <si>
     <t xml:space="preserve">27.7157421112061</t>
@@ -4451,7 +4451,7 @@
     <t xml:space="preserve">27.9667263031006</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9398365020752</t>
+    <t xml:space="preserve">27.9398345947266</t>
   </si>
   <si>
     <t xml:space="preserve">27.7605609893799</t>
@@ -4463,16 +4463,16 @@
     <t xml:space="preserve">27.4647579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3840866088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3213386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.60817527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9487991333008</t>
+    <t xml:space="preserve">27.3840847015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3213405609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6081771850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9487972259521</t>
   </si>
   <si>
     <t xml:space="preserve">28.0115451812744</t>
@@ -4502,16 +4502,16 @@
     <t xml:space="preserve">28.5045471191406</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7465648651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6927833557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7555332183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9796237945557</t>
+    <t xml:space="preserve">28.7465667724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6927852630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7555313110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9796257019043</t>
   </si>
   <si>
     <t xml:space="preserve">29.0334033966064</t>
@@ -4523,7 +4523,7 @@
     <t xml:space="preserve">29.3740253448486</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2306079864502</t>
+    <t xml:space="preserve">29.2306098937988</t>
   </si>
   <si>
     <t xml:space="preserve">29.705680847168</t>
@@ -4535,13 +4535,13 @@
     <t xml:space="preserve">30.9606018066406</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5482730865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1986808776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8132476806641</t>
+    <t xml:space="preserve">30.5482711791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1986827850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8132457733154</t>
   </si>
   <si>
     <t xml:space="preserve">29.8311710357666</t>
@@ -4550,7 +4550,7 @@
     <t xml:space="preserve">28.7734565734863</t>
   </si>
   <si>
-    <t xml:space="preserve">29.158899307251</t>
+    <t xml:space="preserve">29.1588973999023</t>
   </si>
   <si>
     <t xml:space="preserve">29.3202419281006</t>
@@ -4559,13 +4559,13 @@
     <t xml:space="preserve">29.1140804290771</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4457340240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3650608062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0871887207031</t>
+    <t xml:space="preserve">29.4457321166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3650588989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0871906280518</t>
   </si>
   <si>
     <t xml:space="preserve">28.7017478942871</t>
@@ -4583,7 +4583,7 @@
     <t xml:space="preserve">29.311279296875</t>
   </si>
   <si>
-    <t xml:space="preserve">29.571231842041</t>
+    <t xml:space="preserve">29.5712299346924</t>
   </si>
   <si>
     <t xml:space="preserve">30.1628322601318</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">29.9745922088623</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2166118621826</t>
+    <t xml:space="preserve">30.2166137695312</t>
   </si>
   <si>
     <t xml:space="preserve">30.0014839172363</t>
@@ -4604,25 +4604,25 @@
     <t xml:space="preserve">29.7773933410645</t>
   </si>
   <si>
-    <t xml:space="preserve">29.723611831665</t>
+    <t xml:space="preserve">29.7236099243164</t>
   </si>
   <si>
     <t xml:space="preserve">29.7684288024902</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1717929840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.180757522583</t>
+    <t xml:space="preserve">30.1717910766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1807556152344</t>
   </si>
   <si>
     <t xml:space="preserve">30.4586315155029</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0104503631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2703952789307</t>
+    <t xml:space="preserve">30.0104484558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.270393371582</t>
   </si>
   <si>
     <t xml:space="preserve">30.593090057373</t>
@@ -4631,19 +4631,19 @@
     <t xml:space="preserve">30.144905090332</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1538677215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0463027954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0373363494873</t>
+    <t xml:space="preserve">30.1538696289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0463047027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0373382568359</t>
   </si>
   <si>
     <t xml:space="preserve">29.696720123291</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1678619384766</t>
+    <t xml:space="preserve">29.1678600311279</t>
   </si>
   <si>
     <t xml:space="preserve">29.6877536773682</t>
@@ -4655,49 +4655,49 @@
     <t xml:space="preserve">29.4278106689453</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0552673339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7107124328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5224761962891</t>
+    <t xml:space="preserve">30.055269241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7107105255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5224742889404</t>
   </si>
   <si>
     <t xml:space="preserve">28.4776573181152</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2177085876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7426338195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3392677307129</t>
+    <t xml:space="preserve">28.2177104949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7426319122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3392658233643</t>
   </si>
   <si>
     <t xml:space="preserve">27.5095767974854</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3571949005127</t>
+    <t xml:space="preserve">27.3571968078613</t>
   </si>
   <si>
     <t xml:space="preserve">27.0524291992188</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1868858337402</t>
+    <t xml:space="preserve">27.1868839263916</t>
   </si>
   <si>
     <t xml:space="preserve">27.2854862213135</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2944507598877</t>
+    <t xml:space="preserve">27.2944488525391</t>
   </si>
   <si>
     <t xml:space="preserve">27.4468326568604</t>
   </si>
   <si>
-    <t xml:space="preserve">27.545431137085</t>
+    <t xml:space="preserve">27.5454330444336</t>
   </si>
   <si>
     <t xml:space="preserve">28.0294723510742</t>
@@ -4709,7 +4709,7 @@
     <t xml:space="preserve">28.1191082000732</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2714920043945</t>
+    <t xml:space="preserve">28.2714939117432</t>
   </si>
   <si>
     <t xml:space="preserve">28.6838226318359</t>
@@ -4724,10 +4724,10 @@
     <t xml:space="preserve">29.7325706481934</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7863540649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3919525146484</t>
+    <t xml:space="preserve">29.78635597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3919544219971</t>
   </si>
   <si>
     <t xml:space="preserve">29.4547004699707</t>
@@ -4748,10 +4748,10 @@
     <t xml:space="preserve">29.0602970123291</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1499328613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4367713928223</t>
+    <t xml:space="preserve">29.1499347686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4367733001709</t>
   </si>
   <si>
     <t xml:space="preserve">29.0961513519287</t>
@@ -4760,7 +4760,7 @@
     <t xml:space="preserve">29.24853515625</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5891513824463</t>
+    <t xml:space="preserve">29.5891532897949</t>
   </si>
   <si>
     <t xml:space="preserve">29.6070804595947</t>
@@ -4778,103 +4778,103 @@
     <t xml:space="preserve">30.4048500061035</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4317417144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3600292205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2255783081055</t>
+    <t xml:space="preserve">30.4317436218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3600311279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2255802154541</t>
   </si>
   <si>
     <t xml:space="preserve">30.1359405517578</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3152122497559</t>
+    <t xml:space="preserve">30.3152141571045</t>
   </si>
   <si>
     <t xml:space="preserve">30.3421039581299</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7454719543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3331413269043</t>
+    <t xml:space="preserve">30.7454700469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3331432342529</t>
   </si>
   <si>
     <t xml:space="preserve">30.0642318725586</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6110153198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8440685272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0860919952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1936588287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1578006744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1757259368896</t>
+    <t xml:space="preserve">30.6110172271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8440704345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.086088180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1936550140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1577987670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1757278442383</t>
   </si>
   <si>
     <t xml:space="preserve">31.3818893432617</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5522041320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8121509552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8480072021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0003890991211</t>
+    <t xml:space="preserve">31.5522003173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8121547698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8480033874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0003929138184</t>
   </si>
   <si>
     <t xml:space="preserve">31.2384719848633</t>
   </si>
   <si>
-    <t xml:space="preserve">31.713550567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7314796447754</t>
+    <t xml:space="preserve">31.7135524749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7314777374268</t>
   </si>
   <si>
     <t xml:space="preserve">31.5432395935059</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8300800323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8211097717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1258811950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0900192260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2743282318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9068183898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9785270690918</t>
+    <t xml:space="preserve">31.8300762176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8211154937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1258773803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0900268554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2743263244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9068164825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9785289764404</t>
   </si>
   <si>
     <t xml:space="preserve">30.1090507507324</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3958873748779</t>
+    <t xml:space="preserve">30.3958892822266</t>
   </si>
   <si>
     <t xml:space="preserve">30.8551139831543</t>
@@ -5943,6 +5943,9 @@
   </si>
   <si>
     <t xml:space="preserve">48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5999984741211</t>
   </si>
 </sst>
 </file>
@@ -71125,7 +71128,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.649375</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>188595</v>
@@ -71137,7 +71140,7 @@
         <v>47.3199996948242</v>
       </c>
       <c r="E2495" t="n">
-        <v>46.8800010681152</v>
+        <v>47.4799995422363</v>
       </c>
       <c r="F2495" t="n">
         <v>48.0200004577637</v>
@@ -71146,6 +71149,32 @@
         <v>1973</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.649537037</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>95739</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>48.3199996948242</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>47.560001373291</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>48.1599998474121</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>47.5999984741211</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>1977</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BGN.MI.xlsx
+++ b/data/BGN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="1978">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1979" uniqueCount="1979">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,61 +38,61 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4796009063721</t>
+    <t xml:space="preserve">17.4796028137207</t>
   </si>
   <si>
     <t xml:space="preserve">BGN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">17.294303894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7816543579102</t>
+    <t xml:space="preserve">17.2943058013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7816505432129</t>
   </si>
   <si>
     <t xml:space="preserve">16.528413772583</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2628231048584</t>
+    <t xml:space="preserve">16.262825012207</t>
   </si>
   <si>
     <t xml:space="preserve">16.3678245544434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5098838806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9422435760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6457710266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1269397735596</t>
+    <t xml:space="preserve">16.5098857879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9422416687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6457672119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1269416809082</t>
   </si>
   <si>
     <t xml:space="preserve">15.6760520935059</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9601716995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0707502365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0769290924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5092859268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.540168762207</t>
+    <t xml:space="preserve">15.9601736068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0707540512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0769262313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5092849731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5401706695557</t>
   </si>
   <si>
     <t xml:space="preserve">15.4289894104004</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6019353866577</t>
+    <t xml:space="preserve">15.6019325256348</t>
   </si>
   <si>
     <t xml:space="preserve">15.1942825317383</t>
@@ -104,34 +104,34 @@
     <t xml:space="preserve">15.2931070327759</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0213394165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8230895996094</t>
+    <t xml:space="preserve">15.0213384628296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.823091506958</t>
   </si>
   <si>
     <t xml:space="preserve">13.7180891036987</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5945568084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4580774307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6804342269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5636758804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1745548248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4154396057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0022087097168</t>
+    <t xml:space="preserve">13.5945606231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4580764770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6804323196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5636768341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1745557785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4154405593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0022106170654</t>
   </si>
   <si>
     <t xml:space="preserve">13.8477964401245</t>
@@ -140,103 +140,103 @@
     <t xml:space="preserve">14.3851566314697</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4098606109619</t>
+    <t xml:space="preserve">14.4098634719849</t>
   </si>
   <si>
     <t xml:space="preserve">14.1936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4963350296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1813316345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3233938217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3357429504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5210409164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8607492446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2436933517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5710496902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4969339370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4351673126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4413442611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3239879608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0157585144043</t>
+    <t xml:space="preserve">14.4963331222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1813287734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3233890533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3357458114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5210399627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8607482910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2436952590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5710506439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4969320297241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4351663589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4413404464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3239870071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0157623291016</t>
   </si>
   <si>
     <t xml:space="preserve">16.201057434082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2937049865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1578216552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3431167602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8489952087402</t>
+    <t xml:space="preserve">16.2937068939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1578235626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3431186676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8489942550659</t>
   </si>
   <si>
     <t xml:space="preserve">15.8922319412231</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6081075668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9354639053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9663496017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0095844268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8675260543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8298664093018</t>
+    <t xml:space="preserve">15.6081132888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9354667663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9663505554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0095825195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.867525100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8298654556274</t>
   </si>
   <si>
     <t xml:space="preserve">14.8854560852051</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6569232940674</t>
+    <t xml:space="preserve">14.6569223403931</t>
   </si>
   <si>
     <t xml:space="preserve">14.9410467147827</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3981094360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.533989906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8737020492554</t>
+    <t xml:space="preserve">15.3981056213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5339918136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8737001419067</t>
   </si>
   <si>
     <t xml:space="preserve">15.9478187561035</t>
@@ -254,40 +254,40 @@
     <t xml:space="preserve">16.1084079742432</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2072372436523</t>
+    <t xml:space="preserve">16.2072353363037</t>
   </si>
   <si>
     <t xml:space="preserve">16.0589981079102</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2998809814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1701774597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1207656860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7316408157349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3795804977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1201658248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8916320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.706335067749</t>
+    <t xml:space="preserve">16.2998790740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1701755523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1207637786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7316398620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3795785903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1201639175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8916311264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7063360214233</t>
   </si>
   <si>
     <t xml:space="preserve">14.6383953094482</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6075134277344</t>
+    <t xml:space="preserve">14.6075124740601</t>
   </si>
   <si>
     <t xml:space="preserve">14.2986841201782</t>
@@ -296,61 +296,61 @@
     <t xml:space="preserve">14.4530973434448</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6692781448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3419208526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.366626739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3913316726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3975114822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5537919998169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8142642974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9640340805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5110216140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5956735610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3742742538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3286933898926</t>
+    <t xml:space="preserve">14.6692762374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3419227600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3666286468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3913335800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3975057601929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5537910461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8142623901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9640302658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5110206604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5956716537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3742723464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3286924362183</t>
   </si>
   <si>
     <t xml:space="preserve">15.1138029098511</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0096158981323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0551986694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.211480140686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3547401428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3026437759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2570610046387</t>
+    <t xml:space="preserve">15.009614944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0551948547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2114791870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3547391891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3026447296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2570629119873</t>
   </si>
   <si>
     <t xml:space="preserve">14.8533325195312</t>
@@ -359,40 +359,40 @@
     <t xml:space="preserve">14.0979671478271</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2058553695679</t>
+    <t xml:space="preserve">13.2058563232422</t>
   </si>
   <si>
     <t xml:space="preserve">12.9649219512939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9453859329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1993436813354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6616811752319</t>
+    <t xml:space="preserve">12.945387840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1993465423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.661678314209</t>
   </si>
   <si>
     <t xml:space="preserve">13.8374977111816</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1565752029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5733261108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.87375831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6690807342529</t>
+    <t xml:space="preserve">14.1565742492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5733280181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8737564086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6690826416016</t>
   </si>
   <si>
     <t xml:space="preserve">11.7341995239258</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6560564041138</t>
+    <t xml:space="preserve">11.6560554504395</t>
   </si>
   <si>
     <t xml:space="preserve">11.6821041107178</t>
@@ -401,496 +401,496 @@
     <t xml:space="preserve">11.6039628982544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.200234413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8160390853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.431845664978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7444114685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2588386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.923038482666</t>
+    <t xml:space="preserve">11.2002334594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8160400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4318466186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7444105148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2588396072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9230403900146</t>
   </si>
   <si>
     <t xml:space="preserve">12.3137445449829</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2616500854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5286340713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5677013397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6588687896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3723516464233</t>
+    <t xml:space="preserve">12.2616510391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5286331176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5677042007446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6588706970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3723497390747</t>
   </si>
   <si>
     <t xml:space="preserve">12.5221223831177</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5416564941406</t>
+    <t xml:space="preserve">12.5416555404663</t>
   </si>
   <si>
     <t xml:space="preserve">12.3397922515869</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5025873184204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2551393508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4895648956299</t>
+    <t xml:space="preserve">12.5025863647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2551383972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4895629882812</t>
   </si>
   <si>
     <t xml:space="preserve">12.2421159744263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0337381362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8188495635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6300096511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4281454086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3825616836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8579216003418</t>
+    <t xml:space="preserve">12.0337371826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8188505172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6300115585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4281444549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3825626373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8579225540161</t>
   </si>
   <si>
     <t xml:space="preserve">11.994668006897</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1835079193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2030439376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0532732009888</t>
+    <t xml:space="preserve">12.1835088729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2030448913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0532751083374</t>
   </si>
   <si>
     <t xml:space="preserve">11.94908618927</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7928056716919</t>
+    <t xml:space="preserve">11.7928047180176</t>
   </si>
   <si>
     <t xml:space="preserve">11.525821685791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7667570114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4411687850952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3630285263062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5583791732788</t>
+    <t xml:space="preserve">11.7667560577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4411697387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3630294799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5583810806274</t>
   </si>
   <si>
     <t xml:space="preserve">11.7797794342041</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5388460159302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7472219467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6951265335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9425745010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1314153671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1379280090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4114217758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4830522537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6653823852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8021259307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3788614273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1183929443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1249055862427</t>
+    <t xml:space="preserve">11.5388450622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.747220993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6951274871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9425735473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1314144134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1379261016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4114189147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4830503463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.665379524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8021268844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3788623809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1183948516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1249046325684</t>
   </si>
   <si>
     <t xml:space="preserve">12.2876977920532</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8709440231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7016401290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8514089584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9165267944336</t>
+    <t xml:space="preserve">11.870943069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7016382217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8514099121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9165277481079</t>
   </si>
   <si>
     <t xml:space="preserve">11.2523279190063</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1937217712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1481399536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0830221176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1220922470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1741857528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1090688705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2848863601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1351175308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.076509475708</t>
+    <t xml:space="preserve">11.1937208175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.148138999939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0830202102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1220932006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.174186706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1090707778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2848854064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1351146697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0765104293823</t>
   </si>
   <si>
     <t xml:space="preserve">11.1872100830078</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0244150161743</t>
+    <t xml:space="preserve">11.0244159698486</t>
   </si>
   <si>
     <t xml:space="preserve">11.0179033279419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6430330276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5779151916504</t>
+    <t xml:space="preserve">11.6430339813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.577917098999</t>
   </si>
   <si>
     <t xml:space="preserve">11.9100151062012</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1769971847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2942113876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4309587478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9779443740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0365505218506</t>
+    <t xml:space="preserve">12.1769990921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2942085266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4309558868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9779472351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0365514755249</t>
   </si>
   <si>
     <t xml:space="preserve">13.3816738128662</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5640029907227</t>
+    <t xml:space="preserve">13.5640048980713</t>
   </si>
   <si>
     <t xml:space="preserve">13.414234161377</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1732959747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0560865402222</t>
+    <t xml:space="preserve">13.1732978820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0560855865479</t>
   </si>
   <si>
     <t xml:space="preserve">12.9258518218994</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8281755447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3295793533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7984275817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5444660186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8830795288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8309841156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9481973648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8895921707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1240158081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.492374420166</t>
+    <t xml:space="preserve">12.8281745910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3295803070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7984266281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5444679260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8830804824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8309850692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9481983184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.889591217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1240139007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4923753738403</t>
   </si>
   <si>
     <t xml:space="preserve">12.9388742446899</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9323616027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.867244720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9714317321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9909687042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7760801315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7956132888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7304964065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.74351978302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4691390991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2896213531494</t>
+    <t xml:space="preserve">12.9323625564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8672456741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9714336395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.990966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7760820388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.795615196228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7304973602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.743522644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4691400527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2896184921265</t>
   </si>
   <si>
     <t xml:space="preserve">15.8887014389038</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5761365890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3612480163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4784603118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0747337341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1854295730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8989143371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8793792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.95751953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9770555496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0031051635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.781702041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5863513946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.755654335022</t>
+    <t xml:space="preserve">15.5761384963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3612489700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4784622192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0747327804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.185432434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8989162445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8793811798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9575223922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9770574569702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0031042098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7817029953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5863485336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7556591033936</t>
   </si>
   <si>
     <t xml:space="preserve">14.8598432540894</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3417139053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4459056854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8403091430664</t>
+    <t xml:space="preserve">15.3417148590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4459018707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8403081893921</t>
   </si>
   <si>
     <t xml:space="preserve">15.2700872421265</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5305595397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4133462905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3482294082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5631160736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5138320922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6570949554443</t>
+    <t xml:space="preserve">15.530556678772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4133434295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3482265472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5631151199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5138339996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6570911407471</t>
   </si>
   <si>
     <t xml:space="preserve">16.5659255981445</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1231250762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0514965057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6803283691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7454471588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7584686279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.035662651062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3352031707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2375288009644</t>
+    <t xml:space="preserve">16.1231269836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0514945983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6803255081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7454462051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7584657669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0356636047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3352060317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2375259399414</t>
   </si>
   <si>
     <t xml:space="preserve">15.432879447937</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2208023071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2924365997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1491737365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9538202285767</t>
+    <t xml:space="preserve">16.2208042144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2924327850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1491756439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9538192749023</t>
   </si>
   <si>
     <t xml:space="preserve">16.1752223968506</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8626585006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5566005706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1593856811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2245006561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8468208312988</t>
+    <t xml:space="preserve">15.8626556396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5566024780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1593866348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2244997024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8468227386475</t>
   </si>
   <si>
     <t xml:space="preserve">15.1658973693848</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4003210067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.309157371521</t>
+    <t xml:space="preserve">15.4003248214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3091583251953</t>
   </si>
   <si>
     <t xml:space="preserve">15.6021852493286</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6217193603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6738128662109</t>
+    <t xml:space="preserve">15.6217212677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6738166809082</t>
   </si>
   <si>
     <t xml:space="preserve">15.5500907897949</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3677625656128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3938083648682</t>
+    <t xml:space="preserve">15.3677616119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3938093185425</t>
   </si>
   <si>
     <t xml:space="preserve">15.1398506164551</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1072912216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0812463760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6152057647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6282339096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5435781478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7975397109985</t>
+    <t xml:space="preserve">15.107292175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0812454223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6152095794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6282329559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5435810089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7975378036499</t>
   </si>
   <si>
     <t xml:space="preserve">15.9342880249023</t>
@@ -899,43 +899,43 @@
     <t xml:space="preserve">16.2012691497803</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4422035217285</t>
+    <t xml:space="preserve">16.4422054290771</t>
   </si>
   <si>
     <t xml:space="preserve">16.3770847320557</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2794094085693</t>
+    <t xml:space="preserve">16.279411315918</t>
   </si>
   <si>
     <t xml:space="preserve">16.1426620483398</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4812717437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6049957275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2338275909424</t>
+    <t xml:space="preserve">16.481273651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6049976348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2338256835938</t>
   </si>
   <si>
     <t xml:space="preserve">17.2561721801758</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2691974639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1584987640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1454734802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1845436096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1389617919922</t>
+    <t xml:space="preserve">17.2691993713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1584949493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1454753875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1845455169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1389636993408</t>
   </si>
   <si>
     <t xml:space="preserve">17.646879196167</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">17.6273441314697</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3892211914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1678199768066</t>
+    <t xml:space="preserve">18.3892192840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1678237915039</t>
   </si>
   <si>
     <t xml:space="preserve">18.1027011871338</t>
@@ -962,25 +962,25 @@
     <t xml:space="preserve">18.493408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0896797180176</t>
+    <t xml:space="preserve">18.0896778106689</t>
   </si>
   <si>
     <t xml:space="preserve">18.2264251708984</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8588123321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8723430633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6896438598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6422748565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.513708114624</t>
+    <t xml:space="preserve">18.8588104248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8723449707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.689640045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6422729492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5137100219727</t>
   </si>
   <si>
     <t xml:space="preserve">17.8370380401611</t>
@@ -989,16 +989,16 @@
     <t xml:space="preserve">17.6543388366699</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3836708068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9047031402588</t>
+    <t xml:space="preserve">17.3836688995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9047050476074</t>
   </si>
   <si>
     <t xml:space="preserve">17.9317684173584</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5393028259277</t>
+    <t xml:space="preserve">17.5393009185791</t>
   </si>
   <si>
     <t xml:space="preserve">17.5460681915283</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">18.6761093139648</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9264793395996</t>
+    <t xml:space="preserve">18.9264736175537</t>
   </si>
   <si>
     <t xml:space="preserve">18.8046779632568</t>
@@ -1031,25 +1031,25 @@
     <t xml:space="preserve">18.2092056274414</t>
   </si>
   <si>
-    <t xml:space="preserve">17.999439239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8641033172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.803201675415</t>
+    <t xml:space="preserve">17.9994373321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8641052246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8032035827637</t>
   </si>
   <si>
     <t xml:space="preserve">18.0062084197998</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4054412841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.060338973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6340370178223</t>
+    <t xml:space="preserve">18.4054393768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0603370666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.634033203125</t>
   </si>
   <si>
     <t xml:space="preserve">18.2430381774902</t>
@@ -1058,31 +1058,31 @@
     <t xml:space="preserve">18.2701072692871</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6490421295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4528102874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7031745910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4595718383789</t>
+    <t xml:space="preserve">18.649040222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.452808380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7031764984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4595756530762</t>
   </si>
   <si>
     <t xml:space="preserve">19.1024131774902</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9467754364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9197101593018</t>
+    <t xml:space="preserve">18.94677734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9197082519531</t>
   </si>
   <si>
     <t xml:space="preserve">18.77760887146</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8791103363037</t>
+    <t xml:space="preserve">18.8791122436523</t>
   </si>
   <si>
     <t xml:space="preserve">19.1362457275391</t>
@@ -1091,31 +1091,31 @@
     <t xml:space="preserve">19.0415115356445</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1836109161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3730773925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2918834686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8264503479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9414825439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.300121307373</t>
+    <t xml:space="preserve">19.183614730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3730812072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2918815612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8264484405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9414844512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3001194000244</t>
   </si>
   <si>
     <t xml:space="preserve">20.5166511535645</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0971164703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9956150054932</t>
+    <t xml:space="preserve">20.0971183776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9956188201904</t>
   </si>
   <si>
     <t xml:space="preserve">20.1241836547852</t>
@@ -1127,34 +1127,34 @@
     <t xml:space="preserve">20.6384525299072</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2392177581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8941173553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5625476837158</t>
+    <t xml:space="preserve">20.2392196655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8941135406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5625495910645</t>
   </si>
   <si>
     <t xml:space="preserve">19.7587833404541</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9211864471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9008865356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7993831634521</t>
+    <t xml:space="preserve">19.9211826324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9008808135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7993812561035</t>
   </si>
   <si>
     <t xml:space="preserve">19.7655487060547</t>
   </si>
   <si>
-    <t xml:space="preserve">19.812915802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4813480377197</t>
+    <t xml:space="preserve">19.8129177093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4813499450684</t>
   </si>
   <si>
     <t xml:space="preserve">19.5828475952148</t>
@@ -1163,64 +1163,64 @@
     <t xml:space="preserve">19.4881134033203</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2851123809814</t>
+    <t xml:space="preserve">19.2851161956787</t>
   </si>
   <si>
     <t xml:space="preserve">18.7640743255615</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7573070526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5949096679688</t>
+    <t xml:space="preserve">18.7573089599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5949115753174</t>
   </si>
   <si>
     <t xml:space="preserve">18.8452777862549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8655776977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5340061187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0144443511963</t>
+    <t xml:space="preserve">18.8655757904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.534008026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0144462585449</t>
   </si>
   <si>
     <t xml:space="preserve">19.2242107391357</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1700801849365</t>
+    <t xml:space="preserve">19.1700782775879</t>
   </si>
   <si>
     <t xml:space="preserve">19.2512798309326</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1971454620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4475116729736</t>
+    <t xml:space="preserve">19.1971473693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4475135803223</t>
   </si>
   <si>
     <t xml:space="preserve">19.1633129119873</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2648162841797</t>
+    <t xml:space="preserve">19.2648105621338</t>
   </si>
   <si>
     <t xml:space="preserve">19.4678134918213</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2580413818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8602809906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8670482635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0159168243408</t>
+    <t xml:space="preserve">19.2580451965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8602828979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8670520782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0159149169922</t>
   </si>
   <si>
     <t xml:space="preserve">19.4204483032227</t>
@@ -1229,22 +1229,22 @@
     <t xml:space="preserve">19.569314956665</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5490131378174</t>
+    <t xml:space="preserve">19.549015045166</t>
   </si>
   <si>
     <t xml:space="preserve">19.4272136688232</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3663120269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4136829376221</t>
+    <t xml:space="preserve">19.3663139343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4136810302734</t>
   </si>
   <si>
     <t xml:space="preserve">19.3527793884277</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5016441345215</t>
+    <t xml:space="preserve">19.5016479492188</t>
   </si>
   <si>
     <t xml:space="preserve">18.9400119781494</t>
@@ -1253,7 +1253,7 @@
     <t xml:space="preserve">18.8114433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8858795166016</t>
+    <t xml:space="preserve">18.8858776092529</t>
   </si>
   <si>
     <t xml:space="preserve">19.2783470153809</t>
@@ -1262,10 +1262,10 @@
     <t xml:space="preserve">19.1565456390381</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0685749053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2106781005859</t>
+    <t xml:space="preserve">19.0685787200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2106761932373</t>
   </si>
   <si>
     <t xml:space="preserve">19.1091766357422</t>
@@ -1277,94 +1277,94 @@
     <t xml:space="preserve">19.3324794769287</t>
   </si>
   <si>
-    <t xml:space="preserve">19.230978012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6572799682617</t>
+    <t xml:space="preserve">19.2309799194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6572780609131</t>
   </si>
   <si>
     <t xml:space="preserve">20.1106510162354</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9820823669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7858505249023</t>
+    <t xml:space="preserve">19.982084274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7858467102051</t>
   </si>
   <si>
     <t xml:space="preserve">19.5354804992676</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9482479095459</t>
+    <t xml:space="preserve">19.9482517242432</t>
   </si>
   <si>
     <t xml:space="preserve">19.5760822296143</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6166820526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5557804107666</t>
+    <t xml:space="preserve">19.6166801452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.555778503418</t>
   </si>
   <si>
     <t xml:space="preserve">19.3460140228271</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6911163330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6775817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2986469268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1903800964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3121814727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7911434173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8182067871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9670791625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7708396911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4663391113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1889038085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6084384918213</t>
+    <t xml:space="preserve">19.6911144256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6775856018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2986488342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1903781890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3121776580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7911415100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8182125091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9670753479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7708435058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4663429260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.188907623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6084423065186</t>
   </si>
   <si>
     <t xml:space="preserve">19.1497802734375</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1768474578857</t>
+    <t xml:space="preserve">19.1768436431885</t>
   </si>
   <si>
     <t xml:space="preserve">19.4745826721191</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0294532775879</t>
+    <t xml:space="preserve">20.029447555542</t>
   </si>
   <si>
     <t xml:space="preserve">20.0835838317871</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5301876068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5031204223633</t>
+    <t xml:space="preserve">20.5301895141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5031185150146</t>
   </si>
   <si>
     <t xml:space="preserve">20.8008556365967</t>
@@ -1373,73 +1373,73 @@
     <t xml:space="preserve">20.76025390625</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7196559906006</t>
+    <t xml:space="preserve">20.719654083252</t>
   </si>
   <si>
     <t xml:space="preserve">20.8685207366943</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7061176300049</t>
+    <t xml:space="preserve">20.7061233520508</t>
   </si>
   <si>
     <t xml:space="preserve">20.2459850311279</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4083843231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3136520385742</t>
+    <t xml:space="preserve">20.4083881378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3136501312256</t>
   </si>
   <si>
     <t xml:space="preserve">19.8805809020996</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8926467895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.055046081543</t>
+    <t xml:space="preserve">18.8926429748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0550441741943</t>
   </si>
   <si>
     <t xml:space="preserve">18.0265064239502</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2024421691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2565746307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5813751220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5407772064209</t>
+    <t xml:space="preserve">18.2024383544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2565727233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5813770294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5407733917236</t>
   </si>
   <si>
     <t xml:space="preserve">18.4866409301758</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4189758300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5272426605225</t>
+    <t xml:space="preserve">18.4189739227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5272388458252</t>
   </si>
   <si>
     <t xml:space="preserve">18.473108291626</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9859085083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4460430145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6625785827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5678424835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7437744140625</t>
+    <t xml:space="preserve">17.9859046936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4460411071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.662576675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5678443908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7437801361084</t>
   </si>
   <si>
     <t xml:space="preserve">18.7302436828613</t>
@@ -1448,55 +1448,55 @@
     <t xml:space="preserve">18.3783740997314</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8505706787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.755838394165</t>
+    <t xml:space="preserve">17.8505725860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7558364868164</t>
   </si>
   <si>
     <t xml:space="preserve">17.7287693023682</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9723701477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0671081542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1483097076416</t>
+    <t xml:space="preserve">17.9723720550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0671043395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1483058929443</t>
   </si>
   <si>
     <t xml:space="preserve">18.2159729003906</t>
   </si>
   <si>
-    <t xml:space="preserve">18.324239730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3513069152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.364839553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7167091369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7979106903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.906177520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1618385314941</t>
+    <t xml:space="preserve">18.3242435455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3513088226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3648414611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7167110443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.797908782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9061794281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1618366241455</t>
   </si>
   <si>
     <t xml:space="preserve">18.1212406158447</t>
   </si>
   <si>
-    <t xml:space="preserve">17.82350730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6205024719238</t>
+    <t xml:space="preserve">17.8235034942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6205062866211</t>
   </si>
   <si>
     <t xml:space="preserve">17.6611061096191</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">17.173900604248</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0521011352539</t>
+    <t xml:space="preserve">17.0521030426025</t>
   </si>
   <si>
     <t xml:space="preserve">16.7814311981201</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">16.7600536346436</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8028087615967</t>
+    <t xml:space="preserve">16.8028106689453</t>
   </si>
   <si>
     <t xml:space="preserve">16.5605297088623</t>
@@ -1523,160 +1523,160 @@
     <t xml:space="preserve">16.7030467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3039970397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2066125869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2802515029907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8503217697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8218193054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5344047546387</t>
+    <t xml:space="preserve">16.3039989471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2066135406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2802505493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8503198623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8218154907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5344018936157</t>
   </si>
   <si>
     <t xml:space="preserve">15.320629119873</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8930740356445</t>
+    <t xml:space="preserve">14.8930788040161</t>
   </si>
   <si>
     <t xml:space="preserve">15.4631443023682</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8336887359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3491334915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9477043151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8479433059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8621940612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9192028045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7054281234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7339286804199</t>
+    <t xml:space="preserve">15.8336915969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3491325378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9477062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8479423522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8621921539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9191999435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7054262161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7339305877686</t>
   </si>
   <si>
     <t xml:space="preserve">15.7196760177612</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3633832931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5059022903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4203901290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4488973617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9500827789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9358320236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.178108215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5629072189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6484174728394</t>
+    <t xml:space="preserve">15.3633823394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5058994293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.420389175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4488945007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9500799179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9358310699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1781091690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5629091262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.648416519165</t>
   </si>
   <si>
     <t xml:space="preserve">15.890697479248</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0189666748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4346418380737</t>
+    <t xml:space="preserve">16.0189647674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4346437454224</t>
   </si>
   <si>
     <t xml:space="preserve">15.3776340484619</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4916486740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5201559066772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7909355163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7766828536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6056623458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4750213623047</t>
+    <t xml:space="preserve">15.4916496276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5201530456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7909345626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.776683807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6056613922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4750175476074</t>
   </si>
   <si>
     <t xml:space="preserve">16.2469921112061</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1329784393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4465160369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5035209655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9619569778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0474662780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2184886932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2042369842529</t>
+    <t xml:space="preserve">16.1329765319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4465141296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5035247802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9619550704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0474681854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2184867858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2042350769043</t>
   </si>
   <si>
     <t xml:space="preserve">16.1614818572998</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7481813430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9049501419067</t>
+    <t xml:space="preserve">15.74817943573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9049491882324</t>
   </si>
   <si>
     <t xml:space="preserve">16.2754955291748</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4037590026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3325004577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2636203765869</t>
+    <t xml:space="preserve">16.4037609100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3325023651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2636213302612</t>
   </si>
   <si>
     <t xml:space="preserve">15.0783472061157</t>
@@ -1691,10 +1691,10 @@
     <t xml:space="preserve">15.5486555099487</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6769218444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6175365447998</t>
+    <t xml:space="preserve">15.6769208908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6175346374512</t>
   </si>
   <si>
     <t xml:space="preserve">16.7885570526123</t>
@@ -1703,58 +1703,58 @@
     <t xml:space="preserve">16.8598175048828</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3443737030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3871307373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1020946502686</t>
+    <t xml:space="preserve">17.3443756103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3871288299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1020965576172</t>
   </si>
   <si>
     <t xml:space="preserve">15.876446723938</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6911735534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6626682281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9643325805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7933130264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3515090942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2161178588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3372602462769</t>
+    <t xml:space="preserve">15.6911764144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6626691818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9643363952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7933149337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3515071868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2161159515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3372583389282</t>
   </si>
   <si>
     <t xml:space="preserve">14.7220544815063</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4227685928345</t>
+    <t xml:space="preserve">14.4227695465088</t>
   </si>
   <si>
     <t xml:space="preserve">14.05934715271</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5391597747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2042446136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7268114089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3776416778564</t>
+    <t xml:space="preserve">13.539158821106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2042417526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7268104553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3776426315308</t>
   </si>
   <si>
     <t xml:space="preserve">12.4203977584839</t>
@@ -1766,22 +1766,22 @@
     <t xml:space="preserve">12.4061450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1353607177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3705186843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9049587249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8622007369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9334602355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1472358703613</t>
+    <t xml:space="preserve">12.1353635787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3705167770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9049577713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8622016906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9334592819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.14723777771</t>
   </si>
   <si>
     <t xml:space="preserve">13.275502204895</t>
@@ -1790,7 +1790,7 @@
     <t xml:space="preserve">13.1187334060669</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0688533782959</t>
+    <t xml:space="preserve">13.0688524246216</t>
   </si>
   <si>
     <t xml:space="preserve">13.5462846755981</t>
@@ -1802,25 +1802,25 @@
     <t xml:space="preserve">12.7838172912598</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7339372634888</t>
+    <t xml:space="preserve">12.7339353561401</t>
   </si>
   <si>
     <t xml:space="preserve">12.6698045730591</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9192094802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9548397064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.246997833252</t>
+    <t xml:space="preserve">12.9192085266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9548368453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2469987869263</t>
   </si>
   <si>
     <t xml:space="preserve">13.5961675643921</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1092281341553</t>
+    <t xml:space="preserve">14.109227180481</t>
   </si>
   <si>
     <t xml:space="preserve">13.9453353881836</t>
@@ -1829,133 +1829,133 @@
     <t xml:space="preserve">13.8812017440796</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8883266448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4655227661133</t>
+    <t xml:space="preserve">13.8883285522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4655237197876</t>
   </si>
   <si>
     <t xml:space="preserve">14.2232427597046</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0878524780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3681392669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4679012298584</t>
+    <t xml:space="preserve">14.087851524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3681383132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4679021835327</t>
   </si>
   <si>
     <t xml:space="preserve">13.1258592605591</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9690914154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.489278793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6317939758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2327470779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3966436386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8265714645386</t>
+    <t xml:space="preserve">12.9690885543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4892778396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6317949295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2327461242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3966417312622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8265733718872</t>
   </si>
   <si>
     <t xml:space="preserve">12.5344114303589</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1044816970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9975919723511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6104192733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7529344558716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6389217376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1448583602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3230056762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2018642425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947412490845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8954524993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.39426612854</t>
+    <t xml:space="preserve">13.1044807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9975929260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6104202270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7529354095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6389198303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1448593139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3230075836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2018671035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947393417358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8954515457153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3942642211914</t>
   </si>
   <si>
     <t xml:space="preserve">14.593789100647</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7078008651733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.508279800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6935501098633</t>
+    <t xml:space="preserve">14.707802772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5082788467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6935520172119</t>
   </si>
   <si>
     <t xml:space="preserve">14.8075637817383</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6365442276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7648086547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7363080978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6792984008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2660007476807</t>
+    <t xml:space="preserve">14.6365461349487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7648115158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7363061904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6793003082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.265998840332</t>
   </si>
   <si>
     <t xml:space="preserve">14.5367822647095</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2944993972778</t>
+    <t xml:space="preserve">14.2945022583008</t>
   </si>
   <si>
     <t xml:space="preserve">14.5510330200195</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1923637390137</t>
+    <t xml:space="preserve">15.192361831665</t>
   </si>
   <si>
     <t xml:space="preserve">14.9785861968994</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2778720855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2493696212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2208681106567</t>
+    <t xml:space="preserve">15.2778730392456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2493686676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2208652496338</t>
   </si>
   <si>
     <t xml:space="preserve">15.406138420105</t>
@@ -1964,16 +1964,16 @@
     <t xml:space="preserve">15.8194389343262</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8051862716675</t>
+    <t xml:space="preserve">15.8051872253418</t>
   </si>
   <si>
     <t xml:space="preserve">15.634165763855</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5914096832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4322643280029</t>
+    <t xml:space="preserve">15.5914115905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4322662353516</t>
   </si>
   <si>
     <t xml:space="preserve">16.6032848358154</t>
@@ -1985,10 +1985,10 @@
     <t xml:space="preserve">16.7743053436279</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8170642852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0308380126953</t>
+    <t xml:space="preserve">16.8170623779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0308361053467</t>
   </si>
   <si>
     <t xml:space="preserve">17.1591014862061</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">17.2588653564453</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3158702850342</t>
+    <t xml:space="preserve">17.3158721923828</t>
   </si>
   <si>
     <t xml:space="preserve">17.4583892822266</t>
@@ -2006,13 +2006,13 @@
     <t xml:space="preserve">17.4726428985596</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9714546203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7861766815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9286956787109</t>
+    <t xml:space="preserve">17.9714527130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7861804962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9286975860596</t>
   </si>
   <si>
     <t xml:space="preserve">18.0569648742676</t>
@@ -2033,19 +2033,19 @@
     <t xml:space="preserve">17.4298858642578</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5296459197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4868946075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.719654083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8548011779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2991847991943</t>
+    <t xml:space="preserve">17.5296497344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4868927001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7196521759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8547992706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.299186706543</t>
   </si>
   <si>
     <t xml:space="preserve">17.2241020202637</t>
@@ -2057,13 +2057,13 @@
     <t xml:space="preserve">17.149019241333</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7435703277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8787174224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9237689971924</t>
+    <t xml:space="preserve">16.7435684204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.878719329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9237670898438</t>
   </si>
   <si>
     <t xml:space="preserve">16.6985187530518</t>
@@ -2072,16 +2072,16 @@
     <t xml:space="preserve">17.2541332244873</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5394554138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1640338897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0589160919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4343338012695</t>
+    <t xml:space="preserve">17.5394535064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1640396118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0589179992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4343357086182</t>
   </si>
   <si>
     <t xml:space="preserve">17.8247661590576</t>
@@ -2090,43 +2090,43 @@
     <t xml:space="preserve">17.9298839569092</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8397827148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.749683380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9449024200439</t>
+    <t xml:space="preserve">17.8397846221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7496852874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9448986053467</t>
   </si>
   <si>
     <t xml:space="preserve">18.665699005127</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8458976745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1762676239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3714828491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0561351776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1312198638916</t>
+    <t xml:space="preserve">18.8458995819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.17626953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3714847564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0561332702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1312160491943</t>
   </si>
   <si>
     <t xml:space="preserve">19.4165325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1462326049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0110855102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2213172912598</t>
+    <t xml:space="preserve">19.1462345123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0110836029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2213191986084</t>
   </si>
   <si>
     <t xml:space="preserve">19.7318840026855</t>
@@ -2135,13 +2135,13 @@
     <t xml:space="preserve">19.7769336700439</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7919483184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8069648742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0772647857666</t>
+    <t xml:space="preserve">19.7919502258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8069667816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0772666931152</t>
   </si>
   <si>
     <t xml:space="preserve">19.9721488952637</t>
@@ -2150,67 +2150,67 @@
     <t xml:space="preserve">20.2574653625488</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1373348236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1823825836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8970680236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.047233581543</t>
+    <t xml:space="preserve">20.1373329162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1823844909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8970642089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0472316741943</t>
   </si>
   <si>
     <t xml:space="preserve">20.1523475646973</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0172004699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6567993164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8219833374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6868324279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8369998931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9421138763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3325462341309</t>
+    <t xml:space="preserve">20.0171985626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6568012237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8219814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6868305206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8369960784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9421157836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3325500488281</t>
   </si>
   <si>
     <t xml:space="preserve">19.581714630127</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4916152954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.671817779541</t>
+    <t xml:space="preserve">19.4916172027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6718139648438</t>
   </si>
   <si>
     <t xml:space="preserve">19.7168674468994</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7619171142578</t>
+    <t xml:space="preserve">19.7619190216064</t>
   </si>
   <si>
     <t xml:space="preserve">20.2875003814697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9120826721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1223163604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0622520446777</t>
+    <t xml:space="preserve">19.9120845794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.122314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0622482299805</t>
   </si>
   <si>
     <t xml:space="preserve">20.3025150299072</t>
@@ -2219,13 +2219,13 @@
     <t xml:space="preserve">20.5728130340576</t>
   </si>
   <si>
-    <t xml:space="preserve">20.662914276123</t>
+    <t xml:space="preserve">20.6629161834717</t>
   </si>
   <si>
     <t xml:space="preserve">20.9932804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1434497833252</t>
+    <t xml:space="preserve">21.1434459686279</t>
   </si>
   <si>
     <t xml:space="preserve">21.1584625244141</t>
@@ -2234,13 +2234,13 @@
     <t xml:space="preserve">21.3536815643311</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0082988739014</t>
+    <t xml:space="preserve">21.0082950592041</t>
   </si>
   <si>
     <t xml:space="preserve">21.2635822296143</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2936134338379</t>
+    <t xml:space="preserve">21.2936153411865</t>
   </si>
   <si>
     <t xml:space="preserve">21.4287643432617</t>
@@ -2249,19 +2249,19 @@
     <t xml:space="preserve">21.6089668273926</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5338840484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9782657623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8881664276123</t>
+    <t xml:space="preserve">21.5338802337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9782676696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.888162612915</t>
   </si>
   <si>
     <t xml:space="preserve">21.233549118042</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2485637664795</t>
+    <t xml:space="preserve">21.2485675811768</t>
   </si>
   <si>
     <t xml:space="preserve">21.1734828948975</t>
@@ -2279,10 +2279,10 @@
     <t xml:space="preserve">21.0833835601807</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7980632781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8670310974121</t>
+    <t xml:space="preserve">20.7980670928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8670330047607</t>
   </si>
   <si>
     <t xml:space="preserve">20.7229843139648</t>
@@ -2291,13 +2291,13 @@
     <t xml:space="preserve">21.2035121917725</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3086318969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4888343811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5639133453369</t>
+    <t xml:space="preserve">21.308629989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4888324737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5639152526855</t>
   </si>
   <si>
     <t xml:space="preserve">21.1134166717529</t>
@@ -2306,10 +2306,10 @@
     <t xml:space="preserve">21.3837146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3236503601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5789318084717</t>
+    <t xml:space="preserve">21.3236465454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.578929901123</t>
   </si>
   <si>
     <t xml:space="preserve">21.8191967010498</t>
@@ -2324,16 +2324,16 @@
     <t xml:space="preserve">22.5850467681885</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4799308776855</t>
+    <t xml:space="preserve">22.4799289703369</t>
   </si>
   <si>
     <t xml:space="preserve">22.6601295471191</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1256446838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3208618164062</t>
+    <t xml:space="preserve">23.1256465911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3208637237549</t>
   </si>
   <si>
     <t xml:space="preserve">23.0805969238281</t>
@@ -2342,55 +2342,55 @@
     <t xml:space="preserve">23.2007293701172</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3058490753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4259796142578</t>
+    <t xml:space="preserve">23.3058471679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4259777069092</t>
   </si>
   <si>
     <t xml:space="preserve">23.6962795257568</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9215297698975</t>
+    <t xml:space="preserve">23.9215278625488</t>
   </si>
   <si>
     <t xml:space="preserve">23.7263126373291</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6662502288818</t>
+    <t xml:space="preserve">23.6662464141846</t>
   </si>
   <si>
     <t xml:space="preserve">23.9065132141113</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2908267974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3959465026855</t>
+    <t xml:space="preserve">23.290828704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3959445953369</t>
   </si>
   <si>
     <t xml:space="preserve">23.2758121490479</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0956134796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4949474334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6300964355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5249786376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0355472564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9454479217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5399990081787</t>
+    <t xml:space="preserve">23.0956153869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.494945526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6300983428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5249805450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0355453491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9454460144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5399951934814</t>
   </si>
   <si>
     <t xml:space="preserve">22.6000652313232</t>
@@ -2405,22 +2405,22 @@
     <t xml:space="preserve">22.2096309661865</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1946125030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.104513168335</t>
+    <t xml:space="preserve">22.1946144104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1045150756836</t>
   </si>
   <si>
     <t xml:space="preserve">22.1795959472656</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7290992736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0594615936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7441120147705</t>
+    <t xml:space="preserve">21.729097366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0594635009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7441139221191</t>
   </si>
   <si>
     <t xml:space="preserve">21.5939464569092</t>
@@ -2429,31 +2429,31 @@
     <t xml:space="preserve">21.2785968780518</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0294322967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7652473449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7051792144775</t>
+    <t xml:space="preserve">22.0294284820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7652454376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7051811218262</t>
   </si>
   <si>
     <t xml:space="preserve">22.99049949646</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9754810333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8102970123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8253116607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.07448387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8853759765625</t>
+    <t xml:space="preserve">22.9754829406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8102951049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8253154754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0744781494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8853797912598</t>
   </si>
   <si>
     <t xml:space="preserve">22.1645793914795</t>
@@ -2465,28 +2465,28 @@
     <t xml:space="preserve">22.8553466796875</t>
   </si>
   <si>
-    <t xml:space="preserve">22.795280456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3508949279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1017284393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4471111297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4170799255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.67236328125</t>
+    <t xml:space="preserve">22.7952766418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3508987426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1017265319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.447114944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4170761108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6723613739014</t>
   </si>
   <si>
     <t xml:space="preserve">24.6573467254639</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7774772644043</t>
+    <t xml:space="preserve">24.7774791717529</t>
   </si>
   <si>
     <t xml:space="preserve">24.3269805908203</t>
@@ -2495,43 +2495,43 @@
     <t xml:space="preserve">23.8764781951904</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2396659851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9181976318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4226493835449</t>
+    <t xml:space="preserve">22.2396678924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9181995391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4226474761963</t>
   </si>
   <si>
     <t xml:space="preserve">20.4827175140381</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0411167144775</t>
+    <t xml:space="preserve">19.0411186218262</t>
   </si>
   <si>
     <t xml:space="preserve">18.5906162261963</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9688186645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8876190185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7975168228149</t>
+    <t xml:space="preserve">16.9688167572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8876180648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7975215911865</t>
   </si>
   <si>
     <t xml:space="preserve">13.6201038360596</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6937952041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2146558761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9894065856934</t>
+    <t xml:space="preserve">14.6937980651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.214653968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9894046783447</t>
   </si>
   <si>
     <t xml:space="preserve">12.6590404510498</t>
@@ -2540,124 +2540,124 @@
     <t xml:space="preserve">13.0344562530518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7266149520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8917970657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9054222106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0180463790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.581169128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0781116485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3559188842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1982450485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.318377494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.055588722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7688770294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.46715259552</t>
+    <t xml:space="preserve">12.7266139984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8917989730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.905421257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.018045425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5811700820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0781135559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.355920791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1982460021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3183794021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0555877685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7688789367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4671545028687</t>
   </si>
   <si>
     <t xml:space="preserve">16.7886199951172</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7074184417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9026355743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9326677322388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7674865722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1518039703369</t>
+    <t xml:space="preserve">15.7074193954468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9026384353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9326667785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7674884796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1518049240112</t>
   </si>
   <si>
     <t xml:space="preserve">15.3770532608032</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4821691513062</t>
+    <t xml:space="preserve">15.4821710586548</t>
   </si>
   <si>
     <t xml:space="preserve">16.6835021972656</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8937339782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3442363739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0138683319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5333366394043</t>
+    <t xml:space="preserve">16.8937358856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3442344665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0138702392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5333385467529</t>
   </si>
   <si>
     <t xml:space="preserve">16.5033016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9087505340576</t>
+    <t xml:space="preserve">16.9087524414062</t>
   </si>
   <si>
     <t xml:space="preserve">17.4643688201904</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1039714813232</t>
+    <t xml:space="preserve">17.103967666626</t>
   </si>
   <si>
     <t xml:space="preserve">17.524435043335</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1189842224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2391166687012</t>
+    <t xml:space="preserve">17.1189861297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2391147613525</t>
   </si>
   <si>
     <t xml:space="preserve">17.1340007781982</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3892841339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4043025970459</t>
+    <t xml:space="preserve">17.3892860412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4042987823486</t>
   </si>
   <si>
     <t xml:space="preserve">17.6896190643311</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3653678894043</t>
+    <t xml:space="preserve">18.3653659820557</t>
   </si>
   <si>
     <t xml:space="preserve">18.2902851104736</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4854984283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9510173797607</t>
+    <t xml:space="preserve">18.485502243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9510154724121</t>
   </si>
   <si>
     <t xml:space="preserve">19.2813835144043</t>
@@ -2666,10 +2666,10 @@
     <t xml:space="preserve">19.8520164489746</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3414478302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5516834259033</t>
+    <t xml:space="preserve">19.3414497375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.551685333252</t>
   </si>
   <si>
     <t xml:space="preserve">18.3953990936279</t>
@@ -2681,28 +2681,28 @@
     <t xml:space="preserve">20.167366027832</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3264312744141</t>
+    <t xml:space="preserve">19.3264331817627</t>
   </si>
   <si>
     <t xml:space="preserve">19.9571323394775</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1072978973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6779308319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2663669586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5066318511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8820495605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0922832489014</t>
+    <t xml:space="preserve">20.1072998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6779327392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2663650512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5066356658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8820476531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0922813415527</t>
   </si>
   <si>
     <t xml:space="preserve">20.3475666046143</t>
@@ -2714,22 +2714,22 @@
     <t xml:space="preserve">19.5967350006104</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7107524871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9209823608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7708187103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8308849334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5666999816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0861663818359</t>
+    <t xml:space="preserve">18.7107486724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9209861755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7708168029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.830883026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5666961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0861644744873</t>
   </si>
   <si>
     <t xml:space="preserve">18.9059677124023</t>
@@ -2747,28 +2747,28 @@
     <t xml:space="preserve">19.2964000701904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5366687774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5216522216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3114166259766</t>
+    <t xml:space="preserve">19.5366649627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5216503143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3114128112793</t>
   </si>
   <si>
     <t xml:space="preserve">18.9810485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4526824951172</t>
+    <t xml:space="preserve">20.4526805877686</t>
   </si>
   <si>
     <t xml:space="preserve">20.6178646087646</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6117496490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3625831604004</t>
+    <t xml:space="preserve">19.6117534637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.362585067749</t>
   </si>
   <si>
     <t xml:space="preserve">19.6417827606201</t>
@@ -2783,13 +2783,13 @@
     <t xml:space="preserve">20.2424468994141</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7379989624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0021800994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2152004241943</t>
+    <t xml:space="preserve">20.7379970550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0021839141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2151985168457</t>
   </si>
   <si>
     <t xml:space="preserve">18.1401176452637</t>
@@ -2804,175 +2804,175 @@
     <t xml:space="preserve">20.4376640319824</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1284313201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7830505371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.497730255127</t>
+    <t xml:space="preserve">21.1284332275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7830467224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4977340698242</t>
   </si>
   <si>
     <t xml:space="preserve">21.0233154296875</t>
   </si>
   <si>
-    <t xml:space="preserve">21.413745880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3686943054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9031810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0383338928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4076290130615</t>
+    <t xml:space="preserve">21.4137496948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3686962127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9031829833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0383319854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4076309204102</t>
   </si>
   <si>
     <t xml:space="preserve">20.5427837371826</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3175354003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2124137878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4465656280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7468967437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2363338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5277652740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7140827178955</t>
+    <t xml:space="preserve">20.3175315856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2124156951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4465675354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.746898651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2363357543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5277671813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7140808105469</t>
   </si>
   <si>
     <t xml:space="preserve">21.6840476989746</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6389961242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3386631011963</t>
+    <t xml:space="preserve">21.6389980316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3386650085449</t>
   </si>
   <si>
     <t xml:space="preserve">21.6239814758301</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8642463684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3987312316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4437828063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1884994506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9092979431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8942813873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8342132568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5038471221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2546825408936</t>
+    <t xml:space="preserve">21.8642482757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3987331390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4437789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1884956359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9092960357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8942794799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8342189788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.503849029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2546806335449</t>
   </si>
   <si>
     <t xml:space="preserve">22.0444488525391</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2847118377686</t>
+    <t xml:space="preserve">22.2847137451172</t>
   </si>
   <si>
     <t xml:space="preserve">22.3447799682617</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4649124145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.69016456604</t>
+    <t xml:space="preserve">22.4649143218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6901607513428</t>
   </si>
   <si>
     <t xml:space="preserve">22.8703632354736</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6150817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5700302124023</t>
+    <t xml:space="preserve">22.6150798797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.570032119751</t>
   </si>
   <si>
     <t xml:space="preserve">22.6751480102539</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5775394439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9079036712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0430545806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0881004333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8178062438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8403301239014</t>
+    <t xml:space="preserve">22.5775375366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9079055786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0430564880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0881061553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8178043365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8403282165527</t>
   </si>
   <si>
     <t xml:space="preserve">23.1706962585449</t>
   </si>
   <si>
-    <t xml:space="preserve">23.215747833252</t>
+    <t xml:space="preserve">23.2157440185547</t>
   </si>
   <si>
     <t xml:space="preserve">23.3809280395508</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5235862731934</t>
+    <t xml:space="preserve">23.5235900878906</t>
   </si>
   <si>
     <t xml:space="preserve">23.0505638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9154148101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0730895996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2532901763916</t>
+    <t xml:space="preserve">22.915412902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0730857849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.253288269043</t>
   </si>
   <si>
     <t xml:space="preserve">23.3433876037598</t>
   </si>
   <si>
-    <t xml:space="preserve">23.29833984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8914947509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2594051361084</t>
+    <t xml:space="preserve">23.2983379364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8914985656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2594089508057</t>
   </si>
   <si>
     <t xml:space="preserve">24.0942211151123</t>
@@ -2981,16 +2981,16 @@
     <t xml:space="preserve">24.6648540496826</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5522270202637</t>
+    <t xml:space="preserve">24.5522308349609</t>
   </si>
   <si>
     <t xml:space="preserve">24.4621315002441</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7924938201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.402063369751</t>
+    <t xml:space="preserve">24.7924957275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4020614624023</t>
   </si>
   <si>
     <t xml:space="preserve">24.0491695404053</t>
@@ -2999,61 +2999,61 @@
     <t xml:space="preserve">24.4696388244629</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4245853424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1993389129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9590702056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1617984771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2293720245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.627311706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8075122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8150177001953</t>
+    <t xml:space="preserve">24.4245872497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1993370056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9590682983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1617946624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2293682098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6273155212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8075141906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8150196075439</t>
   </si>
   <si>
     <t xml:space="preserve">25.1078433990479</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2204704284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1003341674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1829299926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2955551147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5208053588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.828649520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8061199188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7385387420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7835941314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0538997650146</t>
+    <t xml:space="preserve">25.2204685211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1003360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1829261779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2955513000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5208015441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8286457061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8061218261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7385444641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.783597946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0538959503174</t>
   </si>
   <si>
     <t xml:space="preserve">25.8661861419678</t>
@@ -3062,34 +3062,34 @@
     <t xml:space="preserve">26.4893760681152</t>
   </si>
   <si>
-    <t xml:space="preserve">26.511905670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3767528533936</t>
+    <t xml:space="preserve">26.5119037628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3767547607422</t>
   </si>
   <si>
     <t xml:space="preserve">26.466854095459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6545600891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5869846343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1050567626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5180187225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1350917816162</t>
+    <t xml:space="preserve">26.65456199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.586986541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1050605773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5180130004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1350898742676</t>
   </si>
   <si>
     <t xml:space="preserve">27.3903751373291</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0149593353271</t>
+    <t xml:space="preserve">27.0149574279785</t>
   </si>
   <si>
     <t xml:space="preserve">27.037483215332</t>
@@ -3098,16 +3098,16 @@
     <t xml:space="preserve">27.2176856994629</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1951637268066</t>
+    <t xml:space="preserve">27.195161819458</t>
   </si>
   <si>
     <t xml:space="preserve">27.2251930236816</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2566204071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6845932006836</t>
+    <t xml:space="preserve">26.2566184997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6845951080322</t>
   </si>
   <si>
     <t xml:space="preserve">27.1726322174072</t>
@@ -3116,172 +3116,172 @@
     <t xml:space="preserve">27.0299777984619</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7446575164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6245269775391</t>
+    <t xml:space="preserve">26.7446594238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6245250701904</t>
   </si>
   <si>
     <t xml:space="preserve">25.8962173461914</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0163536071777</t>
+    <t xml:space="preserve">26.0163555145264</t>
   </si>
   <si>
     <t xml:space="preserve">26.3992767333984</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3542289733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5569496154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.001335144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0238628387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4217987060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2866535186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2115726470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8873176574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1125679016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3603420257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3828716278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6456565856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6231346130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7808074951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5931053161621</t>
+    <t xml:space="preserve">26.3542251586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5569534301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0013389587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0238571166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4218006134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2866516113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2115650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8873233795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.11256980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3603439331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3828678131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6456604003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6231365203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7808113098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5931015014648</t>
   </si>
   <si>
     <t xml:space="preserve">27.4204082489014</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5630645751953</t>
+    <t xml:space="preserve">27.5630664825439</t>
   </si>
   <si>
     <t xml:space="preserve">27.7883148193359</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7132339477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9534969329834</t>
+    <t xml:space="preserve">27.7132358551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9535026550293</t>
   </si>
   <si>
     <t xml:space="preserve">27.9835338592529</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2613430023193</t>
+    <t xml:space="preserve">28.2613410949707</t>
   </si>
   <si>
     <t xml:space="preserve">28.1412105560303</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2087821960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1862602233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3814792633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2012805938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0586185455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1186866760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4115047454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1698474884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3875904083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5077266693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2899856567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9145660400391</t>
+    <t xml:space="preserve">28.2087841033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.18625831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.381477355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2012748718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.058614730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1186828613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4115104675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1698513031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3875961303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5077228546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2899780273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9145679473877</t>
   </si>
   <si>
     <t xml:space="preserve">28.4190158843994</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6442737579346</t>
+    <t xml:space="preserve">28.6442680358887</t>
   </si>
   <si>
     <t xml:space="preserve">29.1923789978027</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1323108673096</t>
+    <t xml:space="preserve">29.1323127746582</t>
   </si>
   <si>
     <t xml:space="preserve">29.2148971557617</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5841999053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4865875244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4565563201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5466556549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4640693664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.87841796875</t>
+    <t xml:space="preserve">28.5842018127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4865894317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4565582275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5466575622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4640712738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8784217834473</t>
   </si>
   <si>
     <t xml:space="preserve">28.4715728759766</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4040031433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0736293792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3964900970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0285816192627</t>
+    <t xml:space="preserve">28.4039974212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.073637008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3964920043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.02858543396</t>
   </si>
   <si>
     <t xml:space="preserve">28.7644023895264</t>
@@ -3290,79 +3290,79 @@
     <t xml:space="preserve">29.6954326629639</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7179622650146</t>
+    <t xml:space="preserve">29.717960357666</t>
   </si>
   <si>
     <t xml:space="preserve">29.9432067871094</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4012184143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7240734100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5213470458984</t>
+    <t xml:space="preserve">30.4012145996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7240715026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5213527679443</t>
   </si>
   <si>
     <t xml:space="preserve">30.6940402984619</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5288543701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7090644836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4988250732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7766284942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7602233886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2107200622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4359703063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7377014160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1506576538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3083305358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3458671569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8728523254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1370334625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8592262268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0544414520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4641056060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2591972351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0342807769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6406879425049</t>
+    <t xml:space="preserve">30.5288562774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.709056854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4988212585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7766342163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7602252960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2107238769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4359741210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.737699508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1506538391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3083267211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.345874786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8728446960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1370296478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.859224319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0544395446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4640998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2592010498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0342826843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6406784057617</t>
   </si>
   <si>
     <t xml:space="preserve">28.8052806854248</t>
@@ -3371,46 +3371,46 @@
     <t xml:space="preserve">29.1265907287598</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0864238739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0583782196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9378910064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.114616394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5885410308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3596782684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3195171356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0303382873535</t>
+    <t xml:space="preserve">29.08642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0583801269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9378929138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1146125793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5885429382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3596839904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3195152282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.030345916748</t>
   </si>
   <si>
     <t xml:space="preserve">31.1508274078369</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3355865478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2632904052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1669006347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1186981201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6046085357666</t>
+    <t xml:space="preserve">31.3355827331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2632942199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.166898727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1187000274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6046047210693</t>
   </si>
   <si>
     <t xml:space="preserve">29.7531433105469</t>
@@ -3419,40 +3419,40 @@
     <t xml:space="preserve">30.4118232727051</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5644474029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5483741760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9419803619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2713203430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1829605102539</t>
+    <t xml:space="preserve">30.5644454956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5483798980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9419860839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2713222503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1829681396484</t>
   </si>
   <si>
     <t xml:space="preserve">31.1267337799072</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2150974273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2311611175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1909961700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4359188079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.202974319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1788730621338</t>
+    <t xml:space="preserve">31.2150955200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2311630249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1909980773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.435920715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2029705047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1788711547852</t>
   </si>
   <si>
     <t xml:space="preserve">30.8375568389893</t>
@@ -3461,31 +3461,31 @@
     <t xml:space="preserve">30.8616504669189</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5082149505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3475608825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2913303375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4800262451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8856067657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3997001647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9338054656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7208690643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1907062530518</t>
+    <t xml:space="preserve">30.5082130432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3475570678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2913360595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4800300598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8856048583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3997039794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9338035583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7208652496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1907024383545</t>
   </si>
   <si>
     <t xml:space="preserve">27.6807022094727</t>
@@ -3497,64 +3497,64 @@
     <t xml:space="preserve">28.0743064880371</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5803680419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9659366607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0783920288086</t>
+    <t xml:space="preserve">28.5803642272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9659404754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0783939361572</t>
   </si>
   <si>
     <t xml:space="preserve">28.8695430755615</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8374156951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8133144378662</t>
+    <t xml:space="preserve">28.8374099731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8133125305176</t>
   </si>
   <si>
     <t xml:space="preserve">28.6285591125488</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3595409393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.09446144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9579048156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3152904510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1587219238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3675727844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8936405181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.802698135376</t>
+    <t xml:space="preserve">29.3595390319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0944576263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9579029083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3152885437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1587200164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3675670623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8936443328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8026962280273</t>
   </si>
   <si>
     <t xml:space="preserve">28.2799034118652</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4106006622314</t>
+    <t xml:space="preserve">28.4106025695801</t>
   </si>
   <si>
     <t xml:space="preserve">25.9600028991699</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9974231719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9810848236084</t>
+    <t xml:space="preserve">26.9974250793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.981086730957</t>
   </si>
   <si>
     <t xml:space="preserve">25.9028205871582</t>
@@ -3563,22 +3563,22 @@
     <t xml:space="preserve">25.9273281097412</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3228454589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3623695373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8885898590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5175743103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3963661193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7102012634277</t>
+    <t xml:space="preserve">25.3228492736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3623676300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8885879516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5175762176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3963642120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7101955413818</t>
   </si>
   <si>
     <t xml:space="preserve">25.3065090179443</t>
@@ -3587,7 +3587,7 @@
     <t xml:space="preserve">25.7231121063232</t>
   </si>
   <si>
-    <t xml:space="preserve">25.821138381958</t>
+    <t xml:space="preserve">25.8211364746094</t>
   </si>
   <si>
     <t xml:space="preserve">27.1281204223633</t>
@@ -3596,16 +3596,16 @@
     <t xml:space="preserve">26.956579208374</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1444568634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7768688201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1036186218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0709381103516</t>
+    <t xml:space="preserve">27.144458770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7768669128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1036167144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0709400177002</t>
   </si>
   <si>
     <t xml:space="preserve">26.9892559051514</t>
@@ -3614,19 +3614,19 @@
     <t xml:space="preserve">27.0300998687744</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3486766815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1328639984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9041423797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5447254180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9776611328125</t>
+    <t xml:space="preserve">27.3486747741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1328659057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.904146194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5447235107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9776630401611</t>
   </si>
   <si>
     <t xml:space="preserve">27.5937366485596</t>
@@ -3635,49 +3635,49 @@
     <t xml:space="preserve">26.5481472015381</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7523632049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8830604553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8667259216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.539981842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4991340637207</t>
+    <t xml:space="preserve">26.7523670196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8830623626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8667221069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5399799346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4991359710693</t>
   </si>
   <si>
     <t xml:space="preserve">26.3439311981201</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6414260864258</t>
+    <t xml:space="preserve">25.6414279937744</t>
   </si>
   <si>
     <t xml:space="preserve">26.2377376556396</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3520965576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1152076721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9109916687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3146800994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.331018447876</t>
+    <t xml:space="preserve">26.3521003723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1152038574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9109935760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3146781921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3310165405273</t>
   </si>
   <si>
     <t xml:space="preserve">25.2738361358643</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6740989685059</t>
+    <t xml:space="preserve">25.6741008758545</t>
   </si>
   <si>
     <t xml:space="preserve">25.8048000335693</t>
@@ -3689,28 +3689,28 @@
     <t xml:space="preserve">24.9634284973145</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9913578033447</t>
+    <t xml:space="preserve">23.9913539886475</t>
   </si>
   <si>
     <t xml:space="preserve">24.3017654418945</t>
   </si>
   <si>
-    <t xml:space="preserve">25.837474822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3766098022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4256172180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5154685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4419536590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6380023956299</t>
+    <t xml:space="preserve">25.8374729156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3766040802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4256153106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5154705047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4419555664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6380043029785</t>
   </si>
   <si>
     <t xml:space="preserve">26.5073051452637</t>
@@ -3719,40 +3719,40 @@
     <t xml:space="preserve">27.5489635467529</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7698345184326</t>
+    <t xml:space="preserve">26.7698364257812</t>
   </si>
   <si>
     <t xml:space="preserve">26.4734287261963</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5743751525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6759948730469</t>
+    <t xml:space="preserve">27.5743713378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6759967803955</t>
   </si>
   <si>
     <t xml:space="preserve">27.9639358520508</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5828399658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3457145690918</t>
+    <t xml:space="preserve">27.5828380584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3457126617432</t>
   </si>
   <si>
     <t xml:space="preserve">27.5235557556152</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7274894714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5320262908936</t>
+    <t xml:space="preserve">26.7274932861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5320281982422</t>
   </si>
   <si>
     <t xml:space="preserve">26.956148147583</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2108955383301</t>
+    <t xml:space="preserve">26.2108974456787</t>
   </si>
   <si>
     <t xml:space="preserve">25.5164546966553</t>
@@ -3764,13 +3764,13 @@
     <t xml:space="preserve">22.8149127960205</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3484420776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9751358032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9250068664551</t>
+    <t xml:space="preserve">23.348445892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9751377105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9250087738037</t>
   </si>
   <si>
     <t xml:space="preserve">23.4161949157715</t>
@@ -3779,19 +3779,19 @@
     <t xml:space="preserve">23.5686340332031</t>
   </si>
   <si>
-    <t xml:space="preserve">23.356912612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.085916519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8904495239258</t>
+    <t xml:space="preserve">23.3569145202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0859146118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8904457092285</t>
   </si>
   <si>
     <t xml:space="preserve">23.6194458007812</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5093517303467</t>
+    <t xml:space="preserve">23.5093536376953</t>
   </si>
   <si>
     <t xml:space="preserve">23.3230400085449</t>
@@ -3800,43 +3800,43 @@
     <t xml:space="preserve">22.8318462371826</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7471618652344</t>
+    <t xml:space="preserve">22.747163772583</t>
   </si>
   <si>
     <t xml:space="preserve">22.713285446167</t>
   </si>
   <si>
-    <t xml:space="preserve">21.64621925354</t>
+    <t xml:space="preserve">21.6462211608887</t>
   </si>
   <si>
     <t xml:space="preserve">21.9510955810547</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2644424438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7810382843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1120052337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4592227935791</t>
+    <t xml:space="preserve">22.264440536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7810363769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1120014190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4592247009277</t>
   </si>
   <si>
     <t xml:space="preserve">22.2220973968506</t>
   </si>
   <si>
-    <t xml:space="preserve">21.307466506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.756311416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2898483276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.052038192749</t>
+    <t xml:space="preserve">21.3074684143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7563133239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2898464202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0520362854004</t>
   </si>
   <si>
     <t xml:space="preserve">23.0351009368896</t>
@@ -3848,7 +3848,7 @@
     <t xml:space="preserve">23.0096950531006</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5015659332275</t>
+    <t xml:space="preserve">22.5015678405762</t>
   </si>
   <si>
     <t xml:space="preserve">22.6116600036621</t>
@@ -3863,22 +3863,22 @@
     <t xml:space="preserve">24.0513553619385</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9327926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4239807128906</t>
+    <t xml:space="preserve">23.9327945709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4239826202393</t>
   </si>
   <si>
     <t xml:space="preserve">24.5256061553955</t>
   </si>
   <si>
-    <t xml:space="preserve">23.949728012085</t>
+    <t xml:space="preserve">23.9497299194336</t>
   </si>
   <si>
     <t xml:space="preserve">23.8565731048584</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4416046142578</t>
+    <t xml:space="preserve">23.4416027069092</t>
   </si>
   <si>
     <t xml:space="preserve">23.7888221740723</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">24.1275749206543</t>
   </si>
   <si>
-    <t xml:space="preserve">24.136043548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.500883102417</t>
+    <t xml:space="preserve">24.1360416412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5008850097656</t>
   </si>
   <si>
     <t xml:space="preserve">23.7380104064941</t>
@@ -3902,55 +3902,55 @@
     <t xml:space="preserve">22.5354423522949</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9334754943848</t>
+    <t xml:space="preserve">22.9334735870361</t>
   </si>
   <si>
     <t xml:space="preserve">22.7725696563721</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0950660705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0273170471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.255973815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.391471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9256896972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.23903465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3237266540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4422874450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.068977355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9243259429932</t>
+    <t xml:space="preserve">22.095064163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0273151397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2559719085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3914737701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.925687789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2390365600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3237228393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4422855377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0689754486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9243240356445</t>
   </si>
   <si>
     <t xml:space="preserve">23.3907909393311</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9419460296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6455364227295</t>
+    <t xml:space="preserve">22.9419441223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6455345153809</t>
   </si>
   <si>
     <t xml:space="preserve">22.730224609375</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3921566009521</t>
+    <t xml:space="preserve">21.3921585083008</t>
   </si>
   <si>
     <t xml:space="preserve">21.5022506713867</t>
@@ -3959,40 +3959,40 @@
     <t xml:space="preserve">21.3413429260254</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7908706665039</t>
+    <t xml:space="preserve">20.7908725738525</t>
   </si>
   <si>
     <t xml:space="preserve">21.0957489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6553707122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8078079223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3335590362549</t>
+    <t xml:space="preserve">20.6553688049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8078117370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3335571289062</t>
   </si>
   <si>
     <t xml:space="preserve">24.2207317352295</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2552871704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0344181060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4246635437012</t>
+    <t xml:space="preserve">23.2552890777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0344142913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4246654510498</t>
   </si>
   <si>
     <t xml:space="preserve">22.7979736328125</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4331321716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6533203125</t>
+    <t xml:space="preserve">23.4331359863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6533222198486</t>
   </si>
   <si>
     <t xml:space="preserve">24.0174808502197</t>
@@ -4004,19 +4004,19 @@
     <t xml:space="preserve">24.3477630615234</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2037925720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.79660987854</t>
+    <t xml:space="preserve">24.2037944793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7966079711914</t>
   </si>
   <si>
     <t xml:space="preserve">25.1438293457031</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8298015594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9737701416016</t>
+    <t xml:space="preserve">25.8297996520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9737682342529</t>
   </si>
   <si>
     <t xml:space="preserve">26.2871170043945</t>
@@ -4025,25 +4025,25 @@
     <t xml:space="preserve">26.3802738189697</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6265506744385</t>
+    <t xml:space="preserve">25.6265525817871</t>
   </si>
   <si>
     <t xml:space="preserve">25.7197074890137</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6858329772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3294582366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3118381500244</t>
+    <t xml:space="preserve">25.6858310699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.329460144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.311840057373</t>
   </si>
   <si>
     <t xml:space="preserve">26.9307422637939</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9053382873535</t>
+    <t xml:space="preserve">26.9053363800049</t>
   </si>
   <si>
     <t xml:space="preserve">28.1756553649902</t>
@@ -4055,55 +4055,55 @@
     <t xml:space="preserve">28.074031829834</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4551239013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2434062957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1163711547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3111553192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1671867370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4297199249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7091884613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1848049163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2779636383057</t>
+    <t xml:space="preserve">28.4551219940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2434043884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1163730621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3111572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1671829223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4297161102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7091903686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1848030090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.277961730957</t>
   </si>
   <si>
     <t xml:space="preserve">27.0069599151611</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9476795196533</t>
+    <t xml:space="preserve">26.9476833343506</t>
   </si>
   <si>
     <t xml:space="preserve">27.2864322662354</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0238990783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6675262451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4981517791748</t>
+    <t xml:space="preserve">27.0239009857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6675243377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4981536865234</t>
   </si>
   <si>
     <t xml:space="preserve">27.2610244750977</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0577754974365</t>
+    <t xml:space="preserve">27.0577774047852</t>
   </si>
   <si>
     <t xml:space="preserve">27.269495010376</t>
@@ -4112,7 +4112,7 @@
     <t xml:space="preserve">27.5574340820312</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0909652709961</t>
+    <t xml:space="preserve">28.0909633636475</t>
   </si>
   <si>
     <t xml:space="preserve">27.125524520874</t>
@@ -4121,7 +4121,7 @@
     <t xml:space="preserve">27.0916500091553</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7105541229248</t>
+    <t xml:space="preserve">26.7105560302734</t>
   </si>
   <si>
     <t xml:space="preserve">26.7952423095703</t>
@@ -4136,40 +4136,40 @@
     <t xml:space="preserve">27.4304008483887</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3203048706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1509304046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7014007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2349395751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9046516418457</t>
+    <t xml:space="preserve">27.3203086853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1509323120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7013988494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.234935760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9046535491943</t>
   </si>
   <si>
     <t xml:space="preserve">28.1925926208496</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4720630645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4635963439941</t>
+    <t xml:space="preserve">28.4720611572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4635925292969</t>
   </si>
   <si>
     <t xml:space="preserve">29.0818176269531</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2935371398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0479393005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7938747406006</t>
+    <t xml:space="preserve">29.2935352325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0479373931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7938766479492</t>
   </si>
   <si>
     <t xml:space="preserve">28.692253112793</t>
@@ -4181,49 +4181,49 @@
     <t xml:space="preserve">28.7176570892334</t>
   </si>
   <si>
-    <t xml:space="preserve">28.844690322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.836217880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8531608581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6245002746582</t>
+    <t xml:space="preserve">28.8446922302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8362197875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8531551361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6244983673096</t>
   </si>
   <si>
     <t xml:space="preserve">28.8108139038086</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8785648345947</t>
+    <t xml:space="preserve">28.8785629272461</t>
   </si>
   <si>
     <t xml:space="preserve">29.0902824401855</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8700942993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8277492523193</t>
+    <t xml:space="preserve">28.870096206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.827751159668</t>
   </si>
   <si>
     <t xml:space="preserve">28.1417770385742</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7599983215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.675313949585</t>
+    <t xml:space="preserve">28.7600002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6753120422363</t>
   </si>
   <si>
     <t xml:space="preserve">28.759183883667</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2301387786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0740280151367</t>
+    <t xml:space="preserve">28.2301406860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0740299224854</t>
   </si>
   <si>
     <t xml:space="preserve">28.1954479217529</t>
@@ -4235,10 +4235,10 @@
     <t xml:space="preserve">28.2908496856689</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.299524307251</t>
+    <t xml:space="preserve">28.3515605926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2995223999023</t>
   </si>
   <si>
     <t xml:space="preserve">28.1520843505859</t>
@@ -4247,16 +4247,16 @@
     <t xml:space="preserve">28.3081970214844</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2214698791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1434154510498</t>
+    <t xml:space="preserve">28.2214660644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1434135437012</t>
   </si>
   <si>
     <t xml:space="preserve">26.9812507629395</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1660022735596</t>
+    <t xml:space="preserve">26.1660003662109</t>
   </si>
   <si>
     <t xml:space="preserve">25.4027900695801</t>
@@ -4268,7 +4268,7 @@
     <t xml:space="preserve">24.934455871582</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0558757781982</t>
+    <t xml:space="preserve">25.0558738708496</t>
   </si>
   <si>
     <t xml:space="preserve">24.2753200531006</t>
@@ -4280,7 +4280,7 @@
     <t xml:space="preserve">25.8017425537109</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3594245910645</t>
+    <t xml:space="preserve">25.3594264984131</t>
   </si>
   <si>
     <t xml:space="preserve">25.3247375488281</t>
@@ -4292,22 +4292,22 @@
     <t xml:space="preserve">25.0125102996826</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7176342010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1686248779297</t>
+    <t xml:space="preserve">24.7176322937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1686229705811</t>
   </si>
   <si>
     <t xml:space="preserve">25.4635009765625</t>
   </si>
   <si>
-    <t xml:space="preserve">25.480842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4461536407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3073902130127</t>
+    <t xml:space="preserve">25.4808444976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4461555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3073883056641</t>
   </si>
   <si>
     <t xml:space="preserve">24.9518032073975</t>
@@ -4322,13 +4322,13 @@
     <t xml:space="preserve">26.1052913665771</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6716499328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.03590965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6196098327637</t>
+    <t xml:space="preserve">25.6716480255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0359058380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6196117401123</t>
   </si>
   <si>
     <t xml:space="preserve">26.2006931304932</t>
@@ -4337,10 +4337,10 @@
     <t xml:space="preserve">26.408842086792</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4435348510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5042419433594</t>
+    <t xml:space="preserve">26.443531036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5042400360107</t>
   </si>
   <si>
     <t xml:space="preserve">26.313440322876</t>
@@ -4349,10 +4349,10 @@
     <t xml:space="preserve">26.1833477020264</t>
   </si>
   <si>
-    <t xml:space="preserve">26.452205657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0966167449951</t>
+    <t xml:space="preserve">26.4522037506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0966186523438</t>
   </si>
   <si>
     <t xml:space="preserve">25.4721736907959</t>
@@ -4361,43 +4361,43 @@
     <t xml:space="preserve">25.6109390258789</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3767700195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3307857513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1920223236084</t>
+    <t xml:space="preserve">25.3767719268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3307838439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1920185089111</t>
   </si>
   <si>
     <t xml:space="preserve">26.0098896026611</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8104152679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5215873718262</t>
+    <t xml:space="preserve">25.8104133605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5215892791748</t>
   </si>
   <si>
     <t xml:space="preserve">26.8424835205078</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4868965148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5996437072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7297344207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1062107086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0882816314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3353328704834</t>
+    <t xml:space="preserve">26.4868984222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.599645614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.729736328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1062126159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0882835388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.335334777832</t>
   </si>
   <si>
     <t xml:space="preserve">26.4070415496826</t>
@@ -4406,52 +4406,52 @@
     <t xml:space="preserve">26.675952911377</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7028465270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.308443069458</t>
+    <t xml:space="preserve">26.702844619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3084411621094</t>
   </si>
   <si>
     <t xml:space="preserve">25.8154373168945</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3622245788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8821182250977</t>
+    <t xml:space="preserve">26.3622264862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8821201324463</t>
   </si>
   <si>
     <t xml:space="preserve">26.6938819885254</t>
   </si>
   <si>
-    <t xml:space="preserve">27.20481300354</t>
+    <t xml:space="preserve">27.2048110961914</t>
   </si>
   <si>
     <t xml:space="preserve">27.4737224578857</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5185432434082</t>
+    <t xml:space="preserve">27.5185413360596</t>
   </si>
   <si>
     <t xml:space="preserve">27.3930492401123</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6529960632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7157421112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9219074249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8860511779785</t>
+    <t xml:space="preserve">27.6529979705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7157440185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9219055175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8860549926758</t>
   </si>
   <si>
     <t xml:space="preserve">27.9667263031006</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9398345947266</t>
+    <t xml:space="preserve">27.9398365020752</t>
   </si>
   <si>
     <t xml:space="preserve">27.7605609893799</t>
@@ -4460,25 +4460,25 @@
     <t xml:space="preserve">27.6619625091553</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4647579193115</t>
+    <t xml:space="preserve">27.4647598266602</t>
   </si>
   <si>
     <t xml:space="preserve">27.3840847015381</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3213405609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6081771850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9487972259521</t>
+    <t xml:space="preserve">27.3213386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.60817527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9487991333008</t>
   </si>
   <si>
     <t xml:space="preserve">28.0115451812744</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2356376647949</t>
+    <t xml:space="preserve">28.2356357574463</t>
   </si>
   <si>
     <t xml:space="preserve">28.7644958496094</t>
@@ -4505,28 +4505,28 @@
     <t xml:space="preserve">28.7465667724609</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6927852630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7555313110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9796257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0334033966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1320037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3740253448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2306098937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.705680847168</t>
+    <t xml:space="preserve">28.6927833557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7555332183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9796237945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0334053039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.132007598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3740272521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2306079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7056827545166</t>
   </si>
   <si>
     <t xml:space="preserve">30.1000862121582</t>
@@ -4544,25 +4544,25 @@
     <t xml:space="preserve">29.8132457733154</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8311710357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7734565734863</t>
+    <t xml:space="preserve">29.8311729431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.773458480835</t>
   </si>
   <si>
     <t xml:space="preserve">29.1588973999023</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3202419281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1140804290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4457321166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3650588989258</t>
+    <t xml:space="preserve">29.3202438354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1140785217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4457340240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3650608062744</t>
   </si>
   <si>
     <t xml:space="preserve">29.0871906280518</t>
@@ -4571,7 +4571,7 @@
     <t xml:space="preserve">28.7017478942871</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9975509643555</t>
+    <t xml:space="preserve">28.9975490570068</t>
   </si>
   <si>
     <t xml:space="preserve">29.1768226623535</t>
@@ -4580,10 +4580,10 @@
     <t xml:space="preserve">29.2574977874756</t>
   </si>
   <si>
-    <t xml:space="preserve">29.311279296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5712299346924</t>
+    <t xml:space="preserve">29.3112812042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5712280273438</t>
   </si>
   <si>
     <t xml:space="preserve">30.1628322601318</t>
@@ -4592,13 +4592,13 @@
     <t xml:space="preserve">29.9745922088623</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2166137695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0014839172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0283737182617</t>
+    <t xml:space="preserve">30.2166118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.001485824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0283756256104</t>
   </si>
   <si>
     <t xml:space="preserve">29.7773933410645</t>
@@ -4607,55 +4607,55 @@
     <t xml:space="preserve">29.7236099243164</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7684288024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1717910766602</t>
+    <t xml:space="preserve">29.7684268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1717948913574</t>
   </si>
   <si>
     <t xml:space="preserve">30.1807556152344</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4586315155029</t>
+    <t xml:space="preserve">30.4586334228516</t>
   </si>
   <si>
     <t xml:space="preserve">30.0104484558105</t>
   </si>
   <si>
-    <t xml:space="preserve">30.270393371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.593090057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.144905090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1538696289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0463047027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0373382568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.696720123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1678600311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6877536773682</t>
+    <t xml:space="preserve">30.2703971862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5930881500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1449069976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1538677215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0463027954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0373363494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6967220306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1678619384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6877555847168</t>
   </si>
   <si>
     <t xml:space="preserve">29.3292102813721</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4278106689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.055269241333</t>
+    <t xml:space="preserve">29.4278087615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0552654266357</t>
   </si>
   <si>
     <t xml:space="preserve">28.7107105255127</t>
@@ -4664,13 +4664,13 @@
     <t xml:space="preserve">28.5224742889404</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4776573181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2177104949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7426319122314</t>
+    <t xml:space="preserve">28.4776592254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2177066802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7426338195801</t>
   </si>
   <si>
     <t xml:space="preserve">27.3392658233643</t>
@@ -4679,52 +4679,52 @@
     <t xml:space="preserve">27.5095767974854</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3571968078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0524291992188</t>
+    <t xml:space="preserve">27.3571949005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0524311065674</t>
   </si>
   <si>
     <t xml:space="preserve">27.1868839263916</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2854862213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2944488525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4468326568604</t>
+    <t xml:space="preserve">27.2854843139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2944507598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4468307495117</t>
   </si>
   <si>
     <t xml:space="preserve">27.5454330444336</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0294723510742</t>
+    <t xml:space="preserve">28.0294742584229</t>
   </si>
   <si>
     <t xml:space="preserve">28.4059467315674</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1191082000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2714939117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6838226318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4955825805664</t>
+    <t xml:space="preserve">28.1191101074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2714920043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6838207244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.495584487915</t>
   </si>
   <si>
     <t xml:space="preserve">29.0423717498779</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7325706481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.78635597229</t>
+    <t xml:space="preserve">29.732572555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7863540649414</t>
   </si>
   <si>
     <t xml:space="preserve">29.3919544219971</t>
@@ -4739,19 +4739,19 @@
     <t xml:space="preserve">29.194751739502</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8989505767822</t>
+    <t xml:space="preserve">28.8989524841309</t>
   </si>
   <si>
     <t xml:space="preserve">29.2664623260498</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0602970123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1499347686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4367733001709</t>
+    <t xml:space="preserve">29.0602951049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1499328613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4367713928223</t>
   </si>
   <si>
     <t xml:space="preserve">29.0961513519287</t>
@@ -4760,46 +4760,46 @@
     <t xml:space="preserve">29.24853515625</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5891532897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6070804595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7953205108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2883224487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0731906890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4048500061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4317436218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3600311279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2255802154541</t>
+    <t xml:space="preserve">29.5891513824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6070823669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7953224182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2883243560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0731925964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4048480987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4317417144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3600330352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2255764007568</t>
   </si>
   <si>
     <t xml:space="preserve">30.1359405517578</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3152141571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3421039581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7454700469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3331432342529</t>
+    <t xml:space="preserve">30.3152122497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3421020507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7454719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3331394195557</t>
   </si>
   <si>
     <t xml:space="preserve">30.0642318725586</t>
@@ -4808,121 +4808,121 @@
     <t xml:space="preserve">30.6110172271729</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8440704345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.086088180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1936550140381</t>
+    <t xml:space="preserve">30.8440723419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0860919952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1936588287354</t>
   </si>
   <si>
     <t xml:space="preserve">31.1577987670898</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1757278442383</t>
+    <t xml:space="preserve">31.1757259368896</t>
   </si>
   <si>
     <t xml:space="preserve">31.3818893432617</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5522003173828</t>
+    <t xml:space="preserve">31.5522079467773</t>
   </si>
   <si>
     <t xml:space="preserve">31.8121547698975</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8480033874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0003929138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2384719848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7135524749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7314777374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5432395935059</t>
+    <t xml:space="preserve">31.8480072021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0003852844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2384738922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.713550567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7314796447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5432357788086</t>
   </si>
   <si>
     <t xml:space="preserve">31.8300762176514</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8211154937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1258773803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0900268554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2743263244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9068164825439</t>
+    <t xml:space="preserve">31.821117401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1258811950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0900230407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2743301391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9068183898926</t>
   </si>
   <si>
     <t xml:space="preserve">30.9785289764404</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1090507507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3958892822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8551139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3069000244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6632423400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.430736541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2895965576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.96067237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.57692527771</t>
+    <t xml:space="preserve">30.1090469360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3958873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8551158905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3069019317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6632404327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4307384490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2896003723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9606704711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5769271850586</t>
   </si>
   <si>
     <t xml:space="preserve">31.3667774200439</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2114524841309</t>
+    <t xml:space="preserve">31.2114505767822</t>
   </si>
   <si>
     <t xml:space="preserve">31.3941860198975</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4764194488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6957015991211</t>
+    <t xml:space="preserve">31.4764213562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6957035064697</t>
   </si>
   <si>
     <t xml:space="preserve">31.8601665496826</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9698123931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.978946685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9241218566895</t>
+    <t xml:space="preserve">31.9698085784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9789447784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9241237640381</t>
   </si>
   <si>
     <t xml:space="preserve">32.6550750732422</t>
@@ -4940,7 +4940,7 @@
     <t xml:space="preserve">33.0205459594727</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2672386169434</t>
+    <t xml:space="preserve">33.2672424316406</t>
   </si>
   <si>
     <t xml:space="preserve">33.3677444458008</t>
@@ -4952,55 +4952,55 @@
     <t xml:space="preserve">33.7423553466797</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7971801757812</t>
+    <t xml:space="preserve">33.797176361084</t>
   </si>
   <si>
     <t xml:space="preserve">33.7514915466309</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6418495178223</t>
+    <t xml:space="preserve">33.6418533325195</t>
   </si>
   <si>
     <t xml:space="preserve">32.947452545166</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2946472167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3311996459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2398338317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4042930603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0936393737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6368026733398</t>
+    <t xml:space="preserve">33.2946510314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3311958312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2398300170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.404296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0936431884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6367988586426</t>
   </si>
   <si>
     <t xml:space="preserve">32.4175148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3809661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.613468170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8144798278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5819778442383</t>
+    <t xml:space="preserve">32.3809623718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6134700775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8144836425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.581974029541</t>
   </si>
   <si>
     <t xml:space="preserve">32.5454292297363</t>
   </si>
   <si>
-    <t xml:space="preserve">33.130184173584</t>
+    <t xml:space="preserve">33.1301879882812</t>
   </si>
   <si>
     <t xml:space="preserve">33.075366973877</t>
@@ -5012,7 +5012,7 @@
     <t xml:space="preserve">33.1850090026855</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4408378601074</t>
+    <t xml:space="preserve">33.4408416748047</t>
   </si>
   <si>
     <t xml:space="preserve">33.7697639465332</t>
@@ -5024,7 +5024,7 @@
     <t xml:space="preserve">34.4093437194824</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8844604492188</t>
+    <t xml:space="preserve">34.884464263916</t>
   </si>
   <si>
     <t xml:space="preserve">35.4692192077637</t>
@@ -5039,28 +5039,28 @@
     <t xml:space="preserve">37.0955772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9128456115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0590286254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7849197387695</t>
+    <t xml:space="preserve">36.912841796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0590324401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7849273681641</t>
   </si>
   <si>
     <t xml:space="preserve">37.0985145568848</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9844818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1555252075195</t>
+    <t xml:space="preserve">36.9844779968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1555290222168</t>
   </si>
   <si>
     <t xml:space="preserve">37.1365280151367</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3265762329102</t>
+    <t xml:space="preserve">37.3265800476074</t>
   </si>
   <si>
     <t xml:space="preserve">37.0224914550781</t>
@@ -5084,7 +5084,7 @@
     <t xml:space="preserve">36.4523315429688</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8704490661621</t>
+    <t xml:space="preserve">36.8704452514648</t>
   </si>
   <si>
     <t xml:space="preserve">36.9084625244141</t>
@@ -5093,10 +5093,10 @@
     <t xml:space="preserve">36.5853691101074</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5473556518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0912284851074</t>
+    <t xml:space="preserve">36.5473594665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0912246704102</t>
   </si>
   <si>
     <t xml:space="preserve">36.5663642883301</t>
@@ -5105,7 +5105,7 @@
     <t xml:space="preserve">35.7301254272461</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0839424133301</t>
+    <t xml:space="preserve">35.0839385986328</t>
   </si>
   <si>
     <t xml:space="preserve">35.1219520568848</t>
@@ -5120,7 +5120,7 @@
     <t xml:space="preserve">35.7491302490234</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3572998046875</t>
+    <t xml:space="preserve">36.3573036193848</t>
   </si>
   <si>
     <t xml:space="preserve">36.0722198486328</t>
@@ -5129,13 +5129,13 @@
     <t xml:space="preserve">35.8821678161621</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7871398925781</t>
+    <t xml:space="preserve">35.7871437072754</t>
   </si>
   <si>
     <t xml:space="preserve">35.5970878601074</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9201774597168</t>
+    <t xml:space="preserve">35.9201812744141</t>
   </si>
   <si>
     <t xml:space="preserve">35.9391860961914</t>
@@ -5147,13 +5147,13 @@
     <t xml:space="preserve">35.8631629943848</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9011764526367</t>
+    <t xml:space="preserve">35.9011726379395</t>
   </si>
   <si>
     <t xml:space="preserve">36.3763084411621</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8514442443848</t>
+    <t xml:space="preserve">36.8514404296875</t>
   </si>
   <si>
     <t xml:space="preserve">37.2885704040527</t>
@@ -5177,7 +5177,7 @@
     <t xml:space="preserve">38.3718757629395</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4478950500488</t>
+    <t xml:space="preserve">38.4478988647461</t>
   </si>
   <si>
     <t xml:space="preserve">38.5429229736328</t>
@@ -5189,7 +5189,7 @@
     <t xml:space="preserve">37.7446975708008</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6423873901367</t>
+    <t xml:space="preserve">36.6423835754395</t>
   </si>
   <si>
     <t xml:space="preserve">35.4450454711914</t>
@@ -5201,7 +5201,7 @@
     <t xml:space="preserve">35.8061485290527</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6921195983887</t>
+    <t xml:space="preserve">35.6921157836914</t>
   </si>
   <si>
     <t xml:space="preserve">36.1862564086914</t>
@@ -5210,7 +5210,7 @@
     <t xml:space="preserve">36.4903450012207</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8894538879395</t>
+    <t xml:space="preserve">36.8894577026367</t>
   </si>
   <si>
     <t xml:space="preserve">37.8017120361328</t>
@@ -5222,16 +5222,16 @@
     <t xml:space="preserve">37.7827072143555</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6876792907715</t>
+    <t xml:space="preserve">37.6876831054688</t>
   </si>
   <si>
     <t xml:space="preserve">37.9727592468262</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9917678833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3338623046875</t>
+    <t xml:space="preserve">37.9917640686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3338661193848</t>
   </si>
   <si>
     <t xml:space="preserve">38.4098815917969</t>
@@ -5246,7 +5246,7 @@
     <t xml:space="preserve">37.7066879272461</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2198333740234</t>
+    <t xml:space="preserve">38.2198295593262</t>
   </si>
   <si>
     <t xml:space="preserve">38.0107727050781</t>
@@ -5255,10 +5255,10 @@
     <t xml:space="preserve">38.2768478393555</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2578392028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.238842010498</t>
+    <t xml:space="preserve">38.2578430175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2388381958008</t>
   </si>
   <si>
     <t xml:space="preserve">38.5809326171875</t>
@@ -5276,7 +5276,7 @@
     <t xml:space="preserve">39.0940780639648</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5999412536621</t>
+    <t xml:space="preserve">38.5999374389648</t>
   </si>
   <si>
     <t xml:space="preserve">37.7256927490234</t>
@@ -5297,7 +5297,7 @@
     <t xml:space="preserve">39.4741897583008</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8162841796875</t>
+    <t xml:space="preserve">39.8162879943848</t>
   </si>
   <si>
     <t xml:space="preserve">39.9493217468262</t>
@@ -5315,7 +5315,7 @@
     <t xml:space="preserve">39.6452369689941</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3981666564941</t>
+    <t xml:space="preserve">39.3981628417969</t>
   </si>
   <si>
     <t xml:space="preserve">39.3601531982422</t>
@@ -5342,10 +5342,10 @@
     <t xml:space="preserve">38.5619316101074</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9873352050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8923072814941</t>
+    <t xml:space="preserve">39.9873313903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8923034667969</t>
   </si>
   <si>
     <t xml:space="preserve">40.1773834228516</t>
@@ -5372,10 +5372,10 @@
     <t xml:space="preserve">40.9946174621582</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3557205200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5267715454102</t>
+    <t xml:space="preserve">41.3557243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5267677307129</t>
   </si>
   <si>
     <t xml:space="preserve">41.3747291564941</t>
@@ -5387,13 +5387,13 @@
     <t xml:space="preserve">41.6978187561035</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1349411010742</t>
+    <t xml:space="preserve">42.1349449157715</t>
   </si>
   <si>
     <t xml:space="preserve">42.0209121704102</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7548294067383</t>
+    <t xml:space="preserve">41.7548332214355</t>
   </si>
   <si>
     <t xml:space="preserve">42.3820114135742</t>
@@ -5402,7 +5402,7 @@
     <t xml:space="preserve">42.4390258789062</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4580345153809</t>
+    <t xml:space="preserve">42.4580307006836</t>
   </si>
   <si>
     <t xml:space="preserve">42.2869834899902</t>
@@ -5420,7 +5420,7 @@
     <t xml:space="preserve">43.5223350524902</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8761520385742</t>
+    <t xml:space="preserve">42.876148223877</t>
   </si>
   <si>
     <t xml:space="preserve">42.9521751403809</t>
@@ -5432,7 +5432,7 @@
     <t xml:space="preserve">43.0852088928223</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3059921264648</t>
+    <t xml:space="preserve">42.3059883117676</t>
   </si>
   <si>
     <t xml:space="preserve">42.7431144714355</t>
@@ -5453,13 +5453,13 @@
     <t xml:space="preserve">42.9901847839355</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8951568603516</t>
+    <t xml:space="preserve">42.8951530456543</t>
   </si>
   <si>
     <t xml:space="preserve">43.7123908996582</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4653205871582</t>
+    <t xml:space="preserve">43.4653167724609</t>
   </si>
   <si>
     <t xml:space="preserve">44.0354804992676</t>
@@ -5477,19 +5477,19 @@
     <t xml:space="preserve">46.6202163696289</t>
   </si>
   <si>
-    <t xml:space="preserve">46.639217376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6962356567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.582202911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7722587585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2781143188477</t>
+    <t xml:space="preserve">46.6392211914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.696231842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5821990966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7722549438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2781181335449</t>
   </si>
   <si>
     <t xml:space="preserve">46.1070671081543</t>
@@ -5498,7 +5498,7 @@
     <t xml:space="preserve">45.8219871520996</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0310440063477</t>
+    <t xml:space="preserve">46.0310478210449</t>
   </si>
   <si>
     <t xml:space="preserve">45.7839736938477</t>
@@ -5540,7 +5540,7 @@
     <t xml:space="preserve">48.9388694763184</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8438415527344</t>
+    <t xml:space="preserve">48.8438453674316</t>
   </si>
   <si>
     <t xml:space="preserve">48.7963256835938</t>
@@ -5946,6 +5946,9 @@
   </si>
   <si>
     <t xml:space="preserve">47.5999984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0400009155273</t>
   </si>
 </sst>
 </file>
@@ -71154,7 +71157,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.649537037</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>95739</v>
@@ -71175,6 +71178,32 @@
         <v>1977</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.6494097222</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>99217</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>48.0999984741211</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>47.3800010681152</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>47.8600006103516</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>48.0400009155273</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>1978</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BGN.MI.xlsx
+++ b/data/BGN.MI.xlsx
@@ -44,73 +44,73 @@
     <t xml:space="preserve">BGN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2943058013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7816505432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.528413772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.262825012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3678245544434</t>
+    <t xml:space="preserve">17.2943077087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7816524505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5284156799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2628231048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.367826461792</t>
   </si>
   <si>
     <t xml:space="preserve">16.5098857879639</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9422416687012</t>
+    <t xml:space="preserve">16.9422435760498</t>
   </si>
   <si>
     <t xml:space="preserve">16.6457672119141</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1269416809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6760520935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9601736068726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0707540512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0769262313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5092849731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5401706695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4289894104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6019325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1942825317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4784021377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2931070327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0213384628296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.823091506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7180891036987</t>
+    <t xml:space="preserve">16.1269397735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6760492324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9601745605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0707530975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0769271850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5092878341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.540168762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.428991317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6019334793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1942796707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.478401184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2931089401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0213375091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8230895996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.718090057373</t>
   </si>
   <si>
     <t xml:space="preserve">13.5945606231689</t>
@@ -122,127 +122,127 @@
     <t xml:space="preserve">12.6804323196411</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5636768341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1745557785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4154405593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0022106170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8477964401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3851566314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4098634719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1936836242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4963331222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1813287734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3233890533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3357458114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5210399627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8607482910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2436952590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5710506439209</t>
+    <t xml:space="preserve">13.5636777877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1745529174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4154386520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0022096633911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8477983474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.385157585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4098615646362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1936845779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4963350296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1813335418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3233909606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3357448577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5210409164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8607501983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2436971664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5710535049438</t>
   </si>
   <si>
     <t xml:space="preserve">15.4969320297241</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4351663589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4413404464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3239870071411</t>
+    <t xml:space="preserve">15.4351634979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4413433074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3239879608154</t>
   </si>
   <si>
     <t xml:space="preserve">16.0157623291016</t>
   </si>
   <si>
-    <t xml:space="preserve">16.201057434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2937068939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1578235626221</t>
+    <t xml:space="preserve">16.2010593414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2937030792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1578254699707</t>
   </si>
   <si>
     <t xml:space="preserve">16.3431186676025</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8489942550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8922319412231</t>
+    <t xml:space="preserve">15.8489952087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8922300338745</t>
   </si>
   <si>
     <t xml:space="preserve">15.6081132888794</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9354667663574</t>
+    <t xml:space="preserve">15.9354658126831</t>
   </si>
   <si>
     <t xml:space="preserve">15.9663505554199</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0095825195312</t>
+    <t xml:space="preserve">16.0095844268799</t>
   </si>
   <si>
     <t xml:space="preserve">15.867525100708</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8298654556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8854560852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6569223403931</t>
+    <t xml:space="preserve">14.8298645019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8854551315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6569213867188</t>
   </si>
   <si>
     <t xml:space="preserve">14.9410467147827</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3981056213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5339918136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8737001419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9478187561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1145877838135</t>
+    <t xml:space="preserve">15.3981065750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.533992767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.873703956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9478206634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1145896911621</t>
   </si>
   <si>
     <t xml:space="preserve">16.083703994751</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">16.0713500976562</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1084079742432</t>
+    <t xml:space="preserve">16.1084098815918</t>
   </si>
   <si>
     <t xml:space="preserve">16.2072353363037</t>
@@ -260,88 +260,88 @@
     <t xml:space="preserve">16.0589981079102</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2998790740967</t>
+    <t xml:space="preserve">16.2998809814453</t>
   </si>
   <si>
     <t xml:space="preserve">16.1701755523682</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1207637786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7316398620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3795785903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1201639175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8916311264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7063360214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6383953094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6075124740601</t>
+    <t xml:space="preserve">16.1207618713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7316379547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.379581451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1201648712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8916320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7063369750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6383972167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6075096130371</t>
   </si>
   <si>
     <t xml:space="preserve">14.2986841201782</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4530973434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6692762374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3419227600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3666286468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3913335800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3975057601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5537910461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8142623901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9640302658081</t>
+    <t xml:space="preserve">14.4530982971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6692771911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3419198989868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3666248321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3913307189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3975105285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5537939071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8142652511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9640331268311</t>
   </si>
   <si>
     <t xml:space="preserve">15.5110206604004</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5956716537476</t>
+    <t xml:space="preserve">15.5956735610962</t>
   </si>
   <si>
     <t xml:space="preserve">15.3742723464966</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3286924362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1138029098511</t>
+    <t xml:space="preserve">15.3286933898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1138048171997</t>
   </si>
   <si>
     <t xml:space="preserve">15.009614944458</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0551948547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2114791870117</t>
+    <t xml:space="preserve">15.0551977157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2114810943604</t>
   </si>
   <si>
     <t xml:space="preserve">15.3547391891479</t>
@@ -350,73 +350,73 @@
     <t xml:space="preserve">15.3026447296143</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2570629119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8533325195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0979671478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2058563232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9649219512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.945387840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1993465423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.661678314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8374977111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1565742492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5733280181885</t>
+    <t xml:space="preserve">15.257061958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8533315658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0979690551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2058572769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9649200439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9453859329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1993446350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6616802215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8374967575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1565752029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5733270645142</t>
   </si>
   <si>
     <t xml:space="preserve">12.8737564086914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6690826416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7341995239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6560554504395</t>
+    <t xml:space="preserve">11.6690788269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7341966629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6560592651367</t>
   </si>
   <si>
     <t xml:space="preserve">11.6821041107178</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6039628982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2002334594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8160400390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4318466186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7444105148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2588396072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9230403900146</t>
+    <t xml:space="preserve">11.6039619445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2002353668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8160419464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.431845664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7444086074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2588386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.923038482666</t>
   </si>
   <si>
     <t xml:space="preserve">12.3137445449829</t>
@@ -428,52 +428,52 @@
     <t xml:space="preserve">12.5286331176758</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5677042007446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6588706970215</t>
+    <t xml:space="preserve">12.567702293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6588697433472</t>
   </si>
   <si>
     <t xml:space="preserve">12.3723497390747</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5221223831177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5416555404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3397922515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5025863647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2551383972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4895629882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2421159744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0337371826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8188505172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6300115585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4281444549561</t>
+    <t xml:space="preserve">12.5221214294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5416564941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3397903442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5025882720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2551422119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4895620346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.242115020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0337390899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8188495635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6300106048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4281454086304</t>
   </si>
   <si>
     <t xml:space="preserve">11.3825626373291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8579225540161</t>
+    <t xml:space="preserve">11.8579206466675</t>
   </si>
   <si>
     <t xml:space="preserve">11.994668006897</t>
@@ -482,133 +482,133 @@
     <t xml:space="preserve">12.1835088729858</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2030448913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0532751083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.94908618927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7928047180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.525821685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7667560577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4411697387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3630294799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5583810806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7797794342041</t>
+    <t xml:space="preserve">12.2030429840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.053277015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9490852355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7928037643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5258226394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7667570114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4411659240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3630285263062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5583801269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7797813415527</t>
   </si>
   <si>
     <t xml:space="preserve">11.5388450622559</t>
   </si>
   <si>
-    <t xml:space="preserve">11.747220993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6951274871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9425735473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1314144134521</t>
+    <t xml:space="preserve">11.7472229003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6951265335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9425745010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1314153671265</t>
   </si>
   <si>
     <t xml:space="preserve">12.1379261016846</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4114189147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4830503463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.665379524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8021268844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3788623809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1183948516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1249046325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2876977920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.870943069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7016382217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8514099121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9165277481079</t>
+    <t xml:space="preserve">12.4114208221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4830532073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6653804779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8021278381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3788633346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1183938980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1249055862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2876996994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8709468841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.701639175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.851411819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9165267944336</t>
   </si>
   <si>
     <t xml:space="preserve">11.2523279190063</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1937208175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.148138999939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0830202102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1220932006836</t>
+    <t xml:space="preserve">11.1937227249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1481409072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0830211639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.122091293335</t>
   </si>
   <si>
     <t xml:space="preserve">11.174186706543</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1090707778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2848854064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1351146697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0765104293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1872100830078</t>
+    <t xml:space="preserve">11.1090688705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2848863601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1351156234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.076509475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1872081756592</t>
   </si>
   <si>
     <t xml:space="preserve">11.0244159698486</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0179033279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6430339813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.577917098999</t>
+    <t xml:space="preserve">11.0179042816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6430330276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5779161453247</t>
   </si>
   <si>
     <t xml:space="preserve">11.9100151062012</t>
@@ -623,34 +623,34 @@
     <t xml:space="preserve">12.4309558868408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9779472351074</t>
+    <t xml:space="preserve">12.9779453277588</t>
   </si>
   <si>
     <t xml:space="preserve">13.0365514755249</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3816738128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5640048980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.414234161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1732978820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0560855865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9258518218994</t>
+    <t xml:space="preserve">13.3816728591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5640020370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.414231300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1732959747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0560865402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9258508682251</t>
   </si>
   <si>
     <t xml:space="preserve">12.8281745910645</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3295803070068</t>
+    <t xml:space="preserve">13.3295812606812</t>
   </si>
   <si>
     <t xml:space="preserve">13.7984266281128</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">13.5444679260254</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8830804824829</t>
+    <t xml:space="preserve">13.8830814361572</t>
   </si>
   <si>
     <t xml:space="preserve">13.8309850692749</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">13.9481983184814</t>
   </si>
   <si>
-    <t xml:space="preserve">13.889591217041</t>
+    <t xml:space="preserve">13.8895893096924</t>
   </si>
   <si>
     <t xml:space="preserve">14.1240139007568</t>
@@ -680,19 +680,19 @@
     <t xml:space="preserve">12.9388742446899</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9323625564575</t>
+    <t xml:space="preserve">12.9323635101318</t>
   </si>
   <si>
     <t xml:space="preserve">12.8672456741333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9714336395264</t>
+    <t xml:space="preserve">12.9714317321777</t>
   </si>
   <si>
     <t xml:space="preserve">12.990966796875</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7760820388794</t>
+    <t xml:space="preserve">12.7760801315308</t>
   </si>
   <si>
     <t xml:space="preserve">12.795615196228</t>
@@ -701,82 +701,82 @@
     <t xml:space="preserve">12.7304973602295</t>
   </si>
   <si>
-    <t xml:space="preserve">12.743522644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4691400527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2896184921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8887014389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5761384963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3612489700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4784622192383</t>
+    <t xml:space="preserve">12.74351978302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4691371917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2896203994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8887062072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5761413574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3612499237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4784631729126</t>
   </si>
   <si>
     <t xml:space="preserve">15.0747327804565</t>
   </si>
   <si>
-    <t xml:space="preserve">15.185432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8989162445068</t>
+    <t xml:space="preserve">15.1854295730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8989124298096</t>
   </si>
   <si>
     <t xml:space="preserve">14.8793811798096</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9575223922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9770574569702</t>
+    <t xml:space="preserve">14.9575204849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9770565032959</t>
   </si>
   <si>
     <t xml:space="preserve">15.0031042098999</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7817029953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5863485336304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7556591033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8598432540894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3417148590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4459018707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8403081893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2700872421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.530556678772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4133434295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3482265472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5631151199341</t>
+    <t xml:space="preserve">14.7817039489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5863513946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7556562423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.859845161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3417158126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4459009170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8403100967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2700862884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5305585861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4133443832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3482255935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5631113052368</t>
   </si>
   <si>
     <t xml:space="preserve">16.5138339996338</t>
@@ -785,43 +785,43 @@
     <t xml:space="preserve">16.6570911407471</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5659255981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1231269836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0514945983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6803255081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7454462051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7584657669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0356636047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3352060317993</t>
+    <t xml:space="preserve">16.5659294128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1231250762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0514965057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6803274154663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7454423904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7584686279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0356607437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3352012634277</t>
   </si>
   <si>
     <t xml:space="preserve">15.2375259399414</t>
   </si>
   <si>
-    <t xml:space="preserve">15.432879447937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2208042144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2924327850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1491756439209</t>
+    <t xml:space="preserve">15.4328813552856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2208023071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2924308776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1491737365723</t>
   </si>
   <si>
     <t xml:space="preserve">15.9538192749023</t>
@@ -833,22 +833,22 @@
     <t xml:space="preserve">15.8626556396484</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5566024780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1593866348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2244997024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8468227386475</t>
+    <t xml:space="preserve">15.5566034317017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1593885421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2245035171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8468198776245</t>
   </si>
   <si>
     <t xml:space="preserve">15.1658973693848</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4003248214722</t>
+    <t xml:space="preserve">15.4003200531006</t>
   </si>
   <si>
     <t xml:space="preserve">15.3091583251953</t>
@@ -857,19 +857,19 @@
     <t xml:space="preserve">15.6021852493286</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6217212677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6738166809082</t>
+    <t xml:space="preserve">15.6217203140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6738128662109</t>
   </si>
   <si>
     <t xml:space="preserve">15.5500907897949</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3677616119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3938093185425</t>
+    <t xml:space="preserve">15.3677635192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3938064575195</t>
   </si>
   <si>
     <t xml:space="preserve">15.1398506164551</t>
@@ -878,64 +878,64 @@
     <t xml:space="preserve">15.107292175293</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0812454223633</t>
+    <t xml:space="preserve">15.0812435150146</t>
   </si>
   <si>
     <t xml:space="preserve">15.6152095794678</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6282329559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5435810089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7975378036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9342880249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2012691497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4422054290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3770847320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.279411315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1426620483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.481273651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6049976348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2338256835938</t>
+    <t xml:space="preserve">15.6282320022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5435771942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7975406646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9342851638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.201265335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4422016143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3770866394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2794094085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1426639556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4812717437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6049995422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2338275909424</t>
   </si>
   <si>
     <t xml:space="preserve">17.2561721801758</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2691993713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1584949493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1454753875732</t>
+    <t xml:space="preserve">17.2691955566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1584968566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.145471572876</t>
   </si>
   <si>
     <t xml:space="preserve">17.1845455169678</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1389636993408</t>
+    <t xml:space="preserve">17.1389617919922</t>
   </si>
   <si>
     <t xml:space="preserve">17.646879196167</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">17.6273441314697</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3892192840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1678237915039</t>
+    <t xml:space="preserve">18.3892211914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1678218841553</t>
   </si>
   <si>
     <t xml:space="preserve">18.1027011871338</t>
@@ -959,49 +959,49 @@
     <t xml:space="preserve">18.1352634429932</t>
   </si>
   <si>
-    <t xml:space="preserve">18.493408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0896778106689</t>
+    <t xml:space="preserve">18.4934062957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0896797180176</t>
   </si>
   <si>
     <t xml:space="preserve">18.2264251708984</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8588104248047</t>
+    <t xml:space="preserve">18.8588085174561</t>
   </si>
   <si>
     <t xml:space="preserve">18.8723449707031</t>
   </si>
   <si>
-    <t xml:space="preserve">18.689640045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6422729492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5137100219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8370380401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6543388366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3836688995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9047050476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9317684173584</t>
+    <t xml:space="preserve">18.6896419525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6422748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.513708114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8370399475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6543350219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3836650848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9047031402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.931770324707</t>
   </si>
   <si>
     <t xml:space="preserve">17.5393009185791</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5460681915283</t>
+    <t xml:space="preserve">17.546070098877</t>
   </si>
   <si>
     <t xml:space="preserve">17.9926719665527</t>
@@ -1010,10 +1010,10 @@
     <t xml:space="preserve">18.6761093139648</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9264736175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8046779632568</t>
+    <t xml:space="preserve">18.926477432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8046760559082</t>
   </si>
   <si>
     <t xml:space="preserve">18.9806098937988</t>
@@ -1022,10 +1022,10 @@
     <t xml:space="preserve">18.6219749450684</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0400409698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3377742767334</t>
+    <t xml:space="preserve">18.0400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3377723693848</t>
   </si>
   <si>
     <t xml:space="preserve">18.2092056274414</t>
@@ -1040,76 +1040,76 @@
     <t xml:space="preserve">17.8032035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0062084197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4054393768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0603370666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.634033203125</t>
+    <t xml:space="preserve">18.0062065124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4054412841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0603408813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6340351104736</t>
   </si>
   <si>
     <t xml:space="preserve">18.2430381774902</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2701072692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.649040222168</t>
+    <t xml:space="preserve">18.2701110839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6490440368652</t>
   </si>
   <si>
     <t xml:space="preserve">18.452808380127</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7031764984131</t>
+    <t xml:space="preserve">18.7031745910645</t>
   </si>
   <si>
     <t xml:space="preserve">18.4595756530762</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1024131774902</t>
+    <t xml:space="preserve">19.102409362793</t>
   </si>
   <si>
     <t xml:space="preserve">18.94677734375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9197082519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.77760887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8791122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1362457275391</t>
+    <t xml:space="preserve">18.9197101593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7776126861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8791103363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1362476348877</t>
   </si>
   <si>
     <t xml:space="preserve">19.0415115356445</t>
   </si>
   <si>
-    <t xml:space="preserve">19.183614730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3730812072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2918815612793</t>
+    <t xml:space="preserve">19.1836128234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3730792999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2918796539307</t>
   </si>
   <si>
     <t xml:space="preserve">19.8264484405518</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9414844512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3001194000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5166511535645</t>
+    <t xml:space="preserve">19.9414825439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3001174926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5166530609131</t>
   </si>
   <si>
     <t xml:space="preserve">20.0971183776855</t>
@@ -1124,16 +1124,16 @@
     <t xml:space="preserve">20.1444854736328</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6384525299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2392196655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8941135406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5625495910645</t>
+    <t xml:space="preserve">20.6384544372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2392177581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8941173553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5625476837158</t>
   </si>
   <si>
     <t xml:space="preserve">19.7587833404541</t>
@@ -1145,85 +1145,85 @@
     <t xml:space="preserve">19.9008808135986</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7993812561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7655487060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8129177093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4813499450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5828475952148</t>
+    <t xml:space="preserve">19.7993850708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7655506134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.812915802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4813480377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5828495025635</t>
   </si>
   <si>
     <t xml:space="preserve">19.4881134033203</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2851161956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7640743255615</t>
+    <t xml:space="preserve">19.2851142883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7640762329102</t>
   </si>
   <si>
     <t xml:space="preserve">18.7573089599609</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5949115753174</t>
+    <t xml:space="preserve">18.5949077606201</t>
   </si>
   <si>
     <t xml:space="preserve">18.8452777862549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8655757904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.534008026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0144462585449</t>
+    <t xml:space="preserve">18.8655776977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5340061187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0144443511963</t>
   </si>
   <si>
     <t xml:space="preserve">19.2242107391357</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1700782775879</t>
+    <t xml:space="preserve">19.1700801849365</t>
   </si>
   <si>
     <t xml:space="preserve">19.2512798309326</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1971473693848</t>
+    <t xml:space="preserve">19.1971454620361</t>
   </si>
   <si>
     <t xml:space="preserve">19.4475135803223</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1633129119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2648105621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4678134918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2580451965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8602828979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8670520782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0159149169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4204483032227</t>
+    <t xml:space="preserve">19.1633110046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2648124694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4678153991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2580432891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8602848052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8670501708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0159168243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4204502105713</t>
   </si>
   <si>
     <t xml:space="preserve">19.569314956665</t>
@@ -1232,25 +1232,25 @@
     <t xml:space="preserve">19.549015045166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4272136688232</t>
+    <t xml:space="preserve">19.4272155761719</t>
   </si>
   <si>
     <t xml:space="preserve">19.3663139343262</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4136810302734</t>
+    <t xml:space="preserve">19.4136772155762</t>
   </si>
   <si>
     <t xml:space="preserve">19.3527793884277</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5016479492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9400119781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8114433288574</t>
+    <t xml:space="preserve">19.5016498565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9400100708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8114414215088</t>
   </si>
   <si>
     <t xml:space="preserve">18.8858776092529</t>
@@ -1262,106 +1262,106 @@
     <t xml:space="preserve">19.1565456390381</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0685787200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2106761932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1091766357422</t>
+    <t xml:space="preserve">19.0685768127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2106800079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1091804504395</t>
   </si>
   <si>
     <t xml:space="preserve">19.3189468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3324794769287</t>
+    <t xml:space="preserve">19.3324813842773</t>
   </si>
   <si>
     <t xml:space="preserve">19.2309799194336</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6572780609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1106510162354</t>
+    <t xml:space="preserve">19.657283782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1106491088867</t>
   </si>
   <si>
     <t xml:space="preserve">19.982084274292</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7858467102051</t>
+    <t xml:space="preserve">19.7858486175537</t>
   </si>
   <si>
     <t xml:space="preserve">19.5354804992676</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9482517242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5760822296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6166801452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.555778503418</t>
+    <t xml:space="preserve">19.9482498168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5760803222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6166820526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5557804107666</t>
   </si>
   <si>
     <t xml:space="preserve">19.3460140228271</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6911144256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6775856018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2986488342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1903781890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3121776580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7911415100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8182125091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9670753479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7708435058594</t>
+    <t xml:space="preserve">19.6911163330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6775817871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2986450195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1903800964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3121814727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7911434173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8182106018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.967077255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7708415985107</t>
   </si>
   <si>
     <t xml:space="preserve">18.4663429260254</t>
   </si>
   <si>
-    <t xml:space="preserve">18.188907623291</t>
+    <t xml:space="preserve">18.1889057159424</t>
   </si>
   <si>
     <t xml:space="preserve">18.6084423065186</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1497802734375</t>
+    <t xml:space="preserve">19.1497783660889</t>
   </si>
   <si>
     <t xml:space="preserve">19.1768436431885</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4745826721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.029447555542</t>
+    <t xml:space="preserve">19.4745807647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0294494628906</t>
   </si>
   <si>
     <t xml:space="preserve">20.0835838317871</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5301895141602</t>
+    <t xml:space="preserve">20.5301856994629</t>
   </si>
   <si>
     <t xml:space="preserve">20.5031185150146</t>
@@ -1370,28 +1370,28 @@
     <t xml:space="preserve">20.8008556365967</t>
   </si>
   <si>
-    <t xml:space="preserve">20.76025390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.719654083252</t>
+    <t xml:space="preserve">20.7602558135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7196559906006</t>
   </si>
   <si>
     <t xml:space="preserve">20.8685207366943</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7061233520508</t>
+    <t xml:space="preserve">20.7061214447021</t>
   </si>
   <si>
     <t xml:space="preserve">20.2459850311279</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4083881378174</t>
+    <t xml:space="preserve">20.4083862304688</t>
   </si>
   <si>
     <t xml:space="preserve">20.3136501312256</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8805809020996</t>
+    <t xml:space="preserve">19.8805828094482</t>
   </si>
   <si>
     <t xml:space="preserve">18.8926429748535</t>
@@ -1400,31 +1400,31 @@
     <t xml:space="preserve">19.0550441741943</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0265064239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2024383544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2565727233887</t>
+    <t xml:space="preserve">18.0265026092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2024402618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2565746307373</t>
   </si>
   <si>
     <t xml:space="preserve">18.5813770294189</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5407733917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4866409301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4189739227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5272388458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.473108291626</t>
+    <t xml:space="preserve">18.5407752990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4866428375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4189720153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5272407531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4731044769287</t>
   </si>
   <si>
     <t xml:space="preserve">17.9859046936035</t>
@@ -1436,103 +1436,103 @@
     <t xml:space="preserve">18.662576675415</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5678443908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7437801361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7302436828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3783740997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8505725860596</t>
+    <t xml:space="preserve">18.5678424835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7437782287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7302417755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3783721923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8505687713623</t>
   </si>
   <si>
     <t xml:space="preserve">17.7558364868164</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7287693023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9723720550537</t>
+    <t xml:space="preserve">17.7287731170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9723701477051</t>
   </si>
   <si>
     <t xml:space="preserve">18.0671043395996</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1483058929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2159729003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3242435455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3513088226318</t>
+    <t xml:space="preserve">18.148307800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2159748077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.324239730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3513069152832</t>
   </si>
   <si>
     <t xml:space="preserve">18.3648414611816</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7167110443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.797908782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9061794281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1618366241455</t>
+    <t xml:space="preserve">18.7167091369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7979106903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.906177520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1618404388428</t>
   </si>
   <si>
     <t xml:space="preserve">18.1212406158447</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8235034942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6205062866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6611061096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.173900604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0521030426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7814311981201</t>
+    <t xml:space="preserve">17.8235054016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6205043792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6611042022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1738986968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0520973205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7814331054688</t>
   </si>
   <si>
     <t xml:space="preserve">16.7600536346436</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8028106689453</t>
+    <t xml:space="preserve">16.8028087615967</t>
   </si>
   <si>
     <t xml:space="preserve">16.5605297088623</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7030467987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3039989471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2066135406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2802505493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8503198623657</t>
+    <t xml:space="preserve">16.7030487060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3039951324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2066106796265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2802495956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.85032081604</t>
   </si>
   <si>
     <t xml:space="preserve">14.8218154907227</t>
@@ -1541,37 +1541,37 @@
     <t xml:space="preserve">15.5344018936157</t>
   </si>
   <si>
-    <t xml:space="preserve">15.320629119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8930788040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4631443023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8336915969849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3491325378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9477062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8479423522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8621921539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9191999435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7054262161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7339305877686</t>
+    <t xml:space="preserve">15.3206272125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8930759429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4631462097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8336887359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3491344451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9477043151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8479442596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8621940612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9192008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7054243087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7339286804199</t>
   </si>
   <si>
     <t xml:space="preserve">15.7196760177612</t>
@@ -1586,22 +1586,22 @@
     <t xml:space="preserve">15.420389175415</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4488945007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9500799179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9358310699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1781091690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5629091262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.648416519165</t>
+    <t xml:space="preserve">15.4488964080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9500827789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.935830116272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.178111076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5629072189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6484174728394</t>
   </si>
   <si>
     <t xml:space="preserve">15.890697479248</t>
@@ -1610,43 +1610,43 @@
     <t xml:space="preserve">16.0189647674561</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4346437454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3776340484619</t>
+    <t xml:space="preserve">15.434642791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3776359558105</t>
   </si>
   <si>
     <t xml:space="preserve">15.4916496276855</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5201530456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7909345626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.776683807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6056613922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4750175476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2469921112061</t>
+    <t xml:space="preserve">15.52015209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7909336090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7766857147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6056604385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4750194549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2469902038574</t>
   </si>
   <si>
     <t xml:space="preserve">16.1329765319824</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4465141296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5035247802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9619550704956</t>
+    <t xml:space="preserve">16.4465160369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5035209655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9619569778442</t>
   </si>
   <si>
     <t xml:space="preserve">16.0474681854248</t>
@@ -1655,94 +1655,94 @@
     <t xml:space="preserve">16.2184867858887</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2042350769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1614818572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.74817943573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9049491882324</t>
+    <t xml:space="preserve">16.2042331695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1614799499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7481803894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9049510955811</t>
   </si>
   <si>
     <t xml:space="preserve">16.2754955291748</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4037609100342</t>
+    <t xml:space="preserve">16.4037590026855</t>
   </si>
   <si>
     <t xml:space="preserve">16.3325023651123</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2636213302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0783472061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3063764572144</t>
+    <t xml:space="preserve">15.2636222839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0783491134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3063745498657</t>
   </si>
   <si>
     <t xml:space="preserve">15.2921228408813</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5486555099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6769208908081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6175346374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7885570526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8598175048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3443756103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3871288299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1020965576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.876446723938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6911764144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6626691818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9643363952637</t>
+    <t xml:space="preserve">15.548659324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6769247055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6175327301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7885589599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8598155975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3443794250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.387134552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1020946502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8764457702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6911706924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6626710891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.964334487915</t>
   </si>
   <si>
     <t xml:space="preserve">14.7933149337769</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3515071868896</t>
+    <t xml:space="preserve">14.351508140564</t>
   </si>
   <si>
     <t xml:space="preserve">14.2161159515381</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3372583389282</t>
+    <t xml:space="preserve">14.3372592926025</t>
   </si>
   <si>
     <t xml:space="preserve">14.7220544815063</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4227695465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.05934715271</t>
+    <t xml:space="preserve">14.4227666854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0593481063843</t>
   </si>
   <si>
     <t xml:space="preserve">13.539158821106</t>
@@ -1754,10 +1754,10 @@
     <t xml:space="preserve">12.7268104553223</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3776426315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4203977584839</t>
+    <t xml:space="preserve">12.3776416778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4203958511353</t>
   </si>
   <si>
     <t xml:space="preserve">12.285005569458</t>
@@ -1766,37 +1766,37 @@
     <t xml:space="preserve">12.4061450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1353635787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3705167770386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9049577713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8622016906738</t>
+    <t xml:space="preserve">12.1353626251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3705158233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.904956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8622026443481</t>
   </si>
   <si>
     <t xml:space="preserve">12.9334592819214</t>
   </si>
   <si>
-    <t xml:space="preserve">13.14723777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.275502204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1187334060669</t>
+    <t xml:space="preserve">13.1472368240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2755012512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1187324523926</t>
   </si>
   <si>
     <t xml:space="preserve">13.0688524246216</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5462846755981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1116065979004</t>
+    <t xml:space="preserve">13.5462856292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1116075515747</t>
   </si>
   <si>
     <t xml:space="preserve">12.7838172912598</t>
@@ -1805,52 +1805,52 @@
     <t xml:space="preserve">12.7339353561401</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6698045730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9192085266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9548368453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2469987869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5961675643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.109227180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9453353881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8812017440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8883285522461</t>
+    <t xml:space="preserve">12.6698036193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9192094802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9548387527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2470006942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5961666107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1092290878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9453325271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8812026977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8883256912231</t>
   </si>
   <si>
     <t xml:space="preserve">14.4655237197876</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2232427597046</t>
+    <t xml:space="preserve">14.223240852356</t>
   </si>
   <si>
     <t xml:space="preserve">14.087851524353</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3681383132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4679021835327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1258592605591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9690885543823</t>
+    <t xml:space="preserve">13.3681373596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4679012298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1258583068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9690914154053</t>
   </si>
   <si>
     <t xml:space="preserve">13.4892778396606</t>
@@ -1859,121 +1859,121 @@
     <t xml:space="preserve">13.6317949295044</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2327461242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3966417312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8265733718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5344114303589</t>
+    <t xml:space="preserve">13.2327470779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3966407775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8265724182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5344123840332</t>
   </si>
   <si>
     <t xml:space="preserve">13.1044807434082</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9975929260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6104202270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7529354095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6389198303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1448593139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3230075836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2018671035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947393417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8954515457153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3942642211914</t>
+    <t xml:space="preserve">12.9975919723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6104192733765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7529335021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6389207839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1448583602905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3230047225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2018661499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947383880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.895453453064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3942651748657</t>
   </si>
   <si>
     <t xml:space="preserve">14.593789100647</t>
   </si>
   <si>
-    <t xml:space="preserve">14.707802772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5082788467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6935520172119</t>
+    <t xml:space="preserve">14.7078018188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.508279800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6935501098633</t>
   </si>
   <si>
     <t xml:space="preserve">14.8075637817383</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6365461349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7648115158081</t>
+    <t xml:space="preserve">14.6365451812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7648105621338</t>
   </si>
   <si>
     <t xml:space="preserve">14.7363061904907</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6793003082275</t>
+    <t xml:space="preserve">14.6792974472046</t>
   </si>
   <si>
     <t xml:space="preserve">14.265998840332</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5367822647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2945022583008</t>
+    <t xml:space="preserve">14.5367832183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2944993972778</t>
   </si>
   <si>
     <t xml:space="preserve">14.5510330200195</t>
   </si>
   <si>
-    <t xml:space="preserve">15.192361831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9785861968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2778730392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2493686676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2208652496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.406138420105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8194389343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8051872253418</t>
+    <t xml:space="preserve">15.1923627853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9785852432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2778739929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2493715286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2208681106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.406135559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8194408416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8051853179932</t>
   </si>
   <si>
     <t xml:space="preserve">15.634165763855</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5914115905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4322662353516</t>
+    <t xml:space="preserve">15.5914106369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4322624206543</t>
   </si>
   <si>
     <t xml:space="preserve">16.6032848358154</t>
@@ -1982,28 +1982,28 @@
     <t xml:space="preserve">16.7172985076904</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7743053436279</t>
+    <t xml:space="preserve">16.7743072509766</t>
   </si>
   <si>
     <t xml:space="preserve">16.8170623779297</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0308361053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1591014862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2588653564453</t>
+    <t xml:space="preserve">17.030834197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1591033935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2588634490967</t>
   </si>
   <si>
     <t xml:space="preserve">17.3158721923828</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4583892822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4726428985596</t>
+    <t xml:space="preserve">17.4583873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4726409912109</t>
   </si>
   <si>
     <t xml:space="preserve">17.9714527130127</t>
@@ -2012,46 +2012,46 @@
     <t xml:space="preserve">17.7861804962158</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9286975860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0569648742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0854663848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5581512451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5866565704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2018585205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4298858642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5296497344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4868927001953</t>
+    <t xml:space="preserve">17.9286956787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0569610595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0854644775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5581493377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5866546630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2018566131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4298839569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5296440124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4868946075439</t>
   </si>
   <si>
     <t xml:space="preserve">17.7196521759033</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8547992706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.299186706543</t>
+    <t xml:space="preserve">17.8548011779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2991847991943</t>
   </si>
   <si>
     <t xml:space="preserve">17.2241020202637</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2691535949707</t>
+    <t xml:space="preserve">17.2691516876221</t>
   </si>
   <si>
     <t xml:space="preserve">17.149019241333</t>
@@ -2063,61 +2063,61 @@
     <t xml:space="preserve">16.878719329834</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9237670898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6985187530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2541332244873</t>
+    <t xml:space="preserve">16.9237689971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6985206604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2541351318359</t>
   </si>
   <si>
     <t xml:space="preserve">17.5394535064697</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1640396118164</t>
+    <t xml:space="preserve">17.1640357971191</t>
   </si>
   <si>
     <t xml:space="preserve">17.0589179992676</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4343357086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8247661590576</t>
+    <t xml:space="preserve">17.4343338012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8247699737549</t>
   </si>
   <si>
     <t xml:space="preserve">17.9298839569092</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8397846221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7496852874756</t>
+    <t xml:space="preserve">17.8397827148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7496814727783</t>
   </si>
   <si>
     <t xml:space="preserve">17.9448986053467</t>
   </si>
   <si>
-    <t xml:space="preserve">18.665699005127</t>
+    <t xml:space="preserve">18.6657028198242</t>
   </si>
   <si>
     <t xml:space="preserve">18.8458995819092</t>
   </si>
   <si>
-    <t xml:space="preserve">19.17626953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3714847564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0561332702637</t>
+    <t xml:space="preserve">19.1762676239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3714809417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.056131362915</t>
   </si>
   <si>
     <t xml:space="preserve">19.1312160491943</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4165325164795</t>
+    <t xml:space="preserve">19.4165344238281</t>
   </si>
   <si>
     <t xml:space="preserve">19.1462345123291</t>
@@ -2126,22 +2126,22 @@
     <t xml:space="preserve">19.0110836029053</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2213191986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7318840026855</t>
+    <t xml:space="preserve">19.2213153839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7318859100342</t>
   </si>
   <si>
     <t xml:space="preserve">19.7769336700439</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7919502258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8069667816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0772666931152</t>
+    <t xml:space="preserve">19.7919521331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8069629669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0772647857666</t>
   </si>
   <si>
     <t xml:space="preserve">19.9721488952637</t>
@@ -2153,58 +2153,58 @@
     <t xml:space="preserve">20.1373329162598</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1823844909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8970642089844</t>
+    <t xml:space="preserve">20.1823806762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.897066116333</t>
   </si>
   <si>
     <t xml:space="preserve">20.0472316741943</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1523475646973</t>
+    <t xml:space="preserve">20.1523494720459</t>
   </si>
   <si>
     <t xml:space="preserve">20.0171985626221</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6568012237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8219814300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6868305206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8369960784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9421157836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3325500488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.581714630127</t>
+    <t xml:space="preserve">19.6567993164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8219833374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6868324279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8369998931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9421138763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3325481414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5817165374756</t>
   </si>
   <si>
     <t xml:space="preserve">19.4916172027588</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6718139648438</t>
+    <t xml:space="preserve">19.671817779541</t>
   </si>
   <si>
     <t xml:space="preserve">19.7168674468994</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7619190216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2875003814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9120845794678</t>
+    <t xml:space="preserve">19.7619152069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2874965667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9120807647705</t>
   </si>
   <si>
     <t xml:space="preserve">20.122314453125</t>
@@ -2216,16 +2216,16 @@
     <t xml:space="preserve">20.3025150299072</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5728130340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6629161834717</t>
+    <t xml:space="preserve">20.5728149414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.662914276123</t>
   </si>
   <si>
     <t xml:space="preserve">20.9932804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1434459686279</t>
+    <t xml:space="preserve">21.1434478759766</t>
   </si>
   <si>
     <t xml:space="preserve">21.1584625244141</t>
@@ -2234,73 +2234,73 @@
     <t xml:space="preserve">21.3536815643311</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0082950592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2635822296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2936153411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4287643432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6089668273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5338802337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9782676696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.888162612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.233549118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2485675811768</t>
+    <t xml:space="preserve">21.00830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2635803222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2936172485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4287662506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6089649200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5338821411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9782657623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8881664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2335510253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2485656738281</t>
   </si>
   <si>
     <t xml:space="preserve">21.1734828948975</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6478996276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6328830718994</t>
+    <t xml:space="preserve">20.6478977203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6328811645508</t>
   </si>
   <si>
     <t xml:space="preserve">20.7680320739746</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0833835601807</t>
+    <t xml:space="preserve">21.0833797454834</t>
   </si>
   <si>
     <t xml:space="preserve">20.7980670928955</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8670330047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7229843139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2035121917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.308629989624</t>
+    <t xml:space="preserve">19.8670310974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7229804992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2035160064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3086318969727</t>
   </si>
   <si>
     <t xml:space="preserve">21.4888324737549</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5639152526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1134166717529</t>
+    <t xml:space="preserve">21.5639133453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1134147644043</t>
   </si>
   <si>
     <t xml:space="preserve">21.3837146759033</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">21.578929901123</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8191967010498</t>
+    <t xml:space="preserve">21.8191947937012</t>
   </si>
   <si>
     <t xml:space="preserve">21.8492317199707</t>
@@ -2321,7 +2321,7 @@
     <t xml:space="preserve">21.9543476104736</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5850467681885</t>
+    <t xml:space="preserve">22.5850486755371</t>
   </si>
   <si>
     <t xml:space="preserve">22.4799289703369</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">23.1256465911865</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3208637237549</t>
+    <t xml:space="preserve">23.3208618164062</t>
   </si>
   <si>
     <t xml:space="preserve">23.0805969238281</t>
@@ -2345,49 +2345,49 @@
     <t xml:space="preserve">23.3058471679688</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4259777069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6962795257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9215278625488</t>
+    <t xml:space="preserve">23.4259834289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6962757110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9215297698975</t>
   </si>
   <si>
     <t xml:space="preserve">23.7263126373291</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6662464141846</t>
+    <t xml:space="preserve">23.6662483215332</t>
   </si>
   <si>
     <t xml:space="preserve">23.9065132141113</t>
   </si>
   <si>
-    <t xml:space="preserve">23.290828704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3959445953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2758121490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0956153869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.494945526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6300983428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5249805450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0355453491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9454460144043</t>
+    <t xml:space="preserve">23.2908306121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3959465026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2758102416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0956134796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4949474334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6300964355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5249786376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0355472564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9454479217529</t>
   </si>
   <si>
     <t xml:space="preserve">22.5399951934814</t>
@@ -2405,79 +2405,79 @@
     <t xml:space="preserve">22.2096309661865</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1946144104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1045150756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1795959472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.729097366333</t>
+    <t xml:space="preserve">22.1946125030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.104513168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1795978546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7291011810303</t>
   </si>
   <si>
     <t xml:space="preserve">22.0594635009766</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7441139221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5939464569092</t>
+    <t xml:space="preserve">21.7441120147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5939483642578</t>
   </si>
   <si>
     <t xml:space="preserve">21.2785968780518</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0294284820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7652454376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7051811218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.99049949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9754829406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8102951049805</t>
+    <t xml:space="preserve">22.0294303894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7652473449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7051830291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9904975891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9754791259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8102970123291</t>
   </si>
   <si>
     <t xml:space="preserve">22.8253154754639</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0744781494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8853797912598</t>
+    <t xml:space="preserve">22.0744819641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8853816986084</t>
   </si>
   <si>
     <t xml:space="preserve">22.1645793914795</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2997303009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8553466796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7952766418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3508987426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1017265319824</t>
+    <t xml:space="preserve">22.299732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8553447723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7952823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3508949279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1017284393311</t>
   </si>
   <si>
     <t xml:space="preserve">24.447114944458</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4170761108398</t>
+    <t xml:space="preserve">24.4170799255371</t>
   </si>
   <si>
     <t xml:space="preserve">24.6723613739014</t>
@@ -2486,28 +2486,28 @@
     <t xml:space="preserve">24.6573467254639</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7774791717529</t>
+    <t xml:space="preserve">24.7774753570557</t>
   </si>
   <si>
     <t xml:space="preserve">24.3269805908203</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8764781951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2396678924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9181995391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4226474761963</t>
+    <t xml:space="preserve">23.8764801025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2396640777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9181976318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4226493835449</t>
   </si>
   <si>
     <t xml:space="preserve">20.4827175140381</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0411186218262</t>
+    <t xml:space="preserve">19.0411167144775</t>
   </si>
   <si>
     <t xml:space="preserve">18.5906162261963</t>
@@ -2516,37 +2516,37 @@
     <t xml:space="preserve">16.9688167572021</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8876180648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7975215911865</t>
+    <t xml:space="preserve">15.8876209259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7975225448608</t>
   </si>
   <si>
     <t xml:space="preserve">13.6201038360596</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6937980651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.214653968811</t>
+    <t xml:space="preserve">14.6937942504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2146549224854</t>
   </si>
   <si>
     <t xml:space="preserve">12.9894046783447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6590404510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0344562530518</t>
+    <t xml:space="preserve">12.6590394973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0344552993774</t>
   </si>
   <si>
     <t xml:space="preserve">12.7266139984131</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8917989730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.905421257019</t>
+    <t xml:space="preserve">12.8917980194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9054203033447</t>
   </si>
   <si>
     <t xml:space="preserve">14.018045425415</t>
@@ -2555,67 +2555,67 @@
     <t xml:space="preserve">14.5811700820923</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0781135559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.355920791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1982460021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3183794021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0555877685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7688789367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4671545028687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7886199951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7074193954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9026384353638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9326667785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7674884796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1518049240112</t>
+    <t xml:space="preserve">14.0781145095825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3559217453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1982450485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3183784484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0555858612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7688798904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4671516418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7886180877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7074165344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9026355743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9326696395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7674865722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1518020629883</t>
   </si>
   <si>
     <t xml:space="preserve">15.3770532608032</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4821710586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6835021972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8937358856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3442344665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0138702392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5333385467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5033016204834</t>
+    <t xml:space="preserve">15.4821691513062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.683500289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8937339782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3442363739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0138683319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.533332824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.503303527832</t>
   </si>
   <si>
     <t xml:space="preserve">16.9087524414062</t>
@@ -2624,34 +2624,34 @@
     <t xml:space="preserve">17.4643688201904</t>
   </si>
   <si>
-    <t xml:space="preserve">17.103967666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.524435043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1189861297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2391147613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1340007781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3892860412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4042987823486</t>
+    <t xml:space="preserve">17.1039695739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5244331359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1189842224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2391204833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1340026855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3892822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4043006896973</t>
   </si>
   <si>
     <t xml:space="preserve">17.6896190643311</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3653659820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2902851104736</t>
+    <t xml:space="preserve">18.365364074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.290283203125</t>
   </si>
   <si>
     <t xml:space="preserve">18.485502243042</t>
@@ -2663,22 +2663,22 @@
     <t xml:space="preserve">19.2813835144043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8520164489746</t>
+    <t xml:space="preserve">19.8520183563232</t>
   </si>
   <si>
     <t xml:space="preserve">19.3414497375488</t>
   </si>
   <si>
-    <t xml:space="preserve">19.551685333252</t>
+    <t xml:space="preserve">19.5516834259033</t>
   </si>
   <si>
     <t xml:space="preserve">18.3953990936279</t>
   </si>
   <si>
-    <t xml:space="preserve">19.431547164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.167366027832</t>
+    <t xml:space="preserve">19.4315490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1673679351807</t>
   </si>
   <si>
     <t xml:space="preserve">19.3264331817627</t>
@@ -2696,28 +2696,28 @@
     <t xml:space="preserve">19.2663650512695</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5066356658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8820476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0922813415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3475666046143</t>
+    <t xml:space="preserve">19.5066337585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8820495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0922832489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3475646972656</t>
   </si>
   <si>
     <t xml:space="preserve">20.3775997161865</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5967350006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7107486724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9209861755371</t>
+    <t xml:space="preserve">19.5967330932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7107467651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9209823608398</t>
   </si>
   <si>
     <t xml:space="preserve">18.7708168029785</t>
@@ -2726,10 +2726,10 @@
     <t xml:space="preserve">18.830883026123</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5666961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0861644744873</t>
+    <t xml:space="preserve">19.5666980743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0861663818359</t>
   </si>
   <si>
     <t xml:space="preserve">18.9059677124023</t>
@@ -2738,46 +2738,46 @@
     <t xml:space="preserve">19.0711498260498</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7558002471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.476598739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2964000701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5366649627686</t>
+    <t xml:space="preserve">18.755802154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4766006469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2964019775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5366668701172</t>
   </si>
   <si>
     <t xml:space="preserve">19.5216503143311</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3114128112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9810485839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4526805877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6178646087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6117534637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.362585067749</t>
+    <t xml:space="preserve">19.3114166259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9810523986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4526824951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6178665161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6117515563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3625831604004</t>
   </si>
   <si>
     <t xml:space="preserve">19.6417827606201</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0322170257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5127487182617</t>
+    <t xml:space="preserve">20.0322189331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5127506256104</t>
   </si>
   <si>
     <t xml:space="preserve">20.2424468994141</t>
@@ -2786,37 +2786,37 @@
     <t xml:space="preserve">20.7379970550537</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0021839141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2151985168457</t>
+    <t xml:space="preserve">20.0021800994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.215202331543</t>
   </si>
   <si>
     <t xml:space="preserve">18.1401176452637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3203144073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5577964782715</t>
+    <t xml:space="preserve">18.3203201293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5577983856201</t>
   </si>
   <si>
     <t xml:space="preserve">20.4376640319824</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1284332275391</t>
+    <t xml:space="preserve">21.1284313201904</t>
   </si>
   <si>
     <t xml:space="preserve">20.7830467224121</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4977340698242</t>
+    <t xml:space="preserve">20.4977283477783</t>
   </si>
   <si>
     <t xml:space="preserve">21.0233154296875</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4137496948242</t>
+    <t xml:space="preserve">21.4137477874756</t>
   </si>
   <si>
     <t xml:space="preserve">21.3686962127686</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">20.4076309204102</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5427837371826</t>
+    <t xml:space="preserve">20.542781829834</t>
   </si>
   <si>
     <t xml:space="preserve">20.3175315856934</t>
@@ -2843,28 +2843,28 @@
     <t xml:space="preserve">19.4465675354004</t>
   </si>
   <si>
-    <t xml:space="preserve">19.746898651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2363357543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5277671813965</t>
+    <t xml:space="preserve">19.7468967437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2363338470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5277633666992</t>
   </si>
   <si>
     <t xml:space="preserve">21.7140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6840476989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6389980316162</t>
+    <t xml:space="preserve">21.684045791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6389999389648</t>
   </si>
   <si>
     <t xml:space="preserve">21.3386650085449</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6239814758301</t>
+    <t xml:space="preserve">21.6239795684814</t>
   </si>
   <si>
     <t xml:space="preserve">21.8642482757568</t>
@@ -2873,28 +2873,28 @@
     <t xml:space="preserve">21.3987331390381</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4437789916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1884956359863</t>
+    <t xml:space="preserve">21.4437808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1884994506836</t>
   </si>
   <si>
     <t xml:space="preserve">21.9092960357666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8942794799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8342189788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.503849029541</t>
+    <t xml:space="preserve">21.8942813873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8342151641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5038452148438</t>
   </si>
   <si>
     <t xml:space="preserve">22.2546806335449</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0444488525391</t>
+    <t xml:space="preserve">22.0444469451904</t>
   </si>
   <si>
     <t xml:space="preserve">22.2847137451172</t>
@@ -2906,16 +2906,16 @@
     <t xml:space="preserve">22.4649143218994</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6901607513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8703632354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6150798797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.570032119751</t>
+    <t xml:space="preserve">22.6901626586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.870361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6150817871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5700302124023</t>
   </si>
   <si>
     <t xml:space="preserve">22.6751480102539</t>
@@ -2924,190 +2924,190 @@
     <t xml:space="preserve">22.5775375366211</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9079055786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0430564880371</t>
+    <t xml:space="preserve">22.9079036712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0430545806885</t>
   </si>
   <si>
     <t xml:space="preserve">23.0881061553955</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8178043365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8403282165527</t>
+    <t xml:space="preserve">22.8178024291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.84033203125</t>
   </si>
   <si>
     <t xml:space="preserve">23.1706962585449</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2157440185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3809280395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5235900878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0505638122559</t>
+    <t xml:space="preserve">23.2157459259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3809261322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.523588180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0505676269531</t>
   </si>
   <si>
     <t xml:space="preserve">22.915412902832</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0730857849121</t>
+    <t xml:space="preserve">23.0730895996094</t>
   </si>
   <si>
     <t xml:space="preserve">23.253288269043</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3433876037598</t>
+    <t xml:space="preserve">23.3433895111084</t>
   </si>
   <si>
     <t xml:space="preserve">23.2983379364014</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8914985656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2594089508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0942211151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6648540496826</t>
+    <t xml:space="preserve">23.8914947509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2594032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0942192077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.664852142334</t>
   </si>
   <si>
     <t xml:space="preserve">24.5522308349609</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4621315002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7924957275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4020614624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0491695404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4696388244629</t>
+    <t xml:space="preserve">24.4621295928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7924976348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.402063369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0491714477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4696369171143</t>
   </si>
   <si>
     <t xml:space="preserve">24.4245872497559</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1993370056152</t>
+    <t xml:space="preserve">24.1993350982666</t>
   </si>
   <si>
     <t xml:space="preserve">23.9590682983398</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1617946624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2293682098389</t>
+    <t xml:space="preserve">24.1617965698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2293701171875</t>
   </si>
   <si>
     <t xml:space="preserve">24.6273155212402</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8075141906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8150196075439</t>
+    <t xml:space="preserve">24.8075103759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8150215148926</t>
   </si>
   <si>
     <t xml:space="preserve">25.1078433990479</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2204685211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1003360748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1829261779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2955513000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5208015441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8286457061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8061218261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7385444641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.783597946167</t>
+    <t xml:space="preserve">25.2204704284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1003379821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1829319000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2955532073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5208053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.828649520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8061199188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7385406494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7835960388184</t>
   </si>
   <si>
     <t xml:space="preserve">26.0538959503174</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8661861419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4893760681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5119037628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3767547607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.466854095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.65456199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.586986541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1050605773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5180130004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1350898742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3903751373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0149574279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.037483215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2176856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.195161819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2251930236816</t>
+    <t xml:space="preserve">25.8661918640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.489372253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5118999481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3767528533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4668483734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6545600891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5869846343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1050624847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5180168151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1350936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3903732299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0149593353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0374813079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2176837921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1951599121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2251949310303</t>
   </si>
   <si>
     <t xml:space="preserve">26.2566184997559</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6845951080322</t>
+    <t xml:space="preserve">26.6845989227295</t>
   </si>
   <si>
     <t xml:space="preserve">27.1726322174072</t>
@@ -3116,31 +3116,31 @@
     <t xml:space="preserve">27.0299777984619</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7446594238281</t>
+    <t xml:space="preserve">26.7446613311768</t>
   </si>
   <si>
     <t xml:space="preserve">26.6245250701904</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8962173461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0163555145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3992767333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3542251586914</t>
+    <t xml:space="preserve">25.8962211608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0163516998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3992786407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.35422706604</t>
   </si>
   <si>
     <t xml:space="preserve">26.5569534301758</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0013389587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0238571166992</t>
+    <t xml:space="preserve">26.0013370513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0238609313965</t>
   </si>
   <si>
     <t xml:space="preserve">26.4218006134033</t>
@@ -3149,25 +3149,25 @@
     <t xml:space="preserve">26.2866516113281</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2115650177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8873233795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.11256980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3603439331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3828678131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6456604003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6231365203857</t>
+    <t xml:space="preserve">26.2115688323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8873157501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1125659942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3603420257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3828659057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.645658493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6231346130371</t>
   </si>
   <si>
     <t xml:space="preserve">27.7808113098145</t>
@@ -3176,151 +3176,151 @@
     <t xml:space="preserve">27.5931015014648</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4204082489014</t>
+    <t xml:space="preserve">27.42041015625</t>
   </si>
   <si>
     <t xml:space="preserve">27.5630664825439</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7883148193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7132358551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9535026550293</t>
+    <t xml:space="preserve">27.7883167266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7132339477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9535007476807</t>
   </si>
   <si>
     <t xml:space="preserve">27.9835338592529</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2613410949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1412105560303</t>
+    <t xml:space="preserve">28.2613468170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1412048339844</t>
   </si>
   <si>
     <t xml:space="preserve">28.2087841033936</t>
   </si>
   <si>
-    <t xml:space="preserve">28.18625831604</t>
+    <t xml:space="preserve">28.1862602233887</t>
   </si>
   <si>
     <t xml:space="preserve">28.381477355957</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2012748718262</t>
+    <t xml:space="preserve">28.2012805938721</t>
   </si>
   <si>
     <t xml:space="preserve">28.058614730835</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1186828613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4115104675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1698513031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3875961303711</t>
+    <t xml:space="preserve">28.1186847686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4115085601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1698474884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3875885009766</t>
   </si>
   <si>
     <t xml:space="preserve">29.5077228546143</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2899780273438</t>
+    <t xml:space="preserve">29.2899799346924</t>
   </si>
   <si>
     <t xml:space="preserve">28.9145679473877</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4190158843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6442680358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1923789978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1323127746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2148971557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5842018127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4865894317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4565582275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5466575622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4640712738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8784217834473</t>
+    <t xml:space="preserve">28.419017791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6442699432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1923770904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1323089599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.214900970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5842037200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4865913391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4565563201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5466594696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4640693664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8784160614014</t>
   </si>
   <si>
     <t xml:space="preserve">28.4715728759766</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4039974212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.073637008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3964920043945</t>
+    <t xml:space="preserve">28.4040012359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0736312866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3964900970459</t>
   </si>
   <si>
     <t xml:space="preserve">28.02858543396</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7644023895264</t>
+    <t xml:space="preserve">28.7643966674805</t>
   </si>
   <si>
     <t xml:space="preserve">29.6954326629639</t>
   </si>
   <si>
-    <t xml:space="preserve">29.717960357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9432067871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4012145996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7240715026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5213527679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6940402984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5288562774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.709056854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4988212585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7766342163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7602252960205</t>
+    <t xml:space="preserve">29.7179584503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9432125091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4012184143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7240676879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5213508605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6940498352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5288581848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7090549468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4988231658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7766304016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7602214813232</t>
   </si>
   <si>
     <t xml:space="preserve">32.2107238769531</t>
@@ -3329,43 +3329,43 @@
     <t xml:space="preserve">32.4359741210938</t>
   </si>
   <si>
-    <t xml:space="preserve">31.737699508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1506538391113</t>
+    <t xml:space="preserve">31.7376937866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1506462097168</t>
   </si>
   <si>
     <t xml:space="preserve">32.3083267211914</t>
   </si>
   <si>
-    <t xml:space="preserve">32.345874786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8728446960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1370296478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.859224319458</t>
+    <t xml:space="preserve">32.3458786010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8728466033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.137035369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8592224121094</t>
   </si>
   <si>
     <t xml:space="preserve">31.0544395446777</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4640998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2592010498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0342826843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6406784057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8052806854248</t>
+    <t xml:space="preserve">31.4641075134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2591972351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0342807769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.640682220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8052825927734</t>
   </si>
   <si>
     <t xml:space="preserve">29.1265907287598</t>
@@ -3374,76 +3374,76 @@
     <t xml:space="preserve">29.08642578125</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0583801269531</t>
+    <t xml:space="preserve">30.0583839416504</t>
   </si>
   <si>
     <t xml:space="preserve">29.9378929138184</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1146125793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5885429382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3596839904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3195152282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.030345916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1508274078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3355827331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2632942199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.166898727417</t>
+    <t xml:space="preserve">30.1146144866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5885448455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3596801757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3195247650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0303382873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1508331298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.335578918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2632827758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1668949127197</t>
   </si>
   <si>
     <t xml:space="preserve">31.1187000274658</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6046047210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7531433105469</t>
+    <t xml:space="preserve">30.6046104431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.753137588501</t>
   </si>
   <si>
     <t xml:space="preserve">30.4118232727051</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5644454956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5483798980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9419860839844</t>
+    <t xml:space="preserve">30.5644416809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5483741760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9419803619385</t>
   </si>
   <si>
     <t xml:space="preserve">31.2713222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1829681396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1267337799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2150955200195</t>
+    <t xml:space="preserve">31.1829643249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1267318725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2150974273682</t>
   </si>
   <si>
     <t xml:space="preserve">31.2311630249023</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1909980773926</t>
+    <t xml:space="preserve">31.1909999847412</t>
   </si>
   <si>
     <t xml:space="preserve">30.435920715332</t>
@@ -3452,40 +3452,40 @@
     <t xml:space="preserve">30.2029705047607</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1788711547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8375568389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8616504669189</t>
+    <t xml:space="preserve">30.1788749694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.837553024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8616542816162</t>
   </si>
   <si>
     <t xml:space="preserve">30.5082130432129</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3475570678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2913360595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4800300598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8856048583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3997039794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9338035583496</t>
+    <t xml:space="preserve">30.3475608825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2913341522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4800262451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8856086730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3996963500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9338073730469</t>
   </si>
   <si>
     <t xml:space="preserve">27.7208652496338</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1907024383545</t>
+    <t xml:space="preserve">27.1907062530518</t>
   </si>
   <si>
     <t xml:space="preserve">27.6807022094727</t>
@@ -3494,94 +3494,94 @@
     <t xml:space="preserve">27.9939765930176</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0743064880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5803642272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9659404754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0783939361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8695430755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8374099731445</t>
+    <t xml:space="preserve">28.0743083953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5803680419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9659328460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.07839012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8695411682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8374156951904</t>
   </si>
   <si>
     <t xml:space="preserve">28.8133125305176</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6285591125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3595390319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0944576263428</t>
+    <t xml:space="preserve">28.6285610198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3595333099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0944595336914</t>
   </si>
   <si>
     <t xml:space="preserve">28.9579029083252</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3152885437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1587200164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3675670623779</t>
+    <t xml:space="preserve">28.3152847290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1587181091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3675727844238</t>
   </si>
   <si>
     <t xml:space="preserve">28.8936443328857</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8026962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2799034118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4106025695801</t>
+    <t xml:space="preserve">28.802698135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2799015045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4105987548828</t>
   </si>
   <si>
     <t xml:space="preserve">25.9600028991699</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9974250793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.981086730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9028205871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9273281097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3228492736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3623676300049</t>
+    <t xml:space="preserve">26.9974231719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9810848236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9028224945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9273300170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3228454589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3623695373535</t>
   </si>
   <si>
     <t xml:space="preserve">22.8885879516602</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5175762176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3963642120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7101955413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3065090179443</t>
+    <t xml:space="preserve">23.5175724029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3963661193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7101974487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3065128326416</t>
   </si>
   <si>
     <t xml:space="preserve">25.7231121063232</t>
@@ -3596,31 +3596,31 @@
     <t xml:space="preserve">26.956579208374</t>
   </si>
   <si>
-    <t xml:space="preserve">27.144458770752</t>
+    <t xml:space="preserve">27.1444625854492</t>
   </si>
   <si>
     <t xml:space="preserve">26.7768669128418</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1036167144775</t>
+    <t xml:space="preserve">27.1036148071289</t>
   </si>
   <si>
     <t xml:space="preserve">27.0709400177002</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9892559051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0300998687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3486747741699</t>
+    <t xml:space="preserve">26.9892539978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0300979614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3486728668213</t>
   </si>
   <si>
     <t xml:space="preserve">28.1328659057617</t>
   </si>
   <si>
-    <t xml:space="preserve">27.904146194458</t>
+    <t xml:space="preserve">27.9041423797607</t>
   </si>
   <si>
     <t xml:space="preserve">27.5447235107422</t>
@@ -3629,67 +3629,67 @@
     <t xml:space="preserve">27.9776630401611</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5937366485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5481472015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7523670196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8830623626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8667221069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5399799346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4991359710693</t>
+    <t xml:space="preserve">27.5937328338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5481452941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7523651123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8830604553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8667240142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5399780273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4991340637207</t>
   </si>
   <si>
     <t xml:space="preserve">26.3439311981201</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6414279937744</t>
+    <t xml:space="preserve">25.6414241790771</t>
   </si>
   <si>
     <t xml:space="preserve">26.2377376556396</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3521003723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1152038574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9109935760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3146781921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3310165405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2738361358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6741008758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8048000335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3555240631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9634284973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9913539886475</t>
+    <t xml:space="preserve">26.3520984649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1152057647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9109897613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3146800994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3310146331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2738342285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6740989685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8047981262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3555221557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9634265899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9913558959961</t>
   </si>
   <si>
     <t xml:space="preserve">24.3017654418945</t>
@@ -3698,7 +3698,7 @@
     <t xml:space="preserve">25.8374729156494</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3766040802002</t>
+    <t xml:space="preserve">26.3766078948975</t>
   </si>
   <si>
     <t xml:space="preserve">26.4256153106689</t>
@@ -3710,46 +3710,46 @@
     <t xml:space="preserve">26.4419555664062</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6380043029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5073051452637</t>
+    <t xml:space="preserve">26.6380004882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.507303237915</t>
   </si>
   <si>
     <t xml:space="preserve">27.5489635467529</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7698364257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4734287261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5743713378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6759967803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9639358520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5828380584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3457126617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5235557556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7274932861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5320281982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.956148147583</t>
+    <t xml:space="preserve">26.7698345184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4734306335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5743732452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6759948730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9639339447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5828399658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3457145690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5235576629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7274894714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5320243835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9561500549316</t>
   </si>
   <si>
     <t xml:space="preserve">26.2108974456787</t>
@@ -3758,34 +3758,34 @@
     <t xml:space="preserve">25.5164546966553</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3992576599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8149127960205</t>
+    <t xml:space="preserve">23.3992557525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8149108886719</t>
   </si>
   <si>
     <t xml:space="preserve">23.348445892334</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9751377105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9250087738037</t>
+    <t xml:space="preserve">23.9751358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9250068664551</t>
   </si>
   <si>
     <t xml:space="preserve">23.4161949157715</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5686340332031</t>
+    <t xml:space="preserve">23.5686359405518</t>
   </si>
   <si>
     <t xml:space="preserve">23.3569145202637</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0859146118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8904457092285</t>
+    <t xml:space="preserve">23.0859127044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8904495239258</t>
   </si>
   <si>
     <t xml:space="preserve">23.6194458007812</t>
@@ -3797,28 +3797,28 @@
     <t xml:space="preserve">23.3230400085449</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8318462371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.747163772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.713285446167</t>
+    <t xml:space="preserve">22.8318481445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7471618652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7132835388184</t>
   </si>
   <si>
     <t xml:space="preserve">21.6462211608887</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9510955810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.264440536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7810363769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1120014190674</t>
+    <t xml:space="preserve">21.9510974884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2644424438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7810382843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.112003326416</t>
   </si>
   <si>
     <t xml:space="preserve">22.4592247009277</t>
@@ -3827,28 +3827,28 @@
     <t xml:space="preserve">22.2220973968506</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3074684143066</t>
+    <t xml:space="preserve">21.3074703216553</t>
   </si>
   <si>
     <t xml:space="preserve">21.7563133239746</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2898464202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0520362854004</t>
+    <t xml:space="preserve">22.2898483276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.052038192749</t>
   </si>
   <si>
     <t xml:space="preserve">23.0351009368896</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5185050964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0096950531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5015678405762</t>
+    <t xml:space="preserve">22.5185031890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.009693145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5015659332275</t>
   </si>
   <si>
     <t xml:space="preserve">22.6116600036621</t>
@@ -3863,10 +3863,10 @@
     <t xml:space="preserve">24.0513553619385</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9327945709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4239826202393</t>
+    <t xml:space="preserve">23.9327926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4239807128906</t>
   </si>
   <si>
     <t xml:space="preserve">24.5256061553955</t>
@@ -3875,10 +3875,10 @@
     <t xml:space="preserve">23.9497299194336</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8565731048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4416027069092</t>
+    <t xml:space="preserve">23.8565711975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4416065216064</t>
   </si>
   <si>
     <t xml:space="preserve">23.7888221740723</t>
@@ -3896,37 +3896,37 @@
     <t xml:space="preserve">23.7380104064941</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0774459838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5354423522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9334735870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7725696563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.095064163208</t>
+    <t xml:space="preserve">23.0774440765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5354442596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9334754943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7725677490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0950660705566</t>
   </si>
   <si>
     <t xml:space="preserve">22.0273151397705</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2559719085693</t>
+    <t xml:space="preserve">22.255973815918</t>
   </si>
   <si>
     <t xml:space="preserve">22.3914737701416</t>
   </si>
   <si>
-    <t xml:space="preserve">21.925687789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2390365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3237228393555</t>
+    <t xml:space="preserve">21.9256896972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.23903465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3237247467041</t>
   </si>
   <si>
     <t xml:space="preserve">22.4422855377197</t>
@@ -3935,61 +3935,61 @@
     <t xml:space="preserve">23.0689754486084</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9243240356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3907909393311</t>
+    <t xml:space="preserve">23.9243221282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3907871246338</t>
   </si>
   <si>
     <t xml:space="preserve">22.9419441223145</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6455345153809</t>
+    <t xml:space="preserve">22.6455364227295</t>
   </si>
   <si>
     <t xml:space="preserve">22.730224609375</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3921585083008</t>
+    <t xml:space="preserve">21.3921546936035</t>
   </si>
   <si>
     <t xml:space="preserve">21.5022506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3413429260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7908725738525</t>
+    <t xml:space="preserve">21.341344833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7908706665039</t>
   </si>
   <si>
     <t xml:space="preserve">21.0957489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6553688049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8078117370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3335571289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2207317352295</t>
+    <t xml:space="preserve">20.6553726196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8078079223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3335590362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2207298278809</t>
   </si>
   <si>
     <t xml:space="preserve">23.2552890777588</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0344142913818</t>
+    <t xml:space="preserve">24.0344161987305</t>
   </si>
   <si>
     <t xml:space="preserve">23.4246654510498</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7979736328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4331359863281</t>
+    <t xml:space="preserve">22.7979755401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4331340789795</t>
   </si>
   <si>
     <t xml:space="preserve">23.6533222198486</t>
@@ -3998,7 +3998,7 @@
     <t xml:space="preserve">24.0174808502197</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3308238983154</t>
+    <t xml:space="preserve">24.3308258056641</t>
   </si>
   <si>
     <t xml:space="preserve">24.3477630615234</t>
@@ -4007,13 +4007,13 @@
     <t xml:space="preserve">24.2037944793701</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7966079711914</t>
+    <t xml:space="preserve">24.7966117858887</t>
   </si>
   <si>
     <t xml:space="preserve">25.1438293457031</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8297996520996</t>
+    <t xml:space="preserve">25.8298015594482</t>
   </si>
   <si>
     <t xml:space="preserve">25.9737682342529</t>
@@ -4028,25 +4028,25 @@
     <t xml:space="preserve">25.6265525817871</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7197074890137</t>
+    <t xml:space="preserve">25.719705581665</t>
   </si>
   <si>
     <t xml:space="preserve">25.6858310699463</t>
   </si>
   <si>
-    <t xml:space="preserve">26.329460144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.311840057373</t>
+    <t xml:space="preserve">26.3294582366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3118381500244</t>
   </si>
   <si>
     <t xml:space="preserve">26.9307422637939</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9053363800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1756553649902</t>
+    <t xml:space="preserve">26.9053382873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1756534576416</t>
   </si>
   <si>
     <t xml:space="preserve">28.226469039917</t>
@@ -4064,34 +4064,34 @@
     <t xml:space="preserve">28.1163730621338</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3111572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1671829223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4297161102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7091903686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1848030090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.277961730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0069599151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9476833343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2864322662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0239009857178</t>
+    <t xml:space="preserve">28.3111534118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1671848297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4297180175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7091884613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1848068237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2779636383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0069580078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9476795196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2864303588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0238990783691</t>
   </si>
   <si>
     <t xml:space="preserve">27.6675243377686</t>
@@ -4103,16 +4103,16 @@
     <t xml:space="preserve">27.2610244750977</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0577774047852</t>
+    <t xml:space="preserve">27.0577793121338</t>
   </si>
   <si>
     <t xml:space="preserve">27.269495010376</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5574340820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0909633636475</t>
+    <t xml:space="preserve">27.5574321746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0909671783447</t>
   </si>
   <si>
     <t xml:space="preserve">27.125524520874</t>
@@ -4127,22 +4127,22 @@
     <t xml:space="preserve">26.7952423095703</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4219341278076</t>
+    <t xml:space="preserve">27.4219360351562</t>
   </si>
   <si>
     <t xml:space="preserve">27.2271518707275</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4304008483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3203086853027</t>
+    <t xml:space="preserve">27.4304027557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3203048706055</t>
   </si>
   <si>
     <t xml:space="preserve">27.1509323120117</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7013988494873</t>
+    <t xml:space="preserve">27.7014045715332</t>
   </si>
   <si>
     <t xml:space="preserve">28.234935760498</t>
@@ -4160,40 +4160,40 @@
     <t xml:space="preserve">28.4635925292969</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0818176269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2935352325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0479373931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7938766479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.692253112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4043121337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7176570892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8446922302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8362197875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8531551361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6244983673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8108139038086</t>
+    <t xml:space="preserve">29.0818157196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2935333251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0479412078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7938747406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6922550201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4043140411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7176551818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.844690322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.836217880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8531589508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6244964599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8108158111572</t>
   </si>
   <si>
     <t xml:space="preserve">28.8785629272461</t>
@@ -4208,25 +4208,25 @@
     <t xml:space="preserve">28.827751159668</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1417770385742</t>
+    <t xml:space="preserve">28.1417808532715</t>
   </si>
   <si>
     <t xml:space="preserve">28.7600002288818</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6753120422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.759183883667</t>
+    <t xml:space="preserve">28.675313949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7591857910156</t>
   </si>
   <si>
     <t xml:space="preserve">28.2301406860352</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0740299224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1954479217529</t>
+    <t xml:space="preserve">28.0740280151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1954460144043</t>
   </si>
   <si>
     <t xml:space="preserve">28.0133190155029</t>
@@ -4235,40 +4235,40 @@
     <t xml:space="preserve">28.2908496856689</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3515605926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2995223999023</t>
+    <t xml:space="preserve">28.3515586853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.299524307251</t>
   </si>
   <si>
     <t xml:space="preserve">28.1520843505859</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3081970214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2214660644531</t>
+    <t xml:space="preserve">28.3081951141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2214679718018</t>
   </si>
   <si>
     <t xml:space="preserve">28.1434135437012</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9812507629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1660003662109</t>
+    <t xml:space="preserve">26.9812488555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1660022735596</t>
   </si>
   <si>
     <t xml:space="preserve">25.4027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0185623168945</t>
+    <t xml:space="preserve">26.0185642242432</t>
   </si>
   <si>
     <t xml:space="preserve">24.934455871582</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0558738708496</t>
+    <t xml:space="preserve">25.0558757781982</t>
   </si>
   <si>
     <t xml:space="preserve">24.2753200531006</t>
@@ -4277,28 +4277,28 @@
     <t xml:space="preserve">24.9951648712158</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8017425537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3594264984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3247375488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8997650146484</t>
+    <t xml:space="preserve">25.8017387390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3594245910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3247356414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8997631072998</t>
   </si>
   <si>
     <t xml:space="preserve">25.0125102996826</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7176322937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1686229705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4635009765625</t>
+    <t xml:space="preserve">24.7176342010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1686248779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4635028839111</t>
   </si>
   <si>
     <t xml:space="preserve">25.4808444976807</t>
@@ -4310,46 +4310,46 @@
     <t xml:space="preserve">25.3073883056641</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9518032073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5068645477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9058170318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1052913665771</t>
+    <t xml:space="preserve">24.9518013000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5068626403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9058151245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1052894592285</t>
   </si>
   <si>
     <t xml:space="preserve">25.6716480255127</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0359058380127</t>
+    <t xml:space="preserve">26.03590965271</t>
   </si>
   <si>
     <t xml:space="preserve">25.6196117401123</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2006931304932</t>
+    <t xml:space="preserve">26.2006912231445</t>
   </si>
   <si>
     <t xml:space="preserve">26.408842086792</t>
   </si>
   <si>
-    <t xml:space="preserve">26.443531036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5042400360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.313440322876</t>
+    <t xml:space="preserve">26.4435329437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5042419433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3134422302246</t>
   </si>
   <si>
     <t xml:space="preserve">26.1833477020264</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4522037506104</t>
+    <t xml:space="preserve">26.452205657959</t>
   </si>
   <si>
     <t xml:space="preserve">26.0966186523438</t>
@@ -4358,19 +4358,19 @@
     <t xml:space="preserve">25.4721736907959</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6109390258789</t>
+    <t xml:space="preserve">25.6109371185303</t>
   </si>
   <si>
     <t xml:space="preserve">25.3767719268799</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3307838439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1920185089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0098896026611</t>
+    <t xml:space="preserve">26.3307857513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1920204162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0098876953125</t>
   </si>
   <si>
     <t xml:space="preserve">25.8104133605957</t>
@@ -4379,58 +4379,58 @@
     <t xml:space="preserve">26.5215892791748</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8424835205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4868984222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.599645614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.729736328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1062126159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0882835388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.335334777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4070415496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.675952911377</t>
+    <t xml:space="preserve">26.8424854278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4868965148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5996417999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7297344207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1062107086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0882816314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3353328704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4070434570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6759548187256</t>
   </si>
   <si>
     <t xml:space="preserve">26.702844619751</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3084411621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8154373168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3622264862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8821201324463</t>
+    <t xml:space="preserve">26.3084449768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8154392242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3622245788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.882116317749</t>
   </si>
   <si>
     <t xml:space="preserve">26.6938819885254</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2048110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4737224578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5185413360596</t>
+    <t xml:space="preserve">27.20481300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4737243652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5185432434082</t>
   </si>
   <si>
     <t xml:space="preserve">27.3930492401123</t>
@@ -4439,37 +4439,37 @@
     <t xml:space="preserve">27.6529979705811</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7157440185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9219055175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8860549926758</t>
+    <t xml:space="preserve">27.7157421112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9219074249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8860530853271</t>
   </si>
   <si>
     <t xml:space="preserve">27.9667263031006</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9398365020752</t>
+    <t xml:space="preserve">27.9398345947266</t>
   </si>
   <si>
     <t xml:space="preserve">27.7605609893799</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6619625091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4647598266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3840847015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3213386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.60817527771</t>
+    <t xml:space="preserve">27.6619606018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4647579193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3840827941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3213405609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6081790924072</t>
   </si>
   <si>
     <t xml:space="preserve">27.9487991333008</t>
@@ -4478,16 +4478,16 @@
     <t xml:space="preserve">28.0115451812744</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2356357574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7644958496094</t>
+    <t xml:space="preserve">28.2356376647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7644939422607</t>
   </si>
   <si>
     <t xml:space="preserve">28.3611278533936</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9129428863525</t>
+    <t xml:space="preserve">27.9129447937012</t>
   </si>
   <si>
     <t xml:space="preserve">27.4378681182861</t>
@@ -4499,16 +4499,16 @@
     <t xml:space="preserve">27.957763671875</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5045471191406</t>
+    <t xml:space="preserve">28.504545211792</t>
   </si>
   <si>
     <t xml:space="preserve">28.7465667724609</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6927833557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7555332183838</t>
+    <t xml:space="preserve">28.6927852630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7555313110352</t>
   </si>
   <si>
     <t xml:space="preserve">28.9796237945557</t>
@@ -4517,28 +4517,28 @@
     <t xml:space="preserve">29.0334053039551</t>
   </si>
   <si>
-    <t xml:space="preserve">29.132007598877</t>
+    <t xml:space="preserve">29.1320056915283</t>
   </si>
   <si>
     <t xml:space="preserve">29.3740272521973</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2306079864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7056827545166</t>
+    <t xml:space="preserve">29.2306060791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7056846618652</t>
   </si>
   <si>
     <t xml:space="preserve">30.1000862121582</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9606018066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5482711791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1986827850342</t>
+    <t xml:space="preserve">30.9605979919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5482730865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1986865997314</t>
   </si>
   <si>
     <t xml:space="preserve">29.8132457733154</t>
@@ -4547,10 +4547,10 @@
     <t xml:space="preserve">29.8311729431152</t>
   </si>
   <si>
-    <t xml:space="preserve">28.773458480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1588973999023</t>
+    <t xml:space="preserve">28.7734565734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1588954925537</t>
   </si>
   <si>
     <t xml:space="preserve">29.3202438354492</t>
@@ -4562,16 +4562,16 @@
     <t xml:space="preserve">29.4457340240479</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3650608062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0871906280518</t>
+    <t xml:space="preserve">29.365062713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0871887207031</t>
   </si>
   <si>
     <t xml:space="preserve">28.7017478942871</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9975490570068</t>
+    <t xml:space="preserve">28.9975509643555</t>
   </si>
   <si>
     <t xml:space="preserve">29.1768226623535</t>
@@ -4583,13 +4583,13 @@
     <t xml:space="preserve">29.3112812042236</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5712280273438</t>
+    <t xml:space="preserve">29.5712299346924</t>
   </si>
   <si>
     <t xml:space="preserve">30.1628322601318</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9745922088623</t>
+    <t xml:space="preserve">29.9745903015137</t>
   </si>
   <si>
     <t xml:space="preserve">30.2166118621826</t>
@@ -4604,7 +4604,7 @@
     <t xml:space="preserve">29.7773933410645</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7236099243164</t>
+    <t xml:space="preserve">29.7236080169678</t>
   </si>
   <si>
     <t xml:space="preserve">29.7684268951416</t>
@@ -4616,19 +4616,19 @@
     <t xml:space="preserve">30.1807556152344</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4586334228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0104484558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2703971862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5930881500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1449069976807</t>
+    <t xml:space="preserve">30.4586353302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0104503631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.270393371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5930919647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.144905090332</t>
   </si>
   <si>
     <t xml:space="preserve">30.1538677215576</t>
@@ -4637,22 +4637,22 @@
     <t xml:space="preserve">30.0463027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0373363494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6967220306396</t>
+    <t xml:space="preserve">30.0373401641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.696720123291</t>
   </si>
   <si>
     <t xml:space="preserve">29.1678619384766</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6877555847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3292102813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4278087615967</t>
+    <t xml:space="preserve">29.6877536773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3292083740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4278106689453</t>
   </si>
   <si>
     <t xml:space="preserve">30.0552654266357</t>
@@ -4664,10 +4664,10 @@
     <t xml:space="preserve">28.5224742889404</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4776592254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2177066802979</t>
+    <t xml:space="preserve">28.4776573181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2177085876465</t>
   </si>
   <si>
     <t xml:space="preserve">27.7426338195801</t>
@@ -4679,7 +4679,7 @@
     <t xml:space="preserve">27.5095767974854</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3571949005127</t>
+    <t xml:space="preserve">27.3571968078613</t>
   </si>
   <si>
     <t xml:space="preserve">27.0524311065674</t>
@@ -4691,13 +4691,13 @@
     <t xml:space="preserve">27.2854843139648</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2944507598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4468307495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5454330444336</t>
+    <t xml:space="preserve">27.2944488525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4468326568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.545431137085</t>
   </si>
   <si>
     <t xml:space="preserve">28.0294742584229</t>
@@ -4715,7 +4715,7 @@
     <t xml:space="preserve">28.6838207244873</t>
   </si>
   <si>
-    <t xml:space="preserve">28.495584487915</t>
+    <t xml:space="preserve">28.4955825805664</t>
   </si>
   <si>
     <t xml:space="preserve">29.0423717498779</t>
@@ -4724,10 +4724,10 @@
     <t xml:space="preserve">29.732572555542</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7863540649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3919544219971</t>
+    <t xml:space="preserve">29.7863578796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3919525146484</t>
   </si>
   <si>
     <t xml:space="preserve">29.4547004699707</t>
@@ -4736,19 +4736,19 @@
     <t xml:space="preserve">29.8491020202637</t>
   </si>
   <si>
-    <t xml:space="preserve">29.194751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8989524841309</t>
+    <t xml:space="preserve">29.1947536468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8989505767822</t>
   </si>
   <si>
     <t xml:space="preserve">29.2664623260498</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0602951049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1499328613281</t>
+    <t xml:space="preserve">29.0602931976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1499366760254</t>
   </si>
   <si>
     <t xml:space="preserve">29.4367713928223</t>
@@ -4760,10 +4760,10 @@
     <t xml:space="preserve">29.24853515625</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5891513824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6070823669434</t>
+    <t xml:space="preserve">29.5891551971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6070804595947</t>
   </si>
   <si>
     <t xml:space="preserve">29.7953224182129</t>
@@ -4772,28 +4772,28 @@
     <t xml:space="preserve">30.2883243560791</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0731925964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4048480987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4317417144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3600330352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2255764007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1359405517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3152122497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3421020507812</t>
+    <t xml:space="preserve">30.0731945037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4048500061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4317436218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3600292205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2255744934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1359367370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3152141571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3421039581299</t>
   </si>
   <si>
     <t xml:space="preserve">30.7454719543457</t>
@@ -4808,43 +4808,43 @@
     <t xml:space="preserve">30.6110172271729</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8440723419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0860919952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1936588287354</t>
+    <t xml:space="preserve">30.8440742492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.086088180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1936511993408</t>
   </si>
   <si>
     <t xml:space="preserve">31.1577987670898</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1757259368896</t>
+    <t xml:space="preserve">31.1757278442383</t>
   </si>
   <si>
     <t xml:space="preserve">31.3818893432617</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5522079467773</t>
+    <t xml:space="preserve">31.5522003173828</t>
   </si>
   <si>
     <t xml:space="preserve">31.8121547698975</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8480072021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0003852844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2384738922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.713550567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7314796447754</t>
+    <t xml:space="preserve">31.8480033874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0003890991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2384719848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7135486602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.731481552124</t>
   </si>
   <si>
     <t xml:space="preserve">31.5432357788086</t>
@@ -4853,19 +4853,19 @@
     <t xml:space="preserve">31.8300762176514</t>
   </si>
   <si>
-    <t xml:space="preserve">31.821117401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1258811950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0900230407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2743301391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9068183898926</t>
+    <t xml:space="preserve">31.8211154937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1258773803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0900268554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2743263244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9068202972412</t>
   </si>
   <si>
     <t xml:space="preserve">30.9785289764404</t>
@@ -4877,40 +4877,40 @@
     <t xml:space="preserve">30.3958873748779</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8551158905029</t>
+    <t xml:space="preserve">30.8551139831543</t>
   </si>
   <si>
     <t xml:space="preserve">30.3069019317627</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6632404327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4307384490967</t>
+    <t xml:space="preserve">30.6632423400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.430736541748</t>
   </si>
   <si>
     <t xml:space="preserve">32.2896003723145</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9606704711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5769271850586</t>
+    <t xml:space="preserve">31.96067237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.57692527771</t>
   </si>
   <si>
     <t xml:space="preserve">31.3667774200439</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2114505767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3941860198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4764213562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6957035064697</t>
+    <t xml:space="preserve">31.2114524841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3941898345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4764194488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6957015991211</t>
   </si>
   <si>
     <t xml:space="preserve">31.8601665496826</t>
@@ -4919,19 +4919,19 @@
     <t xml:space="preserve">31.9698085784912</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9789447784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9241237640381</t>
+    <t xml:space="preserve">31.978946685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9241256713867</t>
   </si>
   <si>
     <t xml:space="preserve">32.6550750732422</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3626899719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3718299865723</t>
+    <t xml:space="preserve">32.3626937866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3718338012695</t>
   </si>
   <si>
     <t xml:space="preserve">32.9748611450195</t>
@@ -4940,19 +4940,19 @@
     <t xml:space="preserve">33.0205459594727</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2672424316406</t>
+    <t xml:space="preserve">33.2672386169434</t>
   </si>
   <si>
     <t xml:space="preserve">33.3677444458008</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5413436889648</t>
+    <t xml:space="preserve">33.5413475036621</t>
   </si>
   <si>
     <t xml:space="preserve">33.7423553466797</t>
   </si>
   <si>
-    <t xml:space="preserve">33.797176361084</t>
+    <t xml:space="preserve">33.7971801757812</t>
   </si>
   <si>
     <t xml:space="preserve">33.7514915466309</t>
@@ -4964,37 +4964,37 @@
     <t xml:space="preserve">32.947452545166</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2946510314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3311958312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2398300170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.404296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0936431884766</t>
+    <t xml:space="preserve">33.2946472167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3311996459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2398338317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4042930603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0936393737793</t>
   </si>
   <si>
     <t xml:space="preserve">32.6367988586426</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4175148010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3809623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6134700775146</t>
+    <t xml:space="preserve">32.4175109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3809661865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6134719848633</t>
   </si>
   <si>
     <t xml:space="preserve">31.8144836425781</t>
   </si>
   <si>
-    <t xml:space="preserve">32.581974029541</t>
+    <t xml:space="preserve">32.5819778442383</t>
   </si>
   <si>
     <t xml:space="preserve">32.5454292297363</t>
@@ -5009,7 +5009,7 @@
     <t xml:space="preserve">32.9109039306641</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1850090026855</t>
+    <t xml:space="preserve">33.1850051879883</t>
   </si>
   <si>
     <t xml:space="preserve">33.4408416748047</t>
@@ -5018,16 +5018,16 @@
     <t xml:space="preserve">33.7697639465332</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9525032043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4093437194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.884464263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4692192077637</t>
+    <t xml:space="preserve">33.9524993896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4093475341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8844604492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4692230224609</t>
   </si>
   <si>
     <t xml:space="preserve">36.5108184814453</t>
@@ -5042,10 +5042,10 @@
     <t xml:space="preserve">36.912841796875</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0590324401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7849273681641</t>
+    <t xml:space="preserve">37.0590286254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7849235534668</t>
   </si>
   <si>
     <t xml:space="preserve">37.0985145568848</t>
@@ -71183,7 +71183,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6494097222</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>99217</v>
@@ -71204,6 +71204,32 @@
         <v>1978</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.69125</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>119691</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>48.5200004577637</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>47.9199981689453</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>48.2999992370605</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>48.4000015258789</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1974</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BGN.MI.xlsx
+++ b/data/BGN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1979" uniqueCount="1979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1980" uniqueCount="1980">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4796028137207</t>
+    <t xml:space="preserve">17.4795989990234</t>
   </si>
   <si>
     <t xml:space="preserve">BGN.MI</t>
@@ -56,292 +56,292 @@
     <t xml:space="preserve">16.2628231048584</t>
   </si>
   <si>
-    <t xml:space="preserve">16.367826461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5098857879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9422435760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6457672119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1269397735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6760492324829</t>
+    <t xml:space="preserve">16.3678245544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5098876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9422416687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6457710266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1269378662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6760511398315</t>
   </si>
   <si>
     <t xml:space="preserve">15.9601745605469</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0707530975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0769271850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5092878341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.540168762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.428991317749</t>
+    <t xml:space="preserve">15.0707502365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0769300460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5092859268188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5401706695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4289894104004</t>
   </si>
   <si>
     <t xml:space="preserve">15.6019334793091</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1942796707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.478401184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2931089401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0213375091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8230895996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.718090057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5945606231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4580764770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6804323196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5636777877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1745529174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4154386520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0022096633911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8477983474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.385157585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4098615646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1936845779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4963350296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1813335418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3233909606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3357448577881</t>
+    <t xml:space="preserve">15.1942834854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.478404045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2931079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0213413238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8230905532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7180910110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5945587158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4580783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6804304122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5636758804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1745567321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4154405593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0022134780884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8477964401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3851537704468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4098625183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1936817169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4963331222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1813316345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.323392868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3357429504395</t>
   </si>
   <si>
     <t xml:space="preserve">14.5210409164429</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8607501983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2436971664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5710535049438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4969320297241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4351634979248</t>
+    <t xml:space="preserve">14.8607511520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2436943054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5710506439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4969329833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4351682662964</t>
   </si>
   <si>
     <t xml:space="preserve">15.4413433074951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3239879608154</t>
+    <t xml:space="preserve">15.3239908218384</t>
   </si>
   <si>
     <t xml:space="preserve">16.0157623291016</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2010593414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2937030792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1578254699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3431186676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8489952087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8922300338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6081132888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9354658126831</t>
+    <t xml:space="preserve">16.201057434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2937049865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1578216552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3431167602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8489933013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8922309875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6081104278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9354677200317</t>
   </si>
   <si>
     <t xml:space="preserve">15.9663505554199</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0095844268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.867525100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8298645019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8854551315308</t>
+    <t xml:space="preserve">16.0095863342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8675270080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8298664093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8854532241821</t>
   </si>
   <si>
     <t xml:space="preserve">14.6569213867188</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9410467147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3981065750122</t>
+    <t xml:space="preserve">14.9410448074341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3981084823608</t>
   </si>
   <si>
     <t xml:space="preserve">15.533992767334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.873703956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9478206634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1145896911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.083703994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0713500976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1084098815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2072353363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0589981079102</t>
+    <t xml:space="preserve">15.8737030029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9478168487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1145839691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0837059020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0713481903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1084079742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2072315216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0589962005615</t>
   </si>
   <si>
     <t xml:space="preserve">16.2998809814453</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1701755523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1207618713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7316379547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.379581451416</t>
+    <t xml:space="preserve">16.1701774597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1207656860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7316408157349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3795795440674</t>
   </si>
   <si>
     <t xml:space="preserve">15.1201648712158</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8916320800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7063369750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6383972167969</t>
+    <t xml:space="preserve">14.8916301727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7063360214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6383943557739</t>
   </si>
   <si>
     <t xml:space="preserve">14.6075096130371</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2986841201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4530982971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6692771911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3419198989868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3666248321533</t>
+    <t xml:space="preserve">14.2986812591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4530973434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6692790985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3419179916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.366623878479</t>
   </si>
   <si>
     <t xml:space="preserve">14.3913307189941</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3975105285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5537939071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8142652511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9640331268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5110206604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5956735610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3742723464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3286933898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1138048171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.009614944458</t>
+    <t xml:space="preserve">14.3975076675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5537929534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8142604827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9640321731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5110187530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5956745147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3742752075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3286914825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1138038635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.009617805481</t>
   </si>
   <si>
     <t xml:space="preserve">15.0551977157593</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2114810943604</t>
+    <t xml:space="preserve">15.211480140686</t>
   </si>
   <si>
     <t xml:space="preserve">15.3547391891479</t>
@@ -350,82 +350,82 @@
     <t xml:space="preserve">15.3026447296143</t>
   </si>
   <si>
-    <t xml:space="preserve">15.257061958313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8533315658569</t>
+    <t xml:space="preserve">15.2570638656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8533353805542</t>
   </si>
   <si>
     <t xml:space="preserve">14.0979690551758</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2058572769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9649200439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9453859329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1993446350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6616802215576</t>
+    <t xml:space="preserve">13.2058553695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9649219512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9453868865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1993427276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6616811752319</t>
   </si>
   <si>
     <t xml:space="preserve">13.8374967575073</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1565752029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5733270645142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8737564086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6690788269043</t>
+    <t xml:space="preserve">14.1565704345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5733251571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8737554550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6690807342529</t>
   </si>
   <si>
     <t xml:space="preserve">11.7341966629028</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6560592651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6821041107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6039619445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2002353668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8160419464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.431845664978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7444086074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2588386535645</t>
+    <t xml:space="preserve">11.6560554504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6821050643921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6039609909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2002334594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8160390853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4318447113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7444095611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2588405609131</t>
   </si>
   <si>
     <t xml:space="preserve">11.923038482666</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3137445449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2616510391235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5286331176758</t>
+    <t xml:space="preserve">12.3137454986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2616500854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5286340713501</t>
   </si>
   <si>
     <t xml:space="preserve">12.567702293396</t>
@@ -437,115 +437,115 @@
     <t xml:space="preserve">12.3723497390747</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5221214294434</t>
+    <t xml:space="preserve">12.522120475769</t>
   </si>
   <si>
     <t xml:space="preserve">12.5416564941406</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3397903442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5025882720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2551422119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4895620346069</t>
+    <t xml:space="preserve">12.3397912979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5025873184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2551383972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4895639419556</t>
   </si>
   <si>
     <t xml:space="preserve">12.242115020752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0337390899658</t>
+    <t xml:space="preserve">12.0337381362915</t>
   </si>
   <si>
     <t xml:space="preserve">11.8188495635986</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6300106048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4281454086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3825626373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8579206466675</t>
+    <t xml:space="preserve">11.6300115585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4281444549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3825635910034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8579216003418</t>
   </si>
   <si>
     <t xml:space="preserve">11.994668006897</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1835088729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2030429840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.053277015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9490852355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7928037643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5258226394653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7667570114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4411659240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3630285263062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5583801269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7797813415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5388450622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7472229003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6951265335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9425745010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1314153671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1379261016846</t>
+    <t xml:space="preserve">12.1835107803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2030458450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0532751083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9490880966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7928047180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.525821685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7667560577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4411678314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3630275726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5583820343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7797784805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5388441085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.747220993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6951274871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9425735473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1314163208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1379289627075</t>
   </si>
   <si>
     <t xml:space="preserve">12.4114208221436</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4830532073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6653804779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8021278381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3788633346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1183938980103</t>
+    <t xml:space="preserve">12.4830503463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6653814315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8021287918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3788604736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1183929443359</t>
   </si>
   <si>
     <t xml:space="preserve">12.1249055862427</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">12.2876996994019</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8709468841553</t>
+    <t xml:space="preserve">11.8709440231323</t>
   </si>
   <si>
     <t xml:space="preserve">11.701639175415</t>
@@ -569,28 +569,28 @@
     <t xml:space="preserve">11.2523279190063</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1937227249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1481409072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0830211639404</t>
+    <t xml:space="preserve">11.1937217712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1481399536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0830230712891</t>
   </si>
   <si>
     <t xml:space="preserve">11.122091293335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.174186706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1090688705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2848863601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1351156234741</t>
+    <t xml:space="preserve">11.1741847991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1090679168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2848854064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1351165771484</t>
   </si>
   <si>
     <t xml:space="preserve">11.076509475708</t>
@@ -602,163 +602,163 @@
     <t xml:space="preserve">11.0244159698486</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0179042816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6430330276489</t>
+    <t xml:space="preserve">11.0179052352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6430339813232</t>
   </si>
   <si>
     <t xml:space="preserve">11.5779161453247</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9100151062012</t>
+    <t xml:space="preserve">11.9100160598755</t>
   </si>
   <si>
     <t xml:space="preserve">12.1769990921021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2942085266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4309558868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9779453277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0365514755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3816728591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5640020370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.414231300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1732959747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0560865402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9258508682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8281745910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3295812606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7984266281128</t>
+    <t xml:space="preserve">12.2942094802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4309577941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9779443740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0365505218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3816747665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.564003944397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4142351150513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1732978820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0560836791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9258527755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8281736373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3295803070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7984294891357</t>
   </si>
   <si>
     <t xml:space="preserve">13.5444679260254</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8830814361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8309850692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9481983184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8895893096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1240139007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4923753738403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9388742446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9323635101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8672456741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9714317321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.990966796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7760801315308</t>
+    <t xml:space="preserve">13.88307762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8309860229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9481973648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8895921707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1240167617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4923725128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9388771057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9323625564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.867244720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9714326858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9909696578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7760810852051</t>
   </si>
   <si>
     <t xml:space="preserve">12.795615196228</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7304973602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.74351978302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4691371917725</t>
+    <t xml:space="preserve">12.7304992675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7435216903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4691390991211</t>
   </si>
   <si>
     <t xml:space="preserve">15.2896203994751</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8887062072754</t>
+    <t xml:space="preserve">15.8887014389038</t>
   </si>
   <si>
     <t xml:space="preserve">15.5761413574219</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3612499237061</t>
+    <t xml:space="preserve">15.3612508773804</t>
   </si>
   <si>
     <t xml:space="preserve">15.4784631729126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0747327804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1854295730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8989124298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8793811798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9575204849243</t>
+    <t xml:space="preserve">15.0747289657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1854343414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8989133834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8793773651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9575214385986</t>
   </si>
   <si>
     <t xml:space="preserve">14.9770565032959</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0031042098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7817039489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5863513946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7556562423706</t>
+    <t xml:space="preserve">15.0031061172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.781702041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5863485336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7556571960449</t>
   </si>
   <si>
     <t xml:space="preserve">14.859845161438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3417158126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4459009170532</t>
+    <t xml:space="preserve">15.3417148590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4458999633789</t>
   </si>
   <si>
     <t xml:space="preserve">14.8403100967407</t>
@@ -767,172 +767,172 @@
     <t xml:space="preserve">15.2700862884521</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5305585861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4133443832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3482255935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5631113052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5138339996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6570911407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5659294128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1231250762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0514965057373</t>
+    <t xml:space="preserve">15.5305576324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4133424758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3482246398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5631170272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5138320922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6570892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5659255981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1231288909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0514984130859</t>
   </si>
   <si>
     <t xml:space="preserve">15.6803274154663</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7454423904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7584686279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0356607437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3352012634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2375259399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4328813552856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2208023071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2924308776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1491737365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9538192749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1752223968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8626556396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5566034317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1593885421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2245035171509</t>
+    <t xml:space="preserve">15.7454462051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.758469581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0356636047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3352041244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2375268936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.432879447937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2208042144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2924327850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1491756439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.953821182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1752185821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8626575469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5566005706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1593856811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2245044708252</t>
   </si>
   <si>
     <t xml:space="preserve">14.8468198776245</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1658973693848</t>
+    <t xml:space="preserve">15.1658945083618</t>
   </si>
   <si>
     <t xml:space="preserve">15.4003200531006</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3091583251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6021852493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6217203140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6738128662109</t>
+    <t xml:space="preserve">15.3091554641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6021842956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6217231750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6738157272339</t>
   </si>
   <si>
     <t xml:space="preserve">15.5500907897949</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3677635192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3938064575195</t>
+    <t xml:space="preserve">15.3677616119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3938074111938</t>
   </si>
   <si>
     <t xml:space="preserve">15.1398506164551</t>
   </si>
   <si>
-    <t xml:space="preserve">15.107292175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0812435150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6152095794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6282320022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5435771942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7975406646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9342851638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.201265335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4422016143799</t>
+    <t xml:space="preserve">15.1072912216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.081244468689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6152076721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6282339096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5435781478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7975368499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9342832565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2012672424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4422035217285</t>
   </si>
   <si>
     <t xml:space="preserve">16.3770866394043</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2794094085693</t>
+    <t xml:space="preserve">16.2794055938721</t>
   </si>
   <si>
     <t xml:space="preserve">16.1426639556885</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4812717437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6049995422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2338275909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2561721801758</t>
+    <t xml:space="preserve">16.4812755584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6049976348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2338256835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2561740875244</t>
   </si>
   <si>
     <t xml:space="preserve">17.2691955566406</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1584968566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.145471572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1845455169678</t>
+    <t xml:space="preserve">17.1584949493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1454734802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1845436096191</t>
   </si>
   <si>
     <t xml:space="preserve">17.1389617919922</t>
@@ -941,22 +941,22 @@
     <t xml:space="preserve">17.646879196167</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6273441314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3892211914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1678218841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1027011871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3501491546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1352634429932</t>
+    <t xml:space="preserve">17.6273422241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.389217376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1678199768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1027030944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3501510620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1352596282959</t>
   </si>
   <si>
     <t xml:space="preserve">18.4934062957764</t>
@@ -965,16 +965,16 @@
     <t xml:space="preserve">18.0896797180176</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2264251708984</t>
+    <t xml:space="preserve">18.2264289855957</t>
   </si>
   <si>
     <t xml:space="preserve">18.8588085174561</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8723449707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6896419525146</t>
+    <t xml:space="preserve">18.8723430633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6896438598633</t>
   </si>
   <si>
     <t xml:space="preserve">18.6422748565674</t>
@@ -983,37 +983,37 @@
     <t xml:space="preserve">18.513708114624</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8370399475098</t>
+    <t xml:space="preserve">17.8370380401611</t>
   </si>
   <si>
     <t xml:space="preserve">17.6543350219727</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3836650848389</t>
+    <t xml:space="preserve">17.3836708068848</t>
   </si>
   <si>
     <t xml:space="preserve">17.9047031402588</t>
   </si>
   <si>
-    <t xml:space="preserve">17.931770324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5393009185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.546070098877</t>
+    <t xml:space="preserve">17.9317722320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5393028259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5460681915283</t>
   </si>
   <si>
     <t xml:space="preserve">17.9926719665527</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6761093139648</t>
+    <t xml:space="preserve">18.6761131286621</t>
   </si>
   <si>
     <t xml:space="preserve">18.926477432251</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8046760559082</t>
+    <t xml:space="preserve">18.8046798706055</t>
   </si>
   <si>
     <t xml:space="preserve">18.9806098937988</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">18.3377723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2092056274414</t>
+    <t xml:space="preserve">18.2092037200928</t>
   </si>
   <si>
     <t xml:space="preserve">17.9994373321533</t>
@@ -1037,31 +1037,31 @@
     <t xml:space="preserve">17.8641052246094</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8032035827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0062065124512</t>
+    <t xml:space="preserve">17.8032054901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0062084197998</t>
   </si>
   <si>
     <t xml:space="preserve">18.4054412841797</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0603408813477</t>
+    <t xml:space="preserve">18.0603370666504</t>
   </si>
   <si>
     <t xml:space="preserve">17.6340351104736</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2430381774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2701110839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6490440368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.452808380127</t>
+    <t xml:space="preserve">18.2430362701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2701072692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6490421295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4528064727783</t>
   </si>
   <si>
     <t xml:space="preserve">18.7031745910645</t>
@@ -1076,10 +1076,10 @@
     <t xml:space="preserve">18.94677734375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9197101593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7776126861572</t>
+    <t xml:space="preserve">18.9197082519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7776107788086</t>
   </si>
   <si>
     <t xml:space="preserve">18.8791103363037</t>
@@ -1088,19 +1088,19 @@
     <t xml:space="preserve">19.1362476348877</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0415115356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1836128234863</t>
+    <t xml:space="preserve">19.0415134429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1836109161377</t>
   </si>
   <si>
     <t xml:space="preserve">19.3730792999268</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2918796539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8264484405518</t>
+    <t xml:space="preserve">19.2918815612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8264503479004</t>
   </si>
   <si>
     <t xml:space="preserve">19.9414825439453</t>
@@ -1109,19 +1109,19 @@
     <t xml:space="preserve">20.3001174926758</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5166530609131</t>
+    <t xml:space="preserve">20.5166549682617</t>
   </si>
   <si>
     <t xml:space="preserve">20.0971183776855</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9956188201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1241836547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1444854736328</t>
+    <t xml:space="preserve">19.9956150054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1241855621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1444835662842</t>
   </si>
   <si>
     <t xml:space="preserve">20.6384544372559</t>
@@ -1136,67 +1136,67 @@
     <t xml:space="preserve">19.5625476837158</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7587833404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9211826324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9008808135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7993850708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7655506134033</t>
+    <t xml:space="preserve">19.7587814331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9211845397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9008865356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7993812561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7655487060547</t>
   </si>
   <si>
     <t xml:space="preserve">19.812915802002</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4813480377197</t>
+    <t xml:space="preserve">19.4813461303711</t>
   </si>
   <si>
     <t xml:space="preserve">19.5828495025635</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4881134033203</t>
+    <t xml:space="preserve">19.4881114959717</t>
   </si>
   <si>
     <t xml:space="preserve">19.2851142883301</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7640762329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7573089599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5949077606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8452777862549</t>
+    <t xml:space="preserve">18.7640781402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7573108673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5949058532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8452739715576</t>
   </si>
   <si>
     <t xml:space="preserve">18.8655776977539</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5340061187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0144443511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2242107391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1700801849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2512798309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1971454620361</t>
+    <t xml:space="preserve">18.5340099334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0144462585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2242126464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1700782775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.251277923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1971435546875</t>
   </si>
   <si>
     <t xml:space="preserve">19.4475135803223</t>
@@ -1205,28 +1205,28 @@
     <t xml:space="preserve">19.1633110046387</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2648124694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4678153991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2580432891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8602848052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8670501708984</t>
+    <t xml:space="preserve">19.2648143768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4678115844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2580451965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8602809906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8670520782471</t>
   </si>
   <si>
     <t xml:space="preserve">20.0159168243408</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4204502105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.569314956665</t>
+    <t xml:space="preserve">19.4204483032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5693168640137</t>
   </si>
   <si>
     <t xml:space="preserve">19.549015045166</t>
@@ -1238,55 +1238,55 @@
     <t xml:space="preserve">19.3663139343262</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4136772155762</t>
+    <t xml:space="preserve">19.4136829376221</t>
   </si>
   <si>
     <t xml:space="preserve">19.3527793884277</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5016498565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9400100708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8114414215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8858776092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2783470153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1565456390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0685768127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2106800079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1091804504395</t>
+    <t xml:space="preserve">19.5016441345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9400119781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8114452362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8858757019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2783489227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1565437316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0685787200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2106781005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1091766357422</t>
   </si>
   <si>
     <t xml:space="preserve">19.3189468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3324813842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2309799194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.657283782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1106491088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.982084274292</t>
+    <t xml:space="preserve">19.3324794769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.230978012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6572818756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1106510162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9820823669434</t>
   </si>
   <si>
     <t xml:space="preserve">19.7858486175537</t>
@@ -1295,31 +1295,31 @@
     <t xml:space="preserve">19.5354804992676</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9482498168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5760803222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6166820526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5557804107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3460140228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6911163330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6775817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2986450195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1903800964355</t>
+    <t xml:space="preserve">19.9482517242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5760822296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6166839599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5557823181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3460102081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6911144256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.677583694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2986488342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1903781890869</t>
   </si>
   <si>
     <t xml:space="preserve">19.3121814727783</t>
@@ -1331,52 +1331,52 @@
     <t xml:space="preserve">18.8182106018066</t>
   </si>
   <si>
-    <t xml:space="preserve">18.967077255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7708415985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4663429260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1889057159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6084423065186</t>
+    <t xml:space="preserve">18.9670791625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7708435058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4663410186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.188907623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6084403991699</t>
   </si>
   <si>
     <t xml:space="preserve">19.1497783660889</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1768436431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4745807647705</t>
+    <t xml:space="preserve">19.1768455505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4745826721191</t>
   </si>
   <si>
     <t xml:space="preserve">20.0294494628906</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0835838317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5301856994629</t>
+    <t xml:space="preserve">20.0835857391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5301876068115</t>
   </si>
   <si>
     <t xml:space="preserve">20.5031185150146</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8008556365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7602558135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7196559906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8685207366943</t>
+    <t xml:space="preserve">20.800853729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7602577209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7196578979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.868522644043</t>
   </si>
   <si>
     <t xml:space="preserve">20.7061214447021</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">20.4083862304688</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3136501312256</t>
+    <t xml:space="preserve">20.3136520385742</t>
   </si>
   <si>
     <t xml:space="preserve">19.8805828094482</t>
@@ -1397,43 +1397,43 @@
     <t xml:space="preserve">18.8926429748535</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0550441741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0265026092529</t>
+    <t xml:space="preserve">19.055046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0265045166016</t>
   </si>
   <si>
     <t xml:space="preserve">18.2024402618408</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2565746307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5813770294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5407752990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4866428375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4189720153809</t>
+    <t xml:space="preserve">18.2565727233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5813732147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5407733917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4866409301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4189758300781</t>
   </si>
   <si>
     <t xml:space="preserve">18.5272407531738</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4731044769287</t>
+    <t xml:space="preserve">18.4731101989746</t>
   </si>
   <si>
     <t xml:space="preserve">17.9859046936035</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4460411071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.662576675415</t>
+    <t xml:space="preserve">18.4460430145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6625785827637</t>
   </si>
   <si>
     <t xml:space="preserve">18.5678424835205</t>
@@ -1442,37 +1442,37 @@
     <t xml:space="preserve">18.7437782287598</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7302417755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3783721923828</t>
+    <t xml:space="preserve">18.7302436828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3783779144287</t>
   </si>
   <si>
     <t xml:space="preserve">17.8505687713623</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7558364868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7287731170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9723701477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0671043395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.148307800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2159748077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.324239730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3513069152832</t>
+    <t xml:space="preserve">17.7558345794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7287693023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9723720550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0671081542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1483039855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2159729003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3242416381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3513088226318</t>
   </si>
   <si>
     <t xml:space="preserve">18.3648414611816</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">18.7979106903076</t>
   </si>
   <si>
-    <t xml:space="preserve">18.906177520752</t>
+    <t xml:space="preserve">18.9061756134033</t>
   </si>
   <si>
     <t xml:space="preserve">18.1618404388428</t>
@@ -1502,10 +1502,10 @@
     <t xml:space="preserve">17.6611042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1738986968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0520973205566</t>
+    <t xml:space="preserve">17.173900604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0520992279053</t>
   </si>
   <si>
     <t xml:space="preserve">16.7814331054688</t>
@@ -1517,76 +1517,76 @@
     <t xml:space="preserve">16.8028087615967</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5605297088623</t>
+    <t xml:space="preserve">16.5605278015137</t>
   </si>
   <si>
     <t xml:space="preserve">16.7030487060547</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3039951324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2066106796265</t>
+    <t xml:space="preserve">16.3039970397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2066144943237</t>
   </si>
   <si>
     <t xml:space="preserve">14.2802495956421</t>
   </si>
   <si>
-    <t xml:space="preserve">14.85032081604</t>
+    <t xml:space="preserve">14.8503217697144</t>
   </si>
   <si>
     <t xml:space="preserve">14.8218154907227</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5344018936157</t>
+    <t xml:space="preserve">15.5344047546387</t>
   </si>
   <si>
     <t xml:space="preserve">15.3206272125244</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8930759429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4631462097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8336887359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3491344451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9477043151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8479442596436</t>
+    <t xml:space="preserve">14.8930749893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4631481170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8336906433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3491334915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9477033615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8479404449463</t>
   </si>
   <si>
     <t xml:space="preserve">15.8621940612793</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9192008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7054243087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7339286804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7196760177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3633823394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5058994293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.420389175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4488964080811</t>
+    <t xml:space="preserve">15.9192028045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7054271697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7339296340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7196779251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3633842468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5059022903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4203901290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4488935470581</t>
   </si>
   <si>
     <t xml:space="preserve">14.9500827789307</t>
@@ -1595,43 +1595,43 @@
     <t xml:space="preserve">14.935830116272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.178111076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5629072189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6484174728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.890697479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0189647674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.434642791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3776359558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4916496276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.52015209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7909336090088</t>
+    <t xml:space="preserve">15.178108215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5629091262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6484155654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8906984329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0189628601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4346418380737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3776350021362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4916467666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5201539993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7909364700317</t>
   </si>
   <si>
     <t xml:space="preserve">15.7766857147217</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6056604385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4750194549561</t>
+    <t xml:space="preserve">15.605658531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4750213623047</t>
   </si>
   <si>
     <t xml:space="preserve">16.2469902038574</t>
@@ -1643,10 +1643,10 @@
     <t xml:space="preserve">16.4465160369873</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5035209655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9619569778442</t>
+    <t xml:space="preserve">16.5035228729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.961953163147</t>
   </si>
   <si>
     <t xml:space="preserve">16.0474681854248</t>
@@ -1655,94 +1655,94 @@
     <t xml:space="preserve">16.2184867858887</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2042331695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1614799499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7481803894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9049510955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2754955291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4037590026855</t>
+    <t xml:space="preserve">16.2042350769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1614818572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7481813430786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9049472808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2754917144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4037628173828</t>
   </si>
   <si>
     <t xml:space="preserve">16.3325023651123</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2636222839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0783491134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3063745498657</t>
+    <t xml:space="preserve">15.2636213302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0783452987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3063764572144</t>
   </si>
   <si>
     <t xml:space="preserve">15.2921228408813</t>
   </si>
   <si>
-    <t xml:space="preserve">15.548659324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6769247055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6175327301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7885589599609</t>
+    <t xml:space="preserve">15.5486545562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6769218444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6175384521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7885551452637</t>
   </si>
   <si>
     <t xml:space="preserve">16.8598155975342</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3443794250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.387134552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1020946502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8764457702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6911706924438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6626710891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.964334487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7933149337769</t>
+    <t xml:space="preserve">17.3443756103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3871307373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1020965576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.876446723938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6911735534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6626691818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9643306732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7933139801025</t>
   </si>
   <si>
     <t xml:space="preserve">14.351508140564</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2161159515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3372592926025</t>
+    <t xml:space="preserve">14.2161178588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3372573852539</t>
   </si>
   <si>
     <t xml:space="preserve">14.7220544815063</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4227666854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0593481063843</t>
+    <t xml:space="preserve">14.4227685928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0593490600586</t>
   </si>
   <si>
     <t xml:space="preserve">13.539158821106</t>
@@ -1760,91 +1760,91 @@
     <t xml:space="preserve">12.4203958511353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.285005569458</t>
+    <t xml:space="preserve">12.2850065231323</t>
   </si>
   <si>
     <t xml:space="preserve">12.4061450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1353626251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3705158233643</t>
+    <t xml:space="preserve">12.1353645324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3705167770386</t>
   </si>
   <si>
     <t xml:space="preserve">12.904956817627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8622026443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9334592819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1472368240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2755012512207</t>
+    <t xml:space="preserve">12.8621988296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9334583282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1472358703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2755031585693</t>
   </si>
   <si>
     <t xml:space="preserve">13.1187324523926</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0688524246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5462856292725</t>
+    <t xml:space="preserve">13.0688505172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5462837219238</t>
   </si>
   <si>
     <t xml:space="preserve">13.1116075515747</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7838172912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7339353561401</t>
+    <t xml:space="preserve">12.7838163375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7339363098145</t>
   </si>
   <si>
     <t xml:space="preserve">12.6698036193848</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9192094802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9548387527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2470006942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5961666107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1092290878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9453325271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8812026977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8883256912231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4655237197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.223240852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.087851524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3681373596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4679012298584</t>
+    <t xml:space="preserve">12.9192085266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9548397064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2469968795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5961685180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1092281341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9453353881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8812007904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8883285522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4655208587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2232427597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0878496170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3681402206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4678983688354</t>
   </si>
   <si>
     <t xml:space="preserve">13.1258583068848</t>
@@ -1853,58 +1853,58 @@
     <t xml:space="preserve">12.9690914154053</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4892778396606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6317949295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2327470779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3966407775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8265724182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5344123840332</t>
+    <t xml:space="preserve">13.4892797470093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.631796836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2327461242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3966417312622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8265733718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5344114303589</t>
   </si>
   <si>
     <t xml:space="preserve">13.1044807434082</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9975919723511</t>
+    <t xml:space="preserve">12.9975938796997</t>
   </si>
   <si>
     <t xml:space="preserve">13.6104192733765</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7529335021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6389207839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1448583602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3230047225952</t>
+    <t xml:space="preserve">13.7529354095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6389217376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1448602676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3230056762695</t>
   </si>
   <si>
     <t xml:space="preserve">14.2018661499023</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1947383880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.895453453064</t>
+    <t xml:space="preserve">14.1947402954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8954553604126</t>
   </si>
   <si>
     <t xml:space="preserve">14.3942651748657</t>
   </si>
   <si>
-    <t xml:space="preserve">14.593789100647</t>
+    <t xml:space="preserve">14.5937881469727</t>
   </si>
   <si>
     <t xml:space="preserve">14.7078018188477</t>
@@ -1913,94 +1913,94 @@
     <t xml:space="preserve">14.508279800415</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6935501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8075637817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6365451812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7648105621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7363061904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6792974472046</t>
+    <t xml:space="preserve">14.6935510635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8075656890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6365442276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7648077011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7363080978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6793003082275</t>
   </si>
   <si>
     <t xml:space="preserve">14.265998840332</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5367832183838</t>
+    <t xml:space="preserve">14.5367813110352</t>
   </si>
   <si>
     <t xml:space="preserve">14.2944993972778</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5510330200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1923627853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9785852432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2778739929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2493715286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2208681106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.406135559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8194408416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8051853179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.634165763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5914106369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4322624206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6032848358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7172985076904</t>
+    <t xml:space="preserve">14.5510320663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1923599243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9785842895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2778701782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2493696212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2208652496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4061412811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8194398880005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8051862716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6341648101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5914087295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4322643280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6032829284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7173004150391</t>
   </si>
   <si>
     <t xml:space="preserve">16.7743072509766</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8170623779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.030834197998</t>
+    <t xml:space="preserve">16.8170604705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0308380126953</t>
   </si>
   <si>
     <t xml:space="preserve">17.1591033935547</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2588634490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3158721923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4583873748779</t>
+    <t xml:space="preserve">17.2588672637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3158740997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4583892822266</t>
   </si>
   <si>
     <t xml:space="preserve">17.4726409912109</t>
@@ -2012,49 +2012,49 @@
     <t xml:space="preserve">17.7861804962158</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9286956787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0569610595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0854644775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5581493377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5866546630859</t>
+    <t xml:space="preserve">17.9286975860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0569629669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0854663848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5581512451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5866565704346</t>
   </si>
   <si>
     <t xml:space="preserve">17.2018566131592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4298839569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5296440124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4868946075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7196521759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8548011779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2991847991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2241020202637</t>
+    <t xml:space="preserve">17.4298858642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5296497344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4868907928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7196502685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8548030853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.299186706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2241039276123</t>
   </si>
   <si>
     <t xml:space="preserve">17.2691516876221</t>
   </si>
   <si>
-    <t xml:space="preserve">17.149019241333</t>
+    <t xml:space="preserve">17.1490173339844</t>
   </si>
   <si>
     <t xml:space="preserve">16.7435684204102</t>
@@ -2066,61 +2066,61 @@
     <t xml:space="preserve">16.9237689971924</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6985206604004</t>
+    <t xml:space="preserve">16.6985168457031</t>
   </si>
   <si>
     <t xml:space="preserve">17.2541351318359</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5394535064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1640357971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0589179992676</t>
+    <t xml:space="preserve">17.5394515991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1640319824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0589199066162</t>
   </si>
   <si>
     <t xml:space="preserve">17.4343338012695</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8247699737549</t>
+    <t xml:space="preserve">17.8247661590576</t>
   </si>
   <si>
     <t xml:space="preserve">17.9298839569092</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8397827148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7496814727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9448986053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6657028198242</t>
+    <t xml:space="preserve">17.839786529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.749683380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9449005126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.665699005127</t>
   </si>
   <si>
     <t xml:space="preserve">18.8458995819092</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1762676239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3714809417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.056131362915</t>
+    <t xml:space="preserve">19.17626953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3714828491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0561351776123</t>
   </si>
   <si>
     <t xml:space="preserve">19.1312160491943</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4165344238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1462345123291</t>
+    <t xml:space="preserve">19.4165306091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1462306976318</t>
   </si>
   <si>
     <t xml:space="preserve">19.0110836029053</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">19.2213153839111</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7318859100342</t>
+    <t xml:space="preserve">19.7318820953369</t>
   </si>
   <si>
     <t xml:space="preserve">19.7769336700439</t>
@@ -2144,19 +2144,19 @@
     <t xml:space="preserve">20.0772647857666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9721488952637</t>
+    <t xml:space="preserve">19.972146987915</t>
   </si>
   <si>
     <t xml:space="preserve">20.2574653625488</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1373329162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1823806762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.897066116333</t>
+    <t xml:space="preserve">20.1373310089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1823825836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8970680236816</t>
   </si>
   <si>
     <t xml:space="preserve">20.0472316741943</t>
@@ -2168,88 +2168,88 @@
     <t xml:space="preserve">20.0171985626221</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6567993164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8219833374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6868324279785</t>
+    <t xml:space="preserve">19.6568012237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.821985244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6868286132812</t>
   </si>
   <si>
     <t xml:space="preserve">19.8369998931885</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9421138763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3325481414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5817165374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4916172027588</t>
+    <t xml:space="preserve">19.9421157836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3325500488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5817127227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4916191101074</t>
   </si>
   <si>
     <t xml:space="preserve">19.671817779541</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7168674468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7619152069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2874965667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9120807647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.122314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0622482299805</t>
+    <t xml:space="preserve">19.7168655395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7619171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2875003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9120826721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1223163604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0622463226318</t>
   </si>
   <si>
     <t xml:space="preserve">20.3025150299072</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5728149414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.662914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9932804107666</t>
+    <t xml:space="preserve">20.572811126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6629161834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.993278503418</t>
   </si>
   <si>
     <t xml:space="preserve">21.1434478759766</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1584625244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3536815643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.00830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2635803222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2936172485352</t>
+    <t xml:space="preserve">21.1584644317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3536834716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0082988739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.263578414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2936153411865</t>
   </si>
   <si>
     <t xml:space="preserve">21.4287662506104</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6089649200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5338821411133</t>
+    <t xml:space="preserve">21.6089687347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5338802337646</t>
   </si>
   <si>
     <t xml:space="preserve">20.9782657623291</t>
@@ -2258,10 +2258,10 @@
     <t xml:space="preserve">20.8881664276123</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2335510253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2485656738281</t>
+    <t xml:space="preserve">21.233549118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2485637664795</t>
   </si>
   <si>
     <t xml:space="preserve">21.1734828948975</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">20.7680320739746</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0833797454834</t>
+    <t xml:space="preserve">21.083381652832</t>
   </si>
   <si>
     <t xml:space="preserve">20.7980670928955</t>
@@ -2285,22 +2285,22 @@
     <t xml:space="preserve">19.8670310974121</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7229804992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2035160064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3086318969727</t>
+    <t xml:space="preserve">20.7229824066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2035140991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3086338043213</t>
   </si>
   <si>
     <t xml:space="preserve">21.4888324737549</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5639133453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1134147644043</t>
+    <t xml:space="preserve">21.5639114379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1134166717529</t>
   </si>
   <si>
     <t xml:space="preserve">21.3837146759033</t>
@@ -2309,55 +2309,55 @@
     <t xml:space="preserve">21.3236465454102</t>
   </si>
   <si>
-    <t xml:space="preserve">21.578929901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8191947937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8492317199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9543476104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5850486755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4799289703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6601295471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1256465911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3208618164062</t>
+    <t xml:space="preserve">21.5789318084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8191967010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8492298126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.954345703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5850467681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4799327850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6601314544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1256446838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3208637237549</t>
   </si>
   <si>
     <t xml:space="preserve">23.0805969238281</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2007293701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3058471679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4259834289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6962757110596</t>
+    <t xml:space="preserve">23.2007274627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3058490753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4259815216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6962814331055</t>
   </si>
   <si>
     <t xml:space="preserve">23.9215297698975</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7263126373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6662483215332</t>
+    <t xml:space="preserve">23.7263145446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6662445068359</t>
   </si>
   <si>
     <t xml:space="preserve">23.9065132141113</t>
@@ -2366,37 +2366,37 @@
     <t xml:space="preserve">23.2908306121826</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3959465026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2758102416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0956134796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4949474334717</t>
+    <t xml:space="preserve">23.3959445953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2758121490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0956115722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.494945526123</t>
   </si>
   <si>
     <t xml:space="preserve">22.6300964355469</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5249786376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0355472564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9454479217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5399951934814</t>
+    <t xml:space="preserve">22.5249805450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0355491638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9454441070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5399971008301</t>
   </si>
   <si>
     <t xml:space="preserve">22.6000652313232</t>
   </si>
   <si>
-    <t xml:space="preserve">22.645112991333</t>
+    <t xml:space="preserve">22.6451148986816</t>
   </si>
   <si>
     <t xml:space="preserve">22.7352142333984</t>
@@ -2408,13 +2408,13 @@
     <t xml:space="preserve">22.1946125030518</t>
   </si>
   <si>
-    <t xml:space="preserve">22.104513168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1795978546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7291011810303</t>
+    <t xml:space="preserve">22.1045150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1795959472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7290992736816</t>
   </si>
   <si>
     <t xml:space="preserve">22.0594635009766</t>
@@ -2438,16 +2438,16 @@
     <t xml:space="preserve">22.7051830291748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9904975891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9754791259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8102970123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8253154754639</t>
+    <t xml:space="preserve">22.9905014038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9754810333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8102989196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8253135681152</t>
   </si>
   <si>
     <t xml:space="preserve">22.0744819641113</t>
@@ -2456,49 +2456,49 @@
     <t xml:space="preserve">22.8853816986084</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1645793914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.299732208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8553447723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7952823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3508949279785</t>
+    <t xml:space="preserve">22.1645812988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2997303009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8553466796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7952785491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3508968353271</t>
   </si>
   <si>
     <t xml:space="preserve">24.1017284393311</t>
   </si>
   <si>
-    <t xml:space="preserve">24.447114944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4170799255371</t>
+    <t xml:space="preserve">24.4471130371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4170780181885</t>
   </si>
   <si>
     <t xml:space="preserve">24.6723613739014</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6573467254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7774753570557</t>
+    <t xml:space="preserve">24.6573448181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7774772644043</t>
   </si>
   <si>
     <t xml:space="preserve">24.3269805908203</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8764801025391</t>
+    <t xml:space="preserve">23.8764781951904</t>
   </si>
   <si>
     <t xml:space="preserve">22.2396640777588</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9181976318359</t>
+    <t xml:space="preserve">20.9181995391846</t>
   </si>
   <si>
     <t xml:space="preserve">20.4226493835449</t>
@@ -2507,91 +2507,91 @@
     <t xml:space="preserve">20.4827175140381</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0411167144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5906162261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9688167572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8876209259033</t>
+    <t xml:space="preserve">19.0411148071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5906143188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9688186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8876171112061</t>
   </si>
   <si>
     <t xml:space="preserve">15.7975225448608</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6201038360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6937942504883</t>
+    <t xml:space="preserve">13.6201057434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6937961578369</t>
   </si>
   <si>
     <t xml:space="preserve">13.2146549224854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9894046783447</t>
+    <t xml:space="preserve">12.989405632019</t>
   </si>
   <si>
     <t xml:space="preserve">12.6590394973755</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0344552993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7266139984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8917980194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9054203033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.018045425415</t>
+    <t xml:space="preserve">13.0344562530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7266149520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8917970657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9054193496704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0180473327637</t>
   </si>
   <si>
     <t xml:space="preserve">14.5811700820923</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0781145095825</t>
+    <t xml:space="preserve">14.0781126022339</t>
   </si>
   <si>
     <t xml:space="preserve">14.3559217453003</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1982450485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3183784484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0555858612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7688798904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4671516418457</t>
+    <t xml:space="preserve">14.1982460021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3183813095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0555868148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7688789367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.467155456543</t>
   </si>
   <si>
     <t xml:space="preserve">16.7886180877686</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7074165344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9026355743408</t>
+    <t xml:space="preserve">15.7074203491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9026365280151</t>
   </si>
   <si>
     <t xml:space="preserve">15.9326696395874</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7674865722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1518020629883</t>
+    <t xml:space="preserve">15.7674827575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1518058776855</t>
   </si>
   <si>
     <t xml:space="preserve">15.3770532608032</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">15.4821691513062</t>
   </si>
   <si>
-    <t xml:space="preserve">16.683500289917</t>
+    <t xml:space="preserve">16.6835041046143</t>
   </si>
   <si>
     <t xml:space="preserve">16.8937339782715</t>
@@ -2612,22 +2612,22 @@
     <t xml:space="preserve">17.0138683319092</t>
   </si>
   <si>
-    <t xml:space="preserve">16.533332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.503303527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9087524414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4643688201904</t>
+    <t xml:space="preserve">16.5333347320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5033016204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9087543487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4643669128418</t>
   </si>
   <si>
     <t xml:space="preserve">17.1039695739746</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5244331359863</t>
+    <t xml:space="preserve">17.5244369506836</t>
   </si>
   <si>
     <t xml:space="preserve">17.1189842224121</t>
@@ -2636,25 +2636,25 @@
     <t xml:space="preserve">17.2391204833984</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1340026855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3892822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4043006896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6896190643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.365364074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.290283203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.485502243042</t>
+    <t xml:space="preserve">17.1339988708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3892841339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4043025970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6896152496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3653659820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2902812957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4855003356934</t>
   </si>
   <si>
     <t xml:space="preserve">18.9510154724121</t>
@@ -2663,55 +2663,55 @@
     <t xml:space="preserve">19.2813835144043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8520183563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3414497375488</t>
+    <t xml:space="preserve">19.8520164489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3414516448975</t>
   </si>
   <si>
     <t xml:space="preserve">19.5516834259033</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3953990936279</t>
+    <t xml:space="preserve">18.3954010009766</t>
   </si>
   <si>
     <t xml:space="preserve">19.4315490722656</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1673679351807</t>
+    <t xml:space="preserve">20.167366027832</t>
   </si>
   <si>
     <t xml:space="preserve">19.3264331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9571323394775</t>
+    <t xml:space="preserve">19.9571342468262</t>
   </si>
   <si>
     <t xml:space="preserve">20.1072998046875</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6779327392578</t>
+    <t xml:space="preserve">20.6779308319092</t>
   </si>
   <si>
     <t xml:space="preserve">19.2663650512695</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5066337585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8820495605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0922832489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3475646972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3775997161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5967330932617</t>
+    <t xml:space="preserve">19.5066318511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8820476531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.09228515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.347562789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3775978088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5967350006104</t>
   </si>
   <si>
     <t xml:space="preserve">18.7107467651367</t>
@@ -2720,31 +2720,31 @@
     <t xml:space="preserve">18.9209823608398</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7708168029785</t>
+    <t xml:space="preserve">18.7708148956299</t>
   </si>
   <si>
     <t xml:space="preserve">18.830883026123</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5666980743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0861663818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9059677124023</t>
+    <t xml:space="preserve">19.5666999816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0861644744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.905969619751</t>
   </si>
   <si>
     <t xml:space="preserve">19.0711498260498</t>
   </si>
   <si>
-    <t xml:space="preserve">18.755802154541</t>
+    <t xml:space="preserve">18.7558002471924</t>
   </si>
   <si>
     <t xml:space="preserve">19.4766006469727</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2964019775391</t>
+    <t xml:space="preserve">19.2964000701904</t>
   </si>
   <si>
     <t xml:space="preserve">19.5366668701172</t>
@@ -2753,13 +2753,13 @@
     <t xml:space="preserve">19.5216503143311</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3114166259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9810523986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4526824951172</t>
+    <t xml:space="preserve">19.3114147186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.981050491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4526844024658</t>
   </si>
   <si>
     <t xml:space="preserve">20.6178665161133</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">20.3625831604004</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6417827606201</t>
+    <t xml:space="preserve">19.6417808532715</t>
   </si>
   <si>
     <t xml:space="preserve">20.0322189331055</t>
@@ -2780,13 +2780,13 @@
     <t xml:space="preserve">20.5127506256104</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2424468994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7379970550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0021800994873</t>
+    <t xml:space="preserve">20.2424449920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7379989624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0021820068359</t>
   </si>
   <si>
     <t xml:space="preserve">18.215202331543</t>
@@ -2795,22 +2795,22 @@
     <t xml:space="preserve">18.1401176452637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3203201293945</t>
+    <t xml:space="preserve">18.3203182220459</t>
   </si>
   <si>
     <t xml:space="preserve">20.5577983856201</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4376640319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1284313201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7830467224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4977283477783</t>
+    <t xml:space="preserve">20.4376659393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1284332275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7830486297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4977321624756</t>
   </si>
   <si>
     <t xml:space="preserve">21.0233154296875</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">21.3686962127686</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9031829833984</t>
+    <t xml:space="preserve">20.9031791687012</t>
   </si>
   <si>
     <t xml:space="preserve">21.0383319854736</t>
@@ -2837,94 +2837,94 @@
     <t xml:space="preserve">20.3175315856934</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2124156951904</t>
+    <t xml:space="preserve">20.2124176025391</t>
   </si>
   <si>
     <t xml:space="preserve">19.4465675354004</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7468967437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2363338470459</t>
+    <t xml:space="preserve">19.746898651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2363357543945</t>
   </si>
   <si>
     <t xml:space="preserve">20.5277633666992</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7140808105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.684045791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6389999389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3386650085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6239795684814</t>
+    <t xml:space="preserve">21.7140827178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6840476989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6389980316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3386631011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6239776611328</t>
   </si>
   <si>
     <t xml:space="preserve">21.8642482757568</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3987331390381</t>
+    <t xml:space="preserve">21.3987312316895</t>
   </si>
   <si>
     <t xml:space="preserve">21.4437808990479</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1884994506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9092960357666</t>
+    <t xml:space="preserve">21.188497543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9092979431152</t>
   </si>
   <si>
     <t xml:space="preserve">21.8942813873291</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8342151641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5038452148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2546806335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0444469451904</t>
+    <t xml:space="preserve">21.8342132568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.503849029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2546768188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0444507598877</t>
   </si>
   <si>
     <t xml:space="preserve">22.2847137451172</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3447799682617</t>
+    <t xml:space="preserve">22.3447818756104</t>
   </si>
   <si>
     <t xml:space="preserve">22.4649143218994</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6901626586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.870361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6150817871094</t>
+    <t xml:space="preserve">22.6901607513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8703632354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6150798797607</t>
   </si>
   <si>
     <t xml:space="preserve">22.5700302124023</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6751480102539</t>
+    <t xml:space="preserve">22.6751461029053</t>
   </si>
   <si>
     <t xml:space="preserve">22.5775375366211</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9079036712646</t>
+    <t xml:space="preserve">22.9079055786133</t>
   </si>
   <si>
     <t xml:space="preserve">23.0430545806885</t>
@@ -2933,79 +2933,79 @@
     <t xml:space="preserve">23.0881061553955</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8178024291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.84033203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1706962585449</t>
+    <t xml:space="preserve">22.8178043365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8403282165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1706981658936</t>
   </si>
   <si>
     <t xml:space="preserve">23.2157459259033</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3809261322021</t>
+    <t xml:space="preserve">23.3809280395508</t>
   </si>
   <si>
     <t xml:space="preserve">23.523588180542</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0505676269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.915412902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0730895996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.253288269043</t>
+    <t xml:space="preserve">23.0505638122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9154148101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0730876922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2532863616943</t>
   </si>
   <si>
     <t xml:space="preserve">23.3433895111084</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2983379364014</t>
+    <t xml:space="preserve">23.29833984375</t>
   </si>
   <si>
     <t xml:space="preserve">23.8914947509766</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2594032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0942192077637</t>
+    <t xml:space="preserve">24.259407043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0942230224609</t>
   </si>
   <si>
     <t xml:space="preserve">24.664852142334</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5522308349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4621295928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7924976348877</t>
+    <t xml:space="preserve">24.5522270202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4621315002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7924957275391</t>
   </si>
   <si>
     <t xml:space="preserve">24.402063369751</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0491714477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4696369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4245872497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1993350982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9590682983398</t>
+    <t xml:space="preserve">24.0491695404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4696388244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4245853424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1993370056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9590702056885</t>
   </si>
   <si>
     <t xml:space="preserve">24.1617965698242</t>
@@ -3014,100 +3014,100 @@
     <t xml:space="preserve">24.2293701171875</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6273155212402</t>
+    <t xml:space="preserve">24.6273136138916</t>
   </si>
   <si>
     <t xml:space="preserve">24.8075103759766</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8150215148926</t>
+    <t xml:space="preserve">24.8150196075439</t>
   </si>
   <si>
     <t xml:space="preserve">25.1078433990479</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2204704284668</t>
+    <t xml:space="preserve">25.2204723358154</t>
   </si>
   <si>
     <t xml:space="preserve">25.1003379821777</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1829319000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2955532073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5208053588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.828649520874</t>
+    <t xml:space="preserve">25.1829299926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2955513000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5208034515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8286457061768</t>
   </si>
   <si>
     <t xml:space="preserve">25.8061199188232</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7385406494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7835960388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0538959503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8661918640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.489372253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5118999481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3767528533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4668483734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6545600891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5869846343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1050624847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5180168151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1350936889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3903732299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0149593353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0374813079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2176837921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1951599121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2251949310303</t>
+    <t xml:space="preserve">25.73854637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7835941314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0538940429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8661861419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4893760681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5119075775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3767547607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4668521881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.65456199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5869884490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1050567626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5180206298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1350917816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3903770446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0149612426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.037483215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2176856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.195161819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2251930236816</t>
   </si>
   <si>
     <t xml:space="preserve">26.2566184997559</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6845989227295</t>
+    <t xml:space="preserve">26.6845951080322</t>
   </si>
   <si>
     <t xml:space="preserve">27.1726322174072</t>
@@ -3116,58 +3116,58 @@
     <t xml:space="preserve">27.0299777984619</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7446613311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6245250701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8962211608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0163516998291</t>
+    <t xml:space="preserve">26.7446594238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6245269775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.89621925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0163555145264</t>
   </si>
   <si>
     <t xml:space="preserve">26.3992786407471</t>
   </si>
   <si>
-    <t xml:space="preserve">26.35422706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5569534301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0013370513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0238609313965</t>
+    <t xml:space="preserve">26.3542251586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5569553375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0013389587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0238628387451</t>
   </si>
   <si>
     <t xml:space="preserve">26.4218006134033</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2866516113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2115688323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8873157501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1125659942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3603420257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3828659057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.645658493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6231346130371</t>
+    <t xml:space="preserve">26.2866497039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2115707397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8873233795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1125679016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3603439331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.382869720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6456565856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6231365203857</t>
   </si>
   <si>
     <t xml:space="preserve">27.7808113098145</t>
@@ -3176,16 +3176,16 @@
     <t xml:space="preserve">27.5931015014648</t>
   </si>
   <si>
-    <t xml:space="preserve">27.42041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5630664825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7883167266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7132339477539</t>
+    <t xml:space="preserve">27.4204120635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5630645751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7883148193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7132320404053</t>
   </si>
   <si>
     <t xml:space="preserve">27.9535007476807</t>
@@ -3194,64 +3194,64 @@
     <t xml:space="preserve">27.9835338592529</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2613468170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1412048339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2087841033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1862602233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.381477355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2012805938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.058614730835</t>
+    <t xml:space="preserve">28.2613430023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1412086486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2087821960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.18625831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3814697265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2012767791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0586166381836</t>
   </si>
   <si>
     <t xml:space="preserve">28.1186847686768</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4115085601807</t>
+    <t xml:space="preserve">28.411506652832</t>
   </si>
   <si>
     <t xml:space="preserve">29.1698474884033</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3875885009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5077228546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2899799346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9145679473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.419017791748</t>
+    <t xml:space="preserve">29.3875923156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5077247619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.289981842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9145660400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4190139770508</t>
   </si>
   <si>
     <t xml:space="preserve">28.6442699432373</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1923770904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1323089599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.214900970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5842037200928</t>
+    <t xml:space="preserve">29.1923751831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1323051452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2148990631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5842018127441</t>
   </si>
   <si>
     <t xml:space="preserve">28.4865913391113</t>
@@ -3260,13 +3260,13 @@
     <t xml:space="preserve">28.4565563201904</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5466594696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4640693664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8784160614014</t>
+    <t xml:space="preserve">28.5466556549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4640655517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8784198760986</t>
   </si>
   <si>
     <t xml:space="preserve">28.4715728759766</t>
@@ -3275,16 +3275,16 @@
     <t xml:space="preserve">28.4040012359619</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0736312866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3964900970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.02858543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7643966674805</t>
+    <t xml:space="preserve">28.0736331939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3964920043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0285873413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7644004821777</t>
   </si>
   <si>
     <t xml:space="preserve">29.6954326629639</t>
@@ -3293,34 +3293,34 @@
     <t xml:space="preserve">29.7179584503174</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9432125091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4012184143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7240676879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5213508605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6940498352051</t>
+    <t xml:space="preserve">29.9432067871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4012145996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7240753173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5213489532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6940402984619</t>
   </si>
   <si>
     <t xml:space="preserve">30.5288581848145</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7090549468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4988231658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7766304016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7602214813232</t>
+    <t xml:space="preserve">30.7090606689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4988250732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7766342163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.760217666626</t>
   </si>
   <si>
     <t xml:space="preserve">32.2107238769531</t>
@@ -3332,19 +3332,19 @@
     <t xml:space="preserve">31.7376937866211</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1506462097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3083267211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3458786010742</t>
+    <t xml:space="preserve">32.1506538391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3083229064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3458709716797</t>
   </si>
   <si>
     <t xml:space="preserve">31.8728466033936</t>
   </si>
   <si>
-    <t xml:space="preserve">31.137035369873</t>
+    <t xml:space="preserve">31.1370315551758</t>
   </si>
   <si>
     <t xml:space="preserve">30.8592224121094</t>
@@ -3356,22 +3356,22 @@
     <t xml:space="preserve">31.4641075134277</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2591972351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0342807769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.640682220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8052825927734</t>
+    <t xml:space="preserve">30.2591953277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0342826843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6406803131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8052806854248</t>
   </si>
   <si>
     <t xml:space="preserve">29.1265907287598</t>
   </si>
   <si>
-    <t xml:space="preserve">29.08642578125</t>
+    <t xml:space="preserve">29.0864219665527</t>
   </si>
   <si>
     <t xml:space="preserve">30.0583839416504</t>
@@ -3386,64 +3386,64 @@
     <t xml:space="preserve">30.5885448455811</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3596801757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3195247650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0303382873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1508331298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.335578918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2632827758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1668949127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1187000274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6046104431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.753137588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4118232727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5644416809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5483741760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9419803619385</t>
+    <t xml:space="preserve">31.3596878051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3195209503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0303421020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.150821685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3355827331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2632865905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1668910980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1187038421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6046085357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7531356811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4118213653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5644435882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.548376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9419765472412</t>
   </si>
   <si>
     <t xml:space="preserve">31.2713222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1829643249512</t>
+    <t xml:space="preserve">31.1829605102539</t>
   </si>
   <si>
     <t xml:space="preserve">31.1267318725586</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2150974273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2311630249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1909999847412</t>
+    <t xml:space="preserve">31.2150936126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2311592102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1909923553467</t>
   </si>
   <si>
     <t xml:space="preserve">30.435920715332</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">30.2029705047607</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1788749694824</t>
+    <t xml:space="preserve">30.1788730621338</t>
   </si>
   <si>
     <t xml:space="preserve">30.837553024292</t>
@@ -3461,25 +3461,25 @@
     <t xml:space="preserve">30.8616542816162</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5082130432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3475608825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2913341522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4800262451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8856086730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3996963500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9338073730469</t>
+    <t xml:space="preserve">30.5082149505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3475570678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2913265228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4800319671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8856067657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3997001647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9338054656982</t>
   </si>
   <si>
     <t xml:space="preserve">27.7208652496338</t>
@@ -3488,82 +3488,82 @@
     <t xml:space="preserve">27.1907062530518</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6807022094727</t>
+    <t xml:space="preserve">27.680700302124</t>
   </si>
   <si>
     <t xml:space="preserve">27.9939765930176</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0743083953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5803680419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9659328460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.07839012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8695411682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8374156951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8133125305176</t>
+    <t xml:space="preserve">28.0743045806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5803661346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.965934753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0783920288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8695430755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8374118804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8133106231689</t>
   </si>
   <si>
     <t xml:space="preserve">28.6285610198975</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3595333099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0944595336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9579029083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3152847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1587181091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3675727844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8936443328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.802698135376</t>
+    <t xml:space="preserve">29.3595371246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.09446144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9578990936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3152866363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1587142944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3675708770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8936405181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8026962280273</t>
   </si>
   <si>
     <t xml:space="preserve">28.2799015045166</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4105987548828</t>
+    <t xml:space="preserve">28.4106025695801</t>
   </si>
   <si>
     <t xml:space="preserve">25.9600028991699</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9974231719971</t>
+    <t xml:space="preserve">26.9974250793457</t>
   </si>
   <si>
     <t xml:space="preserve">26.9810848236084</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9028224945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9273300170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3228454589844</t>
+    <t xml:space="preserve">25.9028244018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9273262023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.322847366333</t>
   </si>
   <si>
     <t xml:space="preserve">23.3623695373535</t>
@@ -3572,16 +3572,16 @@
     <t xml:space="preserve">22.8885879516602</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5175724029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3963661193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7101974487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3065128326416</t>
+    <t xml:space="preserve">23.5175743103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3963680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7101993560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3065090179443</t>
   </si>
   <si>
     <t xml:space="preserve">25.7231121063232</t>
@@ -3590,22 +3590,22 @@
     <t xml:space="preserve">25.8211364746094</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1281204223633</t>
+    <t xml:space="preserve">27.1281242370605</t>
   </si>
   <si>
     <t xml:space="preserve">26.956579208374</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1444625854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7768669128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1036148071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0709400177002</t>
+    <t xml:space="preserve">27.144458770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7768688201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1036186218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0709381103516</t>
   </si>
   <si>
     <t xml:space="preserve">26.9892539978027</t>
@@ -3614,40 +3614,40 @@
     <t xml:space="preserve">27.0300979614258</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3486728668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1328659057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9041423797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5447235107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9776630401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5937328338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5481452941895</t>
+    <t xml:space="preserve">27.3486766815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1328678131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9041442871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5447254180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9776611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5937347412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5481472015381</t>
   </si>
   <si>
     <t xml:space="preserve">26.7523651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8830604553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8667240142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5399780273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4991340637207</t>
+    <t xml:space="preserve">26.8830585479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8667221069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5399799346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4991321563721</t>
   </si>
   <si>
     <t xml:space="preserve">26.3439311981201</t>
@@ -3656,10 +3656,10 @@
     <t xml:space="preserve">25.6414241790771</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2377376556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3520984649658</t>
+    <t xml:space="preserve">26.2377395629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3520965576172</t>
   </si>
   <si>
     <t xml:space="preserve">26.1152057647705</t>
@@ -3671,34 +3671,34 @@
     <t xml:space="preserve">25.3146800994873</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3310146331787</t>
+    <t xml:space="preserve">25.331018447876</t>
   </si>
   <si>
     <t xml:space="preserve">25.2738342285156</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6740989685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8047981262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3555221557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9634265899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9913558959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3017654418945</t>
+    <t xml:space="preserve">25.6741008758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8048000335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3555240631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9634246826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9913578033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3017635345459</t>
   </si>
   <si>
     <t xml:space="preserve">25.8374729156494</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3766078948975</t>
+    <t xml:space="preserve">26.3766059875488</t>
   </si>
   <si>
     <t xml:space="preserve">26.4256153106689</t>
@@ -3710,10 +3710,10 @@
     <t xml:space="preserve">26.4419555664062</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6380004882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.507303237915</t>
+    <t xml:space="preserve">26.6380043029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5073070526123</t>
   </si>
   <si>
     <t xml:space="preserve">27.5489635467529</t>
@@ -3722,19 +3722,19 @@
     <t xml:space="preserve">26.7698345184326</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4734306335449</t>
+    <t xml:space="preserve">26.4734287261963</t>
   </si>
   <si>
     <t xml:space="preserve">27.5743732452393</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6759948730469</t>
+    <t xml:space="preserve">27.6759967803955</t>
   </si>
   <si>
     <t xml:space="preserve">27.9639339447021</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5828399658203</t>
+    <t xml:space="preserve">27.5828380584717</t>
   </si>
   <si>
     <t xml:space="preserve">27.3457145690918</t>
@@ -3743,13 +3743,13 @@
     <t xml:space="preserve">27.5235576629639</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7274894714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5320243835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9561500549316</t>
+    <t xml:space="preserve">26.7274913787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5320262908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.956148147583</t>
   </si>
   <si>
     <t xml:space="preserve">26.2108974456787</t>
@@ -3758,46 +3758,46 @@
     <t xml:space="preserve">25.5164546966553</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3992557525635</t>
+    <t xml:space="preserve">23.3992595672607</t>
   </si>
   <si>
     <t xml:space="preserve">22.8149108886719</t>
   </si>
   <si>
-    <t xml:space="preserve">23.348445892334</t>
+    <t xml:space="preserve">23.3484439849854</t>
   </si>
   <si>
     <t xml:space="preserve">23.9751358032227</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9250068664551</t>
+    <t xml:space="preserve">22.9250049591064</t>
   </si>
   <si>
     <t xml:space="preserve">23.4161949157715</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5686359405518</t>
+    <t xml:space="preserve">23.5686340332031</t>
   </si>
   <si>
     <t xml:space="preserve">23.3569145202637</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0859127044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8904495239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6194458007812</t>
+    <t xml:space="preserve">23.0859146118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8904476165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6194477081299</t>
   </si>
   <si>
     <t xml:space="preserve">23.5093536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3230400085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8318481445312</t>
+    <t xml:space="preserve">23.3230419158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8318462371826</t>
   </si>
   <si>
     <t xml:space="preserve">22.7471618652344</t>
@@ -3809,7 +3809,7 @@
     <t xml:space="preserve">21.6462211608887</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9510974884033</t>
+    <t xml:space="preserve">21.9510955810547</t>
   </si>
   <si>
     <t xml:space="preserve">22.2644424438477</t>
@@ -3818,16 +3818,16 @@
     <t xml:space="preserve">22.7810382843018</t>
   </si>
   <si>
-    <t xml:space="preserve">22.112003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4592247009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2220973968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3074703216553</t>
+    <t xml:space="preserve">22.1120014190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4592227935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.222095489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3074684143066</t>
   </si>
   <si>
     <t xml:space="preserve">21.7563133239746</t>
@@ -3845,19 +3845,19 @@
     <t xml:space="preserve">22.5185031890869</t>
   </si>
   <si>
-    <t xml:space="preserve">23.009693145752</t>
+    <t xml:space="preserve">23.0096969604492</t>
   </si>
   <si>
     <t xml:space="preserve">22.5015659332275</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6116600036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1536636352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.966667175293</t>
+    <t xml:space="preserve">22.6116638183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1536655426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9666652679443</t>
   </si>
   <si>
     <t xml:space="preserve">24.0513553619385</t>
@@ -3866,43 +3866,43 @@
     <t xml:space="preserve">23.9327926635742</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4239807128906</t>
+    <t xml:space="preserve">24.423978805542</t>
   </si>
   <si>
     <t xml:space="preserve">24.5256061553955</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9497299194336</t>
+    <t xml:space="preserve">23.9497318267822</t>
   </si>
   <si>
     <t xml:space="preserve">23.8565711975098</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4416065216064</t>
+    <t xml:space="preserve">23.4416007995605</t>
   </si>
   <si>
     <t xml:space="preserve">23.7888221740723</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1275749206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1360416412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5008850097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7380104064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0774440765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5354442596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9334754943848</t>
+    <t xml:space="preserve">24.1275730133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1360454559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.500883102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7380123138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0774459838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5354423522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9334735870361</t>
   </si>
   <si>
     <t xml:space="preserve">22.7725677490234</t>
@@ -3914,10 +3914,10 @@
     <t xml:space="preserve">22.0273151397705</t>
   </si>
   <si>
-    <t xml:space="preserve">22.255973815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3914737701416</t>
+    <t xml:space="preserve">22.2559757232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.391471862793</t>
   </si>
   <si>
     <t xml:space="preserve">21.9256896972656</t>
@@ -3926,7 +3926,7 @@
     <t xml:space="preserve">22.23903465271</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3237247467041</t>
+    <t xml:space="preserve">22.3237228393555</t>
   </si>
   <si>
     <t xml:space="preserve">22.4422855377197</t>
@@ -3935,13 +3935,13 @@
     <t xml:space="preserve">23.0689754486084</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9243221282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3907871246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9419441223145</t>
+    <t xml:space="preserve">23.9243240356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3907890319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9419460296631</t>
   </si>
   <si>
     <t xml:space="preserve">22.6455364227295</t>
@@ -3950,37 +3950,37 @@
     <t xml:space="preserve">22.730224609375</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3921546936035</t>
+    <t xml:space="preserve">21.3921566009521</t>
   </si>
   <si>
     <t xml:space="preserve">21.5022506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">21.341344833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7908706665039</t>
+    <t xml:space="preserve">21.3413429260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7908744812012</t>
   </si>
   <si>
     <t xml:space="preserve">21.0957489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6553726196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8078079223633</t>
+    <t xml:space="preserve">20.6553707122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8078098297119</t>
   </si>
   <si>
     <t xml:space="preserve">20.3335590362549</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2207298278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2552890777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0344161987305</t>
+    <t xml:space="preserve">24.2207317352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2552852630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0344181060791</t>
   </si>
   <si>
     <t xml:space="preserve">23.4246654510498</t>
@@ -3992,13 +3992,13 @@
     <t xml:space="preserve">23.4331340789795</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6533222198486</t>
+    <t xml:space="preserve">23.6533203125</t>
   </si>
   <si>
     <t xml:space="preserve">24.0174808502197</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3308258056641</t>
+    <t xml:space="preserve">24.3308238983154</t>
   </si>
   <si>
     <t xml:space="preserve">24.3477630615234</t>
@@ -4007,28 +4007,28 @@
     <t xml:space="preserve">24.2037944793701</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7966117858887</t>
+    <t xml:space="preserve">24.79660987854</t>
   </si>
   <si>
     <t xml:space="preserve">25.1438293457031</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8298015594482</t>
+    <t xml:space="preserve">25.8297996520996</t>
   </si>
   <si>
     <t xml:space="preserve">25.9737682342529</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2871170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3802738189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6265525817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.719705581665</t>
+    <t xml:space="preserve">26.2871150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3802719116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6265506744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7197074890137</t>
   </si>
   <si>
     <t xml:space="preserve">25.6858310699463</t>
@@ -4043,10 +4043,10 @@
     <t xml:space="preserve">26.9307422637939</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9053382873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1756534576416</t>
+    <t xml:space="preserve">26.9053363800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1756553649902</t>
   </si>
   <si>
     <t xml:space="preserve">28.226469039917</t>
@@ -4055,7 +4055,7 @@
     <t xml:space="preserve">28.074031829834</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4551219940186</t>
+    <t xml:space="preserve">28.4551239013672</t>
   </si>
   <si>
     <t xml:space="preserve">28.2434043884277</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">28.1163730621338</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3111534118652</t>
+    <t xml:space="preserve">28.3111572265625</t>
   </si>
   <si>
     <t xml:space="preserve">28.1671848297119</t>
@@ -4073,22 +4073,22 @@
     <t xml:space="preserve">28.4297180175781</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7091884613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1848068237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2779636383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0069580078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9476795196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2864303588867</t>
+    <t xml:space="preserve">28.7091903686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1848049163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.277961730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0069599151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.947681427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2864322662354</t>
   </si>
   <si>
     <t xml:space="preserve">27.0238990783691</t>
@@ -4103,7 +4103,7 @@
     <t xml:space="preserve">27.2610244750977</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0577793121338</t>
+    <t xml:space="preserve">27.0577774047852</t>
   </si>
   <si>
     <t xml:space="preserve">27.269495010376</t>
@@ -4112,94 +4112,94 @@
     <t xml:space="preserve">27.5574321746826</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0909671783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.125524520874</t>
+    <t xml:space="preserve">28.0909633636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1255207061768</t>
   </si>
   <si>
     <t xml:space="preserve">27.0916500091553</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7105560302734</t>
+    <t xml:space="preserve">26.7105541229248</t>
   </si>
   <si>
     <t xml:space="preserve">26.7952423095703</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4219360351562</t>
+    <t xml:space="preserve">27.421932220459</t>
   </si>
   <si>
     <t xml:space="preserve">27.2271518707275</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4304027557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3203048706055</t>
+    <t xml:space="preserve">27.4304008483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3203086853027</t>
   </si>
   <si>
     <t xml:space="preserve">27.1509323120117</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7014045715332</t>
+    <t xml:space="preserve">27.7014026641846</t>
   </si>
   <si>
     <t xml:space="preserve">28.234935760498</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9046535491943</t>
+    <t xml:space="preserve">27.9046516418457</t>
   </si>
   <si>
     <t xml:space="preserve">28.1925926208496</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4720611572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4635925292969</t>
+    <t xml:space="preserve">28.4720630645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4635944366455</t>
   </si>
   <si>
     <t xml:space="preserve">29.0818157196045</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2935333251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0479412078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7938747406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6922550201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4043140411377</t>
+    <t xml:space="preserve">29.2935371398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0479393005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7938766479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6922512054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4043121337891</t>
   </si>
   <si>
     <t xml:space="preserve">28.7176551818848</t>
   </si>
   <si>
-    <t xml:space="preserve">28.844690322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.836217880249</t>
+    <t xml:space="preserve">28.8446922302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8362159729004</t>
   </si>
   <si>
     <t xml:space="preserve">28.8531589508057</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6244964599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8108158111572</t>
+    <t xml:space="preserve">28.6244983673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.81081199646</t>
   </si>
   <si>
     <t xml:space="preserve">28.8785629272461</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0902824401855</t>
+    <t xml:space="preserve">29.0902843475342</t>
   </si>
   <si>
     <t xml:space="preserve">28.870096206665</t>
@@ -4208,25 +4208,25 @@
     <t xml:space="preserve">28.827751159668</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1417808532715</t>
+    <t xml:space="preserve">28.1417789459229</t>
   </si>
   <si>
     <t xml:space="preserve">28.7600002288818</t>
   </si>
   <si>
-    <t xml:space="preserve">28.675313949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7591857910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2301406860352</t>
+    <t xml:space="preserve">28.6753120422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7591876983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2301387786865</t>
   </si>
   <si>
     <t xml:space="preserve">28.0740280151367</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1954460144043</t>
+    <t xml:space="preserve">28.1954479217529</t>
   </si>
   <si>
     <t xml:space="preserve">28.0133190155029</t>
@@ -4256,13 +4256,13 @@
     <t xml:space="preserve">26.9812488555908</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1660022735596</t>
+    <t xml:space="preserve">26.1660003662109</t>
   </si>
   <si>
     <t xml:space="preserve">25.4027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0185642242432</t>
+    <t xml:space="preserve">26.0185623168945</t>
   </si>
   <si>
     <t xml:space="preserve">24.934455871582</t>
@@ -4277,10 +4277,10 @@
     <t xml:space="preserve">24.9951648712158</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8017387390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3594245910645</t>
+    <t xml:space="preserve">25.8017425537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3594264984131</t>
   </si>
   <si>
     <t xml:space="preserve">25.3247356414795</t>
@@ -4295,13 +4295,13 @@
     <t xml:space="preserve">24.7176342010498</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1686248779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4635028839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4808444976807</t>
+    <t xml:space="preserve">25.1686229705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4635009765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.480842590332</t>
   </si>
   <si>
     <t xml:space="preserve">25.4461555480957</t>
@@ -4310,28 +4310,28 @@
     <t xml:space="preserve">25.3073883056641</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9518013000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5068626403809</t>
+    <t xml:space="preserve">24.9518032073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5068645477295</t>
   </si>
   <si>
     <t xml:space="preserve">25.9058151245117</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1052894592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6716480255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.03590965271</t>
+    <t xml:space="preserve">26.1052913665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6716499328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0359077453613</t>
   </si>
   <si>
     <t xml:space="preserve">25.6196117401123</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2006912231445</t>
+    <t xml:space="preserve">26.2006931304932</t>
   </si>
   <si>
     <t xml:space="preserve">26.408842086792</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">26.452205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0966186523438</t>
+    <t xml:space="preserve">26.0966167449951</t>
   </si>
   <si>
     <t xml:space="preserve">25.4721736907959</t>
@@ -4370,16 +4370,16 @@
     <t xml:space="preserve">26.1920204162598</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0098876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8104133605957</t>
+    <t xml:space="preserve">26.0098896026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8104152679443</t>
   </si>
   <si>
     <t xml:space="preserve">26.5215892791748</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8424854278564</t>
+    <t xml:space="preserve">26.8424835205078</t>
   </si>
   <si>
     <t xml:space="preserve">26.4868965148926</t>
@@ -4388,16 +4388,16 @@
     <t xml:space="preserve">26.5996417999268</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7297344207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1062107086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0882816314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3353328704834</t>
+    <t xml:space="preserve">26.729736328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1062126159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0882835388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3353309631348</t>
   </si>
   <si>
     <t xml:space="preserve">26.4070434570312</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">26.3622245788574</t>
   </si>
   <si>
-    <t xml:space="preserve">26.882116317749</t>
+    <t xml:space="preserve">26.8821182250977</t>
   </si>
   <si>
     <t xml:space="preserve">26.6938819885254</t>
@@ -4436,16 +4436,16 @@
     <t xml:space="preserve">27.3930492401123</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6529979705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7157421112061</t>
+    <t xml:space="preserve">27.6529960632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7157440185547</t>
   </si>
   <si>
     <t xml:space="preserve">27.9219074249268</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8860530853271</t>
+    <t xml:space="preserve">27.8860511779785</t>
   </si>
   <si>
     <t xml:space="preserve">27.9667263031006</t>
@@ -4454,10 +4454,10 @@
     <t xml:space="preserve">27.9398345947266</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7605609893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6619606018066</t>
+    <t xml:space="preserve">27.7605590820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6619625091553</t>
   </si>
   <si>
     <t xml:space="preserve">27.4647579193115</t>
@@ -4475,7 +4475,7 @@
     <t xml:space="preserve">27.9487991333008</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0115451812744</t>
+    <t xml:space="preserve">28.0115432739258</t>
   </si>
   <si>
     <t xml:space="preserve">28.2356376647949</t>
@@ -4487,7 +4487,7 @@
     <t xml:space="preserve">28.3611278533936</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9129447937012</t>
+    <t xml:space="preserve">27.9129428863525</t>
   </si>
   <si>
     <t xml:space="preserve">27.4378681182861</t>
@@ -4496,10 +4496,10 @@
     <t xml:space="preserve">27.8233089447021</t>
   </si>
   <si>
-    <t xml:space="preserve">27.957763671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.504545211792</t>
+    <t xml:space="preserve">27.9577617645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5045471191406</t>
   </si>
   <si>
     <t xml:space="preserve">28.7465667724609</t>
@@ -4511,22 +4511,22 @@
     <t xml:space="preserve">28.7555313110352</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9796237945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0334053039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1320056915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3740272521973</t>
+    <t xml:space="preserve">28.9796257019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0334072113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.132007598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3740253448486</t>
   </si>
   <si>
     <t xml:space="preserve">29.2306060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7056846618652</t>
+    <t xml:space="preserve">29.7056827545166</t>
   </si>
   <si>
     <t xml:space="preserve">30.1000862121582</t>
@@ -4535,19 +4535,19 @@
     <t xml:space="preserve">30.9605979919434</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5482730865479</t>
+    <t xml:space="preserve">30.5482692718506</t>
   </si>
   <si>
     <t xml:space="preserve">30.1986865997314</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8132457733154</t>
+    <t xml:space="preserve">29.8132438659668</t>
   </si>
   <si>
     <t xml:space="preserve">29.8311729431152</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7734565734863</t>
+    <t xml:space="preserve">28.773458480835</t>
   </si>
   <si>
     <t xml:space="preserve">29.1588954925537</t>
@@ -4559,10 +4559,10 @@
     <t xml:space="preserve">29.1140785217285</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4457340240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.365062713623</t>
+    <t xml:space="preserve">29.4457359313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3650608062744</t>
   </si>
   <si>
     <t xml:space="preserve">29.0871887207031</t>
@@ -4577,22 +4577,22 @@
     <t xml:space="preserve">29.1768226623535</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2574977874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3112812042236</t>
+    <t xml:space="preserve">29.257495880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.311279296875</t>
   </si>
   <si>
     <t xml:space="preserve">29.5712299346924</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1628322601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9745903015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2166118621826</t>
+    <t xml:space="preserve">30.1628360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9745922088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2166137695312</t>
   </si>
   <si>
     <t xml:space="preserve">30.001485824585</t>
@@ -4601,10 +4601,10 @@
     <t xml:space="preserve">30.0283756256104</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7773933410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7236080169678</t>
+    <t xml:space="preserve">29.7773952484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7236099243164</t>
   </si>
   <si>
     <t xml:space="preserve">29.7684268951416</t>
@@ -4613,31 +4613,31 @@
     <t xml:space="preserve">30.1717948913574</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1807556152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4586353302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0104503631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.270393371582</t>
+    <t xml:space="preserve">30.180757522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4586315155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0104484558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2703952789307</t>
   </si>
   <si>
     <t xml:space="preserve">30.5930919647217</t>
   </si>
   <si>
-    <t xml:space="preserve">30.144905090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1538677215576</t>
+    <t xml:space="preserve">30.1449031829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.153865814209</t>
   </si>
   <si>
     <t xml:space="preserve">30.0463027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0373401641846</t>
+    <t xml:space="preserve">30.0373363494873</t>
   </si>
   <si>
     <t xml:space="preserve">29.696720123291</t>
@@ -4652,16 +4652,16 @@
     <t xml:space="preserve">29.3292083740234</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4278106689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0552654266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7107105255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5224742889404</t>
+    <t xml:space="preserve">29.4278087615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0552673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7107124328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5224761962891</t>
   </si>
   <si>
     <t xml:space="preserve">28.4776573181152</t>
@@ -4676,7 +4676,7 @@
     <t xml:space="preserve">27.3392658233643</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5095767974854</t>
+    <t xml:space="preserve">27.509578704834</t>
   </si>
   <si>
     <t xml:space="preserve">27.3571968078613</t>
@@ -4685,7 +4685,7 @@
     <t xml:space="preserve">27.0524311065674</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1868839263916</t>
+    <t xml:space="preserve">27.1868858337402</t>
   </si>
   <si>
     <t xml:space="preserve">27.2854843139648</t>
@@ -4694,7 +4694,7 @@
     <t xml:space="preserve">27.2944488525391</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4468326568604</t>
+    <t xml:space="preserve">27.4468307495117</t>
   </si>
   <si>
     <t xml:space="preserve">27.545431137085</t>
@@ -4703,13 +4703,13 @@
     <t xml:space="preserve">28.0294742584229</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4059467315674</t>
+    <t xml:space="preserve">28.405948638916</t>
   </si>
   <si>
     <t xml:space="preserve">28.1191101074219</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2714920043945</t>
+    <t xml:space="preserve">28.2714939117432</t>
   </si>
   <si>
     <t xml:space="preserve">28.6838207244873</t>
@@ -4721,10 +4721,10 @@
     <t xml:space="preserve">29.0423717498779</t>
   </si>
   <si>
-    <t xml:space="preserve">29.732572555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7863578796387</t>
+    <t xml:space="preserve">29.7325706481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.78635597229</t>
   </si>
   <si>
     <t xml:space="preserve">29.3919525146484</t>
@@ -4739,7 +4739,7 @@
     <t xml:space="preserve">29.1947536468506</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8989505767822</t>
+    <t xml:space="preserve">28.8989524841309</t>
   </si>
   <si>
     <t xml:space="preserve">29.2664623260498</t>
@@ -4757,16 +4757,16 @@
     <t xml:space="preserve">29.0961513519287</t>
   </si>
   <si>
-    <t xml:space="preserve">29.24853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5891551971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6070804595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7953224182129</t>
+    <t xml:space="preserve">29.2485370635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5891532897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6070823669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7953205108643</t>
   </si>
   <si>
     <t xml:space="preserve">30.2883243560791</t>
@@ -4778,13 +4778,13 @@
     <t xml:space="preserve">30.4048500061035</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4317436218262</t>
+    <t xml:space="preserve">30.4317398071289</t>
   </si>
   <si>
     <t xml:space="preserve">30.3600292205811</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2255744934082</t>
+    <t xml:space="preserve">30.2255764007568</t>
   </si>
   <si>
     <t xml:space="preserve">30.1359367370605</t>
@@ -4793,13 +4793,13 @@
     <t xml:space="preserve">30.3152141571045</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3421039581299</t>
+    <t xml:space="preserve">30.3421020507812</t>
   </si>
   <si>
     <t xml:space="preserve">30.7454719543457</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3331394195557</t>
+    <t xml:space="preserve">30.3331413269043</t>
   </si>
   <si>
     <t xml:space="preserve">30.0642318725586</t>
@@ -4808,10 +4808,10 @@
     <t xml:space="preserve">30.6110172271729</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8440742492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.086088180542</t>
+    <t xml:space="preserve">30.8440704345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0860919952393</t>
   </si>
   <si>
     <t xml:space="preserve">31.1936511993408</t>
@@ -4826,28 +4826,28 @@
     <t xml:space="preserve">31.3818893432617</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5522003173828</t>
+    <t xml:space="preserve">31.5522041320801</t>
   </si>
   <si>
     <t xml:space="preserve">31.8121547698975</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8480033874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0003890991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2384719848633</t>
+    <t xml:space="preserve">31.8480072021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0003929138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2384757995605</t>
   </si>
   <si>
     <t xml:space="preserve">31.7135486602783</t>
   </si>
   <si>
-    <t xml:space="preserve">31.731481552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5432357788086</t>
+    <t xml:space="preserve">31.7314777374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5432395935059</t>
   </si>
   <si>
     <t xml:space="preserve">31.8300762176514</t>
@@ -4862,7 +4862,7 @@
     <t xml:space="preserve">32.0900268554688</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2743263244629</t>
+    <t xml:space="preserve">31.2743301391602</t>
   </si>
   <si>
     <t xml:space="preserve">30.9068202972412</t>
@@ -4871,7 +4871,7 @@
     <t xml:space="preserve">30.9785289764404</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1090469360352</t>
+    <t xml:space="preserve">30.1090488433838</t>
   </si>
   <si>
     <t xml:space="preserve">30.3958873748779</t>
@@ -5949,6 +5949,9 @@
   </si>
   <si>
     <t xml:space="preserve">48.0400009155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2000007629395</t>
   </si>
 </sst>
 </file>
@@ -71209,7 +71212,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.69125</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>119691</v>
@@ -71230,6 +71233,32 @@
         <v>1974</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6910185185</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>302049</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>49.5999984741211</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>48.0999984741211</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>48.2400016784668</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>49.2000007629395</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>1979</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BGN.MI.xlsx
+++ b/data/BGN.MI.xlsx
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4796028137207</t>
+    <t xml:space="preserve">17.4796009063721</t>
   </si>
   <si>
     <t xml:space="preserve">BGN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2943058013916</t>
+    <t xml:space="preserve">17.2943077087402</t>
   </si>
   <si>
     <t xml:space="preserve">16.7816524505615</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5284194946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.262825012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.367826461792</t>
+    <t xml:space="preserve">16.5284175872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2628231048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3678245544434</t>
   </si>
   <si>
     <t xml:space="preserve">16.5098857879639</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9422473907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6457653045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1269378662109</t>
+    <t xml:space="preserve">16.9422416687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6457691192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1269397735596</t>
   </si>
   <si>
     <t xml:space="preserve">15.6760511398315</t>
@@ -77,133 +77,133 @@
     <t xml:space="preserve">15.9601716995239</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0707511901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0769262313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5092859268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5401678085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4289922714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6019325256348</t>
+    <t xml:space="preserve">15.0707559585571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0769281387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5092849731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5401668548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4289894104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6019353866577</t>
   </si>
   <si>
     <t xml:space="preserve">15.1942834854126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4784021377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2931070327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0213375091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.823091506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7180891036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5945587158203</t>
+    <t xml:space="preserve">15.4784030914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2931089401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0213422775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8230886459351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7180910110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5945606231689</t>
   </si>
   <si>
     <t xml:space="preserve">12.4580774307251</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6804323196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5636768341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1745557785034</t>
+    <t xml:space="preserve">12.6804294586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5636758804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1745519638062</t>
   </si>
   <si>
     <t xml:space="preserve">13.4154376983643</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0022087097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8477983474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3851566314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4098625183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1936836242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4963340759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1813278198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3233919143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3357439041138</t>
+    <t xml:space="preserve">14.0022125244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8477964401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3851556777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4098615646362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1936826705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4963331222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1813335418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.323390007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3357419967651</t>
   </si>
   <si>
     <t xml:space="preserve">14.5210399627686</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8607501983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2436962127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5710487365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4969291687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4351654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4413414001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3239898681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0157604217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2010555267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2937030792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1578254699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3431186676025</t>
+    <t xml:space="preserve">14.8607482910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2436943054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5710496902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4969348907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4351673126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4413452148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3239879608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0157642364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2010593414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2937068939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1578216552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3431205749512</t>
   </si>
   <si>
     <t xml:space="preserve">15.8489971160889</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8922328948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6081104278564</t>
+    <t xml:space="preserve">15.8922300338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6081113815308</t>
   </si>
   <si>
     <t xml:space="preserve">15.9354639053345</t>
@@ -218,64 +218,64 @@
     <t xml:space="preserve">15.867525100708</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8298673629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8854551315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.656925201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9410467147827</t>
+    <t xml:space="preserve">14.8298645019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8854598999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6569232940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9410429000854</t>
   </si>
   <si>
     <t xml:space="preserve">15.3981094360352</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5339946746826</t>
+    <t xml:space="preserve">15.5339908599854</t>
   </si>
   <si>
     <t xml:space="preserve">15.8737020492554</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9478216171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1145839691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0837059020996</t>
+    <t xml:space="preserve">15.9478235244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1145896911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.083703994751</t>
   </si>
   <si>
     <t xml:space="preserve">16.0713500976562</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1084079742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2072353363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0590000152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2998847961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1701736450195</t>
+    <t xml:space="preserve">16.1084117889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2072334289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0589981079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2998809814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1701755523682</t>
   </si>
   <si>
     <t xml:space="preserve">16.1207618713379</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7316408157349</t>
+    <t xml:space="preserve">15.7316417694092</t>
   </si>
   <si>
     <t xml:space="preserve">15.3795785903931</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1201667785645</t>
+    <t xml:space="preserve">15.1201639175415</t>
   </si>
   <si>
     <t xml:space="preserve">14.8916339874268</t>
@@ -287,13 +287,13 @@
     <t xml:space="preserve">14.6383953094482</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6075134277344</t>
+    <t xml:space="preserve">14.6075105667114</t>
   </si>
   <si>
     <t xml:space="preserve">14.2986850738525</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4530982971191</t>
+    <t xml:space="preserve">14.4531021118164</t>
   </si>
   <si>
     <t xml:space="preserve">14.6692781448364</t>
@@ -302,79 +302,79 @@
     <t xml:space="preserve">14.3419198989868</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3666276931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3913326263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3975114822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5537939071655</t>
+    <t xml:space="preserve">14.366626739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3913316726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3975086212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5537919998169</t>
   </si>
   <si>
     <t xml:space="preserve">14.8142623901367</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9640331268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5110206604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5956764221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3742742538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3286914825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1138038635254</t>
+    <t xml:space="preserve">14.9640340805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5110197067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5956745147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3742723464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3286933898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1138029098511</t>
   </si>
   <si>
     <t xml:space="preserve">15.009614944458</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0551958084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2114810943604</t>
+    <t xml:space="preserve">15.0551986694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.211480140686</t>
   </si>
   <si>
     <t xml:space="preserve">15.3547391891479</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3026437759399</t>
+    <t xml:space="preserve">15.3026466369629</t>
   </si>
   <si>
     <t xml:space="preserve">15.257061958313</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8533325195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0979690551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2058572769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9649219512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9453859329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1993446350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6616811752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8374967575073</t>
+    <t xml:space="preserve">14.8533315658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0979681015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2058582305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9649200439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.945387840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1993465423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6616802215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.837495803833</t>
   </si>
   <si>
     <t xml:space="preserve">14.1565732955933</t>
@@ -383,19 +383,19 @@
     <t xml:space="preserve">14.5733270645142</t>
   </si>
   <si>
-    <t xml:space="preserve">12.87375831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6690797805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7341995239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6560554504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6821031570435</t>
+    <t xml:space="preserve">12.8737573623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6690816879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7341985702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6560564041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6821050643921</t>
   </si>
   <si>
     <t xml:space="preserve">11.6039619445801</t>
@@ -404,82 +404,82 @@
     <t xml:space="preserve">11.2002353668213</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8160400390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.431845664978</t>
+    <t xml:space="preserve">10.8160409927368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4318447113037</t>
   </si>
   <si>
     <t xml:space="preserve">10.7444095611572</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2588396072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9230375289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3137454986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2616510391235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5286331176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5677051544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6588678359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.372350692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5221223831177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5416574478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3397951126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5025844573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2551374435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4895629882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.242115020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0337371826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8188514709473</t>
+    <t xml:space="preserve">11.2588386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.923038482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3137445449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2616500854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5286340713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.567702293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6588697433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3723516464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5221195220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5416584014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.339789390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5025882720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2551383972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4895639419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2421140670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0337400436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8188505172729</t>
   </si>
   <si>
     <t xml:space="preserve">11.6300106048584</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4281454086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3825635910034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8579225540161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9946699142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1835088729858</t>
+    <t xml:space="preserve">11.4281463623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3825626373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8579196929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9946689605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1835098266602</t>
   </si>
   <si>
     <t xml:space="preserve">12.2030458450317</t>
@@ -494,22 +494,22 @@
     <t xml:space="preserve">11.7928047180176</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5258235931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7667570114136</t>
+    <t xml:space="preserve">11.525821685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7667551040649</t>
   </si>
   <si>
     <t xml:space="preserve">11.4411678314209</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3630266189575</t>
+    <t xml:space="preserve">11.3630275726318</t>
   </si>
   <si>
     <t xml:space="preserve">11.5583810806274</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7797803878784</t>
+    <t xml:space="preserve">11.7797813415527</t>
   </si>
   <si>
     <t xml:space="preserve">11.5388450622559</t>
@@ -518,37 +518,37 @@
     <t xml:space="preserve">11.7472219467163</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6951265335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9425745010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1314144134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1379299163818</t>
+    <t xml:space="preserve">11.6951274871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.942572593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1314163208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1379261016846</t>
   </si>
   <si>
     <t xml:space="preserve">12.4114208221436</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4830503463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6653804779053</t>
+    <t xml:space="preserve">12.4830513000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6653814315796</t>
   </si>
   <si>
     <t xml:space="preserve">12.8021268844604</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3788623809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1183948516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.124903678894</t>
+    <t xml:space="preserve">12.3788633346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1183929443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1249046325684</t>
   </si>
   <si>
     <t xml:space="preserve">12.2876987457275</t>
@@ -557,10 +557,10 @@
     <t xml:space="preserve">11.8709449768066</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7016372680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8514099121094</t>
+    <t xml:space="preserve">11.7016382217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8514089584351</t>
   </si>
   <si>
     <t xml:space="preserve">11.9165267944336</t>
@@ -569,7 +569,7 @@
     <t xml:space="preserve">11.2523279190063</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1937227249146</t>
+    <t xml:space="preserve">11.1937208175659</t>
   </si>
   <si>
     <t xml:space="preserve">11.148138999939</t>
@@ -587,76 +587,76 @@
     <t xml:space="preserve">11.1090698242188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2848854064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1351156234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.076509475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1872100830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0244169235229</t>
+    <t xml:space="preserve">11.2848873138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1351146697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0765113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1872091293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0244159698486</t>
   </si>
   <si>
     <t xml:space="preserve">11.0179042816162</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6430311203003</t>
+    <t xml:space="preserve">11.6430330276489</t>
   </si>
   <si>
     <t xml:space="preserve">11.5779161453247</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9100170135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1769971847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2942094802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4309568405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9779443740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0365514755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3816747665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.564001083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4142351150513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1732978820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0560846328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9258527755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8281736373901</t>
+    <t xml:space="preserve">11.9100151062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1769981384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.29421043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4309577941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9779453277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0365505218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3816738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5640048980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4142332077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1732969284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0560865402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9258499145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8281745910645</t>
   </si>
   <si>
     <t xml:space="preserve">13.3295803070068</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7984256744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5444669723511</t>
+    <t xml:space="preserve">13.7984275817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5444660186768</t>
   </si>
   <si>
     <t xml:space="preserve">13.8830795288086</t>
@@ -665,10 +665,10 @@
     <t xml:space="preserve">13.8309869766235</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9481983184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8895902633667</t>
+    <t xml:space="preserve">13.9481973648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8895893096924</t>
   </si>
   <si>
     <t xml:space="preserve">14.1240158081055</t>
@@ -677,295 +677,295 @@
     <t xml:space="preserve">13.4923725128174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9388771057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9323635101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8672456741333</t>
+    <t xml:space="preserve">12.9388732910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9323616027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8672437667847</t>
   </si>
   <si>
     <t xml:space="preserve">12.9714326858521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9909687042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7760810852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7956142425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7304954528809</t>
+    <t xml:space="preserve">12.9909706115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7760791778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7956161499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7304983139038</t>
   </si>
   <si>
     <t xml:space="preserve">12.7435216903687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4691371917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2896213531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8887042999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5761404037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3612508773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4784603118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0747308731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1854314804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8989114761353</t>
+    <t xml:space="preserve">14.4691390991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2896223068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8887033462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5761375427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3612518310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4784622192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0747318267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1854333877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8989143371582</t>
   </si>
   <si>
     <t xml:space="preserve">14.8793792724609</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9575176239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9770565032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0031032562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7817029953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5863513946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7556571960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.859842300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3417139053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4459047317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8403129577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2700853347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5305547714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4133462905884</t>
+    <t xml:space="preserve">14.9575214385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9770555496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0031042098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7817039489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.586350440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7556562423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8598442077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3417158126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4459018707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8403100967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2700834274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.530556678772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4133453369141</t>
   </si>
   <si>
     <t xml:space="preserve">15.3482284545898</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5631151199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5138301849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6570892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5659255981445</t>
+    <t xml:space="preserve">15.5631141662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5138320922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6570930480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5659294128418</t>
   </si>
   <si>
     <t xml:space="preserve">16.1231269836426</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0514984130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6803255081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7454442977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7584657669067</t>
+    <t xml:space="preserve">16.0515003204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.680326461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7454452514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7584686279297</t>
   </si>
   <si>
     <t xml:space="preserve">15.035662651062</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3352022171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2375249862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4328775405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2208003997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2924346923828</t>
+    <t xml:space="preserve">15.3352031707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.23752784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4328804016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2208042144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2924308776855</t>
   </si>
   <si>
     <t xml:space="preserve">16.1491737365723</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9538230895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.175220489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8626575469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5566024780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1593866348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2245025634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8468208312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1658983230591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4003219604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3091583251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6021871566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6217212677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6738147735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5500898361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3677616119385</t>
+    <t xml:space="preserve">15.953821182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1752185821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8626537322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5566053390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.159384727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2245035171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8468227386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1658954620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4003200531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.309157371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6021852493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6217193603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6738119125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5500926971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3677587509155</t>
   </si>
   <si>
     <t xml:space="preserve">15.3938093185425</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1398477554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1072931289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0812454223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6152086257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.628228187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5435800552368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7975378036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9342832565308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.201265335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4422016143799</t>
+    <t xml:space="preserve">15.1398487091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1072902679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0812435150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6152067184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6282339096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5435819625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7975397109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9342851638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2012634277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4422035217285</t>
   </si>
   <si>
     <t xml:space="preserve">16.3770866394043</t>
   </si>
   <si>
-    <t xml:space="preserve">16.279411315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1426639556885</t>
+    <t xml:space="preserve">16.2794094085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1426620483398</t>
   </si>
   <si>
     <t xml:space="preserve">16.481273651123</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6049957275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2338256835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2561740875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2691974639893</t>
+    <t xml:space="preserve">16.6049976348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2338275909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2561721801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.269193649292</t>
   </si>
   <si>
     <t xml:space="preserve">17.1584987640381</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1454734802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1845455169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1389617919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6468772888184</t>
+    <t xml:space="preserve">17.145471572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1845417022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1389636993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.646879196167</t>
   </si>
   <si>
     <t xml:space="preserve">17.6273441314697</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3892192840576</t>
+    <t xml:space="preserve">18.3892211914062</t>
   </si>
   <si>
     <t xml:space="preserve">18.1678218841553</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1027030944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3501491546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1352596282959</t>
+    <t xml:space="preserve">18.1027011871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3501510620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1352634429932</t>
   </si>
   <si>
     <t xml:space="preserve">18.493408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0896797180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2264289855957</t>
+    <t xml:space="preserve">18.0896778106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2264270782471</t>
   </si>
   <si>
     <t xml:space="preserve">18.8588104248047</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">18.8723430633545</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6896419525146</t>
+    <t xml:space="preserve">18.6896438598633</t>
   </si>
   <si>
     <t xml:space="preserve">18.6422748565674</t>
@@ -986,10 +986,10 @@
     <t xml:space="preserve">17.8370380401611</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6543388366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3836688995361</t>
+    <t xml:space="preserve">17.6543369293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3836708068848</t>
   </si>
   <si>
     <t xml:space="preserve">17.9047050476074</t>
@@ -998,28 +998,28 @@
     <t xml:space="preserve">17.9317722320557</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5393009185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.546070098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9926700592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6761074066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9264755249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8046798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9806118011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.621976852417</t>
+    <t xml:space="preserve">17.5393047332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5460681915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9926719665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6761093139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.926477432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8046779632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9806098937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6219749450684</t>
   </si>
   <si>
     <t xml:space="preserve">18.0400409698486</t>
@@ -1034,13 +1034,13 @@
     <t xml:space="preserve">17.9994373321533</t>
   </si>
   <si>
-    <t xml:space="preserve">17.864107131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.803201675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0062046051025</t>
+    <t xml:space="preserve">17.8641033172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8032054901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0062065124512</t>
   </si>
   <si>
     <t xml:space="preserve">18.4054412841797</t>
@@ -1052,82 +1052,82 @@
     <t xml:space="preserve">17.6340351104736</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2430400848389</t>
+    <t xml:space="preserve">18.2430381774902</t>
   </si>
   <si>
     <t xml:space="preserve">18.2701072692871</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6490421295166</t>
+    <t xml:space="preserve">18.6490440368652</t>
   </si>
   <si>
     <t xml:space="preserve">18.452808380127</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7031764984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4595737457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.102409362793</t>
+    <t xml:space="preserve">18.7031745910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4595756530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1024112701416</t>
   </si>
   <si>
     <t xml:space="preserve">18.94677734375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9197101593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7776107788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8791122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1362438201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0415134429932</t>
+    <t xml:space="preserve">18.9197082519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7776126861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8791084289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1362476348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0415115356445</t>
   </si>
   <si>
     <t xml:space="preserve">19.1836128234863</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3730792999268</t>
+    <t xml:space="preserve">19.373083114624</t>
   </si>
   <si>
     <t xml:space="preserve">19.2918796539307</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8264465332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9414806365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.300121307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5166549682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0971183776855</t>
+    <t xml:space="preserve">19.8264503479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9414844512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3001174926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5166530609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0971164703369</t>
   </si>
   <si>
     <t xml:space="preserve">19.9956150054932</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1241836547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1444854736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6384563446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2392139434814</t>
+    <t xml:space="preserve">20.1241855621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1444873809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6384544372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2392177581787</t>
   </si>
   <si>
     <t xml:space="preserve">19.894115447998</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">19.5625457763672</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7587814331055</t>
+    <t xml:space="preserve">19.7587833404541</t>
   </si>
   <si>
     <t xml:space="preserve">19.9211826324463</t>
@@ -1145,25 +1145,25 @@
     <t xml:space="preserve">19.9008827209473</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7993831634521</t>
+    <t xml:space="preserve">19.7993850708008</t>
   </si>
   <si>
     <t xml:space="preserve">19.7655487060547</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8129138946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4813499450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5828495025635</t>
+    <t xml:space="preserve">19.812915802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4813461303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5828475952148</t>
   </si>
   <si>
     <t xml:space="preserve">19.4881134033203</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2851123809814</t>
+    <t xml:space="preserve">19.2851142883301</t>
   </si>
   <si>
     <t xml:space="preserve">18.7640762329102</t>
@@ -1172,22 +1172,22 @@
     <t xml:space="preserve">18.7573089599609</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5949077606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8452758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8655738830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.534008026123</t>
+    <t xml:space="preserve">18.5949115753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8452777862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8655757904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5340061187744</t>
   </si>
   <si>
     <t xml:space="preserve">19.0144443511963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2242126464844</t>
+    <t xml:space="preserve">19.2242107391357</t>
   </si>
   <si>
     <t xml:space="preserve">19.1700782775879</t>
@@ -1202,10 +1202,10 @@
     <t xml:space="preserve">19.4475135803223</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1633129119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2648105621338</t>
+    <t xml:space="preserve">19.1633148193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2648124694824</t>
   </si>
   <si>
     <t xml:space="preserve">19.4678153991699</t>
@@ -1214,58 +1214,58 @@
     <t xml:space="preserve">19.2580471038818</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8602828979492</t>
+    <t xml:space="preserve">19.8602848052979</t>
   </si>
   <si>
     <t xml:space="preserve">19.8670501708984</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0159168243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4204502105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5693168640137</t>
+    <t xml:space="preserve">20.0159187316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.420446395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.569314956665</t>
   </si>
   <si>
     <t xml:space="preserve">19.549015045166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4272155761719</t>
+    <t xml:space="preserve">19.4272136688232</t>
   </si>
   <si>
     <t xml:space="preserve">19.3663139343262</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4136829376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3527774810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5016479492188</t>
+    <t xml:space="preserve">19.4136810302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3527812957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5016460418701</t>
   </si>
   <si>
     <t xml:space="preserve">18.9400119781494</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8114433288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8858776092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2783489227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1565437316895</t>
+    <t xml:space="preserve">18.8114414215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8858757019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2783451080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1565456390381</t>
   </si>
   <si>
     <t xml:space="preserve">19.0685787200928</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2106781005859</t>
+    <t xml:space="preserve">19.2106761932373</t>
   </si>
   <si>
     <t xml:space="preserve">19.1091785430908</t>
@@ -1274,43 +1274,43 @@
     <t xml:space="preserve">19.3189449310303</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3324775695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2309799194336</t>
+    <t xml:space="preserve">19.3324813842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2309761047363</t>
   </si>
   <si>
     <t xml:space="preserve">19.6572799682617</t>
   </si>
   <si>
-    <t xml:space="preserve">20.110652923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9820823669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7858467102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5354843139648</t>
+    <t xml:space="preserve">20.1106510162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.982084274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7858505249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5354804992676</t>
   </si>
   <si>
     <t xml:space="preserve">19.9482479095459</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5760822296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6166820526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.555778503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3460121154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6911144256592</t>
+    <t xml:space="preserve">19.5760803222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6166801452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5557804107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3460159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6911163330078</t>
   </si>
   <si>
     <t xml:space="preserve">19.6775817871094</t>
@@ -1319,10 +1319,10 @@
     <t xml:space="preserve">19.2986469268799</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1903820037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3121776580811</t>
+    <t xml:space="preserve">19.1903800964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3121795654297</t>
   </si>
   <si>
     <t xml:space="preserve">18.7911434173584</t>
@@ -1334,13 +1334,13 @@
     <t xml:space="preserve">18.967077255249</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7708435058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4663429260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1889038085938</t>
+    <t xml:space="preserve">18.770845413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4663410186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1889057159424</t>
   </si>
   <si>
     <t xml:space="preserve">18.6084403991699</t>
@@ -1352,40 +1352,40 @@
     <t xml:space="preserve">19.1768455505371</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4745807647705</t>
+    <t xml:space="preserve">19.4745826721191</t>
   </si>
   <si>
     <t xml:space="preserve">20.0294494628906</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0835838317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5301837921143</t>
+    <t xml:space="preserve">20.0835819244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5301876068115</t>
   </si>
   <si>
     <t xml:space="preserve">20.5031204223633</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8008575439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7602519989014</t>
+    <t xml:space="preserve">20.8008556365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.76025390625</t>
   </si>
   <si>
     <t xml:space="preserve">20.7196559906006</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8685207366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7061195373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2459850311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4083862304688</t>
+    <t xml:space="preserve">20.8685188293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7061233520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2459831237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.408390045166</t>
   </si>
   <si>
     <t xml:space="preserve">20.3136539459229</t>
@@ -1394,19 +1394,19 @@
     <t xml:space="preserve">19.8805828094482</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8926429748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0550441741943</t>
+    <t xml:space="preserve">18.8926410675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.055046081543</t>
   </si>
   <si>
     <t xml:space="preserve">18.0265045166016</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2024421691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2565746307373</t>
+    <t xml:space="preserve">18.2024402618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2565727233887</t>
   </si>
   <si>
     <t xml:space="preserve">18.5813751220703</t>
@@ -1418,88 +1418,88 @@
     <t xml:space="preserve">18.4866428375244</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4189720153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5272407531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4731063842773</t>
+    <t xml:space="preserve">18.4189739227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5272388458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.473108291626</t>
   </si>
   <si>
     <t xml:space="preserve">17.9859066009521</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4460411071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.662576675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5678405761719</t>
+    <t xml:space="preserve">18.4460391998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6625747680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5678462982178</t>
   </si>
   <si>
     <t xml:space="preserve">18.7437763214111</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7302417755127</t>
+    <t xml:space="preserve">18.7302436828613</t>
   </si>
   <si>
     <t xml:space="preserve">18.3783740997314</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8505725860596</t>
+    <t xml:space="preserve">17.8505706787109</t>
   </si>
   <si>
     <t xml:space="preserve">17.7558364868164</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7287731170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9723720550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0671062469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.148307800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2159729003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.324239730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3513107299805</t>
+    <t xml:space="preserve">17.7287712097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9723701477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0671081542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1483058929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2159748077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3242416381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3513069152832</t>
   </si>
   <si>
     <t xml:space="preserve">18.364839553833</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7167091369629</t>
+    <t xml:space="preserve">18.7167072296143</t>
   </si>
   <si>
     <t xml:space="preserve">18.7979106903076</t>
   </si>
   <si>
-    <t xml:space="preserve">18.906177520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1618404388428</t>
+    <t xml:space="preserve">18.9061794281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1618385314941</t>
   </si>
   <si>
     <t xml:space="preserve">18.1212406158447</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8235054016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6205024719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6611042022705</t>
+    <t xml:space="preserve">17.8235015869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6205062866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6611022949219</t>
   </si>
   <si>
     <t xml:space="preserve">17.173900604248</t>
@@ -1508,16 +1508,16 @@
     <t xml:space="preserve">17.0521011352539</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7814311981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7600555419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.802806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.560525894165</t>
+    <t xml:space="preserve">16.7814292907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7600536346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8028087615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5605297088623</t>
   </si>
   <si>
     <t xml:space="preserve">16.7030467987061</t>
@@ -1526,52 +1526,52 @@
     <t xml:space="preserve">16.3039970397949</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2066135406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2802495956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8503189086914</t>
+    <t xml:space="preserve">15.2066125869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2802515029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8503198623657</t>
   </si>
   <si>
     <t xml:space="preserve">14.8218154907227</t>
   </si>
   <si>
-    <t xml:space="preserve">15.53440284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3206253051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8930768966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4631452560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8336925506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3491315841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9477033615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8479413986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8621959686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9191999435425</t>
+    <t xml:space="preserve">15.5344009399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3206281661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8930749893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4631443023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8336906433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3491325378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9477043151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8479433059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8621940612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9192028045654</t>
   </si>
   <si>
     <t xml:space="preserve">15.7054252624512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7339305877686</t>
+    <t xml:space="preserve">15.7339277267456</t>
   </si>
   <si>
     <t xml:space="preserve">15.7196760177612</t>
@@ -1580,13 +1580,13 @@
     <t xml:space="preserve">15.3633823394775</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5059013366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4203910827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4488935470581</t>
+    <t xml:space="preserve">15.505898475647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.420389175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4488916397095</t>
   </si>
   <si>
     <t xml:space="preserve">14.9500818252563</t>
@@ -1601,43 +1601,43 @@
     <t xml:space="preserve">15.5629062652588</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6484174728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8906993865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0189647674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4346408843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3776340484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4916496276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.52015209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7909374237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7766828536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6056632995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4750194549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2469902038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1329746246338</t>
+    <t xml:space="preserve">15.6484184265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.890697479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0189628601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.434642791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3776350021362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4916486740112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5201539993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7909345626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7766819000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6056604385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4750213623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2469921112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1329765319824</t>
   </si>
   <si>
     <t xml:space="preserve">16.4465160369873</t>
@@ -1646,25 +1646,25 @@
     <t xml:space="preserve">16.5035228729248</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9619579315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0474662780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2184886932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2042331695557</t>
+    <t xml:space="preserve">15.9619550704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0474643707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2184867858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2042350769043</t>
   </si>
   <si>
     <t xml:space="preserve">16.1614818572998</t>
   </si>
   <si>
-    <t xml:space="preserve">15.74817943573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9049472808838</t>
+    <t xml:space="preserve">15.7481803894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9049501419067</t>
   </si>
   <si>
     <t xml:space="preserve">16.2754936218262</t>
@@ -1676,28 +1676,28 @@
     <t xml:space="preserve">16.3325004577637</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2636203765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0783491134644</t>
+    <t xml:space="preserve">15.2636213302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.078351020813</t>
   </si>
   <si>
     <t xml:space="preserve">15.30637550354</t>
   </si>
   <si>
-    <t xml:space="preserve">15.29212474823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5486555099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6769208908081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6175384521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7885551452637</t>
+    <t xml:space="preserve">15.2921237945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5486536026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6769237518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6175365447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7885570526123</t>
   </si>
   <si>
     <t xml:space="preserve">16.8598155975342</t>
@@ -1709,49 +1709,49 @@
     <t xml:space="preserve">17.3871307373047</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1020946502686</t>
+    <t xml:space="preserve">17.1020984649658</t>
   </si>
   <si>
     <t xml:space="preserve">15.876446723938</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6911735534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6626720428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.964334487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7933111190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3515071868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2161169052124</t>
+    <t xml:space="preserve">15.6911745071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6626710891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9643335342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7933101654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.351508140564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.216118812561</t>
   </si>
   <si>
     <t xml:space="preserve">14.3372573852539</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7220525741577</t>
+    <t xml:space="preserve">14.722056388855</t>
   </si>
   <si>
     <t xml:space="preserve">14.4227666854858</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0593481063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5391616821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2042436599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7268114089966</t>
+    <t xml:space="preserve">14.0593461990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5391607284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2042427062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7268104553223</t>
   </si>
   <si>
     <t xml:space="preserve">12.3776435852051</t>
@@ -1760,7 +1760,7 @@
     <t xml:space="preserve">12.4203977584839</t>
   </si>
   <si>
-    <t xml:space="preserve">12.285005569458</t>
+    <t xml:space="preserve">12.2850065231323</t>
   </si>
   <si>
     <t xml:space="preserve">12.4061450958252</t>
@@ -1769,43 +1769,43 @@
     <t xml:space="preserve">12.1353626251221</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3705167770386</t>
+    <t xml:space="preserve">12.3705177307129</t>
   </si>
   <si>
     <t xml:space="preserve">12.904956817627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8622016906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9334592819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1472358703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2755012512207</t>
+    <t xml:space="preserve">12.8622007369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9334583282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1472368240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.275502204895</t>
   </si>
   <si>
     <t xml:space="preserve">13.1187324523926</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0688514709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5462856292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1116075515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7838182449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7339353561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6698036193848</t>
+    <t xml:space="preserve">13.0688505172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5462846755981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1116065979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7838172912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7339344024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6698026657104</t>
   </si>
   <si>
     <t xml:space="preserve">12.9192085266113</t>
@@ -1817,22 +1817,22 @@
     <t xml:space="preserve">13.246997833252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5961656570435</t>
+    <t xml:space="preserve">13.5961666107178</t>
   </si>
   <si>
     <t xml:space="preserve">14.1092281341553</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9453344345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8812007904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8883266448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4655227661133</t>
+    <t xml:space="preserve">13.9453353881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8812017440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8883256912231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.465521812439</t>
   </si>
   <si>
     <t xml:space="preserve">14.2232427597046</t>
@@ -1841,49 +1841,49 @@
     <t xml:space="preserve">14.0878524780273</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3681392669678</t>
+    <t xml:space="preserve">13.3681383132935</t>
   </si>
   <si>
     <t xml:space="preserve">13.4679002761841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1258573532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.969090461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.489278793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.631796836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2327451705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3966407775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8265714645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5344104766846</t>
+    <t xml:space="preserve">13.1258592605591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9690895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4892778396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6317958831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2327461242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3966426849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8265724182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5344133377075</t>
   </si>
   <si>
     <t xml:space="preserve">13.1044816970825</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9975929260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6104192733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7529363632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6389198303223</t>
+    <t xml:space="preserve">12.9975938796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6104183197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7529354095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6389226913452</t>
   </si>
   <si>
     <t xml:space="preserve">14.1448583602905</t>
@@ -1895,31 +1895,31 @@
     <t xml:space="preserve">14.2018661499023</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1947402954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.895453453064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.39426612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5937871932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7078037261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.508279800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6935520172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8075637817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6365451812744</t>
+    <t xml:space="preserve">14.1947393417358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8954544067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3942651748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.593789100647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7078008651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5082807540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6935482025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8075675964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6365432739258</t>
   </si>
   <si>
     <t xml:space="preserve">14.7648096084595</t>
@@ -1928,52 +1928,52 @@
     <t xml:space="preserve">14.7363052368164</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6792993545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.265998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5367822647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2945003509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5510330200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1923627853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9785871505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2778739929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2493686676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2208681106567</t>
+    <t xml:space="preserve">14.6792984008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2660007476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5367841720581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2945022583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5510339736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1923608779907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9785861968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2778730392456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2493696212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2208671569824</t>
   </si>
   <si>
     <t xml:space="preserve">15.4061393737793</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8194379806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8051853179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6341686248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5914125442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4322643280029</t>
+    <t xml:space="preserve">15.8194398880005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8051872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6341676712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5914096832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4322662353516</t>
   </si>
   <si>
     <t xml:space="preserve">16.6032848358154</t>
@@ -1982,13 +1982,13 @@
     <t xml:space="preserve">16.7172985076904</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7743034362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8170642852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0308361053467</t>
+    <t xml:space="preserve">16.7743072509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8170585632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0308380126953</t>
   </si>
   <si>
     <t xml:space="preserve">17.1591033935547</t>
@@ -2003,46 +2003,46 @@
     <t xml:space="preserve">17.4583892822266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4726428985596</t>
+    <t xml:space="preserve">17.4726409912109</t>
   </si>
   <si>
     <t xml:space="preserve">17.9714508056641</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7861804962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9286956787109</t>
+    <t xml:space="preserve">17.7861766815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9286994934082</t>
   </si>
   <si>
     <t xml:space="preserve">18.0569629669189</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0854663848877</t>
+    <t xml:space="preserve">18.0854644775391</t>
   </si>
   <si>
     <t xml:space="preserve">17.5581512451172</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5866565704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2018585205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4298858642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5296497344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4868927001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7196521759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8548030853271</t>
+    <t xml:space="preserve">17.5866546630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2018604278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4298839569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5296478271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4868907928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7196502685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8548011779785</t>
   </si>
   <si>
     <t xml:space="preserve">17.2991847991943</t>
@@ -2051,13 +2051,13 @@
     <t xml:space="preserve">17.2241020202637</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2691516876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1490154266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7435703277588</t>
+    <t xml:space="preserve">17.2691535949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1490173339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7435684204102</t>
   </si>
   <si>
     <t xml:space="preserve">16.878719329834</t>
@@ -2066,52 +2066,52 @@
     <t xml:space="preserve">16.9237689971924</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6985187530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2541351318359</t>
+    <t xml:space="preserve">16.6985206604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2541332244873</t>
   </si>
   <si>
     <t xml:space="preserve">17.5394515991211</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1640338897705</t>
+    <t xml:space="preserve">17.1640357971191</t>
   </si>
   <si>
     <t xml:space="preserve">17.0589179992676</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4343357086182</t>
+    <t xml:space="preserve">17.4343338012695</t>
   </si>
   <si>
     <t xml:space="preserve">17.8247661590576</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9298820495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8397827148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7496852874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9449005126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6657028198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8459014892578</t>
+    <t xml:space="preserve">17.9298839569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8397846221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.749683380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9449024200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6657009124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8458995819092</t>
   </si>
   <si>
     <t xml:space="preserve">19.1762676239014</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3714809417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0561351776123</t>
+    <t xml:space="preserve">19.3714828491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.056131362915</t>
   </si>
   <si>
     <t xml:space="preserve">19.131217956543</t>
@@ -2120,40 +2120,40 @@
     <t xml:space="preserve">19.4165344238281</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1462306976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0110855102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2213153839111</t>
+    <t xml:space="preserve">19.1462345123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0110836029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2213134765625</t>
   </si>
   <si>
     <t xml:space="preserve">19.7318859100342</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7769336700439</t>
+    <t xml:space="preserve">19.7769317626953</t>
   </si>
   <si>
     <t xml:space="preserve">19.7919502258301</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8069667816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0772666931152</t>
+    <t xml:space="preserve">19.8069648742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0772647857666</t>
   </si>
   <si>
     <t xml:space="preserve">19.9721488952637</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2574653625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1373329162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1823806762695</t>
+    <t xml:space="preserve">20.2574672698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1373310089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1823787689209</t>
   </si>
   <si>
     <t xml:space="preserve">19.897066116333</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">19.8219814300537</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6868305206299</t>
+    <t xml:space="preserve">19.6868343353271</t>
   </si>
   <si>
     <t xml:space="preserve">19.8369998931885</t>
@@ -2183,7 +2183,7 @@
     <t xml:space="preserve">19.9421157836914</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3325481414795</t>
+    <t xml:space="preserve">20.3325519561768</t>
   </si>
   <si>
     <t xml:space="preserve">19.5817165374756</t>
@@ -2192,16 +2192,16 @@
     <t xml:space="preserve">19.4916152954102</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6718158721924</t>
+    <t xml:space="preserve">19.671817779541</t>
   </si>
   <si>
     <t xml:space="preserve">19.7168655395508</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7619171142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2875003814697</t>
+    <t xml:space="preserve">19.7619152069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2874965667725</t>
   </si>
   <si>
     <t xml:space="preserve">19.9120807647705</t>
@@ -2210,19 +2210,19 @@
     <t xml:space="preserve">20.122314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0622501373291</t>
+    <t xml:space="preserve">20.0622482299805</t>
   </si>
   <si>
     <t xml:space="preserve">20.3025169372559</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5728168487549</t>
+    <t xml:space="preserve">20.5728149414062</t>
   </si>
   <si>
     <t xml:space="preserve">20.662914276123</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9932804107666</t>
+    <t xml:space="preserve">20.993278503418</t>
   </si>
   <si>
     <t xml:space="preserve">21.1434478759766</t>
@@ -2231,25 +2231,25 @@
     <t xml:space="preserve">21.1584644317627</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3536815643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0082950592041</t>
+    <t xml:space="preserve">21.3536834716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0082988739014</t>
   </si>
   <si>
     <t xml:space="preserve">21.2635822296143</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2936191558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4287662506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6089668273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5338821411133</t>
+    <t xml:space="preserve">21.2936172485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4287624359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6089649200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5338764190674</t>
   </si>
   <si>
     <t xml:space="preserve">20.9782657623291</t>
@@ -2258,25 +2258,25 @@
     <t xml:space="preserve">20.8881664276123</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2335472106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2485618591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1734828948975</t>
+    <t xml:space="preserve">21.233549118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2485599517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1734848022461</t>
   </si>
   <si>
     <t xml:space="preserve">20.6478977203369</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6328811645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7680339813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0833797454834</t>
+    <t xml:space="preserve">20.6328830718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.768030166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.083381652832</t>
   </si>
   <si>
     <t xml:space="preserve">20.7980651855469</t>
@@ -2288,19 +2288,19 @@
     <t xml:space="preserve">20.7229804992676</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2035140991211</t>
+    <t xml:space="preserve">21.2035160064697</t>
   </si>
   <si>
     <t xml:space="preserve">21.308629989624</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4888324737549</t>
+    <t xml:space="preserve">21.4888343811035</t>
   </si>
   <si>
     <t xml:space="preserve">21.5639133453369</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1134166717529</t>
+    <t xml:space="preserve">21.1134185791016</t>
   </si>
   <si>
     <t xml:space="preserve">21.383716583252</t>
@@ -2309,82 +2309,82 @@
     <t xml:space="preserve">21.3236465454102</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5789337158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8191967010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8492298126221</t>
+    <t xml:space="preserve">21.5789318084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8191947937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8492317199707</t>
   </si>
   <si>
     <t xml:space="preserve">21.9543476104736</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5850448608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4799327850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6601295471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1256465911865</t>
+    <t xml:space="preserve">22.5850467681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4799308776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6601276397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1256446838379</t>
   </si>
   <si>
     <t xml:space="preserve">23.3208618164062</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0805988311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2007312774658</t>
+    <t xml:space="preserve">23.0805950164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2007293701172</t>
   </si>
   <si>
     <t xml:space="preserve">23.3058471679688</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4259777069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6962776184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9215316772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7263126373291</t>
+    <t xml:space="preserve">23.4259815216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6962795257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9215297698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7263107299805</t>
   </si>
   <si>
     <t xml:space="preserve">23.6662464141846</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9065113067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2908306121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3959445953369</t>
+    <t xml:space="preserve">23.9065093994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2908267974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3959465026855</t>
   </si>
   <si>
     <t xml:space="preserve">23.2758140563965</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0956115722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.494945526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6300945281982</t>
+    <t xml:space="preserve">23.0956153869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4949436187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6300964355469</t>
   </si>
   <si>
     <t xml:space="preserve">22.5249805450439</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0355472564697</t>
+    <t xml:space="preserve">23.0355453491211</t>
   </si>
   <si>
     <t xml:space="preserve">22.9454441070557</t>
@@ -2393,46 +2393,46 @@
     <t xml:space="preserve">22.5399971008301</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6000652313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.645112991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7352142333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2096290588379</t>
+    <t xml:space="preserve">22.6000633239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6451168060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7352161407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2096309661865</t>
   </si>
   <si>
     <t xml:space="preserve">22.1946125030518</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1045169830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1795997619629</t>
+    <t xml:space="preserve">22.104513168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1795978546143</t>
   </si>
   <si>
     <t xml:space="preserve">21.7290992736816</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0594654083252</t>
+    <t xml:space="preserve">22.0594635009766</t>
   </si>
   <si>
     <t xml:space="preserve">21.7441139221191</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5939483642578</t>
+    <t xml:space="preserve">21.5939464569092</t>
   </si>
   <si>
     <t xml:space="preserve">21.2785987854004</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0294303894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7652473449707</t>
+    <t xml:space="preserve">22.0294342041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7652454376221</t>
   </si>
   <si>
     <t xml:space="preserve">22.7051811218262</t>
@@ -2441,10 +2441,10 @@
     <t xml:space="preserve">22.99049949646</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9754791259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8102951049805</t>
+    <t xml:space="preserve">22.9754810333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8102970123291</t>
   </si>
   <si>
     <t xml:space="preserve">22.8253154754639</t>
@@ -2453,28 +2453,28 @@
     <t xml:space="preserve">22.0744819641113</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8853778839111</t>
+    <t xml:space="preserve">22.8853797912598</t>
   </si>
   <si>
     <t xml:space="preserve">22.1645793914795</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2997341156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8553485870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7952785491943</t>
+    <t xml:space="preserve">22.299732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8553466796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7952823638916</t>
   </si>
   <si>
     <t xml:space="preserve">23.3508949279785</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1017284393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4471130371094</t>
+    <t xml:space="preserve">24.1017265319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.447114944458</t>
   </si>
   <si>
     <t xml:space="preserve">24.4170780181885</t>
@@ -2483,64 +2483,64 @@
     <t xml:space="preserve">24.67236328125</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6573429107666</t>
+    <t xml:space="preserve">24.6573448181152</t>
   </si>
   <si>
     <t xml:space="preserve">24.7774791717529</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3269786834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8764801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2396621704102</t>
+    <t xml:space="preserve">24.3269824981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8764781951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2396659851074</t>
   </si>
   <si>
     <t xml:space="preserve">20.9181995391846</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4226493835449</t>
+    <t xml:space="preserve">20.4226512908936</t>
   </si>
   <si>
     <t xml:space="preserve">20.4827156066895</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0411186218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5906181335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9688205718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8876190185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7975215911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6201038360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6937961578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2146549224854</t>
+    <t xml:space="preserve">19.0411167144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5906143188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9688186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.887622833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7975206375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6201047897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6937971115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2146558761597</t>
   </si>
   <si>
     <t xml:space="preserve">12.9894046783447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6590394973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0344552993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7266130447388</t>
+    <t xml:space="preserve">12.6590385437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0344572067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7266139984131</t>
   </si>
   <si>
     <t xml:space="preserve">12.8917970657349</t>
@@ -2549,25 +2549,25 @@
     <t xml:space="preserve">13.905421257019</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0180473327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.581169128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0781116485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.355920791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1982450485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3183794021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0555868148804</t>
+    <t xml:space="preserve">14.018045425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5811700820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0781135559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3559226989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1982469558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3183784484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0555849075317</t>
   </si>
   <si>
     <t xml:space="preserve">14.7688798904419</t>
@@ -2579,130 +2579,130 @@
     <t xml:space="preserve">16.7886219024658</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7074222564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9026355743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9326686859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7674865722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1518030166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3770513534546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4821729660034</t>
+    <t xml:space="preserve">15.7074213027954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9026374816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9326696395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7674856185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1518020629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3770532608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4821672439575</t>
   </si>
   <si>
     <t xml:space="preserve">16.6835021972656</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8937377929688</t>
+    <t xml:space="preserve">16.8937339782715</t>
   </si>
   <si>
     <t xml:space="preserve">17.3442344665527</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0138683319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5333347320557</t>
+    <t xml:space="preserve">17.0138664245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5333366394043</t>
   </si>
   <si>
     <t xml:space="preserve">16.503303527832</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9087524414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4643688201904</t>
+    <t xml:space="preserve">16.908748626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4643669128418</t>
   </si>
   <si>
     <t xml:space="preserve">17.1039695739746</t>
   </si>
   <si>
-    <t xml:space="preserve">17.524435043335</t>
+    <t xml:space="preserve">17.5244331359863</t>
   </si>
   <si>
     <t xml:space="preserve">17.1189842224121</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2391166687012</t>
+    <t xml:space="preserve">17.2391185760498</t>
   </si>
   <si>
     <t xml:space="preserve">17.1340007781982</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3892841339111</t>
+    <t xml:space="preserve">17.3892860412598</t>
   </si>
   <si>
     <t xml:space="preserve">17.4043025970459</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6896152496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3653659820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2902851104736</t>
+    <t xml:space="preserve">17.6896171569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.365364074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2902870178223</t>
   </si>
   <si>
     <t xml:space="preserve">18.4855003356934</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9510173797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2813873291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8520183563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3414516448975</t>
+    <t xml:space="preserve">18.9510154724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2813816070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8520164489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3414478302002</t>
   </si>
   <si>
     <t xml:space="preserve">19.5516834259033</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3954029083252</t>
+    <t xml:space="preserve">18.3954010009766</t>
   </si>
   <si>
     <t xml:space="preserve">19.4315490722656</t>
   </si>
   <si>
-    <t xml:space="preserve">20.167366027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3264331817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9571342468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1073017120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6779327392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2663688659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5066356658936</t>
+    <t xml:space="preserve">20.1673679351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3264312744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9571323394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1072998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6779308319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2663669586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5066318511963</t>
   </si>
   <si>
     <t xml:space="preserve">19.8820514678955</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0922832489014</t>
+    <t xml:space="preserve">20.0922813415527</t>
   </si>
   <si>
     <t xml:space="preserve">20.3475646972656</t>
@@ -2711,19 +2711,19 @@
     <t xml:space="preserve">20.3775978088379</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5967311859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7107467651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9209842681885</t>
+    <t xml:space="preserve">19.5967330932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7107486724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9209861755371</t>
   </si>
   <si>
     <t xml:space="preserve">18.7708168029785</t>
   </si>
   <si>
-    <t xml:space="preserve">18.830883026123</t>
+    <t xml:space="preserve">18.8308868408203</t>
   </si>
   <si>
     <t xml:space="preserve">19.5666980743408</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">18.9059658050537</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0711498260498</t>
+    <t xml:space="preserve">19.0711517333984</t>
   </si>
   <si>
     <t xml:space="preserve">18.7558002471924</t>
@@ -2747,22 +2747,22 @@
     <t xml:space="preserve">19.2964000701904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5366649627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5216503143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3114166259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.981050491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4526824951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6178665161133</t>
+    <t xml:space="preserve">19.5366668701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5216484069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3114147186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9810523986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4526805877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6178646087646</t>
   </si>
   <si>
     <t xml:space="preserve">19.6117496490479</t>
@@ -2771,46 +2771,46 @@
     <t xml:space="preserve">20.3625831604004</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6417827606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0322189331055</t>
+    <t xml:space="preserve">19.6417846679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0322170257568</t>
   </si>
   <si>
     <t xml:space="preserve">20.5127487182617</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2424449920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.738000869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0021820068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2151985168457</t>
+    <t xml:space="preserve">20.2424468994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7379989624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0021800994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.215202331543</t>
   </si>
   <si>
     <t xml:space="preserve">18.140115737915</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3203201293945</t>
+    <t xml:space="preserve">18.3203163146973</t>
   </si>
   <si>
     <t xml:space="preserve">20.5577983856201</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4376640319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1284294128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7830467224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4977321624756</t>
+    <t xml:space="preserve">20.4376659393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1284332275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7830505371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4977340698242</t>
   </si>
   <si>
     <t xml:space="preserve">21.0233135223389</t>
@@ -2819,13 +2819,13 @@
     <t xml:space="preserve">21.4137477874756</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3686981201172</t>
+    <t xml:space="preserve">21.3686962127686</t>
   </si>
   <si>
     <t xml:space="preserve">20.9031829833984</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0383319854736</t>
+    <t xml:space="preserve">21.038330078125</t>
   </si>
   <si>
     <t xml:space="preserve">20.4076328277588</t>
@@ -2834,49 +2834,49 @@
     <t xml:space="preserve">20.5427837371826</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3175315856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2124137878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4465637207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.746898651123</t>
+    <t xml:space="preserve">20.3175354003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2124176025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4465675354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7469005584717</t>
   </si>
   <si>
     <t xml:space="preserve">19.2363319396973</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5277671813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7140827178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6840476989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6389999389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3386650085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6239795684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8642463684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3987293243408</t>
+    <t xml:space="preserve">20.5277652740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7140789031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.684045791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6389980316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3386631011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6239776611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8642482757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3987331390381</t>
   </si>
   <si>
     <t xml:space="preserve">21.4437808990479</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1884956359863</t>
+    <t xml:space="preserve">21.188497543335</t>
   </si>
   <si>
     <t xml:space="preserve">21.9092960357666</t>
@@ -2888,13 +2888,13 @@
     <t xml:space="preserve">21.8342151641846</t>
   </si>
   <si>
-    <t xml:space="preserve">21.503849029541</t>
+    <t xml:space="preserve">21.5038471221924</t>
   </si>
   <si>
     <t xml:space="preserve">22.2546806335449</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0444469451904</t>
+    <t xml:space="preserve">22.0444488525391</t>
   </si>
   <si>
     <t xml:space="preserve">22.2847118377686</t>
@@ -2903,22 +2903,22 @@
     <t xml:space="preserve">22.3447799682617</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4649124145508</t>
+    <t xml:space="preserve">22.4649143218994</t>
   </si>
   <si>
     <t xml:space="preserve">22.6901626586914</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8703632354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6150817871094</t>
+    <t xml:space="preserve">22.870361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.615083694458</t>
   </si>
   <si>
     <t xml:space="preserve">22.5700283050537</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6751461029053</t>
+    <t xml:space="preserve">22.6751480102539</t>
   </si>
   <si>
     <t xml:space="preserve">22.5775375366211</t>
@@ -2927,25 +2927,25 @@
     <t xml:space="preserve">22.9079055786133</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0430545806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0881061553955</t>
+    <t xml:space="preserve">23.0430564880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0881042480469</t>
   </si>
   <si>
     <t xml:space="preserve">22.8178024291992</t>
   </si>
   <si>
-    <t xml:space="preserve">22.84033203125</t>
+    <t xml:space="preserve">22.8403301239014</t>
   </si>
   <si>
     <t xml:space="preserve">23.1706962585449</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2157459259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.380931854248</t>
+    <t xml:space="preserve">23.215747833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3809299468994</t>
   </si>
   <si>
     <t xml:space="preserve">23.523588180542</t>
@@ -2954,7 +2954,7 @@
     <t xml:space="preserve">23.0505638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9154148101807</t>
+    <t xml:space="preserve">22.915412902832</t>
   </si>
   <si>
     <t xml:space="preserve">23.0730876922607</t>
@@ -2963,10 +2963,10 @@
     <t xml:space="preserve">23.253288269043</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3433876037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.29833984375</t>
+    <t xml:space="preserve">23.3433856964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2983379364014</t>
   </si>
   <si>
     <t xml:space="preserve">23.8914966583252</t>
@@ -2975,25 +2975,25 @@
     <t xml:space="preserve">24.2594051361084</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0942211151123</t>
+    <t xml:space="preserve">24.0942230224609</t>
   </si>
   <si>
     <t xml:space="preserve">24.664852142334</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5522289276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4621276855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7924957275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4020614624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0491714477539</t>
+    <t xml:space="preserve">24.5522308349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4621295928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7924938201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.402063369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0491676330566</t>
   </si>
   <si>
     <t xml:space="preserve">24.4696369171143</t>
@@ -3002,43 +3002,43 @@
     <t xml:space="preserve">24.4245853424072</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1993370056152</t>
+    <t xml:space="preserve">24.1993350982666</t>
   </si>
   <si>
     <t xml:space="preserve">23.9590702056885</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1617946624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2293701171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6273136138916</t>
+    <t xml:space="preserve">24.1617965698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2293682098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.627311706543</t>
   </si>
   <si>
     <t xml:space="preserve">24.8075103759766</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8150196075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1078395843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2204685211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1003379821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1829261779785</t>
+    <t xml:space="preserve">24.8150215148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1078433990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2204704284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1003360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1829299926758</t>
   </si>
   <si>
     <t xml:space="preserve">25.2955551147461</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5208053588867</t>
+    <t xml:space="preserve">25.5208072662354</t>
   </si>
   <si>
     <t xml:space="preserve">25.828649520874</t>
@@ -3053,49 +3053,49 @@
     <t xml:space="preserve">25.7835941314697</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0538959503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8661861419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4893760681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5118999481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3767490386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4668521881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6545600891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5869846343994</t>
+    <t xml:space="preserve">26.0538921356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.866189956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.489372253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5119018554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3767528533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4668560028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.65456199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5869884490967</t>
   </si>
   <si>
     <t xml:space="preserve">27.1050586700439</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5180206298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1350955963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3903770446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0149631500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0374813079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2176818847656</t>
+    <t xml:space="preserve">27.5180168151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1350879669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3903789520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0149593353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0374851226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2176856994629</t>
   </si>
   <si>
     <t xml:space="preserve">27.1951599121094</t>
@@ -3107,13 +3107,13 @@
     <t xml:space="preserve">26.2566184997559</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6845951080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1726360321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0299739837646</t>
+    <t xml:space="preserve">26.6845932006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1726341247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0299777984619</t>
   </si>
   <si>
     <t xml:space="preserve">26.7446575164795</t>
@@ -3122,22 +3122,22 @@
     <t xml:space="preserve">26.6245288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8962230682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0163536071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3992805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3542289733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5569515228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0013332366943</t>
+    <t xml:space="preserve">25.8962211608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.016357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3992748260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.35422706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5569477081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0013313293457</t>
   </si>
   <si>
     <t xml:space="preserve">26.0238609313965</t>
@@ -3146,31 +3146,31 @@
     <t xml:space="preserve">26.421802520752</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2866516113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2115726470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.887321472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1125679016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3603420257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3828678131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6456565856934</t>
+    <t xml:space="preserve">26.2866497039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2115707397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8873157501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1125659942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3603401184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.382869720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.645658493042</t>
   </si>
   <si>
     <t xml:space="preserve">27.6231327056885</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7808094024658</t>
+    <t xml:space="preserve">27.7808132171631</t>
   </si>
   <si>
     <t xml:space="preserve">27.5930995941162</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">27.4204082489014</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5630626678467</t>
+    <t xml:space="preserve">27.5630645751953</t>
   </si>
   <si>
     <t xml:space="preserve">27.7883129119873</t>
@@ -3188,154 +3188,154 @@
     <t xml:space="preserve">27.7132339477539</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9535026550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9835338592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2613410949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1412086486816</t>
+    <t xml:space="preserve">27.953498840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9835376739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2613391876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1412124633789</t>
   </si>
   <si>
     <t xml:space="preserve">28.2087821960449</t>
   </si>
   <si>
-    <t xml:space="preserve">28.18625831604</t>
+    <t xml:space="preserve">28.1862621307373</t>
   </si>
   <si>
     <t xml:space="preserve">28.3814735412598</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2012748718262</t>
+    <t xml:space="preserve">28.2012767791748</t>
   </si>
   <si>
     <t xml:space="preserve">28.0586166381836</t>
   </si>
   <si>
-    <t xml:space="preserve">28.118688583374</t>
+    <t xml:space="preserve">28.1186828613281</t>
   </si>
   <si>
     <t xml:space="preserve">28.4115085601807</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1698455810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3875923156738</t>
+    <t xml:space="preserve">29.169849395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3875942230225</t>
   </si>
   <si>
     <t xml:space="preserve">29.5077247619629</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2899780273438</t>
+    <t xml:space="preserve">29.2899799346924</t>
   </si>
   <si>
     <t xml:space="preserve">28.9145622253418</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4190139770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6442680358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1923751831055</t>
+    <t xml:space="preserve">28.4190101623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.64426612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1923770904541</t>
   </si>
   <si>
     <t xml:space="preserve">29.1323051452637</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2148990631104</t>
+    <t xml:space="preserve">29.2148971557617</t>
   </si>
   <si>
     <t xml:space="preserve">28.5842018127441</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4865913391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4565601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5466613769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4640674591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8784141540527</t>
+    <t xml:space="preserve">28.4865875244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4565582275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5466575622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4640655517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.87841796875</t>
   </si>
   <si>
     <t xml:space="preserve">28.4715728759766</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4040050506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0736331939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3964900970459</t>
+    <t xml:space="preserve">28.4040031433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0736312866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3964939117432</t>
   </si>
   <si>
     <t xml:space="preserve">28.0285873413086</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7644004821777</t>
+    <t xml:space="preserve">28.7643985748291</t>
   </si>
   <si>
     <t xml:space="preserve">29.6954345703125</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7179565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.943208694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4012145996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7240715026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5213470458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6940422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5288562774658</t>
+    <t xml:space="preserve">29.7179584503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9432144165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.401216506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7240734100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5213489532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6940441131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5288543701172</t>
   </si>
   <si>
     <t xml:space="preserve">30.709056854248</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4988231658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7766361236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7602157592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2107200622559</t>
+    <t xml:space="preserve">30.4988212585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7766342163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7602195739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2107238769531</t>
   </si>
   <si>
     <t xml:space="preserve">32.4359703063965</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7376976013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1506576538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3083343505859</t>
+    <t xml:space="preserve">31.7376937866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1506500244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3083229064941</t>
   </si>
   <si>
     <t xml:space="preserve">32.345874786377</t>
@@ -3344,181 +3344,181 @@
     <t xml:space="preserve">31.8728485107422</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1370334625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8592224121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0544414520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4640998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2591972351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0342864990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.640682220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8052806854248</t>
+    <t xml:space="preserve">31.1370315551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.859224319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0544376373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4641036987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2592010498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0342807769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6406841278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8052825927734</t>
   </si>
   <si>
     <t xml:space="preserve">29.1265888214111</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0864276885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0583839416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9378910064697</t>
+    <t xml:space="preserve">29.08642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0583801269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.937894821167</t>
   </si>
   <si>
     <t xml:space="preserve">30.1146125793457</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5885410308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.359676361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.319522857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0303421020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1508293151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.335578918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2632846832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1668968200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1186962127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6046104431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7531394958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4118213653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5644416809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.548376083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9419803619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2713203430176</t>
+    <t xml:space="preserve">30.5885448455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3596820831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3195171356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0303401947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1508331298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3355808258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2632865905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1668949127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1187000274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.604606628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7531414031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4118232727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5644454956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5483779907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9419841766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2713260650635</t>
   </si>
   <si>
     <t xml:space="preserve">31.1829624176025</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1267356872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2150955200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2311592102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1910018920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4359226226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2029685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1788749694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8375549316406</t>
+    <t xml:space="preserve">31.1267337799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2150917053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2311611175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1909999847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4359188079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2029724121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1788730621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.837553024292</t>
   </si>
   <si>
     <t xml:space="preserve">30.8616504669189</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5082130432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3475608825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2913303375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4800357818604</t>
+    <t xml:space="preserve">30.5082168579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.347562789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2913341522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4800281524658</t>
   </si>
   <si>
     <t xml:space="preserve">28.885612487793</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3997020721436</t>
+    <t xml:space="preserve">29.3996982574463</t>
   </si>
   <si>
     <t xml:space="preserve">28.9338073730469</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7208633422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1907062530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.680700302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9939727783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0743064880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5803642272949</t>
+    <t xml:space="preserve">27.7208652496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1907024383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6807022094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9939765930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0743026733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5803661346436</t>
   </si>
   <si>
     <t xml:space="preserve">28.965934753418</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0783920288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8695411682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8374099731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8133125305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6285629272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3595333099365</t>
+    <t xml:space="preserve">29.0783977508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8695430755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8374118804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8133106231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6285610198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3595390319824</t>
   </si>
   <si>
     <t xml:space="preserve">29.0944595336914</t>
@@ -3527,139 +3527,139 @@
     <t xml:space="preserve">28.9579029083252</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3152847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1587200164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3675727844238</t>
+    <t xml:space="preserve">28.3152885437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1587162017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3675708770752</t>
   </si>
   <si>
     <t xml:space="preserve">28.8936424255371</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8026943206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2799034118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4106006622314</t>
+    <t xml:space="preserve">28.802698135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2799015045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4105987548828</t>
   </si>
   <si>
     <t xml:space="preserve">25.9600028991699</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9974212646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.981086730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9028205871582</t>
+    <t xml:space="preserve">26.9974231719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9810848236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9028224945068</t>
   </si>
   <si>
     <t xml:space="preserve">25.9273281097412</t>
   </si>
   <si>
-    <t xml:space="preserve">25.322847366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3623695373535</t>
+    <t xml:space="preserve">25.3228492736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3623676300049</t>
   </si>
   <si>
     <t xml:space="preserve">22.8885860443115</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5175724029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3963680267334</t>
+    <t xml:space="preserve">23.5175743103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3963642120361</t>
   </si>
   <si>
     <t xml:space="preserve">24.7101974487305</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3065128326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7231121063232</t>
+    <t xml:space="preserve">25.306510925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.723108291626</t>
   </si>
   <si>
     <t xml:space="preserve">25.821138381958</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1281223297119</t>
+    <t xml:space="preserve">27.1281204223633</t>
   </si>
   <si>
     <t xml:space="preserve">26.956579208374</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1444606781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7768688201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1036167144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0709400177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9892559051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.030101776123</t>
+    <t xml:space="preserve">27.1444568634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7768707275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1036186218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0709381103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9892539978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0300979614258</t>
   </si>
   <si>
     <t xml:space="preserve">27.3486747741699</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1328659057617</t>
+    <t xml:space="preserve">28.1328678131104</t>
   </si>
   <si>
     <t xml:space="preserve">27.9041442871094</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5447273254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9776630401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5937366485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5481472015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7523651123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8830642700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8667240142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.539981842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4991340637207</t>
+    <t xml:space="preserve">27.5447235107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9776592254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5937347412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5481491088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7523632049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8830604553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8667259216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5399799346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4991359710693</t>
   </si>
   <si>
     <t xml:space="preserve">26.3439311981201</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6414260864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2377376556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3520965576172</t>
+    <t xml:space="preserve">25.6414241790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.237735748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3520984649658</t>
   </si>
   <si>
     <t xml:space="preserve">26.1152076721191</t>
@@ -3671,43 +3671,43 @@
     <t xml:space="preserve">25.3146781921387</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3310165405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2738342285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6740989685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8048000335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.355525970459</t>
+    <t xml:space="preserve">25.3310146331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2738361358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6741008758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8047981262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3555240631104</t>
   </si>
   <si>
     <t xml:space="preserve">24.9634246826172</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9913578033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3017654418945</t>
+    <t xml:space="preserve">23.9913558959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3017635345459</t>
   </si>
   <si>
     <t xml:space="preserve">25.8374729156494</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3766059875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4256172180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.515474319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4419555664062</t>
+    <t xml:space="preserve">26.3766040802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4256153106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5154705047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4419536590576</t>
   </si>
   <si>
     <t xml:space="preserve">26.6380023956299</t>
@@ -3716,16 +3716,16 @@
     <t xml:space="preserve">26.5073051452637</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5489635467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7698364257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4734268188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5743732452393</t>
+    <t xml:space="preserve">27.5489616394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7698383331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4734287261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5743713378906</t>
   </si>
   <si>
     <t xml:space="preserve">27.6759967803955</t>
@@ -3737,16 +3737,16 @@
     <t xml:space="preserve">27.5828399658203</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3457164764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5235576629639</t>
+    <t xml:space="preserve">27.3457126617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5235595703125</t>
   </si>
   <si>
     <t xml:space="preserve">26.7274913787842</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5320243835449</t>
+    <t xml:space="preserve">27.5320262908936</t>
   </si>
   <si>
     <t xml:space="preserve">26.956148147583</t>
@@ -3761,10 +3761,10 @@
     <t xml:space="preserve">23.3992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8149147033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3484477996826</t>
+    <t xml:space="preserve">22.8149127960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.348445892334</t>
   </si>
   <si>
     <t xml:space="preserve">23.9751358032227</t>
@@ -3773,13 +3773,13 @@
     <t xml:space="preserve">22.9250049591064</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4161968231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5686340332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3569164276123</t>
+    <t xml:space="preserve">23.4161949157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5686321258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3569145202637</t>
   </si>
   <si>
     <t xml:space="preserve">23.0859127044678</t>
@@ -3788,16 +3788,16 @@
     <t xml:space="preserve">23.8904457092285</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6194477081299</t>
+    <t xml:space="preserve">23.6194458007812</t>
   </si>
   <si>
     <t xml:space="preserve">23.5093536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3230400085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8318500518799</t>
+    <t xml:space="preserve">23.3230419158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8318481445312</t>
   </si>
   <si>
     <t xml:space="preserve">22.747163772583</t>
@@ -3806,37 +3806,37 @@
     <t xml:space="preserve">22.7132873535156</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6462211608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9510974884033</t>
+    <t xml:space="preserve">21.64621925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9510955810547</t>
   </si>
   <si>
     <t xml:space="preserve">22.2644424438477</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7810382843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1120052337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4592247009277</t>
+    <t xml:space="preserve">22.7810363769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1120014190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4592266082764</t>
   </si>
   <si>
     <t xml:space="preserve">22.2220973968506</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3074684143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7563152313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2898464202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0520401000977</t>
+    <t xml:space="preserve">21.307466506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7563133239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2898483276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0520362854004</t>
   </si>
   <si>
     <t xml:space="preserve">23.0351009368896</t>
@@ -3860,31 +3860,31 @@
     <t xml:space="preserve">23.9666652679443</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0513553619385</t>
+    <t xml:space="preserve">24.0513534545898</t>
   </si>
   <si>
     <t xml:space="preserve">23.9327945709229</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4239807128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5256061553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9497318267822</t>
+    <t xml:space="preserve">24.4239826202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5256080627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9497299194336</t>
   </si>
   <si>
     <t xml:space="preserve">23.8565731048584</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4416027069092</t>
+    <t xml:space="preserve">23.4416046142578</t>
   </si>
   <si>
     <t xml:space="preserve">23.7888221740723</t>
   </si>
   <si>
-    <t xml:space="preserve">24.127571105957</t>
+    <t xml:space="preserve">24.1275749206543</t>
   </si>
   <si>
     <t xml:space="preserve">24.1360416412354</t>
@@ -3893,13 +3893,13 @@
     <t xml:space="preserve">23.5008850097656</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7380104064941</t>
+    <t xml:space="preserve">23.7380084991455</t>
   </si>
   <si>
     <t xml:space="preserve">23.0774440765381</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5354442596436</t>
+    <t xml:space="preserve">22.5354423522949</t>
   </si>
   <si>
     <t xml:space="preserve">22.9334735870361</t>
@@ -3908,16 +3908,16 @@
     <t xml:space="preserve">22.7725677490234</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0950660705566</t>
+    <t xml:space="preserve">22.095064163208</t>
   </si>
   <si>
     <t xml:space="preserve">22.0273151397705</t>
   </si>
   <si>
-    <t xml:space="preserve">22.255973815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3914737701416</t>
+    <t xml:space="preserve">22.2559719085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.391471862793</t>
   </si>
   <si>
     <t xml:space="preserve">21.925687789917</t>
@@ -3932,16 +3932,16 @@
     <t xml:space="preserve">22.4422836303711</t>
   </si>
   <si>
-    <t xml:space="preserve">23.068977355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9243221282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3907871246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9419460296631</t>
+    <t xml:space="preserve">23.0689754486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9243259429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3907909393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9419441223145</t>
   </si>
   <si>
     <t xml:space="preserve">22.6455364227295</t>
@@ -3953,22 +3953,22 @@
     <t xml:space="preserve">21.3921566009521</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5022506713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3413429260254</t>
+    <t xml:space="preserve">21.5022525787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3413467407227</t>
   </si>
   <si>
     <t xml:space="preserve">20.7908706665039</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0957469940186</t>
+    <t xml:space="preserve">21.0957489013672</t>
   </si>
   <si>
     <t xml:space="preserve">20.6553707122803</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8078079223633</t>
+    <t xml:space="preserve">20.8078098297119</t>
   </si>
   <si>
     <t xml:space="preserve">20.3335590362549</t>
@@ -3980,13 +3980,13 @@
     <t xml:space="preserve">23.2552871704102</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0344161987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4246635437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7979736328125</t>
+    <t xml:space="preserve">24.0344181060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4246654510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7979774475098</t>
   </si>
   <si>
     <t xml:space="preserve">23.4331340789795</t>
@@ -3995,22 +3995,22 @@
     <t xml:space="preserve">23.6533222198486</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0174827575684</t>
+    <t xml:space="preserve">24.0174808502197</t>
   </si>
   <si>
     <t xml:space="preserve">24.3308258056641</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3477649688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2037944793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7966079711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1438312530518</t>
+    <t xml:space="preserve">24.3477630615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2037963867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.79660987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1438293457031</t>
   </si>
   <si>
     <t xml:space="preserve">25.8297996520996</t>
@@ -4022,22 +4022,22 @@
     <t xml:space="preserve">26.2871170043945</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3802738189697</t>
+    <t xml:space="preserve">26.3802719116211</t>
   </si>
   <si>
     <t xml:space="preserve">25.6265506744385</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7197074890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6858329772949</t>
+    <t xml:space="preserve">25.719705581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6858310699463</t>
   </si>
   <si>
     <t xml:space="preserve">26.3294582366943</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3118381500244</t>
+    <t xml:space="preserve">27.311840057373</t>
   </si>
   <si>
     <t xml:space="preserve">26.9307441711426</t>
@@ -4049,34 +4049,34 @@
     <t xml:space="preserve">28.1756572723389</t>
   </si>
   <si>
-    <t xml:space="preserve">28.226469039917</t>
+    <t xml:space="preserve">28.2264652252197</t>
   </si>
   <si>
     <t xml:space="preserve">28.074031829834</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4551200866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2434043884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1163730621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3111553192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1671829223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4297199249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7091884613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1848087310791</t>
+    <t xml:space="preserve">28.4551258087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2434062957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1163749694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3111515045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1671848297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4297161102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7091903686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1848049163818</t>
   </si>
   <si>
     <t xml:space="preserve">27.2779636383057</t>
@@ -4088,7 +4088,7 @@
     <t xml:space="preserve">26.947681427002</t>
   </si>
   <si>
-    <t xml:space="preserve">27.286434173584</t>
+    <t xml:space="preserve">27.2864303588867</t>
   </si>
   <si>
     <t xml:space="preserve">27.0238990783691</t>
@@ -4100,7 +4100,7 @@
     <t xml:space="preserve">27.4981517791748</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2610244750977</t>
+    <t xml:space="preserve">27.2610263824463</t>
   </si>
   <si>
     <t xml:space="preserve">27.0577754974365</t>
@@ -4115,31 +4115,31 @@
     <t xml:space="preserve">28.0909652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">27.125524520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0916481018066</t>
+    <t xml:space="preserve">27.1255226135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0916500091553</t>
   </si>
   <si>
     <t xml:space="preserve">26.7105560302734</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7952404022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.421932220459</t>
+    <t xml:space="preserve">26.7952423095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4219341278076</t>
   </si>
   <si>
     <t xml:space="preserve">27.2271499633789</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4304027557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3203048706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1509323120117</t>
+    <t xml:space="preserve">27.4304008483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3203067779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1509342193604</t>
   </si>
   <si>
     <t xml:space="preserve">27.7014026641846</t>
@@ -4148,7 +4148,7 @@
     <t xml:space="preserve">28.2349376678467</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9046516418457</t>
+    <t xml:space="preserve">27.9046535491943</t>
   </si>
   <si>
     <t xml:space="preserve">28.192590713501</t>
@@ -4157,7 +4157,7 @@
     <t xml:space="preserve">28.4720592498779</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4635925292969</t>
+    <t xml:space="preserve">28.4635944366455</t>
   </si>
   <si>
     <t xml:space="preserve">29.0818157196045</t>
@@ -4169,22 +4169,22 @@
     <t xml:space="preserve">29.0479393005371</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7938766479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6922492980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4043159484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7176570892334</t>
+    <t xml:space="preserve">28.7938747406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.692253112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4043140411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7176551818848</t>
   </si>
   <si>
     <t xml:space="preserve">28.844690322876</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8362197875977</t>
+    <t xml:space="preserve">28.8362216949463</t>
   </si>
   <si>
     <t xml:space="preserve">28.8531551361084</t>
@@ -4193,34 +4193,34 @@
     <t xml:space="preserve">28.6244983673096</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8108158111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8785610198975</t>
+    <t xml:space="preserve">28.8108177185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8785629272461</t>
   </si>
   <si>
     <t xml:space="preserve">29.0902843475342</t>
   </si>
   <si>
-    <t xml:space="preserve">28.870096206665</t>
+    <t xml:space="preserve">28.8700923919678</t>
   </si>
   <si>
     <t xml:space="preserve">28.8277549743652</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1417789459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7600002288818</t>
+    <t xml:space="preserve">28.1417770385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7599983215332</t>
   </si>
   <si>
     <t xml:space="preserve">28.675313949585</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7591857910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2301387786865</t>
+    <t xml:space="preserve">28.759183883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2301406860352</t>
   </si>
   <si>
     <t xml:space="preserve">28.0740299224854</t>
@@ -4232,25 +4232,25 @@
     <t xml:space="preserve">28.0133190155029</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2908496856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3515605926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.299524307251</t>
+    <t xml:space="preserve">28.2908477783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3515586853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2995223999023</t>
   </si>
   <si>
     <t xml:space="preserve">28.1520843505859</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3081951141357</t>
+    <t xml:space="preserve">28.3081970214844</t>
   </si>
   <si>
     <t xml:space="preserve">28.2214679718018</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1434116363525</t>
+    <t xml:space="preserve">28.1434154510498</t>
   </si>
   <si>
     <t xml:space="preserve">26.9812507629395</t>
@@ -4259,16 +4259,16 @@
     <t xml:space="preserve">26.1660003662109</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4027919769287</t>
+    <t xml:space="preserve">25.4027900695801</t>
   </si>
   <si>
     <t xml:space="preserve">26.0185623168945</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9344577789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0558738708496</t>
+    <t xml:space="preserve">24.934455871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0558757781982</t>
   </si>
   <si>
     <t xml:space="preserve">24.275318145752</t>
@@ -4277,7 +4277,7 @@
     <t xml:space="preserve">24.9951648712158</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8017425537109</t>
+    <t xml:space="preserve">25.8017387390137</t>
   </si>
   <si>
     <t xml:space="preserve">25.3594264984131</t>
@@ -4295,13 +4295,13 @@
     <t xml:space="preserve">24.7176342010498</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1686229705811</t>
+    <t xml:space="preserve">25.1686248779297</t>
   </si>
   <si>
     <t xml:space="preserve">25.4634990692139</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4808444976807</t>
+    <t xml:space="preserve">25.4808464050293</t>
   </si>
   <si>
     <t xml:space="preserve">25.4461536407471</t>
@@ -4316,7 +4316,7 @@
     <t xml:space="preserve">25.5068645477295</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9058170318604</t>
+    <t xml:space="preserve">25.9058151245117</t>
   </si>
   <si>
     <t xml:space="preserve">26.1052913665771</t>
@@ -4334,10 +4334,10 @@
     <t xml:space="preserve">26.2006912231445</t>
   </si>
   <si>
-    <t xml:space="preserve">26.408842086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.443531036377</t>
+    <t xml:space="preserve">26.4088401794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4435329437256</t>
   </si>
   <si>
     <t xml:space="preserve">26.5042400360107</t>
@@ -4346,10 +4346,10 @@
     <t xml:space="preserve">26.313440322876</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1833457946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.452205657959</t>
+    <t xml:space="preserve">26.1833477020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4522037506104</t>
   </si>
   <si>
     <t xml:space="preserve">26.0966186523438</t>
@@ -4358,10 +4358,10 @@
     <t xml:space="preserve">25.4721736907959</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6109390258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3767700195312</t>
+    <t xml:space="preserve">25.6109409332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3767719268799</t>
   </si>
   <si>
     <t xml:space="preserve">26.3307857513428</t>
@@ -4370,16 +4370,16 @@
     <t xml:space="preserve">26.1920223236084</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0098896026611</t>
+    <t xml:space="preserve">26.0098915100098</t>
   </si>
   <si>
     <t xml:space="preserve">25.8104133605957</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5215892791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8424854278564</t>
+    <t xml:space="preserve">26.5215873718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8424835205078</t>
   </si>
   <si>
     <t xml:space="preserve">26.4868984222412</t>
@@ -4388,16 +4388,16 @@
     <t xml:space="preserve">26.5996437072754</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7297382354736</t>
+    <t xml:space="preserve">26.729736328125</t>
   </si>
   <si>
     <t xml:space="preserve">27.1062107086182</t>
   </si>
   <si>
-    <t xml:space="preserve">27.088285446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3353328704834</t>
+    <t xml:space="preserve">27.0882835388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.335334777832</t>
   </si>
   <si>
     <t xml:space="preserve">26.4070415496826</t>
@@ -4406,10 +4406,10 @@
     <t xml:space="preserve">26.675952911377</t>
   </si>
   <si>
-    <t xml:space="preserve">26.702844619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.308443069458</t>
+    <t xml:space="preserve">26.7028465270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3084411621094</t>
   </si>
   <si>
     <t xml:space="preserve">25.8154392242432</t>
@@ -4418,10 +4418,10 @@
     <t xml:space="preserve">26.3622245788574</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8821182250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6938819885254</t>
+    <t xml:space="preserve">26.8821201324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.693883895874</t>
   </si>
   <si>
     <t xml:space="preserve">27.20481300354</t>
@@ -4430,13 +4430,13 @@
     <t xml:space="preserve">27.4737224578857</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5185432434082</t>
+    <t xml:space="preserve">27.5185413360596</t>
   </si>
   <si>
     <t xml:space="preserve">27.3930473327637</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6529960632324</t>
+    <t xml:space="preserve">27.6529979705811</t>
   </si>
   <si>
     <t xml:space="preserve">27.7157440185547</t>
@@ -4445,28 +4445,28 @@
     <t xml:space="preserve">27.9219074249268</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8860530853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9667282104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9398345947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7605590820312</t>
+    <t xml:space="preserve">27.8860549926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.966724395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9398365020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7605609893799</t>
   </si>
   <si>
     <t xml:space="preserve">27.6619625091553</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4647579193115</t>
+    <t xml:space="preserve">27.4647598266602</t>
   </si>
   <si>
     <t xml:space="preserve">27.3840847015381</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3213405609131</t>
+    <t xml:space="preserve">27.3213386535645</t>
   </si>
   <si>
     <t xml:space="preserve">27.6081790924072</t>
@@ -4478,10 +4478,10 @@
     <t xml:space="preserve">28.0115451812744</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2356376647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7644958496094</t>
+    <t xml:space="preserve">28.2356357574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7644939422607</t>
   </si>
   <si>
     <t xml:space="preserve">28.3611278533936</t>
@@ -4490,64 +4490,64 @@
     <t xml:space="preserve">27.9129428863525</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4378681182861</t>
+    <t xml:space="preserve">27.4378700256348</t>
   </si>
   <si>
     <t xml:space="preserve">27.8233089447021</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9577617645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5045490264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7465686798096</t>
+    <t xml:space="preserve">27.957763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5045471191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7465667724609</t>
   </si>
   <si>
     <t xml:space="preserve">28.6927833557129</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7555313110352</t>
+    <t xml:space="preserve">28.7555332183838</t>
   </si>
   <si>
     <t xml:space="preserve">28.9796257019043</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0334072113037</t>
+    <t xml:space="preserve">29.0334053039551</t>
   </si>
   <si>
     <t xml:space="preserve">29.132007598877</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3740253448486</t>
+    <t xml:space="preserve">29.3740291595459</t>
   </si>
   <si>
     <t xml:space="preserve">29.2306060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7056827545166</t>
+    <t xml:space="preserve">29.705680847168</t>
   </si>
   <si>
     <t xml:space="preserve">30.1000862121582</t>
   </si>
   <si>
-    <t xml:space="preserve">30.960599899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5482692718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1986865997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8132438659668</t>
+    <t xml:space="preserve">30.9606037139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5482711791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1986827850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8132457733154</t>
   </si>
   <si>
     <t xml:space="preserve">29.8311729431152</t>
   </si>
   <si>
-    <t xml:space="preserve">28.773458480835</t>
+    <t xml:space="preserve">28.7734565734863</t>
   </si>
   <si>
     <t xml:space="preserve">29.1588954925537</t>
@@ -4565,52 +4565,52 @@
     <t xml:space="preserve">29.3650608062744</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0871868133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7017498016357</t>
+    <t xml:space="preserve">29.0871906280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7017478942871</t>
   </si>
   <si>
     <t xml:space="preserve">28.9975490570068</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1768226623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2574977874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.311279296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5712299346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1628341674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9745941162109</t>
+    <t xml:space="preserve">29.1768245697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2574996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3112812042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5712280273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1628322601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9745903015137</t>
   </si>
   <si>
     <t xml:space="preserve">30.2166137695312</t>
   </si>
   <si>
-    <t xml:space="preserve">30.001485824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0283737182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7773952484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.723611831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7684288024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1717948913574</t>
+    <t xml:space="preserve">30.0014896392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0283756256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7773933410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7236099243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7684268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1717967987061</t>
   </si>
   <si>
     <t xml:space="preserve">30.180757522583</t>
@@ -4622,31 +4622,31 @@
     <t xml:space="preserve">30.0104484558105</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2703952789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5930919647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1449031829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.153865814209</t>
+    <t xml:space="preserve">30.2703971862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5930881500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.144905090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1538677215576</t>
   </si>
   <si>
     <t xml:space="preserve">30.0463027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0373363494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6967182159424</t>
+    <t xml:space="preserve">30.0373382568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.696720123291</t>
   </si>
   <si>
     <t xml:space="preserve">29.1678619384766</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6877555847168</t>
+    <t xml:space="preserve">29.6877536773682</t>
   </si>
   <si>
     <t xml:space="preserve">29.3292083740234</t>
@@ -4655,10 +4655,10 @@
     <t xml:space="preserve">29.4278087615967</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0552673339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7107124328613</t>
+    <t xml:space="preserve">30.0552654266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7107105255127</t>
   </si>
   <si>
     <t xml:space="preserve">28.5224761962891</t>
@@ -4670,28 +4670,28 @@
     <t xml:space="preserve">28.2177085876465</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7426357269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3392677307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.509578704834</t>
+    <t xml:space="preserve">27.7426338195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3392658233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5095767974854</t>
   </si>
   <si>
     <t xml:space="preserve">27.3571968078613</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0524311065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1868858337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2854843139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2944507598877</t>
+    <t xml:space="preserve">27.0524291992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1868839263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2854862213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2944488525391</t>
   </si>
   <si>
     <t xml:space="preserve">27.4468307495117</t>
@@ -4700,10 +4700,10 @@
     <t xml:space="preserve">27.5454330444336</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0294742584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.405948638916</t>
+    <t xml:space="preserve">28.0294723510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4059467315674</t>
   </si>
   <si>
     <t xml:space="preserve">28.1191101074219</t>
@@ -4712,10 +4712,10 @@
     <t xml:space="preserve">28.2714920043945</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6838226318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4955825805664</t>
+    <t xml:space="preserve">28.6838207244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.495584487915</t>
   </si>
   <si>
     <t xml:space="preserve">29.0423698425293</t>
@@ -4724,16 +4724,16 @@
     <t xml:space="preserve">29.732572555542</t>
   </si>
   <si>
-    <t xml:space="preserve">29.78635597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3919525146484</t>
+    <t xml:space="preserve">29.7863540649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3919544219971</t>
   </si>
   <si>
     <t xml:space="preserve">29.4547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8491020202637</t>
+    <t xml:space="preserve">29.849100112915</t>
   </si>
   <si>
     <t xml:space="preserve">29.1947536468506</t>
@@ -4742,22 +4742,22 @@
     <t xml:space="preserve">28.8989524841309</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2664623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0602951049805</t>
+    <t xml:space="preserve">29.2664642333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0602931976318</t>
   </si>
   <si>
     <t xml:space="preserve">29.1499347686768</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4367713928223</t>
+    <t xml:space="preserve">29.4367733001709</t>
   </si>
   <si>
     <t xml:space="preserve">29.0961513519287</t>
   </si>
   <si>
-    <t xml:space="preserve">29.24853515625</t>
+    <t xml:space="preserve">29.2485332489014</t>
   </si>
   <si>
     <t xml:space="preserve">29.5891532897949</t>
@@ -4772,13 +4772,13 @@
     <t xml:space="preserve">30.2883243560791</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0731945037842</t>
+    <t xml:space="preserve">30.0731906890869</t>
   </si>
   <si>
     <t xml:space="preserve">30.4048500061035</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4317398071289</t>
+    <t xml:space="preserve">30.4317436218262</t>
   </si>
   <si>
     <t xml:space="preserve">30.3600311279297</t>
@@ -4790,7 +4790,7 @@
     <t xml:space="preserve">30.1359386444092</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3152122497559</t>
+    <t xml:space="preserve">30.3152141571045</t>
   </si>
   <si>
     <t xml:space="preserve">30.3421020507812</t>
@@ -4802,43 +4802,43 @@
     <t xml:space="preserve">30.3331413269043</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0642337799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6110172271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8440704345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0860919952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1936511993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1577987670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1757278442383</t>
+    <t xml:space="preserve">30.0642318725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6110191345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8440723419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0860958099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1936550140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1577968597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1757259368896</t>
   </si>
   <si>
     <t xml:space="preserve">31.3818912506104</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5522060394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8121547698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8480072021484</t>
+    <t xml:space="preserve">31.5522041320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8121528625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8480014801025</t>
   </si>
   <si>
     <t xml:space="preserve">32.0003890991211</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2384757995605</t>
+    <t xml:space="preserve">31.2384719848633</t>
   </si>
   <si>
     <t xml:space="preserve">31.713550567627</t>
@@ -4847,22 +4847,22 @@
     <t xml:space="preserve">31.7314777374268</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5432415008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8300743103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8211154937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1258811950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0900230407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2743301391602</t>
+    <t xml:space="preserve">31.5432376861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.821117401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1258773803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0900268554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2743244171143</t>
   </si>
   <si>
     <t xml:space="preserve">30.9068183898926</t>
@@ -4874,13 +4874,13 @@
     <t xml:space="preserve">30.1090488433838</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3958873748779</t>
+    <t xml:space="preserve">30.3958854675293</t>
   </si>
   <si>
     <t xml:space="preserve">30.8551158905029</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3069019317627</t>
+    <t xml:space="preserve">30.3069038391113</t>
   </si>
   <si>
     <t xml:space="preserve">30.6632423400879</t>
@@ -4895,28 +4895,28 @@
     <t xml:space="preserve">31.9606704711914</t>
   </si>
   <si>
-    <t xml:space="preserve">31.57692527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3667774200439</t>
+    <t xml:space="preserve">31.5769271850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3667812347412</t>
   </si>
   <si>
     <t xml:space="preserve">31.2114505767822</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3941898345947</t>
+    <t xml:space="preserve">31.3941860198975</t>
   </si>
   <si>
     <t xml:space="preserve">31.4764194488525</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6957035064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8601665496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9698085784912</t>
+    <t xml:space="preserve">31.6957015991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.860164642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9698104858398</t>
   </si>
   <si>
     <t xml:space="preserve">31.9789447784424</t>
@@ -4925,13 +4925,13 @@
     <t xml:space="preserve">31.9241237640381</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6550712585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3626937866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3718338012695</t>
+    <t xml:space="preserve">32.6550750732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3626899719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3718299865723</t>
   </si>
   <si>
     <t xml:space="preserve">32.9748611450195</t>
@@ -4952,28 +4952,28 @@
     <t xml:space="preserve">33.7423553466797</t>
   </si>
   <si>
-    <t xml:space="preserve">33.797176361084</t>
+    <t xml:space="preserve">33.7971801757812</t>
   </si>
   <si>
     <t xml:space="preserve">33.7514953613281</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6418533325195</t>
+    <t xml:space="preserve">33.6418495178223</t>
   </si>
   <si>
     <t xml:space="preserve">32.947452545166</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2946510314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3311958312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2398338317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4042930603027</t>
+    <t xml:space="preserve">33.2946472167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3311996459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2398300170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.404296875</t>
   </si>
   <si>
     <t xml:space="preserve">33.0936393737793</t>
@@ -4982,16 +4982,16 @@
     <t xml:space="preserve">32.6367988586426</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4175109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3809661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6134719848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8144836425781</t>
+    <t xml:space="preserve">32.4175148010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3809623718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.613468170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8144817352295</t>
   </si>
   <si>
     <t xml:space="preserve">32.5819778442383</t>
@@ -5003,7 +5003,7 @@
     <t xml:space="preserve">33.130184173584</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0753631591797</t>
+    <t xml:space="preserve">33.075366973877</t>
   </si>
   <si>
     <t xml:space="preserve">32.9109039306641</t>
@@ -5012,19 +5012,19 @@
     <t xml:space="preserve">33.1850090026855</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4408416748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7697639465332</t>
+    <t xml:space="preserve">33.4408378601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7697677612305</t>
   </si>
   <si>
     <t xml:space="preserve">33.9525032043457</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4093475341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.884464263916</t>
+    <t xml:space="preserve">34.4093437194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8844604492188</t>
   </si>
   <si>
     <t xml:space="preserve">35.4692192077637</t>
@@ -5039,10 +5039,10 @@
     <t xml:space="preserve">37.0955772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">36.912841796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0590286254883</t>
+    <t xml:space="preserve">36.9128456115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0590324401855</t>
   </si>
   <si>
     <t xml:space="preserve">36.7849235534668</t>
@@ -5051,16 +5051,16 @@
     <t xml:space="preserve">37.0985145568848</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9844779968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1555290222168</t>
+    <t xml:space="preserve">36.9844818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1555252075195</t>
   </si>
   <si>
     <t xml:space="preserve">37.1365280151367</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3265800476074</t>
+    <t xml:space="preserve">37.3265762329102</t>
   </si>
   <si>
     <t xml:space="preserve">37.0224914550781</t>
@@ -5084,7 +5084,7 @@
     <t xml:space="preserve">36.4523315429688</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8704452514648</t>
+    <t xml:space="preserve">36.8704490661621</t>
   </si>
   <si>
     <t xml:space="preserve">36.9084625244141</t>
@@ -5093,10 +5093,10 @@
     <t xml:space="preserve">36.5853691101074</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5473594665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0912246704102</t>
+    <t xml:space="preserve">36.5473556518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0912284851074</t>
   </si>
   <si>
     <t xml:space="preserve">36.5663642883301</t>
@@ -5105,7 +5105,7 @@
     <t xml:space="preserve">35.7301254272461</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0839385986328</t>
+    <t xml:space="preserve">35.0839424133301</t>
   </si>
   <si>
     <t xml:space="preserve">35.1219520568848</t>
@@ -5120,7 +5120,7 @@
     <t xml:space="preserve">35.7491302490234</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3573036193848</t>
+    <t xml:space="preserve">36.3572998046875</t>
   </si>
   <si>
     <t xml:space="preserve">36.0722198486328</t>
@@ -5129,13 +5129,13 @@
     <t xml:space="preserve">35.8821678161621</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7871437072754</t>
+    <t xml:space="preserve">35.7871398925781</t>
   </si>
   <si>
     <t xml:space="preserve">35.5970878601074</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9201812744141</t>
+    <t xml:space="preserve">35.9201774597168</t>
   </si>
   <si>
     <t xml:space="preserve">35.9391860961914</t>
@@ -5147,13 +5147,13 @@
     <t xml:space="preserve">35.8631629943848</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9011726379395</t>
+    <t xml:space="preserve">35.9011764526367</t>
   </si>
   <si>
     <t xml:space="preserve">36.3763084411621</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8514404296875</t>
+    <t xml:space="preserve">36.8514442443848</t>
   </si>
   <si>
     <t xml:space="preserve">37.2885704040527</t>
@@ -5177,7 +5177,7 @@
     <t xml:space="preserve">38.3718757629395</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4478988647461</t>
+    <t xml:space="preserve">38.4478950500488</t>
   </si>
   <si>
     <t xml:space="preserve">38.5429229736328</t>
@@ -5189,7 +5189,7 @@
     <t xml:space="preserve">37.7446975708008</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6423835754395</t>
+    <t xml:space="preserve">36.6423873901367</t>
   </si>
   <si>
     <t xml:space="preserve">35.4450454711914</t>
@@ -5201,7 +5201,7 @@
     <t xml:space="preserve">35.8061485290527</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6921157836914</t>
+    <t xml:space="preserve">35.6921195983887</t>
   </si>
   <si>
     <t xml:space="preserve">36.1862564086914</t>
@@ -5210,7 +5210,7 @@
     <t xml:space="preserve">36.4903450012207</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8894577026367</t>
+    <t xml:space="preserve">36.8894538879395</t>
   </si>
   <si>
     <t xml:space="preserve">37.8017120361328</t>
@@ -5222,16 +5222,16 @@
     <t xml:space="preserve">37.7827072143555</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6876831054688</t>
+    <t xml:space="preserve">37.6876792907715</t>
   </si>
   <si>
     <t xml:space="preserve">37.9727592468262</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9917640686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3338661193848</t>
+    <t xml:space="preserve">37.9917678833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3338623046875</t>
   </si>
   <si>
     <t xml:space="preserve">38.4098815917969</t>
@@ -5246,7 +5246,7 @@
     <t xml:space="preserve">37.7066879272461</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2198295593262</t>
+    <t xml:space="preserve">38.2198333740234</t>
   </si>
   <si>
     <t xml:space="preserve">38.0107727050781</t>
@@ -5255,10 +5255,10 @@
     <t xml:space="preserve">38.2768478393555</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2578430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2388381958008</t>
+    <t xml:space="preserve">38.2578392028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.238842010498</t>
   </si>
   <si>
     <t xml:space="preserve">38.5809326171875</t>
@@ -5276,7 +5276,7 @@
     <t xml:space="preserve">39.0940780639648</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5999374389648</t>
+    <t xml:space="preserve">38.5999412536621</t>
   </si>
   <si>
     <t xml:space="preserve">37.7256927490234</t>
@@ -5297,7 +5297,7 @@
     <t xml:space="preserve">39.4741897583008</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8162879943848</t>
+    <t xml:space="preserve">39.8162841796875</t>
   </si>
   <si>
     <t xml:space="preserve">39.9493217468262</t>
@@ -5315,7 +5315,7 @@
     <t xml:space="preserve">39.6452369689941</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3981628417969</t>
+    <t xml:space="preserve">39.3981666564941</t>
   </si>
   <si>
     <t xml:space="preserve">39.3601531982422</t>
@@ -5342,10 +5342,10 @@
     <t xml:space="preserve">38.5619316101074</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9873313903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8923034667969</t>
+    <t xml:space="preserve">39.9873352050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8923072814941</t>
   </si>
   <si>
     <t xml:space="preserve">40.1773834228516</t>
@@ -5372,10 +5372,10 @@
     <t xml:space="preserve">40.9946174621582</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3557243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5267677307129</t>
+    <t xml:space="preserve">41.3557205200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5267715454102</t>
   </si>
   <si>
     <t xml:space="preserve">41.3747291564941</t>
@@ -5387,13 +5387,13 @@
     <t xml:space="preserve">41.6978187561035</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1349449157715</t>
+    <t xml:space="preserve">42.1349411010742</t>
   </si>
   <si>
     <t xml:space="preserve">42.0209121704102</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7548332214355</t>
+    <t xml:space="preserve">41.7548294067383</t>
   </si>
   <si>
     <t xml:space="preserve">42.3820114135742</t>
@@ -5402,7 +5402,7 @@
     <t xml:space="preserve">42.4390258789062</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4580307006836</t>
+    <t xml:space="preserve">42.4580345153809</t>
   </si>
   <si>
     <t xml:space="preserve">42.2869834899902</t>
@@ -5420,7 +5420,7 @@
     <t xml:space="preserve">43.5223350524902</t>
   </si>
   <si>
-    <t xml:space="preserve">42.876148223877</t>
+    <t xml:space="preserve">42.8761520385742</t>
   </si>
   <si>
     <t xml:space="preserve">42.9521751403809</t>
@@ -5432,7 +5432,7 @@
     <t xml:space="preserve">43.0852088928223</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3059883117676</t>
+    <t xml:space="preserve">42.3059921264648</t>
   </si>
   <si>
     <t xml:space="preserve">42.7431144714355</t>
@@ -5453,13 +5453,13 @@
     <t xml:space="preserve">42.9901847839355</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8951530456543</t>
+    <t xml:space="preserve">42.8951568603516</t>
   </si>
   <si>
     <t xml:space="preserve">43.7123908996582</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4653167724609</t>
+    <t xml:space="preserve">43.4653205871582</t>
   </si>
   <si>
     <t xml:space="preserve">44.0354804992676</t>
@@ -5477,19 +5477,19 @@
     <t xml:space="preserve">46.6202163696289</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6392211914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.696231842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5821990966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7722549438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2781181335449</t>
+    <t xml:space="preserve">46.639217376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6962356567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.582202911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7722587585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2781143188477</t>
   </si>
   <si>
     <t xml:space="preserve">46.1070671081543</t>
@@ -5498,7 +5498,7 @@
     <t xml:space="preserve">45.8219871520996</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0310478210449</t>
+    <t xml:space="preserve">46.0310440063477</t>
   </si>
   <si>
     <t xml:space="preserve">45.7839736938477</t>
@@ -5540,7 +5540,7 @@
     <t xml:space="preserve">48.9388694763184</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8438453674316</t>
+    <t xml:space="preserve">48.8438415527344</t>
   </si>
   <si>
     <t xml:space="preserve">48.7963256835938</t>
@@ -71296,7 +71296,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.691087963</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>204898</v>
@@ -71317,6 +71317,32 @@
         <v>1981</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6909722222</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>142806</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>49.4799995422363</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>48.7400016784668</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>49.4599990844727</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>1966</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BGN.MI.xlsx
+++ b/data/BGN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="1982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="1983">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4796009063721</t>
+    <t xml:space="preserve">17.4796028137207</t>
   </si>
   <si>
     <t xml:space="preserve">BGN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2943077087402</t>
+    <t xml:space="preserve">17.294303894043</t>
   </si>
   <si>
     <t xml:space="preserve">16.7816524505615</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5284175872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2628231048584</t>
+    <t xml:space="preserve">16.528413772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2628269195557</t>
   </si>
   <si>
     <t xml:space="preserve">16.3678245544434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5098857879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9422416687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6457691192627</t>
+    <t xml:space="preserve">16.5098838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9422435760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6457710266113</t>
   </si>
   <si>
     <t xml:space="preserve">16.1269397735596</t>
@@ -74,19 +74,19 @@
     <t xml:space="preserve">15.6760511398315</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9601716995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0707559585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0769281387329</t>
+    <t xml:space="preserve">15.9601755142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0707502365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0769271850586</t>
   </si>
   <si>
     <t xml:space="preserve">15.5092849731445</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5401668548584</t>
+    <t xml:space="preserve">15.5401725769043</t>
   </si>
   <si>
     <t xml:space="preserve">15.4289894104004</t>
@@ -95,94 +95,94 @@
     <t xml:space="preserve">15.6019353866577</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1942834854126</t>
+    <t xml:space="preserve">15.1942844390869</t>
   </si>
   <si>
     <t xml:space="preserve">15.4784030914307</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2931089401245</t>
+    <t xml:space="preserve">15.2931070327759</t>
   </si>
   <si>
     <t xml:space="preserve">15.0213422775269</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8230886459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7180910110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5945606231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4580774307251</t>
+    <t xml:space="preserve">13.8230905532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.718092918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5945596694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4580764770508</t>
   </si>
   <si>
     <t xml:space="preserve">12.6804294586182</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5636758804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1745519638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4154376983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0022125244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8477964401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3851556777954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4098615646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1936826705933</t>
+    <t xml:space="preserve">13.5636768341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1745567321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4154367446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0022106170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8477954864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3851594924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4098644256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1936817169189</t>
   </si>
   <si>
     <t xml:space="preserve">14.4963331222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1813335418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.323390007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3357419967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5210399627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8607482910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2436943054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5710496902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4969348907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4351673126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4413452148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3239879608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0157642364502</t>
+    <t xml:space="preserve">14.1813316345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3233938217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3357400894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5210409164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8607492446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2436952590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5710525512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4969329833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4351682662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4413433074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3239898681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0157604217529</t>
   </si>
   <si>
     <t xml:space="preserve">16.2010593414307</t>
@@ -194,19 +194,19 @@
     <t xml:space="preserve">16.1578216552734</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3431205749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8489971160889</t>
+    <t xml:space="preserve">16.3431224822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8489952087402</t>
   </si>
   <si>
     <t xml:space="preserve">15.8922300338745</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6081113815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9354639053345</t>
+    <t xml:space="preserve">15.6081132888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9354658126831</t>
   </si>
   <si>
     <t xml:space="preserve">15.9663496017456</t>
@@ -215,58 +215,58 @@
     <t xml:space="preserve">16.0095863342285</t>
   </si>
   <si>
-    <t xml:space="preserve">15.867525100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8298645019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8854598999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6569232940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9410429000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3981094360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5339908599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8737020492554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9478235244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1145896911621</t>
+    <t xml:space="preserve">15.8675241470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8298673629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8854570388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6569223403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9410438537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3981075286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5339946746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8737001419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9478216171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1145877838135</t>
   </si>
   <si>
     <t xml:space="preserve">16.083703994751</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0713500976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1084117889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2072334289551</t>
+    <t xml:space="preserve">16.0713520050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1084079742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2072353363037</t>
   </si>
   <si>
     <t xml:space="preserve">16.0589981079102</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2998809814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1701755523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1207618713379</t>
+    <t xml:space="preserve">16.2998828887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1701774597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1207637786865</t>
   </si>
   <si>
     <t xml:space="preserve">15.7316417694092</t>
@@ -275,58 +275,58 @@
     <t xml:space="preserve">15.3795785903931</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1201639175415</t>
+    <t xml:space="preserve">15.1201648712158</t>
   </si>
   <si>
     <t xml:space="preserve">14.8916339874268</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7063360214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6383953094482</t>
+    <t xml:space="preserve">14.7063369750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6383934020996</t>
   </si>
   <si>
     <t xml:space="preserve">14.6075105667114</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2986850738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4531021118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6692781448364</t>
+    <t xml:space="preserve">14.2986841201782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4530982971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6692771911621</t>
   </si>
   <si>
     <t xml:space="preserve">14.3419198989868</t>
   </si>
   <si>
-    <t xml:space="preserve">14.366626739502</t>
+    <t xml:space="preserve">14.3666276931763</t>
   </si>
   <si>
     <t xml:space="preserve">14.3913316726685</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3975086212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5537919998169</t>
+    <t xml:space="preserve">14.3975076675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5537900924683</t>
   </si>
   <si>
     <t xml:space="preserve">14.8142623901367</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9640340805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5110197067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5956745147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3742723464966</t>
+    <t xml:space="preserve">14.9640331268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5110177993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5956726074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3742742538452</t>
   </si>
   <si>
     <t xml:space="preserve">15.3286933898926</t>
@@ -335,22 +335,22 @@
     <t xml:space="preserve">15.1138029098511</t>
   </si>
   <si>
-    <t xml:space="preserve">15.009614944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0551986694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.211480140686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3547391891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3026466369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.257061958313</t>
+    <t xml:space="preserve">15.0096139907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0551977157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2114791870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3547353744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3026437759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2570667266846</t>
   </si>
   <si>
     <t xml:space="preserve">14.8533315658569</t>
@@ -359,109 +359,109 @@
     <t xml:space="preserve">14.0979681015015</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2058582305908</t>
+    <t xml:space="preserve">13.2058563232422</t>
   </si>
   <si>
     <t xml:space="preserve">12.9649200439453</t>
   </si>
   <si>
-    <t xml:space="preserve">12.945387840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1993465423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6616802215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.837495803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1565732955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5733270645142</t>
+    <t xml:space="preserve">12.945384979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1993455886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6616821289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8374977111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1565742492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5733261108398</t>
   </si>
   <si>
     <t xml:space="preserve">12.8737573623657</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6690816879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7341985702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6560564041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6821050643921</t>
+    <t xml:space="preserve">11.6690797805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7341995239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6560583114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6821031570435</t>
   </si>
   <si>
     <t xml:space="preserve">11.6039619445801</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2002353668213</t>
+    <t xml:space="preserve">11.2002334594727</t>
   </si>
   <si>
     <t xml:space="preserve">10.8160409927368</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4318447113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7444095611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2588386535645</t>
+    <t xml:space="preserve">10.4318466186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7444086074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2588396072388</t>
   </si>
   <si>
     <t xml:space="preserve">11.923038482666</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3137445449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2616500854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5286340713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.567702293396</t>
+    <t xml:space="preserve">12.3137454986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2616510391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5286331176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5677013397217</t>
   </si>
   <si>
     <t xml:space="preserve">12.6588697433472</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3723516464233</t>
+    <t xml:space="preserve">12.3723497390747</t>
   </si>
   <si>
     <t xml:space="preserve">12.5221195220947</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5416584014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.339789390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5025882720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2551383972168</t>
+    <t xml:space="preserve">12.5416593551636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3397922515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5025863647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2551374435425</t>
   </si>
   <si>
     <t xml:space="preserve">12.4895639419556</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2421140670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0337400436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8188505172729</t>
+    <t xml:space="preserve">12.242115020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0337390899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8188514709473</t>
   </si>
   <si>
     <t xml:space="preserve">11.6300106048584</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">11.4281463623047</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3825626373291</t>
+    <t xml:space="preserve">11.3825616836548</t>
   </si>
   <si>
     <t xml:space="preserve">11.8579196929932</t>
@@ -479,37 +479,37 @@
     <t xml:space="preserve">11.9946689605713</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1835098266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2030458450317</t>
+    <t xml:space="preserve">12.1835107803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2030448913574</t>
   </si>
   <si>
     <t xml:space="preserve">12.0532760620117</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9490852355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7928047180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.525821685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7667551040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4411678314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3630275726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5583810806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7797813415527</t>
+    <t xml:space="preserve">11.9490871429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7928028106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5258226394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7667560577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4411687850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3630285263062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5583791732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7797794342041</t>
   </si>
   <si>
     <t xml:space="preserve">11.5388450622559</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">11.7472219467163</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6951274871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.942572593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1314163208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1379261016846</t>
+    <t xml:space="preserve">11.6951246261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9425745010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1314153671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1379280090332</t>
   </si>
   <si>
     <t xml:space="preserve">12.4114208221436</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">12.6653814315796</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8021268844604</t>
+    <t xml:space="preserve">12.8021259307861</t>
   </si>
   <si>
     <t xml:space="preserve">12.3788633346558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1183929443359</t>
+    <t xml:space="preserve">12.1183919906616</t>
   </si>
   <si>
     <t xml:space="preserve">12.1249046325684</t>
@@ -554,49 +554,49 @@
     <t xml:space="preserve">12.2876987457275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8709449768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7016382217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8514089584351</t>
+    <t xml:space="preserve">11.870945930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7016372680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.851411819458</t>
   </si>
   <si>
     <t xml:space="preserve">11.9165267944336</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2523279190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1937208175659</t>
+    <t xml:space="preserve">11.252326965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1937217712402</t>
   </si>
   <si>
     <t xml:space="preserve">11.148138999939</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0830221176147</t>
+    <t xml:space="preserve">11.0830230712891</t>
   </si>
   <si>
     <t xml:space="preserve">11.1220922470093</t>
   </si>
   <si>
-    <t xml:space="preserve">11.174186706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1090698242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2848873138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1351146697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0765113830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1872091293335</t>
+    <t xml:space="preserve">11.1741857528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1090679168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2848863601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1351156234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.076509475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1872100830078</t>
   </si>
   <si>
     <t xml:space="preserve">11.0244159698486</t>
@@ -614,145 +614,145 @@
     <t xml:space="preserve">11.9100151062012</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1769981384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.29421043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4309577941895</t>
+    <t xml:space="preserve">12.1770000457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2942085266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4309568405151</t>
   </si>
   <si>
     <t xml:space="preserve">12.9779453277588</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0365505218506</t>
+    <t xml:space="preserve">13.0365514755249</t>
   </si>
   <si>
     <t xml:space="preserve">13.3816738128662</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5640048980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4142332077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1732969284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0560865402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9258499145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8281745910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3295803070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7984275817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5444660186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8830795288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8309869766235</t>
+    <t xml:space="preserve">13.564003944397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4142322540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1732959747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0560855865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9258518218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8281755447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3295783996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7984266281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5444679260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8830823898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8309850692749</t>
   </si>
   <si>
     <t xml:space="preserve">13.9481973648071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8895893096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1240158081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4923725128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9388732910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9323616027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8672437667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9714326858521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9909706115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7760791778564</t>
+    <t xml:space="preserve">13.889594078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1240177154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.492374420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9388751983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9323625564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8672475814819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9714336395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9909687042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7760820388794</t>
   </si>
   <si>
     <t xml:space="preserve">12.7956161499023</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7304983139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7435216903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4691390991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2896223068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8887033462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5761375427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3612518310547</t>
+    <t xml:space="preserve">12.7304973602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7435207366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4691381454468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2896203994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8887014389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5761394500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3612489700317</t>
   </si>
   <si>
     <t xml:space="preserve">15.4784622192383</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0747318267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1854333877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8989143371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8793792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9575214385986</t>
+    <t xml:space="preserve">15.0747327804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1854343414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8989152908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8793811798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.95751953125</t>
   </si>
   <si>
     <t xml:space="preserve">14.9770555496216</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0031042098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7817039489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.586350440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7556562423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8598442077637</t>
+    <t xml:space="preserve">15.0031051635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.781702041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5863513946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.755654335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.859845161438</t>
   </si>
   <si>
     <t xml:space="preserve">15.3417158126831</t>
@@ -764,37 +764,37 @@
     <t xml:space="preserve">14.8403100967407</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2700834274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.530556678772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4133453369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3482284545898</t>
+    <t xml:space="preserve">15.2700843811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5305547714233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4133443832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3482265472412</t>
   </si>
   <si>
     <t xml:space="preserve">15.5631141662598</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5138320922852</t>
+    <t xml:space="preserve">16.5138301849365</t>
   </si>
   <si>
     <t xml:space="preserve">16.6570930480957</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5659294128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1231269836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0515003204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.680326461792</t>
+    <t xml:space="preserve">16.5659255981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1231307983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0514984130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6803255081177</t>
   </si>
   <si>
     <t xml:space="preserve">15.7454452514648</t>
@@ -809,16 +809,16 @@
     <t xml:space="preserve">15.3352031707764</t>
   </si>
   <si>
-    <t xml:space="preserve">15.23752784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4328804016113</t>
+    <t xml:space="preserve">15.2375259399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.43288230896</t>
   </si>
   <si>
     <t xml:space="preserve">16.2208042144775</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2924308776855</t>
+    <t xml:space="preserve">16.2924327850342</t>
   </si>
   <si>
     <t xml:space="preserve">16.1491737365723</t>
@@ -827,82 +827,82 @@
     <t xml:space="preserve">15.953821182251</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1752185821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8626537322998</t>
+    <t xml:space="preserve">16.175220489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8626556396484</t>
   </si>
   <si>
     <t xml:space="preserve">15.5566053390503</t>
   </si>
   <si>
-    <t xml:space="preserve">15.159384727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2245035171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8468227386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1658954620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4003200531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.309157371521</t>
+    <t xml:space="preserve">15.159387588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2245025634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8468198776245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1658973693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4003210067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3091564178467</t>
   </si>
   <si>
     <t xml:space="preserve">15.6021852493286</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6217193603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6738119125366</t>
+    <t xml:space="preserve">15.6217174530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6738138198853</t>
   </si>
   <si>
     <t xml:space="preserve">15.5500926971436</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3677587509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3938093185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1398487091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1072902679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0812435150146</t>
+    <t xml:space="preserve">15.3677635192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3938064575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1398506164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1072940826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0812454223633</t>
   </si>
   <si>
     <t xml:space="preserve">15.6152067184448</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6282339096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5435819625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7975397109985</t>
+    <t xml:space="preserve">15.6282320022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5435800552368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7975378036499</t>
   </si>
   <si>
     <t xml:space="preserve">15.9342851638794</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2012634277344</t>
+    <t xml:space="preserve">16.2012672424316</t>
   </si>
   <si>
     <t xml:space="preserve">16.4422035217285</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3770866394043</t>
+    <t xml:space="preserve">16.3770847320557</t>
   </si>
   <si>
     <t xml:space="preserve">16.2794094085693</t>
@@ -911,100 +911,100 @@
     <t xml:space="preserve">16.1426620483398</t>
   </si>
   <si>
-    <t xml:space="preserve">16.481273651123</t>
+    <t xml:space="preserve">16.4812755584717</t>
   </si>
   <si>
     <t xml:space="preserve">16.6049976348877</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2338275909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2561721801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.269193649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1584987640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.145471572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1845417022705</t>
+    <t xml:space="preserve">16.2338256835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2561779022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2691974639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1584968566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1454734802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1845455169678</t>
   </si>
   <si>
     <t xml:space="preserve">17.1389636993408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.646879196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6273441314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3892211914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1678218841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1027011871338</t>
+    <t xml:space="preserve">17.6468811035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6273422241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3892230987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1678199768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1027030944824</t>
   </si>
   <si>
     <t xml:space="preserve">18.3501510620117</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1352634429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.493408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0896778106689</t>
+    <t xml:space="preserve">18.1352615356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4934101104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0896797180176</t>
   </si>
   <si>
     <t xml:space="preserve">18.2264270782471</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8588104248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8723430633545</t>
+    <t xml:space="preserve">18.8588123321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8723449707031</t>
   </si>
   <si>
     <t xml:space="preserve">18.6896438598633</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6422748565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5137100219727</t>
+    <t xml:space="preserve">18.6422729492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5137062072754</t>
   </si>
   <si>
     <t xml:space="preserve">17.8370380401611</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6543369293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3836708068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9047050476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9317722320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5393047332764</t>
+    <t xml:space="preserve">17.6543388366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3836669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9047069549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9317760467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5393028259277</t>
   </si>
   <si>
     <t xml:space="preserve">17.5460681915283</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9926719665527</t>
+    <t xml:space="preserve">17.9926738739014</t>
   </si>
   <si>
     <t xml:space="preserve">18.6761093139648</t>
@@ -1016,52 +1016,52 @@
     <t xml:space="preserve">18.8046779632568</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9806098937988</t>
+    <t xml:space="preserve">18.9806118011475</t>
   </si>
   <si>
     <t xml:space="preserve">18.6219749450684</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0400409698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3377723693848</t>
+    <t xml:space="preserve">18.0400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3377742767334</t>
   </si>
   <si>
     <t xml:space="preserve">18.2092056274414</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9994373321533</t>
+    <t xml:space="preserve">17.999439239502</t>
   </si>
   <si>
     <t xml:space="preserve">17.8641033172607</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8032054901123</t>
+    <t xml:space="preserve">17.8032035827637</t>
   </si>
   <si>
     <t xml:space="preserve">18.0062065124512</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4054412841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.060338973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6340351104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2430381774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2701072692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6490440368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.452808380127</t>
+    <t xml:space="preserve">18.4054393768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0603408813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6340370178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2430419921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2701053619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6490421295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4528064727783</t>
   </si>
   <si>
     <t xml:space="preserve">18.7031745910645</t>
@@ -1076,10 +1076,10 @@
     <t xml:space="preserve">18.94677734375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9197082519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7776126861572</t>
+    <t xml:space="preserve">18.9197101593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.77760887146</t>
   </si>
   <si>
     <t xml:space="preserve">18.8791084289551</t>
@@ -1088,25 +1088,25 @@
     <t xml:space="preserve">19.1362476348877</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0415115356445</t>
+    <t xml:space="preserve">19.0415077209473</t>
   </si>
   <si>
     <t xml:space="preserve">19.1836128234863</t>
   </si>
   <si>
-    <t xml:space="preserve">19.373083114624</t>
+    <t xml:space="preserve">19.3730812072754</t>
   </si>
   <si>
     <t xml:space="preserve">19.2918796539307</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8264503479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9414844512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3001174926758</t>
+    <t xml:space="preserve">19.8264484405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9414806365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.300121307373</t>
   </si>
   <si>
     <t xml:space="preserve">20.5166530609131</t>
@@ -1115,13 +1115,13 @@
     <t xml:space="preserve">20.0971164703369</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9956150054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1241855621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1444873809814</t>
+    <t xml:space="preserve">19.9956169128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1241817474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1444835662842</t>
   </si>
   <si>
     <t xml:space="preserve">20.6384544372559</t>
@@ -1133,22 +1133,22 @@
     <t xml:space="preserve">19.894115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5625457763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7587833404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9211826324463</t>
+    <t xml:space="preserve">19.5625476837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7587814331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9211864471436</t>
   </si>
   <si>
     <t xml:space="preserve">19.9008827209473</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7993850708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7655487060547</t>
+    <t xml:space="preserve">19.7993831634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7655467987061</t>
   </si>
   <si>
     <t xml:space="preserve">19.812915802002</t>
@@ -1157,22 +1157,22 @@
     <t xml:space="preserve">19.4813461303711</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5828475952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4881134033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2851142883301</t>
+    <t xml:space="preserve">19.5828495025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4881153106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2851104736328</t>
   </si>
   <si>
     <t xml:space="preserve">18.7640762329102</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7573089599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5949115753174</t>
+    <t xml:space="preserve">18.7573108673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5949096679688</t>
   </si>
   <si>
     <t xml:space="preserve">18.8452777862549</t>
@@ -1181,22 +1181,22 @@
     <t xml:space="preserve">18.8655757904053</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5340061187744</t>
+    <t xml:space="preserve">18.534008026123</t>
   </si>
   <si>
     <t xml:space="preserve">19.0144443511963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2242107391357</t>
+    <t xml:space="preserve">19.2242126464844</t>
   </si>
   <si>
     <t xml:space="preserve">19.1700782775879</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2512798309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1971454620361</t>
+    <t xml:space="preserve">19.2512817382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1971492767334</t>
   </si>
   <si>
     <t xml:space="preserve">19.4475135803223</t>
@@ -1205,13 +1205,13 @@
     <t xml:space="preserve">19.1633148193359</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2648124694824</t>
+    <t xml:space="preserve">19.2648105621338</t>
   </si>
   <si>
     <t xml:space="preserve">19.4678153991699</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2580471038818</t>
+    <t xml:space="preserve">19.2580451965332</t>
   </si>
   <si>
     <t xml:space="preserve">19.8602848052979</t>
@@ -1226,16 +1226,16 @@
     <t xml:space="preserve">19.420446395874</t>
   </si>
   <si>
-    <t xml:space="preserve">19.569314956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.549015045166</t>
+    <t xml:space="preserve">19.5693130493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5490131378174</t>
   </si>
   <si>
     <t xml:space="preserve">19.4272136688232</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3663139343262</t>
+    <t xml:space="preserve">19.3663120269775</t>
   </si>
   <si>
     <t xml:space="preserve">19.4136810302734</t>
@@ -1247,91 +1247,91 @@
     <t xml:space="preserve">19.5016460418701</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9400119781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8114414215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8858757019043</t>
+    <t xml:space="preserve">18.9400100708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8114452362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8858776092529</t>
   </si>
   <si>
     <t xml:space="preserve">19.2783451080322</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1565456390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0685787200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2106761932373</t>
+    <t xml:space="preserve">19.1565437316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0685768127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2106800079346</t>
   </si>
   <si>
     <t xml:space="preserve">19.1091785430908</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3189449310303</t>
+    <t xml:space="preserve">19.3189487457275</t>
   </si>
   <si>
     <t xml:space="preserve">19.3324813842773</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2309761047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6572799682617</t>
+    <t xml:space="preserve">19.2309799194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6572818756104</t>
   </si>
   <si>
     <t xml:space="preserve">20.1106510162354</t>
   </si>
   <si>
-    <t xml:space="preserve">19.982084274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7858505249023</t>
+    <t xml:space="preserve">19.9820823669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7858486175537</t>
   </si>
   <si>
     <t xml:space="preserve">19.5354804992676</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9482479095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5760803222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6166801452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5557804107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3460159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6911163330078</t>
+    <t xml:space="preserve">19.9482498168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5760822296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.616678237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.555778503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3460140228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6911144256592</t>
   </si>
   <si>
     <t xml:space="preserve">19.6775817871094</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2986469268799</t>
+    <t xml:space="preserve">19.2986488342285</t>
   </si>
   <si>
     <t xml:space="preserve">19.1903800964355</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3121795654297</t>
+    <t xml:space="preserve">19.3121814727783</t>
   </si>
   <si>
     <t xml:space="preserve">18.7911434173584</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8182106018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.967077255249</t>
+    <t xml:space="preserve">18.818208694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9670810699463</t>
   </si>
   <si>
     <t xml:space="preserve">18.770845413208</t>
@@ -1340,31 +1340,31 @@
     <t xml:space="preserve">18.4663410186768</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1889057159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6084403991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1497764587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1768455505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4745826721191</t>
+    <t xml:space="preserve">18.188907623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6084423065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1497783660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1768436431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4745807647705</t>
   </si>
   <si>
     <t xml:space="preserve">20.0294494628906</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0835819244385</t>
+    <t xml:space="preserve">20.0835857391357</t>
   </si>
   <si>
     <t xml:space="preserve">20.5301876068115</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5031204223633</t>
+    <t xml:space="preserve">20.5031242370605</t>
   </si>
   <si>
     <t xml:space="preserve">20.8008556365967</t>
@@ -1373,13 +1373,13 @@
     <t xml:space="preserve">20.76025390625</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7196559906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8685188293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7061233520508</t>
+    <t xml:space="preserve">20.719654083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8685207366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7061214447021</t>
   </si>
   <si>
     <t xml:space="preserve">20.2459831237793</t>
@@ -1391,10 +1391,10 @@
     <t xml:space="preserve">20.3136539459229</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8805828094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8926410675049</t>
+    <t xml:space="preserve">19.8805809020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8926429748535</t>
   </si>
   <si>
     <t xml:space="preserve">19.055046081543</t>
@@ -1403,70 +1403,70 @@
     <t xml:space="preserve">18.0265045166016</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2024402618408</t>
+    <t xml:space="preserve">18.2024421691895</t>
   </si>
   <si>
     <t xml:space="preserve">18.2565727233887</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5813751220703</t>
+    <t xml:space="preserve">18.5813732147217</t>
   </si>
   <si>
     <t xml:space="preserve">18.5407752990723</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4866428375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4189739227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5272388458252</t>
+    <t xml:space="preserve">18.4866409301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4189758300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5272407531738</t>
   </si>
   <si>
     <t xml:space="preserve">18.473108291626</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9859066009521</t>
+    <t xml:space="preserve">17.9859027862549</t>
   </si>
   <si>
     <t xml:space="preserve">18.4460391998291</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6625747680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5678462982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7437763214111</t>
+    <t xml:space="preserve">18.6625785827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5678424835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7437782287598</t>
   </si>
   <si>
     <t xml:space="preserve">18.7302436828613</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3783740997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8505706787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7558364868164</t>
+    <t xml:space="preserve">18.3783721923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8505744934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.755838394165</t>
   </si>
   <si>
     <t xml:space="preserve">17.7287712097168</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9723701477051</t>
+    <t xml:space="preserve">17.9723720550537</t>
   </si>
   <si>
     <t xml:space="preserve">18.0671081542969</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1483058929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2159748077393</t>
+    <t xml:space="preserve">18.1483097076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2159729003906</t>
   </si>
   <si>
     <t xml:space="preserve">18.3242416381836</t>
@@ -1475,16 +1475,16 @@
     <t xml:space="preserve">18.3513069152832</t>
   </si>
   <si>
-    <t xml:space="preserve">18.364839553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7167072296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7979106903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9061794281006</t>
+    <t xml:space="preserve">18.3648414611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7167091369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.797908782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9061756134033</t>
   </si>
   <si>
     <t xml:space="preserve">18.1618385314941</t>
@@ -1493,22 +1493,22 @@
     <t xml:space="preserve">18.1212406158447</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8235015869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6205062866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6611022949219</t>
+    <t xml:space="preserve">17.8235034942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6205024719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6611042022705</t>
   </si>
   <si>
     <t xml:space="preserve">17.173900604248</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0521011352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7814292907715</t>
+    <t xml:space="preserve">17.0520992279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7814331054688</t>
   </si>
   <si>
     <t xml:space="preserve">16.7600536346436</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">16.8028087615967</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5605297088623</t>
+    <t xml:space="preserve">16.5605316162109</t>
   </si>
   <si>
     <t xml:space="preserve">16.7030467987061</t>
@@ -1526,169 +1526,169 @@
     <t xml:space="preserve">16.3039970397949</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2066125869751</t>
+    <t xml:space="preserve">15.2066173553467</t>
   </si>
   <si>
     <t xml:space="preserve">14.2802515029907</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8503198623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8218154907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5344009399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3206281661987</t>
+    <t xml:space="preserve">14.8503217697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.821816444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.53440284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3206262588501</t>
   </si>
   <si>
     <t xml:space="preserve">14.8930749893188</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4631443023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8336906433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3491325378418</t>
+    <t xml:space="preserve">15.4631462097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8336887359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3491315841675</t>
   </si>
   <si>
     <t xml:space="preserve">15.9477043151855</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8479433059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8621940612793</t>
+    <t xml:space="preserve">15.8479413986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8621921539307</t>
   </si>
   <si>
     <t xml:space="preserve">15.9192028045654</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7054252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7339277267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7196760177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3633823394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.505898475647</t>
+    <t xml:space="preserve">15.7054262161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7339267730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7196741104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3633832931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5058994293213</t>
   </si>
   <si>
     <t xml:space="preserve">15.420389175415</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4488916397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9500818252563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9358310699463</t>
+    <t xml:space="preserve">15.4488954544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9500827789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9358329772949</t>
   </si>
   <si>
     <t xml:space="preserve">15.1781101226807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5629062652588</t>
+    <t xml:space="preserve">15.5629100799561</t>
   </si>
   <si>
     <t xml:space="preserve">15.6484184265137</t>
   </si>
   <si>
-    <t xml:space="preserve">15.890697479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0189628601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.434642791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3776350021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4916486740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5201539993286</t>
+    <t xml:space="preserve">15.8906955718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0189647674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4346408843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3776340484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4916477203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5201501846313</t>
   </si>
   <si>
     <t xml:space="preserve">15.7909345626831</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7766819000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6056604385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4750213623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2469921112061</t>
+    <t xml:space="preserve">15.776683807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6056642532349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4750194549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2469882965088</t>
   </si>
   <si>
     <t xml:space="preserve">16.1329765319824</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4465160369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5035228729248</t>
+    <t xml:space="preserve">16.4465179443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5035209655762</t>
   </si>
   <si>
     <t xml:space="preserve">15.9619550704956</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0474643707275</t>
+    <t xml:space="preserve">16.0474681854248</t>
   </si>
   <si>
     <t xml:space="preserve">16.2184867858887</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2042350769043</t>
+    <t xml:space="preserve">16.2042369842529</t>
   </si>
   <si>
     <t xml:space="preserve">16.1614818572998</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7481803894043</t>
+    <t xml:space="preserve">15.7481784820557</t>
   </si>
   <si>
     <t xml:space="preserve">15.9049501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2754936218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4037609100342</t>
+    <t xml:space="preserve">16.2754955291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4037628173828</t>
   </si>
   <si>
     <t xml:space="preserve">16.3325004577637</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2636213302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.078351020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.30637550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2921237945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5486536026001</t>
+    <t xml:space="preserve">15.2636203765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0783472061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3063735961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.29212474823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5486555099487</t>
   </si>
   <si>
     <t xml:space="preserve">15.6769237518311</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">16.6175365447998</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7885570526123</t>
+    <t xml:space="preserve">16.7885551452637</t>
   </si>
   <si>
     <t xml:space="preserve">16.8598155975342</t>
@@ -1709,253 +1709,253 @@
     <t xml:space="preserve">17.3871307373047</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1020984649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.876446723938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6911745071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6626710891724</t>
+    <t xml:space="preserve">17.1020946502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8764448165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6911764144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.662672996521</t>
   </si>
   <si>
     <t xml:space="preserve">14.9643335342407</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7933101654053</t>
+    <t xml:space="preserve">14.7933120727539</t>
   </si>
   <si>
     <t xml:space="preserve">14.351508140564</t>
   </si>
   <si>
-    <t xml:space="preserve">14.216118812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3372573852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.722056388855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4227666854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0593461990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5391607284546</t>
+    <t xml:space="preserve">14.2161169052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3372583389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.722053527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4227676391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0593490600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.539158821106</t>
   </si>
   <si>
     <t xml:space="preserve">13.2042427062988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7268104553223</t>
+    <t xml:space="preserve">12.7268114089966</t>
   </si>
   <si>
     <t xml:space="preserve">12.3776435852051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4203977584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2850065231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4061450958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1353626251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3705177307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.904956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8622007369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9334583282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1472368240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.275502204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1187324523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0688505172729</t>
+    <t xml:space="preserve">12.4203958511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.285005569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4061441421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.135365486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3705167770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9049549102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8622016906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9334592819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1472358703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2755002975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1187334060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0688524246216</t>
   </si>
   <si>
     <t xml:space="preserve">13.5462846755981</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1116065979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7838172912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7339344024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6698026657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9192085266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9548377990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.246997833252</t>
+    <t xml:space="preserve">13.111608505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7838163375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7339363098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6698045730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.919207572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9548368453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2469987869263</t>
   </si>
   <si>
     <t xml:space="preserve">13.5961666107178</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1092281341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9453353881836</t>
+    <t xml:space="preserve">14.1092300415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9453344345093</t>
   </si>
   <si>
     <t xml:space="preserve">13.8812017440796</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8883256912231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.465521812439</t>
+    <t xml:space="preserve">13.8883266448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4655227661133</t>
   </si>
   <si>
     <t xml:space="preserve">14.2232427597046</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0878524780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3681383132935</t>
+    <t xml:space="preserve">14.087851524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3681411743164</t>
   </si>
   <si>
     <t xml:space="preserve">13.4679002761841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1258592605591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9690895080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4892778396606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6317958831787</t>
+    <t xml:space="preserve">13.1258602142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.969090461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4892797470093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6317949295044</t>
   </si>
   <si>
     <t xml:space="preserve">13.2327461242676</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3966426849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8265724182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5344133377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1044816970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9975938796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6104183197021</t>
+    <t xml:space="preserve">13.3966407775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8265733718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5344114303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1044807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9975919723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6104173660278</t>
   </si>
   <si>
     <t xml:space="preserve">13.7529354095459</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6389226913452</t>
+    <t xml:space="preserve">13.6389217376709</t>
   </si>
   <si>
     <t xml:space="preserve">14.1448583602905</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3230056762695</t>
+    <t xml:space="preserve">14.3230066299438</t>
   </si>
   <si>
     <t xml:space="preserve">14.2018661499023</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1947393417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8954544067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3942651748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.593789100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7078008651733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5082807540894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6935482025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8075675964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6365432739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7648096084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7363052368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6792984008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2660007476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5367841720581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2945022583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5510339736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1923608779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9785861968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2778730392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2493696212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2208671569824</t>
+    <t xml:space="preserve">14.1947412490845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8954515457153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.39426612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5937881469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7078037261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5082788467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6935520172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8075656890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6365451812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7648086547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7363080978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6792974472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2659978866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5367822647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2945013046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5510330200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.192364692688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9785852432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.277871131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2493705749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2208662033081</t>
   </si>
   <si>
     <t xml:space="preserve">15.4061393737793</t>
@@ -1964,19 +1964,19 @@
     <t xml:space="preserve">15.8194398880005</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8051872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6341676712036</t>
+    <t xml:space="preserve">15.8051891326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.634165763855</t>
   </si>
   <si>
     <t xml:space="preserve">15.5914096832275</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4322662353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6032848358154</t>
+    <t xml:space="preserve">16.4322681427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6032829284668</t>
   </si>
   <si>
     <t xml:space="preserve">16.7172985076904</t>
@@ -1985,10 +1985,10 @@
     <t xml:space="preserve">16.7743072509766</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8170585632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0308380126953</t>
+    <t xml:space="preserve">16.8170623779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0308361053467</t>
   </si>
   <si>
     <t xml:space="preserve">17.1591033935547</t>
@@ -2000,16 +2000,16 @@
     <t xml:space="preserve">17.3158721923828</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4583892822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4726409912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9714508056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7861766815186</t>
+    <t xml:space="preserve">17.4583873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4726448059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9714488983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7861804962158</t>
   </si>
   <si>
     <t xml:space="preserve">17.9286994934082</t>
@@ -2018,31 +2018,31 @@
     <t xml:space="preserve">18.0569629669189</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0854644775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5581512451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5866546630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2018604278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4298839569092</t>
+    <t xml:space="preserve">18.0854663848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5581493377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5866565704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2018566131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4298877716064</t>
   </si>
   <si>
     <t xml:space="preserve">17.5296478271484</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4868907928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7196502685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8548011779785</t>
+    <t xml:space="preserve">17.4868927001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7196521759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8548030853271</t>
   </si>
   <si>
     <t xml:space="preserve">17.2991847991943</t>
@@ -2051,13 +2051,13 @@
     <t xml:space="preserve">17.2241020202637</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2691535949707</t>
+    <t xml:space="preserve">17.2691555023193</t>
   </si>
   <si>
     <t xml:space="preserve">17.1490173339844</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7435684204102</t>
+    <t xml:space="preserve">16.7435665130615</t>
   </si>
   <si>
     <t xml:space="preserve">16.878719329834</t>
@@ -2066,28 +2066,28 @@
     <t xml:space="preserve">16.9237689971924</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6985206604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2541332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5394515991211</t>
+    <t xml:space="preserve">16.6985168457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2541370391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5394535064697</t>
   </si>
   <si>
     <t xml:space="preserve">17.1640357971191</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0589179992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4343338012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8247661590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9298839569092</t>
+    <t xml:space="preserve">17.0589160919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4343357086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8247680664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9298820495605</t>
   </si>
   <si>
     <t xml:space="preserve">17.8397846221924</t>
@@ -2096,10 +2096,10 @@
     <t xml:space="preserve">17.749683380127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9449024200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6657009124756</t>
+    <t xml:space="preserve">17.9449005126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.665699005127</t>
   </si>
   <si>
     <t xml:space="preserve">18.8458995819092</t>
@@ -2114,25 +2114,25 @@
     <t xml:space="preserve">19.056131362915</t>
   </si>
   <si>
-    <t xml:space="preserve">19.131217956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4165344238281</t>
+    <t xml:space="preserve">19.1312160491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4165325164795</t>
   </si>
   <si>
     <t xml:space="preserve">19.1462345123291</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0110836029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2213134765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7318859100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7769317626953</t>
+    <t xml:space="preserve">19.0110816955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2213153839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7318840026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7769336700439</t>
   </si>
   <si>
     <t xml:space="preserve">19.7919502258301</t>
@@ -2141,19 +2141,19 @@
     <t xml:space="preserve">19.8069648742676</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0772647857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9721488952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2574672698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1373310089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1823787689209</t>
+    <t xml:space="preserve">20.0772666931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9721508026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2574653625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1373329162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1823844909668</t>
   </si>
   <si>
     <t xml:space="preserve">19.897066116333</t>
@@ -2162,13 +2162,13 @@
     <t xml:space="preserve">20.047233581543</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1523494720459</t>
+    <t xml:space="preserve">20.1523475646973</t>
   </si>
   <si>
     <t xml:space="preserve">20.0172004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6567993164062</t>
+    <t xml:space="preserve">19.6568012237549</t>
   </si>
   <si>
     <t xml:space="preserve">19.8219814300537</t>
@@ -2177,13 +2177,13 @@
     <t xml:space="preserve">19.6868343353271</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8369998931885</t>
+    <t xml:space="preserve">19.8369979858398</t>
   </si>
   <si>
     <t xml:space="preserve">19.9421157836914</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3325519561768</t>
+    <t xml:space="preserve">20.3325500488281</t>
   </si>
   <si>
     <t xml:space="preserve">19.5817165374756</t>
@@ -2192,64 +2192,64 @@
     <t xml:space="preserve">19.4916152954102</t>
   </si>
   <si>
-    <t xml:space="preserve">19.671817779541</t>
+    <t xml:space="preserve">19.6718158721924</t>
   </si>
   <si>
     <t xml:space="preserve">19.7168655395508</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7619152069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2874965667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9120807647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.122314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0622482299805</t>
+    <t xml:space="preserve">19.7619171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2874984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9120826721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1223125457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0622463226318</t>
   </si>
   <si>
     <t xml:space="preserve">20.3025169372559</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5728149414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.662914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.993278503418</t>
+    <t xml:space="preserve">20.5728130340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6629161834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9932823181152</t>
   </si>
   <si>
     <t xml:space="preserve">21.1434478759766</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1584644317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3536834716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0082988739014</t>
+    <t xml:space="preserve">21.1584663391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3536815643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.00830078125</t>
   </si>
   <si>
     <t xml:space="preserve">21.2635822296143</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2936172485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4287624359131</t>
+    <t xml:space="preserve">21.2936153411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4287643432617</t>
   </si>
   <si>
     <t xml:space="preserve">21.6089649200439</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5338764190674</t>
+    <t xml:space="preserve">21.5338802337646</t>
   </si>
   <si>
     <t xml:space="preserve">20.9782657623291</t>
@@ -2261,16 +2261,16 @@
     <t xml:space="preserve">21.233549118042</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2485599517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1734848022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6478977203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6328830718994</t>
+    <t xml:space="preserve">21.2485637664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1734828948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6478996276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6328811645508</t>
   </si>
   <si>
     <t xml:space="preserve">20.768030166626</t>
@@ -2279,34 +2279,34 @@
     <t xml:space="preserve">21.083381652832</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7980651855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8670310974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7229804992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2035160064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.308629989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4888343811035</t>
+    <t xml:space="preserve">20.7980670928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8670330047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7229785919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2035140991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3086338043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4888324737549</t>
   </si>
   <si>
     <t xml:space="preserve">21.5639133453369</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1134185791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.383716583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3236465454102</t>
+    <t xml:space="preserve">21.1134166717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3837146759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3236484527588</t>
   </si>
   <si>
     <t xml:space="preserve">21.5789318084717</t>
@@ -2324,25 +2324,25 @@
     <t xml:space="preserve">22.5850467681885</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4799308776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6601276397705</t>
+    <t xml:space="preserve">22.4799327850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6601295471191</t>
   </si>
   <si>
     <t xml:space="preserve">23.1256446838379</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3208618164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0805950164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2007293701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3058471679688</t>
+    <t xml:space="preserve">23.3208637237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0805969238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2007331848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3058490753174</t>
   </si>
   <si>
     <t xml:space="preserve">23.4259815216064</t>
@@ -2351,19 +2351,19 @@
     <t xml:space="preserve">23.6962795257568</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9215297698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7263107299805</t>
+    <t xml:space="preserve">23.9215316772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7263145446777</t>
   </si>
   <si>
     <t xml:space="preserve">23.6662464141846</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9065093994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2908267974854</t>
+    <t xml:space="preserve">23.9065113067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.290828704834</t>
   </si>
   <si>
     <t xml:space="preserve">23.3959465026855</t>
@@ -2375,10 +2375,10 @@
     <t xml:space="preserve">23.0956153869629</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4949436187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6300964355469</t>
+    <t xml:space="preserve">22.494945526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6300945281982</t>
   </si>
   <si>
     <t xml:space="preserve">22.5249805450439</t>
@@ -2396,58 +2396,58 @@
     <t xml:space="preserve">22.6000633239746</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6451168060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7352161407471</t>
+    <t xml:space="preserve">22.645112991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7352104187012</t>
   </si>
   <si>
     <t xml:space="preserve">22.2096309661865</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1946125030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.104513168335</t>
+    <t xml:space="preserve">22.1946182250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1045150756836</t>
   </si>
   <si>
     <t xml:space="preserve">22.1795978546143</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7290992736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0594635009766</t>
+    <t xml:space="preserve">21.7290954589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0594615936279</t>
   </si>
   <si>
     <t xml:space="preserve">21.7441139221191</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5939464569092</t>
+    <t xml:space="preserve">21.5939483642578</t>
   </si>
   <si>
     <t xml:space="preserve">21.2785987854004</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0294342041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7652454376221</t>
+    <t xml:space="preserve">22.0294303894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7652473449707</t>
   </si>
   <si>
     <t xml:space="preserve">22.7051811218262</t>
   </si>
   <si>
-    <t xml:space="preserve">22.99049949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9754810333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8102970123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8253154754639</t>
+    <t xml:space="preserve">22.9904975891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9754791259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8102989196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8253135681152</t>
   </si>
   <si>
     <t xml:space="preserve">22.0744819641113</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">22.8853797912598</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1645793914795</t>
+    <t xml:space="preserve">22.1645812988281</t>
   </si>
   <si>
     <t xml:space="preserve">22.299732208252</t>
@@ -2465,19 +2465,19 @@
     <t xml:space="preserve">22.8553466796875</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7952823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3508949279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1017265319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.447114944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4170780181885</t>
+    <t xml:space="preserve">22.795280456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3508968353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1017284393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4471111297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4170818328857</t>
   </si>
   <si>
     <t xml:space="preserve">24.67236328125</t>
@@ -2486,49 +2486,49 @@
     <t xml:space="preserve">24.6573448181152</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7774791717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3269824981689</t>
+    <t xml:space="preserve">24.7774772644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3269805908203</t>
   </si>
   <si>
     <t xml:space="preserve">23.8764781951904</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2396659851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9181995391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4226512908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4827156066895</t>
+    <t xml:space="preserve">22.2396640777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9181976318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4226474761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4827175140381</t>
   </si>
   <si>
     <t xml:space="preserve">19.0411167144775</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5906143188477</t>
+    <t xml:space="preserve">18.5906181335449</t>
   </si>
   <si>
     <t xml:space="preserve">16.9688186645508</t>
   </si>
   <si>
-    <t xml:space="preserve">15.887622833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7975206375122</t>
+    <t xml:space="preserve">15.8876171112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7975196838379</t>
   </si>
   <si>
     <t xml:space="preserve">13.6201047897339</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6937971115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2146558761597</t>
+    <t xml:space="preserve">14.693793296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2146549224854</t>
   </si>
   <si>
     <t xml:space="preserve">12.9894046783447</t>
@@ -2537,10 +2537,10 @@
     <t xml:space="preserve">12.6590385437012</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0344572067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7266139984131</t>
+    <t xml:space="preserve">13.0344562530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7266130447388</t>
   </si>
   <si>
     <t xml:space="preserve">12.8917970657349</t>
@@ -2549,40 +2549,40 @@
     <t xml:space="preserve">13.905421257019</t>
   </si>
   <si>
-    <t xml:space="preserve">14.018045425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5811700820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0781135559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3559226989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1982469558716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3183784484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0555849075317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7688798904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.46715259552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7886219024658</t>
+    <t xml:space="preserve">14.0180463790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5811710357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0781106948853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.355920791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1982460021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3183794021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0555858612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7688808441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4671545028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7886180877686</t>
   </si>
   <si>
     <t xml:space="preserve">15.7074213027954</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9026374816895</t>
+    <t xml:space="preserve">15.9026355743408</t>
   </si>
   <si>
     <t xml:space="preserve">15.9326696395874</t>
@@ -2597,40 +2597,40 @@
     <t xml:space="preserve">15.3770532608032</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4821672439575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6835021972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8937339782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3442344665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0138664245605</t>
+    <t xml:space="preserve">15.4821691513062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6834983825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8937320709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3442363739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0138702392578</t>
   </si>
   <si>
     <t xml:space="preserve">16.5333366394043</t>
   </si>
   <si>
-    <t xml:space="preserve">16.503303527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.908748626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4643669128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1039695739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5244331359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1189842224121</t>
+    <t xml:space="preserve">16.5032997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9087524414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4643688201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.103967666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.524435043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1189823150635</t>
   </si>
   <si>
     <t xml:space="preserve">17.2391185760498</t>
@@ -2642,19 +2642,19 @@
     <t xml:space="preserve">17.3892860412598</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4043025970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6896171569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.365364074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2902870178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4855003356934</t>
+    <t xml:space="preserve">17.4043006896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6896152496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3653659820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2902851104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4855041503906</t>
   </si>
   <si>
     <t xml:space="preserve">18.9510154724121</t>
@@ -2666,49 +2666,49 @@
     <t xml:space="preserve">19.8520164489746</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3414478302002</t>
+    <t xml:space="preserve">19.3414497375488</t>
   </si>
   <si>
     <t xml:space="preserve">19.5516834259033</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3954010009766</t>
+    <t xml:space="preserve">18.3953990936279</t>
   </si>
   <si>
     <t xml:space="preserve">19.4315490722656</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1673679351807</t>
+    <t xml:space="preserve">20.167366027832</t>
   </si>
   <si>
     <t xml:space="preserve">19.3264312744141</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9571323394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1072998046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6779308319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2663669586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5066318511963</t>
+    <t xml:space="preserve">19.9571304321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1072978973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6779327392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2663650512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5066299438477</t>
   </si>
   <si>
     <t xml:space="preserve">19.8820514678955</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0922813415527</t>
+    <t xml:space="preserve">20.0922832489014</t>
   </si>
   <si>
     <t xml:space="preserve">20.3475646972656</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3775978088379</t>
+    <t xml:space="preserve">20.3775997161865</t>
   </si>
   <si>
     <t xml:space="preserve">19.5967330932617</t>
@@ -2717,43 +2717,43 @@
     <t xml:space="preserve">18.7107486724854</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9209861755371</t>
+    <t xml:space="preserve">18.9209842681885</t>
   </si>
   <si>
     <t xml:space="preserve">18.7708168029785</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8308868408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5666980743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0861682891846</t>
+    <t xml:space="preserve">18.8308849334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5666961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0861701965332</t>
   </si>
   <si>
     <t xml:space="preserve">18.9059658050537</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0711517333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7558002471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.476598739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2964000701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5366668701172</t>
+    <t xml:space="preserve">19.0711498260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7557983398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4766006469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2964019775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5366649627686</t>
   </si>
   <si>
     <t xml:space="preserve">19.5216484069824</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3114147186279</t>
+    <t xml:space="preserve">19.3114166259766</t>
   </si>
   <si>
     <t xml:space="preserve">18.9810523986816</t>
@@ -2762,10 +2762,10 @@
     <t xml:space="preserve">20.4526805877686</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6178646087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6117496490479</t>
+    <t xml:space="preserve">20.617862701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6117477416992</t>
   </si>
   <si>
     <t xml:space="preserve">20.3625831604004</t>
@@ -2774,22 +2774,22 @@
     <t xml:space="preserve">19.6417846679688</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0322170257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5127487182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2424468994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7379989624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0021800994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.215202331543</t>
+    <t xml:space="preserve">20.0322189331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5127449035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2424488067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7379951477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0021820068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2151985168457</t>
   </si>
   <si>
     <t xml:space="preserve">18.140115737915</t>
@@ -2801,22 +2801,22 @@
     <t xml:space="preserve">20.5577983856201</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4376659393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1284332275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7830505371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4977340698242</t>
+    <t xml:space="preserve">20.4376640319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1284313201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7830486297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4977321624756</t>
   </si>
   <si>
     <t xml:space="preserve">21.0233135223389</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4137477874756</t>
+    <t xml:space="preserve">21.4137496948242</t>
   </si>
   <si>
     <t xml:space="preserve">21.3686962127686</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">20.9031829833984</t>
   </si>
   <si>
-    <t xml:space="preserve">21.038330078125</t>
+    <t xml:space="preserve">21.0383319854736</t>
   </si>
   <si>
     <t xml:space="preserve">20.4076328277588</t>
@@ -2834,25 +2834,25 @@
     <t xml:space="preserve">20.5427837371826</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3175354003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2124176025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4465675354004</t>
+    <t xml:space="preserve">20.3175315856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2124137878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4465656280518</t>
   </si>
   <si>
     <t xml:space="preserve">19.7469005584717</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2363319396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5277652740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7140789031982</t>
+    <t xml:space="preserve">19.2363338470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5277633666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7140808105469</t>
   </si>
   <si>
     <t xml:space="preserve">21.684045791626</t>
@@ -2864,34 +2864,34 @@
     <t xml:space="preserve">21.3386631011963</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6239776611328</t>
+    <t xml:space="preserve">21.6239814758301</t>
   </si>
   <si>
     <t xml:space="preserve">21.8642482757568</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3987331390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4437808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.188497543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9092960357666</t>
+    <t xml:space="preserve">21.3987312316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4437789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1884994506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9092998504639</t>
   </si>
   <si>
     <t xml:space="preserve">21.8942813873291</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8342151641846</t>
+    <t xml:space="preserve">21.8342132568359</t>
   </si>
   <si>
     <t xml:space="preserve">21.5038471221924</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2546806335449</t>
+    <t xml:space="preserve">22.2546825408936</t>
   </si>
   <si>
     <t xml:space="preserve">22.0444488525391</t>
@@ -2900,76 +2900,76 @@
     <t xml:space="preserve">22.2847118377686</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3447799682617</t>
+    <t xml:space="preserve">22.3447818756104</t>
   </si>
   <si>
     <t xml:space="preserve">22.4649143218994</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6901626586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.870361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.615083694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5700283050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6751480102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5775375366211</t>
+    <t xml:space="preserve">22.69016456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8703651428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6150817871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5700302124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6751461029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5775356292725</t>
   </si>
   <si>
     <t xml:space="preserve">22.9079055786133</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0430564880371</t>
+    <t xml:space="preserve">23.0430526733398</t>
   </si>
   <si>
     <t xml:space="preserve">23.0881042480469</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8178024291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8403301239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1706962585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.215747833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3809299468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.523588180542</t>
+    <t xml:space="preserve">22.8178043365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8403282165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1706943511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2157459259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.380931854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5235862731934</t>
   </si>
   <si>
     <t xml:space="preserve">23.0505638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">22.915412902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0730876922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.253288269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3433856964111</t>
+    <t xml:space="preserve">22.9154148101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0730895996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2532863616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3433876037598</t>
   </si>
   <si>
     <t xml:space="preserve">23.2983379364014</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8914966583252</t>
+    <t xml:space="preserve">23.8914947509766</t>
   </si>
   <si>
     <t xml:space="preserve">24.2594051361084</t>
@@ -2981,28 +2981,28 @@
     <t xml:space="preserve">24.664852142334</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5522308349609</t>
+    <t xml:space="preserve">24.5522289276123</t>
   </si>
   <si>
     <t xml:space="preserve">24.4621295928955</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7924938201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.402063369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0491676330566</t>
+    <t xml:space="preserve">24.7924957275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4020652770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0491695404053</t>
   </si>
   <si>
     <t xml:space="preserve">24.4696369171143</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4245853424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1993350982666</t>
+    <t xml:space="preserve">24.4245872497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1993370056152</t>
   </si>
   <si>
     <t xml:space="preserve">23.9590702056885</t>
@@ -3011,16 +3011,16 @@
     <t xml:space="preserve">24.1617965698242</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2293682098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.627311706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8075103759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8150215148926</t>
+    <t xml:space="preserve">24.2293720245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6273136138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8075141906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8150196075439</t>
   </si>
   <si>
     <t xml:space="preserve">25.1078433990479</t>
@@ -3035,19 +3035,19 @@
     <t xml:space="preserve">25.1829299926758</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2955551147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5208072662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.828649520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8061180114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7385425567627</t>
+    <t xml:space="preserve">25.2955532073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5208053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8286457061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.806116104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.73854637146</t>
   </si>
   <si>
     <t xml:space="preserve">25.7835941314697</t>
@@ -3056,109 +3056,109 @@
     <t xml:space="preserve">26.0538921356201</t>
   </si>
   <si>
-    <t xml:space="preserve">25.866189956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.489372253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5119018554688</t>
+    <t xml:space="preserve">25.8661861419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4893741607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5119037628174</t>
   </si>
   <si>
     <t xml:space="preserve">26.3767528533936</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4668560028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.65456199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5869884490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1050586700439</t>
+    <t xml:space="preserve">26.466854095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6545600891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.586986541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1050567626953</t>
   </si>
   <si>
     <t xml:space="preserve">27.5180168151855</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1350879669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3903789520264</t>
+    <t xml:space="preserve">27.1350936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3903713226318</t>
   </si>
   <si>
     <t xml:space="preserve">27.0149593353271</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0374851226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2176856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1951599121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2251930236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2566184997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6845932006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1726341247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0299777984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7446575164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6245288848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8962211608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.016357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3992748260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.35422706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5569477081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0013313293457</t>
+    <t xml:space="preserve">27.0374813079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2176837921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1951580047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2251892089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2566165924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.684591293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1726322174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0299797058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7446594238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6245269775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.89621925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0163536071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3992767333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3542251586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5569515228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0013370513916</t>
   </si>
   <si>
     <t xml:space="preserve">26.0238609313965</t>
   </si>
   <si>
-    <t xml:space="preserve">26.421802520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2866497039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2115707397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8873157501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1125659942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3603401184082</t>
+    <t xml:space="preserve">26.4218006134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2866477966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2115669250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8873176574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1125679016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3603420257568</t>
   </si>
   <si>
     <t xml:space="preserve">27.382869720459</t>
@@ -3167,46 +3167,46 @@
     <t xml:space="preserve">27.645658493042</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6231327056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7808132171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5930995941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4204082489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5630645751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7883129119873</t>
+    <t xml:space="preserve">27.6231346130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7808074951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5931034088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4204120635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5630683898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7883186340332</t>
   </si>
   <si>
     <t xml:space="preserve">27.7132339477539</t>
   </si>
   <si>
-    <t xml:space="preserve">27.953498840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9835376739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2613391876221</t>
+    <t xml:space="preserve">27.9535026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9835357666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.261344909668</t>
   </si>
   <si>
     <t xml:space="preserve">28.1412124633789</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2087821960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1862621307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3814735412598</t>
+    <t xml:space="preserve">28.2087860107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1862659454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3814716339111</t>
   </si>
   <si>
     <t xml:space="preserve">28.2012767791748</t>
@@ -3215,19 +3215,19 @@
     <t xml:space="preserve">28.0586166381836</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1186828613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4115085601807</t>
+    <t xml:space="preserve">28.1186847686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4115047454834</t>
   </si>
   <si>
     <t xml:space="preserve">29.169849395752</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3875942230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5077247619629</t>
+    <t xml:space="preserve">29.3875865936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5077228546143</t>
   </si>
   <si>
     <t xml:space="preserve">29.2899799346924</t>
@@ -3236,49 +3236,49 @@
     <t xml:space="preserve">28.9145622253418</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4190101623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.64426612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1923770904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1323051452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2148971557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5842018127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4865875244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4565582275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5466575622559</t>
+    <t xml:space="preserve">28.419017791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6442699432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1923732757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1323089599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.214900970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5841999053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4865913391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4565544128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5466594696045</t>
   </si>
   <si>
     <t xml:space="preserve">28.4640655517578</t>
   </si>
   <si>
-    <t xml:space="preserve">27.87841796875</t>
+    <t xml:space="preserve">27.8784217834473</t>
   </si>
   <si>
     <t xml:space="preserve">28.4715728759766</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4040031433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0736312866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3964939117432</t>
+    <t xml:space="preserve">28.4039993286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0736331939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3964920043945</t>
   </si>
   <si>
     <t xml:space="preserve">28.0285873413086</t>
@@ -3287,40 +3287,40 @@
     <t xml:space="preserve">28.7643985748291</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6954345703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7179584503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9432144165039</t>
+    <t xml:space="preserve">29.6954288482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7179565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9432106018066</t>
   </si>
   <si>
     <t xml:space="preserve">30.401216506958</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7240734100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5213489532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6940441131592</t>
+    <t xml:space="preserve">30.7240753173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5213508605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6940383911133</t>
   </si>
   <si>
     <t xml:space="preserve">30.5288543701172</t>
   </si>
   <si>
-    <t xml:space="preserve">30.709056854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4988212585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7766342163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7602195739746</t>
+    <t xml:space="preserve">30.7090587615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4988193511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7766304016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7602233886719</t>
   </si>
   <si>
     <t xml:space="preserve">32.2107238769531</t>
@@ -3329,28 +3329,28 @@
     <t xml:space="preserve">32.4359703063965</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7376937866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1506500244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3083229064941</t>
+    <t xml:space="preserve">31.7377033233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1506538391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3083305358887</t>
   </si>
   <si>
     <t xml:space="preserve">32.345874786377</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8728485107422</t>
+    <t xml:space="preserve">31.8728446960449</t>
   </si>
   <si>
     <t xml:space="preserve">31.1370315551758</t>
   </si>
   <si>
-    <t xml:space="preserve">30.859224319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0544376373291</t>
+    <t xml:space="preserve">30.8592185974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0544414520264</t>
   </si>
   <si>
     <t xml:space="preserve">31.4641036987305</t>
@@ -3359,22 +3359,22 @@
     <t xml:space="preserve">30.2592010498047</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0342807769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6406841278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8052825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1265888214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.08642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0583801269531</t>
+    <t xml:space="preserve">30.0342845916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.640682220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8052806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1265850067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0864238739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0583839416504</t>
   </si>
   <si>
     <t xml:space="preserve">29.937894821167</t>
@@ -3383,13 +3383,13 @@
     <t xml:space="preserve">30.1146125793457</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5885448455811</t>
+    <t xml:space="preserve">30.5885429382324</t>
   </si>
   <si>
     <t xml:space="preserve">31.3596820831299</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3195171356201</t>
+    <t xml:space="preserve">31.3195209503174</t>
   </si>
   <si>
     <t xml:space="preserve">31.0303401947021</t>
@@ -3401,10 +3401,10 @@
     <t xml:space="preserve">31.3355808258057</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2632865905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1668949127197</t>
+    <t xml:space="preserve">31.2632827758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.166898727417</t>
   </si>
   <si>
     <t xml:space="preserve">31.1187000274658</t>
@@ -3416,148 +3416,148 @@
     <t xml:space="preserve">29.7531414031982</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4118232727051</t>
+    <t xml:space="preserve">30.4118194580078</t>
   </si>
   <si>
     <t xml:space="preserve">30.5644454956055</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5483779907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9419841766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2713260650635</t>
+    <t xml:space="preserve">30.548376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9419803619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2713184356689</t>
   </si>
   <si>
     <t xml:space="preserve">31.1829624176025</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1267337799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2150917053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2311611175537</t>
+    <t xml:space="preserve">31.12672996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2150955200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2311573028564</t>
   </si>
   <si>
     <t xml:space="preserve">31.1909999847412</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4359188079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2029724121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1788730621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.837553024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8616504669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5082168579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.347562789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2913341522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4800281524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.885612487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3996982574463</t>
+    <t xml:space="preserve">30.435920715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2029762268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1788768768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8375549316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8616561889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5082130432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3475570678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2913265228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4800300598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8856086730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3997001647949</t>
   </si>
   <si>
     <t xml:space="preserve">28.9338073730469</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7208652496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1907024383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6807022094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9939765930176</t>
+    <t xml:space="preserve">27.7208671569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1907081604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6806983947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9939746856689</t>
   </si>
   <si>
     <t xml:space="preserve">28.0743026733398</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5803661346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.965934753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0783977508545</t>
+    <t xml:space="preserve">28.5803623199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9659404754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0783920288086</t>
   </si>
   <si>
     <t xml:space="preserve">28.8695430755615</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8374118804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8133106231689</t>
+    <t xml:space="preserve">28.8374176025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8133144378662</t>
   </si>
   <si>
     <t xml:space="preserve">28.6285610198975</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3595390319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0944595336914</t>
+    <t xml:space="preserve">29.3595371246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0944576263428</t>
   </si>
   <si>
     <t xml:space="preserve">28.9579029083252</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3152885437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1587162017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3675708770752</t>
+    <t xml:space="preserve">28.3152866363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1587200164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3675746917725</t>
   </si>
   <si>
     <t xml:space="preserve">28.8936424255371</t>
   </si>
   <si>
-    <t xml:space="preserve">28.802698135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2799015045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4105987548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9600028991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9974231719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9810848236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9028224945068</t>
+    <t xml:space="preserve">28.8026943206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2799034118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4106006622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9600048065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9974212646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9810829162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9028244018555</t>
   </si>
   <si>
     <t xml:space="preserve">25.9273281097412</t>
@@ -3566,13 +3566,13 @@
     <t xml:space="preserve">25.3228492736816</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3623676300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8885860443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5175743103027</t>
+    <t xml:space="preserve">23.3623714447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8885879516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5175762176514</t>
   </si>
   <si>
     <t xml:space="preserve">25.3963642120361</t>
@@ -3581,13 +3581,13 @@
     <t xml:space="preserve">24.7101974487305</t>
   </si>
   <si>
-    <t xml:space="preserve">25.306510925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.723108291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.821138381958</t>
+    <t xml:space="preserve">25.3065090179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7231101989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8211364746094</t>
   </si>
   <si>
     <t xml:space="preserve">27.1281204223633</t>
@@ -3596,19 +3596,19 @@
     <t xml:space="preserve">26.956579208374</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1444568634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7768707275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1036186218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0709381103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9892539978027</t>
+    <t xml:space="preserve">27.1444606781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7768688201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1036148071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0709419250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9892578125</t>
   </si>
   <si>
     <t xml:space="preserve">27.0300979614258</t>
@@ -3617,25 +3617,25 @@
     <t xml:space="preserve">27.3486747741699</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1328678131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9041442871094</t>
+    <t xml:space="preserve">28.1328639984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9041481018066</t>
   </si>
   <si>
     <t xml:space="preserve">27.5447235107422</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9776592254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5937347412109</t>
+    <t xml:space="preserve">27.9776630401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5937328338623</t>
   </si>
   <si>
     <t xml:space="preserve">26.5481491088867</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7523632049561</t>
+    <t xml:space="preserve">26.7523612976074</t>
   </si>
   <si>
     <t xml:space="preserve">26.8830604553223</t>
@@ -3644,22 +3644,22 @@
     <t xml:space="preserve">26.8667259216309</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5399799346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4991359710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3439311981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6414241790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.237735748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3520984649658</t>
+    <t xml:space="preserve">26.539981842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4991340637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3439292907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6414260864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2377376556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3520965576172</t>
   </si>
   <si>
     <t xml:space="preserve">26.1152076721191</t>
@@ -3674,10 +3674,10 @@
     <t xml:space="preserve">25.3310146331787</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2738361358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6741008758545</t>
+    <t xml:space="preserve">25.2738380432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6740970611572</t>
   </si>
   <si>
     <t xml:space="preserve">25.8047981262207</t>
@@ -3692,73 +3692,73 @@
     <t xml:space="preserve">23.9913558959961</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3017635345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8374729156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3766040802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4256153106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5154705047607</t>
+    <t xml:space="preserve">24.3017654418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8374710083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3766059875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4256172180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5154724121094</t>
   </si>
   <si>
     <t xml:space="preserve">26.4419536590576</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6380023956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5073051452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5489616394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7698383331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4734287261963</t>
+    <t xml:space="preserve">26.6380004882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.507303237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5489635467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7698364257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4734306335449</t>
   </si>
   <si>
     <t xml:space="preserve">27.5743713378906</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6759967803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9639339447021</t>
+    <t xml:space="preserve">27.6759986877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9639358520508</t>
   </si>
   <si>
     <t xml:space="preserve">27.5828399658203</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3457126617432</t>
+    <t xml:space="preserve">27.3457145690918</t>
   </si>
   <si>
     <t xml:space="preserve">27.5235595703125</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7274913787842</t>
+    <t xml:space="preserve">26.7274932861328</t>
   </si>
   <si>
     <t xml:space="preserve">27.5320262908936</t>
   </si>
   <si>
-    <t xml:space="preserve">26.956148147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2108974456787</t>
+    <t xml:space="preserve">26.9561500549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2108955383301</t>
   </si>
   <si>
     <t xml:space="preserve">25.5164546966553</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3992576599121</t>
+    <t xml:space="preserve">23.3992557525635</t>
   </si>
   <si>
     <t xml:space="preserve">22.8149127960205</t>
@@ -3770,37 +3770,37 @@
     <t xml:space="preserve">23.9751358032227</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9250049591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4161949157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5686321258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3569145202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0859127044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8904457092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6194458007812</t>
+    <t xml:space="preserve">22.9250087738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4161930084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5686340332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3569164276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0859146118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8904476165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6194477081299</t>
   </si>
   <si>
     <t xml:space="preserve">23.5093536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3230419158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8318481445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.747163772583</t>
+    <t xml:space="preserve">23.3230381011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8318500518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7471618652344</t>
   </si>
   <si>
     <t xml:space="preserve">22.7132873535156</t>
@@ -3809,7 +3809,7 @@
     <t xml:space="preserve">21.64621925354</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9510955810547</t>
+    <t xml:space="preserve">21.9510974884033</t>
   </si>
   <si>
     <t xml:space="preserve">22.2644424438477</t>
@@ -3818,19 +3818,19 @@
     <t xml:space="preserve">22.7810363769531</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1120014190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4592266082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2220973968506</t>
+    <t xml:space="preserve">22.112003326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4592247009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2220993041992</t>
   </si>
   <si>
     <t xml:space="preserve">21.307466506958</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7563133239746</t>
+    <t xml:space="preserve">21.7563152313232</t>
   </si>
   <si>
     <t xml:space="preserve">22.2898483276367</t>
@@ -3845,40 +3845,40 @@
     <t xml:space="preserve">22.5185050964355</t>
   </si>
   <si>
-    <t xml:space="preserve">23.009693145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5015659332275</t>
+    <t xml:space="preserve">23.0096950531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5015678405762</t>
   </si>
   <si>
     <t xml:space="preserve">22.6116619110107</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1536636352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9666652679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0513534545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9327945709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4239826202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5256080627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9497299194336</t>
+    <t xml:space="preserve">23.1536617279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.966667175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0513572692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9327926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4239807128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5256061553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9497318267822</t>
   </si>
   <si>
     <t xml:space="preserve">23.8565731048584</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4416046142578</t>
+    <t xml:space="preserve">23.4416007995605</t>
   </si>
   <si>
     <t xml:space="preserve">23.7888221740723</t>
@@ -3890,22 +3890,22 @@
     <t xml:space="preserve">24.1360416412354</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5008850097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7380084991455</t>
+    <t xml:space="preserve">23.500883102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7380104064941</t>
   </si>
   <si>
     <t xml:space="preserve">23.0774440765381</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5354423522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9334735870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7725677490234</t>
+    <t xml:space="preserve">22.5354404449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9334754943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7725658416748</t>
   </si>
   <si>
     <t xml:space="preserve">22.095064163208</t>
@@ -3914,13 +3914,13 @@
     <t xml:space="preserve">22.0273151397705</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2559719085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.391471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.925687789917</t>
+    <t xml:space="preserve">22.255973815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3914737701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9256916046143</t>
   </si>
   <si>
     <t xml:space="preserve">22.2390365600586</t>
@@ -3929,37 +3929,37 @@
     <t xml:space="preserve">22.3237228393555</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4422836303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0689754486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9243259429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3907909393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9419441223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6455364227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.730224609375</t>
+    <t xml:space="preserve">22.4422855377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0689735412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9243221282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3907871246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9419460296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6455383300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7302227020264</t>
   </si>
   <si>
     <t xml:space="preserve">21.3921566009521</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5022525787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3413467407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7908706665039</t>
+    <t xml:space="preserve">21.5022506713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3413429260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7908725738525</t>
   </si>
   <si>
     <t xml:space="preserve">21.0957489013672</t>
@@ -3974,28 +3974,28 @@
     <t xml:space="preserve">20.3335590362549</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2207298278809</t>
+    <t xml:space="preserve">24.2207336425781</t>
   </si>
   <si>
     <t xml:space="preserve">23.2552871704102</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0344181060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4246654510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7979774475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4331340789795</t>
+    <t xml:space="preserve">24.0344200134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4246635437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7979736328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4331359863281</t>
   </si>
   <si>
     <t xml:space="preserve">23.6533222198486</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0174808502197</t>
+    <t xml:space="preserve">24.0174789428711</t>
   </si>
   <si>
     <t xml:space="preserve">24.3308258056641</t>
@@ -4004,16 +4004,16 @@
     <t xml:space="preserve">24.3477630615234</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2037963867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.79660987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1438293457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8297996520996</t>
+    <t xml:space="preserve">24.2037925720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7966079711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1438274383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.829797744751</t>
   </si>
   <si>
     <t xml:space="preserve">25.9737701416016</t>
@@ -4028,52 +4028,52 @@
     <t xml:space="preserve">25.6265506744385</t>
   </si>
   <si>
-    <t xml:space="preserve">25.719705581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6858310699463</t>
+    <t xml:space="preserve">25.7197074890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6858329772949</t>
   </si>
   <si>
     <t xml:space="preserve">26.3294582366943</t>
   </si>
   <si>
-    <t xml:space="preserve">27.311840057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9307441711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9053363800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1756572723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2264652252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.074031829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4551258087158</t>
+    <t xml:space="preserve">27.3118362426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9307422637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9053382873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1756553649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2264709472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0740299224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4551219940186</t>
   </si>
   <si>
     <t xml:space="preserve">28.2434062957764</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1163749694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3111515045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1671848297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4297161102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7091903686523</t>
+    <t xml:space="preserve">28.1163768768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3111553192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1671867370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4297180175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7091884613037</t>
   </si>
   <si>
     <t xml:space="preserve">27.1848049163818</t>
@@ -4082,13 +4082,13 @@
     <t xml:space="preserve">27.2779636383057</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0069599151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.947681427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2864303588867</t>
+    <t xml:space="preserve">27.0069637298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9476776123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2864322662354</t>
   </si>
   <si>
     <t xml:space="preserve">27.0238990783691</t>
@@ -4097,67 +4097,67 @@
     <t xml:space="preserve">27.6675262451172</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4981517791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2610263824463</t>
+    <t xml:space="preserve">27.4981536865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2610244750977</t>
   </si>
   <si>
     <t xml:space="preserve">27.0577754974365</t>
   </si>
   <si>
-    <t xml:space="preserve">27.269495010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5574340820312</t>
+    <t xml:space="preserve">27.2694931030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5574359893799</t>
   </si>
   <si>
     <t xml:space="preserve">28.0909652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1255226135254</t>
+    <t xml:space="preserve">27.125524520874</t>
   </si>
   <si>
     <t xml:space="preserve">27.0916500091553</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7105560302734</t>
+    <t xml:space="preserve">26.7105541229248</t>
   </si>
   <si>
     <t xml:space="preserve">26.7952423095703</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4219341278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2271499633789</t>
+    <t xml:space="preserve">27.421932220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2271518707275</t>
   </si>
   <si>
     <t xml:space="preserve">27.4304008483887</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3203067779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1509342193604</t>
+    <t xml:space="preserve">27.3203048706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1509323120117</t>
   </si>
   <si>
     <t xml:space="preserve">27.7014026641846</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2349376678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9046535491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.192590713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4720592498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4635944366455</t>
+    <t xml:space="preserve">28.234935760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.904655456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1925964355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4720573425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4635963439941</t>
   </si>
   <si>
     <t xml:space="preserve">29.0818157196045</t>
@@ -4172,58 +4172,58 @@
     <t xml:space="preserve">28.7938747406006</t>
   </si>
   <si>
-    <t xml:space="preserve">28.692253112793</t>
+    <t xml:space="preserve">28.6922512054443</t>
   </si>
   <si>
     <t xml:space="preserve">28.4043140411377</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7176551818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.844690322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8362216949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8531551361084</t>
+    <t xml:space="preserve">28.7176609039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8446884155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.836217880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.853157043457</t>
   </si>
   <si>
     <t xml:space="preserve">28.6244983673096</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8108177185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8785629272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0902843475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8700923919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8277549743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1417770385742</t>
+    <t xml:space="preserve">28.8108139038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8785648345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0902824401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8700904846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8277530670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1417808532715</t>
   </si>
   <si>
     <t xml:space="preserve">28.7599983215332</t>
   </si>
   <si>
-    <t xml:space="preserve">28.675313949585</t>
+    <t xml:space="preserve">28.6753120422363</t>
   </si>
   <si>
     <t xml:space="preserve">28.759183883667</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2301406860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0740299224854</t>
+    <t xml:space="preserve">28.2301387786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0740280151367</t>
   </si>
   <si>
     <t xml:space="preserve">28.1954479217529</t>
@@ -4232,13 +4232,13 @@
     <t xml:space="preserve">28.0133190155029</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2908477783203</t>
+    <t xml:space="preserve">28.2908496856689</t>
   </si>
   <si>
     <t xml:space="preserve">28.3515586853027</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2995223999023</t>
+    <t xml:space="preserve">28.299524307251</t>
   </si>
   <si>
     <t xml:space="preserve">28.1520843505859</t>
@@ -4247,10 +4247,10 @@
     <t xml:space="preserve">28.3081970214844</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2214679718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1434154510498</t>
+    <t xml:space="preserve">28.2214698791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1434116363525</t>
   </si>
   <si>
     <t xml:space="preserve">26.9812507629395</t>
@@ -4265,25 +4265,25 @@
     <t xml:space="preserve">26.0185623168945</t>
   </si>
   <si>
-    <t xml:space="preserve">24.934455871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0558757781982</t>
+    <t xml:space="preserve">24.9344539642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0558738708496</t>
   </si>
   <si>
     <t xml:space="preserve">24.275318145752</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9951648712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8017387390137</t>
+    <t xml:space="preserve">24.9951667785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8017406463623</t>
   </si>
   <si>
     <t xml:space="preserve">25.3594264984131</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3247356414795</t>
+    <t xml:space="preserve">25.3247337341309</t>
   </si>
   <si>
     <t xml:space="preserve">24.8997650146484</t>
@@ -4298,16 +4298,16 @@
     <t xml:space="preserve">25.1686248779297</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4634990692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4808464050293</t>
+    <t xml:space="preserve">25.4635009765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4808444976807</t>
   </si>
   <si>
     <t xml:space="preserve">25.4461536407471</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3073902130127</t>
+    <t xml:space="preserve">25.3073863983154</t>
   </si>
   <si>
     <t xml:space="preserve">24.9518032073975</t>
@@ -4316,22 +4316,22 @@
     <t xml:space="preserve">25.5068645477295</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9058151245117</t>
+    <t xml:space="preserve">25.905818939209</t>
   </si>
   <si>
     <t xml:space="preserve">26.1052913665771</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6716499328613</t>
+    <t xml:space="preserve">25.6716480255127</t>
   </si>
   <si>
     <t xml:space="preserve">26.0359077453613</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6196117401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2006912231445</t>
+    <t xml:space="preserve">25.6196098327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2006931304932</t>
   </si>
   <si>
     <t xml:space="preserve">26.4088401794434</t>
@@ -4340,40 +4340,40 @@
     <t xml:space="preserve">26.4435329437256</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5042400360107</t>
+    <t xml:space="preserve">26.5042419433594</t>
   </si>
   <si>
     <t xml:space="preserve">26.313440322876</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1833477020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4522037506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0966186523438</t>
+    <t xml:space="preserve">26.1833457946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.452205657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0966167449951</t>
   </si>
   <si>
     <t xml:space="preserve">25.4721736907959</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6109409332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3767719268799</t>
+    <t xml:space="preserve">25.6109390258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3767700195312</t>
   </si>
   <si>
     <t xml:space="preserve">26.3307857513428</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1920223236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0098915100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8104133605957</t>
+    <t xml:space="preserve">26.1920204162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0098876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8104152679443</t>
   </si>
   <si>
     <t xml:space="preserve">26.5215873718262</t>
@@ -4382,13 +4382,13 @@
     <t xml:space="preserve">26.8424835205078</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4868984222412</t>
+    <t xml:space="preserve">26.4868965148926</t>
   </si>
   <si>
     <t xml:space="preserve">26.5996437072754</t>
   </si>
   <si>
-    <t xml:space="preserve">26.729736328125</t>
+    <t xml:space="preserve">26.7297344207764</t>
   </si>
   <si>
     <t xml:space="preserve">27.1062107086182</t>
@@ -4397,13 +4397,13 @@
     <t xml:space="preserve">27.0882835388184</t>
   </si>
   <si>
-    <t xml:space="preserve">26.335334777832</t>
+    <t xml:space="preserve">26.3353328704834</t>
   </si>
   <si>
     <t xml:space="preserve">26.4070415496826</t>
   </si>
   <si>
-    <t xml:space="preserve">26.675952911377</t>
+    <t xml:space="preserve">26.6759548187256</t>
   </si>
   <si>
     <t xml:space="preserve">26.7028465270996</t>
@@ -4412,34 +4412,34 @@
     <t xml:space="preserve">26.3084411621094</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8154392242432</t>
+    <t xml:space="preserve">25.8154373168945</t>
   </si>
   <si>
     <t xml:space="preserve">26.3622245788574</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8821201324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.693883895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.20481300354</t>
+    <t xml:space="preserve">26.882116317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6938819885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2048110961914</t>
   </si>
   <si>
     <t xml:space="preserve">27.4737224578857</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5185413360596</t>
+    <t xml:space="preserve">27.5185432434082</t>
   </si>
   <si>
     <t xml:space="preserve">27.3930473327637</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6529979705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7157440185547</t>
+    <t xml:space="preserve">27.6529960632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7157421112061</t>
   </si>
   <si>
     <t xml:space="preserve">27.9219074249268</t>
@@ -4448,19 +4448,19 @@
     <t xml:space="preserve">27.8860549926758</t>
   </si>
   <si>
-    <t xml:space="preserve">27.966724395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9398365020752</t>
+    <t xml:space="preserve">27.9667263031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9398345947266</t>
   </si>
   <si>
     <t xml:space="preserve">27.7605609893799</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6619625091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4647598266602</t>
+    <t xml:space="preserve">27.6619606018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4647579193115</t>
   </si>
   <si>
     <t xml:space="preserve">27.3840847015381</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">27.3213386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6081790924072</t>
+    <t xml:space="preserve">27.6081771850586</t>
   </si>
   <si>
     <t xml:space="preserve">27.9487991333008</t>
@@ -4478,37 +4478,37 @@
     <t xml:space="preserve">28.0115451812744</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2356357574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7644939422607</t>
+    <t xml:space="preserve">28.2356376647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7644958496094</t>
   </si>
   <si>
     <t xml:space="preserve">28.3611278533936</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9129428863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4378700256348</t>
+    <t xml:space="preserve">27.9129447937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4378681182861</t>
   </si>
   <si>
     <t xml:space="preserve">27.8233089447021</t>
   </si>
   <si>
-    <t xml:space="preserve">27.957763671875</t>
+    <t xml:space="preserve">27.9577617645264</t>
   </si>
   <si>
     <t xml:space="preserve">28.5045471191406</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7465667724609</t>
+    <t xml:space="preserve">28.7465686798096</t>
   </si>
   <si>
     <t xml:space="preserve">28.6927833557129</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7555332183838</t>
+    <t xml:space="preserve">28.7555313110352</t>
   </si>
   <si>
     <t xml:space="preserve">28.9796257019043</t>
@@ -4517,28 +4517,28 @@
     <t xml:space="preserve">29.0334053039551</t>
   </si>
   <si>
-    <t xml:space="preserve">29.132007598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3740291595459</t>
+    <t xml:space="preserve">29.1320056915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3740272521973</t>
   </si>
   <si>
     <t xml:space="preserve">29.2306060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">29.705680847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1000862121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9606037139893</t>
+    <t xml:space="preserve">29.7056846618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1000881195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9606018066406</t>
   </si>
   <si>
     <t xml:space="preserve">30.5482711791992</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1986827850342</t>
+    <t xml:space="preserve">30.1986865997314</t>
   </si>
   <si>
     <t xml:space="preserve">29.8132457733154</t>
@@ -4559,73 +4559,73 @@
     <t xml:space="preserve">29.1140785217285</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4457340240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3650608062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0871906280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7017478942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9975490570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1768245697021</t>
+    <t xml:space="preserve">29.4457321166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.365062713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0871868133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7017498016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9975509643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1768226623535</t>
   </si>
   <si>
     <t xml:space="preserve">29.2574996948242</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3112812042236</t>
+    <t xml:space="preserve">29.3112831115723</t>
   </si>
   <si>
     <t xml:space="preserve">29.5712280273438</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1628322601318</t>
+    <t xml:space="preserve">30.1628303527832</t>
   </si>
   <si>
     <t xml:space="preserve">29.9745903015137</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2166137695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0014896392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0283756256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7773933410645</t>
+    <t xml:space="preserve">30.2166118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0014839172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0283737182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7773914337158</t>
   </si>
   <si>
     <t xml:space="preserve">29.7236099243164</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7684268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1717967987061</t>
+    <t xml:space="preserve">29.7684288024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1717948913574</t>
   </si>
   <si>
     <t xml:space="preserve">30.180757522583</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4586315155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0104484558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2703971862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5930881500244</t>
+    <t xml:space="preserve">30.4586334228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0104503631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2703952789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.593090057373</t>
   </si>
   <si>
     <t xml:space="preserve">30.144905090332</t>
@@ -4637,22 +4637,22 @@
     <t xml:space="preserve">30.0463027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0373382568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.696720123291</t>
+    <t xml:space="preserve">30.0373401641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6967182159424</t>
   </si>
   <si>
     <t xml:space="preserve">29.1678619384766</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6877536773682</t>
+    <t xml:space="preserve">29.6877555847168</t>
   </si>
   <si>
     <t xml:space="preserve">29.3292083740234</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4278087615967</t>
+    <t xml:space="preserve">29.4278106689453</t>
   </si>
   <si>
     <t xml:space="preserve">30.0552654266357</t>
@@ -4661,7 +4661,7 @@
     <t xml:space="preserve">28.7107105255127</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5224761962891</t>
+    <t xml:space="preserve">28.5224742889404</t>
   </si>
   <si>
     <t xml:space="preserve">28.4776573181152</t>
@@ -4673,7 +4673,7 @@
     <t xml:space="preserve">27.7426338195801</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3392658233643</t>
+    <t xml:space="preserve">27.3392677307129</t>
   </si>
   <si>
     <t xml:space="preserve">27.5095767974854</t>
@@ -4682,19 +4682,19 @@
     <t xml:space="preserve">27.3571968078613</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0524291992188</t>
+    <t xml:space="preserve">27.0524311065674</t>
   </si>
   <si>
     <t xml:space="preserve">27.1868839263916</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2854862213135</t>
+    <t xml:space="preserve">27.2854843139648</t>
   </si>
   <si>
     <t xml:space="preserve">27.2944488525391</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4468307495117</t>
+    <t xml:space="preserve">27.4468326568604</t>
   </si>
   <si>
     <t xml:space="preserve">27.5454330444336</t>
@@ -4706,7 +4706,7 @@
     <t xml:space="preserve">28.4059467315674</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1191101074219</t>
+    <t xml:space="preserve">28.1191082000732</t>
   </si>
   <si>
     <t xml:space="preserve">28.2714920043945</t>
@@ -4715,43 +4715,43 @@
     <t xml:space="preserve">28.6838207244873</t>
   </si>
   <si>
-    <t xml:space="preserve">28.495584487915</t>
+    <t xml:space="preserve">28.4955825805664</t>
   </si>
   <si>
     <t xml:space="preserve">29.0423698425293</t>
   </si>
   <si>
-    <t xml:space="preserve">29.732572555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7863540649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3919544219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4547004699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.849100112915</t>
+    <t xml:space="preserve">29.7325744628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.78635597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3919525146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4546985626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8491020202637</t>
   </si>
   <si>
     <t xml:space="preserve">29.1947536468506</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8989524841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2664642333984</t>
+    <t xml:space="preserve">28.8989505767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2664623260498</t>
   </si>
   <si>
     <t xml:space="preserve">29.0602931976318</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1499347686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4367733001709</t>
+    <t xml:space="preserve">29.1499328613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4367713928223</t>
   </si>
   <si>
     <t xml:space="preserve">29.0961513519287</t>
@@ -4760,10 +4760,10 @@
     <t xml:space="preserve">29.2485332489014</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5891532897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6070823669434</t>
+    <t xml:space="preserve">29.5891551971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6070804595947</t>
   </si>
   <si>
     <t xml:space="preserve">29.7953205108643</t>
@@ -4772,13 +4772,13 @@
     <t xml:space="preserve">30.2883243560791</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0731906890869</t>
+    <t xml:space="preserve">30.0731945037842</t>
   </si>
   <si>
     <t xml:space="preserve">30.4048500061035</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4317436218262</t>
+    <t xml:space="preserve">30.4317417144775</t>
   </si>
   <si>
     <t xml:space="preserve">30.3600311279297</t>
@@ -4793,34 +4793,34 @@
     <t xml:space="preserve">30.3152141571045</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3421020507812</t>
+    <t xml:space="preserve">30.3421058654785</t>
   </si>
   <si>
     <t xml:space="preserve">30.7454719543457</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3331413269043</t>
+    <t xml:space="preserve">30.3331394195557</t>
   </si>
   <si>
     <t xml:space="preserve">30.0642318725586</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6110191345215</t>
+    <t xml:space="preserve">30.6110153198242</t>
   </si>
   <si>
     <t xml:space="preserve">30.8440723419189</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0860958099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1936550140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1577968597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1757259368896</t>
+    <t xml:space="preserve">31.086088180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1936511993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1577987670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1757278442383</t>
   </si>
   <si>
     <t xml:space="preserve">31.3818912506104</t>
@@ -4829,64 +4829,64 @@
     <t xml:space="preserve">31.5522041320801</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8121528625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8480014801025</t>
+    <t xml:space="preserve">31.8121547698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8480033874512</t>
   </si>
   <si>
     <t xml:space="preserve">32.0003890991211</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2384719848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.713550567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7314777374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5432376861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.821117401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1258773803711</t>
+    <t xml:space="preserve">31.2384738922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7135543823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.731481552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5432415008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8300743103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8211116790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1258811950684</t>
   </si>
   <si>
     <t xml:space="preserve">32.0900268554688</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2743244171143</t>
+    <t xml:space="preserve">31.2743263244629</t>
   </si>
   <si>
     <t xml:space="preserve">30.9068183898926</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9785289764404</t>
+    <t xml:space="preserve">30.9785308837891</t>
   </si>
   <si>
     <t xml:space="preserve">30.1090488433838</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3958854675293</t>
+    <t xml:space="preserve">30.3958873748779</t>
   </si>
   <si>
     <t xml:space="preserve">30.8551158905029</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3069038391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6632423400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.430736541748</t>
+    <t xml:space="preserve">30.3069019317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6632404327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4307384490967</t>
   </si>
   <si>
     <t xml:space="preserve">32.2896003723145</t>
@@ -4898,7 +4898,7 @@
     <t xml:space="preserve">31.5769271850586</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3667812347412</t>
+    <t xml:space="preserve">31.3667774200439</t>
   </si>
   <si>
     <t xml:space="preserve">31.2114505767822</t>
@@ -4907,16 +4907,16 @@
     <t xml:space="preserve">31.3941860198975</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4764194488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6957015991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.860164642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9698104858398</t>
+    <t xml:space="preserve">31.4764213562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6957035064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8601665496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9698085784912</t>
   </si>
   <si>
     <t xml:space="preserve">31.9789447784424</t>
@@ -4952,22 +4952,22 @@
     <t xml:space="preserve">33.7423553466797</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7971801757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7514953613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6418495178223</t>
+    <t xml:space="preserve">33.797176361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7514915466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6418533325195</t>
   </si>
   <si>
     <t xml:space="preserve">32.947452545166</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2946472167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3311996459961</t>
+    <t xml:space="preserve">33.2946510314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3311958312988</t>
   </si>
   <si>
     <t xml:space="preserve">33.2398300170898</t>
@@ -4976,7 +4976,7 @@
     <t xml:space="preserve">33.404296875</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0936393737793</t>
+    <t xml:space="preserve">33.0936431884766</t>
   </si>
   <si>
     <t xml:space="preserve">32.6367988586426</t>
@@ -4988,19 +4988,19 @@
     <t xml:space="preserve">32.3809623718262</t>
   </si>
   <si>
-    <t xml:space="preserve">31.613468170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8144817352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5819778442383</t>
+    <t xml:space="preserve">31.6134700775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8144836425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.581974029541</t>
   </si>
   <si>
     <t xml:space="preserve">32.5454292297363</t>
   </si>
   <si>
-    <t xml:space="preserve">33.130184173584</t>
+    <t xml:space="preserve">33.1301879882812</t>
   </si>
   <si>
     <t xml:space="preserve">33.075366973877</t>
@@ -5012,10 +5012,10 @@
     <t xml:space="preserve">33.1850090026855</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4408378601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7697677612305</t>
+    <t xml:space="preserve">33.4408416748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7697639465332</t>
   </si>
   <si>
     <t xml:space="preserve">33.9525032043457</t>
@@ -5024,7 +5024,7 @@
     <t xml:space="preserve">34.4093437194824</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8844604492188</t>
+    <t xml:space="preserve">34.884464263916</t>
   </si>
   <si>
     <t xml:space="preserve">35.4692192077637</t>
@@ -5039,28 +5039,28 @@
     <t xml:space="preserve">37.0955772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9128456115723</t>
+    <t xml:space="preserve">36.912841796875</t>
   </si>
   <si>
     <t xml:space="preserve">37.0590324401855</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7849235534668</t>
+    <t xml:space="preserve">36.7849273681641</t>
   </si>
   <si>
     <t xml:space="preserve">37.0985145568848</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9844818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1555252075195</t>
+    <t xml:space="preserve">36.9844779968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1555290222168</t>
   </si>
   <si>
     <t xml:space="preserve">37.1365280151367</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3265762329102</t>
+    <t xml:space="preserve">37.3265800476074</t>
   </si>
   <si>
     <t xml:space="preserve">37.0224914550781</t>
@@ -5084,7 +5084,7 @@
     <t xml:space="preserve">36.4523315429688</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8704490661621</t>
+    <t xml:space="preserve">36.8704452514648</t>
   </si>
   <si>
     <t xml:space="preserve">36.9084625244141</t>
@@ -5093,10 +5093,10 @@
     <t xml:space="preserve">36.5853691101074</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5473556518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0912284851074</t>
+    <t xml:space="preserve">36.5473594665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0912246704102</t>
   </si>
   <si>
     <t xml:space="preserve">36.5663642883301</t>
@@ -5105,7 +5105,7 @@
     <t xml:space="preserve">35.7301254272461</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0839424133301</t>
+    <t xml:space="preserve">35.0839385986328</t>
   </si>
   <si>
     <t xml:space="preserve">35.1219520568848</t>
@@ -5120,7 +5120,7 @@
     <t xml:space="preserve">35.7491302490234</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3572998046875</t>
+    <t xml:space="preserve">36.3573036193848</t>
   </si>
   <si>
     <t xml:space="preserve">36.0722198486328</t>
@@ -5129,13 +5129,13 @@
     <t xml:space="preserve">35.8821678161621</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7871398925781</t>
+    <t xml:space="preserve">35.7871437072754</t>
   </si>
   <si>
     <t xml:space="preserve">35.5970878601074</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9201774597168</t>
+    <t xml:space="preserve">35.9201812744141</t>
   </si>
   <si>
     <t xml:space="preserve">35.9391860961914</t>
@@ -5147,13 +5147,13 @@
     <t xml:space="preserve">35.8631629943848</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9011764526367</t>
+    <t xml:space="preserve">35.9011726379395</t>
   </si>
   <si>
     <t xml:space="preserve">36.3763084411621</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8514442443848</t>
+    <t xml:space="preserve">36.8514404296875</t>
   </si>
   <si>
     <t xml:space="preserve">37.2885704040527</t>
@@ -5177,7 +5177,7 @@
     <t xml:space="preserve">38.3718757629395</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4478950500488</t>
+    <t xml:space="preserve">38.4478988647461</t>
   </si>
   <si>
     <t xml:space="preserve">38.5429229736328</t>
@@ -5189,7 +5189,7 @@
     <t xml:space="preserve">37.7446975708008</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6423873901367</t>
+    <t xml:space="preserve">36.6423835754395</t>
   </si>
   <si>
     <t xml:space="preserve">35.4450454711914</t>
@@ -5201,7 +5201,7 @@
     <t xml:space="preserve">35.8061485290527</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6921195983887</t>
+    <t xml:space="preserve">35.6921157836914</t>
   </si>
   <si>
     <t xml:space="preserve">36.1862564086914</t>
@@ -5210,7 +5210,7 @@
     <t xml:space="preserve">36.4903450012207</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8894538879395</t>
+    <t xml:space="preserve">36.8894577026367</t>
   </si>
   <si>
     <t xml:space="preserve">37.8017120361328</t>
@@ -5222,16 +5222,16 @@
     <t xml:space="preserve">37.7827072143555</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6876792907715</t>
+    <t xml:space="preserve">37.6876831054688</t>
   </si>
   <si>
     <t xml:space="preserve">37.9727592468262</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9917678833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3338623046875</t>
+    <t xml:space="preserve">37.9917640686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3338661193848</t>
   </si>
   <si>
     <t xml:space="preserve">38.4098815917969</t>
@@ -5246,7 +5246,7 @@
     <t xml:space="preserve">37.7066879272461</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2198333740234</t>
+    <t xml:space="preserve">38.2198295593262</t>
   </si>
   <si>
     <t xml:space="preserve">38.0107727050781</t>
@@ -5255,10 +5255,10 @@
     <t xml:space="preserve">38.2768478393555</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2578392028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.238842010498</t>
+    <t xml:space="preserve">38.2578430175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2388381958008</t>
   </si>
   <si>
     <t xml:space="preserve">38.5809326171875</t>
@@ -5276,7 +5276,7 @@
     <t xml:space="preserve">39.0940780639648</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5999412536621</t>
+    <t xml:space="preserve">38.5999374389648</t>
   </si>
   <si>
     <t xml:space="preserve">37.7256927490234</t>
@@ -5297,7 +5297,7 @@
     <t xml:space="preserve">39.4741897583008</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8162841796875</t>
+    <t xml:space="preserve">39.8162879943848</t>
   </si>
   <si>
     <t xml:space="preserve">39.9493217468262</t>
@@ -5315,7 +5315,7 @@
     <t xml:space="preserve">39.6452369689941</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3981666564941</t>
+    <t xml:space="preserve">39.3981628417969</t>
   </si>
   <si>
     <t xml:space="preserve">39.3601531982422</t>
@@ -5342,10 +5342,10 @@
     <t xml:space="preserve">38.5619316101074</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9873352050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8923072814941</t>
+    <t xml:space="preserve">39.9873313903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8923034667969</t>
   </si>
   <si>
     <t xml:space="preserve">40.1773834228516</t>
@@ -5372,10 +5372,10 @@
     <t xml:space="preserve">40.9946174621582</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3557205200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5267715454102</t>
+    <t xml:space="preserve">41.3557243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5267677307129</t>
   </si>
   <si>
     <t xml:space="preserve">41.3747291564941</t>
@@ -5387,13 +5387,13 @@
     <t xml:space="preserve">41.6978187561035</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1349411010742</t>
+    <t xml:space="preserve">42.1349449157715</t>
   </si>
   <si>
     <t xml:space="preserve">42.0209121704102</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7548294067383</t>
+    <t xml:space="preserve">41.7548332214355</t>
   </si>
   <si>
     <t xml:space="preserve">42.3820114135742</t>
@@ -5402,7 +5402,7 @@
     <t xml:space="preserve">42.4390258789062</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4580345153809</t>
+    <t xml:space="preserve">42.4580307006836</t>
   </si>
   <si>
     <t xml:space="preserve">42.2869834899902</t>
@@ -5420,7 +5420,7 @@
     <t xml:space="preserve">43.5223350524902</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8761520385742</t>
+    <t xml:space="preserve">42.876148223877</t>
   </si>
   <si>
     <t xml:space="preserve">42.9521751403809</t>
@@ -5432,7 +5432,7 @@
     <t xml:space="preserve">43.0852088928223</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3059921264648</t>
+    <t xml:space="preserve">42.3059883117676</t>
   </si>
   <si>
     <t xml:space="preserve">42.7431144714355</t>
@@ -5453,13 +5453,13 @@
     <t xml:space="preserve">42.9901847839355</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8951568603516</t>
+    <t xml:space="preserve">42.8951530456543</t>
   </si>
   <si>
     <t xml:space="preserve">43.7123908996582</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4653205871582</t>
+    <t xml:space="preserve">43.4653167724609</t>
   </si>
   <si>
     <t xml:space="preserve">44.0354804992676</t>
@@ -5477,19 +5477,19 @@
     <t xml:space="preserve">46.6202163696289</t>
   </si>
   <si>
-    <t xml:space="preserve">46.639217376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6962356567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.582202911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7722587585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2781143188477</t>
+    <t xml:space="preserve">46.6392211914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.696231842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5821990966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7722549438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2781181335449</t>
   </si>
   <si>
     <t xml:space="preserve">46.1070671081543</t>
@@ -5498,7 +5498,7 @@
     <t xml:space="preserve">45.8219871520996</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0310440063477</t>
+    <t xml:space="preserve">46.0310478210449</t>
   </si>
   <si>
     <t xml:space="preserve">45.7839736938477</t>
@@ -5540,7 +5540,7 @@
     <t xml:space="preserve">48.9388694763184</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8438415527344</t>
+    <t xml:space="preserve">48.8438453674316</t>
   </si>
   <si>
     <t xml:space="preserve">48.7963256835938</t>
@@ -5958,6 +5958,9 @@
   </si>
   <si>
     <t xml:space="preserve">49.3800010681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6199989318848</t>
   </si>
 </sst>
 </file>
@@ -71322,7 +71325,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6909722222</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>142806</v>
@@ -71343,6 +71346,32 @@
         <v>1966</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6919791667</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>190897</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>49.7999992370605</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>48.9000015258789</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>49</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>49.6199989318848</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>1982</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BGN.MI.xlsx
+++ b/data/BGN.MI.xlsx
@@ -47,373 +47,373 @@
     <t xml:space="preserve">17.2943058013916</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7816524505615</t>
+    <t xml:space="preserve">16.7816543579102</t>
   </si>
   <si>
     <t xml:space="preserve">16.5284156799316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2628231048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3678245544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5098857879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9422473907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6457691192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1269378662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6760511398315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9601745605469</t>
+    <t xml:space="preserve">16.262825012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3678283691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5098838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9422416687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6457672119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1269416809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6760492324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9601726531982</t>
   </si>
   <si>
     <t xml:space="preserve">15.0707511901855</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0769290924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5092868804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5401697158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4289894104004</t>
+    <t xml:space="preserve">15.0769300460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5092897415161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.540168762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.428991317749</t>
   </si>
   <si>
     <t xml:space="preserve">15.6019334793091</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1942844390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4784021377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2931060791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0213394165039</t>
+    <t xml:space="preserve">15.194281578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4784049987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2931070327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0213403701782</t>
   </si>
   <si>
     <t xml:space="preserve">13.8230905532837</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7180871963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5945596694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4580783843994</t>
+    <t xml:space="preserve">13.718090057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.594557762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4580755233765</t>
   </si>
   <si>
     <t xml:space="preserve">12.6804313659668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5636749267578</t>
+    <t xml:space="preserve">13.5636777877808</t>
   </si>
   <si>
     <t xml:space="preserve">13.1745557785034</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4154415130615</t>
+    <t xml:space="preserve">13.4154396057129</t>
   </si>
   <si>
     <t xml:space="preserve">14.0022106170654</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8477983474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3851556777954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4098615646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1936817169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4963340759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1813287734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3233919143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3357419967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5210418701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8607501983643</t>
+    <t xml:space="preserve">13.8477954864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3851585388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4098634719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1936836242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4963321685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1813297271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3233909606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3357439041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5210399627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8607492446899</t>
   </si>
   <si>
     <t xml:space="preserve">15.2436952590942</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5710506439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4969310760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4351673126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4413442611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3239889144897</t>
+    <t xml:space="preserve">15.5710496902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4969320297241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4351654052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4413471221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3239898681641</t>
   </si>
   <si>
     <t xml:space="preserve">16.0157623291016</t>
   </si>
   <si>
-    <t xml:space="preserve">16.201057434082</t>
+    <t xml:space="preserve">16.2010593414307</t>
   </si>
   <si>
     <t xml:space="preserve">16.2937049865723</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1578216552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3431167602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8489952087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8922309875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6081113815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9354648590088</t>
+    <t xml:space="preserve">16.1578235626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3431186676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8489971160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8922290802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6081132888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9354658126831</t>
   </si>
   <si>
     <t xml:space="preserve">15.9663486480713</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0095882415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8675260543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8298654556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8854560852051</t>
+    <t xml:space="preserve">16.0095863342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.867525100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8298664093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8854541778564</t>
   </si>
   <si>
     <t xml:space="preserve">14.6569261550903</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9410457611084</t>
+    <t xml:space="preserve">14.9410438537598</t>
   </si>
   <si>
     <t xml:space="preserve">15.3981084823608</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5339889526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8737030029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9478178024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1145877838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0837059020996</t>
+    <t xml:space="preserve">15.5339908599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8737020492554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9478206634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1145839691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.083703994751</t>
   </si>
   <si>
     <t xml:space="preserve">16.0713520050049</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1084060668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2072353363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0589962005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2998809814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1701755523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1207656860352</t>
+    <t xml:space="preserve">16.1084098815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2072334289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0590019226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2998790740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1701793670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1207637786865</t>
   </si>
   <si>
     <t xml:space="preserve">15.7316427230835</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3795785903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1201639175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8916339874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7063388824463</t>
+    <t xml:space="preserve">15.3795757293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1201629638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8916320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.706335067749</t>
   </si>
   <si>
     <t xml:space="preserve">14.6383943557739</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6075086593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2986850738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4530992507935</t>
+    <t xml:space="preserve">14.6075096130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2986822128296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4530973434448</t>
   </si>
   <si>
     <t xml:space="preserve">14.6692771911621</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3419198989868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.366626739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3913335800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3975086212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5537919998169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8142642974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9640312194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5110197067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5956735610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3742742538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3286924362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1138010025024</t>
+    <t xml:space="preserve">14.3419227600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3666286468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3913307189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3975076675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5537910461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8142614364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9640331268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5110177993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5956754684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3742723464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3286914825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1138019561768</t>
   </si>
   <si>
     <t xml:space="preserve">15.0096139907837</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0551958084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2114791870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3547401428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3026447296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2570629119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8533325195312</t>
+    <t xml:space="preserve">15.055196762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.211483001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3547372817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3026466369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2570600509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8533296585083</t>
   </si>
   <si>
     <t xml:space="preserve">14.0979700088501</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2058544158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9649209976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.945384979248</t>
+    <t xml:space="preserve">13.2058601379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9649200439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9453859329224</t>
   </si>
   <si>
     <t xml:space="preserve">13.1993455886841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6616802215576</t>
+    <t xml:space="preserve">13.6616821289062</t>
   </si>
   <si>
     <t xml:space="preserve">13.837498664856</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1565742492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5733270645142</t>
+    <t xml:space="preserve">14.1565732955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5733261108398</t>
   </si>
   <si>
     <t xml:space="preserve">12.8737573623657</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6690816879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7341976165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6560554504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6821050643921</t>
+    <t xml:space="preserve">11.6690797805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7341985702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6560573577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6821041107178</t>
   </si>
   <si>
     <t xml:space="preserve">11.6039619445801</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2002334594727</t>
+    <t xml:space="preserve">11.200234413147</t>
   </si>
   <si>
     <t xml:space="preserve">10.8160400390625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.431845664978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7444095611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2588386535645</t>
+    <t xml:space="preserve">10.4318447113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7444086074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2588415145874</t>
   </si>
   <si>
     <t xml:space="preserve">11.923038482666</t>
@@ -422,10 +422,10 @@
     <t xml:space="preserve">12.3137454986572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2616529464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5286321640015</t>
+    <t xml:space="preserve">12.2616500854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5286331176758</t>
   </si>
   <si>
     <t xml:space="preserve">12.567702293396</t>
@@ -434,22 +434,22 @@
     <t xml:space="preserve">12.6588687896729</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3723497390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5221223831177</t>
+    <t xml:space="preserve">12.3723526000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5221214294434</t>
   </si>
   <si>
     <t xml:space="preserve">12.5416555404663</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3397922515869</t>
+    <t xml:space="preserve">12.3397903442383</t>
   </si>
   <si>
     <t xml:space="preserve">12.5025863647461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2551383972168</t>
+    <t xml:space="preserve">12.2551403045654</t>
   </si>
   <si>
     <t xml:space="preserve">12.4895620346069</t>
@@ -458,46 +458,46 @@
     <t xml:space="preserve">12.242115020752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0337390899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8188495635986</t>
+    <t xml:space="preserve">12.0337371826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8188514709473</t>
   </si>
   <si>
     <t xml:space="preserve">11.6300106048584</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4281444549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3825635910034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8579206466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9946689605713</t>
+    <t xml:space="preserve">11.4281454086304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3825645446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8579216003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9946699142456</t>
   </si>
   <si>
     <t xml:space="preserve">12.1835098266602</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2030448913574</t>
+    <t xml:space="preserve">12.2030467987061</t>
   </si>
   <si>
     <t xml:space="preserve">12.0532741546631</t>
   </si>
   <si>
-    <t xml:space="preserve">11.94908618927</t>
+    <t xml:space="preserve">11.9490871429443</t>
   </si>
   <si>
     <t xml:space="preserve">11.7928037643433</t>
   </si>
   <si>
-    <t xml:space="preserve">11.525821685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7667579650879</t>
+    <t xml:space="preserve">11.5258226394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7667589187622</t>
   </si>
   <si>
     <t xml:space="preserve">11.4411687850952</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">11.3630275726318</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5583810806274</t>
+    <t xml:space="preserve">11.5583782196045</t>
   </si>
   <si>
     <t xml:space="preserve">11.7797803878784</t>
@@ -515,118 +515,118 @@
     <t xml:space="preserve">11.5388450622559</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472219467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.695125579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9425754547119</t>
+    <t xml:space="preserve">11.7472229003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6951265335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9425745010376</t>
   </si>
   <si>
     <t xml:space="preserve">12.1314153671265</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1379261016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4114217758179</t>
+    <t xml:space="preserve">12.1379280090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4114227294922</t>
   </si>
   <si>
     <t xml:space="preserve">12.4830503463745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6653814315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8021259307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3788633346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1183938980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1249017715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2876987457275</t>
+    <t xml:space="preserve">12.6653804779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8021240234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3788623809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1183919906616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1249046325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2876977920532</t>
   </si>
   <si>
     <t xml:space="preserve">11.8709449768066</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7016410827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8514089584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9165267944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.252329826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1937208175659</t>
+    <t xml:space="preserve">11.701639175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8514099121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9165258407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2523279190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1937236785889</t>
   </si>
   <si>
     <t xml:space="preserve">11.1481399536133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0830202102661</t>
+    <t xml:space="preserve">11.0830221176147</t>
   </si>
   <si>
     <t xml:space="preserve">11.1220922470093</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1741857528687</t>
+    <t xml:space="preserve">11.17418384552</t>
   </si>
   <si>
     <t xml:space="preserve">11.1090688705444</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2848863601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1351146697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0765104293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1872091293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0244159698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0179052352905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6430330276489</t>
+    <t xml:space="preserve">11.2848854064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1351165771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0765113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1872100830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0244150161743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0179033279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6430320739746</t>
   </si>
   <si>
     <t xml:space="preserve">11.5779161453247</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9100170135498</t>
+    <t xml:space="preserve">11.9100160598755</t>
   </si>
   <si>
     <t xml:space="preserve">12.1769990921021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2942094802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4309577941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9779472351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0365505218506</t>
+    <t xml:space="preserve">12.2942066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4309558868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9779443740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0365514755249</t>
   </si>
   <si>
     <t xml:space="preserve">13.3816738128662</t>
@@ -638,112 +638,112 @@
     <t xml:space="preserve">13.4142332077026</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1732969284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0560827255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9258518218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8281736373901</t>
+    <t xml:space="preserve">13.1732959747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0560855865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9258508682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8281745910645</t>
   </si>
   <si>
     <t xml:space="preserve">13.3295803070068</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7984294891357</t>
+    <t xml:space="preserve">13.7984256744385</t>
   </si>
   <si>
     <t xml:space="preserve">13.5444669723511</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8830804824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8309888839722</t>
+    <t xml:space="preserve">13.8830785751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8309850692749</t>
   </si>
   <si>
     <t xml:space="preserve">13.9481973648071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8895931243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1240139007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4923715591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9388751983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9323644638062</t>
+    <t xml:space="preserve">13.889594078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1240167617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.492374420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9388732910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9323625564575</t>
   </si>
   <si>
     <t xml:space="preserve">12.8672456741333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9714317321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9909677505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7760810852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.795615196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7304964065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7435207366943</t>
+    <t xml:space="preserve">12.9714326858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9909696578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7760820388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7956142425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7304973602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7435216903687</t>
   </si>
   <si>
     <t xml:space="preserve">14.4691400527954</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2896203994751</t>
+    <t xml:space="preserve">15.2896184921265</t>
   </si>
   <si>
     <t xml:space="preserve">15.8887023925781</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5761384963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3612518310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4784641265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0747327804565</t>
+    <t xml:space="preserve">15.5761394500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3612499237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4784631729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0747318267822</t>
   </si>
   <si>
     <t xml:space="preserve">15.185432434082</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8989133834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8793792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9575204849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9770574569702</t>
+    <t xml:space="preserve">14.8989152908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8793811798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9575214385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9770593643188</t>
   </si>
   <si>
     <t xml:space="preserve">15.0031042098999</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7817077636719</t>
+    <t xml:space="preserve">14.7817058563232</t>
   </si>
   <si>
     <t xml:space="preserve">14.5863494873047</t>
@@ -752,43 +752,43 @@
     <t xml:space="preserve">14.7556552886963</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8598442077637</t>
+    <t xml:space="preserve">14.8598432540894</t>
   </si>
   <si>
     <t xml:space="preserve">15.3417148590088</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4459037780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8403091430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2700872421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5305576324463</t>
+    <t xml:space="preserve">15.4459066390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8403081893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2700824737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5305547714233</t>
   </si>
   <si>
     <t xml:space="preserve">15.4133443832397</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3482246398926</t>
+    <t xml:space="preserve">15.3482275009155</t>
   </si>
   <si>
     <t xml:space="preserve">15.5631151199341</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5138359069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6570911407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5659255981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1231250762939</t>
+    <t xml:space="preserve">16.5138339996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6570892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5659275054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1231269836426</t>
   </si>
   <si>
     <t xml:space="preserve">16.0514965057373</t>
@@ -797,34 +797,34 @@
     <t xml:space="preserve">15.6803274154663</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7454462051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.758469581604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0356616973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.335205078125</t>
+    <t xml:space="preserve">15.7454442977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7584648132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.035662651062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3352031707764</t>
   </si>
   <si>
     <t xml:space="preserve">15.23752784729</t>
   </si>
   <si>
-    <t xml:space="preserve">15.432879447937</t>
+    <t xml:space="preserve">15.4328813552856</t>
   </si>
   <si>
     <t xml:space="preserve">16.2208023071289</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2924346923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1491718292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9538221359253</t>
+    <t xml:space="preserve">16.2924308776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1491737365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9538192749023</t>
   </si>
   <si>
     <t xml:space="preserve">16.1752223968506</t>
@@ -833,76 +833,76 @@
     <t xml:space="preserve">15.8626565933228</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5566034317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.159384727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2245044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8468217849731</t>
+    <t xml:space="preserve">15.5566024780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1593856811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2245054244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8468170166016</t>
   </si>
   <si>
     <t xml:space="preserve">15.1658983230591</t>
   </si>
   <si>
-    <t xml:space="preserve">15.400318145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.309157371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6021842956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6217212677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6738138198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5500917434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3677616119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3938074111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1398487091064</t>
+    <t xml:space="preserve">15.4003219604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.309154510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6021852493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6217203140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6738166809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5500907897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3677635192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3938102722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1398515701294</t>
   </si>
   <si>
     <t xml:space="preserve">15.1072931289673</t>
   </si>
   <si>
-    <t xml:space="preserve">15.081244468689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6152105331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6282291412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5435810089111</t>
+    <t xml:space="preserve">15.0812425613403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6152095794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6282300949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5435771942139</t>
   </si>
   <si>
     <t xml:space="preserve">15.7975368499756</t>
   </si>
   <si>
-    <t xml:space="preserve">15.934287071228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2012691497803</t>
+    <t xml:space="preserve">15.9342832565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2012672424316</t>
   </si>
   <si>
     <t xml:space="preserve">16.4422035217285</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3770847320557</t>
+    <t xml:space="preserve">16.3770866394043</t>
   </si>
   <si>
     <t xml:space="preserve">16.279411315918</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">16.1426620483398</t>
   </si>
   <si>
-    <t xml:space="preserve">16.481273651123</t>
+    <t xml:space="preserve">16.4812755584717</t>
   </si>
   <si>
     <t xml:space="preserve">16.6049957275391</t>
@@ -920,82 +920,82 @@
     <t xml:space="preserve">16.233829498291</t>
   </si>
   <si>
-    <t xml:space="preserve">17.256175994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2691955566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1584987640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1454734802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1845455169678</t>
+    <t xml:space="preserve">17.2561740875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2691974639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1584968566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.145471572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1845436096191</t>
   </si>
   <si>
     <t xml:space="preserve">17.1389617919922</t>
   </si>
   <si>
-    <t xml:space="preserve">17.646879196167</t>
+    <t xml:space="preserve">17.6468811035156</t>
   </si>
   <si>
     <t xml:space="preserve">17.6273460388184</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3892192840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1678199768066</t>
+    <t xml:space="preserve">18.3892211914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1678237915039</t>
   </si>
   <si>
     <t xml:space="preserve">18.1027011871338</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3501510620117</t>
+    <t xml:space="preserve">18.3501491546631</t>
   </si>
   <si>
     <t xml:space="preserve">18.1352634429932</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4934101104736</t>
+    <t xml:space="preserve">18.493408203125</t>
   </si>
   <si>
     <t xml:space="preserve">18.0896797180176</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2264270782471</t>
+    <t xml:space="preserve">18.2264289855957</t>
   </si>
   <si>
     <t xml:space="preserve">18.8588104248047</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8723430633545</t>
+    <t xml:space="preserve">18.8723449707031</t>
   </si>
   <si>
     <t xml:space="preserve">18.6896419525146</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6422729492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5137100219727</t>
+    <t xml:space="preserve">18.642276763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.513708114624</t>
   </si>
   <si>
     <t xml:space="preserve">17.8370380401611</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6543388366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3836708068848</t>
+    <t xml:space="preserve">17.6543369293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3836669921875</t>
   </si>
   <si>
     <t xml:space="preserve">17.9047050476074</t>
   </si>
   <si>
-    <t xml:space="preserve">17.931770324707</t>
+    <t xml:space="preserve">17.9317722320557</t>
   </si>
   <si>
     <t xml:space="preserve">17.5393028259277</t>
@@ -1004,31 +1004,31 @@
     <t xml:space="preserve">17.546070098877</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9926738739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6761074066162</t>
+    <t xml:space="preserve">17.9926719665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6761093139648</t>
   </si>
   <si>
     <t xml:space="preserve">18.9264755249023</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8046741485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9806079864502</t>
+    <t xml:space="preserve">18.8046798706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9806098937988</t>
   </si>
   <si>
     <t xml:space="preserve">18.621976852417</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0400371551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.337776184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2092056274414</t>
+    <t xml:space="preserve">18.0400409698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3377723693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.20920753479</t>
   </si>
   <si>
     <t xml:space="preserve">17.999439239502</t>
@@ -1037,16 +1037,16 @@
     <t xml:space="preserve">17.8641052246094</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8032035827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0062084197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4054412841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0603370666504</t>
+    <t xml:space="preserve">17.803201675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0062026977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4054431915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0603408813477</t>
   </si>
   <si>
     <t xml:space="preserve">17.6340370178223</t>
@@ -1055,28 +1055,28 @@
     <t xml:space="preserve">18.2430381774902</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2701034545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.649040222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.452808380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7031764984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4595775604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1024131774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9467792510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9197120666504</t>
+    <t xml:space="preserve">18.2701072692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6490459442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4528045654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7031745910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4595756530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1024112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.94677734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9197101593018</t>
   </si>
   <si>
     <t xml:space="preserve">18.7776126861572</t>
@@ -1085,19 +1085,19 @@
     <t xml:space="preserve">18.8791103363037</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1362438201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0415096282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1836109161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3730792999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2918796539307</t>
+    <t xml:space="preserve">19.1362457275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0415115356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1836128234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.373083114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2918815612793</t>
   </si>
   <si>
     <t xml:space="preserve">19.8264503479004</t>
@@ -1106,82 +1106,82 @@
     <t xml:space="preserve">19.9414825439453</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3001194000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5166530609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0971164703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9956169128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1241855621338</t>
+    <t xml:space="preserve">20.300121307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5166549682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0971183776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9956150054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1241817474365</t>
   </si>
   <si>
     <t xml:space="preserve">20.1444854736328</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6384525299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2392158508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8941173553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5625476837158</t>
+    <t xml:space="preserve">20.6384544372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2392177581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.894115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5625495910645</t>
   </si>
   <si>
     <t xml:space="preserve">19.7587833404541</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9211864471436</t>
+    <t xml:space="preserve">19.9211826324463</t>
   </si>
   <si>
     <t xml:space="preserve">19.9008827209473</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7993831634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7655467987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.812915802002</t>
+    <t 